--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3241"/>
+  <dimension ref="A1:G3265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80188,7 +80188,7 @@
         <v>2</v>
       </c>
       <c r="G2954" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2955">
@@ -80215,7 +80215,7 @@
         <v>2</v>
       </c>
       <c r="G2955" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2956">
@@ -80226,7 +80226,7 @@
         <v>3</v>
       </c>
       <c r="C2956" t="n">
-        <v>10.29</v>
+        <v>10.28</v>
       </c>
       <c r="D2956" t="inlineStr">
         <is>
@@ -80242,7 +80242,7 @@
         <v>2</v>
       </c>
       <c r="G2956" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2957">
@@ -80269,7 +80269,7 @@
         <v>2</v>
       </c>
       <c r="G2957" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2958">
@@ -80296,7 +80296,7 @@
         <v>2</v>
       </c>
       <c r="G2958" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2959">
@@ -80307,7 +80307,7 @@
         <v>6</v>
       </c>
       <c r="C2959" t="n">
-        <v>15.51</v>
+        <v>15.5</v>
       </c>
       <c r="D2959" t="inlineStr">
         <is>
@@ -80323,7 +80323,7 @@
         <v>2</v>
       </c>
       <c r="G2959" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2960">
@@ -80350,7 +80350,7 @@
         <v>2</v>
       </c>
       <c r="G2960" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2961">
@@ -80377,7 +80377,7 @@
         <v>2</v>
       </c>
       <c r="G2961" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2962">
@@ -80388,7 +80388,7 @@
         <v>9</v>
       </c>
       <c r="C2962" t="n">
-        <v>37.82</v>
+        <v>37.81</v>
       </c>
       <c r="D2962" t="inlineStr">
         <is>
@@ -80404,7 +80404,7 @@
         <v>2</v>
       </c>
       <c r="G2962" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2963">
@@ -80415,7 +80415,7 @@
         <v>10</v>
       </c>
       <c r="C2963" t="n">
-        <v>25.87</v>
+        <v>25.83</v>
       </c>
       <c r="D2963" t="inlineStr">
         <is>
@@ -80431,7 +80431,7 @@
         <v>2</v>
       </c>
       <c r="G2963" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2964">
@@ -80442,7 +80442,7 @@
         <v>11</v>
       </c>
       <c r="C2964" t="n">
-        <v>23.16</v>
+        <v>23.14</v>
       </c>
       <c r="D2964" t="inlineStr">
         <is>
@@ -80458,7 +80458,7 @@
         <v>2</v>
       </c>
       <c r="G2964" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2965">
@@ -80469,7 +80469,7 @@
         <v>12</v>
       </c>
       <c r="C2965" t="n">
-        <v>25.85</v>
+        <v>25.83</v>
       </c>
       <c r="D2965" t="inlineStr">
         <is>
@@ -80485,7 +80485,7 @@
         <v>2</v>
       </c>
       <c r="G2965" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2966">
@@ -80496,7 +80496,7 @@
         <v>13</v>
       </c>
       <c r="C2966" t="n">
-        <v>26.53</v>
+        <v>26.51</v>
       </c>
       <c r="D2966" t="inlineStr">
         <is>
@@ -80512,7 +80512,7 @@
         <v>2</v>
       </c>
       <c r="G2966" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2967">
@@ -80523,7 +80523,7 @@
         <v>14</v>
       </c>
       <c r="C2967" t="n">
-        <v>27.03</v>
+        <v>27.01</v>
       </c>
       <c r="D2967" t="inlineStr">
         <is>
@@ -80539,7 +80539,7 @@
         <v>2</v>
       </c>
       <c r="G2967" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2968">
@@ -80566,7 +80566,7 @@
         <v>2</v>
       </c>
       <c r="G2968" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2969">
@@ -80593,7 +80593,7 @@
         <v>2</v>
       </c>
       <c r="G2969" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2970">
@@ -80604,7 +80604,7 @@
         <v>17</v>
       </c>
       <c r="C2970" t="n">
-        <v>36.07</v>
+        <v>36.05</v>
       </c>
       <c r="D2970" t="inlineStr">
         <is>
@@ -80620,7 +80620,7 @@
         <v>2</v>
       </c>
       <c r="G2970" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2971">
@@ -80647,7 +80647,7 @@
         <v>2</v>
       </c>
       <c r="G2971" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2972">
@@ -80658,7 +80658,7 @@
         <v>19</v>
       </c>
       <c r="C2972" t="n">
-        <v>21.73</v>
+        <v>21.76</v>
       </c>
       <c r="D2972" t="inlineStr">
         <is>
@@ -80674,7 +80674,7 @@
         <v>2</v>
       </c>
       <c r="G2972" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2973">
@@ -80701,7 +80701,7 @@
         <v>2</v>
       </c>
       <c r="G2973" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2974">
@@ -80728,7 +80728,7 @@
         <v>2</v>
       </c>
       <c r="G2974" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2975">
@@ -80755,7 +80755,7 @@
         <v>2</v>
       </c>
       <c r="G2975" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2976">
@@ -80782,7 +80782,7 @@
         <v>2</v>
       </c>
       <c r="G2976" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2977">
@@ -80809,7 +80809,7 @@
         <v>2</v>
       </c>
       <c r="G2977" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2978">
@@ -80836,7 +80836,7 @@
         <v>2</v>
       </c>
       <c r="G2978" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2979">
@@ -80847,7 +80847,7 @@
         <v>2</v>
       </c>
       <c r="C2979" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="D2979" t="inlineStr">
         <is>
@@ -80863,7 +80863,7 @@
         <v>2</v>
       </c>
       <c r="G2979" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2980">
@@ -80890,7 +80890,7 @@
         <v>2</v>
       </c>
       <c r="G2980" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2981">
@@ -80917,7 +80917,7 @@
         <v>2</v>
       </c>
       <c r="G2981" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2982">
@@ -80928,7 +80928,7 @@
         <v>5</v>
       </c>
       <c r="C2982" t="n">
-        <v>8.68</v>
+        <v>8.67</v>
       </c>
       <c r="D2982" t="inlineStr">
         <is>
@@ -80944,7 +80944,7 @@
         <v>2</v>
       </c>
       <c r="G2982" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2983">
@@ -80971,7 +80971,7 @@
         <v>2</v>
       </c>
       <c r="G2983" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2984">
@@ -80982,7 +80982,7 @@
         <v>7</v>
       </c>
       <c r="C2984" t="n">
-        <v>27.44</v>
+        <v>27.43</v>
       </c>
       <c r="D2984" t="inlineStr">
         <is>
@@ -80998,7 +80998,7 @@
         <v>2</v>
       </c>
       <c r="G2984" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2985">
@@ -81025,7 +81025,7 @@
         <v>2</v>
       </c>
       <c r="G2985" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2986">
@@ -81036,7 +81036,7 @@
         <v>9</v>
       </c>
       <c r="C2986" t="n">
-        <v>41.61</v>
+        <v>41.6</v>
       </c>
       <c r="D2986" t="inlineStr">
         <is>
@@ -81052,7 +81052,7 @@
         <v>2</v>
       </c>
       <c r="G2986" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2987">
@@ -81063,7 +81063,7 @@
         <v>10</v>
       </c>
       <c r="C2987" t="n">
-        <v>17.66</v>
+        <v>17.67</v>
       </c>
       <c r="D2987" t="inlineStr">
         <is>
@@ -81079,7 +81079,7 @@
         <v>2</v>
       </c>
       <c r="G2987" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2988">
@@ -81090,7 +81090,7 @@
         <v>11</v>
       </c>
       <c r="C2988" t="n">
-        <v>19.71</v>
+        <v>19.72</v>
       </c>
       <c r="D2988" t="inlineStr">
         <is>
@@ -81106,7 +81106,7 @@
         <v>2</v>
       </c>
       <c r="G2988" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2989">
@@ -81133,7 +81133,7 @@
         <v>2</v>
       </c>
       <c r="G2989" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2990">
@@ -81144,7 +81144,7 @@
         <v>13</v>
       </c>
       <c r="C2990" t="n">
-        <v>31.86</v>
+        <v>31.85</v>
       </c>
       <c r="D2990" t="inlineStr">
         <is>
@@ -81160,7 +81160,7 @@
         <v>2</v>
       </c>
       <c r="G2990" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2991">
@@ -81187,7 +81187,7 @@
         <v>2</v>
       </c>
       <c r="G2991" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2992">
@@ -81198,7 +81198,7 @@
         <v>15</v>
       </c>
       <c r="C2992" t="n">
-        <v>31.53</v>
+        <v>31.52</v>
       </c>
       <c r="D2992" t="inlineStr">
         <is>
@@ -81214,7 +81214,7 @@
         <v>2</v>
       </c>
       <c r="G2992" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2993">
@@ -81225,7 +81225,7 @@
         <v>16</v>
       </c>
       <c r="C2993" t="n">
-        <v>34.15</v>
+        <v>34.14</v>
       </c>
       <c r="D2993" t="inlineStr">
         <is>
@@ -81241,7 +81241,7 @@
         <v>2</v>
       </c>
       <c r="G2993" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2994">
@@ -81268,7 +81268,7 @@
         <v>2</v>
       </c>
       <c r="G2994" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2995">
@@ -81279,7 +81279,7 @@
         <v>18</v>
       </c>
       <c r="C2995" t="n">
-        <v>25.28</v>
+        <v>25.27</v>
       </c>
       <c r="D2995" t="inlineStr">
         <is>
@@ -81295,7 +81295,7 @@
         <v>2</v>
       </c>
       <c r="G2995" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2996">
@@ -81306,7 +81306,7 @@
         <v>19</v>
       </c>
       <c r="C2996" t="n">
-        <v>20.13</v>
+        <v>20.12</v>
       </c>
       <c r="D2996" t="inlineStr">
         <is>
@@ -81322,7 +81322,7 @@
         <v>2</v>
       </c>
       <c r="G2996" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2997">
@@ -81333,7 +81333,7 @@
         <v>20</v>
       </c>
       <c r="C2997" t="n">
-        <v>24.85</v>
+        <v>24.84</v>
       </c>
       <c r="D2997" t="inlineStr">
         <is>
@@ -81349,7 +81349,7 @@
         <v>2</v>
       </c>
       <c r="G2997" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2998">
@@ -81376,7 +81376,7 @@
         <v>2</v>
       </c>
       <c r="G2998" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="2999">
@@ -81403,7 +81403,7 @@
         <v>2</v>
       </c>
       <c r="G2999" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3000">
@@ -81430,7 +81430,7 @@
         <v>2</v>
       </c>
       <c r="G3000" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3001">
@@ -81441,7 +81441,7 @@
         <v>24</v>
       </c>
       <c r="C3001" t="n">
-        <v>25.33</v>
+        <v>25.32</v>
       </c>
       <c r="D3001" t="inlineStr">
         <is>
@@ -81457,7 +81457,7 @@
         <v>2</v>
       </c>
       <c r="G3001" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3002">
@@ -81484,7 +81484,7 @@
         <v>2</v>
       </c>
       <c r="G3002" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3003">
@@ -81511,7 +81511,7 @@
         <v>2</v>
       </c>
       <c r="G3003" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3004">
@@ -81522,7 +81522,7 @@
         <v>3</v>
       </c>
       <c r="C3004" t="n">
-        <v>12.65</v>
+        <v>12.64</v>
       </c>
       <c r="D3004" t="inlineStr">
         <is>
@@ -81538,7 +81538,7 @@
         <v>2</v>
       </c>
       <c r="G3004" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3005">
@@ -81549,7 +81549,7 @@
         <v>4</v>
       </c>
       <c r="C3005" t="n">
-        <v>13.39</v>
+        <v>13.38</v>
       </c>
       <c r="D3005" t="inlineStr">
         <is>
@@ -81565,7 +81565,7 @@
         <v>2</v>
       </c>
       <c r="G3005" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3006">
@@ -81592,7 +81592,7 @@
         <v>2</v>
       </c>
       <c r="G3006" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3007">
@@ -81619,7 +81619,7 @@
         <v>2</v>
       </c>
       <c r="G3007" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3008">
@@ -81646,7 +81646,7 @@
         <v>2</v>
       </c>
       <c r="G3008" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3009">
@@ -81657,7 +81657,7 @@
         <v>8</v>
       </c>
       <c r="C3009" t="n">
-        <v>50.35</v>
+        <v>50.34</v>
       </c>
       <c r="D3009" t="inlineStr">
         <is>
@@ -81673,7 +81673,7 @@
         <v>2</v>
       </c>
       <c r="G3009" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3010">
@@ -81684,7 +81684,7 @@
         <v>9</v>
       </c>
       <c r="C3010" t="n">
-        <v>52.81</v>
+        <v>52.79</v>
       </c>
       <c r="D3010" t="inlineStr">
         <is>
@@ -81700,7 +81700,7 @@
         <v>2</v>
       </c>
       <c r="G3010" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3011">
@@ -81711,7 +81711,7 @@
         <v>10</v>
       </c>
       <c r="C3011" t="n">
-        <v>24.94</v>
+        <v>24.88</v>
       </c>
       <c r="D3011" t="inlineStr">
         <is>
@@ -81727,7 +81727,7 @@
         <v>2</v>
       </c>
       <c r="G3011" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3012">
@@ -81754,7 +81754,7 @@
         <v>2</v>
       </c>
       <c r="G3012" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3013">
@@ -81765,7 +81765,7 @@
         <v>12</v>
       </c>
       <c r="C3013" t="n">
-        <v>21.09</v>
+        <v>21.06</v>
       </c>
       <c r="D3013" t="inlineStr">
         <is>
@@ -81781,7 +81781,7 @@
         <v>2</v>
       </c>
       <c r="G3013" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3014">
@@ -81792,7 +81792,7 @@
         <v>13</v>
       </c>
       <c r="C3014" t="n">
-        <v>23.51</v>
+        <v>23.56</v>
       </c>
       <c r="D3014" t="inlineStr">
         <is>
@@ -81808,7 +81808,7 @@
         <v>2</v>
       </c>
       <c r="G3014" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3015">
@@ -81819,7 +81819,7 @@
         <v>14</v>
       </c>
       <c r="C3015" t="n">
-        <v>22.71</v>
+        <v>22.7</v>
       </c>
       <c r="D3015" t="inlineStr">
         <is>
@@ -81835,7 +81835,7 @@
         <v>2</v>
       </c>
       <c r="G3015" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3016">
@@ -81862,7 +81862,7 @@
         <v>2</v>
       </c>
       <c r="G3016" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3017">
@@ -81873,7 +81873,7 @@
         <v>16</v>
       </c>
       <c r="C3017" t="n">
-        <v>23.42</v>
+        <v>23.48</v>
       </c>
       <c r="D3017" t="inlineStr">
         <is>
@@ -81889,7 +81889,7 @@
         <v>2</v>
       </c>
       <c r="G3017" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3018">
@@ -81900,7 +81900,7 @@
         <v>17</v>
       </c>
       <c r="C3018" t="n">
-        <v>22.75</v>
+        <v>22.76</v>
       </c>
       <c r="D3018" t="inlineStr">
         <is>
@@ -81916,7 +81916,7 @@
         <v>2</v>
       </c>
       <c r="G3018" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3019">
@@ -81927,7 +81927,7 @@
         <v>18</v>
       </c>
       <c r="C3019" t="n">
-        <v>21.24</v>
+        <v>21.22</v>
       </c>
       <c r="D3019" t="inlineStr">
         <is>
@@ -81943,7 +81943,7 @@
         <v>2</v>
       </c>
       <c r="G3019" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3020">
@@ -81954,7 +81954,7 @@
         <v>19</v>
       </c>
       <c r="C3020" t="n">
-        <v>23.58</v>
+        <v>23.57</v>
       </c>
       <c r="D3020" t="inlineStr">
         <is>
@@ -81970,7 +81970,7 @@
         <v>2</v>
       </c>
       <c r="G3020" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3021">
@@ -81981,7 +81981,7 @@
         <v>20</v>
       </c>
       <c r="C3021" t="n">
-        <v>36.49</v>
+        <v>36.48</v>
       </c>
       <c r="D3021" t="inlineStr">
         <is>
@@ -81997,7 +81997,7 @@
         <v>2</v>
       </c>
       <c r="G3021" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3022">
@@ -82024,7 +82024,7 @@
         <v>2</v>
       </c>
       <c r="G3022" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3023">
@@ -82051,7 +82051,7 @@
         <v>2</v>
       </c>
       <c r="G3023" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3024">
@@ -82078,7 +82078,7 @@
         <v>2</v>
       </c>
       <c r="G3024" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3025">
@@ -82105,7 +82105,7 @@
         <v>2</v>
       </c>
       <c r="G3025" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3026">
@@ -82132,7 +82132,7 @@
         <v>2</v>
       </c>
       <c r="G3026" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3027">
@@ -82159,7 +82159,7 @@
         <v>2</v>
       </c>
       <c r="G3027" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3028">
@@ -82186,7 +82186,7 @@
         <v>2</v>
       </c>
       <c r="G3028" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3029">
@@ -82213,7 +82213,7 @@
         <v>2</v>
       </c>
       <c r="G3029" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3030">
@@ -82240,7 +82240,7 @@
         <v>2</v>
       </c>
       <c r="G3030" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3031">
@@ -82267,7 +82267,7 @@
         <v>2</v>
       </c>
       <c r="G3031" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3032">
@@ -82294,7 +82294,7 @@
         <v>2</v>
       </c>
       <c r="G3032" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3033">
@@ -82321,7 +82321,7 @@
         <v>2</v>
       </c>
       <c r="G3033" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3034">
@@ -82332,7 +82332,7 @@
         <v>9</v>
       </c>
       <c r="C3034" t="n">
-        <v>49.15</v>
+        <v>49.14</v>
       </c>
       <c r="D3034" t="inlineStr">
         <is>
@@ -82348,7 +82348,7 @@
         <v>2</v>
       </c>
       <c r="G3034" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3035">
@@ -82359,7 +82359,7 @@
         <v>10</v>
       </c>
       <c r="C3035" t="n">
-        <v>24.35</v>
+        <v>24.28</v>
       </c>
       <c r="D3035" t="inlineStr">
         <is>
@@ -82375,7 +82375,7 @@
         <v>2</v>
       </c>
       <c r="G3035" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3036">
@@ -82386,7 +82386,7 @@
         <v>11</v>
       </c>
       <c r="C3036" t="n">
-        <v>21.25</v>
+        <v>21.29</v>
       </c>
       <c r="D3036" t="inlineStr">
         <is>
@@ -82402,7 +82402,7 @@
         <v>2</v>
       </c>
       <c r="G3036" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3037">
@@ -82413,7 +82413,7 @@
         <v>12</v>
       </c>
       <c r="C3037" t="n">
-        <v>16.36</v>
+        <v>16.35</v>
       </c>
       <c r="D3037" t="inlineStr">
         <is>
@@ -82429,7 +82429,7 @@
         <v>2</v>
       </c>
       <c r="G3037" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3038">
@@ -82440,7 +82440,7 @@
         <v>13</v>
       </c>
       <c r="C3038" t="n">
-        <v>15.52</v>
+        <v>15.53</v>
       </c>
       <c r="D3038" t="inlineStr">
         <is>
@@ -82456,7 +82456,7 @@
         <v>2</v>
       </c>
       <c r="G3038" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3039">
@@ -82483,7 +82483,7 @@
         <v>2</v>
       </c>
       <c r="G3039" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3040">
@@ -82510,7 +82510,7 @@
         <v>2</v>
       </c>
       <c r="G3040" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3041">
@@ -82521,7 +82521,7 @@
         <v>16</v>
       </c>
       <c r="C3041" t="n">
-        <v>12.66</v>
+        <v>12.67</v>
       </c>
       <c r="D3041" t="inlineStr">
         <is>
@@ -82537,7 +82537,7 @@
         <v>2</v>
       </c>
       <c r="G3041" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3042">
@@ -82548,7 +82548,7 @@
         <v>17</v>
       </c>
       <c r="C3042" t="n">
-        <v>13.59</v>
+        <v>13.6</v>
       </c>
       <c r="D3042" t="inlineStr">
         <is>
@@ -82564,7 +82564,7 @@
         <v>2</v>
       </c>
       <c r="G3042" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3043">
@@ -82591,7 +82591,7 @@
         <v>2</v>
       </c>
       <c r="G3043" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3044">
@@ -82618,7 +82618,7 @@
         <v>2</v>
       </c>
       <c r="G3044" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3045">
@@ -82629,7 +82629,7 @@
         <v>20</v>
       </c>
       <c r="C3045" t="n">
-        <v>27.97</v>
+        <v>27.96</v>
       </c>
       <c r="D3045" t="inlineStr">
         <is>
@@ -82645,7 +82645,7 @@
         <v>2</v>
       </c>
       <c r="G3045" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3046">
@@ -82656,7 +82656,7 @@
         <v>21</v>
       </c>
       <c r="C3046" t="n">
-        <v>29.77</v>
+        <v>29.76</v>
       </c>
       <c r="D3046" t="inlineStr">
         <is>
@@ -82672,7 +82672,7 @@
         <v>2</v>
       </c>
       <c r="G3046" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3047">
@@ -82683,7 +82683,7 @@
         <v>22</v>
       </c>
       <c r="C3047" t="n">
-        <v>38.09</v>
+        <v>38.08</v>
       </c>
       <c r="D3047" t="inlineStr">
         <is>
@@ -82699,7 +82699,7 @@
         <v>2</v>
       </c>
       <c r="G3047" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3048">
@@ -82710,7 +82710,7 @@
         <v>23</v>
       </c>
       <c r="C3048" t="n">
-        <v>42.08</v>
+        <v>42.07</v>
       </c>
       <c r="D3048" t="inlineStr">
         <is>
@@ -82726,7 +82726,7 @@
         <v>2</v>
       </c>
       <c r="G3048" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3049">
@@ -82737,7 +82737,7 @@
         <v>24</v>
       </c>
       <c r="C3049" t="n">
-        <v>32.44</v>
+        <v>32.43</v>
       </c>
       <c r="D3049" t="inlineStr">
         <is>
@@ -82753,7 +82753,7 @@
         <v>2</v>
       </c>
       <c r="G3049" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3050">
@@ -82780,7 +82780,7 @@
         <v>2</v>
       </c>
       <c r="G3050" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3051">
@@ -82807,7 +82807,7 @@
         <v>2</v>
       </c>
       <c r="G3051" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3052">
@@ -82818,7 +82818,7 @@
         <v>3</v>
       </c>
       <c r="C3052" t="n">
-        <v>12.02</v>
+        <v>12.01</v>
       </c>
       <c r="D3052" t="inlineStr">
         <is>
@@ -82834,7 +82834,7 @@
         <v>2</v>
       </c>
       <c r="G3052" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3053">
@@ -82861,7 +82861,7 @@
         <v>2</v>
       </c>
       <c r="G3053" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3054">
@@ -82888,7 +82888,7 @@
         <v>2</v>
       </c>
       <c r="G3054" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3055">
@@ -82915,7 +82915,7 @@
         <v>2</v>
       </c>
       <c r="G3055" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3056">
@@ -82942,7 +82942,7 @@
         <v>2</v>
       </c>
       <c r="G3056" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3057">
@@ -82953,7 +82953,7 @@
         <v>8</v>
       </c>
       <c r="C3057" t="n">
-        <v>30.96</v>
+        <v>30.95</v>
       </c>
       <c r="D3057" t="inlineStr">
         <is>
@@ -82969,7 +82969,7 @@
         <v>2</v>
       </c>
       <c r="G3057" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3058">
@@ -82980,7 +82980,7 @@
         <v>9</v>
       </c>
       <c r="C3058" t="n">
-        <v>36</v>
+        <v>35.99</v>
       </c>
       <c r="D3058" t="inlineStr">
         <is>
@@ -82996,7 +82996,7 @@
         <v>2</v>
       </c>
       <c r="G3058" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3059">
@@ -83007,7 +83007,7 @@
         <v>10</v>
       </c>
       <c r="C3059" t="n">
-        <v>31.88</v>
+        <v>31.87</v>
       </c>
       <c r="D3059" t="inlineStr">
         <is>
@@ -83023,7 +83023,7 @@
         <v>2</v>
       </c>
       <c r="G3059" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3060">
@@ -83034,7 +83034,7 @@
         <v>11</v>
       </c>
       <c r="C3060" t="n">
-        <v>18.49</v>
+        <v>18.46</v>
       </c>
       <c r="D3060" t="inlineStr">
         <is>
@@ -83050,7 +83050,7 @@
         <v>2</v>
       </c>
       <c r="G3060" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3061">
@@ -83061,7 +83061,7 @@
         <v>12</v>
       </c>
       <c r="C3061" t="n">
-        <v>14.95</v>
+        <v>14.93</v>
       </c>
       <c r="D3061" t="inlineStr">
         <is>
@@ -83077,7 +83077,7 @@
         <v>2</v>
       </c>
       <c r="G3061" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3062">
@@ -83088,7 +83088,7 @@
         <v>13</v>
       </c>
       <c r="C3062" t="n">
-        <v>14.13</v>
+        <v>14.12</v>
       </c>
       <c r="D3062" t="inlineStr">
         <is>
@@ -83104,7 +83104,7 @@
         <v>2</v>
       </c>
       <c r="G3062" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3063">
@@ -83115,7 +83115,7 @@
         <v>14</v>
       </c>
       <c r="C3063" t="n">
-        <v>14.31</v>
+        <v>14.3</v>
       </c>
       <c r="D3063" t="inlineStr">
         <is>
@@ -83131,7 +83131,7 @@
         <v>2</v>
       </c>
       <c r="G3063" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3064">
@@ -83142,7 +83142,7 @@
         <v>15</v>
       </c>
       <c r="C3064" t="n">
-        <v>17.63</v>
+        <v>17.62</v>
       </c>
       <c r="D3064" t="inlineStr">
         <is>
@@ -83158,7 +83158,7 @@
         <v>2</v>
       </c>
       <c r="G3064" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3065">
@@ -83185,7 +83185,7 @@
         <v>2</v>
       </c>
       <c r="G3065" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3066">
@@ -83196,7 +83196,7 @@
         <v>17</v>
       </c>
       <c r="C3066" t="n">
-        <v>14.89</v>
+        <v>14.87</v>
       </c>
       <c r="D3066" t="inlineStr">
         <is>
@@ -83212,7 +83212,7 @@
         <v>2</v>
       </c>
       <c r="G3066" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3067">
@@ -83223,7 +83223,7 @@
         <v>18</v>
       </c>
       <c r="C3067" t="n">
-        <v>12.1</v>
+        <v>12.07</v>
       </c>
       <c r="D3067" t="inlineStr">
         <is>
@@ -83239,7 +83239,7 @@
         <v>2</v>
       </c>
       <c r="G3067" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3068">
@@ -83250,7 +83250,7 @@
         <v>19</v>
       </c>
       <c r="C3068" t="n">
-        <v>30.12</v>
+        <v>30.09</v>
       </c>
       <c r="D3068" t="inlineStr">
         <is>
@@ -83266,7 +83266,7 @@
         <v>2</v>
       </c>
       <c r="G3068" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3069">
@@ -83277,7 +83277,7 @@
         <v>20</v>
       </c>
       <c r="C3069" t="n">
-        <v>37.64</v>
+        <v>37.63</v>
       </c>
       <c r="D3069" t="inlineStr">
         <is>
@@ -83293,7 +83293,7 @@
         <v>2</v>
       </c>
       <c r="G3069" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3070">
@@ -83304,7 +83304,7 @@
         <v>21</v>
       </c>
       <c r="C3070" t="n">
-        <v>36.86</v>
+        <v>36.85</v>
       </c>
       <c r="D3070" t="inlineStr">
         <is>
@@ -83320,7 +83320,7 @@
         <v>2</v>
       </c>
       <c r="G3070" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3071">
@@ -83331,7 +83331,7 @@
         <v>22</v>
       </c>
       <c r="C3071" t="n">
-        <v>25.69</v>
+        <v>25.68</v>
       </c>
       <c r="D3071" t="inlineStr">
         <is>
@@ -83347,7 +83347,7 @@
         <v>2</v>
       </c>
       <c r="G3071" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3072">
@@ -83374,7 +83374,7 @@
         <v>2</v>
       </c>
       <c r="G3072" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3073">
@@ -83401,7 +83401,7 @@
         <v>2</v>
       </c>
       <c r="G3073" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3074">
@@ -83412,7 +83412,7 @@
         <v>1</v>
       </c>
       <c r="C3074" t="n">
-        <v>8.6</v>
+        <v>8.65</v>
       </c>
       <c r="D3074" t="inlineStr">
         <is>
@@ -83428,7 +83428,7 @@
         <v>2</v>
       </c>
       <c r="G3074" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3075">
@@ -83439,7 +83439,7 @@
         <v>2</v>
       </c>
       <c r="C3075" t="n">
-        <v>8.59</v>
+        <v>8.65</v>
       </c>
       <c r="D3075" t="inlineStr">
         <is>
@@ -83455,7 +83455,7 @@
         <v>2</v>
       </c>
       <c r="G3075" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3076">
@@ -83466,7 +83466,7 @@
         <v>3</v>
       </c>
       <c r="C3076" t="n">
-        <v>8.23</v>
+        <v>8.34</v>
       </c>
       <c r="D3076" t="inlineStr">
         <is>
@@ -83482,7 +83482,7 @@
         <v>2</v>
       </c>
       <c r="G3076" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3077">
@@ -83493,7 +83493,7 @@
         <v>4</v>
       </c>
       <c r="C3077" t="n">
-        <v>8.619999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="D3077" t="inlineStr">
         <is>
@@ -83509,7 +83509,7 @@
         <v>2</v>
       </c>
       <c r="G3077" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3078">
@@ -83520,7 +83520,7 @@
         <v>5</v>
       </c>
       <c r="C3078" t="n">
-        <v>10.96</v>
+        <v>10.9</v>
       </c>
       <c r="D3078" t="inlineStr">
         <is>
@@ -83536,7 +83536,7 @@
         <v>2</v>
       </c>
       <c r="G3078" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3079">
@@ -83547,7 +83547,7 @@
         <v>6</v>
       </c>
       <c r="C3079" t="n">
-        <v>11.29</v>
+        <v>11.21</v>
       </c>
       <c r="D3079" t="inlineStr">
         <is>
@@ -83563,7 +83563,7 @@
         <v>2</v>
       </c>
       <c r="G3079" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3080">
@@ -83574,7 +83574,7 @@
         <v>7</v>
       </c>
       <c r="C3080" t="n">
-        <v>14.75</v>
+        <v>14.73</v>
       </c>
       <c r="D3080" t="inlineStr">
         <is>
@@ -83590,7 +83590,7 @@
         <v>2</v>
       </c>
       <c r="G3080" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3081">
@@ -83601,7 +83601,7 @@
         <v>8</v>
       </c>
       <c r="C3081" t="n">
-        <v>24.76</v>
+        <v>24.69</v>
       </c>
       <c r="D3081" t="inlineStr">
         <is>
@@ -83617,7 +83617,7 @@
         <v>2</v>
       </c>
       <c r="G3081" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3082">
@@ -83628,7 +83628,7 @@
         <v>9</v>
       </c>
       <c r="C3082" t="n">
-        <v>25.96</v>
+        <v>25.83</v>
       </c>
       <c r="D3082" t="inlineStr">
         <is>
@@ -83644,7 +83644,7 @@
         <v>2</v>
       </c>
       <c r="G3082" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3083">
@@ -83655,7 +83655,7 @@
         <v>10</v>
       </c>
       <c r="C3083" t="n">
-        <v>24.15</v>
+        <v>24.19</v>
       </c>
       <c r="D3083" t="inlineStr">
         <is>
@@ -83671,7 +83671,7 @@
         <v>2</v>
       </c>
       <c r="G3083" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3084">
@@ -83682,7 +83682,7 @@
         <v>11</v>
       </c>
       <c r="C3084" t="n">
-        <v>21.25</v>
+        <v>21.19</v>
       </c>
       <c r="D3084" t="inlineStr">
         <is>
@@ -83698,7 +83698,7 @@
         <v>2</v>
       </c>
       <c r="G3084" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3085">
@@ -83725,7 +83725,7 @@
         <v>2</v>
       </c>
       <c r="G3085" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3086">
@@ -83736,7 +83736,7 @@
         <v>13</v>
       </c>
       <c r="C3086" t="n">
-        <v>22.48</v>
+        <v>22.47</v>
       </c>
       <c r="D3086" t="inlineStr">
         <is>
@@ -83752,7 +83752,7 @@
         <v>2</v>
       </c>
       <c r="G3086" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3087">
@@ -83763,7 +83763,7 @@
         <v>14</v>
       </c>
       <c r="C3087" t="n">
-        <v>21.49</v>
+        <v>21.51</v>
       </c>
       <c r="D3087" t="inlineStr">
         <is>
@@ -83779,7 +83779,7 @@
         <v>2</v>
       </c>
       <c r="G3087" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3088">
@@ -83790,7 +83790,7 @@
         <v>15</v>
       </c>
       <c r="C3088" t="n">
-        <v>20.87</v>
+        <v>20.88</v>
       </c>
       <c r="D3088" t="inlineStr">
         <is>
@@ -83806,7 +83806,7 @@
         <v>2</v>
       </c>
       <c r="G3088" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3089">
@@ -83833,7 +83833,7 @@
         <v>2</v>
       </c>
       <c r="G3089" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3090">
@@ -83844,7 +83844,7 @@
         <v>17</v>
       </c>
       <c r="C3090" t="n">
-        <v>24.11</v>
+        <v>24.07</v>
       </c>
       <c r="D3090" t="inlineStr">
         <is>
@@ -83860,7 +83860,7 @@
         <v>2</v>
       </c>
       <c r="G3090" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3091">
@@ -83871,7 +83871,7 @@
         <v>18</v>
       </c>
       <c r="C3091" t="n">
-        <v>22.76</v>
+        <v>22.69</v>
       </c>
       <c r="D3091" t="inlineStr">
         <is>
@@ -83887,7 +83887,7 @@
         <v>2</v>
       </c>
       <c r="G3091" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3092">
@@ -83898,7 +83898,7 @@
         <v>19</v>
       </c>
       <c r="C3092" t="n">
-        <v>30.98</v>
+        <v>30.91</v>
       </c>
       <c r="D3092" t="inlineStr">
         <is>
@@ -83914,7 +83914,7 @@
         <v>2</v>
       </c>
       <c r="G3092" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3093">
@@ -83925,7 +83925,7 @@
         <v>20</v>
       </c>
       <c r="C3093" t="n">
-        <v>29.21</v>
+        <v>29.34</v>
       </c>
       <c r="D3093" t="inlineStr">
         <is>
@@ -83941,7 +83941,7 @@
         <v>2</v>
       </c>
       <c r="G3093" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3094">
@@ -83952,7 +83952,7 @@
         <v>21</v>
       </c>
       <c r="C3094" t="n">
-        <v>38.08</v>
+        <v>38</v>
       </c>
       <c r="D3094" t="inlineStr">
         <is>
@@ -83968,7 +83968,7 @@
         <v>2</v>
       </c>
       <c r="G3094" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3095">
@@ -83979,7 +83979,7 @@
         <v>22</v>
       </c>
       <c r="C3095" t="n">
-        <v>37</v>
+        <v>37.11</v>
       </c>
       <c r="D3095" t="inlineStr">
         <is>
@@ -83995,7 +83995,7 @@
         <v>2</v>
       </c>
       <c r="G3095" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3096">
@@ -84006,7 +84006,7 @@
         <v>23</v>
       </c>
       <c r="C3096" t="n">
-        <v>21.89</v>
+        <v>21.84</v>
       </c>
       <c r="D3096" t="inlineStr">
         <is>
@@ -84022,7 +84022,7 @@
         <v>2</v>
       </c>
       <c r="G3096" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3097">
@@ -84033,7 +84033,7 @@
         <v>24</v>
       </c>
       <c r="C3097" t="n">
-        <v>24.48</v>
+        <v>24.56</v>
       </c>
       <c r="D3097" t="inlineStr">
         <is>
@@ -84049,7 +84049,7 @@
         <v>2</v>
       </c>
       <c r="G3097" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3098">
@@ -84076,7 +84076,7 @@
         <v>2</v>
       </c>
       <c r="G3098" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3099">
@@ -84103,7 +84103,7 @@
         <v>2</v>
       </c>
       <c r="G3099" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3100">
@@ -84130,7 +84130,7 @@
         <v>2</v>
       </c>
       <c r="G3100" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3101">
@@ -84157,7 +84157,7 @@
         <v>2</v>
       </c>
       <c r="G3101" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3102">
@@ -84184,7 +84184,7 @@
         <v>2</v>
       </c>
       <c r="G3102" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3103">
@@ -84211,7 +84211,7 @@
         <v>2</v>
       </c>
       <c r="G3103" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3104">
@@ -84238,7 +84238,7 @@
         <v>2</v>
       </c>
       <c r="G3104" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3105">
@@ -84249,7 +84249,7 @@
         <v>8</v>
       </c>
       <c r="C3105" t="n">
-        <v>50.38</v>
+        <v>50.37</v>
       </c>
       <c r="D3105" t="inlineStr">
         <is>
@@ -84265,7 +84265,7 @@
         <v>2</v>
       </c>
       <c r="G3105" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3106">
@@ -84276,7 +84276,7 @@
         <v>9</v>
       </c>
       <c r="C3106" t="n">
-        <v>50.21</v>
+        <v>50.2</v>
       </c>
       <c r="D3106" t="inlineStr">
         <is>
@@ -84292,7 +84292,7 @@
         <v>2</v>
       </c>
       <c r="G3106" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3107">
@@ -84303,7 +84303,7 @@
         <v>10</v>
       </c>
       <c r="C3107" t="n">
-        <v>22.74</v>
+        <v>22.76</v>
       </c>
       <c r="D3107" t="inlineStr">
         <is>
@@ -84319,7 +84319,7 @@
         <v>2</v>
       </c>
       <c r="G3107" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3108">
@@ -84330,7 +84330,7 @@
         <v>11</v>
       </c>
       <c r="C3108" t="n">
-        <v>18.02</v>
+        <v>18.06</v>
       </c>
       <c r="D3108" t="inlineStr">
         <is>
@@ -84346,7 +84346,7 @@
         <v>2</v>
       </c>
       <c r="G3108" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3109">
@@ -84357,7 +84357,7 @@
         <v>12</v>
       </c>
       <c r="C3109" t="n">
-        <v>20.35</v>
+        <v>20.39</v>
       </c>
       <c r="D3109" t="inlineStr">
         <is>
@@ -84373,7 +84373,7 @@
         <v>2</v>
       </c>
       <c r="G3109" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3110">
@@ -84384,7 +84384,7 @@
         <v>13</v>
       </c>
       <c r="C3110" t="n">
-        <v>21.73</v>
+        <v>21.74</v>
       </c>
       <c r="D3110" t="inlineStr">
         <is>
@@ -84400,7 +84400,7 @@
         <v>2</v>
       </c>
       <c r="G3110" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3111">
@@ -84411,7 +84411,7 @@
         <v>14</v>
       </c>
       <c r="C3111" t="n">
-        <v>21.66</v>
+        <v>21.71</v>
       </c>
       <c r="D3111" t="inlineStr">
         <is>
@@ -84427,7 +84427,7 @@
         <v>2</v>
       </c>
       <c r="G3111" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3112">
@@ -84438,7 +84438,7 @@
         <v>15</v>
       </c>
       <c r="C3112" t="n">
-        <v>22.82</v>
+        <v>22.86</v>
       </c>
       <c r="D3112" t="inlineStr">
         <is>
@@ -84454,7 +84454,7 @@
         <v>2</v>
       </c>
       <c r="G3112" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3113">
@@ -84465,7 +84465,7 @@
         <v>16</v>
       </c>
       <c r="C3113" t="n">
-        <v>23.48</v>
+        <v>23.52</v>
       </c>
       <c r="D3113" t="inlineStr">
         <is>
@@ -84481,7 +84481,7 @@
         <v>2</v>
       </c>
       <c r="G3113" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3114">
@@ -84492,7 +84492,7 @@
         <v>17</v>
       </c>
       <c r="C3114" t="n">
-        <v>22.79</v>
+        <v>22.78</v>
       </c>
       <c r="D3114" t="inlineStr">
         <is>
@@ -84508,7 +84508,7 @@
         <v>2</v>
       </c>
       <c r="G3114" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3115">
@@ -84519,7 +84519,7 @@
         <v>18</v>
       </c>
       <c r="C3115" t="n">
-        <v>21.19</v>
+        <v>21.17</v>
       </c>
       <c r="D3115" t="inlineStr">
         <is>
@@ -84535,7 +84535,7 @@
         <v>2</v>
       </c>
       <c r="G3115" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3116">
@@ -84562,7 +84562,7 @@
         <v>2</v>
       </c>
       <c r="G3116" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3117">
@@ -84573,7 +84573,7 @@
         <v>20</v>
       </c>
       <c r="C3117" t="n">
-        <v>29.98</v>
+        <v>29.97</v>
       </c>
       <c r="D3117" t="inlineStr">
         <is>
@@ -84589,7 +84589,7 @@
         <v>2</v>
       </c>
       <c r="G3117" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3118">
@@ -84616,7 +84616,7 @@
         <v>2</v>
       </c>
       <c r="G3118" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3119">
@@ -84643,7 +84643,7 @@
         <v>2</v>
       </c>
       <c r="G3119" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3120">
@@ -84654,7 +84654,7 @@
         <v>23</v>
       </c>
       <c r="C3120" t="n">
-        <v>31.97</v>
+        <v>31.98</v>
       </c>
       <c r="D3120" t="inlineStr">
         <is>
@@ -84670,7 +84670,7 @@
         <v>2</v>
       </c>
       <c r="G3120" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3121">
@@ -84697,7 +84697,7 @@
         <v>2</v>
       </c>
       <c r="G3121" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3122">
@@ -84724,7 +84724,7 @@
         <v>2</v>
       </c>
       <c r="G3122" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3123">
@@ -84735,7 +84735,7 @@
         <v>2</v>
       </c>
       <c r="C3123" t="n">
-        <v>12.4</v>
+        <v>12.39</v>
       </c>
       <c r="D3123" t="inlineStr">
         <is>
@@ -84751,7 +84751,7 @@
         <v>2</v>
       </c>
       <c r="G3123" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3124">
@@ -84762,7 +84762,7 @@
         <v>3</v>
       </c>
       <c r="C3124" t="n">
-        <v>11</v>
+        <v>10.99</v>
       </c>
       <c r="D3124" t="inlineStr">
         <is>
@@ -84778,7 +84778,7 @@
         <v>2</v>
       </c>
       <c r="G3124" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3125">
@@ -84805,7 +84805,7 @@
         <v>2</v>
       </c>
       <c r="G3125" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3126">
@@ -84832,7 +84832,7 @@
         <v>2</v>
       </c>
       <c r="G3126" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3127">
@@ -84843,7 +84843,7 @@
         <v>6</v>
       </c>
       <c r="C3127" t="n">
-        <v>14.01</v>
+        <v>14</v>
       </c>
       <c r="D3127" t="inlineStr">
         <is>
@@ -84859,7 +84859,7 @@
         <v>2</v>
       </c>
       <c r="G3127" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3128">
@@ -84870,7 +84870,7 @@
         <v>7</v>
       </c>
       <c r="C3128" t="n">
-        <v>20.07</v>
+        <v>20.06</v>
       </c>
       <c r="D3128" t="inlineStr">
         <is>
@@ -84886,7 +84886,7 @@
         <v>2</v>
       </c>
       <c r="G3128" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3129">
@@ -84897,7 +84897,7 @@
         <v>8</v>
       </c>
       <c r="C3129" t="n">
-        <v>33.57</v>
+        <v>33.54</v>
       </c>
       <c r="D3129" t="inlineStr">
         <is>
@@ -84913,7 +84913,7 @@
         <v>2</v>
       </c>
       <c r="G3129" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3130">
@@ -84924,7 +84924,7 @@
         <v>9</v>
       </c>
       <c r="C3130" t="n">
-        <v>28.98</v>
+        <v>28.95</v>
       </c>
       <c r="D3130" t="inlineStr">
         <is>
@@ -84940,7 +84940,7 @@
         <v>2</v>
       </c>
       <c r="G3130" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3131">
@@ -84951,7 +84951,7 @@
         <v>10</v>
       </c>
       <c r="C3131" t="n">
-        <v>23.68</v>
+        <v>23.72</v>
       </c>
       <c r="D3131" t="inlineStr">
         <is>
@@ -84967,7 +84967,7 @@
         <v>2</v>
       </c>
       <c r="G3131" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3132">
@@ -84978,7 +84978,7 @@
         <v>11</v>
       </c>
       <c r="C3132" t="n">
-        <v>17.25</v>
+        <v>17.51</v>
       </c>
       <c r="D3132" t="inlineStr">
         <is>
@@ -84994,7 +84994,7 @@
         <v>2</v>
       </c>
       <c r="G3132" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3133">
@@ -85005,7 +85005,7 @@
         <v>12</v>
       </c>
       <c r="C3133" t="n">
-        <v>19.66</v>
+        <v>19.88</v>
       </c>
       <c r="D3133" t="inlineStr">
         <is>
@@ -85021,7 +85021,7 @@
         <v>2</v>
       </c>
       <c r="G3133" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3134">
@@ -85032,7 +85032,7 @@
         <v>13</v>
       </c>
       <c r="C3134" t="n">
-        <v>20.14</v>
+        <v>20.39</v>
       </c>
       <c r="D3134" t="inlineStr">
         <is>
@@ -85048,7 +85048,7 @@
         <v>2</v>
       </c>
       <c r="G3134" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3135">
@@ -85059,7 +85059,7 @@
         <v>14</v>
       </c>
       <c r="C3135" t="n">
-        <v>21.26</v>
+        <v>21.42</v>
       </c>
       <c r="D3135" t="inlineStr">
         <is>
@@ -85075,7 +85075,7 @@
         <v>2</v>
       </c>
       <c r="G3135" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3136">
@@ -85086,7 +85086,7 @@
         <v>15</v>
       </c>
       <c r="C3136" t="n">
-        <v>20.89</v>
+        <v>20.94</v>
       </c>
       <c r="D3136" t="inlineStr">
         <is>
@@ -85102,7 +85102,7 @@
         <v>2</v>
       </c>
       <c r="G3136" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3137">
@@ -85113,7 +85113,7 @@
         <v>16</v>
       </c>
       <c r="C3137" t="n">
-        <v>19.81</v>
+        <v>20.02</v>
       </c>
       <c r="D3137" t="inlineStr">
         <is>
@@ -85129,7 +85129,7 @@
         <v>2</v>
       </c>
       <c r="G3137" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3138">
@@ -85140,7 +85140,7 @@
         <v>17</v>
       </c>
       <c r="C3138" t="n">
-        <v>17.26</v>
+        <v>17.42</v>
       </c>
       <c r="D3138" t="inlineStr">
         <is>
@@ -85156,7 +85156,7 @@
         <v>2</v>
       </c>
       <c r="G3138" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3139">
@@ -85167,7 +85167,7 @@
         <v>18</v>
       </c>
       <c r="C3139" t="n">
-        <v>17.15</v>
+        <v>17.13</v>
       </c>
       <c r="D3139" t="inlineStr">
         <is>
@@ -85183,7 +85183,7 @@
         <v>2</v>
       </c>
       <c r="G3139" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3140">
@@ -85194,7 +85194,7 @@
         <v>19</v>
       </c>
       <c r="C3140" t="n">
-        <v>15.85</v>
+        <v>15.86</v>
       </c>
       <c r="D3140" t="inlineStr">
         <is>
@@ -85210,7 +85210,7 @@
         <v>2</v>
       </c>
       <c r="G3140" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3141">
@@ -85221,7 +85221,7 @@
         <v>20</v>
       </c>
       <c r="C3141" t="n">
-        <v>28.45</v>
+        <v>28.39</v>
       </c>
       <c r="D3141" t="inlineStr">
         <is>
@@ -85237,7 +85237,7 @@
         <v>2</v>
       </c>
       <c r="G3141" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3142">
@@ -85248,7 +85248,7 @@
         <v>21</v>
       </c>
       <c r="C3142" t="n">
-        <v>36.6</v>
+        <v>36.55</v>
       </c>
       <c r="D3142" t="inlineStr">
         <is>
@@ -85264,7 +85264,7 @@
         <v>2</v>
       </c>
       <c r="G3142" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3143">
@@ -85275,7 +85275,7 @@
         <v>22</v>
       </c>
       <c r="C3143" t="n">
-        <v>36.05</v>
+        <v>36</v>
       </c>
       <c r="D3143" t="inlineStr">
         <is>
@@ -85291,7 +85291,7 @@
         <v>2</v>
       </c>
       <c r="G3143" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3144">
@@ -85302,7 +85302,7 @@
         <v>23</v>
       </c>
       <c r="C3144" t="n">
-        <v>33.46</v>
+        <v>33.42</v>
       </c>
       <c r="D3144" t="inlineStr">
         <is>
@@ -85318,7 +85318,7 @@
         <v>2</v>
       </c>
       <c r="G3144" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3145">
@@ -85329,7 +85329,7 @@
         <v>24</v>
       </c>
       <c r="C3145" t="n">
-        <v>27.69</v>
+        <v>27.65</v>
       </c>
       <c r="D3145" t="inlineStr">
         <is>
@@ -85345,7 +85345,7 @@
         <v>2</v>
       </c>
       <c r="G3145" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3146">
@@ -85356,7 +85356,7 @@
         <v>1</v>
       </c>
       <c r="C3146" t="n">
-        <v>19.95</v>
+        <v>19.72</v>
       </c>
       <c r="D3146" t="inlineStr">
         <is>
@@ -85372,7 +85372,7 @@
         <v>2</v>
       </c>
       <c r="G3146" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3147">
@@ -85383,7 +85383,7 @@
         <v>2</v>
       </c>
       <c r="C3147" t="n">
-        <v>13.87</v>
+        <v>13.78</v>
       </c>
       <c r="D3147" t="inlineStr">
         <is>
@@ -85399,7 +85399,7 @@
         <v>2</v>
       </c>
       <c r="G3147" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3148">
@@ -85410,7 +85410,7 @@
         <v>3</v>
       </c>
       <c r="C3148" t="n">
-        <v>13.91</v>
+        <v>13.6</v>
       </c>
       <c r="D3148" t="inlineStr">
         <is>
@@ -85426,7 +85426,7 @@
         <v>2</v>
       </c>
       <c r="G3148" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3149">
@@ -85437,7 +85437,7 @@
         <v>4</v>
       </c>
       <c r="C3149" t="n">
-        <v>14.9</v>
+        <v>14.66</v>
       </c>
       <c r="D3149" t="inlineStr">
         <is>
@@ -85453,7 +85453,7 @@
         <v>2</v>
       </c>
       <c r="G3149" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3150">
@@ -85464,7 +85464,7 @@
         <v>5</v>
       </c>
       <c r="C3150" t="n">
-        <v>16.28</v>
+        <v>16.06</v>
       </c>
       <c r="D3150" t="inlineStr">
         <is>
@@ -85480,7 +85480,7 @@
         <v>2</v>
       </c>
       <c r="G3150" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3151">
@@ -85491,7 +85491,7 @@
         <v>6</v>
       </c>
       <c r="C3151" t="n">
-        <v>17.68</v>
+        <v>17.47</v>
       </c>
       <c r="D3151" t="inlineStr">
         <is>
@@ -85507,7 +85507,7 @@
         <v>2</v>
       </c>
       <c r="G3151" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3152">
@@ -85518,7 +85518,7 @@
         <v>7</v>
       </c>
       <c r="C3152" t="n">
-        <v>23.14</v>
+        <v>22.81</v>
       </c>
       <c r="D3152" t="inlineStr">
         <is>
@@ -85534,7 +85534,7 @@
         <v>2</v>
       </c>
       <c r="G3152" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3153">
@@ -85545,7 +85545,7 @@
         <v>8</v>
       </c>
       <c r="C3153" t="n">
-        <v>47.54</v>
+        <v>47.01</v>
       </c>
       <c r="D3153" t="inlineStr">
         <is>
@@ -85561,7 +85561,7 @@
         <v>2</v>
       </c>
       <c r="G3153" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3154">
@@ -85572,7 +85572,7 @@
         <v>9</v>
       </c>
       <c r="C3154" t="n">
-        <v>49.52</v>
+        <v>49.03</v>
       </c>
       <c r="D3154" t="inlineStr">
         <is>
@@ -85588,7 +85588,7 @@
         <v>2</v>
       </c>
       <c r="G3154" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3155">
@@ -85599,7 +85599,7 @@
         <v>10</v>
       </c>
       <c r="C3155" t="n">
-        <v>30.57</v>
+        <v>29.58</v>
       </c>
       <c r="D3155" t="inlineStr">
         <is>
@@ -85615,7 +85615,7 @@
         <v>2</v>
       </c>
       <c r="G3155" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3156">
@@ -85626,7 +85626,7 @@
         <v>11</v>
       </c>
       <c r="C3156" t="n">
-        <v>20.66</v>
+        <v>20.37</v>
       </c>
       <c r="D3156" t="inlineStr">
         <is>
@@ -85642,7 +85642,7 @@
         <v>2</v>
       </c>
       <c r="G3156" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3157">
@@ -85653,7 +85653,7 @@
         <v>12</v>
       </c>
       <c r="C3157" t="n">
-        <v>29.67</v>
+        <v>29.55</v>
       </c>
       <c r="D3157" t="inlineStr">
         <is>
@@ -85669,7 +85669,7 @@
         <v>2</v>
       </c>
       <c r="G3157" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3158">
@@ -85680,7 +85680,7 @@
         <v>13</v>
       </c>
       <c r="C3158" t="n">
-        <v>31.4</v>
+        <v>31.05</v>
       </c>
       <c r="D3158" t="inlineStr">
         <is>
@@ -85696,7 +85696,7 @@
         <v>2</v>
       </c>
       <c r="G3158" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3159">
@@ -85707,7 +85707,7 @@
         <v>14</v>
       </c>
       <c r="C3159" t="n">
-        <v>32.31</v>
+        <v>31.96</v>
       </c>
       <c r="D3159" t="inlineStr">
         <is>
@@ -85723,7 +85723,7 @@
         <v>2</v>
       </c>
       <c r="G3159" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3160">
@@ -85734,7 +85734,7 @@
         <v>15</v>
       </c>
       <c r="C3160" t="n">
-        <v>32.66</v>
+        <v>32.34</v>
       </c>
       <c r="D3160" t="inlineStr">
         <is>
@@ -85750,7 +85750,7 @@
         <v>2</v>
       </c>
       <c r="G3160" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3161">
@@ -85761,7 +85761,7 @@
         <v>16</v>
       </c>
       <c r="C3161" t="n">
-        <v>31.78</v>
+        <v>31.43</v>
       </c>
       <c r="D3161" t="inlineStr">
         <is>
@@ -85777,7 +85777,7 @@
         <v>2</v>
       </c>
       <c r="G3161" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3162">
@@ -85788,7 +85788,7 @@
         <v>17</v>
       </c>
       <c r="C3162" t="n">
-        <v>31.73</v>
+        <v>31.52</v>
       </c>
       <c r="D3162" t="inlineStr">
         <is>
@@ -85804,7 +85804,7 @@
         <v>2</v>
       </c>
       <c r="G3162" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3163">
@@ -85815,7 +85815,7 @@
         <v>18</v>
       </c>
       <c r="C3163" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="D3163" t="inlineStr">
         <is>
@@ -85831,7 +85831,7 @@
         <v>2</v>
       </c>
       <c r="G3163" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3164">
@@ -85842,7 +85842,7 @@
         <v>19</v>
       </c>
       <c r="C3164" t="n">
-        <v>32.96</v>
+        <v>32.56</v>
       </c>
       <c r="D3164" t="inlineStr">
         <is>
@@ -85858,7 +85858,7 @@
         <v>2</v>
       </c>
       <c r="G3164" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3165">
@@ -85869,7 +85869,7 @@
         <v>20</v>
       </c>
       <c r="C3165" t="n">
-        <v>32.54</v>
+        <v>32.42</v>
       </c>
       <c r="D3165" t="inlineStr">
         <is>
@@ -85885,7 +85885,7 @@
         <v>2</v>
       </c>
       <c r="G3165" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3166">
@@ -85896,7 +85896,7 @@
         <v>21</v>
       </c>
       <c r="C3166" t="n">
-        <v>37.38</v>
+        <v>37.16</v>
       </c>
       <c r="D3166" t="inlineStr">
         <is>
@@ -85912,7 +85912,7 @@
         <v>2</v>
       </c>
       <c r="G3166" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3167">
@@ -85923,7 +85923,7 @@
         <v>22</v>
       </c>
       <c r="C3167" t="n">
-        <v>38.1</v>
+        <v>37.77</v>
       </c>
       <c r="D3167" t="inlineStr">
         <is>
@@ -85939,7 +85939,7 @@
         <v>2</v>
       </c>
       <c r="G3167" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3168">
@@ -85950,7 +85950,7 @@
         <v>23</v>
       </c>
       <c r="C3168" t="n">
-        <v>37.53</v>
+        <v>37.23</v>
       </c>
       <c r="D3168" t="inlineStr">
         <is>
@@ -85966,7 +85966,7 @@
         <v>2</v>
       </c>
       <c r="G3168" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3169">
@@ -85977,7 +85977,7 @@
         <v>24</v>
       </c>
       <c r="C3169" t="n">
-        <v>37.37</v>
+        <v>37.24</v>
       </c>
       <c r="D3169" t="inlineStr">
         <is>
@@ -85993,7 +85993,7 @@
         <v>2</v>
       </c>
       <c r="G3169" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3170">
@@ -86004,7 +86004,7 @@
         <v>1</v>
       </c>
       <c r="C3170" t="n">
-        <v>-1.86</v>
+        <v>20.02</v>
       </c>
       <c r="D3170" t="inlineStr">
         <is>
@@ -86020,7 +86020,7 @@
         <v>2</v>
       </c>
       <c r="G3170" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3171">
@@ -86031,7 +86031,7 @@
         <v>2</v>
       </c>
       <c r="C3171" t="n">
-        <v>-6.98</v>
+        <v>15.26</v>
       </c>
       <c r="D3171" t="inlineStr">
         <is>
@@ -86047,7 +86047,7 @@
         <v>2</v>
       </c>
       <c r="G3171" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3172">
@@ -86058,7 +86058,7 @@
         <v>3</v>
       </c>
       <c r="C3172" t="n">
-        <v>-2.49</v>
+        <v>16.4</v>
       </c>
       <c r="D3172" t="inlineStr">
         <is>
@@ -86074,7 +86074,7 @@
         <v>2</v>
       </c>
       <c r="G3172" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3173">
@@ -86085,7 +86085,7 @@
         <v>4</v>
       </c>
       <c r="C3173" t="n">
-        <v>10.09</v>
+        <v>15.84</v>
       </c>
       <c r="D3173" t="inlineStr">
         <is>
@@ -86101,7 +86101,7 @@
         <v>2</v>
       </c>
       <c r="G3173" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3174">
@@ -86112,7 +86112,7 @@
         <v>5</v>
       </c>
       <c r="C3174" t="n">
-        <v>2.28</v>
+        <v>13.79</v>
       </c>
       <c r="D3174" t="inlineStr">
         <is>
@@ -86128,7 +86128,7 @@
         <v>2</v>
       </c>
       <c r="G3174" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3175">
@@ -86139,7 +86139,7 @@
         <v>6</v>
       </c>
       <c r="C3175" t="n">
-        <v>-0.58</v>
+        <v>13.19</v>
       </c>
       <c r="D3175" t="inlineStr">
         <is>
@@ -86155,7 +86155,7 @@
         <v>2</v>
       </c>
       <c r="G3175" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3176">
@@ -86166,7 +86166,7 @@
         <v>7</v>
       </c>
       <c r="C3176" t="n">
-        <v>-8.970000000000001</v>
+        <v>20.04</v>
       </c>
       <c r="D3176" t="inlineStr">
         <is>
@@ -86182,7 +86182,7 @@
         <v>2</v>
       </c>
       <c r="G3176" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3177">
@@ -86193,7 +86193,7 @@
         <v>8</v>
       </c>
       <c r="C3177" t="n">
-        <v>40</v>
+        <v>41.05</v>
       </c>
       <c r="D3177" t="inlineStr">
         <is>
@@ -86209,7 +86209,7 @@
         <v>2</v>
       </c>
       <c r="G3177" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3178">
@@ -86220,7 +86220,7 @@
         <v>9</v>
       </c>
       <c r="C3178" t="n">
-        <v>35.73</v>
+        <v>42.19</v>
       </c>
       <c r="D3178" t="inlineStr">
         <is>
@@ -86236,7 +86236,7 @@
         <v>2</v>
       </c>
       <c r="G3178" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3179">
@@ -86247,7 +86247,7 @@
         <v>10</v>
       </c>
       <c r="C3179" t="n">
-        <v>6.23</v>
+        <v>19.66</v>
       </c>
       <c r="D3179" t="inlineStr">
         <is>
@@ -86263,7 +86263,7 @@
         <v>2</v>
       </c>
       <c r="G3179" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3180">
@@ -86274,7 +86274,7 @@
         <v>11</v>
       </c>
       <c r="C3180" t="n">
-        <v>-15.03</v>
+        <v>12.47</v>
       </c>
       <c r="D3180" t="inlineStr">
         <is>
@@ -86290,7 +86290,7 @@
         <v>2</v>
       </c>
       <c r="G3180" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3181">
@@ -86301,7 +86301,7 @@
         <v>12</v>
       </c>
       <c r="C3181" t="n">
-        <v>36.54</v>
+        <v>29.51</v>
       </c>
       <c r="D3181" t="inlineStr">
         <is>
@@ -86317,7 +86317,7 @@
         <v>2</v>
       </c>
       <c r="G3181" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3182">
@@ -86328,7 +86328,7 @@
         <v>13</v>
       </c>
       <c r="C3182" t="n">
-        <v>38.1</v>
+        <v>30.58</v>
       </c>
       <c r="D3182" t="inlineStr">
         <is>
@@ -86344,7 +86344,7 @@
         <v>2</v>
       </c>
       <c r="G3182" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3183">
@@ -86355,7 +86355,7 @@
         <v>14</v>
       </c>
       <c r="C3183" t="n">
-        <v>32.03</v>
+        <v>28.64</v>
       </c>
       <c r="D3183" t="inlineStr">
         <is>
@@ -86371,7 +86371,7 @@
         <v>2</v>
       </c>
       <c r="G3183" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3184">
@@ -86382,7 +86382,7 @@
         <v>15</v>
       </c>
       <c r="C3184" t="n">
-        <v>36.77</v>
+        <v>32.25</v>
       </c>
       <c r="D3184" t="inlineStr">
         <is>
@@ -86398,7 +86398,7 @@
         <v>2</v>
       </c>
       <c r="G3184" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3185">
@@ -86409,7 +86409,7 @@
         <v>16</v>
       </c>
       <c r="C3185" t="n">
-        <v>38.45</v>
+        <v>33.25</v>
       </c>
       <c r="D3185" t="inlineStr">
         <is>
@@ -86425,7 +86425,7 @@
         <v>2</v>
       </c>
       <c r="G3185" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3186">
@@ -86436,7 +86436,7 @@
         <v>17</v>
       </c>
       <c r="C3186" t="n">
-        <v>29.53</v>
+        <v>31.74</v>
       </c>
       <c r="D3186" t="inlineStr">
         <is>
@@ -86452,7 +86452,7 @@
         <v>2</v>
       </c>
       <c r="G3186" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3187">
@@ -86463,7 +86463,7 @@
         <v>18</v>
       </c>
       <c r="C3187" t="n">
-        <v>30.19</v>
+        <v>27.32</v>
       </c>
       <c r="D3187" t="inlineStr">
         <is>
@@ -86479,7 +86479,7 @@
         <v>2</v>
       </c>
       <c r="G3187" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3188">
@@ -86490,7 +86490,7 @@
         <v>19</v>
       </c>
       <c r="C3188" t="n">
-        <v>11.7</v>
+        <v>21.81</v>
       </c>
       <c r="D3188" t="inlineStr">
         <is>
@@ -86506,7 +86506,7 @@
         <v>2</v>
       </c>
       <c r="G3188" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3189">
@@ -86517,7 +86517,7 @@
         <v>20</v>
       </c>
       <c r="C3189" t="n">
-        <v>-22.44</v>
+        <v>16.54</v>
       </c>
       <c r="D3189" t="inlineStr">
         <is>
@@ -86533,7 +86533,7 @@
         <v>2</v>
       </c>
       <c r="G3189" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3190">
@@ -86544,7 +86544,7 @@
         <v>21</v>
       </c>
       <c r="C3190" t="n">
-        <v>23.44</v>
+        <v>26.78</v>
       </c>
       <c r="D3190" t="inlineStr">
         <is>
@@ -86560,7 +86560,7 @@
         <v>2</v>
       </c>
       <c r="G3190" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3191">
@@ -86571,7 +86571,7 @@
         <v>22</v>
       </c>
       <c r="C3191" t="n">
-        <v>9.77</v>
+        <v>28.61</v>
       </c>
       <c r="D3191" t="inlineStr">
         <is>
@@ -86587,7 +86587,7 @@
         <v>2</v>
       </c>
       <c r="G3191" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3192">
@@ -86598,7 +86598,7 @@
         <v>23</v>
       </c>
       <c r="C3192" t="n">
-        <v>-7.34</v>
+        <v>27.75</v>
       </c>
       <c r="D3192" t="inlineStr">
         <is>
@@ -86614,7 +86614,7 @@
         <v>2</v>
       </c>
       <c r="G3192" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3193">
@@ -86625,7 +86625,7 @@
         <v>24</v>
       </c>
       <c r="C3193" t="n">
-        <v>3.41</v>
+        <v>28.19</v>
       </c>
       <c r="D3193" t="inlineStr">
         <is>
@@ -86641,7 +86641,7 @@
         <v>2</v>
       </c>
       <c r="G3193" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3194">
@@ -86652,7 +86652,7 @@
         <v>1</v>
       </c>
       <c r="C3194" t="n">
-        <v>8.6</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="D3194" t="inlineStr">
         <is>
@@ -86668,7 +86668,7 @@
         <v>2</v>
       </c>
       <c r="G3194" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3195">
@@ -86679,7 +86679,7 @@
         <v>2</v>
       </c>
       <c r="C3195" t="n">
-        <v>8.94</v>
+        <v>8.43</v>
       </c>
       <c r="D3195" t="inlineStr">
         <is>
@@ -86695,7 +86695,7 @@
         <v>2</v>
       </c>
       <c r="G3195" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3196">
@@ -86706,7 +86706,7 @@
         <v>3</v>
       </c>
       <c r="C3196" t="n">
-        <v>9.18</v>
+        <v>11.04</v>
       </c>
       <c r="D3196" t="inlineStr">
         <is>
@@ -86722,7 +86722,7 @@
         <v>2</v>
       </c>
       <c r="G3196" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3197">
@@ -86733,7 +86733,7 @@
         <v>4</v>
       </c>
       <c r="C3197" t="n">
-        <v>8.76</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="D3197" t="inlineStr">
         <is>
@@ -86749,7 +86749,7 @@
         <v>2</v>
       </c>
       <c r="G3197" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3198">
@@ -86760,7 +86760,7 @@
         <v>5</v>
       </c>
       <c r="C3198" t="n">
-        <v>9.470000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="D3198" t="inlineStr">
         <is>
@@ -86776,7 +86776,7 @@
         <v>2</v>
       </c>
       <c r="G3198" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3199">
@@ -86787,7 +86787,7 @@
         <v>6</v>
       </c>
       <c r="C3199" t="n">
-        <v>10.94</v>
+        <v>10.2</v>
       </c>
       <c r="D3199" t="inlineStr">
         <is>
@@ -86803,7 +86803,7 @@
         <v>2</v>
       </c>
       <c r="G3199" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3200">
@@ -86814,7 +86814,7 @@
         <v>7</v>
       </c>
       <c r="C3200" t="n">
-        <v>16.09</v>
+        <v>21.78</v>
       </c>
       <c r="D3200" t="inlineStr">
         <is>
@@ -86830,7 +86830,7 @@
         <v>2</v>
       </c>
       <c r="G3200" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3201">
@@ -86841,7 +86841,7 @@
         <v>8</v>
       </c>
       <c r="C3201" t="n">
-        <v>15.93</v>
+        <v>37.35</v>
       </c>
       <c r="D3201" t="inlineStr">
         <is>
@@ -86857,7 +86857,7 @@
         <v>2</v>
       </c>
       <c r="G3201" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3202">
@@ -86868,7 +86868,7 @@
         <v>9</v>
       </c>
       <c r="C3202" t="n">
-        <v>16.71</v>
+        <v>35.43</v>
       </c>
       <c r="D3202" t="inlineStr">
         <is>
@@ -86884,7 +86884,7 @@
         <v>2</v>
       </c>
       <c r="G3202" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3203">
@@ -86895,7 +86895,7 @@
         <v>10</v>
       </c>
       <c r="C3203" t="n">
-        <v>15.28</v>
+        <v>25.1</v>
       </c>
       <c r="D3203" t="inlineStr">
         <is>
@@ -86911,7 +86911,7 @@
         <v>2</v>
       </c>
       <c r="G3203" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3204">
@@ -86922,7 +86922,7 @@
         <v>11</v>
       </c>
       <c r="C3204" t="n">
-        <v>22.86</v>
+        <v>31.37</v>
       </c>
       <c r="D3204" t="inlineStr">
         <is>
@@ -86938,7 +86938,7 @@
         <v>2</v>
       </c>
       <c r="G3204" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3205">
@@ -86949,7 +86949,7 @@
         <v>12</v>
       </c>
       <c r="C3205" t="n">
-        <v>34.49</v>
+        <v>45.47</v>
       </c>
       <c r="D3205" t="inlineStr">
         <is>
@@ -86965,7 +86965,7 @@
         <v>2</v>
       </c>
       <c r="G3205" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3206">
@@ -86976,7 +86976,7 @@
         <v>13</v>
       </c>
       <c r="C3206" t="n">
-        <v>38.1</v>
+        <v>48.74</v>
       </c>
       <c r="D3206" t="inlineStr">
         <is>
@@ -86992,7 +86992,7 @@
         <v>2</v>
       </c>
       <c r="G3206" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3207">
@@ -87003,7 +87003,7 @@
         <v>14</v>
       </c>
       <c r="C3207" t="n">
-        <v>40.08</v>
+        <v>52.91</v>
       </c>
       <c r="D3207" t="inlineStr">
         <is>
@@ -87019,7 +87019,7 @@
         <v>2</v>
       </c>
       <c r="G3207" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3208">
@@ -87030,7 +87030,7 @@
         <v>15</v>
       </c>
       <c r="C3208" t="n">
-        <v>38.66</v>
+        <v>52.39</v>
       </c>
       <c r="D3208" t="inlineStr">
         <is>
@@ -87046,7 +87046,7 @@
         <v>2</v>
       </c>
       <c r="G3208" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3209">
@@ -87057,7 +87057,7 @@
         <v>16</v>
       </c>
       <c r="C3209" t="n">
-        <v>40.11</v>
+        <v>53.66</v>
       </c>
       <c r="D3209" t="inlineStr">
         <is>
@@ -87073,7 +87073,7 @@
         <v>2</v>
       </c>
       <c r="G3209" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3210">
@@ -87084,7 +87084,7 @@
         <v>17</v>
       </c>
       <c r="C3210" t="n">
-        <v>37.38</v>
+        <v>50.2</v>
       </c>
       <c r="D3210" t="inlineStr">
         <is>
@@ -87100,7 +87100,7 @@
         <v>2</v>
       </c>
       <c r="G3210" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3211">
@@ -87111,7 +87111,7 @@
         <v>18</v>
       </c>
       <c r="C3211" t="n">
-        <v>32.11</v>
+        <v>43.27</v>
       </c>
       <c r="D3211" t="inlineStr">
         <is>
@@ -87127,7 +87127,7 @@
         <v>2</v>
       </c>
       <c r="G3211" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3212">
@@ -87138,7 +87138,7 @@
         <v>19</v>
       </c>
       <c r="C3212" t="n">
-        <v>21.65</v>
+        <v>28.57</v>
       </c>
       <c r="D3212" t="inlineStr">
         <is>
@@ -87154,7 +87154,7 @@
         <v>2</v>
       </c>
       <c r="G3212" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3213">
@@ -87165,7 +87165,7 @@
         <v>20</v>
       </c>
       <c r="C3213" t="n">
-        <v>14.51</v>
+        <v>21.86</v>
       </c>
       <c r="D3213" t="inlineStr">
         <is>
@@ -87181,7 +87181,7 @@
         <v>2</v>
       </c>
       <c r="G3213" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3214">
@@ -87192,7 +87192,7 @@
         <v>21</v>
       </c>
       <c r="C3214" t="n">
-        <v>11.12</v>
+        <v>34.45</v>
       </c>
       <c r="D3214" t="inlineStr">
         <is>
@@ -87208,7 +87208,7 @@
         <v>2</v>
       </c>
       <c r="G3214" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3215">
@@ -87219,7 +87219,7 @@
         <v>22</v>
       </c>
       <c r="C3215" t="n">
-        <v>10.78</v>
+        <v>38.41</v>
       </c>
       <c r="D3215" t="inlineStr">
         <is>
@@ -87235,7 +87235,7 @@
         <v>2</v>
       </c>
       <c r="G3215" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3216">
@@ -87246,7 +87246,7 @@
         <v>23</v>
       </c>
       <c r="C3216" t="n">
-        <v>14.24</v>
+        <v>38.62</v>
       </c>
       <c r="D3216" t="inlineStr">
         <is>
@@ -87262,7 +87262,7 @@
         <v>2</v>
       </c>
       <c r="G3216" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3217">
@@ -87273,7 +87273,7 @@
         <v>24</v>
       </c>
       <c r="C3217" t="n">
-        <v>14.49</v>
+        <v>29.73</v>
       </c>
       <c r="D3217" t="inlineStr">
         <is>
@@ -87289,7 +87289,7 @@
         <v>2</v>
       </c>
       <c r="G3217" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3218">
@@ -87300,7 +87300,7 @@
         <v>1</v>
       </c>
       <c r="C3218" t="n">
-        <v>8.710000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="D3218" t="inlineStr">
         <is>
@@ -87316,7 +87316,7 @@
         <v>2</v>
       </c>
       <c r="G3218" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3219">
@@ -87327,7 +87327,7 @@
         <v>2</v>
       </c>
       <c r="C3219" t="n">
-        <v>9.02</v>
+        <v>9.07</v>
       </c>
       <c r="D3219" t="inlineStr">
         <is>
@@ -87343,7 +87343,7 @@
         <v>2</v>
       </c>
       <c r="G3219" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3220">
@@ -87354,7 +87354,7 @@
         <v>3</v>
       </c>
       <c r="C3220" t="n">
-        <v>8.789999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="D3220" t="inlineStr">
         <is>
@@ -87370,7 +87370,7 @@
         <v>2</v>
       </c>
       <c r="G3220" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3221">
@@ -87381,7 +87381,7 @@
         <v>4</v>
       </c>
       <c r="C3221" t="n">
-        <v>9.01</v>
+        <v>9.06</v>
       </c>
       <c r="D3221" t="inlineStr">
         <is>
@@ -87397,7 +87397,7 @@
         <v>2</v>
       </c>
       <c r="G3221" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3222">
@@ -87408,7 +87408,7 @@
         <v>5</v>
       </c>
       <c r="C3222" t="n">
-        <v>9.18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D3222" t="inlineStr">
         <is>
@@ -87424,7 +87424,7 @@
         <v>2</v>
       </c>
       <c r="G3222" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3223">
@@ -87435,7 +87435,7 @@
         <v>6</v>
       </c>
       <c r="C3223" t="n">
-        <v>9.289999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="D3223" t="inlineStr">
         <is>
@@ -87451,7 +87451,7 @@
         <v>2</v>
       </c>
       <c r="G3223" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3224">
@@ -87462,7 +87462,7 @@
         <v>7</v>
       </c>
       <c r="C3224" t="n">
-        <v>21.07</v>
+        <v>13.97</v>
       </c>
       <c r="D3224" t="inlineStr">
         <is>
@@ -87478,7 +87478,7 @@
         <v>2</v>
       </c>
       <c r="G3224" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3225">
@@ -87489,7 +87489,7 @@
         <v>8</v>
       </c>
       <c r="C3225" t="n">
-        <v>31.43</v>
+        <v>24.31</v>
       </c>
       <c r="D3225" t="inlineStr">
         <is>
@@ -87505,7 +87505,7 @@
         <v>2</v>
       </c>
       <c r="G3225" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3226">
@@ -87516,7 +87516,7 @@
         <v>9</v>
       </c>
       <c r="C3226" t="n">
-        <v>30.29</v>
+        <v>28.82</v>
       </c>
       <c r="D3226" t="inlineStr">
         <is>
@@ -87532,7 +87532,7 @@
         <v>2</v>
       </c>
       <c r="G3226" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3227">
@@ -87543,7 +87543,7 @@
         <v>10</v>
       </c>
       <c r="C3227" t="n">
-        <v>23.22</v>
+        <v>22.28</v>
       </c>
       <c r="D3227" t="inlineStr">
         <is>
@@ -87559,7 +87559,7 @@
         <v>2</v>
       </c>
       <c r="G3227" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3228">
@@ -87570,7 +87570,7 @@
         <v>11</v>
       </c>
       <c r="C3228" t="n">
-        <v>27.04</v>
+        <v>26.12</v>
       </c>
       <c r="D3228" t="inlineStr">
         <is>
@@ -87586,7 +87586,7 @@
         <v>2</v>
       </c>
       <c r="G3228" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3229">
@@ -87597,7 +87597,7 @@
         <v>12</v>
       </c>
       <c r="C3229" t="n">
-        <v>28.79</v>
+        <v>27.75</v>
       </c>
       <c r="D3229" t="inlineStr">
         <is>
@@ -87613,7 +87613,7 @@
         <v>2</v>
       </c>
       <c r="G3229" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3230">
@@ -87624,7 +87624,7 @@
         <v>13</v>
       </c>
       <c r="C3230" t="n">
-        <v>28.98</v>
+        <v>28.27</v>
       </c>
       <c r="D3230" t="inlineStr">
         <is>
@@ -87640,7 +87640,7 @@
         <v>2</v>
       </c>
       <c r="G3230" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3231">
@@ -87651,7 +87651,7 @@
         <v>14</v>
       </c>
       <c r="C3231" t="n">
-        <v>26.9</v>
+        <v>26.31</v>
       </c>
       <c r="D3231" t="inlineStr">
         <is>
@@ -87667,7 +87667,7 @@
         <v>2</v>
       </c>
       <c r="G3231" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3232">
@@ -87678,7 +87678,7 @@
         <v>15</v>
       </c>
       <c r="C3232" t="n">
-        <v>26.64</v>
+        <v>26.09</v>
       </c>
       <c r="D3232" t="inlineStr">
         <is>
@@ -87694,7 +87694,7 @@
         <v>2</v>
       </c>
       <c r="G3232" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3233">
@@ -87705,7 +87705,7 @@
         <v>16</v>
       </c>
       <c r="C3233" t="n">
-        <v>27.35</v>
+        <v>26.74</v>
       </c>
       <c r="D3233" t="inlineStr">
         <is>
@@ -87721,7 +87721,7 @@
         <v>2</v>
       </c>
       <c r="G3233" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3234">
@@ -87732,7 +87732,7 @@
         <v>17</v>
       </c>
       <c r="C3234" t="n">
-        <v>29.04</v>
+        <v>28.31</v>
       </c>
       <c r="D3234" t="inlineStr">
         <is>
@@ -87748,7 +87748,7 @@
         <v>2</v>
       </c>
       <c r="G3234" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3235">
@@ -87759,7 +87759,7 @@
         <v>18</v>
       </c>
       <c r="C3235" t="n">
-        <v>30.12</v>
+        <v>29.51</v>
       </c>
       <c r="D3235" t="inlineStr">
         <is>
@@ -87775,7 +87775,7 @@
         <v>2</v>
       </c>
       <c r="G3235" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3236">
@@ -87786,7 +87786,7 @@
         <v>19</v>
       </c>
       <c r="C3236" t="n">
-        <v>27.77</v>
+        <v>26.18</v>
       </c>
       <c r="D3236" t="inlineStr">
         <is>
@@ -87802,7 +87802,7 @@
         <v>2</v>
       </c>
       <c r="G3236" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3237">
@@ -87813,7 +87813,7 @@
         <v>20</v>
       </c>
       <c r="C3237" t="n">
-        <v>21.34</v>
+        <v>15.75</v>
       </c>
       <c r="D3237" t="inlineStr">
         <is>
@@ -87829,7 +87829,7 @@
         <v>2</v>
       </c>
       <c r="G3237" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3238">
@@ -87840,7 +87840,7 @@
         <v>21</v>
       </c>
       <c r="C3238" t="n">
-        <v>32.7</v>
+        <v>16.83</v>
       </c>
       <c r="D3238" t="inlineStr">
         <is>
@@ -87856,7 +87856,7 @@
         <v>2</v>
       </c>
       <c r="G3238" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3239">
@@ -87867,7 +87867,7 @@
         <v>22</v>
       </c>
       <c r="C3239" t="n">
-        <v>30.33</v>
+        <v>11.9</v>
       </c>
       <c r="D3239" t="inlineStr">
         <is>
@@ -87883,7 +87883,7 @@
         <v>2</v>
       </c>
       <c r="G3239" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3240">
@@ -87894,7 +87894,7 @@
         <v>23</v>
       </c>
       <c r="C3240" t="n">
-        <v>21.29</v>
+        <v>10</v>
       </c>
       <c r="D3240" t="inlineStr">
         <is>
@@ -87910,7 +87910,7 @@
         <v>2</v>
       </c>
       <c r="G3240" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
       </c>
     </row>
     <row r="3241">
@@ -87921,7 +87921,7 @@
         <v>24</v>
       </c>
       <c r="C3241" t="n">
-        <v>19.67</v>
+        <v>9.56</v>
       </c>
       <c r="D3241" t="inlineStr">
         <is>
@@ -87937,7 +87937,655 @@
         <v>2</v>
       </c>
       <c r="G3241" s="2" t="n">
-        <v>46277.84822489289</v>
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3242">
+      <c r="A3242" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3242" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3242" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="D3242" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3242" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3242" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3242" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3243">
+      <c r="A3243" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3243" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3243" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="D3243" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3243" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3243" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3243" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3244">
+      <c r="A3244" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3244" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3244" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="D3244" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3244" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3244" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3244" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3245">
+      <c r="A3245" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3245" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3245" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="D3245" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3245" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3245" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3245" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3246">
+      <c r="A3246" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3246" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3246" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="D3246" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3246" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3246" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3246" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3247">
+      <c r="A3247" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3247" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3247" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="D3247" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3247" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3247" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3247" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3248">
+      <c r="A3248" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3248" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3248" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="D3248" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3248" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3248" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3248" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3249">
+      <c r="A3249" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3249" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3249" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="D3249" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3249" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3249" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3249" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3250">
+      <c r="A3250" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3250" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3250" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="D3250" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3250" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3250" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3250" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3251">
+      <c r="A3251" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3251" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3251" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="D3251" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3251" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3251" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3251" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3252">
+      <c r="A3252" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3252" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3252" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="D3252" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3252" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3252" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3252" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3253">
+      <c r="A3253" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3253" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3253" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="D3253" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3253" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3253" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3253" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3254">
+      <c r="A3254" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3254" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3254" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="D3254" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3254" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3254" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3254" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3255">
+      <c r="A3255" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3255" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3255" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="D3255" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3255" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3255" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3255" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3256">
+      <c r="A3256" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3256" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3256" t="n">
+        <v>33.18</v>
+      </c>
+      <c r="D3256" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3256" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3256" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3256" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3257">
+      <c r="A3257" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3257" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3257" t="n">
+        <v>36</v>
+      </c>
+      <c r="D3257" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3257" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3257" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3257" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3258">
+      <c r="A3258" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3258" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3258" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="D3258" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3258" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3258" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3258" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3259">
+      <c r="A3259" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3259" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3259" t="n">
+        <v>32.06</v>
+      </c>
+      <c r="D3259" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3259" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3259" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3259" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3260">
+      <c r="A3260" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3260" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3260" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D3260" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3260" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3260" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3260" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3261">
+      <c r="A3261" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3261" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3261" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="D3261" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3261" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3261" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3261" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3262">
+      <c r="A3262" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3262" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3262" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="D3262" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3262" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3262" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3262" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3263">
+      <c r="A3263" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3263" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3263" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="D3263" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3263" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3263" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3263" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3264">
+      <c r="A3264" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3264" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3264" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="D3264" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3264" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3264" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3264" s="2" t="n">
+        <v>46278.46597506487</v>
+      </c>
+    </row>
+    <row r="3265">
+      <c r="A3265" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B3265" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3265" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="D3265" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3265" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3265" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3265" s="2" t="n">
+        <v>46278.46597506487</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -80188,7 +80188,7 @@
         <v>2</v>
       </c>
       <c r="G2954" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2955">
@@ -80215,7 +80215,7 @@
         <v>2</v>
       </c>
       <c r="G2955" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2956">
@@ -80242,7 +80242,7 @@
         <v>2</v>
       </c>
       <c r="G2956" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2957">
@@ -80269,7 +80269,7 @@
         <v>2</v>
       </c>
       <c r="G2957" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2958">
@@ -80296,7 +80296,7 @@
         <v>2</v>
       </c>
       <c r="G2958" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2959">
@@ -80323,7 +80323,7 @@
         <v>2</v>
       </c>
       <c r="G2959" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2960">
@@ -80350,7 +80350,7 @@
         <v>2</v>
       </c>
       <c r="G2960" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2961">
@@ -80377,7 +80377,7 @@
         <v>2</v>
       </c>
       <c r="G2961" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2962">
@@ -80404,7 +80404,7 @@
         <v>2</v>
       </c>
       <c r="G2962" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2963">
@@ -80431,7 +80431,7 @@
         <v>2</v>
       </c>
       <c r="G2963" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2964">
@@ -80458,7 +80458,7 @@
         <v>2</v>
       </c>
       <c r="G2964" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2965">
@@ -80485,7 +80485,7 @@
         <v>2</v>
       </c>
       <c r="G2965" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2966">
@@ -80512,7 +80512,7 @@
         <v>2</v>
       </c>
       <c r="G2966" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2967">
@@ -80539,7 +80539,7 @@
         <v>2</v>
       </c>
       <c r="G2967" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2968">
@@ -80566,7 +80566,7 @@
         <v>2</v>
       </c>
       <c r="G2968" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2969">
@@ -80593,7 +80593,7 @@
         <v>2</v>
       </c>
       <c r="G2969" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2970">
@@ -80620,7 +80620,7 @@
         <v>2</v>
       </c>
       <c r="G2970" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2971">
@@ -80647,7 +80647,7 @@
         <v>2</v>
       </c>
       <c r="G2971" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2972">
@@ -80674,7 +80674,7 @@
         <v>2</v>
       </c>
       <c r="G2972" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2973">
@@ -80701,7 +80701,7 @@
         <v>2</v>
       </c>
       <c r="G2973" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2974">
@@ -80728,7 +80728,7 @@
         <v>2</v>
       </c>
       <c r="G2974" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2975">
@@ -80755,7 +80755,7 @@
         <v>2</v>
       </c>
       <c r="G2975" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2976">
@@ -80782,7 +80782,7 @@
         <v>2</v>
       </c>
       <c r="G2976" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2977">
@@ -80809,7 +80809,7 @@
         <v>2</v>
       </c>
       <c r="G2977" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2978">
@@ -80836,7 +80836,7 @@
         <v>2</v>
       </c>
       <c r="G2978" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2979">
@@ -80863,7 +80863,7 @@
         <v>2</v>
       </c>
       <c r="G2979" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2980">
@@ -80890,7 +80890,7 @@
         <v>2</v>
       </c>
       <c r="G2980" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2981">
@@ -80917,7 +80917,7 @@
         <v>2</v>
       </c>
       <c r="G2981" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2982">
@@ -80944,7 +80944,7 @@
         <v>2</v>
       </c>
       <c r="G2982" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2983">
@@ -80971,7 +80971,7 @@
         <v>2</v>
       </c>
       <c r="G2983" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2984">
@@ -80998,7 +80998,7 @@
         <v>2</v>
       </c>
       <c r="G2984" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2985">
@@ -81025,7 +81025,7 @@
         <v>2</v>
       </c>
       <c r="G2985" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2986">
@@ -81052,7 +81052,7 @@
         <v>2</v>
       </c>
       <c r="G2986" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2987">
@@ -81079,7 +81079,7 @@
         <v>2</v>
       </c>
       <c r="G2987" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2988">
@@ -81106,7 +81106,7 @@
         <v>2</v>
       </c>
       <c r="G2988" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2989">
@@ -81133,7 +81133,7 @@
         <v>2</v>
       </c>
       <c r="G2989" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2990">
@@ -81160,7 +81160,7 @@
         <v>2</v>
       </c>
       <c r="G2990" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2991">
@@ -81187,7 +81187,7 @@
         <v>2</v>
       </c>
       <c r="G2991" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2992">
@@ -81214,7 +81214,7 @@
         <v>2</v>
       </c>
       <c r="G2992" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2993">
@@ -81241,7 +81241,7 @@
         <v>2</v>
       </c>
       <c r="G2993" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2994">
@@ -81268,7 +81268,7 @@
         <v>2</v>
       </c>
       <c r="G2994" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2995">
@@ -81295,7 +81295,7 @@
         <v>2</v>
       </c>
       <c r="G2995" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2996">
@@ -81322,7 +81322,7 @@
         <v>2</v>
       </c>
       <c r="G2996" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2997">
@@ -81349,7 +81349,7 @@
         <v>2</v>
       </c>
       <c r="G2997" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2998">
@@ -81376,7 +81376,7 @@
         <v>2</v>
       </c>
       <c r="G2998" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="2999">
@@ -81403,7 +81403,7 @@
         <v>2</v>
       </c>
       <c r="G2999" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3000">
@@ -81430,7 +81430,7 @@
         <v>2</v>
       </c>
       <c r="G3000" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3001">
@@ -81457,7 +81457,7 @@
         <v>2</v>
       </c>
       <c r="G3001" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3002">
@@ -81484,7 +81484,7 @@
         <v>2</v>
       </c>
       <c r="G3002" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3003">
@@ -81511,7 +81511,7 @@
         <v>2</v>
       </c>
       <c r="G3003" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3004">
@@ -81538,7 +81538,7 @@
         <v>2</v>
       </c>
       <c r="G3004" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3005">
@@ -81565,7 +81565,7 @@
         <v>2</v>
       </c>
       <c r="G3005" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3006">
@@ -81592,7 +81592,7 @@
         <v>2</v>
       </c>
       <c r="G3006" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3007">
@@ -81619,7 +81619,7 @@
         <v>2</v>
       </c>
       <c r="G3007" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3008">
@@ -81646,7 +81646,7 @@
         <v>2</v>
       </c>
       <c r="G3008" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3009">
@@ -81673,7 +81673,7 @@
         <v>2</v>
       </c>
       <c r="G3009" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3010">
@@ -81700,7 +81700,7 @@
         <v>2</v>
       </c>
       <c r="G3010" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3011">
@@ -81727,7 +81727,7 @@
         <v>2</v>
       </c>
       <c r="G3011" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3012">
@@ -81754,7 +81754,7 @@
         <v>2</v>
       </c>
       <c r="G3012" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3013">
@@ -81781,7 +81781,7 @@
         <v>2</v>
       </c>
       <c r="G3013" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3014">
@@ -81808,7 +81808,7 @@
         <v>2</v>
       </c>
       <c r="G3014" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3015">
@@ -81835,7 +81835,7 @@
         <v>2</v>
       </c>
       <c r="G3015" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3016">
@@ -81862,7 +81862,7 @@
         <v>2</v>
       </c>
       <c r="G3016" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3017">
@@ -81889,7 +81889,7 @@
         <v>2</v>
       </c>
       <c r="G3017" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3018">
@@ -81916,7 +81916,7 @@
         <v>2</v>
       </c>
       <c r="G3018" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3019">
@@ -81943,7 +81943,7 @@
         <v>2</v>
       </c>
       <c r="G3019" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3020">
@@ -81970,7 +81970,7 @@
         <v>2</v>
       </c>
       <c r="G3020" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3021">
@@ -81997,7 +81997,7 @@
         <v>2</v>
       </c>
       <c r="G3021" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3022">
@@ -82024,7 +82024,7 @@
         <v>2</v>
       </c>
       <c r="G3022" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3023">
@@ -82051,7 +82051,7 @@
         <v>2</v>
       </c>
       <c r="G3023" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3024">
@@ -82078,7 +82078,7 @@
         <v>2</v>
       </c>
       <c r="G3024" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3025">
@@ -82105,7 +82105,7 @@
         <v>2</v>
       </c>
       <c r="G3025" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3026">
@@ -82132,7 +82132,7 @@
         <v>2</v>
       </c>
       <c r="G3026" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3027">
@@ -82159,7 +82159,7 @@
         <v>2</v>
       </c>
       <c r="G3027" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3028">
@@ -82186,7 +82186,7 @@
         <v>2</v>
       </c>
       <c r="G3028" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3029">
@@ -82213,7 +82213,7 @@
         <v>2</v>
       </c>
       <c r="G3029" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3030">
@@ -82240,7 +82240,7 @@
         <v>2</v>
       </c>
       <c r="G3030" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3031">
@@ -82267,7 +82267,7 @@
         <v>2</v>
       </c>
       <c r="G3031" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3032">
@@ -82294,7 +82294,7 @@
         <v>2</v>
       </c>
       <c r="G3032" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3033">
@@ -82321,7 +82321,7 @@
         <v>2</v>
       </c>
       <c r="G3033" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3034">
@@ -82348,7 +82348,7 @@
         <v>2</v>
       </c>
       <c r="G3034" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3035">
@@ -82375,7 +82375,7 @@
         <v>2</v>
       </c>
       <c r="G3035" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3036">
@@ -82402,7 +82402,7 @@
         <v>2</v>
       </c>
       <c r="G3036" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3037">
@@ -82429,7 +82429,7 @@
         <v>2</v>
       </c>
       <c r="G3037" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3038">
@@ -82456,7 +82456,7 @@
         <v>2</v>
       </c>
       <c r="G3038" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3039">
@@ -82483,7 +82483,7 @@
         <v>2</v>
       </c>
       <c r="G3039" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3040">
@@ -82510,7 +82510,7 @@
         <v>2</v>
       </c>
       <c r="G3040" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3041">
@@ -82537,7 +82537,7 @@
         <v>2</v>
       </c>
       <c r="G3041" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3042">
@@ -82564,7 +82564,7 @@
         <v>2</v>
       </c>
       <c r="G3042" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3043">
@@ -82591,7 +82591,7 @@
         <v>2</v>
       </c>
       <c r="G3043" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3044">
@@ -82618,7 +82618,7 @@
         <v>2</v>
       </c>
       <c r="G3044" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3045">
@@ -82645,7 +82645,7 @@
         <v>2</v>
       </c>
       <c r="G3045" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3046">
@@ -82672,7 +82672,7 @@
         <v>2</v>
       </c>
       <c r="G3046" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3047">
@@ -82699,7 +82699,7 @@
         <v>2</v>
       </c>
       <c r="G3047" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3048">
@@ -82726,7 +82726,7 @@
         <v>2</v>
       </c>
       <c r="G3048" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3049">
@@ -82753,7 +82753,7 @@
         <v>2</v>
       </c>
       <c r="G3049" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3050">
@@ -82780,7 +82780,7 @@
         <v>2</v>
       </c>
       <c r="G3050" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3051">
@@ -82807,7 +82807,7 @@
         <v>2</v>
       </c>
       <c r="G3051" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3052">
@@ -82834,7 +82834,7 @@
         <v>2</v>
       </c>
       <c r="G3052" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3053">
@@ -82861,7 +82861,7 @@
         <v>2</v>
       </c>
       <c r="G3053" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3054">
@@ -82888,7 +82888,7 @@
         <v>2</v>
       </c>
       <c r="G3054" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3055">
@@ -82915,7 +82915,7 @@
         <v>2</v>
       </c>
       <c r="G3055" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3056">
@@ -82942,7 +82942,7 @@
         <v>2</v>
       </c>
       <c r="G3056" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3057">
@@ -82969,7 +82969,7 @@
         <v>2</v>
       </c>
       <c r="G3057" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3058">
@@ -82996,7 +82996,7 @@
         <v>2</v>
       </c>
       <c r="G3058" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3059">
@@ -83023,7 +83023,7 @@
         <v>2</v>
       </c>
       <c r="G3059" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3060">
@@ -83050,7 +83050,7 @@
         <v>2</v>
       </c>
       <c r="G3060" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3061">
@@ -83077,7 +83077,7 @@
         <v>2</v>
       </c>
       <c r="G3061" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3062">
@@ -83104,7 +83104,7 @@
         <v>2</v>
       </c>
       <c r="G3062" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3063">
@@ -83131,7 +83131,7 @@
         <v>2</v>
       </c>
       <c r="G3063" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3064">
@@ -83158,7 +83158,7 @@
         <v>2</v>
       </c>
       <c r="G3064" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3065">
@@ -83185,7 +83185,7 @@
         <v>2</v>
       </c>
       <c r="G3065" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3066">
@@ -83212,7 +83212,7 @@
         <v>2</v>
       </c>
       <c r="G3066" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3067">
@@ -83239,7 +83239,7 @@
         <v>2</v>
       </c>
       <c r="G3067" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3068">
@@ -83266,7 +83266,7 @@
         <v>2</v>
       </c>
       <c r="G3068" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3069">
@@ -83293,7 +83293,7 @@
         <v>2</v>
       </c>
       <c r="G3069" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3070">
@@ -83320,7 +83320,7 @@
         <v>2</v>
       </c>
       <c r="G3070" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3071">
@@ -83347,7 +83347,7 @@
         <v>2</v>
       </c>
       <c r="G3071" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3072">
@@ -83374,7 +83374,7 @@
         <v>2</v>
       </c>
       <c r="G3072" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3073">
@@ -83401,7 +83401,7 @@
         <v>2</v>
       </c>
       <c r="G3073" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3074">
@@ -83428,7 +83428,7 @@
         <v>2</v>
       </c>
       <c r="G3074" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3075">
@@ -83455,7 +83455,7 @@
         <v>2</v>
       </c>
       <c r="G3075" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3076">
@@ -83482,7 +83482,7 @@
         <v>2</v>
       </c>
       <c r="G3076" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3077">
@@ -83509,7 +83509,7 @@
         <v>2</v>
       </c>
       <c r="G3077" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3078">
@@ -83536,7 +83536,7 @@
         <v>2</v>
       </c>
       <c r="G3078" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3079">
@@ -83563,7 +83563,7 @@
         <v>2</v>
       </c>
       <c r="G3079" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3080">
@@ -83590,7 +83590,7 @@
         <v>2</v>
       </c>
       <c r="G3080" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3081">
@@ -83617,7 +83617,7 @@
         <v>2</v>
       </c>
       <c r="G3081" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3082">
@@ -83644,7 +83644,7 @@
         <v>2</v>
       </c>
       <c r="G3082" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3083">
@@ -83671,7 +83671,7 @@
         <v>2</v>
       </c>
       <c r="G3083" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3084">
@@ -83698,7 +83698,7 @@
         <v>2</v>
       </c>
       <c r="G3084" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3085">
@@ -83725,7 +83725,7 @@
         <v>2</v>
       </c>
       <c r="G3085" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3086">
@@ -83752,7 +83752,7 @@
         <v>2</v>
       </c>
       <c r="G3086" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3087">
@@ -83779,7 +83779,7 @@
         <v>2</v>
       </c>
       <c r="G3087" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3088">
@@ -83806,7 +83806,7 @@
         <v>2</v>
       </c>
       <c r="G3088" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3089">
@@ -83833,7 +83833,7 @@
         <v>2</v>
       </c>
       <c r="G3089" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3090">
@@ -83860,7 +83860,7 @@
         <v>2</v>
       </c>
       <c r="G3090" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3091">
@@ -83887,7 +83887,7 @@
         <v>2</v>
       </c>
       <c r="G3091" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3092">
@@ -83914,7 +83914,7 @@
         <v>2</v>
       </c>
       <c r="G3092" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3093">
@@ -83941,7 +83941,7 @@
         <v>2</v>
       </c>
       <c r="G3093" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3094">
@@ -83968,7 +83968,7 @@
         <v>2</v>
       </c>
       <c r="G3094" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3095">
@@ -83995,7 +83995,7 @@
         <v>2</v>
       </c>
       <c r="G3095" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3096">
@@ -84022,7 +84022,7 @@
         <v>2</v>
       </c>
       <c r="G3096" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3097">
@@ -84049,7 +84049,7 @@
         <v>2</v>
       </c>
       <c r="G3097" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3098">
@@ -84076,7 +84076,7 @@
         <v>2</v>
       </c>
       <c r="G3098" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3099">
@@ -84103,7 +84103,7 @@
         <v>2</v>
       </c>
       <c r="G3099" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3100">
@@ -84130,7 +84130,7 @@
         <v>2</v>
       </c>
       <c r="G3100" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3101">
@@ -84157,7 +84157,7 @@
         <v>2</v>
       </c>
       <c r="G3101" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3102">
@@ -84184,7 +84184,7 @@
         <v>2</v>
       </c>
       <c r="G3102" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3103">
@@ -84211,7 +84211,7 @@
         <v>2</v>
       </c>
       <c r="G3103" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3104">
@@ -84238,7 +84238,7 @@
         <v>2</v>
       </c>
       <c r="G3104" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3105">
@@ -84265,7 +84265,7 @@
         <v>2</v>
       </c>
       <c r="G3105" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3106">
@@ -84292,7 +84292,7 @@
         <v>2</v>
       </c>
       <c r="G3106" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3107">
@@ -84319,7 +84319,7 @@
         <v>2</v>
       </c>
       <c r="G3107" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3108">
@@ -84346,7 +84346,7 @@
         <v>2</v>
       </c>
       <c r="G3108" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3109">
@@ -84373,7 +84373,7 @@
         <v>2</v>
       </c>
       <c r="G3109" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3110">
@@ -84400,7 +84400,7 @@
         <v>2</v>
       </c>
       <c r="G3110" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3111">
@@ -84427,7 +84427,7 @@
         <v>2</v>
       </c>
       <c r="G3111" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3112">
@@ -84454,7 +84454,7 @@
         <v>2</v>
       </c>
       <c r="G3112" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3113">
@@ -84481,7 +84481,7 @@
         <v>2</v>
       </c>
       <c r="G3113" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3114">
@@ -84508,7 +84508,7 @@
         <v>2</v>
       </c>
       <c r="G3114" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3115">
@@ -84535,7 +84535,7 @@
         <v>2</v>
       </c>
       <c r="G3115" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3116">
@@ -84562,7 +84562,7 @@
         <v>2</v>
       </c>
       <c r="G3116" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3117">
@@ -84589,7 +84589,7 @@
         <v>2</v>
       </c>
       <c r="G3117" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3118">
@@ -84616,7 +84616,7 @@
         <v>2</v>
       </c>
       <c r="G3118" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3119">
@@ -84643,7 +84643,7 @@
         <v>2</v>
       </c>
       <c r="G3119" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3120">
@@ -84670,7 +84670,7 @@
         <v>2</v>
       </c>
       <c r="G3120" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3121">
@@ -84697,7 +84697,7 @@
         <v>2</v>
       </c>
       <c r="G3121" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3122">
@@ -84724,7 +84724,7 @@
         <v>2</v>
       </c>
       <c r="G3122" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3123">
@@ -84751,7 +84751,7 @@
         <v>2</v>
       </c>
       <c r="G3123" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3124">
@@ -84778,7 +84778,7 @@
         <v>2</v>
       </c>
       <c r="G3124" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3125">
@@ -84805,7 +84805,7 @@
         <v>2</v>
       </c>
       <c r="G3125" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3126">
@@ -84832,7 +84832,7 @@
         <v>2</v>
       </c>
       <c r="G3126" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3127">
@@ -84859,7 +84859,7 @@
         <v>2</v>
       </c>
       <c r="G3127" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3128">
@@ -84886,7 +84886,7 @@
         <v>2</v>
       </c>
       <c r="G3128" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3129">
@@ -84913,7 +84913,7 @@
         <v>2</v>
       </c>
       <c r="G3129" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3130">
@@ -84940,7 +84940,7 @@
         <v>2</v>
       </c>
       <c r="G3130" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3131">
@@ -84967,7 +84967,7 @@
         <v>2</v>
       </c>
       <c r="G3131" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3132">
@@ -84994,7 +84994,7 @@
         <v>2</v>
       </c>
       <c r="G3132" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3133">
@@ -85021,7 +85021,7 @@
         <v>2</v>
       </c>
       <c r="G3133" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3134">
@@ -85048,7 +85048,7 @@
         <v>2</v>
       </c>
       <c r="G3134" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3135">
@@ -85075,7 +85075,7 @@
         <v>2</v>
       </c>
       <c r="G3135" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3136">
@@ -85102,7 +85102,7 @@
         <v>2</v>
       </c>
       <c r="G3136" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3137">
@@ -85129,7 +85129,7 @@
         <v>2</v>
       </c>
       <c r="G3137" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3138">
@@ -85156,7 +85156,7 @@
         <v>2</v>
       </c>
       <c r="G3138" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3139">
@@ -85183,7 +85183,7 @@
         <v>2</v>
       </c>
       <c r="G3139" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3140">
@@ -85210,7 +85210,7 @@
         <v>2</v>
       </c>
       <c r="G3140" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3141">
@@ -85237,7 +85237,7 @@
         <v>2</v>
       </c>
       <c r="G3141" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3142">
@@ -85264,7 +85264,7 @@
         <v>2</v>
       </c>
       <c r="G3142" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3143">
@@ -85291,7 +85291,7 @@
         <v>2</v>
       </c>
       <c r="G3143" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3144">
@@ -85318,7 +85318,7 @@
         <v>2</v>
       </c>
       <c r="G3144" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3145">
@@ -85345,7 +85345,7 @@
         <v>2</v>
       </c>
       <c r="G3145" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3146">
@@ -85372,7 +85372,7 @@
         <v>2</v>
       </c>
       <c r="G3146" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3147">
@@ -85399,7 +85399,7 @@
         <v>2</v>
       </c>
       <c r="G3147" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3148">
@@ -85426,7 +85426,7 @@
         <v>2</v>
       </c>
       <c r="G3148" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3149">
@@ -85453,7 +85453,7 @@
         <v>2</v>
       </c>
       <c r="G3149" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3150">
@@ -85480,7 +85480,7 @@
         <v>2</v>
       </c>
       <c r="G3150" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3151">
@@ -85507,7 +85507,7 @@
         <v>2</v>
       </c>
       <c r="G3151" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3152">
@@ -85534,7 +85534,7 @@
         <v>2</v>
       </c>
       <c r="G3152" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3153">
@@ -85561,7 +85561,7 @@
         <v>2</v>
       </c>
       <c r="G3153" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3154">
@@ -85588,7 +85588,7 @@
         <v>2</v>
       </c>
       <c r="G3154" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3155">
@@ -85615,7 +85615,7 @@
         <v>2</v>
       </c>
       <c r="G3155" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3156">
@@ -85642,7 +85642,7 @@
         <v>2</v>
       </c>
       <c r="G3156" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3157">
@@ -85669,7 +85669,7 @@
         <v>2</v>
       </c>
       <c r="G3157" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3158">
@@ -85696,7 +85696,7 @@
         <v>2</v>
       </c>
       <c r="G3158" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3159">
@@ -85723,7 +85723,7 @@
         <v>2</v>
       </c>
       <c r="G3159" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3160">
@@ -85750,7 +85750,7 @@
         <v>2</v>
       </c>
       <c r="G3160" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3161">
@@ -85777,7 +85777,7 @@
         <v>2</v>
       </c>
       <c r="G3161" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3162">
@@ -85804,7 +85804,7 @@
         <v>2</v>
       </c>
       <c r="G3162" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3163">
@@ -85831,7 +85831,7 @@
         <v>2</v>
       </c>
       <c r="G3163" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3164">
@@ -85858,7 +85858,7 @@
         <v>2</v>
       </c>
       <c r="G3164" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3165">
@@ -85885,7 +85885,7 @@
         <v>2</v>
       </c>
       <c r="G3165" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3166">
@@ -85912,7 +85912,7 @@
         <v>2</v>
       </c>
       <c r="G3166" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3167">
@@ -85939,7 +85939,7 @@
         <v>2</v>
       </c>
       <c r="G3167" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3168">
@@ -85966,7 +85966,7 @@
         <v>2</v>
       </c>
       <c r="G3168" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3169">
@@ -85993,7 +85993,7 @@
         <v>2</v>
       </c>
       <c r="G3169" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3170">
@@ -86020,7 +86020,7 @@
         <v>2</v>
       </c>
       <c r="G3170" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3171">
@@ -86047,7 +86047,7 @@
         <v>2</v>
       </c>
       <c r="G3171" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3172">
@@ -86074,7 +86074,7 @@
         <v>2</v>
       </c>
       <c r="G3172" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3173">
@@ -86101,7 +86101,7 @@
         <v>2</v>
       </c>
       <c r="G3173" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3174">
@@ -86128,7 +86128,7 @@
         <v>2</v>
       </c>
       <c r="G3174" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3175">
@@ -86155,7 +86155,7 @@
         <v>2</v>
       </c>
       <c r="G3175" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3176">
@@ -86182,7 +86182,7 @@
         <v>2</v>
       </c>
       <c r="G3176" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3177">
@@ -86209,7 +86209,7 @@
         <v>2</v>
       </c>
       <c r="G3177" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3178">
@@ -86236,7 +86236,7 @@
         <v>2</v>
       </c>
       <c r="G3178" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3179">
@@ -86263,7 +86263,7 @@
         <v>2</v>
       </c>
       <c r="G3179" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3180">
@@ -86290,7 +86290,7 @@
         <v>2</v>
       </c>
       <c r="G3180" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3181">
@@ -86317,7 +86317,7 @@
         <v>2</v>
       </c>
       <c r="G3181" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3182">
@@ -86344,7 +86344,7 @@
         <v>2</v>
       </c>
       <c r="G3182" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3183">
@@ -86371,7 +86371,7 @@
         <v>2</v>
       </c>
       <c r="G3183" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3184">
@@ -86398,7 +86398,7 @@
         <v>2</v>
       </c>
       <c r="G3184" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3185">
@@ -86425,7 +86425,7 @@
         <v>2</v>
       </c>
       <c r="G3185" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3186">
@@ -86452,7 +86452,7 @@
         <v>2</v>
       </c>
       <c r="G3186" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3187">
@@ -86479,7 +86479,7 @@
         <v>2</v>
       </c>
       <c r="G3187" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3188">
@@ -86506,7 +86506,7 @@
         <v>2</v>
       </c>
       <c r="G3188" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3189">
@@ -86533,7 +86533,7 @@
         <v>2</v>
       </c>
       <c r="G3189" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3190">
@@ -86560,7 +86560,7 @@
         <v>2</v>
       </c>
       <c r="G3190" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3191">
@@ -86587,7 +86587,7 @@
         <v>2</v>
       </c>
       <c r="G3191" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3192">
@@ -86614,7 +86614,7 @@
         <v>2</v>
       </c>
       <c r="G3192" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3193">
@@ -86641,7 +86641,7 @@
         <v>2</v>
       </c>
       <c r="G3193" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3194">
@@ -86668,7 +86668,7 @@
         <v>2</v>
       </c>
       <c r="G3194" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3195">
@@ -86695,7 +86695,7 @@
         <v>2</v>
       </c>
       <c r="G3195" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3196">
@@ -86722,7 +86722,7 @@
         <v>2</v>
       </c>
       <c r="G3196" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3197">
@@ -86749,7 +86749,7 @@
         <v>2</v>
       </c>
       <c r="G3197" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3198">
@@ -86776,7 +86776,7 @@
         <v>2</v>
       </c>
       <c r="G3198" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3199">
@@ -86803,7 +86803,7 @@
         <v>2</v>
       </c>
       <c r="G3199" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3200">
@@ -86830,7 +86830,7 @@
         <v>2</v>
       </c>
       <c r="G3200" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3201">
@@ -86857,7 +86857,7 @@
         <v>2</v>
       </c>
       <c r="G3201" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3202">
@@ -86884,7 +86884,7 @@
         <v>2</v>
       </c>
       <c r="G3202" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3203">
@@ -86911,7 +86911,7 @@
         <v>2</v>
       </c>
       <c r="G3203" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3204">
@@ -86938,7 +86938,7 @@
         <v>2</v>
       </c>
       <c r="G3204" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3205">
@@ -86965,7 +86965,7 @@
         <v>2</v>
       </c>
       <c r="G3205" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3206">
@@ -86992,7 +86992,7 @@
         <v>2</v>
       </c>
       <c r="G3206" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3207">
@@ -87019,7 +87019,7 @@
         <v>2</v>
       </c>
       <c r="G3207" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3208">
@@ -87046,7 +87046,7 @@
         <v>2</v>
       </c>
       <c r="G3208" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3209">
@@ -87073,7 +87073,7 @@
         <v>2</v>
       </c>
       <c r="G3209" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3210">
@@ -87100,7 +87100,7 @@
         <v>2</v>
       </c>
       <c r="G3210" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3211">
@@ -87127,7 +87127,7 @@
         <v>2</v>
       </c>
       <c r="G3211" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3212">
@@ -87154,7 +87154,7 @@
         <v>2</v>
       </c>
       <c r="G3212" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3213">
@@ -87181,7 +87181,7 @@
         <v>2</v>
       </c>
       <c r="G3213" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3214">
@@ -87208,7 +87208,7 @@
         <v>2</v>
       </c>
       <c r="G3214" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3215">
@@ -87235,7 +87235,7 @@
         <v>2</v>
       </c>
       <c r="G3215" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3216">
@@ -87262,7 +87262,7 @@
         <v>2</v>
       </c>
       <c r="G3216" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3217">
@@ -87289,7 +87289,7 @@
         <v>2</v>
       </c>
       <c r="G3217" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3218">
@@ -87316,7 +87316,7 @@
         <v>2</v>
       </c>
       <c r="G3218" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3219">
@@ -87343,7 +87343,7 @@
         <v>2</v>
       </c>
       <c r="G3219" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3220">
@@ -87370,7 +87370,7 @@
         <v>2</v>
       </c>
       <c r="G3220" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3221">
@@ -87397,7 +87397,7 @@
         <v>2</v>
       </c>
       <c r="G3221" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3222">
@@ -87424,7 +87424,7 @@
         <v>2</v>
       </c>
       <c r="G3222" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3223">
@@ -87451,7 +87451,7 @@
         <v>2</v>
       </c>
       <c r="G3223" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3224">
@@ -87478,7 +87478,7 @@
         <v>2</v>
       </c>
       <c r="G3224" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3225">
@@ -87505,7 +87505,7 @@
         <v>2</v>
       </c>
       <c r="G3225" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3226">
@@ -87532,7 +87532,7 @@
         <v>2</v>
       </c>
       <c r="G3226" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3227">
@@ -87559,7 +87559,7 @@
         <v>2</v>
       </c>
       <c r="G3227" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3228">
@@ -87586,7 +87586,7 @@
         <v>2</v>
       </c>
       <c r="G3228" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3229">
@@ -87613,7 +87613,7 @@
         <v>2</v>
       </c>
       <c r="G3229" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3230">
@@ -87640,7 +87640,7 @@
         <v>2</v>
       </c>
       <c r="G3230" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3231">
@@ -87667,7 +87667,7 @@
         <v>2</v>
       </c>
       <c r="G3231" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3232">
@@ -87694,7 +87694,7 @@
         <v>2</v>
       </c>
       <c r="G3232" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3233">
@@ -87721,7 +87721,7 @@
         <v>2</v>
       </c>
       <c r="G3233" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3234">
@@ -87748,7 +87748,7 @@
         <v>2</v>
       </c>
       <c r="G3234" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3235">
@@ -87775,7 +87775,7 @@
         <v>2</v>
       </c>
       <c r="G3235" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3236">
@@ -87802,7 +87802,7 @@
         <v>2</v>
       </c>
       <c r="G3236" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3237">
@@ -87829,7 +87829,7 @@
         <v>2</v>
       </c>
       <c r="G3237" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3238">
@@ -87856,7 +87856,7 @@
         <v>2</v>
       </c>
       <c r="G3238" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3239">
@@ -87883,7 +87883,7 @@
         <v>2</v>
       </c>
       <c r="G3239" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3240">
@@ -87910,7 +87910,7 @@
         <v>2</v>
       </c>
       <c r="G3240" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3241">
@@ -87937,7 +87937,7 @@
         <v>2</v>
       </c>
       <c r="G3241" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3242">
@@ -87964,7 +87964,7 @@
         <v>2</v>
       </c>
       <c r="G3242" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3243">
@@ -87991,7 +87991,7 @@
         <v>2</v>
       </c>
       <c r="G3243" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3244">
@@ -88018,7 +88018,7 @@
         <v>2</v>
       </c>
       <c r="G3244" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3245">
@@ -88045,7 +88045,7 @@
         <v>2</v>
       </c>
       <c r="G3245" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3246">
@@ -88072,7 +88072,7 @@
         <v>2</v>
       </c>
       <c r="G3246" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3247">
@@ -88099,7 +88099,7 @@
         <v>2</v>
       </c>
       <c r="G3247" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3248">
@@ -88126,7 +88126,7 @@
         <v>2</v>
       </c>
       <c r="G3248" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3249">
@@ -88153,7 +88153,7 @@
         <v>2</v>
       </c>
       <c r="G3249" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3250">
@@ -88180,7 +88180,7 @@
         <v>2</v>
       </c>
       <c r="G3250" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3251">
@@ -88207,7 +88207,7 @@
         <v>2</v>
       </c>
       <c r="G3251" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3252">
@@ -88234,7 +88234,7 @@
         <v>2</v>
       </c>
       <c r="G3252" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3253">
@@ -88261,7 +88261,7 @@
         <v>2</v>
       </c>
       <c r="G3253" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3254">
@@ -88288,7 +88288,7 @@
         <v>2</v>
       </c>
       <c r="G3254" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3255">
@@ -88315,7 +88315,7 @@
         <v>2</v>
       </c>
       <c r="G3255" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3256">
@@ -88342,7 +88342,7 @@
         <v>2</v>
       </c>
       <c r="G3256" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3257">
@@ -88369,7 +88369,7 @@
         <v>2</v>
       </c>
       <c r="G3257" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3258">
@@ -88396,7 +88396,7 @@
         <v>2</v>
       </c>
       <c r="G3258" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3259">
@@ -88423,7 +88423,7 @@
         <v>2</v>
       </c>
       <c r="G3259" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3260">
@@ -88450,7 +88450,7 @@
         <v>2</v>
       </c>
       <c r="G3260" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3261">
@@ -88477,7 +88477,7 @@
         <v>2</v>
       </c>
       <c r="G3261" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3262">
@@ -88504,7 +88504,7 @@
         <v>2</v>
       </c>
       <c r="G3262" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3263">
@@ -88531,7 +88531,7 @@
         <v>2</v>
       </c>
       <c r="G3263" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3264">
@@ -88558,7 +88558,7 @@
         <v>2</v>
       </c>
       <c r="G3264" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
     <row r="3265">
@@ -88585,7 +88585,7 @@
         <v>2</v>
       </c>
       <c r="G3265" s="2" t="n">
-        <v>46278.46597506487</v>
+        <v>46278.85101434636</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3265"/>
+  <dimension ref="A1:G3289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80188,7 +80188,7 @@
         <v>2</v>
       </c>
       <c r="G2954" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2955">
@@ -80215,7 +80215,7 @@
         <v>2</v>
       </c>
       <c r="G2955" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2956">
@@ -80242,7 +80242,7 @@
         <v>2</v>
       </c>
       <c r="G2956" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2957">
@@ -80269,7 +80269,7 @@
         <v>2</v>
       </c>
       <c r="G2957" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2958">
@@ -80296,7 +80296,7 @@
         <v>2</v>
       </c>
       <c r="G2958" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2959">
@@ -80323,7 +80323,7 @@
         <v>2</v>
       </c>
       <c r="G2959" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2960">
@@ -80350,7 +80350,7 @@
         <v>2</v>
       </c>
       <c r="G2960" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2961">
@@ -80377,7 +80377,7 @@
         <v>2</v>
       </c>
       <c r="G2961" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2962">
@@ -80404,7 +80404,7 @@
         <v>2</v>
       </c>
       <c r="G2962" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2963">
@@ -80431,7 +80431,7 @@
         <v>2</v>
       </c>
       <c r="G2963" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2964">
@@ -80458,7 +80458,7 @@
         <v>2</v>
       </c>
       <c r="G2964" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2965">
@@ -80485,7 +80485,7 @@
         <v>2</v>
       </c>
       <c r="G2965" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2966">
@@ -80496,7 +80496,7 @@
         <v>13</v>
       </c>
       <c r="C2966" t="n">
-        <v>26.51</v>
+        <v>26.5</v>
       </c>
       <c r="D2966" t="inlineStr">
         <is>
@@ -80512,7 +80512,7 @@
         <v>2</v>
       </c>
       <c r="G2966" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2967">
@@ -80539,7 +80539,7 @@
         <v>2</v>
       </c>
       <c r="G2967" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2968">
@@ -80566,7 +80566,7 @@
         <v>2</v>
       </c>
       <c r="G2968" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2969">
@@ -80593,7 +80593,7 @@
         <v>2</v>
       </c>
       <c r="G2969" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2970">
@@ -80620,7 +80620,7 @@
         <v>2</v>
       </c>
       <c r="G2970" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2971">
@@ -80647,7 +80647,7 @@
         <v>2</v>
       </c>
       <c r="G2971" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2972">
@@ -80658,7 +80658,7 @@
         <v>19</v>
       </c>
       <c r="C2972" t="n">
-        <v>21.76</v>
+        <v>21.75</v>
       </c>
       <c r="D2972" t="inlineStr">
         <is>
@@ -80674,7 +80674,7 @@
         <v>2</v>
       </c>
       <c r="G2972" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2973">
@@ -80701,7 +80701,7 @@
         <v>2</v>
       </c>
       <c r="G2973" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2974">
@@ -80728,7 +80728,7 @@
         <v>2</v>
       </c>
       <c r="G2974" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2975">
@@ -80755,7 +80755,7 @@
         <v>2</v>
       </c>
       <c r="G2975" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2976">
@@ -80782,7 +80782,7 @@
         <v>2</v>
       </c>
       <c r="G2976" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2977">
@@ -80809,7 +80809,7 @@
         <v>2</v>
       </c>
       <c r="G2977" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2978">
@@ -80836,7 +80836,7 @@
         <v>2</v>
       </c>
       <c r="G2978" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2979">
@@ -80863,7 +80863,7 @@
         <v>2</v>
       </c>
       <c r="G2979" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2980">
@@ -80874,7 +80874,7 @@
         <v>3</v>
       </c>
       <c r="C2980" t="n">
-        <v>9.35</v>
+        <v>9.34</v>
       </c>
       <c r="D2980" t="inlineStr">
         <is>
@@ -80890,7 +80890,7 @@
         <v>2</v>
       </c>
       <c r="G2980" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2981">
@@ -80917,7 +80917,7 @@
         <v>2</v>
       </c>
       <c r="G2981" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2982">
@@ -80944,7 +80944,7 @@
         <v>2</v>
       </c>
       <c r="G2982" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2983">
@@ -80971,7 +80971,7 @@
         <v>2</v>
       </c>
       <c r="G2983" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2984">
@@ -80998,7 +80998,7 @@
         <v>2</v>
       </c>
       <c r="G2984" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2985">
@@ -81025,7 +81025,7 @@
         <v>2</v>
       </c>
       <c r="G2985" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2986">
@@ -81052,7 +81052,7 @@
         <v>2</v>
       </c>
       <c r="G2986" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2987">
@@ -81079,7 +81079,7 @@
         <v>2</v>
       </c>
       <c r="G2987" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2988">
@@ -81090,7 +81090,7 @@
         <v>11</v>
       </c>
       <c r="C2988" t="n">
-        <v>19.72</v>
+        <v>19.71</v>
       </c>
       <c r="D2988" t="inlineStr">
         <is>
@@ -81106,7 +81106,7 @@
         <v>2</v>
       </c>
       <c r="G2988" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2989">
@@ -81133,7 +81133,7 @@
         <v>2</v>
       </c>
       <c r="G2989" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2990">
@@ -81160,7 +81160,7 @@
         <v>2</v>
       </c>
       <c r="G2990" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2991">
@@ -81187,7 +81187,7 @@
         <v>2</v>
       </c>
       <c r="G2991" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2992">
@@ -81214,7 +81214,7 @@
         <v>2</v>
       </c>
       <c r="G2992" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2993">
@@ -81241,7 +81241,7 @@
         <v>2</v>
       </c>
       <c r="G2993" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2994">
@@ -81252,7 +81252,7 @@
         <v>17</v>
       </c>
       <c r="C2994" t="n">
-        <v>31.1</v>
+        <v>31.09</v>
       </c>
       <c r="D2994" t="inlineStr">
         <is>
@@ -81268,7 +81268,7 @@
         <v>2</v>
       </c>
       <c r="G2994" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2995">
@@ -81295,7 +81295,7 @@
         <v>2</v>
       </c>
       <c r="G2995" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2996">
@@ -81322,7 +81322,7 @@
         <v>2</v>
       </c>
       <c r="G2996" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2997">
@@ -81349,7 +81349,7 @@
         <v>2</v>
       </c>
       <c r="G2997" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2998">
@@ -81376,7 +81376,7 @@
         <v>2</v>
       </c>
       <c r="G2998" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="2999">
@@ -81403,7 +81403,7 @@
         <v>2</v>
       </c>
       <c r="G2999" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3000">
@@ -81430,7 +81430,7 @@
         <v>2</v>
       </c>
       <c r="G3000" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3001">
@@ -81457,7 +81457,7 @@
         <v>2</v>
       </c>
       <c r="G3001" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3002">
@@ -81484,7 +81484,7 @@
         <v>2</v>
       </c>
       <c r="G3002" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3003">
@@ -81511,7 +81511,7 @@
         <v>2</v>
       </c>
       <c r="G3003" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3004">
@@ -81538,7 +81538,7 @@
         <v>2</v>
       </c>
       <c r="G3004" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3005">
@@ -81565,7 +81565,7 @@
         <v>2</v>
       </c>
       <c r="G3005" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3006">
@@ -81592,7 +81592,7 @@
         <v>2</v>
       </c>
       <c r="G3006" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3007">
@@ -81603,7 +81603,7 @@
         <v>6</v>
       </c>
       <c r="C3007" t="n">
-        <v>15.38</v>
+        <v>15.37</v>
       </c>
       <c r="D3007" t="inlineStr">
         <is>
@@ -81619,7 +81619,7 @@
         <v>2</v>
       </c>
       <c r="G3007" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3008">
@@ -81646,7 +81646,7 @@
         <v>2</v>
       </c>
       <c r="G3008" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3009">
@@ -81673,7 +81673,7 @@
         <v>2</v>
       </c>
       <c r="G3009" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3010">
@@ -81700,7 +81700,7 @@
         <v>2</v>
       </c>
       <c r="G3010" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3011">
@@ -81711,7 +81711,7 @@
         <v>10</v>
       </c>
       <c r="C3011" t="n">
-        <v>24.88</v>
+        <v>24.87</v>
       </c>
       <c r="D3011" t="inlineStr">
         <is>
@@ -81727,7 +81727,7 @@
         <v>2</v>
       </c>
       <c r="G3011" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3012">
@@ -81754,7 +81754,7 @@
         <v>2</v>
       </c>
       <c r="G3012" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3013">
@@ -81781,7 +81781,7 @@
         <v>2</v>
       </c>
       <c r="G3013" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3014">
@@ -81808,7 +81808,7 @@
         <v>2</v>
       </c>
       <c r="G3014" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3015">
@@ -81835,7 +81835,7 @@
         <v>2</v>
       </c>
       <c r="G3015" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3016">
@@ -81846,7 +81846,7 @@
         <v>15</v>
       </c>
       <c r="C3016" t="n">
-        <v>22.2</v>
+        <v>22.19</v>
       </c>
       <c r="D3016" t="inlineStr">
         <is>
@@ -81862,7 +81862,7 @@
         <v>2</v>
       </c>
       <c r="G3016" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3017">
@@ -81889,7 +81889,7 @@
         <v>2</v>
       </c>
       <c r="G3017" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3018">
@@ -81916,7 +81916,7 @@
         <v>2</v>
       </c>
       <c r="G3018" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3019">
@@ -81943,7 +81943,7 @@
         <v>2</v>
       </c>
       <c r="G3019" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3020">
@@ -81970,7 +81970,7 @@
         <v>2</v>
       </c>
       <c r="G3020" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3021">
@@ -81997,7 +81997,7 @@
         <v>2</v>
       </c>
       <c r="G3021" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3022">
@@ -82024,7 +82024,7 @@
         <v>2</v>
       </c>
       <c r="G3022" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3023">
@@ -82051,7 +82051,7 @@
         <v>2</v>
       </c>
       <c r="G3023" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3024">
@@ -82078,7 +82078,7 @@
         <v>2</v>
       </c>
       <c r="G3024" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3025">
@@ -82105,7 +82105,7 @@
         <v>2</v>
       </c>
       <c r="G3025" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3026">
@@ -82132,7 +82132,7 @@
         <v>2</v>
       </c>
       <c r="G3026" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3027">
@@ -82159,7 +82159,7 @@
         <v>2</v>
       </c>
       <c r="G3027" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3028">
@@ -82186,7 +82186,7 @@
         <v>2</v>
       </c>
       <c r="G3028" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3029">
@@ -82213,7 +82213,7 @@
         <v>2</v>
       </c>
       <c r="G3029" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3030">
@@ -82240,7 +82240,7 @@
         <v>2</v>
       </c>
       <c r="G3030" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3031">
@@ -82267,7 +82267,7 @@
         <v>2</v>
       </c>
       <c r="G3031" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3032">
@@ -82294,7 +82294,7 @@
         <v>2</v>
       </c>
       <c r="G3032" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3033">
@@ -82321,7 +82321,7 @@
         <v>2</v>
       </c>
       <c r="G3033" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3034">
@@ -82348,7 +82348,7 @@
         <v>2</v>
       </c>
       <c r="G3034" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3035">
@@ -82375,7 +82375,7 @@
         <v>2</v>
       </c>
       <c r="G3035" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3036">
@@ -82386,7 +82386,7 @@
         <v>11</v>
       </c>
       <c r="C3036" t="n">
-        <v>21.29</v>
+        <v>21.28</v>
       </c>
       <c r="D3036" t="inlineStr">
         <is>
@@ -82402,7 +82402,7 @@
         <v>2</v>
       </c>
       <c r="G3036" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3037">
@@ -82429,7 +82429,7 @@
         <v>2</v>
       </c>
       <c r="G3037" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3038">
@@ -82456,7 +82456,7 @@
         <v>2</v>
       </c>
       <c r="G3038" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3039">
@@ -82483,7 +82483,7 @@
         <v>2</v>
       </c>
       <c r="G3039" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3040">
@@ -82510,7 +82510,7 @@
         <v>2</v>
       </c>
       <c r="G3040" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3041">
@@ -82521,7 +82521,7 @@
         <v>16</v>
       </c>
       <c r="C3041" t="n">
-        <v>12.67</v>
+        <v>12.66</v>
       </c>
       <c r="D3041" t="inlineStr">
         <is>
@@ -82537,7 +82537,7 @@
         <v>2</v>
       </c>
       <c r="G3041" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3042">
@@ -82564,7 +82564,7 @@
         <v>2</v>
       </c>
       <c r="G3042" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3043">
@@ -82591,7 +82591,7 @@
         <v>2</v>
       </c>
       <c r="G3043" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3044">
@@ -82618,7 +82618,7 @@
         <v>2</v>
       </c>
       <c r="G3044" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3045">
@@ -82629,7 +82629,7 @@
         <v>20</v>
       </c>
       <c r="C3045" t="n">
-        <v>27.96</v>
+        <v>27.97</v>
       </c>
       <c r="D3045" t="inlineStr">
         <is>
@@ -82645,7 +82645,7 @@
         <v>2</v>
       </c>
       <c r="G3045" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3046">
@@ -82672,7 +82672,7 @@
         <v>2</v>
       </c>
       <c r="G3046" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3047">
@@ -82699,7 +82699,7 @@
         <v>2</v>
       </c>
       <c r="G3047" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3048">
@@ -82726,7 +82726,7 @@
         <v>2</v>
       </c>
       <c r="G3048" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3049">
@@ -82753,7 +82753,7 @@
         <v>2</v>
       </c>
       <c r="G3049" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3050">
@@ -82780,7 +82780,7 @@
         <v>2</v>
       </c>
       <c r="G3050" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3051">
@@ -82807,7 +82807,7 @@
         <v>2</v>
       </c>
       <c r="G3051" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3052">
@@ -82834,7 +82834,7 @@
         <v>2</v>
       </c>
       <c r="G3052" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3053">
@@ -82861,7 +82861,7 @@
         <v>2</v>
       </c>
       <c r="G3053" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3054">
@@ -82888,7 +82888,7 @@
         <v>2</v>
       </c>
       <c r="G3054" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3055">
@@ -82915,7 +82915,7 @@
         <v>2</v>
       </c>
       <c r="G3055" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3056">
@@ -82942,7 +82942,7 @@
         <v>2</v>
       </c>
       <c r="G3056" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3057">
@@ -82969,7 +82969,7 @@
         <v>2</v>
       </c>
       <c r="G3057" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3058">
@@ -82996,7 +82996,7 @@
         <v>2</v>
       </c>
       <c r="G3058" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3059">
@@ -83023,7 +83023,7 @@
         <v>2</v>
       </c>
       <c r="G3059" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3060">
@@ -83034,7 +83034,7 @@
         <v>11</v>
       </c>
       <c r="C3060" t="n">
-        <v>18.46</v>
+        <v>18.45</v>
       </c>
       <c r="D3060" t="inlineStr">
         <is>
@@ -83050,7 +83050,7 @@
         <v>2</v>
       </c>
       <c r="G3060" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3061">
@@ -83077,7 +83077,7 @@
         <v>2</v>
       </c>
       <c r="G3061" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3062">
@@ -83104,7 +83104,7 @@
         <v>2</v>
       </c>
       <c r="G3062" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3063">
@@ -83115,7 +83115,7 @@
         <v>14</v>
       </c>
       <c r="C3063" t="n">
-        <v>14.3</v>
+        <v>14.29</v>
       </c>
       <c r="D3063" t="inlineStr">
         <is>
@@ -83131,7 +83131,7 @@
         <v>2</v>
       </c>
       <c r="G3063" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3064">
@@ -83158,7 +83158,7 @@
         <v>2</v>
       </c>
       <c r="G3064" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3065">
@@ -83169,7 +83169,7 @@
         <v>16</v>
       </c>
       <c r="C3065" t="n">
-        <v>20.9</v>
+        <v>20.89</v>
       </c>
       <c r="D3065" t="inlineStr">
         <is>
@@ -83185,7 +83185,7 @@
         <v>2</v>
       </c>
       <c r="G3065" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3066">
@@ -83212,7 +83212,7 @@
         <v>2</v>
       </c>
       <c r="G3066" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3067">
@@ -83223,7 +83223,7 @@
         <v>18</v>
       </c>
       <c r="C3067" t="n">
-        <v>12.07</v>
+        <v>12.06</v>
       </c>
       <c r="D3067" t="inlineStr">
         <is>
@@ -83239,7 +83239,7 @@
         <v>2</v>
       </c>
       <c r="G3067" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3068">
@@ -83250,7 +83250,7 @@
         <v>19</v>
       </c>
       <c r="C3068" t="n">
-        <v>30.09</v>
+        <v>30.08</v>
       </c>
       <c r="D3068" t="inlineStr">
         <is>
@@ -83266,7 +83266,7 @@
         <v>2</v>
       </c>
       <c r="G3068" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3069">
@@ -83277,7 +83277,7 @@
         <v>20</v>
       </c>
       <c r="C3069" t="n">
-        <v>37.63</v>
+        <v>37.62</v>
       </c>
       <c r="D3069" t="inlineStr">
         <is>
@@ -83293,7 +83293,7 @@
         <v>2</v>
       </c>
       <c r="G3069" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3070">
@@ -83304,7 +83304,7 @@
         <v>21</v>
       </c>
       <c r="C3070" t="n">
-        <v>36.85</v>
+        <v>36.84</v>
       </c>
       <c r="D3070" t="inlineStr">
         <is>
@@ -83320,7 +83320,7 @@
         <v>2</v>
       </c>
       <c r="G3070" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3071">
@@ -83347,7 +83347,7 @@
         <v>2</v>
       </c>
       <c r="G3071" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3072">
@@ -83358,7 +83358,7 @@
         <v>23</v>
       </c>
       <c r="C3072" t="n">
-        <v>25.05</v>
+        <v>25.04</v>
       </c>
       <c r="D3072" t="inlineStr">
         <is>
@@ -83374,7 +83374,7 @@
         <v>2</v>
       </c>
       <c r="G3072" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3073">
@@ -83385,7 +83385,7 @@
         <v>24</v>
       </c>
       <c r="C3073" t="n">
-        <v>26.62</v>
+        <v>26.61</v>
       </c>
       <c r="D3073" t="inlineStr">
         <is>
@@ -83401,7 +83401,7 @@
         <v>2</v>
       </c>
       <c r="G3073" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3074">
@@ -83428,7 +83428,7 @@
         <v>2</v>
       </c>
       <c r="G3074" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3075">
@@ -83439,7 +83439,7 @@
         <v>2</v>
       </c>
       <c r="C3075" t="n">
-        <v>8.65</v>
+        <v>8.6</v>
       </c>
       <c r="D3075" t="inlineStr">
         <is>
@@ -83455,7 +83455,7 @@
         <v>2</v>
       </c>
       <c r="G3075" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3076">
@@ -83466,7 +83466,7 @@
         <v>3</v>
       </c>
       <c r="C3076" t="n">
-        <v>8.34</v>
+        <v>8.33</v>
       </c>
       <c r="D3076" t="inlineStr">
         <is>
@@ -83482,7 +83482,7 @@
         <v>2</v>
       </c>
       <c r="G3076" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3077">
@@ -83509,7 +83509,7 @@
         <v>2</v>
       </c>
       <c r="G3077" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3078">
@@ -83536,7 +83536,7 @@
         <v>2</v>
       </c>
       <c r="G3078" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3079">
@@ -83563,7 +83563,7 @@
         <v>2</v>
       </c>
       <c r="G3079" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3080">
@@ -83590,7 +83590,7 @@
         <v>2</v>
       </c>
       <c r="G3080" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3081">
@@ -83601,7 +83601,7 @@
         <v>8</v>
       </c>
       <c r="C3081" t="n">
-        <v>24.69</v>
+        <v>24.68</v>
       </c>
       <c r="D3081" t="inlineStr">
         <is>
@@ -83617,7 +83617,7 @@
         <v>2</v>
       </c>
       <c r="G3081" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3082">
@@ -83628,7 +83628,7 @@
         <v>9</v>
       </c>
       <c r="C3082" t="n">
-        <v>25.83</v>
+        <v>25.82</v>
       </c>
       <c r="D3082" t="inlineStr">
         <is>
@@ -83644,7 +83644,7 @@
         <v>2</v>
       </c>
       <c r="G3082" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3083">
@@ -83655,7 +83655,7 @@
         <v>10</v>
       </c>
       <c r="C3083" t="n">
-        <v>24.19</v>
+        <v>24.18</v>
       </c>
       <c r="D3083" t="inlineStr">
         <is>
@@ -83671,7 +83671,7 @@
         <v>2</v>
       </c>
       <c r="G3083" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3084">
@@ -83698,7 +83698,7 @@
         <v>2</v>
       </c>
       <c r="G3084" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3085">
@@ -83725,7 +83725,7 @@
         <v>2</v>
       </c>
       <c r="G3085" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3086">
@@ -83752,7 +83752,7 @@
         <v>2</v>
       </c>
       <c r="G3086" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3087">
@@ -83779,7 +83779,7 @@
         <v>2</v>
       </c>
       <c r="G3087" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3088">
@@ -83790,7 +83790,7 @@
         <v>15</v>
       </c>
       <c r="C3088" t="n">
-        <v>20.88</v>
+        <v>20.87</v>
       </c>
       <c r="D3088" t="inlineStr">
         <is>
@@ -83806,7 +83806,7 @@
         <v>2</v>
       </c>
       <c r="G3088" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3089">
@@ -83833,7 +83833,7 @@
         <v>2</v>
       </c>
       <c r="G3089" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3090">
@@ -83860,7 +83860,7 @@
         <v>2</v>
       </c>
       <c r="G3090" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3091">
@@ -83887,7 +83887,7 @@
         <v>2</v>
       </c>
       <c r="G3091" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3092">
@@ -83898,7 +83898,7 @@
         <v>19</v>
       </c>
       <c r="C3092" t="n">
-        <v>30.91</v>
+        <v>30.89</v>
       </c>
       <c r="D3092" t="inlineStr">
         <is>
@@ -83914,7 +83914,7 @@
         <v>2</v>
       </c>
       <c r="G3092" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3093">
@@ -83925,7 +83925,7 @@
         <v>20</v>
       </c>
       <c r="C3093" t="n">
-        <v>29.34</v>
+        <v>29.31</v>
       </c>
       <c r="D3093" t="inlineStr">
         <is>
@@ -83941,7 +83941,7 @@
         <v>2</v>
       </c>
       <c r="G3093" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3094">
@@ -83952,7 +83952,7 @@
         <v>21</v>
       </c>
       <c r="C3094" t="n">
-        <v>38</v>
+        <v>37.99</v>
       </c>
       <c r="D3094" t="inlineStr">
         <is>
@@ -83968,7 +83968,7 @@
         <v>2</v>
       </c>
       <c r="G3094" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3095">
@@ -83979,7 +83979,7 @@
         <v>22</v>
       </c>
       <c r="C3095" t="n">
-        <v>37.11</v>
+        <v>37.1</v>
       </c>
       <c r="D3095" t="inlineStr">
         <is>
@@ -83995,7 +83995,7 @@
         <v>2</v>
       </c>
       <c r="G3095" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3096">
@@ -84006,7 +84006,7 @@
         <v>23</v>
       </c>
       <c r="C3096" t="n">
-        <v>21.84</v>
+        <v>21.83</v>
       </c>
       <c r="D3096" t="inlineStr">
         <is>
@@ -84022,7 +84022,7 @@
         <v>2</v>
       </c>
       <c r="G3096" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3097">
@@ -84033,7 +84033,7 @@
         <v>24</v>
       </c>
       <c r="C3097" t="n">
-        <v>24.56</v>
+        <v>24.55</v>
       </c>
       <c r="D3097" t="inlineStr">
         <is>
@@ -84049,7 +84049,7 @@
         <v>2</v>
       </c>
       <c r="G3097" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3098">
@@ -84060,7 +84060,7 @@
         <v>1</v>
       </c>
       <c r="C3098" t="n">
-        <v>9.41</v>
+        <v>9.4</v>
       </c>
       <c r="D3098" t="inlineStr">
         <is>
@@ -84076,7 +84076,7 @@
         <v>2</v>
       </c>
       <c r="G3098" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3099">
@@ -84087,7 +84087,7 @@
         <v>2</v>
       </c>
       <c r="C3099" t="n">
-        <v>12.33</v>
+        <v>12.31</v>
       </c>
       <c r="D3099" t="inlineStr">
         <is>
@@ -84103,7 +84103,7 @@
         <v>2</v>
       </c>
       <c r="G3099" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3100">
@@ -84114,7 +84114,7 @@
         <v>3</v>
       </c>
       <c r="C3100" t="n">
-        <v>9.640000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="D3100" t="inlineStr">
         <is>
@@ -84130,7 +84130,7 @@
         <v>2</v>
       </c>
       <c r="G3100" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3101">
@@ -84157,7 +84157,7 @@
         <v>2</v>
       </c>
       <c r="G3101" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3102">
@@ -84184,7 +84184,7 @@
         <v>2</v>
       </c>
       <c r="G3102" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3103">
@@ -84211,7 +84211,7 @@
         <v>2</v>
       </c>
       <c r="G3103" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3104">
@@ -84238,7 +84238,7 @@
         <v>2</v>
       </c>
       <c r="G3104" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3105">
@@ -84249,7 +84249,7 @@
         <v>8</v>
       </c>
       <c r="C3105" t="n">
-        <v>50.37</v>
+        <v>50.35</v>
       </c>
       <c r="D3105" t="inlineStr">
         <is>
@@ -84265,7 +84265,7 @@
         <v>2</v>
       </c>
       <c r="G3105" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3106">
@@ -84276,7 +84276,7 @@
         <v>9</v>
       </c>
       <c r="C3106" t="n">
-        <v>50.2</v>
+        <v>50.18</v>
       </c>
       <c r="D3106" t="inlineStr">
         <is>
@@ -84292,7 +84292,7 @@
         <v>2</v>
       </c>
       <c r="G3106" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3107">
@@ -84319,7 +84319,7 @@
         <v>2</v>
       </c>
       <c r="G3107" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3108">
@@ -84346,7 +84346,7 @@
         <v>2</v>
       </c>
       <c r="G3108" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3109">
@@ -84357,7 +84357,7 @@
         <v>12</v>
       </c>
       <c r="C3109" t="n">
-        <v>20.39</v>
+        <v>20.38</v>
       </c>
       <c r="D3109" t="inlineStr">
         <is>
@@ -84373,7 +84373,7 @@
         <v>2</v>
       </c>
       <c r="G3109" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3110">
@@ -84384,7 +84384,7 @@
         <v>13</v>
       </c>
       <c r="C3110" t="n">
-        <v>21.74</v>
+        <v>21.72</v>
       </c>
       <c r="D3110" t="inlineStr">
         <is>
@@ -84400,7 +84400,7 @@
         <v>2</v>
       </c>
       <c r="G3110" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3111">
@@ -84411,7 +84411,7 @@
         <v>14</v>
       </c>
       <c r="C3111" t="n">
-        <v>21.71</v>
+        <v>21.72</v>
       </c>
       <c r="D3111" t="inlineStr">
         <is>
@@ -84427,7 +84427,7 @@
         <v>2</v>
       </c>
       <c r="G3111" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3112">
@@ -84438,7 +84438,7 @@
         <v>15</v>
       </c>
       <c r="C3112" t="n">
-        <v>22.86</v>
+        <v>22.85</v>
       </c>
       <c r="D3112" t="inlineStr">
         <is>
@@ -84454,7 +84454,7 @@
         <v>2</v>
       </c>
       <c r="G3112" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3113">
@@ -84465,7 +84465,7 @@
         <v>16</v>
       </c>
       <c r="C3113" t="n">
-        <v>23.52</v>
+        <v>23.48</v>
       </c>
       <c r="D3113" t="inlineStr">
         <is>
@@ -84481,7 +84481,7 @@
         <v>2</v>
       </c>
       <c r="G3113" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3114">
@@ -84492,7 +84492,7 @@
         <v>17</v>
       </c>
       <c r="C3114" t="n">
-        <v>22.78</v>
+        <v>22.76</v>
       </c>
       <c r="D3114" t="inlineStr">
         <is>
@@ -84508,7 +84508,7 @@
         <v>2</v>
       </c>
       <c r="G3114" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3115">
@@ -84519,7 +84519,7 @@
         <v>18</v>
       </c>
       <c r="C3115" t="n">
-        <v>21.17</v>
+        <v>21.15</v>
       </c>
       <c r="D3115" t="inlineStr">
         <is>
@@ -84535,7 +84535,7 @@
         <v>2</v>
       </c>
       <c r="G3115" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3116">
@@ -84546,7 +84546,7 @@
         <v>19</v>
       </c>
       <c r="C3116" t="n">
-        <v>24.26</v>
+        <v>24.25</v>
       </c>
       <c r="D3116" t="inlineStr">
         <is>
@@ -84562,7 +84562,7 @@
         <v>2</v>
       </c>
       <c r="G3116" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3117">
@@ -84573,7 +84573,7 @@
         <v>20</v>
       </c>
       <c r="C3117" t="n">
-        <v>29.97</v>
+        <v>29.96</v>
       </c>
       <c r="D3117" t="inlineStr">
         <is>
@@ -84589,7 +84589,7 @@
         <v>2</v>
       </c>
       <c r="G3117" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3118">
@@ -84616,7 +84616,7 @@
         <v>2</v>
       </c>
       <c r="G3118" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3119">
@@ -84643,7 +84643,7 @@
         <v>2</v>
       </c>
       <c r="G3119" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3120">
@@ -84654,7 +84654,7 @@
         <v>23</v>
       </c>
       <c r="C3120" t="n">
-        <v>31.98</v>
+        <v>31.97</v>
       </c>
       <c r="D3120" t="inlineStr">
         <is>
@@ -84670,7 +84670,7 @@
         <v>2</v>
       </c>
       <c r="G3120" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3121">
@@ -84681,7 +84681,7 @@
         <v>24</v>
       </c>
       <c r="C3121" t="n">
-        <v>34.03</v>
+        <v>34.02</v>
       </c>
       <c r="D3121" t="inlineStr">
         <is>
@@ -84697,7 +84697,7 @@
         <v>2</v>
       </c>
       <c r="G3121" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3122">
@@ -84708,7 +84708,7 @@
         <v>1</v>
       </c>
       <c r="C3122" t="n">
-        <v>9.699999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="D3122" t="inlineStr">
         <is>
@@ -84724,7 +84724,7 @@
         <v>2</v>
       </c>
       <c r="G3122" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3123">
@@ -84735,7 +84735,7 @@
         <v>2</v>
       </c>
       <c r="C3123" t="n">
-        <v>12.39</v>
+        <v>12.38</v>
       </c>
       <c r="D3123" t="inlineStr">
         <is>
@@ -84751,7 +84751,7 @@
         <v>2</v>
       </c>
       <c r="G3123" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3124">
@@ -84762,7 +84762,7 @@
         <v>3</v>
       </c>
       <c r="C3124" t="n">
-        <v>10.99</v>
+        <v>10.97</v>
       </c>
       <c r="D3124" t="inlineStr">
         <is>
@@ -84778,7 +84778,7 @@
         <v>2</v>
       </c>
       <c r="G3124" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3125">
@@ -84789,7 +84789,7 @@
         <v>4</v>
       </c>
       <c r="C3125" t="n">
-        <v>10.59</v>
+        <v>10.58</v>
       </c>
       <c r="D3125" t="inlineStr">
         <is>
@@ -84805,7 +84805,7 @@
         <v>2</v>
       </c>
       <c r="G3125" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3126">
@@ -84816,7 +84816,7 @@
         <v>5</v>
       </c>
       <c r="C3126" t="n">
-        <v>11.04</v>
+        <v>11.03</v>
       </c>
       <c r="D3126" t="inlineStr">
         <is>
@@ -84832,7 +84832,7 @@
         <v>2</v>
       </c>
       <c r="G3126" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3127">
@@ -84843,7 +84843,7 @@
         <v>6</v>
       </c>
       <c r="C3127" t="n">
-        <v>14</v>
+        <v>13.99</v>
       </c>
       <c r="D3127" t="inlineStr">
         <is>
@@ -84859,7 +84859,7 @@
         <v>2</v>
       </c>
       <c r="G3127" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3128">
@@ -84870,7 +84870,7 @@
         <v>7</v>
       </c>
       <c r="C3128" t="n">
-        <v>20.06</v>
+        <v>19.99</v>
       </c>
       <c r="D3128" t="inlineStr">
         <is>
@@ -84886,7 +84886,7 @@
         <v>2</v>
       </c>
       <c r="G3128" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3129">
@@ -84897,7 +84897,7 @@
         <v>8</v>
       </c>
       <c r="C3129" t="n">
-        <v>33.54</v>
+        <v>33.48</v>
       </c>
       <c r="D3129" t="inlineStr">
         <is>
@@ -84913,7 +84913,7 @@
         <v>2</v>
       </c>
       <c r="G3129" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3130">
@@ -84924,7 +84924,7 @@
         <v>9</v>
       </c>
       <c r="C3130" t="n">
-        <v>28.95</v>
+        <v>28.9</v>
       </c>
       <c r="D3130" t="inlineStr">
         <is>
@@ -84940,7 +84940,7 @@
         <v>2</v>
       </c>
       <c r="G3130" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3131">
@@ -84951,7 +84951,7 @@
         <v>10</v>
       </c>
       <c r="C3131" t="n">
-        <v>23.72</v>
+        <v>23.64</v>
       </c>
       <c r="D3131" t="inlineStr">
         <is>
@@ -84967,7 +84967,7 @@
         <v>2</v>
       </c>
       <c r="G3131" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3132">
@@ -84994,7 +84994,7 @@
         <v>2</v>
       </c>
       <c r="G3132" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3133">
@@ -85005,7 +85005,7 @@
         <v>12</v>
       </c>
       <c r="C3133" t="n">
-        <v>19.88</v>
+        <v>19.93</v>
       </c>
       <c r="D3133" t="inlineStr">
         <is>
@@ -85021,7 +85021,7 @@
         <v>2</v>
       </c>
       <c r="G3133" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3134">
@@ -85032,7 +85032,7 @@
         <v>13</v>
       </c>
       <c r="C3134" t="n">
-        <v>20.39</v>
+        <v>20.38</v>
       </c>
       <c r="D3134" t="inlineStr">
         <is>
@@ -85048,7 +85048,7 @@
         <v>2</v>
       </c>
       <c r="G3134" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3135">
@@ -85075,7 +85075,7 @@
         <v>2</v>
       </c>
       <c r="G3135" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3136">
@@ -85086,7 +85086,7 @@
         <v>15</v>
       </c>
       <c r="C3136" t="n">
-        <v>20.94</v>
+        <v>20.91</v>
       </c>
       <c r="D3136" t="inlineStr">
         <is>
@@ -85102,7 +85102,7 @@
         <v>2</v>
       </c>
       <c r="G3136" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3137">
@@ -85113,7 +85113,7 @@
         <v>16</v>
       </c>
       <c r="C3137" t="n">
-        <v>20.02</v>
+        <v>19.93</v>
       </c>
       <c r="D3137" t="inlineStr">
         <is>
@@ -85129,7 +85129,7 @@
         <v>2</v>
       </c>
       <c r="G3137" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3138">
@@ -85140,7 +85140,7 @@
         <v>17</v>
       </c>
       <c r="C3138" t="n">
-        <v>17.42</v>
+        <v>17.37</v>
       </c>
       <c r="D3138" t="inlineStr">
         <is>
@@ -85156,7 +85156,7 @@
         <v>2</v>
       </c>
       <c r="G3138" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3139">
@@ -85167,7 +85167,7 @@
         <v>18</v>
       </c>
       <c r="C3139" t="n">
-        <v>17.13</v>
+        <v>17.1</v>
       </c>
       <c r="D3139" t="inlineStr">
         <is>
@@ -85183,7 +85183,7 @@
         <v>2</v>
       </c>
       <c r="G3139" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3140">
@@ -85194,7 +85194,7 @@
         <v>19</v>
       </c>
       <c r="C3140" t="n">
-        <v>15.86</v>
+        <v>15.88</v>
       </c>
       <c r="D3140" t="inlineStr">
         <is>
@@ -85210,7 +85210,7 @@
         <v>2</v>
       </c>
       <c r="G3140" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3141">
@@ -85221,7 +85221,7 @@
         <v>20</v>
       </c>
       <c r="C3141" t="n">
-        <v>28.39</v>
+        <v>28.36</v>
       </c>
       <c r="D3141" t="inlineStr">
         <is>
@@ -85237,7 +85237,7 @@
         <v>2</v>
       </c>
       <c r="G3141" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3142">
@@ -85248,7 +85248,7 @@
         <v>21</v>
       </c>
       <c r="C3142" t="n">
-        <v>36.55</v>
+        <v>36.52</v>
       </c>
       <c r="D3142" t="inlineStr">
         <is>
@@ -85264,7 +85264,7 @@
         <v>2</v>
       </c>
       <c r="G3142" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3143">
@@ -85275,7 +85275,7 @@
         <v>22</v>
       </c>
       <c r="C3143" t="n">
-        <v>36</v>
+        <v>35.96</v>
       </c>
       <c r="D3143" t="inlineStr">
         <is>
@@ -85291,7 +85291,7 @@
         <v>2</v>
       </c>
       <c r="G3143" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3144">
@@ -85302,7 +85302,7 @@
         <v>23</v>
       </c>
       <c r="C3144" t="n">
-        <v>33.42</v>
+        <v>33.38</v>
       </c>
       <c r="D3144" t="inlineStr">
         <is>
@@ -85318,7 +85318,7 @@
         <v>2</v>
       </c>
       <c r="G3144" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3145">
@@ -85329,7 +85329,7 @@
         <v>24</v>
       </c>
       <c r="C3145" t="n">
-        <v>27.65</v>
+        <v>27.61</v>
       </c>
       <c r="D3145" t="inlineStr">
         <is>
@@ -85345,7 +85345,7 @@
         <v>2</v>
       </c>
       <c r="G3145" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3146">
@@ -85356,7 +85356,7 @@
         <v>1</v>
       </c>
       <c r="C3146" t="n">
-        <v>19.72</v>
+        <v>19.7</v>
       </c>
       <c r="D3146" t="inlineStr">
         <is>
@@ -85372,7 +85372,7 @@
         <v>2</v>
       </c>
       <c r="G3146" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3147">
@@ -85383,7 +85383,7 @@
         <v>2</v>
       </c>
       <c r="C3147" t="n">
-        <v>13.78</v>
+        <v>13.76</v>
       </c>
       <c r="D3147" t="inlineStr">
         <is>
@@ -85399,7 +85399,7 @@
         <v>2</v>
       </c>
       <c r="G3147" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3148">
@@ -85410,7 +85410,7 @@
         <v>3</v>
       </c>
       <c r="C3148" t="n">
-        <v>13.6</v>
+        <v>13.59</v>
       </c>
       <c r="D3148" t="inlineStr">
         <is>
@@ -85426,7 +85426,7 @@
         <v>2</v>
       </c>
       <c r="G3148" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3149">
@@ -85437,7 +85437,7 @@
         <v>4</v>
       </c>
       <c r="C3149" t="n">
-        <v>14.66</v>
+        <v>14.65</v>
       </c>
       <c r="D3149" t="inlineStr">
         <is>
@@ -85453,7 +85453,7 @@
         <v>2</v>
       </c>
       <c r="G3149" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3150">
@@ -85464,7 +85464,7 @@
         <v>5</v>
       </c>
       <c r="C3150" t="n">
-        <v>16.06</v>
+        <v>16.05</v>
       </c>
       <c r="D3150" t="inlineStr">
         <is>
@@ -85480,7 +85480,7 @@
         <v>2</v>
       </c>
       <c r="G3150" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3151">
@@ -85491,7 +85491,7 @@
         <v>6</v>
       </c>
       <c r="C3151" t="n">
-        <v>17.47</v>
+        <v>17.46</v>
       </c>
       <c r="D3151" t="inlineStr">
         <is>
@@ -85507,7 +85507,7 @@
         <v>2</v>
       </c>
       <c r="G3151" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3152">
@@ -85518,7 +85518,7 @@
         <v>7</v>
       </c>
       <c r="C3152" t="n">
-        <v>22.81</v>
+        <v>22.79</v>
       </c>
       <c r="D3152" t="inlineStr">
         <is>
@@ -85534,7 +85534,7 @@
         <v>2</v>
       </c>
       <c r="G3152" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3153">
@@ -85545,7 +85545,7 @@
         <v>8</v>
       </c>
       <c r="C3153" t="n">
-        <v>47.01</v>
+        <v>46.97</v>
       </c>
       <c r="D3153" t="inlineStr">
         <is>
@@ -85561,7 +85561,7 @@
         <v>2</v>
       </c>
       <c r="G3153" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3154">
@@ -85572,7 +85572,7 @@
         <v>9</v>
       </c>
       <c r="C3154" t="n">
-        <v>49.03</v>
+        <v>48.98</v>
       </c>
       <c r="D3154" t="inlineStr">
         <is>
@@ -85588,7 +85588,7 @@
         <v>2</v>
       </c>
       <c r="G3154" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3155">
@@ -85599,7 +85599,7 @@
         <v>10</v>
       </c>
       <c r="C3155" t="n">
-        <v>29.58</v>
+        <v>29.32</v>
       </c>
       <c r="D3155" t="inlineStr">
         <is>
@@ -85615,7 +85615,7 @@
         <v>2</v>
       </c>
       <c r="G3155" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3156">
@@ -85626,7 +85626,7 @@
         <v>11</v>
       </c>
       <c r="C3156" t="n">
-        <v>20.37</v>
+        <v>20.31</v>
       </c>
       <c r="D3156" t="inlineStr">
         <is>
@@ -85642,7 +85642,7 @@
         <v>2</v>
       </c>
       <c r="G3156" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3157">
@@ -85653,7 +85653,7 @@
         <v>12</v>
       </c>
       <c r="C3157" t="n">
-        <v>29.55</v>
+        <v>29.45</v>
       </c>
       <c r="D3157" t="inlineStr">
         <is>
@@ -85669,7 +85669,7 @@
         <v>2</v>
       </c>
       <c r="G3157" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3158">
@@ -85680,7 +85680,7 @@
         <v>13</v>
       </c>
       <c r="C3158" t="n">
-        <v>31.05</v>
+        <v>30.94</v>
       </c>
       <c r="D3158" t="inlineStr">
         <is>
@@ -85696,7 +85696,7 @@
         <v>2</v>
       </c>
       <c r="G3158" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3159">
@@ -85707,7 +85707,7 @@
         <v>14</v>
       </c>
       <c r="C3159" t="n">
-        <v>31.96</v>
+        <v>31.85</v>
       </c>
       <c r="D3159" t="inlineStr">
         <is>
@@ -85723,7 +85723,7 @@
         <v>2</v>
       </c>
       <c r="G3159" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3160">
@@ -85734,7 +85734,7 @@
         <v>15</v>
       </c>
       <c r="C3160" t="n">
-        <v>32.34</v>
+        <v>32.21</v>
       </c>
       <c r="D3160" t="inlineStr">
         <is>
@@ -85750,7 +85750,7 @@
         <v>2</v>
       </c>
       <c r="G3160" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3161">
@@ -85761,7 +85761,7 @@
         <v>16</v>
       </c>
       <c r="C3161" t="n">
-        <v>31.43</v>
+        <v>31.3</v>
       </c>
       <c r="D3161" t="inlineStr">
         <is>
@@ -85777,7 +85777,7 @@
         <v>2</v>
       </c>
       <c r="G3161" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3162">
@@ -85788,7 +85788,7 @@
         <v>17</v>
       </c>
       <c r="C3162" t="n">
-        <v>31.52</v>
+        <v>31.43</v>
       </c>
       <c r="D3162" t="inlineStr">
         <is>
@@ -85804,7 +85804,7 @@
         <v>2</v>
       </c>
       <c r="G3162" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3163">
@@ -85815,7 +85815,7 @@
         <v>18</v>
       </c>
       <c r="C3163" t="n">
-        <v>35.1</v>
+        <v>35.01</v>
       </c>
       <c r="D3163" t="inlineStr">
         <is>
@@ -85831,7 +85831,7 @@
         <v>2</v>
       </c>
       <c r="G3163" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3164">
@@ -85842,7 +85842,7 @@
         <v>19</v>
       </c>
       <c r="C3164" t="n">
-        <v>32.56</v>
+        <v>32.43</v>
       </c>
       <c r="D3164" t="inlineStr">
         <is>
@@ -85858,7 +85858,7 @@
         <v>2</v>
       </c>
       <c r="G3164" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3165">
@@ -85869,7 +85869,7 @@
         <v>20</v>
       </c>
       <c r="C3165" t="n">
-        <v>32.42</v>
+        <v>32.34</v>
       </c>
       <c r="D3165" t="inlineStr">
         <is>
@@ -85885,7 +85885,7 @@
         <v>2</v>
       </c>
       <c r="G3165" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3166">
@@ -85896,7 +85896,7 @@
         <v>21</v>
       </c>
       <c r="C3166" t="n">
-        <v>37.16</v>
+        <v>37.09</v>
       </c>
       <c r="D3166" t="inlineStr">
         <is>
@@ -85912,7 +85912,7 @@
         <v>2</v>
       </c>
       <c r="G3166" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3167">
@@ -85923,7 +85923,7 @@
         <v>22</v>
       </c>
       <c r="C3167" t="n">
-        <v>37.77</v>
+        <v>37.73</v>
       </c>
       <c r="D3167" t="inlineStr">
         <is>
@@ -85939,7 +85939,7 @@
         <v>2</v>
       </c>
       <c r="G3167" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3168">
@@ -85950,7 +85950,7 @@
         <v>23</v>
       </c>
       <c r="C3168" t="n">
-        <v>37.23</v>
+        <v>37.2</v>
       </c>
       <c r="D3168" t="inlineStr">
         <is>
@@ -85966,7 +85966,7 @@
         <v>2</v>
       </c>
       <c r="G3168" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3169">
@@ -85977,7 +85977,7 @@
         <v>24</v>
       </c>
       <c r="C3169" t="n">
-        <v>37.24</v>
+        <v>37.21</v>
       </c>
       <c r="D3169" t="inlineStr">
         <is>
@@ -85993,7 +85993,7 @@
         <v>2</v>
       </c>
       <c r="G3169" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3170">
@@ -86004,7 +86004,7 @@
         <v>1</v>
       </c>
       <c r="C3170" t="n">
-        <v>20.02</v>
+        <v>20.06</v>
       </c>
       <c r="D3170" t="inlineStr">
         <is>
@@ -86020,7 +86020,7 @@
         <v>2</v>
       </c>
       <c r="G3170" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3171">
@@ -86031,7 +86031,7 @@
         <v>2</v>
       </c>
       <c r="C3171" t="n">
-        <v>15.26</v>
+        <v>15.33</v>
       </c>
       <c r="D3171" t="inlineStr">
         <is>
@@ -86047,7 +86047,7 @@
         <v>2</v>
       </c>
       <c r="G3171" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3172">
@@ -86058,7 +86058,7 @@
         <v>3</v>
       </c>
       <c r="C3172" t="n">
-        <v>16.4</v>
+        <v>16.59</v>
       </c>
       <c r="D3172" t="inlineStr">
         <is>
@@ -86074,7 +86074,7 @@
         <v>2</v>
       </c>
       <c r="G3172" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3173">
@@ -86085,7 +86085,7 @@
         <v>4</v>
       </c>
       <c r="C3173" t="n">
-        <v>15.84</v>
+        <v>15.88</v>
       </c>
       <c r="D3173" t="inlineStr">
         <is>
@@ -86101,7 +86101,7 @@
         <v>2</v>
       </c>
       <c r="G3173" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3174">
@@ -86112,7 +86112,7 @@
         <v>5</v>
       </c>
       <c r="C3174" t="n">
-        <v>13.79</v>
+        <v>13.67</v>
       </c>
       <c r="D3174" t="inlineStr">
         <is>
@@ -86128,7 +86128,7 @@
         <v>2</v>
       </c>
       <c r="G3174" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3175">
@@ -86139,7 +86139,7 @@
         <v>6</v>
       </c>
       <c r="C3175" t="n">
-        <v>13.19</v>
+        <v>13.11</v>
       </c>
       <c r="D3175" t="inlineStr">
         <is>
@@ -86155,7 +86155,7 @@
         <v>2</v>
       </c>
       <c r="G3175" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3176">
@@ -86166,7 +86166,7 @@
         <v>7</v>
       </c>
       <c r="C3176" t="n">
-        <v>20.04</v>
+        <v>19.88</v>
       </c>
       <c r="D3176" t="inlineStr">
         <is>
@@ -86182,7 +86182,7 @@
         <v>2</v>
       </c>
       <c r="G3176" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3177">
@@ -86193,7 +86193,7 @@
         <v>8</v>
       </c>
       <c r="C3177" t="n">
-        <v>41.05</v>
+        <v>40.91</v>
       </c>
       <c r="D3177" t="inlineStr">
         <is>
@@ -86209,7 +86209,7 @@
         <v>2</v>
       </c>
       <c r="G3177" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3178">
@@ -86220,7 +86220,7 @@
         <v>9</v>
       </c>
       <c r="C3178" t="n">
-        <v>42.19</v>
+        <v>42.06</v>
       </c>
       <c r="D3178" t="inlineStr">
         <is>
@@ -86236,7 +86236,7 @@
         <v>2</v>
       </c>
       <c r="G3178" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3179">
@@ -86247,7 +86247,7 @@
         <v>10</v>
       </c>
       <c r="C3179" t="n">
-        <v>19.66</v>
+        <v>19.86</v>
       </c>
       <c r="D3179" t="inlineStr">
         <is>
@@ -86263,7 +86263,7 @@
         <v>2</v>
       </c>
       <c r="G3179" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3180">
@@ -86274,7 +86274,7 @@
         <v>11</v>
       </c>
       <c r="C3180" t="n">
-        <v>12.47</v>
+        <v>13.42</v>
       </c>
       <c r="D3180" t="inlineStr">
         <is>
@@ -86290,7 +86290,7 @@
         <v>2</v>
       </c>
       <c r="G3180" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3181">
@@ -86301,7 +86301,7 @@
         <v>12</v>
       </c>
       <c r="C3181" t="n">
-        <v>29.51</v>
+        <v>29.33</v>
       </c>
       <c r="D3181" t="inlineStr">
         <is>
@@ -86317,7 +86317,7 @@
         <v>2</v>
       </c>
       <c r="G3181" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3182">
@@ -86328,7 +86328,7 @@
         <v>13</v>
       </c>
       <c r="C3182" t="n">
-        <v>30.58</v>
+        <v>30.38</v>
       </c>
       <c r="D3182" t="inlineStr">
         <is>
@@ -86344,7 +86344,7 @@
         <v>2</v>
       </c>
       <c r="G3182" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3183">
@@ -86355,7 +86355,7 @@
         <v>14</v>
       </c>
       <c r="C3183" t="n">
-        <v>28.64</v>
+        <v>28.59</v>
       </c>
       <c r="D3183" t="inlineStr">
         <is>
@@ -86371,7 +86371,7 @@
         <v>2</v>
       </c>
       <c r="G3183" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3184">
@@ -86382,7 +86382,7 @@
         <v>15</v>
       </c>
       <c r="C3184" t="n">
-        <v>32.25</v>
+        <v>32.06</v>
       </c>
       <c r="D3184" t="inlineStr">
         <is>
@@ -86398,7 +86398,7 @@
         <v>2</v>
       </c>
       <c r="G3184" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3185">
@@ -86409,7 +86409,7 @@
         <v>16</v>
       </c>
       <c r="C3185" t="n">
-        <v>33.25</v>
+        <v>33.05</v>
       </c>
       <c r="D3185" t="inlineStr">
         <is>
@@ -86425,7 +86425,7 @@
         <v>2</v>
       </c>
       <c r="G3185" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3186">
@@ -86436,7 +86436,7 @@
         <v>17</v>
       </c>
       <c r="C3186" t="n">
-        <v>31.74</v>
+        <v>31.83</v>
       </c>
       <c r="D3186" t="inlineStr">
         <is>
@@ -86452,7 +86452,7 @@
         <v>2</v>
       </c>
       <c r="G3186" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3187">
@@ -86463,7 +86463,7 @@
         <v>18</v>
       </c>
       <c r="C3187" t="n">
-        <v>27.32</v>
+        <v>27.19</v>
       </c>
       <c r="D3187" t="inlineStr">
         <is>
@@ -86479,7 +86479,7 @@
         <v>2</v>
       </c>
       <c r="G3187" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3188">
@@ -86490,7 +86490,7 @@
         <v>19</v>
       </c>
       <c r="C3188" t="n">
-        <v>21.81</v>
+        <v>21.98</v>
       </c>
       <c r="D3188" t="inlineStr">
         <is>
@@ -86506,7 +86506,7 @@
         <v>2</v>
       </c>
       <c r="G3188" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3189">
@@ -86517,7 +86517,7 @@
         <v>20</v>
       </c>
       <c r="C3189" t="n">
-        <v>16.54</v>
+        <v>16.85</v>
       </c>
       <c r="D3189" t="inlineStr">
         <is>
@@ -86533,7 +86533,7 @@
         <v>2</v>
       </c>
       <c r="G3189" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3190">
@@ -86544,7 +86544,7 @@
         <v>21</v>
       </c>
       <c r="C3190" t="n">
-        <v>26.78</v>
+        <v>26.72</v>
       </c>
       <c r="D3190" t="inlineStr">
         <is>
@@ -86560,7 +86560,7 @@
         <v>2</v>
       </c>
       <c r="G3190" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3191">
@@ -86571,7 +86571,7 @@
         <v>22</v>
       </c>
       <c r="C3191" t="n">
-        <v>28.61</v>
+        <v>28.55</v>
       </c>
       <c r="D3191" t="inlineStr">
         <is>
@@ -86587,7 +86587,7 @@
         <v>2</v>
       </c>
       <c r="G3191" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3192">
@@ -86598,7 +86598,7 @@
         <v>23</v>
       </c>
       <c r="C3192" t="n">
-        <v>27.75</v>
+        <v>27.68</v>
       </c>
       <c r="D3192" t="inlineStr">
         <is>
@@ -86614,7 +86614,7 @@
         <v>2</v>
       </c>
       <c r="G3192" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3193">
@@ -86625,7 +86625,7 @@
         <v>24</v>
       </c>
       <c r="C3193" t="n">
-        <v>28.19</v>
+        <v>28.12</v>
       </c>
       <c r="D3193" t="inlineStr">
         <is>
@@ -86641,7 +86641,7 @@
         <v>2</v>
       </c>
       <c r="G3193" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3194">
@@ -86652,7 +86652,7 @@
         <v>1</v>
       </c>
       <c r="C3194" t="n">
-        <v>8.289999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="D3194" t="inlineStr">
         <is>
@@ -86668,7 +86668,7 @@
         <v>2</v>
       </c>
       <c r="G3194" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3195">
@@ -86679,7 +86679,7 @@
         <v>2</v>
       </c>
       <c r="C3195" t="n">
-        <v>8.43</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="D3195" t="inlineStr">
         <is>
@@ -86695,7 +86695,7 @@
         <v>2</v>
       </c>
       <c r="G3195" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3196">
@@ -86706,7 +86706,7 @@
         <v>3</v>
       </c>
       <c r="C3196" t="n">
-        <v>11.04</v>
+        <v>10.72</v>
       </c>
       <c r="D3196" t="inlineStr">
         <is>
@@ -86722,7 +86722,7 @@
         <v>2</v>
       </c>
       <c r="G3196" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3197">
@@ -86733,7 +86733,7 @@
         <v>4</v>
       </c>
       <c r="C3197" t="n">
-        <v>9.220000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="D3197" t="inlineStr">
         <is>
@@ -86749,7 +86749,7 @@
         <v>2</v>
       </c>
       <c r="G3197" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3198">
@@ -86760,7 +86760,7 @@
         <v>5</v>
       </c>
       <c r="C3198" t="n">
-        <v>8.890000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="D3198" t="inlineStr">
         <is>
@@ -86776,7 +86776,7 @@
         <v>2</v>
       </c>
       <c r="G3198" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3199">
@@ -86787,7 +86787,7 @@
         <v>6</v>
       </c>
       <c r="C3199" t="n">
-        <v>10.2</v>
+        <v>11.7</v>
       </c>
       <c r="D3199" t="inlineStr">
         <is>
@@ -86803,7 +86803,7 @@
         <v>2</v>
       </c>
       <c r="G3199" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3200">
@@ -86814,7 +86814,7 @@
         <v>7</v>
       </c>
       <c r="C3200" t="n">
-        <v>21.78</v>
+        <v>22.18</v>
       </c>
       <c r="D3200" t="inlineStr">
         <is>
@@ -86830,7 +86830,7 @@
         <v>2</v>
       </c>
       <c r="G3200" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3201">
@@ -86841,7 +86841,7 @@
         <v>8</v>
       </c>
       <c r="C3201" t="n">
-        <v>37.35</v>
+        <v>35.75</v>
       </c>
       <c r="D3201" t="inlineStr">
         <is>
@@ -86857,7 +86857,7 @@
         <v>2</v>
       </c>
       <c r="G3201" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3202">
@@ -86868,7 +86868,7 @@
         <v>9</v>
       </c>
       <c r="C3202" t="n">
-        <v>35.43</v>
+        <v>35.56</v>
       </c>
       <c r="D3202" t="inlineStr">
         <is>
@@ -86884,7 +86884,7 @@
         <v>2</v>
       </c>
       <c r="G3202" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3203">
@@ -86895,7 +86895,7 @@
         <v>10</v>
       </c>
       <c r="C3203" t="n">
-        <v>25.1</v>
+        <v>23.4</v>
       </c>
       <c r="D3203" t="inlineStr">
         <is>
@@ -86911,7 +86911,7 @@
         <v>2</v>
       </c>
       <c r="G3203" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3204">
@@ -86922,7 +86922,7 @@
         <v>11</v>
       </c>
       <c r="C3204" t="n">
-        <v>31.37</v>
+        <v>29.25</v>
       </c>
       <c r="D3204" t="inlineStr">
         <is>
@@ -86938,7 +86938,7 @@
         <v>2</v>
       </c>
       <c r="G3204" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3205">
@@ -86949,7 +86949,7 @@
         <v>12</v>
       </c>
       <c r="C3205" t="n">
-        <v>45.47</v>
+        <v>43.19</v>
       </c>
       <c r="D3205" t="inlineStr">
         <is>
@@ -86965,7 +86965,7 @@
         <v>2</v>
       </c>
       <c r="G3205" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3206">
@@ -86976,7 +86976,7 @@
         <v>13</v>
       </c>
       <c r="C3206" t="n">
-        <v>48.74</v>
+        <v>46.96</v>
       </c>
       <c r="D3206" t="inlineStr">
         <is>
@@ -86992,7 +86992,7 @@
         <v>2</v>
       </c>
       <c r="G3206" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3207">
@@ -87003,7 +87003,7 @@
         <v>14</v>
       </c>
       <c r="C3207" t="n">
-        <v>52.91</v>
+        <v>51.05</v>
       </c>
       <c r="D3207" t="inlineStr">
         <is>
@@ -87019,7 +87019,7 @@
         <v>2</v>
       </c>
       <c r="G3207" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3208">
@@ -87030,7 +87030,7 @@
         <v>15</v>
       </c>
       <c r="C3208" t="n">
-        <v>52.39</v>
+        <v>49.45</v>
       </c>
       <c r="D3208" t="inlineStr">
         <is>
@@ -87046,7 +87046,7 @@
         <v>2</v>
       </c>
       <c r="G3208" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3209">
@@ -87057,7 +87057,7 @@
         <v>16</v>
       </c>
       <c r="C3209" t="n">
-        <v>53.66</v>
+        <v>51.03</v>
       </c>
       <c r="D3209" t="inlineStr">
         <is>
@@ -87073,7 +87073,7 @@
         <v>2</v>
       </c>
       <c r="G3209" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3210">
@@ -87084,7 +87084,7 @@
         <v>17</v>
       </c>
       <c r="C3210" t="n">
-        <v>50.2</v>
+        <v>47.78</v>
       </c>
       <c r="D3210" t="inlineStr">
         <is>
@@ -87100,7 +87100,7 @@
         <v>2</v>
       </c>
       <c r="G3210" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3211">
@@ -87111,7 +87111,7 @@
         <v>18</v>
       </c>
       <c r="C3211" t="n">
-        <v>43.27</v>
+        <v>41.39</v>
       </c>
       <c r="D3211" t="inlineStr">
         <is>
@@ -87127,7 +87127,7 @@
         <v>2</v>
       </c>
       <c r="G3211" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3212">
@@ -87138,7 +87138,7 @@
         <v>19</v>
       </c>
       <c r="C3212" t="n">
-        <v>28.57</v>
+        <v>28.61</v>
       </c>
       <c r="D3212" t="inlineStr">
         <is>
@@ -87154,7 +87154,7 @@
         <v>2</v>
       </c>
       <c r="G3212" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3213">
@@ -87165,7 +87165,7 @@
         <v>20</v>
       </c>
       <c r="C3213" t="n">
-        <v>21.86</v>
+        <v>22.42</v>
       </c>
       <c r="D3213" t="inlineStr">
         <is>
@@ -87181,7 +87181,7 @@
         <v>2</v>
       </c>
       <c r="G3213" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3214">
@@ -87192,7 +87192,7 @@
         <v>21</v>
       </c>
       <c r="C3214" t="n">
-        <v>34.45</v>
+        <v>33.59</v>
       </c>
       <c r="D3214" t="inlineStr">
         <is>
@@ -87208,7 +87208,7 @@
         <v>2</v>
       </c>
       <c r="G3214" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3215">
@@ -87219,7 +87219,7 @@
         <v>22</v>
       </c>
       <c r="C3215" t="n">
-        <v>38.41</v>
+        <v>37.76</v>
       </c>
       <c r="D3215" t="inlineStr">
         <is>
@@ -87235,7 +87235,7 @@
         <v>2</v>
       </c>
       <c r="G3215" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3216">
@@ -87246,7 +87246,7 @@
         <v>23</v>
       </c>
       <c r="C3216" t="n">
-        <v>38.62</v>
+        <v>37.52</v>
       </c>
       <c r="D3216" t="inlineStr">
         <is>
@@ -87262,7 +87262,7 @@
         <v>2</v>
       </c>
       <c r="G3216" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3217">
@@ -87273,7 +87273,7 @@
         <v>24</v>
       </c>
       <c r="C3217" t="n">
-        <v>29.73</v>
+        <v>29.36</v>
       </c>
       <c r="D3217" t="inlineStr">
         <is>
@@ -87289,7 +87289,7 @@
         <v>2</v>
       </c>
       <c r="G3217" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3218">
@@ -87300,7 +87300,7 @@
         <v>1</v>
       </c>
       <c r="C3218" t="n">
-        <v>8.69</v>
+        <v>10.31</v>
       </c>
       <c r="D3218" t="inlineStr">
         <is>
@@ -87316,7 +87316,7 @@
         <v>2</v>
       </c>
       <c r="G3218" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3219">
@@ -87327,7 +87327,7 @@
         <v>2</v>
       </c>
       <c r="C3219" t="n">
-        <v>9.07</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="D3219" t="inlineStr">
         <is>
@@ -87343,7 +87343,7 @@
         <v>2</v>
       </c>
       <c r="G3219" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3220">
@@ -87354,7 +87354,7 @@
         <v>3</v>
       </c>
       <c r="C3220" t="n">
-        <v>8.85</v>
+        <v>5.05</v>
       </c>
       <c r="D3220" t="inlineStr">
         <is>
@@ -87370,7 +87370,7 @@
         <v>2</v>
       </c>
       <c r="G3220" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3221">
@@ -87381,7 +87381,7 @@
         <v>4</v>
       </c>
       <c r="C3221" t="n">
-        <v>9.06</v>
+        <v>6.88</v>
       </c>
       <c r="D3221" t="inlineStr">
         <is>
@@ -87397,7 +87397,7 @@
         <v>2</v>
       </c>
       <c r="G3221" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3222">
@@ -87408,7 +87408,7 @@
         <v>5</v>
       </c>
       <c r="C3222" t="n">
-        <v>9.199999999999999</v>
+        <v>8.01</v>
       </c>
       <c r="D3222" t="inlineStr">
         <is>
@@ -87424,7 +87424,7 @@
         <v>2</v>
       </c>
       <c r="G3222" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3223">
@@ -87435,7 +87435,7 @@
         <v>6</v>
       </c>
       <c r="C3223" t="n">
-        <v>9.279999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="D3223" t="inlineStr">
         <is>
@@ -87451,7 +87451,7 @@
         <v>2</v>
       </c>
       <c r="G3223" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3224">
@@ -87462,7 +87462,7 @@
         <v>7</v>
       </c>
       <c r="C3224" t="n">
-        <v>13.97</v>
+        <v>18.84</v>
       </c>
       <c r="D3224" t="inlineStr">
         <is>
@@ -87478,7 +87478,7 @@
         <v>2</v>
       </c>
       <c r="G3224" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3225">
@@ -87489,7 +87489,7 @@
         <v>8</v>
       </c>
       <c r="C3225" t="n">
-        <v>24.31</v>
+        <v>31.82</v>
       </c>
       <c r="D3225" t="inlineStr">
         <is>
@@ -87505,7 +87505,7 @@
         <v>2</v>
       </c>
       <c r="G3225" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3226">
@@ -87516,7 +87516,7 @@
         <v>9</v>
       </c>
       <c r="C3226" t="n">
-        <v>28.82</v>
+        <v>29.81</v>
       </c>
       <c r="D3226" t="inlineStr">
         <is>
@@ -87532,7 +87532,7 @@
         <v>2</v>
       </c>
       <c r="G3226" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3227">
@@ -87543,7 +87543,7 @@
         <v>10</v>
       </c>
       <c r="C3227" t="n">
-        <v>22.28</v>
+        <v>23.44</v>
       </c>
       <c r="D3227" t="inlineStr">
         <is>
@@ -87559,7 +87559,7 @@
         <v>2</v>
       </c>
       <c r="G3227" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3228">
@@ -87570,7 +87570,7 @@
         <v>11</v>
       </c>
       <c r="C3228" t="n">
-        <v>26.12</v>
+        <v>27.57</v>
       </c>
       <c r="D3228" t="inlineStr">
         <is>
@@ -87586,7 +87586,7 @@
         <v>2</v>
       </c>
       <c r="G3228" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3229">
@@ -87597,7 +87597,7 @@
         <v>12</v>
       </c>
       <c r="C3229" t="n">
-        <v>27.75</v>
+        <v>30.1</v>
       </c>
       <c r="D3229" t="inlineStr">
         <is>
@@ -87613,7 +87613,7 @@
         <v>2</v>
       </c>
       <c r="G3229" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3230">
@@ -87624,7 +87624,7 @@
         <v>13</v>
       </c>
       <c r="C3230" t="n">
-        <v>28.27</v>
+        <v>35.71</v>
       </c>
       <c r="D3230" t="inlineStr">
         <is>
@@ -87640,7 +87640,7 @@
         <v>2</v>
       </c>
       <c r="G3230" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3231">
@@ -87651,7 +87651,7 @@
         <v>14</v>
       </c>
       <c r="C3231" t="n">
-        <v>26.31</v>
+        <v>35.87</v>
       </c>
       <c r="D3231" t="inlineStr">
         <is>
@@ -87667,7 +87667,7 @@
         <v>2</v>
       </c>
       <c r="G3231" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3232">
@@ -87678,7 +87678,7 @@
         <v>15</v>
       </c>
       <c r="C3232" t="n">
-        <v>26.09</v>
+        <v>34.91</v>
       </c>
       <c r="D3232" t="inlineStr">
         <is>
@@ -87694,7 +87694,7 @@
         <v>2</v>
       </c>
       <c r="G3232" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3233">
@@ -87705,7 +87705,7 @@
         <v>16</v>
       </c>
       <c r="C3233" t="n">
-        <v>26.74</v>
+        <v>36.28</v>
       </c>
       <c r="D3233" t="inlineStr">
         <is>
@@ -87721,7 +87721,7 @@
         <v>2</v>
       </c>
       <c r="G3233" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3234">
@@ -87732,7 +87732,7 @@
         <v>17</v>
       </c>
       <c r="C3234" t="n">
-        <v>28.31</v>
+        <v>37.06</v>
       </c>
       <c r="D3234" t="inlineStr">
         <is>
@@ -87748,7 +87748,7 @@
         <v>2</v>
       </c>
       <c r="G3234" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3235">
@@ -87759,7 +87759,7 @@
         <v>18</v>
       </c>
       <c r="C3235" t="n">
-        <v>29.51</v>
+        <v>34.62</v>
       </c>
       <c r="D3235" t="inlineStr">
         <is>
@@ -87775,7 +87775,7 @@
         <v>2</v>
       </c>
       <c r="G3235" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3236">
@@ -87786,7 +87786,7 @@
         <v>19</v>
       </c>
       <c r="C3236" t="n">
-        <v>26.18</v>
+        <v>24.92</v>
       </c>
       <c r="D3236" t="inlineStr">
         <is>
@@ -87802,7 +87802,7 @@
         <v>2</v>
       </c>
       <c r="G3236" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3237">
@@ -87813,7 +87813,7 @@
         <v>20</v>
       </c>
       <c r="C3237" t="n">
-        <v>15.75</v>
+        <v>17.86</v>
       </c>
       <c r="D3237" t="inlineStr">
         <is>
@@ -87829,7 +87829,7 @@
         <v>2</v>
       </c>
       <c r="G3237" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3238">
@@ -87840,7 +87840,7 @@
         <v>21</v>
       </c>
       <c r="C3238" t="n">
-        <v>16.83</v>
+        <v>31.39</v>
       </c>
       <c r="D3238" t="inlineStr">
         <is>
@@ -87856,7 +87856,7 @@
         <v>2</v>
       </c>
       <c r="G3238" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3239">
@@ -87867,7 +87867,7 @@
         <v>22</v>
       </c>
       <c r="C3239" t="n">
-        <v>11.9</v>
+        <v>32.96</v>
       </c>
       <c r="D3239" t="inlineStr">
         <is>
@@ -87883,7 +87883,7 @@
         <v>2</v>
       </c>
       <c r="G3239" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3240">
@@ -87894,7 +87894,7 @@
         <v>23</v>
       </c>
       <c r="C3240" t="n">
-        <v>10</v>
+        <v>25.21</v>
       </c>
       <c r="D3240" t="inlineStr">
         <is>
@@ -87910,7 +87910,7 @@
         <v>2</v>
       </c>
       <c r="G3240" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3241">
@@ -87921,7 +87921,7 @@
         <v>24</v>
       </c>
       <c r="C3241" t="n">
-        <v>9.56</v>
+        <v>22.7</v>
       </c>
       <c r="D3241" t="inlineStr">
         <is>
@@ -87937,7 +87937,7 @@
         <v>2</v>
       </c>
       <c r="G3241" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3242">
@@ -87948,7 +87948,7 @@
         <v>1</v>
       </c>
       <c r="C3242" t="n">
-        <v>8.32</v>
+        <v>6.29</v>
       </c>
       <c r="D3242" t="inlineStr">
         <is>
@@ -87964,7 +87964,7 @@
         <v>2</v>
       </c>
       <c r="G3242" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3243">
@@ -87975,7 +87975,7 @@
         <v>2</v>
       </c>
       <c r="C3243" t="n">
-        <v>9.81</v>
+        <v>4.31</v>
       </c>
       <c r="D3243" t="inlineStr">
         <is>
@@ -87991,7 +87991,7 @@
         <v>2</v>
       </c>
       <c r="G3243" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3244">
@@ -88002,7 +88002,7 @@
         <v>3</v>
       </c>
       <c r="C3244" t="n">
-        <v>10.26</v>
+        <v>2.87</v>
       </c>
       <c r="D3244" t="inlineStr">
         <is>
@@ -88018,7 +88018,7 @@
         <v>2</v>
       </c>
       <c r="G3244" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3245">
@@ -88029,7 +88029,7 @@
         <v>4</v>
       </c>
       <c r="C3245" t="n">
-        <v>12.31</v>
+        <v>1.85</v>
       </c>
       <c r="D3245" t="inlineStr">
         <is>
@@ -88045,7 +88045,7 @@
         <v>2</v>
       </c>
       <c r="G3245" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3246">
@@ -88056,7 +88056,7 @@
         <v>5</v>
       </c>
       <c r="C3246" t="n">
-        <v>14.07</v>
+        <v>9.92</v>
       </c>
       <c r="D3246" t="inlineStr">
         <is>
@@ -88072,7 +88072,7 @@
         <v>2</v>
       </c>
       <c r="G3246" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3247">
@@ -88083,7 +88083,7 @@
         <v>6</v>
       </c>
       <c r="C3247" t="n">
-        <v>12.34</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="D3247" t="inlineStr">
         <is>
@@ -88099,7 +88099,7 @@
         <v>2</v>
       </c>
       <c r="G3247" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3248">
@@ -88110,7 +88110,7 @@
         <v>7</v>
       </c>
       <c r="C3248" t="n">
-        <v>11.02</v>
+        <v>4.4</v>
       </c>
       <c r="D3248" t="inlineStr">
         <is>
@@ -88126,7 +88126,7 @@
         <v>2</v>
       </c>
       <c r="G3248" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3249">
@@ -88137,7 +88137,7 @@
         <v>8</v>
       </c>
       <c r="C3249" t="n">
-        <v>25.91</v>
+        <v>27.43</v>
       </c>
       <c r="D3249" t="inlineStr">
         <is>
@@ -88153,7 +88153,7 @@
         <v>2</v>
       </c>
       <c r="G3249" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3250">
@@ -88164,7 +88164,7 @@
         <v>9</v>
       </c>
       <c r="C3250" t="n">
-        <v>27.66</v>
+        <v>27.25</v>
       </c>
       <c r="D3250" t="inlineStr">
         <is>
@@ -88180,7 +88180,7 @@
         <v>2</v>
       </c>
       <c r="G3250" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3251">
@@ -88191,7 +88191,7 @@
         <v>10</v>
       </c>
       <c r="C3251" t="n">
-        <v>31.38</v>
+        <v>25.71</v>
       </c>
       <c r="D3251" t="inlineStr">
         <is>
@@ -88207,7 +88207,7 @@
         <v>2</v>
       </c>
       <c r="G3251" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3252">
@@ -88218,7 +88218,7 @@
         <v>11</v>
       </c>
       <c r="C3252" t="n">
-        <v>24.77</v>
+        <v>23.15</v>
       </c>
       <c r="D3252" t="inlineStr">
         <is>
@@ -88234,7 +88234,7 @@
         <v>2</v>
       </c>
       <c r="G3252" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3253">
@@ -88245,7 +88245,7 @@
         <v>12</v>
       </c>
       <c r="C3253" t="n">
-        <v>25.01</v>
+        <v>22.84</v>
       </c>
       <c r="D3253" t="inlineStr">
         <is>
@@ -88261,7 +88261,7 @@
         <v>2</v>
       </c>
       <c r="G3253" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3254">
@@ -88272,7 +88272,7 @@
         <v>13</v>
       </c>
       <c r="C3254" t="n">
-        <v>35.56</v>
+        <v>39.57</v>
       </c>
       <c r="D3254" t="inlineStr">
         <is>
@@ -88288,7 +88288,7 @@
         <v>2</v>
       </c>
       <c r="G3254" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3255">
@@ -88299,7 +88299,7 @@
         <v>14</v>
       </c>
       <c r="C3255" t="n">
-        <v>34.42</v>
+        <v>38.07</v>
       </c>
       <c r="D3255" t="inlineStr">
         <is>
@@ -88315,7 +88315,7 @@
         <v>2</v>
       </c>
       <c r="G3255" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3256">
@@ -88326,7 +88326,7 @@
         <v>15</v>
       </c>
       <c r="C3256" t="n">
-        <v>33.18</v>
+        <v>35.43</v>
       </c>
       <c r="D3256" t="inlineStr">
         <is>
@@ -88342,7 +88342,7 @@
         <v>2</v>
       </c>
       <c r="G3256" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3257">
@@ -88353,7 +88353,7 @@
         <v>16</v>
       </c>
       <c r="C3257" t="n">
-        <v>36</v>
+        <v>36.35</v>
       </c>
       <c r="D3257" t="inlineStr">
         <is>
@@ -88369,7 +88369,7 @@
         <v>2</v>
       </c>
       <c r="G3257" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3258">
@@ -88380,7 +88380,7 @@
         <v>17</v>
       </c>
       <c r="C3258" t="n">
-        <v>33.88</v>
+        <v>31.97</v>
       </c>
       <c r="D3258" t="inlineStr">
         <is>
@@ -88396,7 +88396,7 @@
         <v>2</v>
       </c>
       <c r="G3258" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3259">
@@ -88407,7 +88407,7 @@
         <v>18</v>
       </c>
       <c r="C3259" t="n">
-        <v>32.06</v>
+        <v>30.55</v>
       </c>
       <c r="D3259" t="inlineStr">
         <is>
@@ -88423,7 +88423,7 @@
         <v>2</v>
       </c>
       <c r="G3259" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3260">
@@ -88434,7 +88434,7 @@
         <v>19</v>
       </c>
       <c r="C3260" t="n">
-        <v>24.7</v>
+        <v>18.03</v>
       </c>
       <c r="D3260" t="inlineStr">
         <is>
@@ -88450,7 +88450,7 @@
         <v>2</v>
       </c>
       <c r="G3260" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3261">
@@ -88461,7 +88461,7 @@
         <v>20</v>
       </c>
       <c r="C3261" t="n">
-        <v>25.83</v>
+        <v>16.31</v>
       </c>
       <c r="D3261" t="inlineStr">
         <is>
@@ -88477,7 +88477,7 @@
         <v>2</v>
       </c>
       <c r="G3261" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3262">
@@ -88488,7 +88488,7 @@
         <v>21</v>
       </c>
       <c r="C3262" t="n">
-        <v>41.01</v>
+        <v>34.35</v>
       </c>
       <c r="D3262" t="inlineStr">
         <is>
@@ -88504,7 +88504,7 @@
         <v>2</v>
       </c>
       <c r="G3262" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3263">
@@ -88515,7 +88515,7 @@
         <v>22</v>
       </c>
       <c r="C3263" t="n">
-        <v>38.39</v>
+        <v>36.84</v>
       </c>
       <c r="D3263" t="inlineStr">
         <is>
@@ -88531,7 +88531,7 @@
         <v>2</v>
       </c>
       <c r="G3263" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3264">
@@ -88542,7 +88542,7 @@
         <v>23</v>
       </c>
       <c r="C3264" t="n">
-        <v>24.19</v>
+        <v>23</v>
       </c>
       <c r="D3264" t="inlineStr">
         <is>
@@ -88558,7 +88558,7 @@
         <v>2</v>
       </c>
       <c r="G3264" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
       </c>
     </row>
     <row r="3265">
@@ -88569,7 +88569,7 @@
         <v>24</v>
       </c>
       <c r="C3265" t="n">
-        <v>23.47</v>
+        <v>23.57</v>
       </c>
       <c r="D3265" t="inlineStr">
         <is>
@@ -88585,7 +88585,655 @@
         <v>2</v>
       </c>
       <c r="G3265" s="2" t="n">
-        <v>46278.85101434636</v>
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3266">
+      <c r="A3266" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3266" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3266" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D3266" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3266" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3266" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3266" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3267">
+      <c r="A3267" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3267" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3267" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="D3267" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3267" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3267" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3267" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3268">
+      <c r="A3268" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3268" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3268" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D3268" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3268" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3268" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3268" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3269">
+      <c r="A3269" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3269" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3269" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D3269" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3269" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3269" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3269" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3270">
+      <c r="A3270" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3270" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3270" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="D3270" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3270" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3270" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3270" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3271">
+      <c r="A3271" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3271" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3271" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="D3271" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3271" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3271" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3271" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3272">
+      <c r="A3272" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3272" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3272" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="D3272" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3272" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3272" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3272" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3273">
+      <c r="A3273" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3273" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3273" t="n">
+        <v>59.73</v>
+      </c>
+      <c r="D3273" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3273" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3273" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3273" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3274">
+      <c r="A3274" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3274" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3274" t="n">
+        <v>54.16</v>
+      </c>
+      <c r="D3274" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3274" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3274" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3274" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3275">
+      <c r="A3275" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3275" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3275" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="D3275" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3275" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3275" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3275" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3276">
+      <c r="A3276" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3276" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3276" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="D3276" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3276" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3276" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3276" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3277">
+      <c r="A3277" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3277" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3277" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D3277" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3277" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3277" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3277" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3278">
+      <c r="A3278" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3278" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3278" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="D3278" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3278" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3278" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3278" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3279">
+      <c r="A3279" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3279" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3279" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="D3279" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3279" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3279" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3279" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3280">
+      <c r="A3280" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3280" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3280" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="D3280" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3280" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3280" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3280" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3281">
+      <c r="A3281" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3281" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3281" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="D3281" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3281" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3281" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3281" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3282">
+      <c r="A3282" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3282" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3282" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="D3282" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3282" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3282" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3282" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3283">
+      <c r="A3283" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3283" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3283" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="D3283" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3283" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3283" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3283" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3284">
+      <c r="A3284" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3284" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3284" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="D3284" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3284" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3284" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3284" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3285">
+      <c r="A3285" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3285" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3285" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="D3285" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3285" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3285" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3285" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3286">
+      <c r="A3286" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3286" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3286" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="D3286" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3286" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3286" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3286" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3287">
+      <c r="A3287" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3287" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3287" t="n">
+        <v>45.03</v>
+      </c>
+      <c r="D3287" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3287" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3287" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3287" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3288">
+      <c r="A3288" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3288" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3288" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="D3288" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3288" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3288" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3288" s="2" t="n">
+        <v>46279.49819652397</v>
+      </c>
+    </row>
+    <row r="3289">
+      <c r="A3289" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3289" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3289" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="D3289" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3289" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3289" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3289" s="2" t="n">
+        <v>46279.49819652397</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -80188,7 +80188,7 @@
         <v>2</v>
       </c>
       <c r="G2954" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2955">
@@ -80215,7 +80215,7 @@
         <v>2</v>
       </c>
       <c r="G2955" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2956">
@@ -80242,7 +80242,7 @@
         <v>2</v>
       </c>
       <c r="G2956" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2957">
@@ -80269,7 +80269,7 @@
         <v>2</v>
       </c>
       <c r="G2957" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2958">
@@ -80296,7 +80296,7 @@
         <v>2</v>
       </c>
       <c r="G2958" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2959">
@@ -80323,7 +80323,7 @@
         <v>2</v>
       </c>
       <c r="G2959" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2960">
@@ -80350,7 +80350,7 @@
         <v>2</v>
       </c>
       <c r="G2960" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2961">
@@ -80377,7 +80377,7 @@
         <v>2</v>
       </c>
       <c r="G2961" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2962">
@@ -80404,7 +80404,7 @@
         <v>2</v>
       </c>
       <c r="G2962" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2963">
@@ -80431,7 +80431,7 @@
         <v>2</v>
       </c>
       <c r="G2963" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2964">
@@ -80458,7 +80458,7 @@
         <v>2</v>
       </c>
       <c r="G2964" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2965">
@@ -80485,7 +80485,7 @@
         <v>2</v>
       </c>
       <c r="G2965" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2966">
@@ -80512,7 +80512,7 @@
         <v>2</v>
       </c>
       <c r="G2966" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2967">
@@ -80539,7 +80539,7 @@
         <v>2</v>
       </c>
       <c r="G2967" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2968">
@@ -80566,7 +80566,7 @@
         <v>2</v>
       </c>
       <c r="G2968" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2969">
@@ -80593,7 +80593,7 @@
         <v>2</v>
       </c>
       <c r="G2969" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2970">
@@ -80620,7 +80620,7 @@
         <v>2</v>
       </c>
       <c r="G2970" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2971">
@@ -80647,7 +80647,7 @@
         <v>2</v>
       </c>
       <c r="G2971" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2972">
@@ -80674,7 +80674,7 @@
         <v>2</v>
       </c>
       <c r="G2972" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2973">
@@ -80701,7 +80701,7 @@
         <v>2</v>
       </c>
       <c r="G2973" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2974">
@@ -80728,7 +80728,7 @@
         <v>2</v>
       </c>
       <c r="G2974" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2975">
@@ -80755,7 +80755,7 @@
         <v>2</v>
       </c>
       <c r="G2975" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2976">
@@ -80782,7 +80782,7 @@
         <v>2</v>
       </c>
       <c r="G2976" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2977">
@@ -80809,7 +80809,7 @@
         <v>2</v>
       </c>
       <c r="G2977" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2978">
@@ -80836,7 +80836,7 @@
         <v>2</v>
       </c>
       <c r="G2978" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2979">
@@ -80863,7 +80863,7 @@
         <v>2</v>
       </c>
       <c r="G2979" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2980">
@@ -80890,7 +80890,7 @@
         <v>2</v>
       </c>
       <c r="G2980" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2981">
@@ -80917,7 +80917,7 @@
         <v>2</v>
       </c>
       <c r="G2981" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2982">
@@ -80944,7 +80944,7 @@
         <v>2</v>
       </c>
       <c r="G2982" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2983">
@@ -80971,7 +80971,7 @@
         <v>2</v>
       </c>
       <c r="G2983" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2984">
@@ -80998,7 +80998,7 @@
         <v>2</v>
       </c>
       <c r="G2984" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2985">
@@ -81025,7 +81025,7 @@
         <v>2</v>
       </c>
       <c r="G2985" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2986">
@@ -81052,7 +81052,7 @@
         <v>2</v>
       </c>
       <c r="G2986" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2987">
@@ -81079,7 +81079,7 @@
         <v>2</v>
       </c>
       <c r="G2987" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2988">
@@ -81106,7 +81106,7 @@
         <v>2</v>
       </c>
       <c r="G2988" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2989">
@@ -81133,7 +81133,7 @@
         <v>2</v>
       </c>
       <c r="G2989" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2990">
@@ -81160,7 +81160,7 @@
         <v>2</v>
       </c>
       <c r="G2990" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2991">
@@ -81187,7 +81187,7 @@
         <v>2</v>
       </c>
       <c r="G2991" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2992">
@@ -81214,7 +81214,7 @@
         <v>2</v>
       </c>
       <c r="G2992" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2993">
@@ -81241,7 +81241,7 @@
         <v>2</v>
       </c>
       <c r="G2993" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2994">
@@ -81268,7 +81268,7 @@
         <v>2</v>
       </c>
       <c r="G2994" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2995">
@@ -81295,7 +81295,7 @@
         <v>2</v>
       </c>
       <c r="G2995" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2996">
@@ -81322,7 +81322,7 @@
         <v>2</v>
       </c>
       <c r="G2996" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2997">
@@ -81349,7 +81349,7 @@
         <v>2</v>
       </c>
       <c r="G2997" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2998">
@@ -81376,7 +81376,7 @@
         <v>2</v>
       </c>
       <c r="G2998" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="2999">
@@ -81403,7 +81403,7 @@
         <v>2</v>
       </c>
       <c r="G2999" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3000">
@@ -81430,7 +81430,7 @@
         <v>2</v>
       </c>
       <c r="G3000" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3001">
@@ -81457,7 +81457,7 @@
         <v>2</v>
       </c>
       <c r="G3001" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3002">
@@ -81484,7 +81484,7 @@
         <v>2</v>
       </c>
       <c r="G3002" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3003">
@@ -81511,7 +81511,7 @@
         <v>2</v>
       </c>
       <c r="G3003" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3004">
@@ -81538,7 +81538,7 @@
         <v>2</v>
       </c>
       <c r="G3004" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3005">
@@ -81565,7 +81565,7 @@
         <v>2</v>
       </c>
       <c r="G3005" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3006">
@@ -81592,7 +81592,7 @@
         <v>2</v>
       </c>
       <c r="G3006" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3007">
@@ -81619,7 +81619,7 @@
         <v>2</v>
       </c>
       <c r="G3007" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3008">
@@ -81646,7 +81646,7 @@
         <v>2</v>
       </c>
       <c r="G3008" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3009">
@@ -81673,7 +81673,7 @@
         <v>2</v>
       </c>
       <c r="G3009" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3010">
@@ -81700,7 +81700,7 @@
         <v>2</v>
       </c>
       <c r="G3010" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3011">
@@ -81727,7 +81727,7 @@
         <v>2</v>
       </c>
       <c r="G3011" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3012">
@@ -81754,7 +81754,7 @@
         <v>2</v>
       </c>
       <c r="G3012" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3013">
@@ -81781,7 +81781,7 @@
         <v>2</v>
       </c>
       <c r="G3013" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3014">
@@ -81808,7 +81808,7 @@
         <v>2</v>
       </c>
       <c r="G3014" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3015">
@@ -81835,7 +81835,7 @@
         <v>2</v>
       </c>
       <c r="G3015" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3016">
@@ -81862,7 +81862,7 @@
         <v>2</v>
       </c>
       <c r="G3016" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3017">
@@ -81889,7 +81889,7 @@
         <v>2</v>
       </c>
       <c r="G3017" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3018">
@@ -81916,7 +81916,7 @@
         <v>2</v>
       </c>
       <c r="G3018" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3019">
@@ -81943,7 +81943,7 @@
         <v>2</v>
       </c>
       <c r="G3019" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3020">
@@ -81970,7 +81970,7 @@
         <v>2</v>
       </c>
       <c r="G3020" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3021">
@@ -81997,7 +81997,7 @@
         <v>2</v>
       </c>
       <c r="G3021" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3022">
@@ -82024,7 +82024,7 @@
         <v>2</v>
       </c>
       <c r="G3022" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3023">
@@ -82051,7 +82051,7 @@
         <v>2</v>
       </c>
       <c r="G3023" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3024">
@@ -82078,7 +82078,7 @@
         <v>2</v>
       </c>
       <c r="G3024" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3025">
@@ -82105,7 +82105,7 @@
         <v>2</v>
       </c>
       <c r="G3025" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3026">
@@ -82132,7 +82132,7 @@
         <v>2</v>
       </c>
       <c r="G3026" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3027">
@@ -82159,7 +82159,7 @@
         <v>2</v>
       </c>
       <c r="G3027" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3028">
@@ -82186,7 +82186,7 @@
         <v>2</v>
       </c>
       <c r="G3028" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3029">
@@ -82213,7 +82213,7 @@
         <v>2</v>
       </c>
       <c r="G3029" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3030">
@@ -82240,7 +82240,7 @@
         <v>2</v>
       </c>
       <c r="G3030" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3031">
@@ -82267,7 +82267,7 @@
         <v>2</v>
       </c>
       <c r="G3031" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3032">
@@ -82294,7 +82294,7 @@
         <v>2</v>
       </c>
       <c r="G3032" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3033">
@@ -82321,7 +82321,7 @@
         <v>2</v>
       </c>
       <c r="G3033" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3034">
@@ -82348,7 +82348,7 @@
         <v>2</v>
       </c>
       <c r="G3034" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3035">
@@ -82375,7 +82375,7 @@
         <v>2</v>
       </c>
       <c r="G3035" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3036">
@@ -82402,7 +82402,7 @@
         <v>2</v>
       </c>
       <c r="G3036" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3037">
@@ -82429,7 +82429,7 @@
         <v>2</v>
       </c>
       <c r="G3037" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3038">
@@ -82456,7 +82456,7 @@
         <v>2</v>
       </c>
       <c r="G3038" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3039">
@@ -82483,7 +82483,7 @@
         <v>2</v>
       </c>
       <c r="G3039" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3040">
@@ -82510,7 +82510,7 @@
         <v>2</v>
       </c>
       <c r="G3040" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3041">
@@ -82537,7 +82537,7 @@
         <v>2</v>
       </c>
       <c r="G3041" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3042">
@@ -82564,7 +82564,7 @@
         <v>2</v>
       </c>
       <c r="G3042" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3043">
@@ -82591,7 +82591,7 @@
         <v>2</v>
       </c>
       <c r="G3043" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3044">
@@ -82618,7 +82618,7 @@
         <v>2</v>
       </c>
       <c r="G3044" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3045">
@@ -82645,7 +82645,7 @@
         <v>2</v>
       </c>
       <c r="G3045" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3046">
@@ -82672,7 +82672,7 @@
         <v>2</v>
       </c>
       <c r="G3046" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3047">
@@ -82699,7 +82699,7 @@
         <v>2</v>
       </c>
       <c r="G3047" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3048">
@@ -82726,7 +82726,7 @@
         <v>2</v>
       </c>
       <c r="G3048" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3049">
@@ -82753,7 +82753,7 @@
         <v>2</v>
       </c>
       <c r="G3049" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3050">
@@ -82780,7 +82780,7 @@
         <v>2</v>
       </c>
       <c r="G3050" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3051">
@@ -82807,7 +82807,7 @@
         <v>2</v>
       </c>
       <c r="G3051" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3052">
@@ -82834,7 +82834,7 @@
         <v>2</v>
       </c>
       <c r="G3052" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3053">
@@ -82861,7 +82861,7 @@
         <v>2</v>
       </c>
       <c r="G3053" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3054">
@@ -82888,7 +82888,7 @@
         <v>2</v>
       </c>
       <c r="G3054" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3055">
@@ -82915,7 +82915,7 @@
         <v>2</v>
       </c>
       <c r="G3055" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3056">
@@ -82942,7 +82942,7 @@
         <v>2</v>
       </c>
       <c r="G3056" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3057">
@@ -82969,7 +82969,7 @@
         <v>2</v>
       </c>
       <c r="G3057" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3058">
@@ -82996,7 +82996,7 @@
         <v>2</v>
       </c>
       <c r="G3058" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3059">
@@ -83023,7 +83023,7 @@
         <v>2</v>
       </c>
       <c r="G3059" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3060">
@@ -83050,7 +83050,7 @@
         <v>2</v>
       </c>
       <c r="G3060" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3061">
@@ -83077,7 +83077,7 @@
         <v>2</v>
       </c>
       <c r="G3061" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3062">
@@ -83104,7 +83104,7 @@
         <v>2</v>
       </c>
       <c r="G3062" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3063">
@@ -83131,7 +83131,7 @@
         <v>2</v>
       </c>
       <c r="G3063" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3064">
@@ -83158,7 +83158,7 @@
         <v>2</v>
       </c>
       <c r="G3064" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3065">
@@ -83185,7 +83185,7 @@
         <v>2</v>
       </c>
       <c r="G3065" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3066">
@@ -83212,7 +83212,7 @@
         <v>2</v>
       </c>
       <c r="G3066" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3067">
@@ -83239,7 +83239,7 @@
         <v>2</v>
       </c>
       <c r="G3067" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3068">
@@ -83266,7 +83266,7 @@
         <v>2</v>
       </c>
       <c r="G3068" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3069">
@@ -83293,7 +83293,7 @@
         <v>2</v>
       </c>
       <c r="G3069" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3070">
@@ -83320,7 +83320,7 @@
         <v>2</v>
       </c>
       <c r="G3070" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3071">
@@ -83347,7 +83347,7 @@
         <v>2</v>
       </c>
       <c r="G3071" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3072">
@@ -83374,7 +83374,7 @@
         <v>2</v>
       </c>
       <c r="G3072" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3073">
@@ -83401,7 +83401,7 @@
         <v>2</v>
       </c>
       <c r="G3073" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3074">
@@ -83428,7 +83428,7 @@
         <v>2</v>
       </c>
       <c r="G3074" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3075">
@@ -83455,7 +83455,7 @@
         <v>2</v>
       </c>
       <c r="G3075" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3076">
@@ -83482,7 +83482,7 @@
         <v>2</v>
       </c>
       <c r="G3076" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3077">
@@ -83509,7 +83509,7 @@
         <v>2</v>
       </c>
       <c r="G3077" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3078">
@@ -83536,7 +83536,7 @@
         <v>2</v>
       </c>
       <c r="G3078" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3079">
@@ -83563,7 +83563,7 @@
         <v>2</v>
       </c>
       <c r="G3079" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3080">
@@ -83590,7 +83590,7 @@
         <v>2</v>
       </c>
       <c r="G3080" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3081">
@@ -83617,7 +83617,7 @@
         <v>2</v>
       </c>
       <c r="G3081" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3082">
@@ -83644,7 +83644,7 @@
         <v>2</v>
       </c>
       <c r="G3082" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3083">
@@ -83671,7 +83671,7 @@
         <v>2</v>
       </c>
       <c r="G3083" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3084">
@@ -83698,7 +83698,7 @@
         <v>2</v>
       </c>
       <c r="G3084" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3085">
@@ -83725,7 +83725,7 @@
         <v>2</v>
       </c>
       <c r="G3085" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3086">
@@ -83752,7 +83752,7 @@
         <v>2</v>
       </c>
       <c r="G3086" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3087">
@@ -83779,7 +83779,7 @@
         <v>2</v>
       </c>
       <c r="G3087" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3088">
@@ -83806,7 +83806,7 @@
         <v>2</v>
       </c>
       <c r="G3088" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3089">
@@ -83833,7 +83833,7 @@
         <v>2</v>
       </c>
       <c r="G3089" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3090">
@@ -83860,7 +83860,7 @@
         <v>2</v>
       </c>
       <c r="G3090" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3091">
@@ -83887,7 +83887,7 @@
         <v>2</v>
       </c>
       <c r="G3091" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3092">
@@ -83914,7 +83914,7 @@
         <v>2</v>
       </c>
       <c r="G3092" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3093">
@@ -83941,7 +83941,7 @@
         <v>2</v>
       </c>
       <c r="G3093" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3094">
@@ -83968,7 +83968,7 @@
         <v>2</v>
       </c>
       <c r="G3094" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3095">
@@ -83995,7 +83995,7 @@
         <v>2</v>
       </c>
       <c r="G3095" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3096">
@@ -84022,7 +84022,7 @@
         <v>2</v>
       </c>
       <c r="G3096" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3097">
@@ -84049,7 +84049,7 @@
         <v>2</v>
       </c>
       <c r="G3097" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3098">
@@ -84076,7 +84076,7 @@
         <v>2</v>
       </c>
       <c r="G3098" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3099">
@@ -84103,7 +84103,7 @@
         <v>2</v>
       </c>
       <c r="G3099" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3100">
@@ -84130,7 +84130,7 @@
         <v>2</v>
       </c>
       <c r="G3100" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3101">
@@ -84157,7 +84157,7 @@
         <v>2</v>
       </c>
       <c r="G3101" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3102">
@@ -84184,7 +84184,7 @@
         <v>2</v>
       </c>
       <c r="G3102" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3103">
@@ -84211,7 +84211,7 @@
         <v>2</v>
       </c>
       <c r="G3103" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3104">
@@ -84238,7 +84238,7 @@
         <v>2</v>
       </c>
       <c r="G3104" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3105">
@@ -84265,7 +84265,7 @@
         <v>2</v>
       </c>
       <c r="G3105" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3106">
@@ -84292,7 +84292,7 @@
         <v>2</v>
       </c>
       <c r="G3106" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3107">
@@ -84319,7 +84319,7 @@
         <v>2</v>
       </c>
       <c r="G3107" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3108">
@@ -84346,7 +84346,7 @@
         <v>2</v>
       </c>
       <c r="G3108" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3109">
@@ -84373,7 +84373,7 @@
         <v>2</v>
       </c>
       <c r="G3109" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3110">
@@ -84400,7 +84400,7 @@
         <v>2</v>
       </c>
       <c r="G3110" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3111">
@@ -84427,7 +84427,7 @@
         <v>2</v>
       </c>
       <c r="G3111" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3112">
@@ -84454,7 +84454,7 @@
         <v>2</v>
       </c>
       <c r="G3112" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3113">
@@ -84481,7 +84481,7 @@
         <v>2</v>
       </c>
       <c r="G3113" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3114">
@@ -84508,7 +84508,7 @@
         <v>2</v>
       </c>
       <c r="G3114" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3115">
@@ -84535,7 +84535,7 @@
         <v>2</v>
       </c>
       <c r="G3115" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3116">
@@ -84562,7 +84562,7 @@
         <v>2</v>
       </c>
       <c r="G3116" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3117">
@@ -84589,7 +84589,7 @@
         <v>2</v>
       </c>
       <c r="G3117" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3118">
@@ -84616,7 +84616,7 @@
         <v>2</v>
       </c>
       <c r="G3118" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3119">
@@ -84643,7 +84643,7 @@
         <v>2</v>
       </c>
       <c r="G3119" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3120">
@@ -84670,7 +84670,7 @@
         <v>2</v>
       </c>
       <c r="G3120" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3121">
@@ -84697,7 +84697,7 @@
         <v>2</v>
       </c>
       <c r="G3121" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3122">
@@ -84724,7 +84724,7 @@
         <v>2</v>
       </c>
       <c r="G3122" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3123">
@@ -84751,7 +84751,7 @@
         <v>2</v>
       </c>
       <c r="G3123" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3124">
@@ -84778,7 +84778,7 @@
         <v>2</v>
       </c>
       <c r="G3124" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3125">
@@ -84805,7 +84805,7 @@
         <v>2</v>
       </c>
       <c r="G3125" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3126">
@@ -84832,7 +84832,7 @@
         <v>2</v>
       </c>
       <c r="G3126" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3127">
@@ -84859,7 +84859,7 @@
         <v>2</v>
       </c>
       <c r="G3127" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3128">
@@ -84886,7 +84886,7 @@
         <v>2</v>
       </c>
       <c r="G3128" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3129">
@@ -84913,7 +84913,7 @@
         <v>2</v>
       </c>
       <c r="G3129" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3130">
@@ -84940,7 +84940,7 @@
         <v>2</v>
       </c>
       <c r="G3130" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3131">
@@ -84967,7 +84967,7 @@
         <v>2</v>
       </c>
       <c r="G3131" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3132">
@@ -84994,7 +84994,7 @@
         <v>2</v>
       </c>
       <c r="G3132" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3133">
@@ -85021,7 +85021,7 @@
         <v>2</v>
       </c>
       <c r="G3133" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3134">
@@ -85048,7 +85048,7 @@
         <v>2</v>
       </c>
       <c r="G3134" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3135">
@@ -85075,7 +85075,7 @@
         <v>2</v>
       </c>
       <c r="G3135" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3136">
@@ -85102,7 +85102,7 @@
         <v>2</v>
       </c>
       <c r="G3136" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3137">
@@ -85129,7 +85129,7 @@
         <v>2</v>
       </c>
       <c r="G3137" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3138">
@@ -85156,7 +85156,7 @@
         <v>2</v>
       </c>
       <c r="G3138" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3139">
@@ -85183,7 +85183,7 @@
         <v>2</v>
       </c>
       <c r="G3139" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3140">
@@ -85210,7 +85210,7 @@
         <v>2</v>
       </c>
       <c r="G3140" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3141">
@@ -85237,7 +85237,7 @@
         <v>2</v>
       </c>
       <c r="G3141" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3142">
@@ -85264,7 +85264,7 @@
         <v>2</v>
       </c>
       <c r="G3142" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3143">
@@ -85291,7 +85291,7 @@
         <v>2</v>
       </c>
       <c r="G3143" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3144">
@@ -85318,7 +85318,7 @@
         <v>2</v>
       </c>
       <c r="G3144" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3145">
@@ -85345,7 +85345,7 @@
         <v>2</v>
       </c>
       <c r="G3145" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3146">
@@ -85372,7 +85372,7 @@
         <v>2</v>
       </c>
       <c r="G3146" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3147">
@@ -85399,7 +85399,7 @@
         <v>2</v>
       </c>
       <c r="G3147" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3148">
@@ -85426,7 +85426,7 @@
         <v>2</v>
       </c>
       <c r="G3148" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3149">
@@ -85453,7 +85453,7 @@
         <v>2</v>
       </c>
       <c r="G3149" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3150">
@@ -85480,7 +85480,7 @@
         <v>2</v>
       </c>
       <c r="G3150" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3151">
@@ -85507,7 +85507,7 @@
         <v>2</v>
       </c>
       <c r="G3151" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3152">
@@ -85534,7 +85534,7 @@
         <v>2</v>
       </c>
       <c r="G3152" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3153">
@@ -85561,7 +85561,7 @@
         <v>2</v>
       </c>
       <c r="G3153" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3154">
@@ -85588,7 +85588,7 @@
         <v>2</v>
       </c>
       <c r="G3154" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3155">
@@ -85615,7 +85615,7 @@
         <v>2</v>
       </c>
       <c r="G3155" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3156">
@@ -85642,7 +85642,7 @@
         <v>2</v>
       </c>
       <c r="G3156" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3157">
@@ -85669,7 +85669,7 @@
         <v>2</v>
       </c>
       <c r="G3157" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3158">
@@ -85696,7 +85696,7 @@
         <v>2</v>
       </c>
       <c r="G3158" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3159">
@@ -85723,7 +85723,7 @@
         <v>2</v>
       </c>
       <c r="G3159" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3160">
@@ -85750,7 +85750,7 @@
         <v>2</v>
       </c>
       <c r="G3160" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3161">
@@ -85777,7 +85777,7 @@
         <v>2</v>
       </c>
       <c r="G3161" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3162">
@@ -85804,7 +85804,7 @@
         <v>2</v>
       </c>
       <c r="G3162" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3163">
@@ -85831,7 +85831,7 @@
         <v>2</v>
       </c>
       <c r="G3163" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3164">
@@ -85858,7 +85858,7 @@
         <v>2</v>
       </c>
       <c r="G3164" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3165">
@@ -85885,7 +85885,7 @@
         <v>2</v>
       </c>
       <c r="G3165" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3166">
@@ -85912,7 +85912,7 @@
         <v>2</v>
       </c>
       <c r="G3166" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3167">
@@ -85939,7 +85939,7 @@
         <v>2</v>
       </c>
       <c r="G3167" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3168">
@@ -85966,7 +85966,7 @@
         <v>2</v>
       </c>
       <c r="G3168" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3169">
@@ -85993,7 +85993,7 @@
         <v>2</v>
       </c>
       <c r="G3169" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3170">
@@ -86020,7 +86020,7 @@
         <v>2</v>
       </c>
       <c r="G3170" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3171">
@@ -86047,7 +86047,7 @@
         <v>2</v>
       </c>
       <c r="G3171" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3172">
@@ -86074,7 +86074,7 @@
         <v>2</v>
       </c>
       <c r="G3172" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3173">
@@ -86101,7 +86101,7 @@
         <v>2</v>
       </c>
       <c r="G3173" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3174">
@@ -86128,7 +86128,7 @@
         <v>2</v>
       </c>
       <c r="G3174" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3175">
@@ -86155,7 +86155,7 @@
         <v>2</v>
       </c>
       <c r="G3175" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3176">
@@ -86182,7 +86182,7 @@
         <v>2</v>
       </c>
       <c r="G3176" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3177">
@@ -86209,7 +86209,7 @@
         <v>2</v>
       </c>
       <c r="G3177" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3178">
@@ -86236,7 +86236,7 @@
         <v>2</v>
       </c>
       <c r="G3178" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3179">
@@ -86263,7 +86263,7 @@
         <v>2</v>
       </c>
       <c r="G3179" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3180">
@@ -86290,7 +86290,7 @@
         <v>2</v>
       </c>
       <c r="G3180" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3181">
@@ -86317,7 +86317,7 @@
         <v>2</v>
       </c>
       <c r="G3181" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3182">
@@ -86344,7 +86344,7 @@
         <v>2</v>
       </c>
       <c r="G3182" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3183">
@@ -86371,7 +86371,7 @@
         <v>2</v>
       </c>
       <c r="G3183" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3184">
@@ -86398,7 +86398,7 @@
         <v>2</v>
       </c>
       <c r="G3184" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3185">
@@ -86425,7 +86425,7 @@
         <v>2</v>
       </c>
       <c r="G3185" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3186">
@@ -86452,7 +86452,7 @@
         <v>2</v>
       </c>
       <c r="G3186" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3187">
@@ -86479,7 +86479,7 @@
         <v>2</v>
       </c>
       <c r="G3187" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3188">
@@ -86506,7 +86506,7 @@
         <v>2</v>
       </c>
       <c r="G3188" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3189">
@@ -86533,7 +86533,7 @@
         <v>2</v>
       </c>
       <c r="G3189" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3190">
@@ -86560,7 +86560,7 @@
         <v>2</v>
       </c>
       <c r="G3190" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3191">
@@ -86587,7 +86587,7 @@
         <v>2</v>
       </c>
       <c r="G3191" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3192">
@@ -86614,7 +86614,7 @@
         <v>2</v>
       </c>
       <c r="G3192" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3193">
@@ -86641,7 +86641,7 @@
         <v>2</v>
       </c>
       <c r="G3193" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3194">
@@ -86668,7 +86668,7 @@
         <v>2</v>
       </c>
       <c r="G3194" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3195">
@@ -86695,7 +86695,7 @@
         <v>2</v>
       </c>
       <c r="G3195" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3196">
@@ -86722,7 +86722,7 @@
         <v>2</v>
       </c>
       <c r="G3196" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3197">
@@ -86749,7 +86749,7 @@
         <v>2</v>
       </c>
       <c r="G3197" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3198">
@@ -86776,7 +86776,7 @@
         <v>2</v>
       </c>
       <c r="G3198" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3199">
@@ -86803,7 +86803,7 @@
         <v>2</v>
       </c>
       <c r="G3199" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3200">
@@ -86830,7 +86830,7 @@
         <v>2</v>
       </c>
       <c r="G3200" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3201">
@@ -86857,7 +86857,7 @@
         <v>2</v>
       </c>
       <c r="G3201" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3202">
@@ -86884,7 +86884,7 @@
         <v>2</v>
       </c>
       <c r="G3202" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3203">
@@ -86911,7 +86911,7 @@
         <v>2</v>
       </c>
       <c r="G3203" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3204">
@@ -86938,7 +86938,7 @@
         <v>2</v>
       </c>
       <c r="G3204" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3205">
@@ -86965,7 +86965,7 @@
         <v>2</v>
       </c>
       <c r="G3205" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3206">
@@ -86992,7 +86992,7 @@
         <v>2</v>
       </c>
       <c r="G3206" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3207">
@@ -87019,7 +87019,7 @@
         <v>2</v>
       </c>
       <c r="G3207" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3208">
@@ -87046,7 +87046,7 @@
         <v>2</v>
       </c>
       <c r="G3208" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3209">
@@ -87073,7 +87073,7 @@
         <v>2</v>
       </c>
       <c r="G3209" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3210">
@@ -87100,7 +87100,7 @@
         <v>2</v>
       </c>
       <c r="G3210" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3211">
@@ -87127,7 +87127,7 @@
         <v>2</v>
       </c>
       <c r="G3211" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3212">
@@ -87154,7 +87154,7 @@
         <v>2</v>
       </c>
       <c r="G3212" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3213">
@@ -87181,7 +87181,7 @@
         <v>2</v>
       </c>
       <c r="G3213" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3214">
@@ -87208,7 +87208,7 @@
         <v>2</v>
       </c>
       <c r="G3214" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3215">
@@ -87235,7 +87235,7 @@
         <v>2</v>
       </c>
       <c r="G3215" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3216">
@@ -87262,7 +87262,7 @@
         <v>2</v>
       </c>
       <c r="G3216" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3217">
@@ -87289,7 +87289,7 @@
         <v>2</v>
       </c>
       <c r="G3217" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3218">
@@ -87316,7 +87316,7 @@
         <v>2</v>
       </c>
       <c r="G3218" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3219">
@@ -87343,7 +87343,7 @@
         <v>2</v>
       </c>
       <c r="G3219" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3220">
@@ -87370,7 +87370,7 @@
         <v>2</v>
       </c>
       <c r="G3220" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3221">
@@ -87397,7 +87397,7 @@
         <v>2</v>
       </c>
       <c r="G3221" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3222">
@@ -87424,7 +87424,7 @@
         <v>2</v>
       </c>
       <c r="G3222" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3223">
@@ -87451,7 +87451,7 @@
         <v>2</v>
       </c>
       <c r="G3223" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3224">
@@ -87478,7 +87478,7 @@
         <v>2</v>
       </c>
       <c r="G3224" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3225">
@@ -87505,7 +87505,7 @@
         <v>2</v>
       </c>
       <c r="G3225" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3226">
@@ -87532,7 +87532,7 @@
         <v>2</v>
       </c>
       <c r="G3226" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3227">
@@ -87559,7 +87559,7 @@
         <v>2</v>
       </c>
       <c r="G3227" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3228">
@@ -87586,7 +87586,7 @@
         <v>2</v>
       </c>
       <c r="G3228" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3229">
@@ -87613,7 +87613,7 @@
         <v>2</v>
       </c>
       <c r="G3229" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3230">
@@ -87640,7 +87640,7 @@
         <v>2</v>
       </c>
       <c r="G3230" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3231">
@@ -87667,7 +87667,7 @@
         <v>2</v>
       </c>
       <c r="G3231" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3232">
@@ -87694,7 +87694,7 @@
         <v>2</v>
       </c>
       <c r="G3232" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3233">
@@ -87721,7 +87721,7 @@
         <v>2</v>
       </c>
       <c r="G3233" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3234">
@@ -87748,7 +87748,7 @@
         <v>2</v>
       </c>
       <c r="G3234" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3235">
@@ -87775,7 +87775,7 @@
         <v>2</v>
       </c>
       <c r="G3235" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3236">
@@ -87802,7 +87802,7 @@
         <v>2</v>
       </c>
       <c r="G3236" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3237">
@@ -87829,7 +87829,7 @@
         <v>2</v>
       </c>
       <c r="G3237" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3238">
@@ -87856,7 +87856,7 @@
         <v>2</v>
       </c>
       <c r="G3238" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3239">
@@ -87883,7 +87883,7 @@
         <v>2</v>
       </c>
       <c r="G3239" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3240">
@@ -87910,7 +87910,7 @@
         <v>2</v>
       </c>
       <c r="G3240" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3241">
@@ -87937,7 +87937,7 @@
         <v>2</v>
       </c>
       <c r="G3241" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3242">
@@ -87964,7 +87964,7 @@
         <v>2</v>
       </c>
       <c r="G3242" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3243">
@@ -87991,7 +87991,7 @@
         <v>2</v>
       </c>
       <c r="G3243" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3244">
@@ -88018,7 +88018,7 @@
         <v>2</v>
       </c>
       <c r="G3244" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3245">
@@ -88045,7 +88045,7 @@
         <v>2</v>
       </c>
       <c r="G3245" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3246">
@@ -88072,7 +88072,7 @@
         <v>2</v>
       </c>
       <c r="G3246" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3247">
@@ -88099,7 +88099,7 @@
         <v>2</v>
       </c>
       <c r="G3247" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3248">
@@ -88126,7 +88126,7 @@
         <v>2</v>
       </c>
       <c r="G3248" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3249">
@@ -88153,7 +88153,7 @@
         <v>2</v>
       </c>
       <c r="G3249" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3250">
@@ -88180,7 +88180,7 @@
         <v>2</v>
       </c>
       <c r="G3250" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3251">
@@ -88207,7 +88207,7 @@
         <v>2</v>
       </c>
       <c r="G3251" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3252">
@@ -88234,7 +88234,7 @@
         <v>2</v>
       </c>
       <c r="G3252" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3253">
@@ -88261,7 +88261,7 @@
         <v>2</v>
       </c>
       <c r="G3253" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3254">
@@ -88288,7 +88288,7 @@
         <v>2</v>
       </c>
       <c r="G3254" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3255">
@@ -88315,7 +88315,7 @@
         <v>2</v>
       </c>
       <c r="G3255" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3256">
@@ -88342,7 +88342,7 @@
         <v>2</v>
       </c>
       <c r="G3256" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3257">
@@ -88369,7 +88369,7 @@
         <v>2</v>
       </c>
       <c r="G3257" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3258">
@@ -88396,7 +88396,7 @@
         <v>2</v>
       </c>
       <c r="G3258" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3259">
@@ -88423,7 +88423,7 @@
         <v>2</v>
       </c>
       <c r="G3259" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3260">
@@ -88450,7 +88450,7 @@
         <v>2</v>
       </c>
       <c r="G3260" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3261">
@@ -88477,7 +88477,7 @@
         <v>2</v>
       </c>
       <c r="G3261" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3262">
@@ -88504,7 +88504,7 @@
         <v>2</v>
       </c>
       <c r="G3262" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3263">
@@ -88531,7 +88531,7 @@
         <v>2</v>
       </c>
       <c r="G3263" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3264">
@@ -88558,7 +88558,7 @@
         <v>2</v>
       </c>
       <c r="G3264" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3265">
@@ -88585,7 +88585,7 @@
         <v>2</v>
       </c>
       <c r="G3265" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3266">
@@ -88612,7 +88612,7 @@
         <v>2</v>
       </c>
       <c r="G3266" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3267">
@@ -88639,7 +88639,7 @@
         <v>2</v>
       </c>
       <c r="G3267" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3268">
@@ -88666,7 +88666,7 @@
         <v>2</v>
       </c>
       <c r="G3268" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3269">
@@ -88693,7 +88693,7 @@
         <v>2</v>
       </c>
       <c r="G3269" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3270">
@@ -88720,7 +88720,7 @@
         <v>2</v>
       </c>
       <c r="G3270" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3271">
@@ -88747,7 +88747,7 @@
         <v>2</v>
       </c>
       <c r="G3271" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3272">
@@ -88774,7 +88774,7 @@
         <v>2</v>
       </c>
       <c r="G3272" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3273">
@@ -88801,7 +88801,7 @@
         <v>2</v>
       </c>
       <c r="G3273" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3274">
@@ -88828,7 +88828,7 @@
         <v>2</v>
       </c>
       <c r="G3274" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3275">
@@ -88855,7 +88855,7 @@
         <v>2</v>
       </c>
       <c r="G3275" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3276">
@@ -88882,7 +88882,7 @@
         <v>2</v>
       </c>
       <c r="G3276" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3277">
@@ -88909,7 +88909,7 @@
         <v>2</v>
       </c>
       <c r="G3277" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3278">
@@ -88936,7 +88936,7 @@
         <v>2</v>
       </c>
       <c r="G3278" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3279">
@@ -88963,7 +88963,7 @@
         <v>2</v>
       </c>
       <c r="G3279" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3280">
@@ -88990,7 +88990,7 @@
         <v>2</v>
       </c>
       <c r="G3280" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3281">
@@ -89017,7 +89017,7 @@
         <v>2</v>
       </c>
       <c r="G3281" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3282">
@@ -89044,7 +89044,7 @@
         <v>2</v>
       </c>
       <c r="G3282" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3283">
@@ -89071,7 +89071,7 @@
         <v>2</v>
       </c>
       <c r="G3283" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3284">
@@ -89098,7 +89098,7 @@
         <v>2</v>
       </c>
       <c r="G3284" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3285">
@@ -89125,7 +89125,7 @@
         <v>2</v>
       </c>
       <c r="G3285" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3286">
@@ -89152,7 +89152,7 @@
         <v>2</v>
       </c>
       <c r="G3286" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3287">
@@ -89179,7 +89179,7 @@
         <v>2</v>
       </c>
       <c r="G3287" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3288">
@@ -89206,7 +89206,7 @@
         <v>2</v>
       </c>
       <c r="G3288" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
     <row r="3289">
@@ -89233,7 +89233,7 @@
         <v>2</v>
       </c>
       <c r="G3289" s="2" t="n">
-        <v>46279.49819652397</v>
+        <v>46279.89901818455</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3289"/>
+  <dimension ref="A1:G3313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80188,7 +80188,7 @@
         <v>2</v>
       </c>
       <c r="G2954" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2955">
@@ -80215,7 +80215,7 @@
         <v>2</v>
       </c>
       <c r="G2955" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2956">
@@ -80226,7 +80226,7 @@
         <v>3</v>
       </c>
       <c r="C2956" t="n">
-        <v>10.28</v>
+        <v>10.27</v>
       </c>
       <c r="D2956" t="inlineStr">
         <is>
@@ -80242,7 +80242,7 @@
         <v>2</v>
       </c>
       <c r="G2956" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2957">
@@ -80253,7 +80253,7 @@
         <v>4</v>
       </c>
       <c r="C2957" t="n">
-        <v>11.02</v>
+        <v>11.01</v>
       </c>
       <c r="D2957" t="inlineStr">
         <is>
@@ -80269,7 +80269,7 @@
         <v>2</v>
       </c>
       <c r="G2957" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2958">
@@ -80296,7 +80296,7 @@
         <v>2</v>
       </c>
       <c r="G2958" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2959">
@@ -80307,7 +80307,7 @@
         <v>6</v>
       </c>
       <c r="C2959" t="n">
-        <v>15.5</v>
+        <v>15.49</v>
       </c>
       <c r="D2959" t="inlineStr">
         <is>
@@ -80323,7 +80323,7 @@
         <v>2</v>
       </c>
       <c r="G2959" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2960">
@@ -80350,7 +80350,7 @@
         <v>2</v>
       </c>
       <c r="G2960" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2961">
@@ -80377,7 +80377,7 @@
         <v>2</v>
       </c>
       <c r="G2961" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2962">
@@ -80404,7 +80404,7 @@
         <v>2</v>
       </c>
       <c r="G2962" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2963">
@@ -80431,7 +80431,7 @@
         <v>2</v>
       </c>
       <c r="G2963" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2964">
@@ -80458,7 +80458,7 @@
         <v>2</v>
       </c>
       <c r="G2964" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2965">
@@ -80485,7 +80485,7 @@
         <v>2</v>
       </c>
       <c r="G2965" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2966">
@@ -80512,7 +80512,7 @@
         <v>2</v>
       </c>
       <c r="G2966" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2967">
@@ -80539,7 +80539,7 @@
         <v>2</v>
       </c>
       <c r="G2967" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2968">
@@ -80566,7 +80566,7 @@
         <v>2</v>
       </c>
       <c r="G2968" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2969">
@@ -80577,7 +80577,7 @@
         <v>16</v>
       </c>
       <c r="C2969" t="n">
-        <v>30.65</v>
+        <v>30.64</v>
       </c>
       <c r="D2969" t="inlineStr">
         <is>
@@ -80593,7 +80593,7 @@
         <v>2</v>
       </c>
       <c r="G2969" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2970">
@@ -80620,7 +80620,7 @@
         <v>2</v>
       </c>
       <c r="G2970" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2971">
@@ -80631,7 +80631,7 @@
         <v>18</v>
       </c>
       <c r="C2971" t="n">
-        <v>34.14</v>
+        <v>34.13</v>
       </c>
       <c r="D2971" t="inlineStr">
         <is>
@@ -80647,7 +80647,7 @@
         <v>2</v>
       </c>
       <c r="G2971" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2972">
@@ -80674,7 +80674,7 @@
         <v>2</v>
       </c>
       <c r="G2972" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2973">
@@ -80701,7 +80701,7 @@
         <v>2</v>
       </c>
       <c r="G2973" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2974">
@@ -80728,7 +80728,7 @@
         <v>2</v>
       </c>
       <c r="G2974" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2975">
@@ -80755,7 +80755,7 @@
         <v>2</v>
       </c>
       <c r="G2975" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2976">
@@ -80782,7 +80782,7 @@
         <v>2</v>
       </c>
       <c r="G2976" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2977">
@@ -80809,7 +80809,7 @@
         <v>2</v>
       </c>
       <c r="G2977" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2978">
@@ -80836,7 +80836,7 @@
         <v>2</v>
       </c>
       <c r="G2978" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2979">
@@ -80863,7 +80863,7 @@
         <v>2</v>
       </c>
       <c r="G2979" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2980">
@@ -80890,7 +80890,7 @@
         <v>2</v>
       </c>
       <c r="G2980" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2981">
@@ -80917,7 +80917,7 @@
         <v>2</v>
       </c>
       <c r="G2981" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2982">
@@ -80944,7 +80944,7 @@
         <v>2</v>
       </c>
       <c r="G2982" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2983">
@@ -80971,7 +80971,7 @@
         <v>2</v>
       </c>
       <c r="G2983" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2984">
@@ -80998,7 +80998,7 @@
         <v>2</v>
       </c>
       <c r="G2984" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2985">
@@ -81025,7 +81025,7 @@
         <v>2</v>
       </c>
       <c r="G2985" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2986">
@@ -81052,7 +81052,7 @@
         <v>2</v>
       </c>
       <c r="G2986" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2987">
@@ -81079,7 +81079,7 @@
         <v>2</v>
       </c>
       <c r="G2987" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2988">
@@ -81090,7 +81090,7 @@
         <v>11</v>
       </c>
       <c r="C2988" t="n">
-        <v>19.71</v>
+        <v>19.72</v>
       </c>
       <c r="D2988" t="inlineStr">
         <is>
@@ -81106,7 +81106,7 @@
         <v>2</v>
       </c>
       <c r="G2988" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2989">
@@ -81117,7 +81117,7 @@
         <v>12</v>
       </c>
       <c r="C2989" t="n">
-        <v>26.39</v>
+        <v>26.38</v>
       </c>
       <c r="D2989" t="inlineStr">
         <is>
@@ -81133,7 +81133,7 @@
         <v>2</v>
       </c>
       <c r="G2989" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2990">
@@ -81144,7 +81144,7 @@
         <v>13</v>
       </c>
       <c r="C2990" t="n">
-        <v>31.85</v>
+        <v>31.84</v>
       </c>
       <c r="D2990" t="inlineStr">
         <is>
@@ -81160,7 +81160,7 @@
         <v>2</v>
       </c>
       <c r="G2990" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2991">
@@ -81187,7 +81187,7 @@
         <v>2</v>
       </c>
       <c r="G2991" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2992">
@@ -81198,7 +81198,7 @@
         <v>15</v>
       </c>
       <c r="C2992" t="n">
-        <v>31.52</v>
+        <v>31.5</v>
       </c>
       <c r="D2992" t="inlineStr">
         <is>
@@ -81214,7 +81214,7 @@
         <v>2</v>
       </c>
       <c r="G2992" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2993">
@@ -81225,7 +81225,7 @@
         <v>16</v>
       </c>
       <c r="C2993" t="n">
-        <v>34.14</v>
+        <v>34.13</v>
       </c>
       <c r="D2993" t="inlineStr">
         <is>
@@ -81241,7 +81241,7 @@
         <v>2</v>
       </c>
       <c r="G2993" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2994">
@@ -81252,7 +81252,7 @@
         <v>17</v>
       </c>
       <c r="C2994" t="n">
-        <v>31.09</v>
+        <v>31.06</v>
       </c>
       <c r="D2994" t="inlineStr">
         <is>
@@ -81268,7 +81268,7 @@
         <v>2</v>
       </c>
       <c r="G2994" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2995">
@@ -81279,7 +81279,7 @@
         <v>18</v>
       </c>
       <c r="C2995" t="n">
-        <v>25.27</v>
+        <v>25.22</v>
       </c>
       <c r="D2995" t="inlineStr">
         <is>
@@ -81295,7 +81295,7 @@
         <v>2</v>
       </c>
       <c r="G2995" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2996">
@@ -81306,7 +81306,7 @@
         <v>19</v>
       </c>
       <c r="C2996" t="n">
-        <v>20.12</v>
+        <v>20.07</v>
       </c>
       <c r="D2996" t="inlineStr">
         <is>
@@ -81322,7 +81322,7 @@
         <v>2</v>
       </c>
       <c r="G2996" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2997">
@@ -81333,7 +81333,7 @@
         <v>20</v>
       </c>
       <c r="C2997" t="n">
-        <v>24.84</v>
+        <v>24.83</v>
       </c>
       <c r="D2997" t="inlineStr">
         <is>
@@ -81349,7 +81349,7 @@
         <v>2</v>
       </c>
       <c r="G2997" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2998">
@@ -81376,7 +81376,7 @@
         <v>2</v>
       </c>
       <c r="G2998" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="2999">
@@ -81403,7 +81403,7 @@
         <v>2</v>
       </c>
       <c r="G2999" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3000">
@@ -81430,7 +81430,7 @@
         <v>2</v>
       </c>
       <c r="G3000" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3001">
@@ -81457,7 +81457,7 @@
         <v>2</v>
       </c>
       <c r="G3001" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3002">
@@ -81484,7 +81484,7 @@
         <v>2</v>
       </c>
       <c r="G3002" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3003">
@@ -81511,7 +81511,7 @@
         <v>2</v>
       </c>
       <c r="G3003" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3004">
@@ -81522,7 +81522,7 @@
         <v>3</v>
       </c>
       <c r="C3004" t="n">
-        <v>12.64</v>
+        <v>12.63</v>
       </c>
       <c r="D3004" t="inlineStr">
         <is>
@@ -81538,7 +81538,7 @@
         <v>2</v>
       </c>
       <c r="G3004" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3005">
@@ -81565,7 +81565,7 @@
         <v>2</v>
       </c>
       <c r="G3005" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3006">
@@ -81592,7 +81592,7 @@
         <v>2</v>
       </c>
       <c r="G3006" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3007">
@@ -81619,7 +81619,7 @@
         <v>2</v>
       </c>
       <c r="G3007" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3008">
@@ -81646,7 +81646,7 @@
         <v>2</v>
       </c>
       <c r="G3008" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3009">
@@ -81673,7 +81673,7 @@
         <v>2</v>
       </c>
       <c r="G3009" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3010">
@@ -81684,7 +81684,7 @@
         <v>9</v>
       </c>
       <c r="C3010" t="n">
-        <v>52.79</v>
+        <v>52.78</v>
       </c>
       <c r="D3010" t="inlineStr">
         <is>
@@ -81700,7 +81700,7 @@
         <v>2</v>
       </c>
       <c r="G3010" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3011">
@@ -81711,7 +81711,7 @@
         <v>10</v>
       </c>
       <c r="C3011" t="n">
-        <v>24.87</v>
+        <v>24.86</v>
       </c>
       <c r="D3011" t="inlineStr">
         <is>
@@ -81727,7 +81727,7 @@
         <v>2</v>
       </c>
       <c r="G3011" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3012">
@@ -81738,7 +81738,7 @@
         <v>11</v>
       </c>
       <c r="C3012" t="n">
-        <v>19.11</v>
+        <v>19.09</v>
       </c>
       <c r="D3012" t="inlineStr">
         <is>
@@ -81754,7 +81754,7 @@
         <v>2</v>
       </c>
       <c r="G3012" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3013">
@@ -81781,7 +81781,7 @@
         <v>2</v>
       </c>
       <c r="G3013" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3014">
@@ -81808,7 +81808,7 @@
         <v>2</v>
       </c>
       <c r="G3014" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3015">
@@ -81819,7 +81819,7 @@
         <v>14</v>
       </c>
       <c r="C3015" t="n">
-        <v>22.7</v>
+        <v>22.69</v>
       </c>
       <c r="D3015" t="inlineStr">
         <is>
@@ -81835,7 +81835,7 @@
         <v>2</v>
       </c>
       <c r="G3015" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3016">
@@ -81862,7 +81862,7 @@
         <v>2</v>
       </c>
       <c r="G3016" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3017">
@@ -81873,7 +81873,7 @@
         <v>16</v>
       </c>
       <c r="C3017" t="n">
-        <v>23.48</v>
+        <v>23.44</v>
       </c>
       <c r="D3017" t="inlineStr">
         <is>
@@ -81889,7 +81889,7 @@
         <v>2</v>
       </c>
       <c r="G3017" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3018">
@@ -81900,7 +81900,7 @@
         <v>17</v>
       </c>
       <c r="C3018" t="n">
-        <v>22.76</v>
+        <v>22.72</v>
       </c>
       <c r="D3018" t="inlineStr">
         <is>
@@ -81916,7 +81916,7 @@
         <v>2</v>
       </c>
       <c r="G3018" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3019">
@@ -81927,7 +81927,7 @@
         <v>18</v>
       </c>
       <c r="C3019" t="n">
-        <v>21.22</v>
+        <v>21.19</v>
       </c>
       <c r="D3019" t="inlineStr">
         <is>
@@ -81943,7 +81943,7 @@
         <v>2</v>
       </c>
       <c r="G3019" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3020">
@@ -81954,7 +81954,7 @@
         <v>19</v>
       </c>
       <c r="C3020" t="n">
-        <v>23.57</v>
+        <v>23.52</v>
       </c>
       <c r="D3020" t="inlineStr">
         <is>
@@ -81970,7 +81970,7 @@
         <v>2</v>
       </c>
       <c r="G3020" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3021">
@@ -81981,7 +81981,7 @@
         <v>20</v>
       </c>
       <c r="C3021" t="n">
-        <v>36.48</v>
+        <v>36.47</v>
       </c>
       <c r="D3021" t="inlineStr">
         <is>
@@ -81997,7 +81997,7 @@
         <v>2</v>
       </c>
       <c r="G3021" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3022">
@@ -82024,7 +82024,7 @@
         <v>2</v>
       </c>
       <c r="G3022" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3023">
@@ -82051,7 +82051,7 @@
         <v>2</v>
       </c>
       <c r="G3023" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3024">
@@ -82078,7 +82078,7 @@
         <v>2</v>
       </c>
       <c r="G3024" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3025">
@@ -82105,7 +82105,7 @@
         <v>2</v>
       </c>
       <c r="G3025" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3026">
@@ -82132,7 +82132,7 @@
         <v>2</v>
       </c>
       <c r="G3026" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3027">
@@ -82159,7 +82159,7 @@
         <v>2</v>
       </c>
       <c r="G3027" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3028">
@@ -82186,7 +82186,7 @@
         <v>2</v>
       </c>
       <c r="G3028" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3029">
@@ -82213,7 +82213,7 @@
         <v>2</v>
       </c>
       <c r="G3029" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3030">
@@ -82240,7 +82240,7 @@
         <v>2</v>
       </c>
       <c r="G3030" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3031">
@@ -82267,7 +82267,7 @@
         <v>2</v>
       </c>
       <c r="G3031" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3032">
@@ -82294,7 +82294,7 @@
         <v>2</v>
       </c>
       <c r="G3032" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3033">
@@ -82321,7 +82321,7 @@
         <v>2</v>
       </c>
       <c r="G3033" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3034">
@@ -82348,7 +82348,7 @@
         <v>2</v>
       </c>
       <c r="G3034" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3035">
@@ -82375,7 +82375,7 @@
         <v>2</v>
       </c>
       <c r="G3035" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3036">
@@ -82402,7 +82402,7 @@
         <v>2</v>
       </c>
       <c r="G3036" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3037">
@@ -82429,7 +82429,7 @@
         <v>2</v>
       </c>
       <c r="G3037" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3038">
@@ -82456,7 +82456,7 @@
         <v>2</v>
       </c>
       <c r="G3038" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3039">
@@ -82467,7 +82467,7 @@
         <v>14</v>
       </c>
       <c r="C3039" t="n">
-        <v>16.3</v>
+        <v>16.29</v>
       </c>
       <c r="D3039" t="inlineStr">
         <is>
@@ -82483,7 +82483,7 @@
         <v>2</v>
       </c>
       <c r="G3039" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3040">
@@ -82510,7 +82510,7 @@
         <v>2</v>
       </c>
       <c r="G3040" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3041">
@@ -82537,7 +82537,7 @@
         <v>2</v>
       </c>
       <c r="G3041" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3042">
@@ -82548,7 +82548,7 @@
         <v>17</v>
       </c>
       <c r="C3042" t="n">
-        <v>13.6</v>
+        <v>13.59</v>
       </c>
       <c r="D3042" t="inlineStr">
         <is>
@@ -82564,7 +82564,7 @@
         <v>2</v>
       </c>
       <c r="G3042" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3043">
@@ -82575,7 +82575,7 @@
         <v>18</v>
       </c>
       <c r="C3043" t="n">
-        <v>26.55</v>
+        <v>26.54</v>
       </c>
       <c r="D3043" t="inlineStr">
         <is>
@@ -82591,7 +82591,7 @@
         <v>2</v>
       </c>
       <c r="G3043" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3044">
@@ -82618,7 +82618,7 @@
         <v>2</v>
       </c>
       <c r="G3044" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3045">
@@ -82645,7 +82645,7 @@
         <v>2</v>
       </c>
       <c r="G3045" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3046">
@@ -82672,7 +82672,7 @@
         <v>2</v>
       </c>
       <c r="G3046" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3047">
@@ -82699,7 +82699,7 @@
         <v>2</v>
       </c>
       <c r="G3047" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3048">
@@ -82726,7 +82726,7 @@
         <v>2</v>
       </c>
       <c r="G3048" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3049">
@@ -82753,7 +82753,7 @@
         <v>2</v>
       </c>
       <c r="G3049" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3050">
@@ -82780,7 +82780,7 @@
         <v>2</v>
       </c>
       <c r="G3050" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3051">
@@ -82807,7 +82807,7 @@
         <v>2</v>
       </c>
       <c r="G3051" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3052">
@@ -82834,7 +82834,7 @@
         <v>2</v>
       </c>
       <c r="G3052" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3053">
@@ -82861,7 +82861,7 @@
         <v>2</v>
       </c>
       <c r="G3053" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3054">
@@ -82888,7 +82888,7 @@
         <v>2</v>
       </c>
       <c r="G3054" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3055">
@@ -82915,7 +82915,7 @@
         <v>2</v>
       </c>
       <c r="G3055" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3056">
@@ -82942,7 +82942,7 @@
         <v>2</v>
       </c>
       <c r="G3056" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3057">
@@ -82953,7 +82953,7 @@
         <v>8</v>
       </c>
       <c r="C3057" t="n">
-        <v>30.95</v>
+        <v>30.96</v>
       </c>
       <c r="D3057" t="inlineStr">
         <is>
@@ -82969,7 +82969,7 @@
         <v>2</v>
       </c>
       <c r="G3057" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3058">
@@ -82996,7 +82996,7 @@
         <v>2</v>
       </c>
       <c r="G3058" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3059">
@@ -83023,7 +83023,7 @@
         <v>2</v>
       </c>
       <c r="G3059" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3060">
@@ -83034,7 +83034,7 @@
         <v>11</v>
       </c>
       <c r="C3060" t="n">
-        <v>18.45</v>
+        <v>18.44</v>
       </c>
       <c r="D3060" t="inlineStr">
         <is>
@@ -83050,7 +83050,7 @@
         <v>2</v>
       </c>
       <c r="G3060" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3061">
@@ -83077,7 +83077,7 @@
         <v>2</v>
       </c>
       <c r="G3061" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3062">
@@ -83088,7 +83088,7 @@
         <v>13</v>
       </c>
       <c r="C3062" t="n">
-        <v>14.12</v>
+        <v>14.11</v>
       </c>
       <c r="D3062" t="inlineStr">
         <is>
@@ -83104,7 +83104,7 @@
         <v>2</v>
       </c>
       <c r="G3062" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3063">
@@ -83131,7 +83131,7 @@
         <v>2</v>
       </c>
       <c r="G3063" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3064">
@@ -83158,7 +83158,7 @@
         <v>2</v>
       </c>
       <c r="G3064" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3065">
@@ -83185,7 +83185,7 @@
         <v>2</v>
       </c>
       <c r="G3065" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3066">
@@ -83212,7 +83212,7 @@
         <v>2</v>
       </c>
       <c r="G3066" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3067">
@@ -83239,7 +83239,7 @@
         <v>2</v>
       </c>
       <c r="G3067" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3068">
@@ -83266,7 +83266,7 @@
         <v>2</v>
       </c>
       <c r="G3068" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3069">
@@ -83293,7 +83293,7 @@
         <v>2</v>
       </c>
       <c r="G3069" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3070">
@@ -83320,7 +83320,7 @@
         <v>2</v>
       </c>
       <c r="G3070" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3071">
@@ -83347,7 +83347,7 @@
         <v>2</v>
       </c>
       <c r="G3071" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3072">
@@ -83374,7 +83374,7 @@
         <v>2</v>
       </c>
       <c r="G3072" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3073">
@@ -83401,7 +83401,7 @@
         <v>2</v>
       </c>
       <c r="G3073" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3074">
@@ -83428,7 +83428,7 @@
         <v>2</v>
       </c>
       <c r="G3074" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3075">
@@ -83455,7 +83455,7 @@
         <v>2</v>
       </c>
       <c r="G3075" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3076">
@@ -83482,7 +83482,7 @@
         <v>2</v>
       </c>
       <c r="G3076" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3077">
@@ -83509,7 +83509,7 @@
         <v>2</v>
       </c>
       <c r="G3077" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3078">
@@ -83536,7 +83536,7 @@
         <v>2</v>
       </c>
       <c r="G3078" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3079">
@@ -83563,7 +83563,7 @@
         <v>2</v>
       </c>
       <c r="G3079" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3080">
@@ -83590,7 +83590,7 @@
         <v>2</v>
       </c>
       <c r="G3080" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3081">
@@ -83617,7 +83617,7 @@
         <v>2</v>
       </c>
       <c r="G3081" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3082">
@@ -83644,7 +83644,7 @@
         <v>2</v>
       </c>
       <c r="G3082" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3083">
@@ -83671,7 +83671,7 @@
         <v>2</v>
       </c>
       <c r="G3083" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3084">
@@ -83698,7 +83698,7 @@
         <v>2</v>
       </c>
       <c r="G3084" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3085">
@@ -83725,7 +83725,7 @@
         <v>2</v>
       </c>
       <c r="G3085" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3086">
@@ -83752,7 +83752,7 @@
         <v>2</v>
       </c>
       <c r="G3086" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3087">
@@ -83779,7 +83779,7 @@
         <v>2</v>
       </c>
       <c r="G3087" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3088">
@@ -83806,7 +83806,7 @@
         <v>2</v>
       </c>
       <c r="G3088" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3089">
@@ -83833,7 +83833,7 @@
         <v>2</v>
       </c>
       <c r="G3089" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3090">
@@ -83860,7 +83860,7 @@
         <v>2</v>
       </c>
       <c r="G3090" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3091">
@@ -83871,7 +83871,7 @@
         <v>18</v>
       </c>
       <c r="C3091" t="n">
-        <v>22.69</v>
+        <v>22.68</v>
       </c>
       <c r="D3091" t="inlineStr">
         <is>
@@ -83887,7 +83887,7 @@
         <v>2</v>
       </c>
       <c r="G3091" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3092">
@@ -83898,7 +83898,7 @@
         <v>19</v>
       </c>
       <c r="C3092" t="n">
-        <v>30.89</v>
+        <v>30.88</v>
       </c>
       <c r="D3092" t="inlineStr">
         <is>
@@ -83914,7 +83914,7 @@
         <v>2</v>
       </c>
       <c r="G3092" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3093">
@@ -83925,7 +83925,7 @@
         <v>20</v>
       </c>
       <c r="C3093" t="n">
-        <v>29.31</v>
+        <v>29.3</v>
       </c>
       <c r="D3093" t="inlineStr">
         <is>
@@ -83941,7 +83941,7 @@
         <v>2</v>
       </c>
       <c r="G3093" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3094">
@@ -83968,7 +83968,7 @@
         <v>2</v>
       </c>
       <c r="G3094" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3095">
@@ -83995,7 +83995,7 @@
         <v>2</v>
       </c>
       <c r="G3095" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3096">
@@ -84022,7 +84022,7 @@
         <v>2</v>
       </c>
       <c r="G3096" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3097">
@@ -84049,7 +84049,7 @@
         <v>2</v>
       </c>
       <c r="G3097" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3098">
@@ -84076,7 +84076,7 @@
         <v>2</v>
       </c>
       <c r="G3098" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3099">
@@ -84087,7 +84087,7 @@
         <v>2</v>
       </c>
       <c r="C3099" t="n">
-        <v>12.31</v>
+        <v>12.26</v>
       </c>
       <c r="D3099" t="inlineStr">
         <is>
@@ -84103,7 +84103,7 @@
         <v>2</v>
       </c>
       <c r="G3099" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3100">
@@ -84114,7 +84114,7 @@
         <v>3</v>
       </c>
       <c r="C3100" t="n">
-        <v>9.630000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D3100" t="inlineStr">
         <is>
@@ -84130,7 +84130,7 @@
         <v>2</v>
       </c>
       <c r="G3100" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3101">
@@ -84157,7 +84157,7 @@
         <v>2</v>
       </c>
       <c r="G3101" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3102">
@@ -84184,7 +84184,7 @@
         <v>2</v>
       </c>
       <c r="G3102" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3103">
@@ -84211,7 +84211,7 @@
         <v>2</v>
       </c>
       <c r="G3103" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3104">
@@ -84222,7 +84222,7 @@
         <v>7</v>
       </c>
       <c r="C3104" t="n">
-        <v>23.25</v>
+        <v>23.22</v>
       </c>
       <c r="D3104" t="inlineStr">
         <is>
@@ -84238,7 +84238,7 @@
         <v>2</v>
       </c>
       <c r="G3104" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3105">
@@ -84249,7 +84249,7 @@
         <v>8</v>
       </c>
       <c r="C3105" t="n">
-        <v>50.35</v>
+        <v>50.33</v>
       </c>
       <c r="D3105" t="inlineStr">
         <is>
@@ -84265,7 +84265,7 @@
         <v>2</v>
       </c>
       <c r="G3105" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3106">
@@ -84292,7 +84292,7 @@
         <v>2</v>
       </c>
       <c r="G3106" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3107">
@@ -84303,7 +84303,7 @@
         <v>10</v>
       </c>
       <c r="C3107" t="n">
-        <v>22.76</v>
+        <v>22.73</v>
       </c>
       <c r="D3107" t="inlineStr">
         <is>
@@ -84319,7 +84319,7 @@
         <v>2</v>
       </c>
       <c r="G3107" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3108">
@@ -84330,7 +84330,7 @@
         <v>11</v>
       </c>
       <c r="C3108" t="n">
-        <v>18.06</v>
+        <v>18.02</v>
       </c>
       <c r="D3108" t="inlineStr">
         <is>
@@ -84346,7 +84346,7 @@
         <v>2</v>
       </c>
       <c r="G3108" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3109">
@@ -84357,7 +84357,7 @@
         <v>12</v>
       </c>
       <c r="C3109" t="n">
-        <v>20.38</v>
+        <v>20.34</v>
       </c>
       <c r="D3109" t="inlineStr">
         <is>
@@ -84373,7 +84373,7 @@
         <v>2</v>
       </c>
       <c r="G3109" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3110">
@@ -84384,7 +84384,7 @@
         <v>13</v>
       </c>
       <c r="C3110" t="n">
-        <v>21.72</v>
+        <v>21.69</v>
       </c>
       <c r="D3110" t="inlineStr">
         <is>
@@ -84400,7 +84400,7 @@
         <v>2</v>
       </c>
       <c r="G3110" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3111">
@@ -84411,7 +84411,7 @@
         <v>14</v>
       </c>
       <c r="C3111" t="n">
-        <v>21.72</v>
+        <v>21.68</v>
       </c>
       <c r="D3111" t="inlineStr">
         <is>
@@ -84427,7 +84427,7 @@
         <v>2</v>
       </c>
       <c r="G3111" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3112">
@@ -84438,7 +84438,7 @@
         <v>15</v>
       </c>
       <c r="C3112" t="n">
-        <v>22.85</v>
+        <v>22.81</v>
       </c>
       <c r="D3112" t="inlineStr">
         <is>
@@ -84454,7 +84454,7 @@
         <v>2</v>
       </c>
       <c r="G3112" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3113">
@@ -84481,7 +84481,7 @@
         <v>2</v>
       </c>
       <c r="G3113" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3114">
@@ -84492,7 +84492,7 @@
         <v>17</v>
       </c>
       <c r="C3114" t="n">
-        <v>22.76</v>
+        <v>22.75</v>
       </c>
       <c r="D3114" t="inlineStr">
         <is>
@@ -84508,7 +84508,7 @@
         <v>2</v>
       </c>
       <c r="G3114" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3115">
@@ -84535,7 +84535,7 @@
         <v>2</v>
       </c>
       <c r="G3115" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3116">
@@ -84546,7 +84546,7 @@
         <v>19</v>
       </c>
       <c r="C3116" t="n">
-        <v>24.25</v>
+        <v>24.24</v>
       </c>
       <c r="D3116" t="inlineStr">
         <is>
@@ -84562,7 +84562,7 @@
         <v>2</v>
       </c>
       <c r="G3116" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3117">
@@ -84573,7 +84573,7 @@
         <v>20</v>
       </c>
       <c r="C3117" t="n">
-        <v>29.96</v>
+        <v>29.94</v>
       </c>
       <c r="D3117" t="inlineStr">
         <is>
@@ -84589,7 +84589,7 @@
         <v>2</v>
       </c>
       <c r="G3117" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3118">
@@ -84600,7 +84600,7 @@
         <v>21</v>
       </c>
       <c r="C3118" t="n">
-        <v>32.59</v>
+        <v>32.58</v>
       </c>
       <c r="D3118" t="inlineStr">
         <is>
@@ -84616,7 +84616,7 @@
         <v>2</v>
       </c>
       <c r="G3118" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3119">
@@ -84627,7 +84627,7 @@
         <v>22</v>
       </c>
       <c r="C3119" t="n">
-        <v>37.68</v>
+        <v>37.67</v>
       </c>
       <c r="D3119" t="inlineStr">
         <is>
@@ -84643,7 +84643,7 @@
         <v>2</v>
       </c>
       <c r="G3119" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3120">
@@ -84670,7 +84670,7 @@
         <v>2</v>
       </c>
       <c r="G3120" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3121">
@@ -84681,7 +84681,7 @@
         <v>24</v>
       </c>
       <c r="C3121" t="n">
-        <v>34.02</v>
+        <v>34.01</v>
       </c>
       <c r="D3121" t="inlineStr">
         <is>
@@ -84697,7 +84697,7 @@
         <v>2</v>
       </c>
       <c r="G3121" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3122">
@@ -84708,7 +84708,7 @@
         <v>1</v>
       </c>
       <c r="C3122" t="n">
-        <v>9.69</v>
+        <v>9.91</v>
       </c>
       <c r="D3122" t="inlineStr">
         <is>
@@ -84724,7 +84724,7 @@
         <v>2</v>
       </c>
       <c r="G3122" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3123">
@@ -84735,7 +84735,7 @@
         <v>2</v>
       </c>
       <c r="C3123" t="n">
-        <v>12.38</v>
+        <v>12.3</v>
       </c>
       <c r="D3123" t="inlineStr">
         <is>
@@ -84751,7 +84751,7 @@
         <v>2</v>
       </c>
       <c r="G3123" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3124">
@@ -84762,7 +84762,7 @@
         <v>3</v>
       </c>
       <c r="C3124" t="n">
-        <v>10.97</v>
+        <v>11.02</v>
       </c>
       <c r="D3124" t="inlineStr">
         <is>
@@ -84778,7 +84778,7 @@
         <v>2</v>
       </c>
       <c r="G3124" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3125">
@@ -84789,7 +84789,7 @@
         <v>4</v>
       </c>
       <c r="C3125" t="n">
-        <v>10.58</v>
+        <v>10.54</v>
       </c>
       <c r="D3125" t="inlineStr">
         <is>
@@ -84805,7 +84805,7 @@
         <v>2</v>
       </c>
       <c r="G3125" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3126">
@@ -84816,7 +84816,7 @@
         <v>5</v>
       </c>
       <c r="C3126" t="n">
-        <v>11.03</v>
+        <v>11.02</v>
       </c>
       <c r="D3126" t="inlineStr">
         <is>
@@ -84832,7 +84832,7 @@
         <v>2</v>
       </c>
       <c r="G3126" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3127">
@@ -84843,7 +84843,7 @@
         <v>6</v>
       </c>
       <c r="C3127" t="n">
-        <v>13.99</v>
+        <v>14</v>
       </c>
       <c r="D3127" t="inlineStr">
         <is>
@@ -84859,7 +84859,7 @@
         <v>2</v>
       </c>
       <c r="G3127" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3128">
@@ -84870,7 +84870,7 @@
         <v>7</v>
       </c>
       <c r="C3128" t="n">
-        <v>19.99</v>
+        <v>19.82</v>
       </c>
       <c r="D3128" t="inlineStr">
         <is>
@@ -84886,7 +84886,7 @@
         <v>2</v>
       </c>
       <c r="G3128" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3129">
@@ -84897,7 +84897,7 @@
         <v>8</v>
       </c>
       <c r="C3129" t="n">
-        <v>33.48</v>
+        <v>33.61</v>
       </c>
       <c r="D3129" t="inlineStr">
         <is>
@@ -84913,7 +84913,7 @@
         <v>2</v>
       </c>
       <c r="G3129" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3130">
@@ -84924,7 +84924,7 @@
         <v>9</v>
       </c>
       <c r="C3130" t="n">
-        <v>28.9</v>
+        <v>28.96</v>
       </c>
       <c r="D3130" t="inlineStr">
         <is>
@@ -84940,7 +84940,7 @@
         <v>2</v>
       </c>
       <c r="G3130" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3131">
@@ -84951,7 +84951,7 @@
         <v>10</v>
       </c>
       <c r="C3131" t="n">
-        <v>23.64</v>
+        <v>23.57</v>
       </c>
       <c r="D3131" t="inlineStr">
         <is>
@@ -84967,7 +84967,7 @@
         <v>2</v>
       </c>
       <c r="G3131" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3132">
@@ -84978,7 +84978,7 @@
         <v>11</v>
       </c>
       <c r="C3132" t="n">
-        <v>17.51</v>
+        <v>17.36</v>
       </c>
       <c r="D3132" t="inlineStr">
         <is>
@@ -84994,7 +84994,7 @@
         <v>2</v>
       </c>
       <c r="G3132" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3133">
@@ -85005,7 +85005,7 @@
         <v>12</v>
       </c>
       <c r="C3133" t="n">
-        <v>19.93</v>
+        <v>19.86</v>
       </c>
       <c r="D3133" t="inlineStr">
         <is>
@@ -85021,7 +85021,7 @@
         <v>2</v>
       </c>
       <c r="G3133" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3134">
@@ -85032,7 +85032,7 @@
         <v>13</v>
       </c>
       <c r="C3134" t="n">
-        <v>20.38</v>
+        <v>20.34</v>
       </c>
       <c r="D3134" t="inlineStr">
         <is>
@@ -85048,7 +85048,7 @@
         <v>2</v>
       </c>
       <c r="G3134" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3135">
@@ -85075,7 +85075,7 @@
         <v>2</v>
       </c>
       <c r="G3135" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3136">
@@ -85086,7 +85086,7 @@
         <v>15</v>
       </c>
       <c r="C3136" t="n">
-        <v>20.91</v>
+        <v>20.95</v>
       </c>
       <c r="D3136" t="inlineStr">
         <is>
@@ -85102,7 +85102,7 @@
         <v>2</v>
       </c>
       <c r="G3136" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3137">
@@ -85113,7 +85113,7 @@
         <v>16</v>
       </c>
       <c r="C3137" t="n">
-        <v>19.93</v>
+        <v>20</v>
       </c>
       <c r="D3137" t="inlineStr">
         <is>
@@ -85129,7 +85129,7 @@
         <v>2</v>
       </c>
       <c r="G3137" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3138">
@@ -85156,7 +85156,7 @@
         <v>2</v>
       </c>
       <c r="G3138" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3139">
@@ -85167,7 +85167,7 @@
         <v>18</v>
       </c>
       <c r="C3139" t="n">
-        <v>17.1</v>
+        <v>16.99</v>
       </c>
       <c r="D3139" t="inlineStr">
         <is>
@@ -85183,7 +85183,7 @@
         <v>2</v>
       </c>
       <c r="G3139" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3140">
@@ -85194,7 +85194,7 @@
         <v>19</v>
       </c>
       <c r="C3140" t="n">
-        <v>15.88</v>
+        <v>15.8</v>
       </c>
       <c r="D3140" t="inlineStr">
         <is>
@@ -85210,7 +85210,7 @@
         <v>2</v>
       </c>
       <c r="G3140" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3141">
@@ -85221,7 +85221,7 @@
         <v>20</v>
       </c>
       <c r="C3141" t="n">
-        <v>28.36</v>
+        <v>28.25</v>
       </c>
       <c r="D3141" t="inlineStr">
         <is>
@@ -85237,7 +85237,7 @@
         <v>2</v>
       </c>
       <c r="G3141" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3142">
@@ -85248,7 +85248,7 @@
         <v>21</v>
       </c>
       <c r="C3142" t="n">
-        <v>36.52</v>
+        <v>36.69</v>
       </c>
       <c r="D3142" t="inlineStr">
         <is>
@@ -85264,7 +85264,7 @@
         <v>2</v>
       </c>
       <c r="G3142" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3143">
@@ -85275,7 +85275,7 @@
         <v>22</v>
       </c>
       <c r="C3143" t="n">
-        <v>35.96</v>
+        <v>35.84</v>
       </c>
       <c r="D3143" t="inlineStr">
         <is>
@@ -85291,7 +85291,7 @@
         <v>2</v>
       </c>
       <c r="G3143" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3144">
@@ -85302,7 +85302,7 @@
         <v>23</v>
       </c>
       <c r="C3144" t="n">
-        <v>33.38</v>
+        <v>33.28</v>
       </c>
       <c r="D3144" t="inlineStr">
         <is>
@@ -85318,7 +85318,7 @@
         <v>2</v>
       </c>
       <c r="G3144" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3145">
@@ -85329,7 +85329,7 @@
         <v>24</v>
       </c>
       <c r="C3145" t="n">
-        <v>27.61</v>
+        <v>27.55</v>
       </c>
       <c r="D3145" t="inlineStr">
         <is>
@@ -85345,7 +85345,7 @@
         <v>2</v>
       </c>
       <c r="G3145" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3146">
@@ -85356,7 +85356,7 @@
         <v>1</v>
       </c>
       <c r="C3146" t="n">
-        <v>19.7</v>
+        <v>19.66</v>
       </c>
       <c r="D3146" t="inlineStr">
         <is>
@@ -85372,7 +85372,7 @@
         <v>2</v>
       </c>
       <c r="G3146" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3147">
@@ -85383,7 +85383,7 @@
         <v>2</v>
       </c>
       <c r="C3147" t="n">
-        <v>13.76</v>
+        <v>13.74</v>
       </c>
       <c r="D3147" t="inlineStr">
         <is>
@@ -85399,7 +85399,7 @@
         <v>2</v>
       </c>
       <c r="G3147" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3148">
@@ -85410,7 +85410,7 @@
         <v>3</v>
       </c>
       <c r="C3148" t="n">
-        <v>13.59</v>
+        <v>13.48</v>
       </c>
       <c r="D3148" t="inlineStr">
         <is>
@@ -85426,7 +85426,7 @@
         <v>2</v>
       </c>
       <c r="G3148" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3149">
@@ -85437,7 +85437,7 @@
         <v>4</v>
       </c>
       <c r="C3149" t="n">
-        <v>14.65</v>
+        <v>14.58</v>
       </c>
       <c r="D3149" t="inlineStr">
         <is>
@@ -85453,7 +85453,7 @@
         <v>2</v>
       </c>
       <c r="G3149" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3150">
@@ -85464,7 +85464,7 @@
         <v>5</v>
       </c>
       <c r="C3150" t="n">
-        <v>16.05</v>
+        <v>16.06</v>
       </c>
       <c r="D3150" t="inlineStr">
         <is>
@@ -85480,7 +85480,7 @@
         <v>2</v>
       </c>
       <c r="G3150" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3151">
@@ -85491,7 +85491,7 @@
         <v>6</v>
       </c>
       <c r="C3151" t="n">
-        <v>17.46</v>
+        <v>17.47</v>
       </c>
       <c r="D3151" t="inlineStr">
         <is>
@@ -85507,7 +85507,7 @@
         <v>2</v>
       </c>
       <c r="G3151" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3152">
@@ -85518,7 +85518,7 @@
         <v>7</v>
       </c>
       <c r="C3152" t="n">
-        <v>22.79</v>
+        <v>22.75</v>
       </c>
       <c r="D3152" t="inlineStr">
         <is>
@@ -85534,7 +85534,7 @@
         <v>2</v>
       </c>
       <c r="G3152" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3153">
@@ -85545,7 +85545,7 @@
         <v>8</v>
       </c>
       <c r="C3153" t="n">
-        <v>46.97</v>
+        <v>46.82</v>
       </c>
       <c r="D3153" t="inlineStr">
         <is>
@@ -85561,7 +85561,7 @@
         <v>2</v>
       </c>
       <c r="G3153" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3154">
@@ -85572,7 +85572,7 @@
         <v>9</v>
       </c>
       <c r="C3154" t="n">
-        <v>48.98</v>
+        <v>48.78</v>
       </c>
       <c r="D3154" t="inlineStr">
         <is>
@@ -85588,7 +85588,7 @@
         <v>2</v>
       </c>
       <c r="G3154" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3155">
@@ -85599,7 +85599,7 @@
         <v>10</v>
       </c>
       <c r="C3155" t="n">
-        <v>29.32</v>
+        <v>29.12</v>
       </c>
       <c r="D3155" t="inlineStr">
         <is>
@@ -85615,7 +85615,7 @@
         <v>2</v>
       </c>
       <c r="G3155" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3156">
@@ -85626,7 +85626,7 @@
         <v>11</v>
       </c>
       <c r="C3156" t="n">
-        <v>20.31</v>
+        <v>20.26</v>
       </c>
       <c r="D3156" t="inlineStr">
         <is>
@@ -85642,7 +85642,7 @@
         <v>2</v>
       </c>
       <c r="G3156" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3157">
@@ -85653,7 +85653,7 @@
         <v>12</v>
       </c>
       <c r="C3157" t="n">
-        <v>29.45</v>
+        <v>29.44</v>
       </c>
       <c r="D3157" t="inlineStr">
         <is>
@@ -85669,7 +85669,7 @@
         <v>2</v>
       </c>
       <c r="G3157" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3158">
@@ -85680,7 +85680,7 @@
         <v>13</v>
       </c>
       <c r="C3158" t="n">
-        <v>30.94</v>
+        <v>30.89</v>
       </c>
       <c r="D3158" t="inlineStr">
         <is>
@@ -85696,7 +85696,7 @@
         <v>2</v>
       </c>
       <c r="G3158" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3159">
@@ -85707,7 +85707,7 @@
         <v>14</v>
       </c>
       <c r="C3159" t="n">
-        <v>31.85</v>
+        <v>31.8</v>
       </c>
       <c r="D3159" t="inlineStr">
         <is>
@@ -85723,7 +85723,7 @@
         <v>2</v>
       </c>
       <c r="G3159" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3160">
@@ -85734,7 +85734,7 @@
         <v>15</v>
       </c>
       <c r="C3160" t="n">
-        <v>32.21</v>
+        <v>32.17</v>
       </c>
       <c r="D3160" t="inlineStr">
         <is>
@@ -85750,7 +85750,7 @@
         <v>2</v>
       </c>
       <c r="G3160" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3161">
@@ -85761,7 +85761,7 @@
         <v>16</v>
       </c>
       <c r="C3161" t="n">
-        <v>31.3</v>
+        <v>31.26</v>
       </c>
       <c r="D3161" t="inlineStr">
         <is>
@@ -85777,7 +85777,7 @@
         <v>2</v>
       </c>
       <c r="G3161" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3162">
@@ -85788,7 +85788,7 @@
         <v>17</v>
       </c>
       <c r="C3162" t="n">
-        <v>31.43</v>
+        <v>31.37</v>
       </c>
       <c r="D3162" t="inlineStr">
         <is>
@@ -85804,7 +85804,7 @@
         <v>2</v>
       </c>
       <c r="G3162" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3163">
@@ -85815,7 +85815,7 @@
         <v>18</v>
       </c>
       <c r="C3163" t="n">
-        <v>35.01</v>
+        <v>34.95</v>
       </c>
       <c r="D3163" t="inlineStr">
         <is>
@@ -85831,7 +85831,7 @@
         <v>2</v>
       </c>
       <c r="G3163" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3164">
@@ -85842,7 +85842,7 @@
         <v>19</v>
       </c>
       <c r="C3164" t="n">
-        <v>32.43</v>
+        <v>32.32</v>
       </c>
       <c r="D3164" t="inlineStr">
         <is>
@@ -85858,7 +85858,7 @@
         <v>2</v>
       </c>
       <c r="G3164" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3165">
@@ -85869,7 +85869,7 @@
         <v>20</v>
       </c>
       <c r="C3165" t="n">
-        <v>32.34</v>
+        <v>32.27</v>
       </c>
       <c r="D3165" t="inlineStr">
         <is>
@@ -85885,7 +85885,7 @@
         <v>2</v>
       </c>
       <c r="G3165" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3166">
@@ -85896,7 +85896,7 @@
         <v>21</v>
       </c>
       <c r="C3166" t="n">
-        <v>37.09</v>
+        <v>36.99</v>
       </c>
       <c r="D3166" t="inlineStr">
         <is>
@@ -85912,7 +85912,7 @@
         <v>2</v>
       </c>
       <c r="G3166" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3167">
@@ -85923,7 +85923,7 @@
         <v>22</v>
       </c>
       <c r="C3167" t="n">
-        <v>37.73</v>
+        <v>37.66</v>
       </c>
       <c r="D3167" t="inlineStr">
         <is>
@@ -85939,7 +85939,7 @@
         <v>2</v>
       </c>
       <c r="G3167" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3168">
@@ -85950,7 +85950,7 @@
         <v>23</v>
       </c>
       <c r="C3168" t="n">
-        <v>37.2</v>
+        <v>37.09</v>
       </c>
       <c r="D3168" t="inlineStr">
         <is>
@@ -85966,7 +85966,7 @@
         <v>2</v>
       </c>
       <c r="G3168" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3169">
@@ -85977,7 +85977,7 @@
         <v>24</v>
       </c>
       <c r="C3169" t="n">
-        <v>37.21</v>
+        <v>37.13</v>
       </c>
       <c r="D3169" t="inlineStr">
         <is>
@@ -85993,7 +85993,7 @@
         <v>2</v>
       </c>
       <c r="G3169" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3170">
@@ -86004,7 +86004,7 @@
         <v>1</v>
       </c>
       <c r="C3170" t="n">
-        <v>20.06</v>
+        <v>20.07</v>
       </c>
       <c r="D3170" t="inlineStr">
         <is>
@@ -86020,7 +86020,7 @@
         <v>2</v>
       </c>
       <c r="G3170" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3171">
@@ -86031,7 +86031,7 @@
         <v>2</v>
       </c>
       <c r="C3171" t="n">
-        <v>15.33</v>
+        <v>15.34</v>
       </c>
       <c r="D3171" t="inlineStr">
         <is>
@@ -86047,7 +86047,7 @@
         <v>2</v>
       </c>
       <c r="G3171" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3172">
@@ -86058,7 +86058,7 @@
         <v>3</v>
       </c>
       <c r="C3172" t="n">
-        <v>16.59</v>
+        <v>16.58</v>
       </c>
       <c r="D3172" t="inlineStr">
         <is>
@@ -86074,7 +86074,7 @@
         <v>2</v>
       </c>
       <c r="G3172" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3173">
@@ -86085,7 +86085,7 @@
         <v>4</v>
       </c>
       <c r="C3173" t="n">
-        <v>15.88</v>
+        <v>15.83</v>
       </c>
       <c r="D3173" t="inlineStr">
         <is>
@@ -86101,7 +86101,7 @@
         <v>2</v>
       </c>
       <c r="G3173" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3174">
@@ -86112,7 +86112,7 @@
         <v>5</v>
       </c>
       <c r="C3174" t="n">
-        <v>13.67</v>
+        <v>13.63</v>
       </c>
       <c r="D3174" t="inlineStr">
         <is>
@@ -86128,7 +86128,7 @@
         <v>2</v>
       </c>
       <c r="G3174" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3175">
@@ -86139,7 +86139,7 @@
         <v>6</v>
       </c>
       <c r="C3175" t="n">
-        <v>13.11</v>
+        <v>13.07</v>
       </c>
       <c r="D3175" t="inlineStr">
         <is>
@@ -86155,7 +86155,7 @@
         <v>2</v>
       </c>
       <c r="G3175" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3176">
@@ -86166,7 +86166,7 @@
         <v>7</v>
       </c>
       <c r="C3176" t="n">
-        <v>19.88</v>
+        <v>19.87</v>
       </c>
       <c r="D3176" t="inlineStr">
         <is>
@@ -86182,7 +86182,7 @@
         <v>2</v>
       </c>
       <c r="G3176" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3177">
@@ -86193,7 +86193,7 @@
         <v>8</v>
       </c>
       <c r="C3177" t="n">
-        <v>40.91</v>
+        <v>40.89</v>
       </c>
       <c r="D3177" t="inlineStr">
         <is>
@@ -86209,7 +86209,7 @@
         <v>2</v>
       </c>
       <c r="G3177" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3178">
@@ -86220,7 +86220,7 @@
         <v>9</v>
       </c>
       <c r="C3178" t="n">
-        <v>42.06</v>
+        <v>42.04</v>
       </c>
       <c r="D3178" t="inlineStr">
         <is>
@@ -86236,7 +86236,7 @@
         <v>2</v>
       </c>
       <c r="G3178" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3179">
@@ -86247,7 +86247,7 @@
         <v>10</v>
       </c>
       <c r="C3179" t="n">
-        <v>19.86</v>
+        <v>19.8</v>
       </c>
       <c r="D3179" t="inlineStr">
         <is>
@@ -86263,7 +86263,7 @@
         <v>2</v>
       </c>
       <c r="G3179" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3180">
@@ -86274,7 +86274,7 @@
         <v>11</v>
       </c>
       <c r="C3180" t="n">
-        <v>13.42</v>
+        <v>13.09</v>
       </c>
       <c r="D3180" t="inlineStr">
         <is>
@@ -86290,7 +86290,7 @@
         <v>2</v>
       </c>
       <c r="G3180" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3181">
@@ -86301,7 +86301,7 @@
         <v>12</v>
       </c>
       <c r="C3181" t="n">
-        <v>29.33</v>
+        <v>29.18</v>
       </c>
       <c r="D3181" t="inlineStr">
         <is>
@@ -86317,7 +86317,7 @@
         <v>2</v>
       </c>
       <c r="G3181" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3182">
@@ -86328,7 +86328,7 @@
         <v>13</v>
       </c>
       <c r="C3182" t="n">
-        <v>30.38</v>
+        <v>30.62</v>
       </c>
       <c r="D3182" t="inlineStr">
         <is>
@@ -86344,7 +86344,7 @@
         <v>2</v>
       </c>
       <c r="G3182" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3183">
@@ -86355,7 +86355,7 @@
         <v>14</v>
       </c>
       <c r="C3183" t="n">
-        <v>28.59</v>
+        <v>28.9</v>
       </c>
       <c r="D3183" t="inlineStr">
         <is>
@@ -86371,7 +86371,7 @@
         <v>2</v>
       </c>
       <c r="G3183" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3184">
@@ -86382,7 +86382,7 @@
         <v>15</v>
       </c>
       <c r="C3184" t="n">
-        <v>32.06</v>
+        <v>32.02</v>
       </c>
       <c r="D3184" t="inlineStr">
         <is>
@@ -86398,7 +86398,7 @@
         <v>2</v>
       </c>
       <c r="G3184" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3185">
@@ -86409,7 +86409,7 @@
         <v>16</v>
       </c>
       <c r="C3185" t="n">
-        <v>33.05</v>
+        <v>33.01</v>
       </c>
       <c r="D3185" t="inlineStr">
         <is>
@@ -86425,7 +86425,7 @@
         <v>2</v>
       </c>
       <c r="G3185" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3186">
@@ -86436,7 +86436,7 @@
         <v>17</v>
       </c>
       <c r="C3186" t="n">
-        <v>31.83</v>
+        <v>31.73</v>
       </c>
       <c r="D3186" t="inlineStr">
         <is>
@@ -86452,7 +86452,7 @@
         <v>2</v>
       </c>
       <c r="G3186" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3187">
@@ -86463,7 +86463,7 @@
         <v>18</v>
       </c>
       <c r="C3187" t="n">
-        <v>27.19</v>
+        <v>27.16</v>
       </c>
       <c r="D3187" t="inlineStr">
         <is>
@@ -86479,7 +86479,7 @@
         <v>2</v>
       </c>
       <c r="G3187" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3188">
@@ -86506,7 +86506,7 @@
         <v>2</v>
       </c>
       <c r="G3188" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3189">
@@ -86517,7 +86517,7 @@
         <v>20</v>
       </c>
       <c r="C3189" t="n">
-        <v>16.85</v>
+        <v>16.9</v>
       </c>
       <c r="D3189" t="inlineStr">
         <is>
@@ -86533,7 +86533,7 @@
         <v>2</v>
       </c>
       <c r="G3189" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3190">
@@ -86544,7 +86544,7 @@
         <v>21</v>
       </c>
       <c r="C3190" t="n">
-        <v>26.72</v>
+        <v>26.71</v>
       </c>
       <c r="D3190" t="inlineStr">
         <is>
@@ -86560,7 +86560,7 @@
         <v>2</v>
       </c>
       <c r="G3190" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3191">
@@ -86571,7 +86571,7 @@
         <v>22</v>
       </c>
       <c r="C3191" t="n">
-        <v>28.55</v>
+        <v>28.54</v>
       </c>
       <c r="D3191" t="inlineStr">
         <is>
@@ -86587,7 +86587,7 @@
         <v>2</v>
       </c>
       <c r="G3191" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3192">
@@ -86598,7 +86598,7 @@
         <v>23</v>
       </c>
       <c r="C3192" t="n">
-        <v>27.68</v>
+        <v>27.66</v>
       </c>
       <c r="D3192" t="inlineStr">
         <is>
@@ -86614,7 +86614,7 @@
         <v>2</v>
       </c>
       <c r="G3192" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3193">
@@ -86625,7 +86625,7 @@
         <v>24</v>
       </c>
       <c r="C3193" t="n">
-        <v>28.12</v>
+        <v>28.1</v>
       </c>
       <c r="D3193" t="inlineStr">
         <is>
@@ -86641,7 +86641,7 @@
         <v>2</v>
       </c>
       <c r="G3193" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3194">
@@ -86652,7 +86652,7 @@
         <v>1</v>
       </c>
       <c r="C3194" t="n">
-        <v>8.59</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="D3194" t="inlineStr">
         <is>
@@ -86668,7 +86668,7 @@
         <v>2</v>
       </c>
       <c r="G3194" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3195">
@@ -86679,7 +86679,7 @@
         <v>2</v>
       </c>
       <c r="C3195" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="D3195" t="inlineStr">
         <is>
@@ -86695,7 +86695,7 @@
         <v>2</v>
       </c>
       <c r="G3195" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3196">
@@ -86706,7 +86706,7 @@
         <v>3</v>
       </c>
       <c r="C3196" t="n">
-        <v>10.72</v>
+        <v>10.73</v>
       </c>
       <c r="D3196" t="inlineStr">
         <is>
@@ -86722,7 +86722,7 @@
         <v>2</v>
       </c>
       <c r="G3196" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3197">
@@ -86733,7 +86733,7 @@
         <v>4</v>
       </c>
       <c r="C3197" t="n">
-        <v>10.04</v>
+        <v>10.11</v>
       </c>
       <c r="D3197" t="inlineStr">
         <is>
@@ -86749,7 +86749,7 @@
         <v>2</v>
       </c>
       <c r="G3197" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3198">
@@ -86760,7 +86760,7 @@
         <v>5</v>
       </c>
       <c r="C3198" t="n">
-        <v>9.789999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D3198" t="inlineStr">
         <is>
@@ -86776,7 +86776,7 @@
         <v>2</v>
       </c>
       <c r="G3198" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3199">
@@ -86787,7 +86787,7 @@
         <v>6</v>
       </c>
       <c r="C3199" t="n">
-        <v>11.7</v>
+        <v>11.73</v>
       </c>
       <c r="D3199" t="inlineStr">
         <is>
@@ -86803,7 +86803,7 @@
         <v>2</v>
       </c>
       <c r="G3199" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3200">
@@ -86814,7 +86814,7 @@
         <v>7</v>
       </c>
       <c r="C3200" t="n">
-        <v>22.18</v>
+        <v>22.02</v>
       </c>
       <c r="D3200" t="inlineStr">
         <is>
@@ -86830,7 +86830,7 @@
         <v>2</v>
       </c>
       <c r="G3200" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3201">
@@ -86841,7 +86841,7 @@
         <v>8</v>
       </c>
       <c r="C3201" t="n">
-        <v>35.75</v>
+        <v>35.51</v>
       </c>
       <c r="D3201" t="inlineStr">
         <is>
@@ -86857,7 +86857,7 @@
         <v>2</v>
       </c>
       <c r="G3201" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3202">
@@ -86868,7 +86868,7 @@
         <v>9</v>
       </c>
       <c r="C3202" t="n">
-        <v>35.56</v>
+        <v>35.46</v>
       </c>
       <c r="D3202" t="inlineStr">
         <is>
@@ -86884,7 +86884,7 @@
         <v>2</v>
       </c>
       <c r="G3202" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3203">
@@ -86895,7 +86895,7 @@
         <v>10</v>
       </c>
       <c r="C3203" t="n">
-        <v>23.4</v>
+        <v>23.35</v>
       </c>
       <c r="D3203" t="inlineStr">
         <is>
@@ -86911,7 +86911,7 @@
         <v>2</v>
       </c>
       <c r="G3203" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3204">
@@ -86922,7 +86922,7 @@
         <v>11</v>
       </c>
       <c r="C3204" t="n">
-        <v>29.25</v>
+        <v>29.16</v>
       </c>
       <c r="D3204" t="inlineStr">
         <is>
@@ -86938,7 +86938,7 @@
         <v>2</v>
       </c>
       <c r="G3204" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3205">
@@ -86949,7 +86949,7 @@
         <v>12</v>
       </c>
       <c r="C3205" t="n">
-        <v>43.19</v>
+        <v>43.04</v>
       </c>
       <c r="D3205" t="inlineStr">
         <is>
@@ -86965,7 +86965,7 @@
         <v>2</v>
       </c>
       <c r="G3205" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3206">
@@ -86976,7 +86976,7 @@
         <v>13</v>
       </c>
       <c r="C3206" t="n">
-        <v>46.96</v>
+        <v>46.86</v>
       </c>
       <c r="D3206" t="inlineStr">
         <is>
@@ -86992,7 +86992,7 @@
         <v>2</v>
       </c>
       <c r="G3206" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3207">
@@ -87003,7 +87003,7 @@
         <v>14</v>
       </c>
       <c r="C3207" t="n">
-        <v>51.05</v>
+        <v>50.83</v>
       </c>
       <c r="D3207" t="inlineStr">
         <is>
@@ -87019,7 +87019,7 @@
         <v>2</v>
       </c>
       <c r="G3207" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3208">
@@ -87030,7 +87030,7 @@
         <v>15</v>
       </c>
       <c r="C3208" t="n">
-        <v>49.45</v>
+        <v>49.23</v>
       </c>
       <c r="D3208" t="inlineStr">
         <is>
@@ -87046,7 +87046,7 @@
         <v>2</v>
       </c>
       <c r="G3208" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3209">
@@ -87057,7 +87057,7 @@
         <v>16</v>
       </c>
       <c r="C3209" t="n">
-        <v>51.03</v>
+        <v>50.79</v>
       </c>
       <c r="D3209" t="inlineStr">
         <is>
@@ -87073,7 +87073,7 @@
         <v>2</v>
       </c>
       <c r="G3209" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3210">
@@ -87084,7 +87084,7 @@
         <v>17</v>
       </c>
       <c r="C3210" t="n">
-        <v>47.78</v>
+        <v>47.55</v>
       </c>
       <c r="D3210" t="inlineStr">
         <is>
@@ -87100,7 +87100,7 @@
         <v>2</v>
       </c>
       <c r="G3210" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3211">
@@ -87111,7 +87111,7 @@
         <v>18</v>
       </c>
       <c r="C3211" t="n">
-        <v>41.39</v>
+        <v>41.25</v>
       </c>
       <c r="D3211" t="inlineStr">
         <is>
@@ -87127,7 +87127,7 @@
         <v>2</v>
       </c>
       <c r="G3211" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3212">
@@ -87138,7 +87138,7 @@
         <v>19</v>
       </c>
       <c r="C3212" t="n">
-        <v>28.61</v>
+        <v>28.52</v>
       </c>
       <c r="D3212" t="inlineStr">
         <is>
@@ -87154,7 +87154,7 @@
         <v>2</v>
       </c>
       <c r="G3212" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3213">
@@ -87165,7 +87165,7 @@
         <v>20</v>
       </c>
       <c r="C3213" t="n">
-        <v>22.42</v>
+        <v>22.47</v>
       </c>
       <c r="D3213" t="inlineStr">
         <is>
@@ -87181,7 +87181,7 @@
         <v>2</v>
       </c>
       <c r="G3213" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3214">
@@ -87192,7 +87192,7 @@
         <v>21</v>
       </c>
       <c r="C3214" t="n">
-        <v>33.59</v>
+        <v>33.56</v>
       </c>
       <c r="D3214" t="inlineStr">
         <is>
@@ -87208,7 +87208,7 @@
         <v>2</v>
       </c>
       <c r="G3214" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3215">
@@ -87219,7 +87219,7 @@
         <v>22</v>
       </c>
       <c r="C3215" t="n">
-        <v>37.76</v>
+        <v>37.7</v>
       </c>
       <c r="D3215" t="inlineStr">
         <is>
@@ -87235,7 +87235,7 @@
         <v>2</v>
       </c>
       <c r="G3215" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3216">
@@ -87246,7 +87246,7 @@
         <v>23</v>
       </c>
       <c r="C3216" t="n">
-        <v>37.52</v>
+        <v>37.45</v>
       </c>
       <c r="D3216" t="inlineStr">
         <is>
@@ -87262,7 +87262,7 @@
         <v>2</v>
       </c>
       <c r="G3216" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3217">
@@ -87273,7 +87273,7 @@
         <v>24</v>
       </c>
       <c r="C3217" t="n">
-        <v>29.36</v>
+        <v>29.31</v>
       </c>
       <c r="D3217" t="inlineStr">
         <is>
@@ -87289,7 +87289,7 @@
         <v>2</v>
       </c>
       <c r="G3217" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3218">
@@ -87300,7 +87300,7 @@
         <v>1</v>
       </c>
       <c r="C3218" t="n">
-        <v>10.31</v>
+        <v>10.74</v>
       </c>
       <c r="D3218" t="inlineStr">
         <is>
@@ -87316,7 +87316,7 @@
         <v>2</v>
       </c>
       <c r="G3218" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3219">
@@ -87327,7 +87327,7 @@
         <v>2</v>
       </c>
       <c r="C3219" t="n">
-        <v>9.390000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="D3219" t="inlineStr">
         <is>
@@ -87343,7 +87343,7 @@
         <v>2</v>
       </c>
       <c r="G3219" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3220">
@@ -87354,7 +87354,7 @@
         <v>3</v>
       </c>
       <c r="C3220" t="n">
-        <v>5.05</v>
+        <v>6.54</v>
       </c>
       <c r="D3220" t="inlineStr">
         <is>
@@ -87370,7 +87370,7 @@
         <v>2</v>
       </c>
       <c r="G3220" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3221">
@@ -87381,7 +87381,7 @@
         <v>4</v>
       </c>
       <c r="C3221" t="n">
-        <v>6.88</v>
+        <v>7.12</v>
       </c>
       <c r="D3221" t="inlineStr">
         <is>
@@ -87397,7 +87397,7 @@
         <v>2</v>
       </c>
       <c r="G3221" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3222">
@@ -87408,7 +87408,7 @@
         <v>5</v>
       </c>
       <c r="C3222" t="n">
-        <v>8.01</v>
+        <v>8.15</v>
       </c>
       <c r="D3222" t="inlineStr">
         <is>
@@ -87424,7 +87424,7 @@
         <v>2</v>
       </c>
       <c r="G3222" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3223">
@@ -87435,7 +87435,7 @@
         <v>6</v>
       </c>
       <c r="C3223" t="n">
-        <v>8.83</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="D3223" t="inlineStr">
         <is>
@@ -87451,7 +87451,7 @@
         <v>2</v>
       </c>
       <c r="G3223" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3224">
@@ -87462,7 +87462,7 @@
         <v>7</v>
       </c>
       <c r="C3224" t="n">
-        <v>18.84</v>
+        <v>18.87</v>
       </c>
       <c r="D3224" t="inlineStr">
         <is>
@@ -87478,7 +87478,7 @@
         <v>2</v>
       </c>
       <c r="G3224" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3225">
@@ -87489,7 +87489,7 @@
         <v>8</v>
       </c>
       <c r="C3225" t="n">
-        <v>31.82</v>
+        <v>31.83</v>
       </c>
       <c r="D3225" t="inlineStr">
         <is>
@@ -87505,7 +87505,7 @@
         <v>2</v>
       </c>
       <c r="G3225" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3226">
@@ -87516,7 +87516,7 @@
         <v>9</v>
       </c>
       <c r="C3226" t="n">
-        <v>29.81</v>
+        <v>30.01</v>
       </c>
       <c r="D3226" t="inlineStr">
         <is>
@@ -87532,7 +87532,7 @@
         <v>2</v>
       </c>
       <c r="G3226" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3227">
@@ -87543,7 +87543,7 @@
         <v>10</v>
       </c>
       <c r="C3227" t="n">
-        <v>23.44</v>
+        <v>23.21</v>
       </c>
       <c r="D3227" t="inlineStr">
         <is>
@@ -87559,7 +87559,7 @@
         <v>2</v>
       </c>
       <c r="G3227" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3228">
@@ -87570,7 +87570,7 @@
         <v>11</v>
       </c>
       <c r="C3228" t="n">
-        <v>27.57</v>
+        <v>27.3</v>
       </c>
       <c r="D3228" t="inlineStr">
         <is>
@@ -87586,7 +87586,7 @@
         <v>2</v>
       </c>
       <c r="G3228" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3229">
@@ -87597,7 +87597,7 @@
         <v>12</v>
       </c>
       <c r="C3229" t="n">
-        <v>30.1</v>
+        <v>29.72</v>
       </c>
       <c r="D3229" t="inlineStr">
         <is>
@@ -87613,7 +87613,7 @@
         <v>2</v>
       </c>
       <c r="G3229" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3230">
@@ -87624,7 +87624,7 @@
         <v>13</v>
       </c>
       <c r="C3230" t="n">
-        <v>35.71</v>
+        <v>35.25</v>
       </c>
       <c r="D3230" t="inlineStr">
         <is>
@@ -87640,7 +87640,7 @@
         <v>2</v>
       </c>
       <c r="G3230" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3231">
@@ -87651,7 +87651,7 @@
         <v>14</v>
       </c>
       <c r="C3231" t="n">
-        <v>35.87</v>
+        <v>35.3</v>
       </c>
       <c r="D3231" t="inlineStr">
         <is>
@@ -87667,7 +87667,7 @@
         <v>2</v>
       </c>
       <c r="G3231" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3232">
@@ -87678,7 +87678,7 @@
         <v>15</v>
       </c>
       <c r="C3232" t="n">
-        <v>34.91</v>
+        <v>34.36</v>
       </c>
       <c r="D3232" t="inlineStr">
         <is>
@@ -87694,7 +87694,7 @@
         <v>2</v>
       </c>
       <c r="G3232" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3233">
@@ -87705,7 +87705,7 @@
         <v>16</v>
       </c>
       <c r="C3233" t="n">
-        <v>36.28</v>
+        <v>35.69</v>
       </c>
       <c r="D3233" t="inlineStr">
         <is>
@@ -87721,7 +87721,7 @@
         <v>2</v>
       </c>
       <c r="G3233" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3234">
@@ -87732,7 +87732,7 @@
         <v>17</v>
       </c>
       <c r="C3234" t="n">
-        <v>37.06</v>
+        <v>36.45</v>
       </c>
       <c r="D3234" t="inlineStr">
         <is>
@@ -87748,7 +87748,7 @@
         <v>2</v>
       </c>
       <c r="G3234" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3235">
@@ -87759,7 +87759,7 @@
         <v>18</v>
       </c>
       <c r="C3235" t="n">
-        <v>34.62</v>
+        <v>34.09</v>
       </c>
       <c r="D3235" t="inlineStr">
         <is>
@@ -87775,7 +87775,7 @@
         <v>2</v>
       </c>
       <c r="G3235" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3236">
@@ -87786,7 +87786,7 @@
         <v>19</v>
       </c>
       <c r="C3236" t="n">
-        <v>24.92</v>
+        <v>25.25</v>
       </c>
       <c r="D3236" t="inlineStr">
         <is>
@@ -87802,7 +87802,7 @@
         <v>2</v>
       </c>
       <c r="G3236" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3237">
@@ -87813,7 +87813,7 @@
         <v>20</v>
       </c>
       <c r="C3237" t="n">
-        <v>17.86</v>
+        <v>18.28</v>
       </c>
       <c r="D3237" t="inlineStr">
         <is>
@@ -87829,7 +87829,7 @@
         <v>2</v>
       </c>
       <c r="G3237" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3238">
@@ -87840,7 +87840,7 @@
         <v>21</v>
       </c>
       <c r="C3238" t="n">
-        <v>31.39</v>
+        <v>31.18</v>
       </c>
       <c r="D3238" t="inlineStr">
         <is>
@@ -87856,7 +87856,7 @@
         <v>2</v>
       </c>
       <c r="G3238" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3239">
@@ -87867,7 +87867,7 @@
         <v>22</v>
       </c>
       <c r="C3239" t="n">
-        <v>32.96</v>
+        <v>32.73</v>
       </c>
       <c r="D3239" t="inlineStr">
         <is>
@@ -87883,7 +87883,7 @@
         <v>2</v>
       </c>
       <c r="G3239" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3240">
@@ -87894,7 +87894,7 @@
         <v>23</v>
       </c>
       <c r="C3240" t="n">
-        <v>25.21</v>
+        <v>25.08</v>
       </c>
       <c r="D3240" t="inlineStr">
         <is>
@@ -87910,7 +87910,7 @@
         <v>2</v>
       </c>
       <c r="G3240" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3241">
@@ -87921,7 +87921,7 @@
         <v>24</v>
       </c>
       <c r="C3241" t="n">
-        <v>22.7</v>
+        <v>22.67</v>
       </c>
       <c r="D3241" t="inlineStr">
         <is>
@@ -87937,7 +87937,7 @@
         <v>2</v>
       </c>
       <c r="G3241" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3242">
@@ -87948,7 +87948,7 @@
         <v>1</v>
       </c>
       <c r="C3242" t="n">
-        <v>6.29</v>
+        <v>6.41</v>
       </c>
       <c r="D3242" t="inlineStr">
         <is>
@@ -87964,7 +87964,7 @@
         <v>2</v>
       </c>
       <c r="G3242" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3243">
@@ -87975,7 +87975,7 @@
         <v>2</v>
       </c>
       <c r="C3243" t="n">
-        <v>4.31</v>
+        <v>4.86</v>
       </c>
       <c r="D3243" t="inlineStr">
         <is>
@@ -87991,7 +87991,7 @@
         <v>2</v>
       </c>
       <c r="G3243" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3244">
@@ -88002,7 +88002,7 @@
         <v>3</v>
       </c>
       <c r="C3244" t="n">
-        <v>2.87</v>
+        <v>3.82</v>
       </c>
       <c r="D3244" t="inlineStr">
         <is>
@@ -88018,7 +88018,7 @@
         <v>2</v>
       </c>
       <c r="G3244" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3245">
@@ -88029,7 +88029,7 @@
         <v>4</v>
       </c>
       <c r="C3245" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="D3245" t="inlineStr">
         <is>
@@ -88045,7 +88045,7 @@
         <v>2</v>
       </c>
       <c r="G3245" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3246">
@@ -88056,7 +88056,7 @@
         <v>5</v>
       </c>
       <c r="C3246" t="n">
-        <v>9.92</v>
+        <v>11.4</v>
       </c>
       <c r="D3246" t="inlineStr">
         <is>
@@ -88072,7 +88072,7 @@
         <v>2</v>
       </c>
       <c r="G3246" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3247">
@@ -88083,7 +88083,7 @@
         <v>6</v>
       </c>
       <c r="C3247" t="n">
-        <v>8.369999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="D3247" t="inlineStr">
         <is>
@@ -88099,7 +88099,7 @@
         <v>2</v>
       </c>
       <c r="G3247" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3248">
@@ -88110,7 +88110,7 @@
         <v>7</v>
       </c>
       <c r="C3248" t="n">
-        <v>4.4</v>
+        <v>6.08</v>
       </c>
       <c r="D3248" t="inlineStr">
         <is>
@@ -88126,7 +88126,7 @@
         <v>2</v>
       </c>
       <c r="G3248" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3249">
@@ -88137,7 +88137,7 @@
         <v>8</v>
       </c>
       <c r="C3249" t="n">
-        <v>27.43</v>
+        <v>27.97</v>
       </c>
       <c r="D3249" t="inlineStr">
         <is>
@@ -88153,7 +88153,7 @@
         <v>2</v>
       </c>
       <c r="G3249" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3250">
@@ -88164,7 +88164,7 @@
         <v>9</v>
       </c>
       <c r="C3250" t="n">
-        <v>27.25</v>
+        <v>27.24</v>
       </c>
       <c r="D3250" t="inlineStr">
         <is>
@@ -88180,7 +88180,7 @@
         <v>2</v>
       </c>
       <c r="G3250" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3251">
@@ -88191,7 +88191,7 @@
         <v>10</v>
       </c>
       <c r="C3251" t="n">
-        <v>25.71</v>
+        <v>25.46</v>
       </c>
       <c r="D3251" t="inlineStr">
         <is>
@@ -88207,7 +88207,7 @@
         <v>2</v>
       </c>
       <c r="G3251" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3252">
@@ -88218,7 +88218,7 @@
         <v>11</v>
       </c>
       <c r="C3252" t="n">
-        <v>23.15</v>
+        <v>22.79</v>
       </c>
       <c r="D3252" t="inlineStr">
         <is>
@@ -88234,7 +88234,7 @@
         <v>2</v>
       </c>
       <c r="G3252" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3253">
@@ -88245,7 +88245,7 @@
         <v>12</v>
       </c>
       <c r="C3253" t="n">
-        <v>22.84</v>
+        <v>22.81</v>
       </c>
       <c r="D3253" t="inlineStr">
         <is>
@@ -88261,7 +88261,7 @@
         <v>2</v>
       </c>
       <c r="G3253" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3254">
@@ -88272,7 +88272,7 @@
         <v>13</v>
       </c>
       <c r="C3254" t="n">
-        <v>39.57</v>
+        <v>40.34</v>
       </c>
       <c r="D3254" t="inlineStr">
         <is>
@@ -88288,7 +88288,7 @@
         <v>2</v>
       </c>
       <c r="G3254" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3255">
@@ -88299,7 +88299,7 @@
         <v>14</v>
       </c>
       <c r="C3255" t="n">
-        <v>38.07</v>
+        <v>38.86</v>
       </c>
       <c r="D3255" t="inlineStr">
         <is>
@@ -88315,7 +88315,7 @@
         <v>2</v>
       </c>
       <c r="G3255" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3256">
@@ -88326,7 +88326,7 @@
         <v>15</v>
       </c>
       <c r="C3256" t="n">
-        <v>35.43</v>
+        <v>34.24</v>
       </c>
       <c r="D3256" t="inlineStr">
         <is>
@@ -88342,7 +88342,7 @@
         <v>2</v>
       </c>
       <c r="G3256" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3257">
@@ -88353,7 +88353,7 @@
         <v>16</v>
       </c>
       <c r="C3257" t="n">
-        <v>36.35</v>
+        <v>35.19</v>
       </c>
       <c r="D3257" t="inlineStr">
         <is>
@@ -88369,7 +88369,7 @@
         <v>2</v>
       </c>
       <c r="G3257" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3258">
@@ -88380,7 +88380,7 @@
         <v>17</v>
       </c>
       <c r="C3258" t="n">
-        <v>31.97</v>
+        <v>31.45</v>
       </c>
       <c r="D3258" t="inlineStr">
         <is>
@@ -88396,7 +88396,7 @@
         <v>2</v>
       </c>
       <c r="G3258" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3259">
@@ -88407,7 +88407,7 @@
         <v>18</v>
       </c>
       <c r="C3259" t="n">
-        <v>30.55</v>
+        <v>29.95</v>
       </c>
       <c r="D3259" t="inlineStr">
         <is>
@@ -88423,7 +88423,7 @@
         <v>2</v>
       </c>
       <c r="G3259" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3260">
@@ -88434,7 +88434,7 @@
         <v>19</v>
       </c>
       <c r="C3260" t="n">
-        <v>18.03</v>
+        <v>19.03</v>
       </c>
       <c r="D3260" t="inlineStr">
         <is>
@@ -88450,7 +88450,7 @@
         <v>2</v>
       </c>
       <c r="G3260" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3261">
@@ -88461,7 +88461,7 @@
         <v>20</v>
       </c>
       <c r="C3261" t="n">
-        <v>16.31</v>
+        <v>18.43</v>
       </c>
       <c r="D3261" t="inlineStr">
         <is>
@@ -88477,7 +88477,7 @@
         <v>2</v>
       </c>
       <c r="G3261" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3262">
@@ -88488,7 +88488,7 @@
         <v>21</v>
       </c>
       <c r="C3262" t="n">
-        <v>34.35</v>
+        <v>37.16</v>
       </c>
       <c r="D3262" t="inlineStr">
         <is>
@@ -88504,7 +88504,7 @@
         <v>2</v>
       </c>
       <c r="G3262" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3263">
@@ -88515,7 +88515,7 @@
         <v>22</v>
       </c>
       <c r="C3263" t="n">
-        <v>36.84</v>
+        <v>39.22</v>
       </c>
       <c r="D3263" t="inlineStr">
         <is>
@@ -88531,7 +88531,7 @@
         <v>2</v>
       </c>
       <c r="G3263" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3264">
@@ -88542,7 +88542,7 @@
         <v>23</v>
       </c>
       <c r="C3264" t="n">
-        <v>23</v>
+        <v>24.29</v>
       </c>
       <c r="D3264" t="inlineStr">
         <is>
@@ -88558,7 +88558,7 @@
         <v>2</v>
       </c>
       <c r="G3264" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3265">
@@ -88569,7 +88569,7 @@
         <v>24</v>
       </c>
       <c r="C3265" t="n">
-        <v>23.57</v>
+        <v>24.98</v>
       </c>
       <c r="D3265" t="inlineStr">
         <is>
@@ -88585,7 +88585,7 @@
         <v>2</v>
       </c>
       <c r="G3265" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3266">
@@ -88596,7 +88596,7 @@
         <v>1</v>
       </c>
       <c r="C3266" t="n">
-        <v>9.25</v>
+        <v>12.2</v>
       </c>
       <c r="D3266" t="inlineStr">
         <is>
@@ -88612,7 +88612,7 @@
         <v>2</v>
       </c>
       <c r="G3266" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3267">
@@ -88623,7 +88623,7 @@
         <v>2</v>
       </c>
       <c r="C3267" t="n">
-        <v>9.539999999999999</v>
+        <v>7.47</v>
       </c>
       <c r="D3267" t="inlineStr">
         <is>
@@ -88639,7 +88639,7 @@
         <v>2</v>
       </c>
       <c r="G3267" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3268">
@@ -88650,7 +88650,7 @@
         <v>3</v>
       </c>
       <c r="C3268" t="n">
-        <v>10.3</v>
+        <v>8.18</v>
       </c>
       <c r="D3268" t="inlineStr">
         <is>
@@ -88666,7 +88666,7 @@
         <v>2</v>
       </c>
       <c r="G3268" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3269">
@@ -88677,7 +88677,7 @@
         <v>4</v>
       </c>
       <c r="C3269" t="n">
-        <v>10.7</v>
+        <v>7.27</v>
       </c>
       <c r="D3269" t="inlineStr">
         <is>
@@ -88693,7 +88693,7 @@
         <v>2</v>
       </c>
       <c r="G3269" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3270">
@@ -88704,7 +88704,7 @@
         <v>5</v>
       </c>
       <c r="C3270" t="n">
-        <v>10.92</v>
+        <v>9.09</v>
       </c>
       <c r="D3270" t="inlineStr">
         <is>
@@ -88720,7 +88720,7 @@
         <v>2</v>
       </c>
       <c r="G3270" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3271">
@@ -88731,7 +88731,7 @@
         <v>6</v>
       </c>
       <c r="C3271" t="n">
-        <v>16.22</v>
+        <v>11.35</v>
       </c>
       <c r="D3271" t="inlineStr">
         <is>
@@ -88747,7 +88747,7 @@
         <v>2</v>
       </c>
       <c r="G3271" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3272">
@@ -88758,7 +88758,7 @@
         <v>7</v>
       </c>
       <c r="C3272" t="n">
-        <v>26.62</v>
+        <v>20.4</v>
       </c>
       <c r="D3272" t="inlineStr">
         <is>
@@ -88774,7 +88774,7 @@
         <v>2</v>
       </c>
       <c r="G3272" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3273">
@@ -88785,7 +88785,7 @@
         <v>8</v>
       </c>
       <c r="C3273" t="n">
-        <v>59.73</v>
+        <v>44.91</v>
       </c>
       <c r="D3273" t="inlineStr">
         <is>
@@ -88801,7 +88801,7 @@
         <v>2</v>
       </c>
       <c r="G3273" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3274">
@@ -88812,7 +88812,7 @@
         <v>9</v>
       </c>
       <c r="C3274" t="n">
-        <v>54.16</v>
+        <v>39.79</v>
       </c>
       <c r="D3274" t="inlineStr">
         <is>
@@ -88828,7 +88828,7 @@
         <v>2</v>
       </c>
       <c r="G3274" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3275">
@@ -88839,7 +88839,7 @@
         <v>10</v>
       </c>
       <c r="C3275" t="n">
-        <v>17.48</v>
+        <v>20.53</v>
       </c>
       <c r="D3275" t="inlineStr">
         <is>
@@ -88855,7 +88855,7 @@
         <v>2</v>
       </c>
       <c r="G3275" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3276">
@@ -88866,7 +88866,7 @@
         <v>11</v>
       </c>
       <c r="C3276" t="n">
-        <v>23.72</v>
+        <v>26.28</v>
       </c>
       <c r="D3276" t="inlineStr">
         <is>
@@ -88882,7 +88882,7 @@
         <v>2</v>
       </c>
       <c r="G3276" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3277">
@@ -88893,7 +88893,7 @@
         <v>12</v>
       </c>
       <c r="C3277" t="n">
-        <v>31.5</v>
+        <v>31.38</v>
       </c>
       <c r="D3277" t="inlineStr">
         <is>
@@ -88909,7 +88909,7 @@
         <v>2</v>
       </c>
       <c r="G3277" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3278">
@@ -88920,7 +88920,7 @@
         <v>13</v>
       </c>
       <c r="C3278" t="n">
-        <v>33.74</v>
+        <v>35.89</v>
       </c>
       <c r="D3278" t="inlineStr">
         <is>
@@ -88936,7 +88936,7 @@
         <v>2</v>
       </c>
       <c r="G3278" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3279">
@@ -88947,7 +88947,7 @@
         <v>14</v>
       </c>
       <c r="C3279" t="n">
-        <v>33.97</v>
+        <v>40.99</v>
       </c>
       <c r="D3279" t="inlineStr">
         <is>
@@ -88963,7 +88963,7 @@
         <v>2</v>
       </c>
       <c r="G3279" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3280">
@@ -88974,7 +88974,7 @@
         <v>15</v>
       </c>
       <c r="C3280" t="n">
-        <v>32.91</v>
+        <v>40.24</v>
       </c>
       <c r="D3280" t="inlineStr">
         <is>
@@ -88990,7 +88990,7 @@
         <v>2</v>
       </c>
       <c r="G3280" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3281">
@@ -89001,7 +89001,7 @@
         <v>16</v>
       </c>
       <c r="C3281" t="n">
-        <v>33.42</v>
+        <v>41.22</v>
       </c>
       <c r="D3281" t="inlineStr">
         <is>
@@ -89017,7 +89017,7 @@
         <v>2</v>
       </c>
       <c r="G3281" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3282">
@@ -89028,7 +89028,7 @@
         <v>17</v>
       </c>
       <c r="C3282" t="n">
-        <v>31.58</v>
+        <v>38.6</v>
       </c>
       <c r="D3282" t="inlineStr">
         <is>
@@ -89044,7 +89044,7 @@
         <v>2</v>
       </c>
       <c r="G3282" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3283">
@@ -89055,7 +89055,7 @@
         <v>18</v>
       </c>
       <c r="C3283" t="n">
-        <v>28.34</v>
+        <v>31.96</v>
       </c>
       <c r="D3283" t="inlineStr">
         <is>
@@ -89071,7 +89071,7 @@
         <v>2</v>
       </c>
       <c r="G3283" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3284">
@@ -89082,7 +89082,7 @@
         <v>19</v>
       </c>
       <c r="C3284" t="n">
-        <v>20.64</v>
+        <v>15.37</v>
       </c>
       <c r="D3284" t="inlineStr">
         <is>
@@ -89098,7 +89098,7 @@
         <v>2</v>
       </c>
       <c r="G3284" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3285">
@@ -89109,7 +89109,7 @@
         <v>20</v>
       </c>
       <c r="C3285" t="n">
-        <v>28.74</v>
+        <v>15.85</v>
       </c>
       <c r="D3285" t="inlineStr">
         <is>
@@ -89125,7 +89125,7 @@
         <v>2</v>
       </c>
       <c r="G3285" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3286">
@@ -89136,7 +89136,7 @@
         <v>21</v>
       </c>
       <c r="C3286" t="n">
-        <v>45.16</v>
+        <v>33.38</v>
       </c>
       <c r="D3286" t="inlineStr">
         <is>
@@ -89152,7 +89152,7 @@
         <v>2</v>
       </c>
       <c r="G3286" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3287">
@@ -89163,7 +89163,7 @@
         <v>22</v>
       </c>
       <c r="C3287" t="n">
-        <v>45.03</v>
+        <v>34.13</v>
       </c>
       <c r="D3287" t="inlineStr">
         <is>
@@ -89179,7 +89179,7 @@
         <v>2</v>
       </c>
       <c r="G3287" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3288">
@@ -89190,7 +89190,7 @@
         <v>23</v>
       </c>
       <c r="C3288" t="n">
-        <v>52.94</v>
+        <v>39.34</v>
       </c>
       <c r="D3288" t="inlineStr">
         <is>
@@ -89206,7 +89206,7 @@
         <v>2</v>
       </c>
       <c r="G3288" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
       </c>
     </row>
     <row r="3289">
@@ -89217,7 +89217,7 @@
         <v>24</v>
       </c>
       <c r="C3289" t="n">
-        <v>28.92</v>
+        <v>23.81</v>
       </c>
       <c r="D3289" t="inlineStr">
         <is>
@@ -89233,7 +89233,655 @@
         <v>2</v>
       </c>
       <c r="G3289" s="2" t="n">
-        <v>46279.89901818455</v>
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3290">
+      <c r="A3290" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3290" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3290" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="D3290" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3290" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3290" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3290" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3291">
+      <c r="A3291" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3291" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3291" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D3291" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3291" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3291" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3291" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3292">
+      <c r="A3292" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3292" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3292" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="D3292" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3292" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3292" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3292" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3293">
+      <c r="A3293" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3293" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3293" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="D3293" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3293" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3293" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3293" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3294">
+      <c r="A3294" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3294" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3294" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="D3294" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3294" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3294" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3294" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3295">
+      <c r="A3295" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3295" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3295" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="D3295" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3295" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3295" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3295" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3296">
+      <c r="A3296" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3296" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3296" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="D3296" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3296" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3296" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3296" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3297">
+      <c r="A3297" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3297" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3297" t="n">
+        <v>35.97</v>
+      </c>
+      <c r="D3297" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3297" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3297" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3297" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3298">
+      <c r="A3298" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3298" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3298" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="D3298" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3298" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3298" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3298" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3299">
+      <c r="A3299" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3299" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3299" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="D3299" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3299" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3299" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3299" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3300">
+      <c r="A3300" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3300" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3300" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="D3300" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3300" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3300" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3300" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3301">
+      <c r="A3301" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3301" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3301" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="D3301" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3301" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3301" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3301" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3302">
+      <c r="A3302" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3302" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3302" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="D3302" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3302" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3302" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3302" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3303">
+      <c r="A3303" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3303" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3303" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="D3303" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3303" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3303" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3303" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3304">
+      <c r="A3304" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3304" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3304" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D3304" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3304" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3304" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3304" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3305">
+      <c r="A3305" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3305" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3305" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="D3305" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3305" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3305" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3305" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3306">
+      <c r="A3306" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3306" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3306" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="D3306" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3306" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3306" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3306" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3307">
+      <c r="A3307" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3307" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3307" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D3307" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3307" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3307" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3307" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3308">
+      <c r="A3308" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3308" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3308" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="D3308" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3308" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3308" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3308" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3309">
+      <c r="A3309" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3309" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3309" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="D3309" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3309" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3309" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3309" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3310">
+      <c r="A3310" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3310" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3310" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="D3310" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3310" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3310" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3310" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3311">
+      <c r="A3311" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3311" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3311" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="D3311" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3311" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3311" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3311" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3312">
+      <c r="A3312" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3312" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3312" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="D3312" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3312" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3312" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3312" s="2" t="n">
+        <v>46280.46707375846</v>
+      </c>
+    </row>
+    <row r="3313">
+      <c r="A3313" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3313" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3313" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="D3313" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E3313" t="inlineStr">
+        <is>
+          <t>A1_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3313" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3313" s="2" t="n">
+        <v>46280.46707375846</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -80188,7 +80188,7 @@
         <v>2</v>
       </c>
       <c r="G2954" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2955">
@@ -80215,7 +80215,7 @@
         <v>2</v>
       </c>
       <c r="G2955" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2956">
@@ -80242,7 +80242,7 @@
         <v>2</v>
       </c>
       <c r="G2956" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2957">
@@ -80269,7 +80269,7 @@
         <v>2</v>
       </c>
       <c r="G2957" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2958">
@@ -80296,7 +80296,7 @@
         <v>2</v>
       </c>
       <c r="G2958" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2959">
@@ -80323,7 +80323,7 @@
         <v>2</v>
       </c>
       <c r="G2959" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2960">
@@ -80350,7 +80350,7 @@
         <v>2</v>
       </c>
       <c r="G2960" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2961">
@@ -80377,7 +80377,7 @@
         <v>2</v>
       </c>
       <c r="G2961" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2962">
@@ -80404,7 +80404,7 @@
         <v>2</v>
       </c>
       <c r="G2962" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2963">
@@ -80431,7 +80431,7 @@
         <v>2</v>
       </c>
       <c r="G2963" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2964">
@@ -80458,7 +80458,7 @@
         <v>2</v>
       </c>
       <c r="G2964" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2965">
@@ -80485,7 +80485,7 @@
         <v>2</v>
       </c>
       <c r="G2965" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2966">
@@ -80512,7 +80512,7 @@
         <v>2</v>
       </c>
       <c r="G2966" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2967">
@@ -80539,7 +80539,7 @@
         <v>2</v>
       </c>
       <c r="G2967" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2968">
@@ -80566,7 +80566,7 @@
         <v>2</v>
       </c>
       <c r="G2968" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2969">
@@ -80593,7 +80593,7 @@
         <v>2</v>
       </c>
       <c r="G2969" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2970">
@@ -80620,7 +80620,7 @@
         <v>2</v>
       </c>
       <c r="G2970" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2971">
@@ -80647,7 +80647,7 @@
         <v>2</v>
       </c>
       <c r="G2971" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2972">
@@ -80674,7 +80674,7 @@
         <v>2</v>
       </c>
       <c r="G2972" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2973">
@@ -80701,7 +80701,7 @@
         <v>2</v>
       </c>
       <c r="G2973" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2974">
@@ -80728,7 +80728,7 @@
         <v>2</v>
       </c>
       <c r="G2974" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2975">
@@ -80755,7 +80755,7 @@
         <v>2</v>
       </c>
       <c r="G2975" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2976">
@@ -80782,7 +80782,7 @@
         <v>2</v>
       </c>
       <c r="G2976" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2977">
@@ -80809,7 +80809,7 @@
         <v>2</v>
       </c>
       <c r="G2977" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2978">
@@ -80836,7 +80836,7 @@
         <v>2</v>
       </c>
       <c r="G2978" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2979">
@@ -80863,7 +80863,7 @@
         <v>2</v>
       </c>
       <c r="G2979" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2980">
@@ -80890,7 +80890,7 @@
         <v>2</v>
       </c>
       <c r="G2980" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2981">
@@ -80917,7 +80917,7 @@
         <v>2</v>
       </c>
       <c r="G2981" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2982">
@@ -80944,7 +80944,7 @@
         <v>2</v>
       </c>
       <c r="G2982" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2983">
@@ -80971,7 +80971,7 @@
         <v>2</v>
       </c>
       <c r="G2983" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2984">
@@ -80998,7 +80998,7 @@
         <v>2</v>
       </c>
       <c r="G2984" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2985">
@@ -81025,7 +81025,7 @@
         <v>2</v>
       </c>
       <c r="G2985" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2986">
@@ -81052,7 +81052,7 @@
         <v>2</v>
       </c>
       <c r="G2986" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2987">
@@ -81079,7 +81079,7 @@
         <v>2</v>
       </c>
       <c r="G2987" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2988">
@@ -81106,7 +81106,7 @@
         <v>2</v>
       </c>
       <c r="G2988" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2989">
@@ -81133,7 +81133,7 @@
         <v>2</v>
       </c>
       <c r="G2989" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2990">
@@ -81160,7 +81160,7 @@
         <v>2</v>
       </c>
       <c r="G2990" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2991">
@@ -81187,7 +81187,7 @@
         <v>2</v>
       </c>
       <c r="G2991" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2992">
@@ -81214,7 +81214,7 @@
         <v>2</v>
       </c>
       <c r="G2992" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2993">
@@ -81241,7 +81241,7 @@
         <v>2</v>
       </c>
       <c r="G2993" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2994">
@@ -81268,7 +81268,7 @@
         <v>2</v>
       </c>
       <c r="G2994" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2995">
@@ -81295,7 +81295,7 @@
         <v>2</v>
       </c>
       <c r="G2995" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2996">
@@ -81322,7 +81322,7 @@
         <v>2</v>
       </c>
       <c r="G2996" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2997">
@@ -81349,7 +81349,7 @@
         <v>2</v>
       </c>
       <c r="G2997" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2998">
@@ -81376,7 +81376,7 @@
         <v>2</v>
       </c>
       <c r="G2998" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="2999">
@@ -81403,7 +81403,7 @@
         <v>2</v>
       </c>
       <c r="G2999" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3000">
@@ -81430,7 +81430,7 @@
         <v>2</v>
       </c>
       <c r="G3000" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3001">
@@ -81457,7 +81457,7 @@
         <v>2</v>
       </c>
       <c r="G3001" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3002">
@@ -81484,7 +81484,7 @@
         <v>2</v>
       </c>
       <c r="G3002" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3003">
@@ -81511,7 +81511,7 @@
         <v>2</v>
       </c>
       <c r="G3003" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3004">
@@ -81538,7 +81538,7 @@
         <v>2</v>
       </c>
       <c r="G3004" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3005">
@@ -81565,7 +81565,7 @@
         <v>2</v>
       </c>
       <c r="G3005" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3006">
@@ -81592,7 +81592,7 @@
         <v>2</v>
       </c>
       <c r="G3006" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3007">
@@ -81619,7 +81619,7 @@
         <v>2</v>
       </c>
       <c r="G3007" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3008">
@@ -81646,7 +81646,7 @@
         <v>2</v>
       </c>
       <c r="G3008" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3009">
@@ -81673,7 +81673,7 @@
         <v>2</v>
       </c>
       <c r="G3009" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3010">
@@ -81700,7 +81700,7 @@
         <v>2</v>
       </c>
       <c r="G3010" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3011">
@@ -81727,7 +81727,7 @@
         <v>2</v>
       </c>
       <c r="G3011" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3012">
@@ -81754,7 +81754,7 @@
         <v>2</v>
       </c>
       <c r="G3012" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3013">
@@ -81781,7 +81781,7 @@
         <v>2</v>
       </c>
       <c r="G3013" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3014">
@@ -81808,7 +81808,7 @@
         <v>2</v>
       </c>
       <c r="G3014" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3015">
@@ -81835,7 +81835,7 @@
         <v>2</v>
       </c>
       <c r="G3015" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3016">
@@ -81862,7 +81862,7 @@
         <v>2</v>
       </c>
       <c r="G3016" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3017">
@@ -81889,7 +81889,7 @@
         <v>2</v>
       </c>
       <c r="G3017" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3018">
@@ -81916,7 +81916,7 @@
         <v>2</v>
       </c>
       <c r="G3018" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3019">
@@ -81943,7 +81943,7 @@
         <v>2</v>
       </c>
       <c r="G3019" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3020">
@@ -81970,7 +81970,7 @@
         <v>2</v>
       </c>
       <c r="G3020" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3021">
@@ -81997,7 +81997,7 @@
         <v>2</v>
       </c>
       <c r="G3021" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3022">
@@ -82024,7 +82024,7 @@
         <v>2</v>
       </c>
       <c r="G3022" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3023">
@@ -82051,7 +82051,7 @@
         <v>2</v>
       </c>
       <c r="G3023" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3024">
@@ -82078,7 +82078,7 @@
         <v>2</v>
       </c>
       <c r="G3024" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3025">
@@ -82105,7 +82105,7 @@
         <v>2</v>
       </c>
       <c r="G3025" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3026">
@@ -82132,7 +82132,7 @@
         <v>2</v>
       </c>
       <c r="G3026" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3027">
@@ -82159,7 +82159,7 @@
         <v>2</v>
       </c>
       <c r="G3027" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3028">
@@ -82186,7 +82186,7 @@
         <v>2</v>
       </c>
       <c r="G3028" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3029">
@@ -82213,7 +82213,7 @@
         <v>2</v>
       </c>
       <c r="G3029" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3030">
@@ -82240,7 +82240,7 @@
         <v>2</v>
       </c>
       <c r="G3030" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3031">
@@ -82267,7 +82267,7 @@
         <v>2</v>
       </c>
       <c r="G3031" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3032">
@@ -82294,7 +82294,7 @@
         <v>2</v>
       </c>
       <c r="G3032" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3033">
@@ -82321,7 +82321,7 @@
         <v>2</v>
       </c>
       <c r="G3033" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3034">
@@ -82348,7 +82348,7 @@
         <v>2</v>
       </c>
       <c r="G3034" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3035">
@@ -82375,7 +82375,7 @@
         <v>2</v>
       </c>
       <c r="G3035" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3036">
@@ -82402,7 +82402,7 @@
         <v>2</v>
       </c>
       <c r="G3036" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3037">
@@ -82429,7 +82429,7 @@
         <v>2</v>
       </c>
       <c r="G3037" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3038">
@@ -82456,7 +82456,7 @@
         <v>2</v>
       </c>
       <c r="G3038" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3039">
@@ -82483,7 +82483,7 @@
         <v>2</v>
       </c>
       <c r="G3039" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3040">
@@ -82510,7 +82510,7 @@
         <v>2</v>
       </c>
       <c r="G3040" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3041">
@@ -82537,7 +82537,7 @@
         <v>2</v>
       </c>
       <c r="G3041" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3042">
@@ -82564,7 +82564,7 @@
         <v>2</v>
       </c>
       <c r="G3042" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3043">
@@ -82591,7 +82591,7 @@
         <v>2</v>
       </c>
       <c r="G3043" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3044">
@@ -82618,7 +82618,7 @@
         <v>2</v>
       </c>
       <c r="G3044" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3045">
@@ -82645,7 +82645,7 @@
         <v>2</v>
       </c>
       <c r="G3045" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3046">
@@ -82672,7 +82672,7 @@
         <v>2</v>
       </c>
       <c r="G3046" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3047">
@@ -82699,7 +82699,7 @@
         <v>2</v>
       </c>
       <c r="G3047" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3048">
@@ -82726,7 +82726,7 @@
         <v>2</v>
       </c>
       <c r="G3048" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3049">
@@ -82753,7 +82753,7 @@
         <v>2</v>
       </c>
       <c r="G3049" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3050">
@@ -82780,7 +82780,7 @@
         <v>2</v>
       </c>
       <c r="G3050" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3051">
@@ -82807,7 +82807,7 @@
         <v>2</v>
       </c>
       <c r="G3051" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3052">
@@ -82834,7 +82834,7 @@
         <v>2</v>
       </c>
       <c r="G3052" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3053">
@@ -82861,7 +82861,7 @@
         <v>2</v>
       </c>
       <c r="G3053" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3054">
@@ -82888,7 +82888,7 @@
         <v>2</v>
       </c>
       <c r="G3054" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3055">
@@ -82915,7 +82915,7 @@
         <v>2</v>
       </c>
       <c r="G3055" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3056">
@@ -82942,7 +82942,7 @@
         <v>2</v>
       </c>
       <c r="G3056" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3057">
@@ -82969,7 +82969,7 @@
         <v>2</v>
       </c>
       <c r="G3057" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3058">
@@ -82996,7 +82996,7 @@
         <v>2</v>
       </c>
       <c r="G3058" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3059">
@@ -83023,7 +83023,7 @@
         <v>2</v>
       </c>
       <c r="G3059" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3060">
@@ -83050,7 +83050,7 @@
         <v>2</v>
       </c>
       <c r="G3060" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3061">
@@ -83077,7 +83077,7 @@
         <v>2</v>
       </c>
       <c r="G3061" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3062">
@@ -83104,7 +83104,7 @@
         <v>2</v>
       </c>
       <c r="G3062" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3063">
@@ -83131,7 +83131,7 @@
         <v>2</v>
       </c>
       <c r="G3063" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3064">
@@ -83158,7 +83158,7 @@
         <v>2</v>
       </c>
       <c r="G3064" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3065">
@@ -83185,7 +83185,7 @@
         <v>2</v>
       </c>
       <c r="G3065" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3066">
@@ -83212,7 +83212,7 @@
         <v>2</v>
       </c>
       <c r="G3066" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3067">
@@ -83239,7 +83239,7 @@
         <v>2</v>
       </c>
       <c r="G3067" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3068">
@@ -83266,7 +83266,7 @@
         <v>2</v>
       </c>
       <c r="G3068" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3069">
@@ -83293,7 +83293,7 @@
         <v>2</v>
       </c>
       <c r="G3069" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3070">
@@ -83320,7 +83320,7 @@
         <v>2</v>
       </c>
       <c r="G3070" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3071">
@@ -83347,7 +83347,7 @@
         <v>2</v>
       </c>
       <c r="G3071" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3072">
@@ -83374,7 +83374,7 @@
         <v>2</v>
       </c>
       <c r="G3072" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3073">
@@ -83401,7 +83401,7 @@
         <v>2</v>
       </c>
       <c r="G3073" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3074">
@@ -83428,7 +83428,7 @@
         <v>2</v>
       </c>
       <c r="G3074" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3075">
@@ -83455,7 +83455,7 @@
         <v>2</v>
       </c>
       <c r="G3075" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3076">
@@ -83482,7 +83482,7 @@
         <v>2</v>
       </c>
       <c r="G3076" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3077">
@@ -83509,7 +83509,7 @@
         <v>2</v>
       </c>
       <c r="G3077" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3078">
@@ -83536,7 +83536,7 @@
         <v>2</v>
       </c>
       <c r="G3078" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3079">
@@ -83563,7 +83563,7 @@
         <v>2</v>
       </c>
       <c r="G3079" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3080">
@@ -83590,7 +83590,7 @@
         <v>2</v>
       </c>
       <c r="G3080" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3081">
@@ -83617,7 +83617,7 @@
         <v>2</v>
       </c>
       <c r="G3081" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3082">
@@ -83644,7 +83644,7 @@
         <v>2</v>
       </c>
       <c r="G3082" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3083">
@@ -83671,7 +83671,7 @@
         <v>2</v>
       </c>
       <c r="G3083" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3084">
@@ -83698,7 +83698,7 @@
         <v>2</v>
       </c>
       <c r="G3084" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3085">
@@ -83725,7 +83725,7 @@
         <v>2</v>
       </c>
       <c r="G3085" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3086">
@@ -83752,7 +83752,7 @@
         <v>2</v>
       </c>
       <c r="G3086" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3087">
@@ -83779,7 +83779,7 @@
         <v>2</v>
       </c>
       <c r="G3087" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3088">
@@ -83806,7 +83806,7 @@
         <v>2</v>
       </c>
       <c r="G3088" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3089">
@@ -83833,7 +83833,7 @@
         <v>2</v>
       </c>
       <c r="G3089" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3090">
@@ -83860,7 +83860,7 @@
         <v>2</v>
       </c>
       <c r="G3090" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3091">
@@ -83887,7 +83887,7 @@
         <v>2</v>
       </c>
       <c r="G3091" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3092">
@@ -83914,7 +83914,7 @@
         <v>2</v>
       </c>
       <c r="G3092" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3093">
@@ -83941,7 +83941,7 @@
         <v>2</v>
       </c>
       <c r="G3093" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3094">
@@ -83968,7 +83968,7 @@
         <v>2</v>
       </c>
       <c r="G3094" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3095">
@@ -83995,7 +83995,7 @@
         <v>2</v>
       </c>
       <c r="G3095" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3096">
@@ -84022,7 +84022,7 @@
         <v>2</v>
       </c>
       <c r="G3096" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3097">
@@ -84049,7 +84049,7 @@
         <v>2</v>
       </c>
       <c r="G3097" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3098">
@@ -84076,7 +84076,7 @@
         <v>2</v>
       </c>
       <c r="G3098" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3099">
@@ -84103,7 +84103,7 @@
         <v>2</v>
       </c>
       <c r="G3099" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3100">
@@ -84130,7 +84130,7 @@
         <v>2</v>
       </c>
       <c r="G3100" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3101">
@@ -84157,7 +84157,7 @@
         <v>2</v>
       </c>
       <c r="G3101" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3102">
@@ -84184,7 +84184,7 @@
         <v>2</v>
       </c>
       <c r="G3102" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3103">
@@ -84211,7 +84211,7 @@
         <v>2</v>
       </c>
       <c r="G3103" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3104">
@@ -84238,7 +84238,7 @@
         <v>2</v>
       </c>
       <c r="G3104" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3105">
@@ -84265,7 +84265,7 @@
         <v>2</v>
       </c>
       <c r="G3105" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3106">
@@ -84292,7 +84292,7 @@
         <v>2</v>
       </c>
       <c r="G3106" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3107">
@@ -84319,7 +84319,7 @@
         <v>2</v>
       </c>
       <c r="G3107" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3108">
@@ -84346,7 +84346,7 @@
         <v>2</v>
       </c>
       <c r="G3108" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3109">
@@ -84373,7 +84373,7 @@
         <v>2</v>
       </c>
       <c r="G3109" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3110">
@@ -84400,7 +84400,7 @@
         <v>2</v>
       </c>
       <c r="G3110" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3111">
@@ -84427,7 +84427,7 @@
         <v>2</v>
       </c>
       <c r="G3111" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3112">
@@ -84454,7 +84454,7 @@
         <v>2</v>
       </c>
       <c r="G3112" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3113">
@@ -84481,7 +84481,7 @@
         <v>2</v>
       </c>
       <c r="G3113" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3114">
@@ -84508,7 +84508,7 @@
         <v>2</v>
       </c>
       <c r="G3114" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3115">
@@ -84535,7 +84535,7 @@
         <v>2</v>
       </c>
       <c r="G3115" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3116">
@@ -84562,7 +84562,7 @@
         <v>2</v>
       </c>
       <c r="G3116" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3117">
@@ -84589,7 +84589,7 @@
         <v>2</v>
       </c>
       <c r="G3117" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3118">
@@ -84616,7 +84616,7 @@
         <v>2</v>
       </c>
       <c r="G3118" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3119">
@@ -84643,7 +84643,7 @@
         <v>2</v>
       </c>
       <c r="G3119" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3120">
@@ -84670,7 +84670,7 @@
         <v>2</v>
       </c>
       <c r="G3120" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3121">
@@ -84697,7 +84697,7 @@
         <v>2</v>
       </c>
       <c r="G3121" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3122">
@@ -84724,7 +84724,7 @@
         <v>2</v>
       </c>
       <c r="G3122" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3123">
@@ -84751,7 +84751,7 @@
         <v>2</v>
       </c>
       <c r="G3123" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3124">
@@ -84778,7 +84778,7 @@
         <v>2</v>
       </c>
       <c r="G3124" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3125">
@@ -84805,7 +84805,7 @@
         <v>2</v>
       </c>
       <c r="G3125" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3126">
@@ -84832,7 +84832,7 @@
         <v>2</v>
       </c>
       <c r="G3126" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3127">
@@ -84859,7 +84859,7 @@
         <v>2</v>
       </c>
       <c r="G3127" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3128">
@@ -84886,7 +84886,7 @@
         <v>2</v>
       </c>
       <c r="G3128" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3129">
@@ -84913,7 +84913,7 @@
         <v>2</v>
       </c>
       <c r="G3129" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3130">
@@ -84940,7 +84940,7 @@
         <v>2</v>
       </c>
       <c r="G3130" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3131">
@@ -84967,7 +84967,7 @@
         <v>2</v>
       </c>
       <c r="G3131" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3132">
@@ -84994,7 +84994,7 @@
         <v>2</v>
       </c>
       <c r="G3132" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3133">
@@ -85021,7 +85021,7 @@
         <v>2</v>
       </c>
       <c r="G3133" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3134">
@@ -85048,7 +85048,7 @@
         <v>2</v>
       </c>
       <c r="G3134" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3135">
@@ -85075,7 +85075,7 @@
         <v>2</v>
       </c>
       <c r="G3135" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3136">
@@ -85102,7 +85102,7 @@
         <v>2</v>
       </c>
       <c r="G3136" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3137">
@@ -85129,7 +85129,7 @@
         <v>2</v>
       </c>
       <c r="G3137" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3138">
@@ -85156,7 +85156,7 @@
         <v>2</v>
       </c>
       <c r="G3138" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3139">
@@ -85183,7 +85183,7 @@
         <v>2</v>
       </c>
       <c r="G3139" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3140">
@@ -85210,7 +85210,7 @@
         <v>2</v>
       </c>
       <c r="G3140" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3141">
@@ -85237,7 +85237,7 @@
         <v>2</v>
       </c>
       <c r="G3141" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3142">
@@ -85264,7 +85264,7 @@
         <v>2</v>
       </c>
       <c r="G3142" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3143">
@@ -85291,7 +85291,7 @@
         <v>2</v>
       </c>
       <c r="G3143" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3144">
@@ -85318,7 +85318,7 @@
         <v>2</v>
       </c>
       <c r="G3144" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3145">
@@ -85345,7 +85345,7 @@
         <v>2</v>
       </c>
       <c r="G3145" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3146">
@@ -85372,7 +85372,7 @@
         <v>2</v>
       </c>
       <c r="G3146" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3147">
@@ -85399,7 +85399,7 @@
         <v>2</v>
       </c>
       <c r="G3147" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3148">
@@ -85426,7 +85426,7 @@
         <v>2</v>
       </c>
       <c r="G3148" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3149">
@@ -85453,7 +85453,7 @@
         <v>2</v>
       </c>
       <c r="G3149" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3150">
@@ -85480,7 +85480,7 @@
         <v>2</v>
       </c>
       <c r="G3150" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3151">
@@ -85507,7 +85507,7 @@
         <v>2</v>
       </c>
       <c r="G3151" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3152">
@@ -85534,7 +85534,7 @@
         <v>2</v>
       </c>
       <c r="G3152" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3153">
@@ -85561,7 +85561,7 @@
         <v>2</v>
       </c>
       <c r="G3153" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3154">
@@ -85588,7 +85588,7 @@
         <v>2</v>
       </c>
       <c r="G3154" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3155">
@@ -85615,7 +85615,7 @@
         <v>2</v>
       </c>
       <c r="G3155" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3156">
@@ -85642,7 +85642,7 @@
         <v>2</v>
       </c>
       <c r="G3156" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3157">
@@ -85669,7 +85669,7 @@
         <v>2</v>
       </c>
       <c r="G3157" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3158">
@@ -85696,7 +85696,7 @@
         <v>2</v>
       </c>
       <c r="G3158" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3159">
@@ -85723,7 +85723,7 @@
         <v>2</v>
       </c>
       <c r="G3159" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3160">
@@ -85750,7 +85750,7 @@
         <v>2</v>
       </c>
       <c r="G3160" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3161">
@@ -85777,7 +85777,7 @@
         <v>2</v>
       </c>
       <c r="G3161" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3162">
@@ -85804,7 +85804,7 @@
         <v>2</v>
       </c>
       <c r="G3162" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3163">
@@ -85831,7 +85831,7 @@
         <v>2</v>
       </c>
       <c r="G3163" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3164">
@@ -85858,7 +85858,7 @@
         <v>2</v>
       </c>
       <c r="G3164" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3165">
@@ -85885,7 +85885,7 @@
         <v>2</v>
       </c>
       <c r="G3165" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3166">
@@ -85912,7 +85912,7 @@
         <v>2</v>
       </c>
       <c r="G3166" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3167">
@@ -85939,7 +85939,7 @@
         <v>2</v>
       </c>
       <c r="G3167" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3168">
@@ -85966,7 +85966,7 @@
         <v>2</v>
       </c>
       <c r="G3168" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3169">
@@ -85993,7 +85993,7 @@
         <v>2</v>
       </c>
       <c r="G3169" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3170">
@@ -86020,7 +86020,7 @@
         <v>2</v>
       </c>
       <c r="G3170" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3171">
@@ -86047,7 +86047,7 @@
         <v>2</v>
       </c>
       <c r="G3171" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3172">
@@ -86074,7 +86074,7 @@
         <v>2</v>
       </c>
       <c r="G3172" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3173">
@@ -86101,7 +86101,7 @@
         <v>2</v>
       </c>
       <c r="G3173" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3174">
@@ -86128,7 +86128,7 @@
         <v>2</v>
       </c>
       <c r="G3174" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3175">
@@ -86155,7 +86155,7 @@
         <v>2</v>
       </c>
       <c r="G3175" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3176">
@@ -86182,7 +86182,7 @@
         <v>2</v>
       </c>
       <c r="G3176" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3177">
@@ -86209,7 +86209,7 @@
         <v>2</v>
       </c>
       <c r="G3177" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3178">
@@ -86236,7 +86236,7 @@
         <v>2</v>
       </c>
       <c r="G3178" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3179">
@@ -86263,7 +86263,7 @@
         <v>2</v>
       </c>
       <c r="G3179" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3180">
@@ -86290,7 +86290,7 @@
         <v>2</v>
       </c>
       <c r="G3180" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3181">
@@ -86317,7 +86317,7 @@
         <v>2</v>
       </c>
       <c r="G3181" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3182">
@@ -86344,7 +86344,7 @@
         <v>2</v>
       </c>
       <c r="G3182" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3183">
@@ -86371,7 +86371,7 @@
         <v>2</v>
       </c>
       <c r="G3183" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3184">
@@ -86398,7 +86398,7 @@
         <v>2</v>
       </c>
       <c r="G3184" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3185">
@@ -86425,7 +86425,7 @@
         <v>2</v>
       </c>
       <c r="G3185" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3186">
@@ -86452,7 +86452,7 @@
         <v>2</v>
       </c>
       <c r="G3186" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3187">
@@ -86479,7 +86479,7 @@
         <v>2</v>
       </c>
       <c r="G3187" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3188">
@@ -86506,7 +86506,7 @@
         <v>2</v>
       </c>
       <c r="G3188" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3189">
@@ -86533,7 +86533,7 @@
         <v>2</v>
       </c>
       <c r="G3189" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3190">
@@ -86560,7 +86560,7 @@
         <v>2</v>
       </c>
       <c r="G3190" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3191">
@@ -86587,7 +86587,7 @@
         <v>2</v>
       </c>
       <c r="G3191" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3192">
@@ -86614,7 +86614,7 @@
         <v>2</v>
       </c>
       <c r="G3192" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3193">
@@ -86641,7 +86641,7 @@
         <v>2</v>
       </c>
       <c r="G3193" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3194">
@@ -86668,7 +86668,7 @@
         <v>2</v>
       </c>
       <c r="G3194" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3195">
@@ -86695,7 +86695,7 @@
         <v>2</v>
       </c>
       <c r="G3195" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3196">
@@ -86722,7 +86722,7 @@
         <v>2</v>
       </c>
       <c r="G3196" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3197">
@@ -86749,7 +86749,7 @@
         <v>2</v>
       </c>
       <c r="G3197" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3198">
@@ -86776,7 +86776,7 @@
         <v>2</v>
       </c>
       <c r="G3198" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3199">
@@ -86803,7 +86803,7 @@
         <v>2</v>
       </c>
       <c r="G3199" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3200">
@@ -86830,7 +86830,7 @@
         <v>2</v>
       </c>
       <c r="G3200" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3201">
@@ -86857,7 +86857,7 @@
         <v>2</v>
       </c>
       <c r="G3201" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3202">
@@ -86884,7 +86884,7 @@
         <v>2</v>
       </c>
       <c r="G3202" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3203">
@@ -86911,7 +86911,7 @@
         <v>2</v>
       </c>
       <c r="G3203" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3204">
@@ -86938,7 +86938,7 @@
         <v>2</v>
       </c>
       <c r="G3204" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3205">
@@ -86965,7 +86965,7 @@
         <v>2</v>
       </c>
       <c r="G3205" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3206">
@@ -86992,7 +86992,7 @@
         <v>2</v>
       </c>
       <c r="G3206" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3207">
@@ -87019,7 +87019,7 @@
         <v>2</v>
       </c>
       <c r="G3207" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3208">
@@ -87046,7 +87046,7 @@
         <v>2</v>
       </c>
       <c r="G3208" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3209">
@@ -87073,7 +87073,7 @@
         <v>2</v>
       </c>
       <c r="G3209" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3210">
@@ -87100,7 +87100,7 @@
         <v>2</v>
       </c>
       <c r="G3210" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3211">
@@ -87127,7 +87127,7 @@
         <v>2</v>
       </c>
       <c r="G3211" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3212">
@@ -87154,7 +87154,7 @@
         <v>2</v>
       </c>
       <c r="G3212" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3213">
@@ -87181,7 +87181,7 @@
         <v>2</v>
       </c>
       <c r="G3213" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3214">
@@ -87208,7 +87208,7 @@
         <v>2</v>
       </c>
       <c r="G3214" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3215">
@@ -87235,7 +87235,7 @@
         <v>2</v>
       </c>
       <c r="G3215" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3216">
@@ -87262,7 +87262,7 @@
         <v>2</v>
       </c>
       <c r="G3216" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3217">
@@ -87289,7 +87289,7 @@
         <v>2</v>
       </c>
       <c r="G3217" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3218">
@@ -87316,7 +87316,7 @@
         <v>2</v>
       </c>
       <c r="G3218" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3219">
@@ -87343,7 +87343,7 @@
         <v>2</v>
       </c>
       <c r="G3219" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3220">
@@ -87370,7 +87370,7 @@
         <v>2</v>
       </c>
       <c r="G3220" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3221">
@@ -87397,7 +87397,7 @@
         <v>2</v>
       </c>
       <c r="G3221" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3222">
@@ -87424,7 +87424,7 @@
         <v>2</v>
       </c>
       <c r="G3222" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3223">
@@ -87451,7 +87451,7 @@
         <v>2</v>
       </c>
       <c r="G3223" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3224">
@@ -87478,7 +87478,7 @@
         <v>2</v>
       </c>
       <c r="G3224" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3225">
@@ -87505,7 +87505,7 @@
         <v>2</v>
       </c>
       <c r="G3225" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3226">
@@ -87532,7 +87532,7 @@
         <v>2</v>
       </c>
       <c r="G3226" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3227">
@@ -87559,7 +87559,7 @@
         <v>2</v>
       </c>
       <c r="G3227" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3228">
@@ -87586,7 +87586,7 @@
         <v>2</v>
       </c>
       <c r="G3228" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3229">
@@ -87613,7 +87613,7 @@
         <v>2</v>
       </c>
       <c r="G3229" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3230">
@@ -87640,7 +87640,7 @@
         <v>2</v>
       </c>
       <c r="G3230" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3231">
@@ -87667,7 +87667,7 @@
         <v>2</v>
       </c>
       <c r="G3231" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3232">
@@ -87694,7 +87694,7 @@
         <v>2</v>
       </c>
       <c r="G3232" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3233">
@@ -87721,7 +87721,7 @@
         <v>2</v>
       </c>
       <c r="G3233" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3234">
@@ -87748,7 +87748,7 @@
         <v>2</v>
       </c>
       <c r="G3234" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3235">
@@ -87775,7 +87775,7 @@
         <v>2</v>
       </c>
       <c r="G3235" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3236">
@@ -87802,7 +87802,7 @@
         <v>2</v>
       </c>
       <c r="G3236" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3237">
@@ -87829,7 +87829,7 @@
         <v>2</v>
       </c>
       <c r="G3237" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3238">
@@ -87856,7 +87856,7 @@
         <v>2</v>
       </c>
       <c r="G3238" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3239">
@@ -87883,7 +87883,7 @@
         <v>2</v>
       </c>
       <c r="G3239" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3240">
@@ -87910,7 +87910,7 @@
         <v>2</v>
       </c>
       <c r="G3240" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3241">
@@ -87937,7 +87937,7 @@
         <v>2</v>
       </c>
       <c r="G3241" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3242">
@@ -87964,7 +87964,7 @@
         <v>2</v>
       </c>
       <c r="G3242" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3243">
@@ -87991,7 +87991,7 @@
         <v>2</v>
       </c>
       <c r="G3243" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3244">
@@ -88018,7 +88018,7 @@
         <v>2</v>
       </c>
       <c r="G3244" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3245">
@@ -88045,7 +88045,7 @@
         <v>2</v>
       </c>
       <c r="G3245" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3246">
@@ -88072,7 +88072,7 @@
         <v>2</v>
       </c>
       <c r="G3246" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3247">
@@ -88099,7 +88099,7 @@
         <v>2</v>
       </c>
       <c r="G3247" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3248">
@@ -88126,7 +88126,7 @@
         <v>2</v>
       </c>
       <c r="G3248" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3249">
@@ -88153,7 +88153,7 @@
         <v>2</v>
       </c>
       <c r="G3249" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3250">
@@ -88180,7 +88180,7 @@
         <v>2</v>
       </c>
       <c r="G3250" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3251">
@@ -88207,7 +88207,7 @@
         <v>2</v>
       </c>
       <c r="G3251" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3252">
@@ -88234,7 +88234,7 @@
         <v>2</v>
       </c>
       <c r="G3252" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3253">
@@ -88261,7 +88261,7 @@
         <v>2</v>
       </c>
       <c r="G3253" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3254">
@@ -88288,7 +88288,7 @@
         <v>2</v>
       </c>
       <c r="G3254" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3255">
@@ -88315,7 +88315,7 @@
         <v>2</v>
       </c>
       <c r="G3255" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3256">
@@ -88342,7 +88342,7 @@
         <v>2</v>
       </c>
       <c r="G3256" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3257">
@@ -88369,7 +88369,7 @@
         <v>2</v>
       </c>
       <c r="G3257" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3258">
@@ -88396,7 +88396,7 @@
         <v>2</v>
       </c>
       <c r="G3258" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3259">
@@ -88423,7 +88423,7 @@
         <v>2</v>
       </c>
       <c r="G3259" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3260">
@@ -88450,7 +88450,7 @@
         <v>2</v>
       </c>
       <c r="G3260" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3261">
@@ -88477,7 +88477,7 @@
         <v>2</v>
       </c>
       <c r="G3261" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3262">
@@ -88504,7 +88504,7 @@
         <v>2</v>
       </c>
       <c r="G3262" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3263">
@@ -88531,7 +88531,7 @@
         <v>2</v>
       </c>
       <c r="G3263" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3264">
@@ -88558,7 +88558,7 @@
         <v>2</v>
       </c>
       <c r="G3264" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3265">
@@ -88585,7 +88585,7 @@
         <v>2</v>
       </c>
       <c r="G3265" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3266">
@@ -88612,7 +88612,7 @@
         <v>2</v>
       </c>
       <c r="G3266" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3267">
@@ -88639,7 +88639,7 @@
         <v>2</v>
       </c>
       <c r="G3267" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3268">
@@ -88666,7 +88666,7 @@
         <v>2</v>
       </c>
       <c r="G3268" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3269">
@@ -88693,7 +88693,7 @@
         <v>2</v>
       </c>
       <c r="G3269" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3270">
@@ -88720,7 +88720,7 @@
         <v>2</v>
       </c>
       <c r="G3270" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3271">
@@ -88747,7 +88747,7 @@
         <v>2</v>
       </c>
       <c r="G3271" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3272">
@@ -88774,7 +88774,7 @@
         <v>2</v>
       </c>
       <c r="G3272" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3273">
@@ -88801,7 +88801,7 @@
         <v>2</v>
       </c>
       <c r="G3273" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3274">
@@ -88828,7 +88828,7 @@
         <v>2</v>
       </c>
       <c r="G3274" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3275">
@@ -88855,7 +88855,7 @@
         <v>2</v>
       </c>
       <c r="G3275" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3276">
@@ -88882,7 +88882,7 @@
         <v>2</v>
       </c>
       <c r="G3276" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3277">
@@ -88909,7 +88909,7 @@
         <v>2</v>
       </c>
       <c r="G3277" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3278">
@@ -88936,7 +88936,7 @@
         <v>2</v>
       </c>
       <c r="G3278" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3279">
@@ -88963,7 +88963,7 @@
         <v>2</v>
       </c>
       <c r="G3279" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3280">
@@ -88990,7 +88990,7 @@
         <v>2</v>
       </c>
       <c r="G3280" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3281">
@@ -89017,7 +89017,7 @@
         <v>2</v>
       </c>
       <c r="G3281" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3282">
@@ -89044,7 +89044,7 @@
         <v>2</v>
       </c>
       <c r="G3282" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3283">
@@ -89071,7 +89071,7 @@
         <v>2</v>
       </c>
       <c r="G3283" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3284">
@@ -89098,7 +89098,7 @@
         <v>2</v>
       </c>
       <c r="G3284" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3285">
@@ -89125,7 +89125,7 @@
         <v>2</v>
       </c>
       <c r="G3285" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3286">
@@ -89152,7 +89152,7 @@
         <v>2</v>
       </c>
       <c r="G3286" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3287">
@@ -89179,7 +89179,7 @@
         <v>2</v>
       </c>
       <c r="G3287" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3288">
@@ -89206,7 +89206,7 @@
         <v>2</v>
       </c>
       <c r="G3288" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3289">
@@ -89233,7 +89233,7 @@
         <v>2</v>
       </c>
       <c r="G3289" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3290">
@@ -89260,7 +89260,7 @@
         <v>2</v>
       </c>
       <c r="G3290" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3291">
@@ -89287,7 +89287,7 @@
         <v>2</v>
       </c>
       <c r="G3291" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3292">
@@ -89314,7 +89314,7 @@
         <v>2</v>
       </c>
       <c r="G3292" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3293">
@@ -89341,7 +89341,7 @@
         <v>2</v>
       </c>
       <c r="G3293" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3294">
@@ -89368,7 +89368,7 @@
         <v>2</v>
       </c>
       <c r="G3294" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3295">
@@ -89395,7 +89395,7 @@
         <v>2</v>
       </c>
       <c r="G3295" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3296">
@@ -89422,7 +89422,7 @@
         <v>2</v>
       </c>
       <c r="G3296" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3297">
@@ -89449,7 +89449,7 @@
         <v>2</v>
       </c>
       <c r="G3297" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3298">
@@ -89476,7 +89476,7 @@
         <v>2</v>
       </c>
       <c r="G3298" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3299">
@@ -89503,7 +89503,7 @@
         <v>2</v>
       </c>
       <c r="G3299" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3300">
@@ -89530,7 +89530,7 @@
         <v>2</v>
       </c>
       <c r="G3300" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3301">
@@ -89557,7 +89557,7 @@
         <v>2</v>
       </c>
       <c r="G3301" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3302">
@@ -89584,7 +89584,7 @@
         <v>2</v>
       </c>
       <c r="G3302" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3303">
@@ -89611,7 +89611,7 @@
         <v>2</v>
       </c>
       <c r="G3303" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3304">
@@ -89638,7 +89638,7 @@
         <v>2</v>
       </c>
       <c r="G3304" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3305">
@@ -89665,7 +89665,7 @@
         <v>2</v>
       </c>
       <c r="G3305" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3306">
@@ -89692,7 +89692,7 @@
         <v>2</v>
       </c>
       <c r="G3306" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3307">
@@ -89719,7 +89719,7 @@
         <v>2</v>
       </c>
       <c r="G3307" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3308">
@@ -89746,7 +89746,7 @@
         <v>2</v>
       </c>
       <c r="G3308" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3309">
@@ -89773,7 +89773,7 @@
         <v>2</v>
       </c>
       <c r="G3309" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3310">
@@ -89800,7 +89800,7 @@
         <v>2</v>
       </c>
       <c r="G3310" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3311">
@@ -89827,7 +89827,7 @@
         <v>2</v>
       </c>
       <c r="G3311" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3312">
@@ -89854,7 +89854,7 @@
         <v>2</v>
       </c>
       <c r="G3312" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
     <row r="3313">
@@ -89881,7 +89881,7 @@
         <v>2</v>
       </c>
       <c r="G3313" s="2" t="n">
-        <v>46280.46707375846</v>
+        <v>46280.87221256112</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -80188,7 +80188,7 @@
         <v>2</v>
       </c>
       <c r="G2954" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2955">
@@ -80215,7 +80215,7 @@
         <v>2</v>
       </c>
       <c r="G2955" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2956">
@@ -80242,7 +80242,7 @@
         <v>2</v>
       </c>
       <c r="G2956" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2957">
@@ -80269,7 +80269,7 @@
         <v>2</v>
       </c>
       <c r="G2957" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2958">
@@ -80296,7 +80296,7 @@
         <v>2</v>
       </c>
       <c r="G2958" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2959">
@@ -80323,7 +80323,7 @@
         <v>2</v>
       </c>
       <c r="G2959" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2960">
@@ -80350,7 +80350,7 @@
         <v>2</v>
       </c>
       <c r="G2960" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2961">
@@ -80377,7 +80377,7 @@
         <v>2</v>
       </c>
       <c r="G2961" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2962">
@@ -80404,7 +80404,7 @@
         <v>2</v>
       </c>
       <c r="G2962" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2963">
@@ -80431,7 +80431,7 @@
         <v>2</v>
       </c>
       <c r="G2963" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2964">
@@ -80458,7 +80458,7 @@
         <v>2</v>
       </c>
       <c r="G2964" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2965">
@@ -80485,7 +80485,7 @@
         <v>2</v>
       </c>
       <c r="G2965" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2966">
@@ -80512,7 +80512,7 @@
         <v>2</v>
       </c>
       <c r="G2966" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2967">
@@ -80539,7 +80539,7 @@
         <v>2</v>
       </c>
       <c r="G2967" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2968">
@@ -80566,7 +80566,7 @@
         <v>2</v>
       </c>
       <c r="G2968" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2969">
@@ -80593,7 +80593,7 @@
         <v>2</v>
       </c>
       <c r="G2969" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2970">
@@ -80620,7 +80620,7 @@
         <v>2</v>
       </c>
       <c r="G2970" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2971">
@@ -80647,7 +80647,7 @@
         <v>2</v>
       </c>
       <c r="G2971" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2972">
@@ -80674,7 +80674,7 @@
         <v>2</v>
       </c>
       <c r="G2972" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2973">
@@ -80701,7 +80701,7 @@
         <v>2</v>
       </c>
       <c r="G2973" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2974">
@@ -80728,7 +80728,7 @@
         <v>2</v>
       </c>
       <c r="G2974" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2975">
@@ -80755,7 +80755,7 @@
         <v>2</v>
       </c>
       <c r="G2975" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2976">
@@ -80782,7 +80782,7 @@
         <v>2</v>
       </c>
       <c r="G2976" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2977">
@@ -80809,7 +80809,7 @@
         <v>2</v>
       </c>
       <c r="G2977" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2978">
@@ -80836,7 +80836,7 @@
         <v>2</v>
       </c>
       <c r="G2978" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2979">
@@ -80863,7 +80863,7 @@
         <v>2</v>
       </c>
       <c r="G2979" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2980">
@@ -80890,7 +80890,7 @@
         <v>2</v>
       </c>
       <c r="G2980" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2981">
@@ -80917,7 +80917,7 @@
         <v>2</v>
       </c>
       <c r="G2981" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2982">
@@ -80944,7 +80944,7 @@
         <v>2</v>
       </c>
       <c r="G2982" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2983">
@@ -80971,7 +80971,7 @@
         <v>2</v>
       </c>
       <c r="G2983" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2984">
@@ -80998,7 +80998,7 @@
         <v>2</v>
       </c>
       <c r="G2984" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2985">
@@ -81025,7 +81025,7 @@
         <v>2</v>
       </c>
       <c r="G2985" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2986">
@@ -81052,7 +81052,7 @@
         <v>2</v>
       </c>
       <c r="G2986" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2987">
@@ -81079,7 +81079,7 @@
         <v>2</v>
       </c>
       <c r="G2987" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2988">
@@ -81106,7 +81106,7 @@
         <v>2</v>
       </c>
       <c r="G2988" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2989">
@@ -81133,7 +81133,7 @@
         <v>2</v>
       </c>
       <c r="G2989" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2990">
@@ -81160,7 +81160,7 @@
         <v>2</v>
       </c>
       <c r="G2990" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2991">
@@ -81187,7 +81187,7 @@
         <v>2</v>
       </c>
       <c r="G2991" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2992">
@@ -81214,7 +81214,7 @@
         <v>2</v>
       </c>
       <c r="G2992" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2993">
@@ -81241,7 +81241,7 @@
         <v>2</v>
       </c>
       <c r="G2993" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2994">
@@ -81268,7 +81268,7 @@
         <v>2</v>
       </c>
       <c r="G2994" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2995">
@@ -81295,7 +81295,7 @@
         <v>2</v>
       </c>
       <c r="G2995" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2996">
@@ -81322,7 +81322,7 @@
         <v>2</v>
       </c>
       <c r="G2996" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2997">
@@ -81349,7 +81349,7 @@
         <v>2</v>
       </c>
       <c r="G2997" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2998">
@@ -81376,7 +81376,7 @@
         <v>2</v>
       </c>
       <c r="G2998" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="2999">
@@ -81403,7 +81403,7 @@
         <v>2</v>
       </c>
       <c r="G2999" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3000">
@@ -81430,7 +81430,7 @@
         <v>2</v>
       </c>
       <c r="G3000" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3001">
@@ -81457,7 +81457,7 @@
         <v>2</v>
       </c>
       <c r="G3001" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3002">
@@ -81484,7 +81484,7 @@
         <v>2</v>
       </c>
       <c r="G3002" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3003">
@@ -81511,7 +81511,7 @@
         <v>2</v>
       </c>
       <c r="G3003" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3004">
@@ -81538,7 +81538,7 @@
         <v>2</v>
       </c>
       <c r="G3004" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3005">
@@ -81565,7 +81565,7 @@
         <v>2</v>
       </c>
       <c r="G3005" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3006">
@@ -81592,7 +81592,7 @@
         <v>2</v>
       </c>
       <c r="G3006" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3007">
@@ -81619,7 +81619,7 @@
         <v>2</v>
       </c>
       <c r="G3007" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3008">
@@ -81646,7 +81646,7 @@
         <v>2</v>
       </c>
       <c r="G3008" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3009">
@@ -81673,7 +81673,7 @@
         <v>2</v>
       </c>
       <c r="G3009" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3010">
@@ -81700,7 +81700,7 @@
         <v>2</v>
       </c>
       <c r="G3010" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3011">
@@ -81727,7 +81727,7 @@
         <v>2</v>
       </c>
       <c r="G3011" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3012">
@@ -81754,7 +81754,7 @@
         <v>2</v>
       </c>
       <c r="G3012" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3013">
@@ -81781,7 +81781,7 @@
         <v>2</v>
       </c>
       <c r="G3013" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3014">
@@ -81808,7 +81808,7 @@
         <v>2</v>
       </c>
       <c r="G3014" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3015">
@@ -81835,7 +81835,7 @@
         <v>2</v>
       </c>
       <c r="G3015" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3016">
@@ -81862,7 +81862,7 @@
         <v>2</v>
       </c>
       <c r="G3016" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3017">
@@ -81889,7 +81889,7 @@
         <v>2</v>
       </c>
       <c r="G3017" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3018">
@@ -81916,7 +81916,7 @@
         <v>2</v>
       </c>
       <c r="G3018" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3019">
@@ -81943,7 +81943,7 @@
         <v>2</v>
       </c>
       <c r="G3019" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3020">
@@ -81970,7 +81970,7 @@
         <v>2</v>
       </c>
       <c r="G3020" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3021">
@@ -81997,7 +81997,7 @@
         <v>2</v>
       </c>
       <c r="G3021" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3022">
@@ -82024,7 +82024,7 @@
         <v>2</v>
       </c>
       <c r="G3022" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3023">
@@ -82051,7 +82051,7 @@
         <v>2</v>
       </c>
       <c r="G3023" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3024">
@@ -82078,7 +82078,7 @@
         <v>2</v>
       </c>
       <c r="G3024" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3025">
@@ -82105,7 +82105,7 @@
         <v>2</v>
       </c>
       <c r="G3025" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3026">
@@ -82132,7 +82132,7 @@
         <v>2</v>
       </c>
       <c r="G3026" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3027">
@@ -82159,7 +82159,7 @@
         <v>2</v>
       </c>
       <c r="G3027" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3028">
@@ -82186,7 +82186,7 @@
         <v>2</v>
       </c>
       <c r="G3028" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3029">
@@ -82213,7 +82213,7 @@
         <v>2</v>
       </c>
       <c r="G3029" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3030">
@@ -82240,7 +82240,7 @@
         <v>2</v>
       </c>
       <c r="G3030" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3031">
@@ -82267,7 +82267,7 @@
         <v>2</v>
       </c>
       <c r="G3031" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3032">
@@ -82294,7 +82294,7 @@
         <v>2</v>
       </c>
       <c r="G3032" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3033">
@@ -82321,7 +82321,7 @@
         <v>2</v>
       </c>
       <c r="G3033" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3034">
@@ -82348,7 +82348,7 @@
         <v>2</v>
       </c>
       <c r="G3034" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3035">
@@ -82375,7 +82375,7 @@
         <v>2</v>
       </c>
       <c r="G3035" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3036">
@@ -82402,7 +82402,7 @@
         <v>2</v>
       </c>
       <c r="G3036" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3037">
@@ -82429,7 +82429,7 @@
         <v>2</v>
       </c>
       <c r="G3037" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3038">
@@ -82456,7 +82456,7 @@
         <v>2</v>
       </c>
       <c r="G3038" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3039">
@@ -82483,7 +82483,7 @@
         <v>2</v>
       </c>
       <c r="G3039" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3040">
@@ -82510,7 +82510,7 @@
         <v>2</v>
       </c>
       <c r="G3040" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3041">
@@ -82537,7 +82537,7 @@
         <v>2</v>
       </c>
       <c r="G3041" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3042">
@@ -82564,7 +82564,7 @@
         <v>2</v>
       </c>
       <c r="G3042" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3043">
@@ -82591,7 +82591,7 @@
         <v>2</v>
       </c>
       <c r="G3043" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3044">
@@ -82618,7 +82618,7 @@
         <v>2</v>
       </c>
       <c r="G3044" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3045">
@@ -82645,7 +82645,7 @@
         <v>2</v>
       </c>
       <c r="G3045" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3046">
@@ -82672,7 +82672,7 @@
         <v>2</v>
       </c>
       <c r="G3046" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3047">
@@ -82699,7 +82699,7 @@
         <v>2</v>
       </c>
       <c r="G3047" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3048">
@@ -82726,7 +82726,7 @@
         <v>2</v>
       </c>
       <c r="G3048" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3049">
@@ -82753,7 +82753,7 @@
         <v>2</v>
       </c>
       <c r="G3049" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3050">
@@ -82780,7 +82780,7 @@
         <v>2</v>
       </c>
       <c r="G3050" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3051">
@@ -82807,7 +82807,7 @@
         <v>2</v>
       </c>
       <c r="G3051" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3052">
@@ -82834,7 +82834,7 @@
         <v>2</v>
       </c>
       <c r="G3052" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3053">
@@ -82861,7 +82861,7 @@
         <v>2</v>
       </c>
       <c r="G3053" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3054">
@@ -82888,7 +82888,7 @@
         <v>2</v>
       </c>
       <c r="G3054" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3055">
@@ -82915,7 +82915,7 @@
         <v>2</v>
       </c>
       <c r="G3055" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3056">
@@ -82942,7 +82942,7 @@
         <v>2</v>
       </c>
       <c r="G3056" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3057">
@@ -82969,7 +82969,7 @@
         <v>2</v>
       </c>
       <c r="G3057" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3058">
@@ -82996,7 +82996,7 @@
         <v>2</v>
       </c>
       <c r="G3058" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3059">
@@ -83023,7 +83023,7 @@
         <v>2</v>
       </c>
       <c r="G3059" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3060">
@@ -83050,7 +83050,7 @@
         <v>2</v>
       </c>
       <c r="G3060" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3061">
@@ -83077,7 +83077,7 @@
         <v>2</v>
       </c>
       <c r="G3061" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3062">
@@ -83104,7 +83104,7 @@
         <v>2</v>
       </c>
       <c r="G3062" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3063">
@@ -83131,7 +83131,7 @@
         <v>2</v>
       </c>
       <c r="G3063" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3064">
@@ -83158,7 +83158,7 @@
         <v>2</v>
       </c>
       <c r="G3064" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3065">
@@ -83185,7 +83185,7 @@
         <v>2</v>
       </c>
       <c r="G3065" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3066">
@@ -83212,7 +83212,7 @@
         <v>2</v>
       </c>
       <c r="G3066" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3067">
@@ -83239,7 +83239,7 @@
         <v>2</v>
       </c>
       <c r="G3067" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3068">
@@ -83266,7 +83266,7 @@
         <v>2</v>
       </c>
       <c r="G3068" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3069">
@@ -83293,7 +83293,7 @@
         <v>2</v>
       </c>
       <c r="G3069" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3070">
@@ -83320,7 +83320,7 @@
         <v>2</v>
       </c>
       <c r="G3070" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3071">
@@ -83347,7 +83347,7 @@
         <v>2</v>
       </c>
       <c r="G3071" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3072">
@@ -83374,7 +83374,7 @@
         <v>2</v>
       </c>
       <c r="G3072" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3073">
@@ -83401,7 +83401,7 @@
         <v>2</v>
       </c>
       <c r="G3073" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3074">
@@ -83428,7 +83428,7 @@
         <v>2</v>
       </c>
       <c r="G3074" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3075">
@@ -83455,7 +83455,7 @@
         <v>2</v>
       </c>
       <c r="G3075" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3076">
@@ -83482,7 +83482,7 @@
         <v>2</v>
       </c>
       <c r="G3076" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3077">
@@ -83509,7 +83509,7 @@
         <v>2</v>
       </c>
       <c r="G3077" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3078">
@@ -83536,7 +83536,7 @@
         <v>2</v>
       </c>
       <c r="G3078" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3079">
@@ -83563,7 +83563,7 @@
         <v>2</v>
       </c>
       <c r="G3079" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3080">
@@ -83590,7 +83590,7 @@
         <v>2</v>
       </c>
       <c r="G3080" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3081">
@@ -83617,7 +83617,7 @@
         <v>2</v>
       </c>
       <c r="G3081" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3082">
@@ -83644,7 +83644,7 @@
         <v>2</v>
       </c>
       <c r="G3082" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3083">
@@ -83671,7 +83671,7 @@
         <v>2</v>
       </c>
       <c r="G3083" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3084">
@@ -83698,7 +83698,7 @@
         <v>2</v>
       </c>
       <c r="G3084" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3085">
@@ -83725,7 +83725,7 @@
         <v>2</v>
       </c>
       <c r="G3085" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3086">
@@ -83752,7 +83752,7 @@
         <v>2</v>
       </c>
       <c r="G3086" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3087">
@@ -83779,7 +83779,7 @@
         <v>2</v>
       </c>
       <c r="G3087" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3088">
@@ -83806,7 +83806,7 @@
         <v>2</v>
       </c>
       <c r="G3088" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3089">
@@ -83833,7 +83833,7 @@
         <v>2</v>
       </c>
       <c r="G3089" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3090">
@@ -83860,7 +83860,7 @@
         <v>2</v>
       </c>
       <c r="G3090" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3091">
@@ -83887,7 +83887,7 @@
         <v>2</v>
       </c>
       <c r="G3091" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3092">
@@ -83914,7 +83914,7 @@
         <v>2</v>
       </c>
       <c r="G3092" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3093">
@@ -83941,7 +83941,7 @@
         <v>2</v>
       </c>
       <c r="G3093" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3094">
@@ -83968,7 +83968,7 @@
         <v>2</v>
       </c>
       <c r="G3094" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3095">
@@ -83995,7 +83995,7 @@
         <v>2</v>
       </c>
       <c r="G3095" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3096">
@@ -84022,7 +84022,7 @@
         <v>2</v>
       </c>
       <c r="G3096" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3097">
@@ -84049,7 +84049,7 @@
         <v>2</v>
       </c>
       <c r="G3097" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3098">
@@ -84076,7 +84076,7 @@
         <v>2</v>
       </c>
       <c r="G3098" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3099">
@@ -84103,7 +84103,7 @@
         <v>2</v>
       </c>
       <c r="G3099" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3100">
@@ -84130,7 +84130,7 @@
         <v>2</v>
       </c>
       <c r="G3100" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3101">
@@ -84157,7 +84157,7 @@
         <v>2</v>
       </c>
       <c r="G3101" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3102">
@@ -84184,7 +84184,7 @@
         <v>2</v>
       </c>
       <c r="G3102" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3103">
@@ -84211,7 +84211,7 @@
         <v>2</v>
       </c>
       <c r="G3103" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3104">
@@ -84238,7 +84238,7 @@
         <v>2</v>
       </c>
       <c r="G3104" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3105">
@@ -84265,7 +84265,7 @@
         <v>2</v>
       </c>
       <c r="G3105" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3106">
@@ -84292,7 +84292,7 @@
         <v>2</v>
       </c>
       <c r="G3106" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3107">
@@ -84319,7 +84319,7 @@
         <v>2</v>
       </c>
       <c r="G3107" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3108">
@@ -84346,7 +84346,7 @@
         <v>2</v>
       </c>
       <c r="G3108" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3109">
@@ -84373,7 +84373,7 @@
         <v>2</v>
       </c>
       <c r="G3109" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3110">
@@ -84400,7 +84400,7 @@
         <v>2</v>
       </c>
       <c r="G3110" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3111">
@@ -84427,7 +84427,7 @@
         <v>2</v>
       </c>
       <c r="G3111" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3112">
@@ -84454,7 +84454,7 @@
         <v>2</v>
       </c>
       <c r="G3112" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3113">
@@ -84481,7 +84481,7 @@
         <v>2</v>
       </c>
       <c r="G3113" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3114">
@@ -84508,7 +84508,7 @@
         <v>2</v>
       </c>
       <c r="G3114" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3115">
@@ -84535,7 +84535,7 @@
         <v>2</v>
       </c>
       <c r="G3115" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3116">
@@ -84562,7 +84562,7 @@
         <v>2</v>
       </c>
       <c r="G3116" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3117">
@@ -84589,7 +84589,7 @@
         <v>2</v>
       </c>
       <c r="G3117" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3118">
@@ -84616,7 +84616,7 @@
         <v>2</v>
       </c>
       <c r="G3118" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3119">
@@ -84643,7 +84643,7 @@
         <v>2</v>
       </c>
       <c r="G3119" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3120">
@@ -84670,7 +84670,7 @@
         <v>2</v>
       </c>
       <c r="G3120" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3121">
@@ -84697,7 +84697,7 @@
         <v>2</v>
       </c>
       <c r="G3121" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3122">
@@ -84724,7 +84724,7 @@
         <v>2</v>
       </c>
       <c r="G3122" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3123">
@@ -84751,7 +84751,7 @@
         <v>2</v>
       </c>
       <c r="G3123" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3124">
@@ -84778,7 +84778,7 @@
         <v>2</v>
       </c>
       <c r="G3124" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3125">
@@ -84805,7 +84805,7 @@
         <v>2</v>
       </c>
       <c r="G3125" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3126">
@@ -84832,7 +84832,7 @@
         <v>2</v>
       </c>
       <c r="G3126" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3127">
@@ -84859,7 +84859,7 @@
         <v>2</v>
       </c>
       <c r="G3127" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3128">
@@ -84886,7 +84886,7 @@
         <v>2</v>
       </c>
       <c r="G3128" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3129">
@@ -84913,7 +84913,7 @@
         <v>2</v>
       </c>
       <c r="G3129" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3130">
@@ -84940,7 +84940,7 @@
         <v>2</v>
       </c>
       <c r="G3130" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3131">
@@ -84967,7 +84967,7 @@
         <v>2</v>
       </c>
       <c r="G3131" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3132">
@@ -84994,7 +84994,7 @@
         <v>2</v>
       </c>
       <c r="G3132" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3133">
@@ -85021,7 +85021,7 @@
         <v>2</v>
       </c>
       <c r="G3133" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3134">
@@ -85048,7 +85048,7 @@
         <v>2</v>
       </c>
       <c r="G3134" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3135">
@@ -85075,7 +85075,7 @@
         <v>2</v>
       </c>
       <c r="G3135" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3136">
@@ -85102,7 +85102,7 @@
         <v>2</v>
       </c>
       <c r="G3136" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3137">
@@ -85129,7 +85129,7 @@
         <v>2</v>
       </c>
       <c r="G3137" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3138">
@@ -85156,7 +85156,7 @@
         <v>2</v>
       </c>
       <c r="G3138" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3139">
@@ -85183,7 +85183,7 @@
         <v>2</v>
       </c>
       <c r="G3139" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3140">
@@ -85210,7 +85210,7 @@
         <v>2</v>
       </c>
       <c r="G3140" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3141">
@@ -85237,7 +85237,7 @@
         <v>2</v>
       </c>
       <c r="G3141" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3142">
@@ -85264,7 +85264,7 @@
         <v>2</v>
       </c>
       <c r="G3142" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3143">
@@ -85291,7 +85291,7 @@
         <v>2</v>
       </c>
       <c r="G3143" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3144">
@@ -85318,7 +85318,7 @@
         <v>2</v>
       </c>
       <c r="G3144" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3145">
@@ -85345,7 +85345,7 @@
         <v>2</v>
       </c>
       <c r="G3145" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3146">
@@ -85372,7 +85372,7 @@
         <v>2</v>
       </c>
       <c r="G3146" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3147">
@@ -85399,7 +85399,7 @@
         <v>2</v>
       </c>
       <c r="G3147" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3148">
@@ -85426,7 +85426,7 @@
         <v>2</v>
       </c>
       <c r="G3148" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3149">
@@ -85453,7 +85453,7 @@
         <v>2</v>
       </c>
       <c r="G3149" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3150">
@@ -85480,7 +85480,7 @@
         <v>2</v>
       </c>
       <c r="G3150" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3151">
@@ -85507,7 +85507,7 @@
         <v>2</v>
       </c>
       <c r="G3151" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3152">
@@ -85534,7 +85534,7 @@
         <v>2</v>
       </c>
       <c r="G3152" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3153">
@@ -85561,7 +85561,7 @@
         <v>2</v>
       </c>
       <c r="G3153" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3154">
@@ -85588,7 +85588,7 @@
         <v>2</v>
       </c>
       <c r="G3154" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3155">
@@ -85615,7 +85615,7 @@
         <v>2</v>
       </c>
       <c r="G3155" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3156">
@@ -85642,7 +85642,7 @@
         <v>2</v>
       </c>
       <c r="G3156" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3157">
@@ -85669,7 +85669,7 @@
         <v>2</v>
       </c>
       <c r="G3157" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3158">
@@ -85696,7 +85696,7 @@
         <v>2</v>
       </c>
       <c r="G3158" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3159">
@@ -85723,7 +85723,7 @@
         <v>2</v>
       </c>
       <c r="G3159" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3160">
@@ -85750,7 +85750,7 @@
         <v>2</v>
       </c>
       <c r="G3160" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3161">
@@ -85777,7 +85777,7 @@
         <v>2</v>
       </c>
       <c r="G3161" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3162">
@@ -85804,7 +85804,7 @@
         <v>2</v>
       </c>
       <c r="G3162" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3163">
@@ -85831,7 +85831,7 @@
         <v>2</v>
       </c>
       <c r="G3163" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3164">
@@ -85858,7 +85858,7 @@
         <v>2</v>
       </c>
       <c r="G3164" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3165">
@@ -85885,7 +85885,7 @@
         <v>2</v>
       </c>
       <c r="G3165" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3166">
@@ -85912,7 +85912,7 @@
         <v>2</v>
       </c>
       <c r="G3166" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3167">
@@ -85939,7 +85939,7 @@
         <v>2</v>
       </c>
       <c r="G3167" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3168">
@@ -85966,7 +85966,7 @@
         <v>2</v>
       </c>
       <c r="G3168" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3169">
@@ -85993,7 +85993,7 @@
         <v>2</v>
       </c>
       <c r="G3169" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3170">
@@ -86020,7 +86020,7 @@
         <v>2</v>
       </c>
       <c r="G3170" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3171">
@@ -86047,7 +86047,7 @@
         <v>2</v>
       </c>
       <c r="G3171" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3172">
@@ -86074,7 +86074,7 @@
         <v>2</v>
       </c>
       <c r="G3172" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3173">
@@ -86101,7 +86101,7 @@
         <v>2</v>
       </c>
       <c r="G3173" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3174">
@@ -86128,7 +86128,7 @@
         <v>2</v>
       </c>
       <c r="G3174" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3175">
@@ -86155,7 +86155,7 @@
         <v>2</v>
       </c>
       <c r="G3175" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3176">
@@ -86182,7 +86182,7 @@
         <v>2</v>
       </c>
       <c r="G3176" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3177">
@@ -86209,7 +86209,7 @@
         <v>2</v>
       </c>
       <c r="G3177" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3178">
@@ -86236,7 +86236,7 @@
         <v>2</v>
       </c>
       <c r="G3178" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3179">
@@ -86263,7 +86263,7 @@
         <v>2</v>
       </c>
       <c r="G3179" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3180">
@@ -86290,7 +86290,7 @@
         <v>2</v>
       </c>
       <c r="G3180" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3181">
@@ -86317,7 +86317,7 @@
         <v>2</v>
       </c>
       <c r="G3181" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3182">
@@ -86344,7 +86344,7 @@
         <v>2</v>
       </c>
       <c r="G3182" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3183">
@@ -86371,7 +86371,7 @@
         <v>2</v>
       </c>
       <c r="G3183" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3184">
@@ -86398,7 +86398,7 @@
         <v>2</v>
       </c>
       <c r="G3184" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3185">
@@ -86425,7 +86425,7 @@
         <v>2</v>
       </c>
       <c r="G3185" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3186">
@@ -86452,7 +86452,7 @@
         <v>2</v>
       </c>
       <c r="G3186" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3187">
@@ -86479,7 +86479,7 @@
         <v>2</v>
       </c>
       <c r="G3187" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3188">
@@ -86506,7 +86506,7 @@
         <v>2</v>
       </c>
       <c r="G3188" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3189">
@@ -86533,7 +86533,7 @@
         <v>2</v>
       </c>
       <c r="G3189" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3190">
@@ -86560,7 +86560,7 @@
         <v>2</v>
       </c>
       <c r="G3190" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3191">
@@ -86587,7 +86587,7 @@
         <v>2</v>
       </c>
       <c r="G3191" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3192">
@@ -86614,7 +86614,7 @@
         <v>2</v>
       </c>
       <c r="G3192" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3193">
@@ -86641,7 +86641,7 @@
         <v>2</v>
       </c>
       <c r="G3193" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3194">
@@ -86668,7 +86668,7 @@
         <v>2</v>
       </c>
       <c r="G3194" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3195">
@@ -86695,7 +86695,7 @@
         <v>2</v>
       </c>
       <c r="G3195" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3196">
@@ -86722,7 +86722,7 @@
         <v>2</v>
       </c>
       <c r="G3196" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3197">
@@ -86749,7 +86749,7 @@
         <v>2</v>
       </c>
       <c r="G3197" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3198">
@@ -86776,7 +86776,7 @@
         <v>2</v>
       </c>
       <c r="G3198" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3199">
@@ -86803,7 +86803,7 @@
         <v>2</v>
       </c>
       <c r="G3199" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3200">
@@ -86830,7 +86830,7 @@
         <v>2</v>
       </c>
       <c r="G3200" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3201">
@@ -86857,7 +86857,7 @@
         <v>2</v>
       </c>
       <c r="G3201" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3202">
@@ -86884,7 +86884,7 @@
         <v>2</v>
       </c>
       <c r="G3202" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3203">
@@ -86911,7 +86911,7 @@
         <v>2</v>
       </c>
       <c r="G3203" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3204">
@@ -86938,7 +86938,7 @@
         <v>2</v>
       </c>
       <c r="G3204" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3205">
@@ -86965,7 +86965,7 @@
         <v>2</v>
       </c>
       <c r="G3205" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3206">
@@ -86992,7 +86992,7 @@
         <v>2</v>
       </c>
       <c r="G3206" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3207">
@@ -87019,7 +87019,7 @@
         <v>2</v>
       </c>
       <c r="G3207" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3208">
@@ -87046,7 +87046,7 @@
         <v>2</v>
       </c>
       <c r="G3208" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3209">
@@ -87073,7 +87073,7 @@
         <v>2</v>
       </c>
       <c r="G3209" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3210">
@@ -87100,7 +87100,7 @@
         <v>2</v>
       </c>
       <c r="G3210" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3211">
@@ -87127,7 +87127,7 @@
         <v>2</v>
       </c>
       <c r="G3211" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3212">
@@ -87154,7 +87154,7 @@
         <v>2</v>
       </c>
       <c r="G3212" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3213">
@@ -87181,7 +87181,7 @@
         <v>2</v>
       </c>
       <c r="G3213" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3214">
@@ -87208,7 +87208,7 @@
         <v>2</v>
       </c>
       <c r="G3214" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3215">
@@ -87235,7 +87235,7 @@
         <v>2</v>
       </c>
       <c r="G3215" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3216">
@@ -87262,7 +87262,7 @@
         <v>2</v>
       </c>
       <c r="G3216" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3217">
@@ -87289,7 +87289,7 @@
         <v>2</v>
       </c>
       <c r="G3217" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3218">
@@ -87316,7 +87316,7 @@
         <v>2</v>
       </c>
       <c r="G3218" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3219">
@@ -87343,7 +87343,7 @@
         <v>2</v>
       </c>
       <c r="G3219" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3220">
@@ -87370,7 +87370,7 @@
         <v>2</v>
       </c>
       <c r="G3220" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3221">
@@ -87397,7 +87397,7 @@
         <v>2</v>
       </c>
       <c r="G3221" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3222">
@@ -87424,7 +87424,7 @@
         <v>2</v>
       </c>
       <c r="G3222" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3223">
@@ -87451,7 +87451,7 @@
         <v>2</v>
       </c>
       <c r="G3223" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3224">
@@ -87478,7 +87478,7 @@
         <v>2</v>
       </c>
       <c r="G3224" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3225">
@@ -87505,7 +87505,7 @@
         <v>2</v>
       </c>
       <c r="G3225" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3226">
@@ -87532,7 +87532,7 @@
         <v>2</v>
       </c>
       <c r="G3226" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3227">
@@ -87559,7 +87559,7 @@
         <v>2</v>
       </c>
       <c r="G3227" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3228">
@@ -87586,7 +87586,7 @@
         <v>2</v>
       </c>
       <c r="G3228" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3229">
@@ -87613,7 +87613,7 @@
         <v>2</v>
       </c>
       <c r="G3229" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3230">
@@ -87640,7 +87640,7 @@
         <v>2</v>
       </c>
       <c r="G3230" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3231">
@@ -87667,7 +87667,7 @@
         <v>2</v>
       </c>
       <c r="G3231" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3232">
@@ -87694,7 +87694,7 @@
         <v>2</v>
       </c>
       <c r="G3232" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3233">
@@ -87721,7 +87721,7 @@
         <v>2</v>
       </c>
       <c r="G3233" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3234">
@@ -87748,7 +87748,7 @@
         <v>2</v>
       </c>
       <c r="G3234" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3235">
@@ -87775,7 +87775,7 @@
         <v>2</v>
       </c>
       <c r="G3235" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3236">
@@ -87802,7 +87802,7 @@
         <v>2</v>
       </c>
       <c r="G3236" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3237">
@@ -87829,7 +87829,7 @@
         <v>2</v>
       </c>
       <c r="G3237" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3238">
@@ -87856,7 +87856,7 @@
         <v>2</v>
       </c>
       <c r="G3238" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3239">
@@ -87883,7 +87883,7 @@
         <v>2</v>
       </c>
       <c r="G3239" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3240">
@@ -87910,7 +87910,7 @@
         <v>2</v>
       </c>
       <c r="G3240" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3241">
@@ -87937,7 +87937,7 @@
         <v>2</v>
       </c>
       <c r="G3241" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3242">
@@ -87964,7 +87964,7 @@
         <v>2</v>
       </c>
       <c r="G3242" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3243">
@@ -87991,7 +87991,7 @@
         <v>2</v>
       </c>
       <c r="G3243" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3244">
@@ -88018,7 +88018,7 @@
         <v>2</v>
       </c>
       <c r="G3244" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3245">
@@ -88045,7 +88045,7 @@
         <v>2</v>
       </c>
       <c r="G3245" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3246">
@@ -88072,7 +88072,7 @@
         <v>2</v>
       </c>
       <c r="G3246" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3247">
@@ -88099,7 +88099,7 @@
         <v>2</v>
       </c>
       <c r="G3247" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3248">
@@ -88126,7 +88126,7 @@
         <v>2</v>
       </c>
       <c r="G3248" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3249">
@@ -88153,7 +88153,7 @@
         <v>2</v>
       </c>
       <c r="G3249" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3250">
@@ -88180,7 +88180,7 @@
         <v>2</v>
       </c>
       <c r="G3250" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3251">
@@ -88207,7 +88207,7 @@
         <v>2</v>
       </c>
       <c r="G3251" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3252">
@@ -88234,7 +88234,7 @@
         <v>2</v>
       </c>
       <c r="G3252" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3253">
@@ -88261,7 +88261,7 @@
         <v>2</v>
       </c>
       <c r="G3253" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3254">
@@ -88288,7 +88288,7 @@
         <v>2</v>
       </c>
       <c r="G3254" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3255">
@@ -88315,7 +88315,7 @@
         <v>2</v>
       </c>
       <c r="G3255" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3256">
@@ -88342,7 +88342,7 @@
         <v>2</v>
       </c>
       <c r="G3256" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3257">
@@ -88369,7 +88369,7 @@
         <v>2</v>
       </c>
       <c r="G3257" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3258">
@@ -88396,7 +88396,7 @@
         <v>2</v>
       </c>
       <c r="G3258" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3259">
@@ -88423,7 +88423,7 @@
         <v>2</v>
       </c>
       <c r="G3259" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3260">
@@ -88450,7 +88450,7 @@
         <v>2</v>
       </c>
       <c r="G3260" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3261">
@@ -88477,7 +88477,7 @@
         <v>2</v>
       </c>
       <c r="G3261" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3262">
@@ -88504,7 +88504,7 @@
         <v>2</v>
       </c>
       <c r="G3262" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3263">
@@ -88531,7 +88531,7 @@
         <v>2</v>
       </c>
       <c r="G3263" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3264">
@@ -88558,7 +88558,7 @@
         <v>2</v>
       </c>
       <c r="G3264" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3265">
@@ -88585,7 +88585,7 @@
         <v>2</v>
       </c>
       <c r="G3265" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3266">
@@ -88612,7 +88612,7 @@
         <v>2</v>
       </c>
       <c r="G3266" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3267">
@@ -88639,7 +88639,7 @@
         <v>2</v>
       </c>
       <c r="G3267" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3268">
@@ -88666,7 +88666,7 @@
         <v>2</v>
       </c>
       <c r="G3268" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3269">
@@ -88693,7 +88693,7 @@
         <v>2</v>
       </c>
       <c r="G3269" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3270">
@@ -88720,7 +88720,7 @@
         <v>2</v>
       </c>
       <c r="G3270" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3271">
@@ -88747,7 +88747,7 @@
         <v>2</v>
       </c>
       <c r="G3271" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3272">
@@ -88774,7 +88774,7 @@
         <v>2</v>
       </c>
       <c r="G3272" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3273">
@@ -88801,7 +88801,7 @@
         <v>2</v>
       </c>
       <c r="G3273" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3274">
@@ -88828,7 +88828,7 @@
         <v>2</v>
       </c>
       <c r="G3274" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3275">
@@ -88855,7 +88855,7 @@
         <v>2</v>
       </c>
       <c r="G3275" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3276">
@@ -88882,7 +88882,7 @@
         <v>2</v>
       </c>
       <c r="G3276" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3277">
@@ -88909,7 +88909,7 @@
         <v>2</v>
       </c>
       <c r="G3277" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3278">
@@ -88936,7 +88936,7 @@
         <v>2</v>
       </c>
       <c r="G3278" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3279">
@@ -88963,7 +88963,7 @@
         <v>2</v>
       </c>
       <c r="G3279" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3280">
@@ -88990,7 +88990,7 @@
         <v>2</v>
       </c>
       <c r="G3280" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3281">
@@ -89017,7 +89017,7 @@
         <v>2</v>
       </c>
       <c r="G3281" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3282">
@@ -89044,7 +89044,7 @@
         <v>2</v>
       </c>
       <c r="G3282" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3283">
@@ -89071,7 +89071,7 @@
         <v>2</v>
       </c>
       <c r="G3283" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3284">
@@ -89098,7 +89098,7 @@
         <v>2</v>
       </c>
       <c r="G3284" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3285">
@@ -89125,7 +89125,7 @@
         <v>2</v>
       </c>
       <c r="G3285" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3286">
@@ -89152,7 +89152,7 @@
         <v>2</v>
       </c>
       <c r="G3286" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3287">
@@ -89179,7 +89179,7 @@
         <v>2</v>
       </c>
       <c r="G3287" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3288">
@@ -89206,7 +89206,7 @@
         <v>2</v>
       </c>
       <c r="G3288" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3289">
@@ -89233,7 +89233,7 @@
         <v>2</v>
       </c>
       <c r="G3289" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3290">
@@ -89260,7 +89260,7 @@
         <v>2</v>
       </c>
       <c r="G3290" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3291">
@@ -89287,7 +89287,7 @@
         <v>2</v>
       </c>
       <c r="G3291" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3292">
@@ -89314,7 +89314,7 @@
         <v>2</v>
       </c>
       <c r="G3292" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3293">
@@ -89341,7 +89341,7 @@
         <v>2</v>
       </c>
       <c r="G3293" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3294">
@@ -89368,7 +89368,7 @@
         <v>2</v>
       </c>
       <c r="G3294" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3295">
@@ -89395,7 +89395,7 @@
         <v>2</v>
       </c>
       <c r="G3295" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3296">
@@ -89422,7 +89422,7 @@
         <v>2</v>
       </c>
       <c r="G3296" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3297">
@@ -89449,7 +89449,7 @@
         <v>2</v>
       </c>
       <c r="G3297" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3298">
@@ -89476,7 +89476,7 @@
         <v>2</v>
       </c>
       <c r="G3298" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3299">
@@ -89503,7 +89503,7 @@
         <v>2</v>
       </c>
       <c r="G3299" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3300">
@@ -89530,7 +89530,7 @@
         <v>2</v>
       </c>
       <c r="G3300" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3301">
@@ -89557,7 +89557,7 @@
         <v>2</v>
       </c>
       <c r="G3301" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3302">
@@ -89584,7 +89584,7 @@
         <v>2</v>
       </c>
       <c r="G3302" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3303">
@@ -89611,7 +89611,7 @@
         <v>2</v>
       </c>
       <c r="G3303" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3304">
@@ -89638,7 +89638,7 @@
         <v>2</v>
       </c>
       <c r="G3304" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3305">
@@ -89665,7 +89665,7 @@
         <v>2</v>
       </c>
       <c r="G3305" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3306">
@@ -89692,7 +89692,7 @@
         <v>2</v>
       </c>
       <c r="G3306" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3307">
@@ -89719,7 +89719,7 @@
         <v>2</v>
       </c>
       <c r="G3307" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3308">
@@ -89746,7 +89746,7 @@
         <v>2</v>
       </c>
       <c r="G3308" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3309">
@@ -89773,7 +89773,7 @@
         <v>2</v>
       </c>
       <c r="G3309" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3310">
@@ -89800,7 +89800,7 @@
         <v>2</v>
       </c>
       <c r="G3310" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3311">
@@ -89827,7 +89827,7 @@
         <v>2</v>
       </c>
       <c r="G3311" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3312">
@@ -89854,7 +89854,7 @@
         <v>2</v>
       </c>
       <c r="G3312" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
     <row r="3313">
@@ -89881,7 +89881,7 @@
         <v>2</v>
       </c>
       <c r="G3313" s="2" t="n">
-        <v>46280.87221256112</v>
+        <v>46281.4555915994</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -80172,7 +80172,7 @@
         <v>1</v>
       </c>
       <c r="C2954" t="n">
-        <v>10.03</v>
+        <v>10.04</v>
       </c>
       <c r="D2954" t="inlineStr">
         <is>
@@ -80188,7 +80188,7 @@
         <v>2</v>
       </c>
       <c r="G2954" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2955">
@@ -80215,7 +80215,7 @@
         <v>2</v>
       </c>
       <c r="G2955" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2956">
@@ -80226,7 +80226,7 @@
         <v>3</v>
       </c>
       <c r="C2956" t="n">
-        <v>10.27</v>
+        <v>10.28</v>
       </c>
       <c r="D2956" t="inlineStr">
         <is>
@@ -80242,7 +80242,7 @@
         <v>2</v>
       </c>
       <c r="G2956" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2957">
@@ -80269,7 +80269,7 @@
         <v>2</v>
       </c>
       <c r="G2957" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2958">
@@ -80280,7 +80280,7 @@
         <v>5</v>
       </c>
       <c r="C2958" t="n">
-        <v>12.42</v>
+        <v>12.41</v>
       </c>
       <c r="D2958" t="inlineStr">
         <is>
@@ -80296,7 +80296,7 @@
         <v>2</v>
       </c>
       <c r="G2958" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2959">
@@ -80323,7 +80323,7 @@
         <v>2</v>
       </c>
       <c r="G2959" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2960">
@@ -80334,7 +80334,7 @@
         <v>7</v>
       </c>
       <c r="C2960" t="n">
-        <v>21.41</v>
+        <v>21.42</v>
       </c>
       <c r="D2960" t="inlineStr">
         <is>
@@ -80350,7 +80350,7 @@
         <v>2</v>
       </c>
       <c r="G2960" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2961">
@@ -80377,7 +80377,7 @@
         <v>2</v>
       </c>
       <c r="G2961" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2962">
@@ -80404,7 +80404,7 @@
         <v>2</v>
       </c>
       <c r="G2962" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2963">
@@ -80415,7 +80415,7 @@
         <v>10</v>
       </c>
       <c r="C2963" t="n">
-        <v>25.83</v>
+        <v>25.82</v>
       </c>
       <c r="D2963" t="inlineStr">
         <is>
@@ -80431,7 +80431,7 @@
         <v>2</v>
       </c>
       <c r="G2963" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2964">
@@ -80458,7 +80458,7 @@
         <v>2</v>
       </c>
       <c r="G2964" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2965">
@@ -80485,7 +80485,7 @@
         <v>2</v>
       </c>
       <c r="G2965" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2966">
@@ -80512,7 +80512,7 @@
         <v>2</v>
       </c>
       <c r="G2966" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2967">
@@ -80539,7 +80539,7 @@
         <v>2</v>
       </c>
       <c r="G2967" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2968">
@@ -80566,7 +80566,7 @@
         <v>2</v>
       </c>
       <c r="G2968" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2969">
@@ -80593,7 +80593,7 @@
         <v>2</v>
       </c>
       <c r="G2969" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2970">
@@ -80620,7 +80620,7 @@
         <v>2</v>
       </c>
       <c r="G2970" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2971">
@@ -80631,7 +80631,7 @@
         <v>18</v>
       </c>
       <c r="C2971" t="n">
-        <v>34.13</v>
+        <v>34.12</v>
       </c>
       <c r="D2971" t="inlineStr">
         <is>
@@ -80647,7 +80647,7 @@
         <v>2</v>
       </c>
       <c r="G2971" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2972">
@@ -80674,7 +80674,7 @@
         <v>2</v>
       </c>
       <c r="G2972" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2973">
@@ -80701,7 +80701,7 @@
         <v>2</v>
       </c>
       <c r="G2973" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2974">
@@ -80712,7 +80712,7 @@
         <v>21</v>
       </c>
       <c r="C2974" t="n">
-        <v>36.9</v>
+        <v>36.89</v>
       </c>
       <c r="D2974" t="inlineStr">
         <is>
@@ -80728,7 +80728,7 @@
         <v>2</v>
       </c>
       <c r="G2974" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2975">
@@ -80755,7 +80755,7 @@
         <v>2</v>
       </c>
       <c r="G2975" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2976">
@@ -80782,7 +80782,7 @@
         <v>2</v>
       </c>
       <c r="G2976" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2977">
@@ -80809,7 +80809,7 @@
         <v>2</v>
       </c>
       <c r="G2977" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2978">
@@ -80836,7 +80836,7 @@
         <v>2</v>
       </c>
       <c r="G2978" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2979">
@@ -80863,7 +80863,7 @@
         <v>2</v>
       </c>
       <c r="G2979" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2980">
@@ -80874,7 +80874,7 @@
         <v>3</v>
       </c>
       <c r="C2980" t="n">
-        <v>9.34</v>
+        <v>9.35</v>
       </c>
       <c r="D2980" t="inlineStr">
         <is>
@@ -80890,7 +80890,7 @@
         <v>2</v>
       </c>
       <c r="G2980" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2981">
@@ -80901,7 +80901,7 @@
         <v>4</v>
       </c>
       <c r="C2981" t="n">
-        <v>8.83</v>
+        <v>8.82</v>
       </c>
       <c r="D2981" t="inlineStr">
         <is>
@@ -80917,7 +80917,7 @@
         <v>2</v>
       </c>
       <c r="G2981" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2982">
@@ -80928,7 +80928,7 @@
         <v>5</v>
       </c>
       <c r="C2982" t="n">
-        <v>8.67</v>
+        <v>8.66</v>
       </c>
       <c r="D2982" t="inlineStr">
         <is>
@@ -80944,7 +80944,7 @@
         <v>2</v>
       </c>
       <c r="G2982" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2983">
@@ -80971,7 +80971,7 @@
         <v>2</v>
       </c>
       <c r="G2983" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2984">
@@ -80998,7 +80998,7 @@
         <v>2</v>
       </c>
       <c r="G2984" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2985">
@@ -81009,7 +81009,7 @@
         <v>8</v>
       </c>
       <c r="C2985" t="n">
-        <v>44.35</v>
+        <v>44.34</v>
       </c>
       <c r="D2985" t="inlineStr">
         <is>
@@ -81025,7 +81025,7 @@
         <v>2</v>
       </c>
       <c r="G2985" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2986">
@@ -81052,7 +81052,7 @@
         <v>2</v>
       </c>
       <c r="G2986" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2987">
@@ -81079,7 +81079,7 @@
         <v>2</v>
       </c>
       <c r="G2987" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2988">
@@ -81106,7 +81106,7 @@
         <v>2</v>
       </c>
       <c r="G2988" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2989">
@@ -81133,7 +81133,7 @@
         <v>2</v>
       </c>
       <c r="G2989" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2990">
@@ -81160,7 +81160,7 @@
         <v>2</v>
       </c>
       <c r="G2990" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2991">
@@ -81171,7 +81171,7 @@
         <v>14</v>
       </c>
       <c r="C2991" t="n">
-        <v>31.34</v>
+        <v>31.37</v>
       </c>
       <c r="D2991" t="inlineStr">
         <is>
@@ -81187,7 +81187,7 @@
         <v>2</v>
       </c>
       <c r="G2991" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2992">
@@ -81198,7 +81198,7 @@
         <v>15</v>
       </c>
       <c r="C2992" t="n">
-        <v>31.5</v>
+        <v>31.51</v>
       </c>
       <c r="D2992" t="inlineStr">
         <is>
@@ -81214,7 +81214,7 @@
         <v>2</v>
       </c>
       <c r="G2992" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2993">
@@ -81225,7 +81225,7 @@
         <v>16</v>
       </c>
       <c r="C2993" t="n">
-        <v>34.13</v>
+        <v>34.14</v>
       </c>
       <c r="D2993" t="inlineStr">
         <is>
@@ -81241,7 +81241,7 @@
         <v>2</v>
       </c>
       <c r="G2993" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2994">
@@ -81268,7 +81268,7 @@
         <v>2</v>
       </c>
       <c r="G2994" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2995">
@@ -81295,7 +81295,7 @@
         <v>2</v>
       </c>
       <c r="G2995" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2996">
@@ -81306,7 +81306,7 @@
         <v>19</v>
       </c>
       <c r="C2996" t="n">
-        <v>20.07</v>
+        <v>20.08</v>
       </c>
       <c r="D2996" t="inlineStr">
         <is>
@@ -81322,7 +81322,7 @@
         <v>2</v>
       </c>
       <c r="G2996" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2997">
@@ -81333,7 +81333,7 @@
         <v>20</v>
       </c>
       <c r="C2997" t="n">
-        <v>24.83</v>
+        <v>24.84</v>
       </c>
       <c r="D2997" t="inlineStr">
         <is>
@@ -81349,7 +81349,7 @@
         <v>2</v>
       </c>
       <c r="G2997" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2998">
@@ -81376,7 +81376,7 @@
         <v>2</v>
       </c>
       <c r="G2998" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="2999">
@@ -81403,7 +81403,7 @@
         <v>2</v>
       </c>
       <c r="G2999" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3000">
@@ -81414,7 +81414,7 @@
         <v>23</v>
       </c>
       <c r="C3000" t="n">
-        <v>36.09</v>
+        <v>36.1</v>
       </c>
       <c r="D3000" t="inlineStr">
         <is>
@@ -81430,7 +81430,7 @@
         <v>2</v>
       </c>
       <c r="G3000" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3001">
@@ -81441,7 +81441,7 @@
         <v>24</v>
       </c>
       <c r="C3001" t="n">
-        <v>25.32</v>
+        <v>25.33</v>
       </c>
       <c r="D3001" t="inlineStr">
         <is>
@@ -81457,7 +81457,7 @@
         <v>2</v>
       </c>
       <c r="G3001" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3002">
@@ -81484,7 +81484,7 @@
         <v>2</v>
       </c>
       <c r="G3002" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3003">
@@ -81511,7 +81511,7 @@
         <v>2</v>
       </c>
       <c r="G3003" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3004">
@@ -81522,7 +81522,7 @@
         <v>3</v>
       </c>
       <c r="C3004" t="n">
-        <v>12.63</v>
+        <v>12.64</v>
       </c>
       <c r="D3004" t="inlineStr">
         <is>
@@ -81538,7 +81538,7 @@
         <v>2</v>
       </c>
       <c r="G3004" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3005">
@@ -81565,7 +81565,7 @@
         <v>2</v>
       </c>
       <c r="G3005" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3006">
@@ -81592,7 +81592,7 @@
         <v>2</v>
       </c>
       <c r="G3006" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3007">
@@ -81619,7 +81619,7 @@
         <v>2</v>
       </c>
       <c r="G3007" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3008">
@@ -81630,7 +81630,7 @@
         <v>7</v>
       </c>
       <c r="C3008" t="n">
-        <v>19.65</v>
+        <v>19.66</v>
       </c>
       <c r="D3008" t="inlineStr">
         <is>
@@ -81646,7 +81646,7 @@
         <v>2</v>
       </c>
       <c r="G3008" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3009">
@@ -81673,7 +81673,7 @@
         <v>2</v>
       </c>
       <c r="G3009" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3010">
@@ -81684,7 +81684,7 @@
         <v>9</v>
       </c>
       <c r="C3010" t="n">
-        <v>52.78</v>
+        <v>52.76</v>
       </c>
       <c r="D3010" t="inlineStr">
         <is>
@@ -81700,7 +81700,7 @@
         <v>2</v>
       </c>
       <c r="G3010" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3011">
@@ -81711,7 +81711,7 @@
         <v>10</v>
       </c>
       <c r="C3011" t="n">
-        <v>24.86</v>
+        <v>24.79</v>
       </c>
       <c r="D3011" t="inlineStr">
         <is>
@@ -81727,7 +81727,7 @@
         <v>2</v>
       </c>
       <c r="G3011" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3012">
@@ -81738,7 +81738,7 @@
         <v>11</v>
       </c>
       <c r="C3012" t="n">
-        <v>19.09</v>
+        <v>19.06</v>
       </c>
       <c r="D3012" t="inlineStr">
         <is>
@@ -81754,7 +81754,7 @@
         <v>2</v>
       </c>
       <c r="G3012" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3013">
@@ -81765,7 +81765,7 @@
         <v>12</v>
       </c>
       <c r="C3013" t="n">
-        <v>21.06</v>
+        <v>21.12</v>
       </c>
       <c r="D3013" t="inlineStr">
         <is>
@@ -81781,7 +81781,7 @@
         <v>2</v>
       </c>
       <c r="G3013" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3014">
@@ -81792,7 +81792,7 @@
         <v>13</v>
       </c>
       <c r="C3014" t="n">
-        <v>23.56</v>
+        <v>23.6</v>
       </c>
       <c r="D3014" t="inlineStr">
         <is>
@@ -81808,7 +81808,7 @@
         <v>2</v>
       </c>
       <c r="G3014" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3015">
@@ -81835,7 +81835,7 @@
         <v>2</v>
       </c>
       <c r="G3015" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3016">
@@ -81846,7 +81846,7 @@
         <v>15</v>
       </c>
       <c r="C3016" t="n">
-        <v>22.19</v>
+        <v>22.18</v>
       </c>
       <c r="D3016" t="inlineStr">
         <is>
@@ -81862,7 +81862,7 @@
         <v>2</v>
       </c>
       <c r="G3016" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3017">
@@ -81873,7 +81873,7 @@
         <v>16</v>
       </c>
       <c r="C3017" t="n">
-        <v>23.44</v>
+        <v>23.35</v>
       </c>
       <c r="D3017" t="inlineStr">
         <is>
@@ -81889,7 +81889,7 @@
         <v>2</v>
       </c>
       <c r="G3017" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3018">
@@ -81900,7 +81900,7 @@
         <v>17</v>
       </c>
       <c r="C3018" t="n">
-        <v>22.72</v>
+        <v>22.59</v>
       </c>
       <c r="D3018" t="inlineStr">
         <is>
@@ -81916,7 +81916,7 @@
         <v>2</v>
       </c>
       <c r="G3018" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3019">
@@ -81927,7 +81927,7 @@
         <v>18</v>
       </c>
       <c r="C3019" t="n">
-        <v>21.19</v>
+        <v>21.11</v>
       </c>
       <c r="D3019" t="inlineStr">
         <is>
@@ -81943,7 +81943,7 @@
         <v>2</v>
       </c>
       <c r="G3019" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3020">
@@ -81954,7 +81954,7 @@
         <v>19</v>
       </c>
       <c r="C3020" t="n">
-        <v>23.52</v>
+        <v>23.44</v>
       </c>
       <c r="D3020" t="inlineStr">
         <is>
@@ -81970,7 +81970,7 @@
         <v>2</v>
       </c>
       <c r="G3020" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3021">
@@ -81981,7 +81981,7 @@
         <v>20</v>
       </c>
       <c r="C3021" t="n">
-        <v>36.47</v>
+        <v>36.45</v>
       </c>
       <c r="D3021" t="inlineStr">
         <is>
@@ -81997,7 +81997,7 @@
         <v>2</v>
       </c>
       <c r="G3021" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3022">
@@ -82008,7 +82008,7 @@
         <v>21</v>
       </c>
       <c r="C3022" t="n">
-        <v>38.77</v>
+        <v>38.76</v>
       </c>
       <c r="D3022" t="inlineStr">
         <is>
@@ -82024,7 +82024,7 @@
         <v>2</v>
       </c>
       <c r="G3022" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3023">
@@ -82051,7 +82051,7 @@
         <v>2</v>
       </c>
       <c r="G3023" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3024">
@@ -82078,7 +82078,7 @@
         <v>2</v>
       </c>
       <c r="G3024" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3025">
@@ -82105,7 +82105,7 @@
         <v>2</v>
       </c>
       <c r="G3025" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3026">
@@ -82132,7 +82132,7 @@
         <v>2</v>
       </c>
       <c r="G3026" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3027">
@@ -82159,7 +82159,7 @@
         <v>2</v>
       </c>
       <c r="G3027" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3028">
@@ -82186,7 +82186,7 @@
         <v>2</v>
       </c>
       <c r="G3028" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3029">
@@ -82213,7 +82213,7 @@
         <v>2</v>
       </c>
       <c r="G3029" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3030">
@@ -82240,7 +82240,7 @@
         <v>2</v>
       </c>
       <c r="G3030" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3031">
@@ -82267,7 +82267,7 @@
         <v>2</v>
       </c>
       <c r="G3031" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3032">
@@ -82294,7 +82294,7 @@
         <v>2</v>
       </c>
       <c r="G3032" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3033">
@@ -82321,7 +82321,7 @@
         <v>2</v>
       </c>
       <c r="G3033" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3034">
@@ -82348,7 +82348,7 @@
         <v>2</v>
       </c>
       <c r="G3034" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3035">
@@ -82359,7 +82359,7 @@
         <v>10</v>
       </c>
       <c r="C3035" t="n">
-        <v>24.28</v>
+        <v>24.09</v>
       </c>
       <c r="D3035" t="inlineStr">
         <is>
@@ -82375,7 +82375,7 @@
         <v>2</v>
       </c>
       <c r="G3035" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3036">
@@ -82386,7 +82386,7 @@
         <v>11</v>
       </c>
       <c r="C3036" t="n">
-        <v>21.28</v>
+        <v>21.26</v>
       </c>
       <c r="D3036" t="inlineStr">
         <is>
@@ -82402,7 +82402,7 @@
         <v>2</v>
       </c>
       <c r="G3036" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3037">
@@ -82413,7 +82413,7 @@
         <v>12</v>
       </c>
       <c r="C3037" t="n">
-        <v>16.35</v>
+        <v>16.27</v>
       </c>
       <c r="D3037" t="inlineStr">
         <is>
@@ -82429,7 +82429,7 @@
         <v>2</v>
       </c>
       <c r="G3037" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3038">
@@ -82440,7 +82440,7 @@
         <v>13</v>
       </c>
       <c r="C3038" t="n">
-        <v>15.53</v>
+        <v>15.52</v>
       </c>
       <c r="D3038" t="inlineStr">
         <is>
@@ -82456,7 +82456,7 @@
         <v>2</v>
       </c>
       <c r="G3038" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3039">
@@ -82467,7 +82467,7 @@
         <v>14</v>
       </c>
       <c r="C3039" t="n">
-        <v>16.29</v>
+        <v>16.28</v>
       </c>
       <c r="D3039" t="inlineStr">
         <is>
@@ -82483,7 +82483,7 @@
         <v>2</v>
       </c>
       <c r="G3039" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3040">
@@ -82494,7 +82494,7 @@
         <v>15</v>
       </c>
       <c r="C3040" t="n">
-        <v>13.4</v>
+        <v>13.42</v>
       </c>
       <c r="D3040" t="inlineStr">
         <is>
@@ -82510,7 +82510,7 @@
         <v>2</v>
       </c>
       <c r="G3040" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3041">
@@ -82521,7 +82521,7 @@
         <v>16</v>
       </c>
       <c r="C3041" t="n">
-        <v>12.66</v>
+        <v>12.68</v>
       </c>
       <c r="D3041" t="inlineStr">
         <is>
@@ -82537,7 +82537,7 @@
         <v>2</v>
       </c>
       <c r="G3041" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3042">
@@ -82548,7 +82548,7 @@
         <v>17</v>
       </c>
       <c r="C3042" t="n">
-        <v>13.59</v>
+        <v>13.6</v>
       </c>
       <c r="D3042" t="inlineStr">
         <is>
@@ -82564,7 +82564,7 @@
         <v>2</v>
       </c>
       <c r="G3042" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3043">
@@ -82575,7 +82575,7 @@
         <v>18</v>
       </c>
       <c r="C3043" t="n">
-        <v>26.54</v>
+        <v>26.53</v>
       </c>
       <c r="D3043" t="inlineStr">
         <is>
@@ -82591,7 +82591,7 @@
         <v>2</v>
       </c>
       <c r="G3043" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3044">
@@ -82602,7 +82602,7 @@
         <v>19</v>
       </c>
       <c r="C3044" t="n">
-        <v>24.31</v>
+        <v>24.27</v>
       </c>
       <c r="D3044" t="inlineStr">
         <is>
@@ -82618,7 +82618,7 @@
         <v>2</v>
       </c>
       <c r="G3044" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3045">
@@ -82629,7 +82629,7 @@
         <v>20</v>
       </c>
       <c r="C3045" t="n">
-        <v>27.97</v>
+        <v>27.95</v>
       </c>
       <c r="D3045" t="inlineStr">
         <is>
@@ -82645,7 +82645,7 @@
         <v>2</v>
       </c>
       <c r="G3045" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3046">
@@ -82672,7 +82672,7 @@
         <v>2</v>
       </c>
       <c r="G3046" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3047">
@@ -82683,7 +82683,7 @@
         <v>22</v>
       </c>
       <c r="C3047" t="n">
-        <v>38.08</v>
+        <v>38.09</v>
       </c>
       <c r="D3047" t="inlineStr">
         <is>
@@ -82699,7 +82699,7 @@
         <v>2</v>
       </c>
       <c r="G3047" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3048">
@@ -82726,7 +82726,7 @@
         <v>2</v>
       </c>
       <c r="G3048" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3049">
@@ -82753,7 +82753,7 @@
         <v>2</v>
       </c>
       <c r="G3049" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3050">
@@ -82780,7 +82780,7 @@
         <v>2</v>
       </c>
       <c r="G3050" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3051">
@@ -82807,7 +82807,7 @@
         <v>2</v>
       </c>
       <c r="G3051" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3052">
@@ -82818,7 +82818,7 @@
         <v>3</v>
       </c>
       <c r="C3052" t="n">
-        <v>12.01</v>
+        <v>12.02</v>
       </c>
       <c r="D3052" t="inlineStr">
         <is>
@@ -82834,7 +82834,7 @@
         <v>2</v>
       </c>
       <c r="G3052" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3053">
@@ -82861,7 +82861,7 @@
         <v>2</v>
       </c>
       <c r="G3053" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3054">
@@ -82888,7 +82888,7 @@
         <v>2</v>
       </c>
       <c r="G3054" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3055">
@@ -82899,7 +82899,7 @@
         <v>6</v>
       </c>
       <c r="C3055" t="n">
-        <v>14.14</v>
+        <v>14.16</v>
       </c>
       <c r="D3055" t="inlineStr">
         <is>
@@ -82915,7 +82915,7 @@
         <v>2</v>
       </c>
       <c r="G3055" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3056">
@@ -82926,7 +82926,7 @@
         <v>7</v>
       </c>
       <c r="C3056" t="n">
-        <v>16.63</v>
+        <v>16.67</v>
       </c>
       <c r="D3056" t="inlineStr">
         <is>
@@ -82942,7 +82942,7 @@
         <v>2</v>
       </c>
       <c r="G3056" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3057">
@@ -82969,7 +82969,7 @@
         <v>2</v>
       </c>
       <c r="G3057" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3058">
@@ -82980,7 +82980,7 @@
         <v>9</v>
       </c>
       <c r="C3058" t="n">
-        <v>35.99</v>
+        <v>35.98</v>
       </c>
       <c r="D3058" t="inlineStr">
         <is>
@@ -82996,7 +82996,7 @@
         <v>2</v>
       </c>
       <c r="G3058" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3059">
@@ -83007,7 +83007,7 @@
         <v>10</v>
       </c>
       <c r="C3059" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="D3059" t="inlineStr">
         <is>
@@ -83023,7 +83023,7 @@
         <v>2</v>
       </c>
       <c r="G3059" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3060">
@@ -83034,7 +83034,7 @@
         <v>11</v>
       </c>
       <c r="C3060" t="n">
-        <v>18.44</v>
+        <v>18.42</v>
       </c>
       <c r="D3060" t="inlineStr">
         <is>
@@ -83050,7 +83050,7 @@
         <v>2</v>
       </c>
       <c r="G3060" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3061">
@@ -83061,7 +83061,7 @@
         <v>12</v>
       </c>
       <c r="C3061" t="n">
-        <v>14.93</v>
+        <v>14.89</v>
       </c>
       <c r="D3061" t="inlineStr">
         <is>
@@ -83077,7 +83077,7 @@
         <v>2</v>
       </c>
       <c r="G3061" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3062">
@@ -83088,7 +83088,7 @@
         <v>13</v>
       </c>
       <c r="C3062" t="n">
-        <v>14.11</v>
+        <v>14.08</v>
       </c>
       <c r="D3062" t="inlineStr">
         <is>
@@ -83104,7 +83104,7 @@
         <v>2</v>
       </c>
       <c r="G3062" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3063">
@@ -83115,7 +83115,7 @@
         <v>14</v>
       </c>
       <c r="C3063" t="n">
-        <v>14.29</v>
+        <v>14.28</v>
       </c>
       <c r="D3063" t="inlineStr">
         <is>
@@ -83131,7 +83131,7 @@
         <v>2</v>
       </c>
       <c r="G3063" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3064">
@@ -83142,7 +83142,7 @@
         <v>15</v>
       </c>
       <c r="C3064" t="n">
-        <v>17.62</v>
+        <v>17.53</v>
       </c>
       <c r="D3064" t="inlineStr">
         <is>
@@ -83158,7 +83158,7 @@
         <v>2</v>
       </c>
       <c r="G3064" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3065">
@@ -83169,7 +83169,7 @@
         <v>16</v>
       </c>
       <c r="C3065" t="n">
-        <v>20.89</v>
+        <v>20.81</v>
       </c>
       <c r="D3065" t="inlineStr">
         <is>
@@ -83185,7 +83185,7 @@
         <v>2</v>
       </c>
       <c r="G3065" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3066">
@@ -83196,7 +83196,7 @@
         <v>17</v>
       </c>
       <c r="C3066" t="n">
-        <v>14.87</v>
+        <v>14.85</v>
       </c>
       <c r="D3066" t="inlineStr">
         <is>
@@ -83212,7 +83212,7 @@
         <v>2</v>
       </c>
       <c r="G3066" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3067">
@@ -83239,7 +83239,7 @@
         <v>2</v>
       </c>
       <c r="G3067" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3068">
@@ -83250,7 +83250,7 @@
         <v>19</v>
       </c>
       <c r="C3068" t="n">
-        <v>30.08</v>
+        <v>30.06</v>
       </c>
       <c r="D3068" t="inlineStr">
         <is>
@@ -83266,7 +83266,7 @@
         <v>2</v>
       </c>
       <c r="G3068" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3069">
@@ -83293,7 +83293,7 @@
         <v>2</v>
       </c>
       <c r="G3069" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3070">
@@ -83320,7 +83320,7 @@
         <v>2</v>
       </c>
       <c r="G3070" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3071">
@@ -83347,7 +83347,7 @@
         <v>2</v>
       </c>
       <c r="G3071" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3072">
@@ -83374,7 +83374,7 @@
         <v>2</v>
       </c>
       <c r="G3072" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3073">
@@ -83401,7 +83401,7 @@
         <v>2</v>
       </c>
       <c r="G3073" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3074">
@@ -83428,7 +83428,7 @@
         <v>2</v>
       </c>
       <c r="G3074" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3075">
@@ -83455,7 +83455,7 @@
         <v>2</v>
       </c>
       <c r="G3075" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3076">
@@ -83482,7 +83482,7 @@
         <v>2</v>
       </c>
       <c r="G3076" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3077">
@@ -83509,7 +83509,7 @@
         <v>2</v>
       </c>
       <c r="G3077" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3078">
@@ -83536,7 +83536,7 @@
         <v>2</v>
       </c>
       <c r="G3078" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3079">
@@ -83563,7 +83563,7 @@
         <v>2</v>
       </c>
       <c r="G3079" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3080">
@@ -83574,7 +83574,7 @@
         <v>7</v>
       </c>
       <c r="C3080" t="n">
-        <v>14.73</v>
+        <v>14.74</v>
       </c>
       <c r="D3080" t="inlineStr">
         <is>
@@ -83590,7 +83590,7 @@
         <v>2</v>
       </c>
       <c r="G3080" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3081">
@@ -83601,7 +83601,7 @@
         <v>8</v>
       </c>
       <c r="C3081" t="n">
-        <v>24.68</v>
+        <v>24.69</v>
       </c>
       <c r="D3081" t="inlineStr">
         <is>
@@ -83617,7 +83617,7 @@
         <v>2</v>
       </c>
       <c r="G3081" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3082">
@@ -83628,7 +83628,7 @@
         <v>9</v>
       </c>
       <c r="C3082" t="n">
-        <v>25.82</v>
+        <v>25.83</v>
       </c>
       <c r="D3082" t="inlineStr">
         <is>
@@ -83644,7 +83644,7 @@
         <v>2</v>
       </c>
       <c r="G3082" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3083">
@@ -83655,7 +83655,7 @@
         <v>10</v>
       </c>
       <c r="C3083" t="n">
-        <v>24.18</v>
+        <v>24.24</v>
       </c>
       <c r="D3083" t="inlineStr">
         <is>
@@ -83671,7 +83671,7 @@
         <v>2</v>
       </c>
       <c r="G3083" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3084">
@@ -83682,7 +83682,7 @@
         <v>11</v>
       </c>
       <c r="C3084" t="n">
-        <v>21.19</v>
+        <v>21.25</v>
       </c>
       <c r="D3084" t="inlineStr">
         <is>
@@ -83698,7 +83698,7 @@
         <v>2</v>
       </c>
       <c r="G3084" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3085">
@@ -83709,7 +83709,7 @@
         <v>12</v>
       </c>
       <c r="C3085" t="n">
-        <v>20.52</v>
+        <v>20.5</v>
       </c>
       <c r="D3085" t="inlineStr">
         <is>
@@ -83725,7 +83725,7 @@
         <v>2</v>
       </c>
       <c r="G3085" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3086">
@@ -83736,7 +83736,7 @@
         <v>13</v>
       </c>
       <c r="C3086" t="n">
-        <v>22.47</v>
+        <v>22.45</v>
       </c>
       <c r="D3086" t="inlineStr">
         <is>
@@ -83752,7 +83752,7 @@
         <v>2</v>
       </c>
       <c r="G3086" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3087">
@@ -83763,7 +83763,7 @@
         <v>14</v>
       </c>
       <c r="C3087" t="n">
-        <v>21.51</v>
+        <v>21.48</v>
       </c>
       <c r="D3087" t="inlineStr">
         <is>
@@ -83779,7 +83779,7 @@
         <v>2</v>
       </c>
       <c r="G3087" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3088">
@@ -83790,7 +83790,7 @@
         <v>15</v>
       </c>
       <c r="C3088" t="n">
-        <v>20.87</v>
+        <v>20.84</v>
       </c>
       <c r="D3088" t="inlineStr">
         <is>
@@ -83806,7 +83806,7 @@
         <v>2</v>
       </c>
       <c r="G3088" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3089">
@@ -83817,7 +83817,7 @@
         <v>16</v>
       </c>
       <c r="C3089" t="n">
-        <v>26.85</v>
+        <v>26.84</v>
       </c>
       <c r="D3089" t="inlineStr">
         <is>
@@ -83833,7 +83833,7 @@
         <v>2</v>
       </c>
       <c r="G3089" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3090">
@@ -83844,7 +83844,7 @@
         <v>17</v>
       </c>
       <c r="C3090" t="n">
-        <v>24.07</v>
+        <v>24.11</v>
       </c>
       <c r="D3090" t="inlineStr">
         <is>
@@ -83860,7 +83860,7 @@
         <v>2</v>
       </c>
       <c r="G3090" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3091">
@@ -83871,7 +83871,7 @@
         <v>18</v>
       </c>
       <c r="C3091" t="n">
-        <v>22.68</v>
+        <v>22.69</v>
       </c>
       <c r="D3091" t="inlineStr">
         <is>
@@ -83887,7 +83887,7 @@
         <v>2</v>
       </c>
       <c r="G3091" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3092">
@@ -83898,7 +83898,7 @@
         <v>19</v>
       </c>
       <c r="C3092" t="n">
-        <v>30.88</v>
+        <v>30.87</v>
       </c>
       <c r="D3092" t="inlineStr">
         <is>
@@ -83914,7 +83914,7 @@
         <v>2</v>
       </c>
       <c r="G3092" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3093">
@@ -83925,7 +83925,7 @@
         <v>20</v>
       </c>
       <c r="C3093" t="n">
-        <v>29.3</v>
+        <v>29.27</v>
       </c>
       <c r="D3093" t="inlineStr">
         <is>
@@ -83941,7 +83941,7 @@
         <v>2</v>
       </c>
       <c r="G3093" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3094">
@@ -83968,7 +83968,7 @@
         <v>2</v>
       </c>
       <c r="G3094" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3095">
@@ -83995,7 +83995,7 @@
         <v>2</v>
       </c>
       <c r="G3095" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3096">
@@ -84022,7 +84022,7 @@
         <v>2</v>
       </c>
       <c r="G3096" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3097">
@@ -84049,7 +84049,7 @@
         <v>2</v>
       </c>
       <c r="G3097" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3098">
@@ -84060,7 +84060,7 @@
         <v>1</v>
       </c>
       <c r="C3098" t="n">
-        <v>9.4</v>
+        <v>9.41</v>
       </c>
       <c r="D3098" t="inlineStr">
         <is>
@@ -84076,7 +84076,7 @@
         <v>2</v>
       </c>
       <c r="G3098" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3099">
@@ -84087,7 +84087,7 @@
         <v>2</v>
       </c>
       <c r="C3099" t="n">
-        <v>12.26</v>
+        <v>12.27</v>
       </c>
       <c r="D3099" t="inlineStr">
         <is>
@@ -84103,7 +84103,7 @@
         <v>2</v>
       </c>
       <c r="G3099" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3100">
@@ -84130,7 +84130,7 @@
         <v>2</v>
       </c>
       <c r="G3100" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3101">
@@ -84157,7 +84157,7 @@
         <v>2</v>
       </c>
       <c r="G3101" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3102">
@@ -84168,7 +84168,7 @@
         <v>5</v>
       </c>
       <c r="C3102" t="n">
-        <v>10.77</v>
+        <v>10.78</v>
       </c>
       <c r="D3102" t="inlineStr">
         <is>
@@ -84184,7 +84184,7 @@
         <v>2</v>
       </c>
       <c r="G3102" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3103">
@@ -84195,7 +84195,7 @@
         <v>6</v>
       </c>
       <c r="C3103" t="n">
-        <v>11.58</v>
+        <v>11.59</v>
       </c>
       <c r="D3103" t="inlineStr">
         <is>
@@ -84211,7 +84211,7 @@
         <v>2</v>
       </c>
       <c r="G3103" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3104">
@@ -84222,7 +84222,7 @@
         <v>7</v>
       </c>
       <c r="C3104" t="n">
-        <v>23.22</v>
+        <v>23.23</v>
       </c>
       <c r="D3104" t="inlineStr">
         <is>
@@ -84238,7 +84238,7 @@
         <v>2</v>
       </c>
       <c r="G3104" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3105">
@@ -84265,7 +84265,7 @@
         <v>2</v>
       </c>
       <c r="G3105" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3106">
@@ -84276,7 +84276,7 @@
         <v>9</v>
       </c>
       <c r="C3106" t="n">
-        <v>50.18</v>
+        <v>50.17</v>
       </c>
       <c r="D3106" t="inlineStr">
         <is>
@@ -84292,7 +84292,7 @@
         <v>2</v>
       </c>
       <c r="G3106" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3107">
@@ -84303,7 +84303,7 @@
         <v>10</v>
       </c>
       <c r="C3107" t="n">
-        <v>22.73</v>
+        <v>22.8</v>
       </c>
       <c r="D3107" t="inlineStr">
         <is>
@@ -84319,7 +84319,7 @@
         <v>2</v>
       </c>
       <c r="G3107" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3108">
@@ -84330,7 +84330,7 @@
         <v>11</v>
       </c>
       <c r="C3108" t="n">
-        <v>18.02</v>
+        <v>18.12</v>
       </c>
       <c r="D3108" t="inlineStr">
         <is>
@@ -84346,7 +84346,7 @@
         <v>2</v>
       </c>
       <c r="G3108" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3109">
@@ -84357,7 +84357,7 @@
         <v>12</v>
       </c>
       <c r="C3109" t="n">
-        <v>20.34</v>
+        <v>20.51</v>
       </c>
       <c r="D3109" t="inlineStr">
         <is>
@@ -84373,7 +84373,7 @@
         <v>2</v>
       </c>
       <c r="G3109" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3110">
@@ -84384,7 +84384,7 @@
         <v>13</v>
       </c>
       <c r="C3110" t="n">
-        <v>21.69</v>
+        <v>21.77</v>
       </c>
       <c r="D3110" t="inlineStr">
         <is>
@@ -84400,7 +84400,7 @@
         <v>2</v>
       </c>
       <c r="G3110" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3111">
@@ -84411,7 +84411,7 @@
         <v>14</v>
       </c>
       <c r="C3111" t="n">
-        <v>21.68</v>
+        <v>21.86</v>
       </c>
       <c r="D3111" t="inlineStr">
         <is>
@@ -84427,7 +84427,7 @@
         <v>2</v>
       </c>
       <c r="G3111" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3112">
@@ -84438,7 +84438,7 @@
         <v>15</v>
       </c>
       <c r="C3112" t="n">
-        <v>22.81</v>
+        <v>22.98</v>
       </c>
       <c r="D3112" t="inlineStr">
         <is>
@@ -84454,7 +84454,7 @@
         <v>2</v>
       </c>
       <c r="G3112" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3113">
@@ -84465,7 +84465,7 @@
         <v>16</v>
       </c>
       <c r="C3113" t="n">
-        <v>23.48</v>
+        <v>23.43</v>
       </c>
       <c r="D3113" t="inlineStr">
         <is>
@@ -84481,7 +84481,7 @@
         <v>2</v>
       </c>
       <c r="G3113" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3114">
@@ -84492,7 +84492,7 @@
         <v>17</v>
       </c>
       <c r="C3114" t="n">
-        <v>22.75</v>
+        <v>22.72</v>
       </c>
       <c r="D3114" t="inlineStr">
         <is>
@@ -84508,7 +84508,7 @@
         <v>2</v>
       </c>
       <c r="G3114" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3115">
@@ -84519,7 +84519,7 @@
         <v>18</v>
       </c>
       <c r="C3115" t="n">
-        <v>21.15</v>
+        <v>21.03</v>
       </c>
       <c r="D3115" t="inlineStr">
         <is>
@@ -84535,7 +84535,7 @@
         <v>2</v>
       </c>
       <c r="G3115" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3116">
@@ -84546,7 +84546,7 @@
         <v>19</v>
       </c>
       <c r="C3116" t="n">
-        <v>24.24</v>
+        <v>24.15</v>
       </c>
       <c r="D3116" t="inlineStr">
         <is>
@@ -84562,7 +84562,7 @@
         <v>2</v>
       </c>
       <c r="G3116" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3117">
@@ -84573,7 +84573,7 @@
         <v>20</v>
       </c>
       <c r="C3117" t="n">
-        <v>29.94</v>
+        <v>29.92</v>
       </c>
       <c r="D3117" t="inlineStr">
         <is>
@@ -84589,7 +84589,7 @@
         <v>2</v>
       </c>
       <c r="G3117" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3118">
@@ -84616,7 +84616,7 @@
         <v>2</v>
       </c>
       <c r="G3118" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3119">
@@ -84643,7 +84643,7 @@
         <v>2</v>
       </c>
       <c r="G3119" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3120">
@@ -84670,7 +84670,7 @@
         <v>2</v>
       </c>
       <c r="G3120" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3121">
@@ -84681,7 +84681,7 @@
         <v>24</v>
       </c>
       <c r="C3121" t="n">
-        <v>34.01</v>
+        <v>34.03</v>
       </c>
       <c r="D3121" t="inlineStr">
         <is>
@@ -84697,7 +84697,7 @@
         <v>2</v>
       </c>
       <c r="G3121" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3122">
@@ -84708,7 +84708,7 @@
         <v>1</v>
       </c>
       <c r="C3122" t="n">
-        <v>9.91</v>
+        <v>9.93</v>
       </c>
       <c r="D3122" t="inlineStr">
         <is>
@@ -84724,7 +84724,7 @@
         <v>2</v>
       </c>
       <c r="G3122" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3123">
@@ -84735,7 +84735,7 @@
         <v>2</v>
       </c>
       <c r="C3123" t="n">
-        <v>12.3</v>
+        <v>12.36</v>
       </c>
       <c r="D3123" t="inlineStr">
         <is>
@@ -84751,7 +84751,7 @@
         <v>2</v>
       </c>
       <c r="G3123" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3124">
@@ -84762,7 +84762,7 @@
         <v>3</v>
       </c>
       <c r="C3124" t="n">
-        <v>11.02</v>
+        <v>11.06</v>
       </c>
       <c r="D3124" t="inlineStr">
         <is>
@@ -84778,7 +84778,7 @@
         <v>2</v>
       </c>
       <c r="G3124" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3125">
@@ -84789,7 +84789,7 @@
         <v>4</v>
       </c>
       <c r="C3125" t="n">
-        <v>10.54</v>
+        <v>10.61</v>
       </c>
       <c r="D3125" t="inlineStr">
         <is>
@@ -84805,7 +84805,7 @@
         <v>2</v>
       </c>
       <c r="G3125" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3126">
@@ -84816,7 +84816,7 @@
         <v>5</v>
       </c>
       <c r="C3126" t="n">
-        <v>11.02</v>
+        <v>11.05</v>
       </c>
       <c r="D3126" t="inlineStr">
         <is>
@@ -84832,7 +84832,7 @@
         <v>2</v>
       </c>
       <c r="G3126" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3127">
@@ -84843,7 +84843,7 @@
         <v>6</v>
       </c>
       <c r="C3127" t="n">
-        <v>14</v>
+        <v>14.02</v>
       </c>
       <c r="D3127" t="inlineStr">
         <is>
@@ -84859,7 +84859,7 @@
         <v>2</v>
       </c>
       <c r="G3127" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3128">
@@ -84870,7 +84870,7 @@
         <v>7</v>
       </c>
       <c r="C3128" t="n">
-        <v>19.82</v>
+        <v>19.85</v>
       </c>
       <c r="D3128" t="inlineStr">
         <is>
@@ -84886,7 +84886,7 @@
         <v>2</v>
       </c>
       <c r="G3128" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3129">
@@ -84897,7 +84897,7 @@
         <v>8</v>
       </c>
       <c r="C3129" t="n">
-        <v>33.61</v>
+        <v>33.62</v>
       </c>
       <c r="D3129" t="inlineStr">
         <is>
@@ -84913,7 +84913,7 @@
         <v>2</v>
       </c>
       <c r="G3129" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3130">
@@ -84924,7 +84924,7 @@
         <v>9</v>
       </c>
       <c r="C3130" t="n">
-        <v>28.96</v>
+        <v>28.97</v>
       </c>
       <c r="D3130" t="inlineStr">
         <is>
@@ -84940,7 +84940,7 @@
         <v>2</v>
       </c>
       <c r="G3130" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3131">
@@ -84951,7 +84951,7 @@
         <v>10</v>
       </c>
       <c r="C3131" t="n">
-        <v>23.57</v>
+        <v>23.55</v>
       </c>
       <c r="D3131" t="inlineStr">
         <is>
@@ -84967,7 +84967,7 @@
         <v>2</v>
       </c>
       <c r="G3131" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3132">
@@ -84978,7 +84978,7 @@
         <v>11</v>
       </c>
       <c r="C3132" t="n">
-        <v>17.36</v>
+        <v>17.59</v>
       </c>
       <c r="D3132" t="inlineStr">
         <is>
@@ -84994,7 +84994,7 @@
         <v>2</v>
       </c>
       <c r="G3132" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3133">
@@ -85005,7 +85005,7 @@
         <v>12</v>
       </c>
       <c r="C3133" t="n">
-        <v>19.86</v>
+        <v>20.13</v>
       </c>
       <c r="D3133" t="inlineStr">
         <is>
@@ -85021,7 +85021,7 @@
         <v>2</v>
       </c>
       <c r="G3133" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3134">
@@ -85032,7 +85032,7 @@
         <v>13</v>
       </c>
       <c r="C3134" t="n">
-        <v>20.34</v>
+        <v>20.46</v>
       </c>
       <c r="D3134" t="inlineStr">
         <is>
@@ -85048,7 +85048,7 @@
         <v>2</v>
       </c>
       <c r="G3134" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3135">
@@ -85059,7 +85059,7 @@
         <v>14</v>
       </c>
       <c r="C3135" t="n">
-        <v>21.42</v>
+        <v>21.49</v>
       </c>
       <c r="D3135" t="inlineStr">
         <is>
@@ -85075,7 +85075,7 @@
         <v>2</v>
       </c>
       <c r="G3135" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3136">
@@ -85086,7 +85086,7 @@
         <v>15</v>
       </c>
       <c r="C3136" t="n">
-        <v>20.95</v>
+        <v>20.91</v>
       </c>
       <c r="D3136" t="inlineStr">
         <is>
@@ -85102,7 +85102,7 @@
         <v>2</v>
       </c>
       <c r="G3136" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3137">
@@ -85113,7 +85113,7 @@
         <v>16</v>
       </c>
       <c r="C3137" t="n">
-        <v>20</v>
+        <v>19.99</v>
       </c>
       <c r="D3137" t="inlineStr">
         <is>
@@ -85129,7 +85129,7 @@
         <v>2</v>
       </c>
       <c r="G3137" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3138">
@@ -85140,7 +85140,7 @@
         <v>17</v>
       </c>
       <c r="C3138" t="n">
-        <v>17.37</v>
+        <v>17.33</v>
       </c>
       <c r="D3138" t="inlineStr">
         <is>
@@ -85156,7 +85156,7 @@
         <v>2</v>
       </c>
       <c r="G3138" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3139">
@@ -85167,7 +85167,7 @@
         <v>18</v>
       </c>
       <c r="C3139" t="n">
-        <v>16.99</v>
+        <v>16.87</v>
       </c>
       <c r="D3139" t="inlineStr">
         <is>
@@ -85183,7 +85183,7 @@
         <v>2</v>
       </c>
       <c r="G3139" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3140">
@@ -85194,7 +85194,7 @@
         <v>19</v>
       </c>
       <c r="C3140" t="n">
-        <v>15.8</v>
+        <v>15.72</v>
       </c>
       <c r="D3140" t="inlineStr">
         <is>
@@ -85210,7 +85210,7 @@
         <v>2</v>
       </c>
       <c r="G3140" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3141">
@@ -85221,7 +85221,7 @@
         <v>20</v>
       </c>
       <c r="C3141" t="n">
-        <v>28.25</v>
+        <v>28.24</v>
       </c>
       <c r="D3141" t="inlineStr">
         <is>
@@ -85237,7 +85237,7 @@
         <v>2</v>
       </c>
       <c r="G3141" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3142">
@@ -85264,7 +85264,7 @@
         <v>2</v>
       </c>
       <c r="G3142" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3143">
@@ -85275,7 +85275,7 @@
         <v>22</v>
       </c>
       <c r="C3143" t="n">
-        <v>35.84</v>
+        <v>35.85</v>
       </c>
       <c r="D3143" t="inlineStr">
         <is>
@@ -85291,7 +85291,7 @@
         <v>2</v>
       </c>
       <c r="G3143" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3144">
@@ -85318,7 +85318,7 @@
         <v>2</v>
       </c>
       <c r="G3144" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3145">
@@ -85345,7 +85345,7 @@
         <v>2</v>
       </c>
       <c r="G3145" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3146">
@@ -85356,7 +85356,7 @@
         <v>1</v>
       </c>
       <c r="C3146" t="n">
-        <v>19.66</v>
+        <v>19.67</v>
       </c>
       <c r="D3146" t="inlineStr">
         <is>
@@ -85372,7 +85372,7 @@
         <v>2</v>
       </c>
       <c r="G3146" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3147">
@@ -85399,7 +85399,7 @@
         <v>2</v>
       </c>
       <c r="G3147" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3148">
@@ -85410,7 +85410,7 @@
         <v>3</v>
       </c>
       <c r="C3148" t="n">
-        <v>13.48</v>
+        <v>13.54</v>
       </c>
       <c r="D3148" t="inlineStr">
         <is>
@@ -85426,7 +85426,7 @@
         <v>2</v>
       </c>
       <c r="G3148" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3149">
@@ -85437,7 +85437,7 @@
         <v>4</v>
       </c>
       <c r="C3149" t="n">
-        <v>14.58</v>
+        <v>14.66</v>
       </c>
       <c r="D3149" t="inlineStr">
         <is>
@@ -85453,7 +85453,7 @@
         <v>2</v>
       </c>
       <c r="G3149" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3150">
@@ -85480,7 +85480,7 @@
         <v>2</v>
       </c>
       <c r="G3150" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3151">
@@ -85507,7 +85507,7 @@
         <v>2</v>
       </c>
       <c r="G3151" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3152">
@@ -85518,7 +85518,7 @@
         <v>7</v>
       </c>
       <c r="C3152" t="n">
-        <v>22.75</v>
+        <v>22.77</v>
       </c>
       <c r="D3152" t="inlineStr">
         <is>
@@ -85534,7 +85534,7 @@
         <v>2</v>
       </c>
       <c r="G3152" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3153">
@@ -85545,7 +85545,7 @@
         <v>8</v>
       </c>
       <c r="C3153" t="n">
-        <v>46.82</v>
+        <v>46.84</v>
       </c>
       <c r="D3153" t="inlineStr">
         <is>
@@ -85561,7 +85561,7 @@
         <v>2</v>
       </c>
       <c r="G3153" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3154">
@@ -85572,7 +85572,7 @@
         <v>9</v>
       </c>
       <c r="C3154" t="n">
-        <v>48.78</v>
+        <v>48.85</v>
       </c>
       <c r="D3154" t="inlineStr">
         <is>
@@ -85588,7 +85588,7 @@
         <v>2</v>
       </c>
       <c r="G3154" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3155">
@@ -85599,7 +85599,7 @@
         <v>10</v>
       </c>
       <c r="C3155" t="n">
-        <v>29.12</v>
+        <v>29.06</v>
       </c>
       <c r="D3155" t="inlineStr">
         <is>
@@ -85615,7 +85615,7 @@
         <v>2</v>
       </c>
       <c r="G3155" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3156">
@@ -85626,7 +85626,7 @@
         <v>11</v>
       </c>
       <c r="C3156" t="n">
-        <v>20.26</v>
+        <v>20.09</v>
       </c>
       <c r="D3156" t="inlineStr">
         <is>
@@ -85642,7 +85642,7 @@
         <v>2</v>
       </c>
       <c r="G3156" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3157">
@@ -85653,7 +85653,7 @@
         <v>12</v>
       </c>
       <c r="C3157" t="n">
-        <v>29.44</v>
+        <v>29.39</v>
       </c>
       <c r="D3157" t="inlineStr">
         <is>
@@ -85669,7 +85669,7 @@
         <v>2</v>
       </c>
       <c r="G3157" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3158">
@@ -85680,7 +85680,7 @@
         <v>13</v>
       </c>
       <c r="C3158" t="n">
-        <v>30.89</v>
+        <v>30.81</v>
       </c>
       <c r="D3158" t="inlineStr">
         <is>
@@ -85696,7 +85696,7 @@
         <v>2</v>
       </c>
       <c r="G3158" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3159">
@@ -85707,7 +85707,7 @@
         <v>14</v>
       </c>
       <c r="C3159" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="D3159" t="inlineStr">
         <is>
@@ -85723,7 +85723,7 @@
         <v>2</v>
       </c>
       <c r="G3159" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3160">
@@ -85734,7 +85734,7 @@
         <v>15</v>
       </c>
       <c r="C3160" t="n">
-        <v>32.17</v>
+        <v>32.12</v>
       </c>
       <c r="D3160" t="inlineStr">
         <is>
@@ -85750,7 +85750,7 @@
         <v>2</v>
       </c>
       <c r="G3160" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3161">
@@ -85761,7 +85761,7 @@
         <v>16</v>
       </c>
       <c r="C3161" t="n">
-        <v>31.26</v>
+        <v>31.2</v>
       </c>
       <c r="D3161" t="inlineStr">
         <is>
@@ -85777,7 +85777,7 @@
         <v>2</v>
       </c>
       <c r="G3161" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3162">
@@ -85788,7 +85788,7 @@
         <v>17</v>
       </c>
       <c r="C3162" t="n">
-        <v>31.37</v>
+        <v>31.32</v>
       </c>
       <c r="D3162" t="inlineStr">
         <is>
@@ -85804,7 +85804,7 @@
         <v>2</v>
       </c>
       <c r="G3162" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3163">
@@ -85815,7 +85815,7 @@
         <v>18</v>
       </c>
       <c r="C3163" t="n">
-        <v>34.95</v>
+        <v>34.85</v>
       </c>
       <c r="D3163" t="inlineStr">
         <is>
@@ -85831,7 +85831,7 @@
         <v>2</v>
       </c>
       <c r="G3163" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3164">
@@ -85842,7 +85842,7 @@
         <v>19</v>
       </c>
       <c r="C3164" t="n">
-        <v>32.32</v>
+        <v>32.31</v>
       </c>
       <c r="D3164" t="inlineStr">
         <is>
@@ -85858,7 +85858,7 @@
         <v>2</v>
       </c>
       <c r="G3164" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3165">
@@ -85869,7 +85869,7 @@
         <v>20</v>
       </c>
       <c r="C3165" t="n">
-        <v>32.27</v>
+        <v>32.37</v>
       </c>
       <c r="D3165" t="inlineStr">
         <is>
@@ -85885,7 +85885,7 @@
         <v>2</v>
       </c>
       <c r="G3165" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3166">
@@ -85896,7 +85896,7 @@
         <v>21</v>
       </c>
       <c r="C3166" t="n">
-        <v>36.99</v>
+        <v>37</v>
       </c>
       <c r="D3166" t="inlineStr">
         <is>
@@ -85912,7 +85912,7 @@
         <v>2</v>
       </c>
       <c r="G3166" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3167">
@@ -85923,7 +85923,7 @@
         <v>22</v>
       </c>
       <c r="C3167" t="n">
-        <v>37.66</v>
+        <v>37.67</v>
       </c>
       <c r="D3167" t="inlineStr">
         <is>
@@ -85939,7 +85939,7 @@
         <v>2</v>
       </c>
       <c r="G3167" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3168">
@@ -85950,7 +85950,7 @@
         <v>23</v>
       </c>
       <c r="C3168" t="n">
-        <v>37.09</v>
+        <v>37.08</v>
       </c>
       <c r="D3168" t="inlineStr">
         <is>
@@ -85966,7 +85966,7 @@
         <v>2</v>
       </c>
       <c r="G3168" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3169">
@@ -85977,7 +85977,7 @@
         <v>24</v>
       </c>
       <c r="C3169" t="n">
-        <v>37.13</v>
+        <v>37.12</v>
       </c>
       <c r="D3169" t="inlineStr">
         <is>
@@ -85993,7 +85993,7 @@
         <v>2</v>
       </c>
       <c r="G3169" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3170">
@@ -86004,7 +86004,7 @@
         <v>1</v>
       </c>
       <c r="C3170" t="n">
-        <v>20.07</v>
+        <v>20.06</v>
       </c>
       <c r="D3170" t="inlineStr">
         <is>
@@ -86020,7 +86020,7 @@
         <v>2</v>
       </c>
       <c r="G3170" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3171">
@@ -86031,7 +86031,7 @@
         <v>2</v>
       </c>
       <c r="C3171" t="n">
-        <v>15.34</v>
+        <v>15.38</v>
       </c>
       <c r="D3171" t="inlineStr">
         <is>
@@ -86047,7 +86047,7 @@
         <v>2</v>
       </c>
       <c r="G3171" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3172">
@@ -86074,7 +86074,7 @@
         <v>2</v>
       </c>
       <c r="G3172" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3173">
@@ -86101,7 +86101,7 @@
         <v>2</v>
       </c>
       <c r="G3173" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3174">
@@ -86112,7 +86112,7 @@
         <v>5</v>
       </c>
       <c r="C3174" t="n">
-        <v>13.63</v>
+        <v>13.64</v>
       </c>
       <c r="D3174" t="inlineStr">
         <is>
@@ -86128,7 +86128,7 @@
         <v>2</v>
       </c>
       <c r="G3174" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3175">
@@ -86139,7 +86139,7 @@
         <v>6</v>
       </c>
       <c r="C3175" t="n">
-        <v>13.07</v>
+        <v>13.12</v>
       </c>
       <c r="D3175" t="inlineStr">
         <is>
@@ -86155,7 +86155,7 @@
         <v>2</v>
       </c>
       <c r="G3175" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3176">
@@ -86182,7 +86182,7 @@
         <v>2</v>
       </c>
       <c r="G3176" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3177">
@@ -86209,7 +86209,7 @@
         <v>2</v>
       </c>
       <c r="G3177" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3178">
@@ -86220,7 +86220,7 @@
         <v>9</v>
       </c>
       <c r="C3178" t="n">
-        <v>42.04</v>
+        <v>42.03</v>
       </c>
       <c r="D3178" t="inlineStr">
         <is>
@@ -86236,7 +86236,7 @@
         <v>2</v>
       </c>
       <c r="G3178" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3179">
@@ -86247,7 +86247,7 @@
         <v>10</v>
       </c>
       <c r="C3179" t="n">
-        <v>19.8</v>
+        <v>19.94</v>
       </c>
       <c r="D3179" t="inlineStr">
         <is>
@@ -86263,7 +86263,7 @@
         <v>2</v>
       </c>
       <c r="G3179" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3180">
@@ -86274,7 +86274,7 @@
         <v>11</v>
       </c>
       <c r="C3180" t="n">
-        <v>13.09</v>
+        <v>13.82</v>
       </c>
       <c r="D3180" t="inlineStr">
         <is>
@@ -86290,7 +86290,7 @@
         <v>2</v>
       </c>
       <c r="G3180" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3181">
@@ -86301,7 +86301,7 @@
         <v>12</v>
       </c>
       <c r="C3181" t="n">
-        <v>29.18</v>
+        <v>29.13</v>
       </c>
       <c r="D3181" t="inlineStr">
         <is>
@@ -86317,7 +86317,7 @@
         <v>2</v>
       </c>
       <c r="G3181" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3182">
@@ -86328,7 +86328,7 @@
         <v>13</v>
       </c>
       <c r="C3182" t="n">
-        <v>30.62</v>
+        <v>30.51</v>
       </c>
       <c r="D3182" t="inlineStr">
         <is>
@@ -86344,7 +86344,7 @@
         <v>2</v>
       </c>
       <c r="G3182" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3183">
@@ -86355,7 +86355,7 @@
         <v>14</v>
       </c>
       <c r="C3183" t="n">
-        <v>28.9</v>
+        <v>28.89</v>
       </c>
       <c r="D3183" t="inlineStr">
         <is>
@@ -86371,7 +86371,7 @@
         <v>2</v>
       </c>
       <c r="G3183" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3184">
@@ -86382,7 +86382,7 @@
         <v>15</v>
       </c>
       <c r="C3184" t="n">
-        <v>32.02</v>
+        <v>31.91</v>
       </c>
       <c r="D3184" t="inlineStr">
         <is>
@@ -86398,7 +86398,7 @@
         <v>2</v>
       </c>
       <c r="G3184" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3185">
@@ -86409,7 +86409,7 @@
         <v>16</v>
       </c>
       <c r="C3185" t="n">
-        <v>33.01</v>
+        <v>32.89</v>
       </c>
       <c r="D3185" t="inlineStr">
         <is>
@@ -86425,7 +86425,7 @@
         <v>2</v>
       </c>
       <c r="G3185" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3186">
@@ -86436,7 +86436,7 @@
         <v>17</v>
       </c>
       <c r="C3186" t="n">
-        <v>31.73</v>
+        <v>31.78</v>
       </c>
       <c r="D3186" t="inlineStr">
         <is>
@@ -86452,7 +86452,7 @@
         <v>2</v>
       </c>
       <c r="G3186" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3187">
@@ -86463,7 +86463,7 @@
         <v>18</v>
       </c>
       <c r="C3187" t="n">
-        <v>27.16</v>
+        <v>27.1</v>
       </c>
       <c r="D3187" t="inlineStr">
         <is>
@@ -86479,7 +86479,7 @@
         <v>2</v>
       </c>
       <c r="G3187" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3188">
@@ -86490,7 +86490,7 @@
         <v>19</v>
       </c>
       <c r="C3188" t="n">
-        <v>21.98</v>
+        <v>22.03</v>
       </c>
       <c r="D3188" t="inlineStr">
         <is>
@@ -86506,7 +86506,7 @@
         <v>2</v>
       </c>
       <c r="G3188" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3189">
@@ -86517,7 +86517,7 @@
         <v>20</v>
       </c>
       <c r="C3189" t="n">
-        <v>16.9</v>
+        <v>17.12</v>
       </c>
       <c r="D3189" t="inlineStr">
         <is>
@@ -86533,7 +86533,7 @@
         <v>2</v>
       </c>
       <c r="G3189" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3190">
@@ -86560,7 +86560,7 @@
         <v>2</v>
       </c>
       <c r="G3190" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3191">
@@ -86587,7 +86587,7 @@
         <v>2</v>
       </c>
       <c r="G3191" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3192">
@@ -86598,7 +86598,7 @@
         <v>23</v>
       </c>
       <c r="C3192" t="n">
-        <v>27.66</v>
+        <v>27.68</v>
       </c>
       <c r="D3192" t="inlineStr">
         <is>
@@ -86614,7 +86614,7 @@
         <v>2</v>
       </c>
       <c r="G3192" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3193">
@@ -86641,7 +86641,7 @@
         <v>2</v>
       </c>
       <c r="G3193" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3194">
@@ -86652,7 +86652,7 @@
         <v>1</v>
       </c>
       <c r="C3194" t="n">
-        <v>8.619999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D3194" t="inlineStr">
         <is>
@@ -86668,7 +86668,7 @@
         <v>2</v>
       </c>
       <c r="G3194" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3195">
@@ -86695,7 +86695,7 @@
         <v>2</v>
       </c>
       <c r="G3195" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3196">
@@ -86722,7 +86722,7 @@
         <v>2</v>
       </c>
       <c r="G3196" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3197">
@@ -86733,7 +86733,7 @@
         <v>4</v>
       </c>
       <c r="C3197" t="n">
-        <v>10.11</v>
+        <v>10.13</v>
       </c>
       <c r="D3197" t="inlineStr">
         <is>
@@ -86749,7 +86749,7 @@
         <v>2</v>
       </c>
       <c r="G3197" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3198">
@@ -86760,7 +86760,7 @@
         <v>5</v>
       </c>
       <c r="C3198" t="n">
-        <v>9.800000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="D3198" t="inlineStr">
         <is>
@@ -86776,7 +86776,7 @@
         <v>2</v>
       </c>
       <c r="G3198" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3199">
@@ -86787,7 +86787,7 @@
         <v>6</v>
       </c>
       <c r="C3199" t="n">
-        <v>11.73</v>
+        <v>11.76</v>
       </c>
       <c r="D3199" t="inlineStr">
         <is>
@@ -86803,7 +86803,7 @@
         <v>2</v>
       </c>
       <c r="G3199" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3200">
@@ -86814,7 +86814,7 @@
         <v>7</v>
       </c>
       <c r="C3200" t="n">
-        <v>22.02</v>
+        <v>22.04</v>
       </c>
       <c r="D3200" t="inlineStr">
         <is>
@@ -86830,7 +86830,7 @@
         <v>2</v>
       </c>
       <c r="G3200" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3201">
@@ -86841,7 +86841,7 @@
         <v>8</v>
       </c>
       <c r="C3201" t="n">
-        <v>35.51</v>
+        <v>35.69</v>
       </c>
       <c r="D3201" t="inlineStr">
         <is>
@@ -86857,7 +86857,7 @@
         <v>2</v>
       </c>
       <c r="G3201" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3202">
@@ -86868,7 +86868,7 @@
         <v>9</v>
       </c>
       <c r="C3202" t="n">
-        <v>35.46</v>
+        <v>35.49</v>
       </c>
       <c r="D3202" t="inlineStr">
         <is>
@@ -86884,7 +86884,7 @@
         <v>2</v>
       </c>
       <c r="G3202" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3203">
@@ -86895,7 +86895,7 @@
         <v>10</v>
       </c>
       <c r="C3203" t="n">
-        <v>23.35</v>
+        <v>23.46</v>
       </c>
       <c r="D3203" t="inlineStr">
         <is>
@@ -86911,7 +86911,7 @@
         <v>2</v>
       </c>
       <c r="G3203" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3204">
@@ -86922,7 +86922,7 @@
         <v>11</v>
       </c>
       <c r="C3204" t="n">
-        <v>29.16</v>
+        <v>29.14</v>
       </c>
       <c r="D3204" t="inlineStr">
         <is>
@@ -86938,7 +86938,7 @@
         <v>2</v>
       </c>
       <c r="G3204" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3205">
@@ -86949,7 +86949,7 @@
         <v>12</v>
       </c>
       <c r="C3205" t="n">
-        <v>43.04</v>
+        <v>42.96</v>
       </c>
       <c r="D3205" t="inlineStr">
         <is>
@@ -86965,7 +86965,7 @@
         <v>2</v>
       </c>
       <c r="G3205" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3206">
@@ -86976,7 +86976,7 @@
         <v>13</v>
       </c>
       <c r="C3206" t="n">
-        <v>46.86</v>
+        <v>46.81</v>
       </c>
       <c r="D3206" t="inlineStr">
         <is>
@@ -86992,7 +86992,7 @@
         <v>2</v>
       </c>
       <c r="G3206" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3207">
@@ -87003,7 +87003,7 @@
         <v>14</v>
       </c>
       <c r="C3207" t="n">
-        <v>50.83</v>
+        <v>50.85</v>
       </c>
       <c r="D3207" t="inlineStr">
         <is>
@@ -87019,7 +87019,7 @@
         <v>2</v>
       </c>
       <c r="G3207" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3208">
@@ -87030,7 +87030,7 @@
         <v>15</v>
       </c>
       <c r="C3208" t="n">
-        <v>49.23</v>
+        <v>49.19</v>
       </c>
       <c r="D3208" t="inlineStr">
         <is>
@@ -87046,7 +87046,7 @@
         <v>2</v>
       </c>
       <c r="G3208" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3209">
@@ -87057,7 +87057,7 @@
         <v>16</v>
       </c>
       <c r="C3209" t="n">
-        <v>50.79</v>
+        <v>50.71</v>
       </c>
       <c r="D3209" t="inlineStr">
         <is>
@@ -87073,7 +87073,7 @@
         <v>2</v>
       </c>
       <c r="G3209" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3210">
@@ -87084,7 +87084,7 @@
         <v>17</v>
       </c>
       <c r="C3210" t="n">
-        <v>47.55</v>
+        <v>47.48</v>
       </c>
       <c r="D3210" t="inlineStr">
         <is>
@@ -87100,7 +87100,7 @@
         <v>2</v>
       </c>
       <c r="G3210" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3211">
@@ -87111,7 +87111,7 @@
         <v>18</v>
       </c>
       <c r="C3211" t="n">
-        <v>41.25</v>
+        <v>41.16</v>
       </c>
       <c r="D3211" t="inlineStr">
         <is>
@@ -87127,7 +87127,7 @@
         <v>2</v>
       </c>
       <c r="G3211" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3212">
@@ -87138,7 +87138,7 @@
         <v>19</v>
       </c>
       <c r="C3212" t="n">
-        <v>28.52</v>
+        <v>28.61</v>
       </c>
       <c r="D3212" t="inlineStr">
         <is>
@@ -87154,7 +87154,7 @@
         <v>2</v>
       </c>
       <c r="G3212" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3213">
@@ -87165,7 +87165,7 @@
         <v>20</v>
       </c>
       <c r="C3213" t="n">
-        <v>22.47</v>
+        <v>22.63</v>
       </c>
       <c r="D3213" t="inlineStr">
         <is>
@@ -87181,7 +87181,7 @@
         <v>2</v>
       </c>
       <c r="G3213" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3214">
@@ -87192,7 +87192,7 @@
         <v>21</v>
       </c>
       <c r="C3214" t="n">
-        <v>33.56</v>
+        <v>33.53</v>
       </c>
       <c r="D3214" t="inlineStr">
         <is>
@@ -87208,7 +87208,7 @@
         <v>2</v>
       </c>
       <c r="G3214" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3215">
@@ -87219,7 +87219,7 @@
         <v>22</v>
       </c>
       <c r="C3215" t="n">
-        <v>37.7</v>
+        <v>37.69</v>
       </c>
       <c r="D3215" t="inlineStr">
         <is>
@@ -87235,7 +87235,7 @@
         <v>2</v>
       </c>
       <c r="G3215" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3216">
@@ -87246,7 +87246,7 @@
         <v>23</v>
       </c>
       <c r="C3216" t="n">
-        <v>37.45</v>
+        <v>37.44</v>
       </c>
       <c r="D3216" t="inlineStr">
         <is>
@@ -87262,7 +87262,7 @@
         <v>2</v>
       </c>
       <c r="G3216" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3217">
@@ -87273,7 +87273,7 @@
         <v>24</v>
       </c>
       <c r="C3217" t="n">
-        <v>29.31</v>
+        <v>29.3</v>
       </c>
       <c r="D3217" t="inlineStr">
         <is>
@@ -87289,7 +87289,7 @@
         <v>2</v>
       </c>
       <c r="G3217" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3218">
@@ -87300,7 +87300,7 @@
         <v>1</v>
       </c>
       <c r="C3218" t="n">
-        <v>10.74</v>
+        <v>10.77</v>
       </c>
       <c r="D3218" t="inlineStr">
         <is>
@@ -87316,7 +87316,7 @@
         <v>2</v>
       </c>
       <c r="G3218" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3219">
@@ -87327,7 +87327,7 @@
         <v>2</v>
       </c>
       <c r="C3219" t="n">
-        <v>9.93</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="D3219" t="inlineStr">
         <is>
@@ -87343,7 +87343,7 @@
         <v>2</v>
       </c>
       <c r="G3219" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3220">
@@ -87354,7 +87354,7 @@
         <v>3</v>
       </c>
       <c r="C3220" t="n">
-        <v>6.54</v>
+        <v>6.55</v>
       </c>
       <c r="D3220" t="inlineStr">
         <is>
@@ -87370,7 +87370,7 @@
         <v>2</v>
       </c>
       <c r="G3220" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3221">
@@ -87381,7 +87381,7 @@
         <v>4</v>
       </c>
       <c r="C3221" t="n">
-        <v>7.12</v>
+        <v>7.11</v>
       </c>
       <c r="D3221" t="inlineStr">
         <is>
@@ -87397,7 +87397,7 @@
         <v>2</v>
       </c>
       <c r="G3221" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3222">
@@ -87408,7 +87408,7 @@
         <v>5</v>
       </c>
       <c r="C3222" t="n">
-        <v>8.15</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="D3222" t="inlineStr">
         <is>
@@ -87424,7 +87424,7 @@
         <v>2</v>
       </c>
       <c r="G3222" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3223">
@@ -87435,7 +87435,7 @@
         <v>6</v>
       </c>
       <c r="C3223" t="n">
-        <v>8.970000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="D3223" t="inlineStr">
         <is>
@@ -87451,7 +87451,7 @@
         <v>2</v>
       </c>
       <c r="G3223" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3224">
@@ -87478,7 +87478,7 @@
         <v>2</v>
       </c>
       <c r="G3224" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3225">
@@ -87489,7 +87489,7 @@
         <v>8</v>
       </c>
       <c r="C3225" t="n">
-        <v>31.83</v>
+        <v>31.84</v>
       </c>
       <c r="D3225" t="inlineStr">
         <is>
@@ -87505,7 +87505,7 @@
         <v>2</v>
       </c>
       <c r="G3225" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3226">
@@ -87516,7 +87516,7 @@
         <v>9</v>
       </c>
       <c r="C3226" t="n">
-        <v>30.01</v>
+        <v>30.1</v>
       </c>
       <c r="D3226" t="inlineStr">
         <is>
@@ -87532,7 +87532,7 @@
         <v>2</v>
       </c>
       <c r="G3226" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3227">
@@ -87543,7 +87543,7 @@
         <v>10</v>
       </c>
       <c r="C3227" t="n">
-        <v>23.21</v>
+        <v>23.22</v>
       </c>
       <c r="D3227" t="inlineStr">
         <is>
@@ -87559,7 +87559,7 @@
         <v>2</v>
       </c>
       <c r="G3227" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3228">
@@ -87570,7 +87570,7 @@
         <v>11</v>
       </c>
       <c r="C3228" t="n">
-        <v>27.3</v>
+        <v>27.28</v>
       </c>
       <c r="D3228" t="inlineStr">
         <is>
@@ -87586,7 +87586,7 @@
         <v>2</v>
       </c>
       <c r="G3228" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3229">
@@ -87597,7 +87597,7 @@
         <v>12</v>
       </c>
       <c r="C3229" t="n">
-        <v>29.72</v>
+        <v>29.69</v>
       </c>
       <c r="D3229" t="inlineStr">
         <is>
@@ -87613,7 +87613,7 @@
         <v>2</v>
       </c>
       <c r="G3229" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3230">
@@ -87640,7 +87640,7 @@
         <v>2</v>
       </c>
       <c r="G3230" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3231">
@@ -87651,7 +87651,7 @@
         <v>14</v>
       </c>
       <c r="C3231" t="n">
-        <v>35.3</v>
+        <v>35.27</v>
       </c>
       <c r="D3231" t="inlineStr">
         <is>
@@ -87667,7 +87667,7 @@
         <v>2</v>
       </c>
       <c r="G3231" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3232">
@@ -87678,7 +87678,7 @@
         <v>15</v>
       </c>
       <c r="C3232" t="n">
-        <v>34.36</v>
+        <v>34.33</v>
       </c>
       <c r="D3232" t="inlineStr">
         <is>
@@ -87694,7 +87694,7 @@
         <v>2</v>
       </c>
       <c r="G3232" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3233">
@@ -87705,7 +87705,7 @@
         <v>16</v>
       </c>
       <c r="C3233" t="n">
-        <v>35.69</v>
+        <v>35.66</v>
       </c>
       <c r="D3233" t="inlineStr">
         <is>
@@ -87721,7 +87721,7 @@
         <v>2</v>
       </c>
       <c r="G3233" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3234">
@@ -87732,7 +87732,7 @@
         <v>17</v>
       </c>
       <c r="C3234" t="n">
-        <v>36.45</v>
+        <v>36.4</v>
       </c>
       <c r="D3234" t="inlineStr">
         <is>
@@ -87748,7 +87748,7 @@
         <v>2</v>
       </c>
       <c r="G3234" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3235">
@@ -87759,7 +87759,7 @@
         <v>18</v>
       </c>
       <c r="C3235" t="n">
-        <v>34.09</v>
+        <v>33.97</v>
       </c>
       <c r="D3235" t="inlineStr">
         <is>
@@ -87775,7 +87775,7 @@
         <v>2</v>
       </c>
       <c r="G3235" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3236">
@@ -87786,7 +87786,7 @@
         <v>19</v>
       </c>
       <c r="C3236" t="n">
-        <v>25.25</v>
+        <v>25.44</v>
       </c>
       <c r="D3236" t="inlineStr">
         <is>
@@ -87802,7 +87802,7 @@
         <v>2</v>
       </c>
       <c r="G3236" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3237">
@@ -87829,7 +87829,7 @@
         <v>2</v>
       </c>
       <c r="G3237" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3238">
@@ -87840,7 +87840,7 @@
         <v>21</v>
       </c>
       <c r="C3238" t="n">
-        <v>31.18</v>
+        <v>31.16</v>
       </c>
       <c r="D3238" t="inlineStr">
         <is>
@@ -87856,7 +87856,7 @@
         <v>2</v>
       </c>
       <c r="G3238" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3239">
@@ -87867,7 +87867,7 @@
         <v>22</v>
       </c>
       <c r="C3239" t="n">
-        <v>32.73</v>
+        <v>32.72</v>
       </c>
       <c r="D3239" t="inlineStr">
         <is>
@@ -87883,7 +87883,7 @@
         <v>2</v>
       </c>
       <c r="G3239" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3240">
@@ -87910,7 +87910,7 @@
         <v>2</v>
       </c>
       <c r="G3240" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3241">
@@ -87921,7 +87921,7 @@
         <v>24</v>
       </c>
       <c r="C3241" t="n">
-        <v>22.67</v>
+        <v>22.7</v>
       </c>
       <c r="D3241" t="inlineStr">
         <is>
@@ -87937,7 +87937,7 @@
         <v>2</v>
       </c>
       <c r="G3241" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3242">
@@ -87964,7 +87964,7 @@
         <v>2</v>
       </c>
       <c r="G3242" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3243">
@@ -87975,7 +87975,7 @@
         <v>2</v>
       </c>
       <c r="C3243" t="n">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="D3243" t="inlineStr">
         <is>
@@ -87991,7 +87991,7 @@
         <v>2</v>
       </c>
       <c r="G3243" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3244">
@@ -88002,7 +88002,7 @@
         <v>3</v>
       </c>
       <c r="C3244" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="D3244" t="inlineStr">
         <is>
@@ -88018,7 +88018,7 @@
         <v>2</v>
       </c>
       <c r="G3244" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3245">
@@ -88029,7 +88029,7 @@
         <v>4</v>
       </c>
       <c r="C3245" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="D3245" t="inlineStr">
         <is>
@@ -88045,7 +88045,7 @@
         <v>2</v>
       </c>
       <c r="G3245" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3246">
@@ -88056,7 +88056,7 @@
         <v>5</v>
       </c>
       <c r="C3246" t="n">
-        <v>11.4</v>
+        <v>11.41</v>
       </c>
       <c r="D3246" t="inlineStr">
         <is>
@@ -88072,7 +88072,7 @@
         <v>2</v>
       </c>
       <c r="G3246" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3247">
@@ -88083,7 +88083,7 @@
         <v>6</v>
       </c>
       <c r="C3247" t="n">
-        <v>9.44</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="D3247" t="inlineStr">
         <is>
@@ -88099,7 +88099,7 @@
         <v>2</v>
       </c>
       <c r="G3247" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3248">
@@ -88110,7 +88110,7 @@
         <v>7</v>
       </c>
       <c r="C3248" t="n">
-        <v>6.08</v>
+        <v>6.04</v>
       </c>
       <c r="D3248" t="inlineStr">
         <is>
@@ -88126,7 +88126,7 @@
         <v>2</v>
       </c>
       <c r="G3248" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3249">
@@ -88137,7 +88137,7 @@
         <v>8</v>
       </c>
       <c r="C3249" t="n">
-        <v>27.97</v>
+        <v>27.82</v>
       </c>
       <c r="D3249" t="inlineStr">
         <is>
@@ -88153,7 +88153,7 @@
         <v>2</v>
       </c>
       <c r="G3249" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3250">
@@ -88164,7 +88164,7 @@
         <v>9</v>
       </c>
       <c r="C3250" t="n">
-        <v>27.24</v>
+        <v>27.14</v>
       </c>
       <c r="D3250" t="inlineStr">
         <is>
@@ -88180,7 +88180,7 @@
         <v>2</v>
       </c>
       <c r="G3250" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3251">
@@ -88191,7 +88191,7 @@
         <v>10</v>
       </c>
       <c r="C3251" t="n">
-        <v>25.46</v>
+        <v>25.37</v>
       </c>
       <c r="D3251" t="inlineStr">
         <is>
@@ -88207,7 +88207,7 @@
         <v>2</v>
       </c>
       <c r="G3251" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3252">
@@ -88218,7 +88218,7 @@
         <v>11</v>
       </c>
       <c r="C3252" t="n">
-        <v>22.79</v>
+        <v>22.71</v>
       </c>
       <c r="D3252" t="inlineStr">
         <is>
@@ -88234,7 +88234,7 @@
         <v>2</v>
       </c>
       <c r="G3252" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3253">
@@ -88245,7 +88245,7 @@
         <v>12</v>
       </c>
       <c r="C3253" t="n">
-        <v>22.81</v>
+        <v>22.76</v>
       </c>
       <c r="D3253" t="inlineStr">
         <is>
@@ -88261,7 +88261,7 @@
         <v>2</v>
       </c>
       <c r="G3253" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3254">
@@ -88272,7 +88272,7 @@
         <v>13</v>
       </c>
       <c r="C3254" t="n">
-        <v>40.34</v>
+        <v>40.1</v>
       </c>
       <c r="D3254" t="inlineStr">
         <is>
@@ -88288,7 +88288,7 @@
         <v>2</v>
       </c>
       <c r="G3254" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3255">
@@ -88299,7 +88299,7 @@
         <v>14</v>
       </c>
       <c r="C3255" t="n">
-        <v>38.86</v>
+        <v>38.64</v>
       </c>
       <c r="D3255" t="inlineStr">
         <is>
@@ -88315,7 +88315,7 @@
         <v>2</v>
       </c>
       <c r="G3255" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3256">
@@ -88326,7 +88326,7 @@
         <v>15</v>
       </c>
       <c r="C3256" t="n">
-        <v>34.24</v>
+        <v>34.02</v>
       </c>
       <c r="D3256" t="inlineStr">
         <is>
@@ -88342,7 +88342,7 @@
         <v>2</v>
       </c>
       <c r="G3256" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3257">
@@ -88353,7 +88353,7 @@
         <v>16</v>
       </c>
       <c r="C3257" t="n">
-        <v>35.19</v>
+        <v>34.94</v>
       </c>
       <c r="D3257" t="inlineStr">
         <is>
@@ -88369,7 +88369,7 @@
         <v>2</v>
       </c>
       <c r="G3257" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3258">
@@ -88380,7 +88380,7 @@
         <v>17</v>
       </c>
       <c r="C3258" t="n">
-        <v>31.45</v>
+        <v>31.37</v>
       </c>
       <c r="D3258" t="inlineStr">
         <is>
@@ -88396,7 +88396,7 @@
         <v>2</v>
       </c>
       <c r="G3258" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3259">
@@ -88407,7 +88407,7 @@
         <v>18</v>
       </c>
       <c r="C3259" t="n">
-        <v>29.95</v>
+        <v>29.81</v>
       </c>
       <c r="D3259" t="inlineStr">
         <is>
@@ -88423,7 +88423,7 @@
         <v>2</v>
       </c>
       <c r="G3259" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3260">
@@ -88434,7 +88434,7 @@
         <v>19</v>
       </c>
       <c r="C3260" t="n">
-        <v>19.03</v>
+        <v>19.42</v>
       </c>
       <c r="D3260" t="inlineStr">
         <is>
@@ -88450,7 +88450,7 @@
         <v>2</v>
       </c>
       <c r="G3260" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3261">
@@ -88461,7 +88461,7 @@
         <v>20</v>
       </c>
       <c r="C3261" t="n">
-        <v>18.43</v>
+        <v>18.72</v>
       </c>
       <c r="D3261" t="inlineStr">
         <is>
@@ -88477,7 +88477,7 @@
         <v>2</v>
       </c>
       <c r="G3261" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3262">
@@ -88488,7 +88488,7 @@
         <v>21</v>
       </c>
       <c r="C3262" t="n">
-        <v>37.16</v>
+        <v>37.14</v>
       </c>
       <c r="D3262" t="inlineStr">
         <is>
@@ -88504,7 +88504,7 @@
         <v>2</v>
       </c>
       <c r="G3262" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3263">
@@ -88515,7 +88515,7 @@
         <v>22</v>
       </c>
       <c r="C3263" t="n">
-        <v>39.22</v>
+        <v>39.14</v>
       </c>
       <c r="D3263" t="inlineStr">
         <is>
@@ -88531,7 +88531,7 @@
         <v>2</v>
       </c>
       <c r="G3263" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3264">
@@ -88542,7 +88542,7 @@
         <v>23</v>
       </c>
       <c r="C3264" t="n">
-        <v>24.29</v>
+        <v>24.25</v>
       </c>
       <c r="D3264" t="inlineStr">
         <is>
@@ -88558,7 +88558,7 @@
         <v>2</v>
       </c>
       <c r="G3264" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3265">
@@ -88569,7 +88569,7 @@
         <v>24</v>
       </c>
       <c r="C3265" t="n">
-        <v>24.98</v>
+        <v>24.94</v>
       </c>
       <c r="D3265" t="inlineStr">
         <is>
@@ -88585,7 +88585,7 @@
         <v>2</v>
       </c>
       <c r="G3265" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3266">
@@ -88596,7 +88596,7 @@
         <v>1</v>
       </c>
       <c r="C3266" t="n">
-        <v>12.2</v>
+        <v>11.94</v>
       </c>
       <c r="D3266" t="inlineStr">
         <is>
@@ -88612,7 +88612,7 @@
         <v>2</v>
       </c>
       <c r="G3266" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3267">
@@ -88623,7 +88623,7 @@
         <v>2</v>
       </c>
       <c r="C3267" t="n">
-        <v>7.47</v>
+        <v>7.6</v>
       </c>
       <c r="D3267" t="inlineStr">
         <is>
@@ -88639,7 +88639,7 @@
         <v>2</v>
       </c>
       <c r="G3267" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3268">
@@ -88650,7 +88650,7 @@
         <v>3</v>
       </c>
       <c r="C3268" t="n">
-        <v>8.18</v>
+        <v>8.25</v>
       </c>
       <c r="D3268" t="inlineStr">
         <is>
@@ -88666,7 +88666,7 @@
         <v>2</v>
       </c>
       <c r="G3268" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3269">
@@ -88677,7 +88677,7 @@
         <v>4</v>
       </c>
       <c r="C3269" t="n">
-        <v>7.27</v>
+        <v>7.46</v>
       </c>
       <c r="D3269" t="inlineStr">
         <is>
@@ -88693,7 +88693,7 @@
         <v>2</v>
       </c>
       <c r="G3269" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3270">
@@ -88704,7 +88704,7 @@
         <v>5</v>
       </c>
       <c r="C3270" t="n">
-        <v>9.09</v>
+        <v>9.24</v>
       </c>
       <c r="D3270" t="inlineStr">
         <is>
@@ -88720,7 +88720,7 @@
         <v>2</v>
       </c>
       <c r="G3270" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3271">
@@ -88731,7 +88731,7 @@
         <v>6</v>
       </c>
       <c r="C3271" t="n">
-        <v>11.35</v>
+        <v>12.03</v>
       </c>
       <c r="D3271" t="inlineStr">
         <is>
@@ -88747,7 +88747,7 @@
         <v>2</v>
       </c>
       <c r="G3271" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3272">
@@ -88758,7 +88758,7 @@
         <v>7</v>
       </c>
       <c r="C3272" t="n">
-        <v>20.4</v>
+        <v>21.71</v>
       </c>
       <c r="D3272" t="inlineStr">
         <is>
@@ -88774,7 +88774,7 @@
         <v>2</v>
       </c>
       <c r="G3272" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3273">
@@ -88785,7 +88785,7 @@
         <v>8</v>
       </c>
       <c r="C3273" t="n">
-        <v>44.91</v>
+        <v>50.2</v>
       </c>
       <c r="D3273" t="inlineStr">
         <is>
@@ -88801,7 +88801,7 @@
         <v>2</v>
       </c>
       <c r="G3273" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3274">
@@ -88812,7 +88812,7 @@
         <v>9</v>
       </c>
       <c r="C3274" t="n">
-        <v>39.79</v>
+        <v>45.02</v>
       </c>
       <c r="D3274" t="inlineStr">
         <is>
@@ -88828,7 +88828,7 @@
         <v>2</v>
       </c>
       <c r="G3274" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3275">
@@ -88839,7 +88839,7 @@
         <v>10</v>
       </c>
       <c r="C3275" t="n">
-        <v>20.53</v>
+        <v>19.73</v>
       </c>
       <c r="D3275" t="inlineStr">
         <is>
@@ -88855,7 +88855,7 @@
         <v>2</v>
       </c>
       <c r="G3275" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3276">
@@ -88866,7 +88866,7 @@
         <v>11</v>
       </c>
       <c r="C3276" t="n">
-        <v>26.28</v>
+        <v>25.19</v>
       </c>
       <c r="D3276" t="inlineStr">
         <is>
@@ -88882,7 +88882,7 @@
         <v>2</v>
       </c>
       <c r="G3276" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3277">
@@ -88893,7 +88893,7 @@
         <v>12</v>
       </c>
       <c r="C3277" t="n">
-        <v>31.38</v>
+        <v>30.68</v>
       </c>
       <c r="D3277" t="inlineStr">
         <is>
@@ -88909,7 +88909,7 @@
         <v>2</v>
       </c>
       <c r="G3277" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3278">
@@ -88920,7 +88920,7 @@
         <v>13</v>
       </c>
       <c r="C3278" t="n">
-        <v>35.89</v>
+        <v>34.71</v>
       </c>
       <c r="D3278" t="inlineStr">
         <is>
@@ -88936,7 +88936,7 @@
         <v>2</v>
       </c>
       <c r="G3278" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3279">
@@ -88947,7 +88947,7 @@
         <v>14</v>
       </c>
       <c r="C3279" t="n">
-        <v>40.99</v>
+        <v>38.99</v>
       </c>
       <c r="D3279" t="inlineStr">
         <is>
@@ -88963,7 +88963,7 @@
         <v>2</v>
       </c>
       <c r="G3279" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3280">
@@ -88974,7 +88974,7 @@
         <v>15</v>
       </c>
       <c r="C3280" t="n">
-        <v>40.24</v>
+        <v>38.16</v>
       </c>
       <c r="D3280" t="inlineStr">
         <is>
@@ -88990,7 +88990,7 @@
         <v>2</v>
       </c>
       <c r="G3280" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3281">
@@ -89001,7 +89001,7 @@
         <v>16</v>
       </c>
       <c r="C3281" t="n">
-        <v>41.22</v>
+        <v>39.05</v>
       </c>
       <c r="D3281" t="inlineStr">
         <is>
@@ -89017,7 +89017,7 @@
         <v>2</v>
       </c>
       <c r="G3281" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3282">
@@ -89028,7 +89028,7 @@
         <v>17</v>
       </c>
       <c r="C3282" t="n">
-        <v>38.6</v>
+        <v>36.62</v>
       </c>
       <c r="D3282" t="inlineStr">
         <is>
@@ -89044,7 +89044,7 @@
         <v>2</v>
       </c>
       <c r="G3282" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3283">
@@ -89055,7 +89055,7 @@
         <v>18</v>
       </c>
       <c r="C3283" t="n">
-        <v>31.96</v>
+        <v>31</v>
       </c>
       <c r="D3283" t="inlineStr">
         <is>
@@ -89071,7 +89071,7 @@
         <v>2</v>
       </c>
       <c r="G3283" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3284">
@@ -89082,7 +89082,7 @@
         <v>19</v>
       </c>
       <c r="C3284" t="n">
-        <v>15.37</v>
+        <v>15.79</v>
       </c>
       <c r="D3284" t="inlineStr">
         <is>
@@ -89098,7 +89098,7 @@
         <v>2</v>
       </c>
       <c r="G3284" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3285">
@@ -89109,7 +89109,7 @@
         <v>20</v>
       </c>
       <c r="C3285" t="n">
-        <v>15.85</v>
+        <v>19.55</v>
       </c>
       <c r="D3285" t="inlineStr">
         <is>
@@ -89125,7 +89125,7 @@
         <v>2</v>
       </c>
       <c r="G3285" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3286">
@@ -89136,7 +89136,7 @@
         <v>21</v>
       </c>
       <c r="C3286" t="n">
-        <v>33.38</v>
+        <v>41.78</v>
       </c>
       <c r="D3286" t="inlineStr">
         <is>
@@ -89152,7 +89152,7 @@
         <v>2</v>
       </c>
       <c r="G3286" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3287">
@@ -89163,7 +89163,7 @@
         <v>22</v>
       </c>
       <c r="C3287" t="n">
-        <v>34.13</v>
+        <v>42.32</v>
       </c>
       <c r="D3287" t="inlineStr">
         <is>
@@ -89179,7 +89179,7 @@
         <v>2</v>
       </c>
       <c r="G3287" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3288">
@@ -89190,7 +89190,7 @@
         <v>23</v>
       </c>
       <c r="C3288" t="n">
-        <v>39.34</v>
+        <v>48.36</v>
       </c>
       <c r="D3288" t="inlineStr">
         <is>
@@ -89206,7 +89206,7 @@
         <v>2</v>
       </c>
       <c r="G3288" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3289">
@@ -89217,7 +89217,7 @@
         <v>24</v>
       </c>
       <c r="C3289" t="n">
-        <v>23.81</v>
+        <v>25.59</v>
       </c>
       <c r="D3289" t="inlineStr">
         <is>
@@ -89233,7 +89233,7 @@
         <v>2</v>
       </c>
       <c r="G3289" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3290">
@@ -89244,7 +89244,7 @@
         <v>1</v>
       </c>
       <c r="C3290" t="n">
-        <v>8.34</v>
+        <v>6.18</v>
       </c>
       <c r="D3290" t="inlineStr">
         <is>
@@ -89260,7 +89260,7 @@
         <v>2</v>
       </c>
       <c r="G3290" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3291">
@@ -89271,7 +89271,7 @@
         <v>2</v>
       </c>
       <c r="C3291" t="n">
-        <v>8.800000000000001</v>
+        <v>5.34</v>
       </c>
       <c r="D3291" t="inlineStr">
         <is>
@@ -89287,7 +89287,7 @@
         <v>2</v>
       </c>
       <c r="G3291" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3292">
@@ -89298,7 +89298,7 @@
         <v>3</v>
       </c>
       <c r="C3292" t="n">
-        <v>10.02</v>
+        <v>7.07</v>
       </c>
       <c r="D3292" t="inlineStr">
         <is>
@@ -89314,7 +89314,7 @@
         <v>2</v>
       </c>
       <c r="G3292" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3293">
@@ -89325,7 +89325,7 @@
         <v>4</v>
       </c>
       <c r="C3293" t="n">
-        <v>10.39</v>
+        <v>5.69</v>
       </c>
       <c r="D3293" t="inlineStr">
         <is>
@@ -89341,7 +89341,7 @@
         <v>2</v>
       </c>
       <c r="G3293" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3294">
@@ -89352,7 +89352,7 @@
         <v>5</v>
       </c>
       <c r="C3294" t="n">
-        <v>10.65</v>
+        <v>9.06</v>
       </c>
       <c r="D3294" t="inlineStr">
         <is>
@@ -89368,7 +89368,7 @@
         <v>2</v>
       </c>
       <c r="G3294" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3295">
@@ -89379,7 +89379,7 @@
         <v>6</v>
       </c>
       <c r="C3295" t="n">
-        <v>13.03</v>
+        <v>10.24</v>
       </c>
       <c r="D3295" t="inlineStr">
         <is>
@@ -89395,7 +89395,7 @@
         <v>2</v>
       </c>
       <c r="G3295" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3296">
@@ -89406,7 +89406,7 @@
         <v>7</v>
       </c>
       <c r="C3296" t="n">
-        <v>33.22</v>
+        <v>31.44</v>
       </c>
       <c r="D3296" t="inlineStr">
         <is>
@@ -89422,7 +89422,7 @@
         <v>2</v>
       </c>
       <c r="G3296" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3297">
@@ -89433,7 +89433,7 @@
         <v>8</v>
       </c>
       <c r="C3297" t="n">
-        <v>35.97</v>
+        <v>38.05</v>
       </c>
       <c r="D3297" t="inlineStr">
         <is>
@@ -89449,7 +89449,7 @@
         <v>2</v>
       </c>
       <c r="G3297" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3298">
@@ -89460,7 +89460,7 @@
         <v>9</v>
       </c>
       <c r="C3298" t="n">
-        <v>22.64</v>
+        <v>23.41</v>
       </c>
       <c r="D3298" t="inlineStr">
         <is>
@@ -89476,7 +89476,7 @@
         <v>2</v>
       </c>
       <c r="G3298" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3299">
@@ -89487,7 +89487,7 @@
         <v>10</v>
       </c>
       <c r="C3299" t="n">
-        <v>19.69</v>
+        <v>16.2</v>
       </c>
       <c r="D3299" t="inlineStr">
         <is>
@@ -89503,7 +89503,7 @@
         <v>2</v>
       </c>
       <c r="G3299" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3300">
@@ -89514,7 +89514,7 @@
         <v>11</v>
       </c>
       <c r="C3300" t="n">
-        <v>21.35</v>
+        <v>20.8</v>
       </c>
       <c r="D3300" t="inlineStr">
         <is>
@@ -89530,7 +89530,7 @@
         <v>2</v>
       </c>
       <c r="G3300" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3301">
@@ -89541,7 +89541,7 @@
         <v>12</v>
       </c>
       <c r="C3301" t="n">
-        <v>24.53</v>
+        <v>23.33</v>
       </c>
       <c r="D3301" t="inlineStr">
         <is>
@@ -89557,7 +89557,7 @@
         <v>2</v>
       </c>
       <c r="G3301" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3302">
@@ -89568,7 +89568,7 @@
         <v>13</v>
       </c>
       <c r="C3302" t="n">
-        <v>25.89</v>
+        <v>27.34</v>
       </c>
       <c r="D3302" t="inlineStr">
         <is>
@@ -89584,7 +89584,7 @@
         <v>2</v>
       </c>
       <c r="G3302" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3303">
@@ -89595,7 +89595,7 @@
         <v>14</v>
       </c>
       <c r="C3303" t="n">
-        <v>26.41</v>
+        <v>27.79</v>
       </c>
       <c r="D3303" t="inlineStr">
         <is>
@@ -89611,7 +89611,7 @@
         <v>2</v>
       </c>
       <c r="G3303" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3304">
@@ -89622,7 +89622,7 @@
         <v>15</v>
       </c>
       <c r="C3304" t="n">
-        <v>27.9</v>
+        <v>28.99</v>
       </c>
       <c r="D3304" t="inlineStr">
         <is>
@@ -89638,7 +89638,7 @@
         <v>2</v>
       </c>
       <c r="G3304" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3305">
@@ -89649,7 +89649,7 @@
         <v>16</v>
       </c>
       <c r="C3305" t="n">
-        <v>30.01</v>
+        <v>31.3</v>
       </c>
       <c r="D3305" t="inlineStr">
         <is>
@@ -89665,7 +89665,7 @@
         <v>2</v>
       </c>
       <c r="G3305" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3306">
@@ -89676,7 +89676,7 @@
         <v>17</v>
       </c>
       <c r="C3306" t="n">
-        <v>29.38</v>
+        <v>29.49</v>
       </c>
       <c r="D3306" t="inlineStr">
         <is>
@@ -89692,7 +89692,7 @@
         <v>2</v>
       </c>
       <c r="G3306" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3307">
@@ -89703,7 +89703,7 @@
         <v>18</v>
       </c>
       <c r="C3307" t="n">
-        <v>25.1</v>
+        <v>24.22</v>
       </c>
       <c r="D3307" t="inlineStr">
         <is>
@@ -89719,7 +89719,7 @@
         <v>2</v>
       </c>
       <c r="G3307" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3308">
@@ -89730,7 +89730,7 @@
         <v>19</v>
       </c>
       <c r="C3308" t="n">
-        <v>19.36</v>
+        <v>17.41</v>
       </c>
       <c r="D3308" t="inlineStr">
         <is>
@@ -89746,7 +89746,7 @@
         <v>2</v>
       </c>
       <c r="G3308" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3309">
@@ -89757,7 +89757,7 @@
         <v>20</v>
       </c>
       <c r="C3309" t="n">
-        <v>25.28</v>
+        <v>28.22</v>
       </c>
       <c r="D3309" t="inlineStr">
         <is>
@@ -89773,7 +89773,7 @@
         <v>2</v>
       </c>
       <c r="G3309" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3310">
@@ -89784,7 +89784,7 @@
         <v>21</v>
       </c>
       <c r="C3310" t="n">
-        <v>28.58</v>
+        <v>44.24</v>
       </c>
       <c r="D3310" t="inlineStr">
         <is>
@@ -89800,7 +89800,7 @@
         <v>2</v>
       </c>
       <c r="G3310" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3311">
@@ -89811,7 +89811,7 @@
         <v>22</v>
       </c>
       <c r="C3311" t="n">
-        <v>28.54</v>
+        <v>40.9</v>
       </c>
       <c r="D3311" t="inlineStr">
         <is>
@@ -89827,7 +89827,7 @@
         <v>2</v>
       </c>
       <c r="G3311" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3312">
@@ -89838,7 +89838,7 @@
         <v>23</v>
       </c>
       <c r="C3312" t="n">
-        <v>23.07</v>
+        <v>23.48</v>
       </c>
       <c r="D3312" t="inlineStr">
         <is>
@@ -89854,7 +89854,7 @@
         <v>2</v>
       </c>
       <c r="G3312" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
     <row r="3313">
@@ -89865,7 +89865,7 @@
         <v>24</v>
       </c>
       <c r="C3313" t="n">
-        <v>18.24</v>
+        <v>18.86</v>
       </c>
       <c r="D3313" t="inlineStr">
         <is>
@@ -89881,7 +89881,7 @@
         <v>2</v>
       </c>
       <c r="G3313" s="2" t="n">
-        <v>46281.4555915994</v>
+        <v>46281.87302596348</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -80188,7 +80188,7 @@
         <v>2</v>
       </c>
       <c r="G2954" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2955">
@@ -80215,7 +80215,7 @@
         <v>2</v>
       </c>
       <c r="G2955" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2956">
@@ -80242,7 +80242,7 @@
         <v>2</v>
       </c>
       <c r="G2956" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2957">
@@ -80269,7 +80269,7 @@
         <v>2</v>
       </c>
       <c r="G2957" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2958">
@@ -80296,7 +80296,7 @@
         <v>2</v>
       </c>
       <c r="G2958" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2959">
@@ -80323,7 +80323,7 @@
         <v>2</v>
       </c>
       <c r="G2959" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2960">
@@ -80350,7 +80350,7 @@
         <v>2</v>
       </c>
       <c r="G2960" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2961">
@@ -80377,7 +80377,7 @@
         <v>2</v>
       </c>
       <c r="G2961" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2962">
@@ -80404,7 +80404,7 @@
         <v>2</v>
       </c>
       <c r="G2962" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2963">
@@ -80431,7 +80431,7 @@
         <v>2</v>
       </c>
       <c r="G2963" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2964">
@@ -80458,7 +80458,7 @@
         <v>2</v>
       </c>
       <c r="G2964" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2965">
@@ -80485,7 +80485,7 @@
         <v>2</v>
       </c>
       <c r="G2965" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2966">
@@ -80512,7 +80512,7 @@
         <v>2</v>
       </c>
       <c r="G2966" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2967">
@@ -80539,7 +80539,7 @@
         <v>2</v>
       </c>
       <c r="G2967" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2968">
@@ -80566,7 +80566,7 @@
         <v>2</v>
       </c>
       <c r="G2968" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2969">
@@ -80593,7 +80593,7 @@
         <v>2</v>
       </c>
       <c r="G2969" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2970">
@@ -80604,7 +80604,7 @@
         <v>17</v>
       </c>
       <c r="C2970" t="n">
-        <v>36.05</v>
+        <v>36.04</v>
       </c>
       <c r="D2970" t="inlineStr">
         <is>
@@ -80620,7 +80620,7 @@
         <v>2</v>
       </c>
       <c r="G2970" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2971">
@@ -80631,7 +80631,7 @@
         <v>18</v>
       </c>
       <c r="C2971" t="n">
-        <v>34.12</v>
+        <v>34.11</v>
       </c>
       <c r="D2971" t="inlineStr">
         <is>
@@ -80647,7 +80647,7 @@
         <v>2</v>
       </c>
       <c r="G2971" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2972">
@@ -80674,7 +80674,7 @@
         <v>2</v>
       </c>
       <c r="G2972" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2973">
@@ -80701,7 +80701,7 @@
         <v>2</v>
       </c>
       <c r="G2973" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2974">
@@ -80728,7 +80728,7 @@
         <v>2</v>
       </c>
       <c r="G2974" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2975">
@@ -80755,7 +80755,7 @@
         <v>2</v>
       </c>
       <c r="G2975" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2976">
@@ -80782,7 +80782,7 @@
         <v>2</v>
       </c>
       <c r="G2976" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2977">
@@ -80809,7 +80809,7 @@
         <v>2</v>
       </c>
       <c r="G2977" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2978">
@@ -80836,7 +80836,7 @@
         <v>2</v>
       </c>
       <c r="G2978" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2979">
@@ -80863,7 +80863,7 @@
         <v>2</v>
       </c>
       <c r="G2979" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2980">
@@ -80890,7 +80890,7 @@
         <v>2</v>
       </c>
       <c r="G2980" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2981">
@@ -80917,7 +80917,7 @@
         <v>2</v>
       </c>
       <c r="G2981" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2982">
@@ -80944,7 +80944,7 @@
         <v>2</v>
       </c>
       <c r="G2982" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2983">
@@ -80971,7 +80971,7 @@
         <v>2</v>
       </c>
       <c r="G2983" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2984">
@@ -80998,7 +80998,7 @@
         <v>2</v>
       </c>
       <c r="G2984" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2985">
@@ -81025,7 +81025,7 @@
         <v>2</v>
       </c>
       <c r="G2985" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2986">
@@ -81052,7 +81052,7 @@
         <v>2</v>
       </c>
       <c r="G2986" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2987">
@@ -81079,7 +81079,7 @@
         <v>2</v>
       </c>
       <c r="G2987" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2988">
@@ -81090,7 +81090,7 @@
         <v>11</v>
       </c>
       <c r="C2988" t="n">
-        <v>19.72</v>
+        <v>19.71</v>
       </c>
       <c r="D2988" t="inlineStr">
         <is>
@@ -81106,7 +81106,7 @@
         <v>2</v>
       </c>
       <c r="G2988" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2989">
@@ -81133,7 +81133,7 @@
         <v>2</v>
       </c>
       <c r="G2989" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2990">
@@ -81160,7 +81160,7 @@
         <v>2</v>
       </c>
       <c r="G2990" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2991">
@@ -81171,7 +81171,7 @@
         <v>14</v>
       </c>
       <c r="C2991" t="n">
-        <v>31.37</v>
+        <v>31.36</v>
       </c>
       <c r="D2991" t="inlineStr">
         <is>
@@ -81187,7 +81187,7 @@
         <v>2</v>
       </c>
       <c r="G2991" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2992">
@@ -81198,7 +81198,7 @@
         <v>15</v>
       </c>
       <c r="C2992" t="n">
-        <v>31.51</v>
+        <v>31.5</v>
       </c>
       <c r="D2992" t="inlineStr">
         <is>
@@ -81214,7 +81214,7 @@
         <v>2</v>
       </c>
       <c r="G2992" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2993">
@@ -81225,7 +81225,7 @@
         <v>16</v>
       </c>
       <c r="C2993" t="n">
-        <v>34.14</v>
+        <v>34.13</v>
       </c>
       <c r="D2993" t="inlineStr">
         <is>
@@ -81241,7 +81241,7 @@
         <v>2</v>
       </c>
       <c r="G2993" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2994">
@@ -81268,7 +81268,7 @@
         <v>2</v>
       </c>
       <c r="G2994" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2995">
@@ -81295,7 +81295,7 @@
         <v>2</v>
       </c>
       <c r="G2995" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2996">
@@ -81322,7 +81322,7 @@
         <v>2</v>
       </c>
       <c r="G2996" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2997">
@@ -81349,7 +81349,7 @@
         <v>2</v>
       </c>
       <c r="G2997" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2998">
@@ -81376,7 +81376,7 @@
         <v>2</v>
       </c>
       <c r="G2998" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="2999">
@@ -81403,7 +81403,7 @@
         <v>2</v>
       </c>
       <c r="G2999" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3000">
@@ -81430,7 +81430,7 @@
         <v>2</v>
       </c>
       <c r="G3000" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3001">
@@ -81457,7 +81457,7 @@
         <v>2</v>
       </c>
       <c r="G3001" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3002">
@@ -81484,7 +81484,7 @@
         <v>2</v>
       </c>
       <c r="G3002" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3003">
@@ -81511,7 +81511,7 @@
         <v>2</v>
       </c>
       <c r="G3003" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3004">
@@ -81538,7 +81538,7 @@
         <v>2</v>
       </c>
       <c r="G3004" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3005">
@@ -81565,7 +81565,7 @@
         <v>2</v>
       </c>
       <c r="G3005" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3006">
@@ -81592,7 +81592,7 @@
         <v>2</v>
       </c>
       <c r="G3006" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3007">
@@ -81619,7 +81619,7 @@
         <v>2</v>
       </c>
       <c r="G3007" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3008">
@@ -81646,7 +81646,7 @@
         <v>2</v>
       </c>
       <c r="G3008" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3009">
@@ -81673,7 +81673,7 @@
         <v>2</v>
       </c>
       <c r="G3009" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3010">
@@ -81684,7 +81684,7 @@
         <v>9</v>
       </c>
       <c r="C3010" t="n">
-        <v>52.76</v>
+        <v>52.75</v>
       </c>
       <c r="D3010" t="inlineStr">
         <is>
@@ -81700,7 +81700,7 @@
         <v>2</v>
       </c>
       <c r="G3010" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3011">
@@ -81711,7 +81711,7 @@
         <v>10</v>
       </c>
       <c r="C3011" t="n">
-        <v>24.79</v>
+        <v>24.77</v>
       </c>
       <c r="D3011" t="inlineStr">
         <is>
@@ -81727,7 +81727,7 @@
         <v>2</v>
       </c>
       <c r="G3011" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3012">
@@ -81754,7 +81754,7 @@
         <v>2</v>
       </c>
       <c r="G3012" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3013">
@@ -81781,7 +81781,7 @@
         <v>2</v>
       </c>
       <c r="G3013" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3014">
@@ -81792,7 +81792,7 @@
         <v>13</v>
       </c>
       <c r="C3014" t="n">
-        <v>23.6</v>
+        <v>23.59</v>
       </c>
       <c r="D3014" t="inlineStr">
         <is>
@@ -81808,7 +81808,7 @@
         <v>2</v>
       </c>
       <c r="G3014" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3015">
@@ -81819,7 +81819,7 @@
         <v>14</v>
       </c>
       <c r="C3015" t="n">
-        <v>22.69</v>
+        <v>22.66</v>
       </c>
       <c r="D3015" t="inlineStr">
         <is>
@@ -81835,7 +81835,7 @@
         <v>2</v>
       </c>
       <c r="G3015" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3016">
@@ -81846,7 +81846,7 @@
         <v>15</v>
       </c>
       <c r="C3016" t="n">
-        <v>22.18</v>
+        <v>22.15</v>
       </c>
       <c r="D3016" t="inlineStr">
         <is>
@@ -81862,7 +81862,7 @@
         <v>2</v>
       </c>
       <c r="G3016" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3017">
@@ -81889,7 +81889,7 @@
         <v>2</v>
       </c>
       <c r="G3017" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3018">
@@ -81916,7 +81916,7 @@
         <v>2</v>
       </c>
       <c r="G3018" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3019">
@@ -81943,7 +81943,7 @@
         <v>2</v>
       </c>
       <c r="G3019" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3020">
@@ -81954,7 +81954,7 @@
         <v>19</v>
       </c>
       <c r="C3020" t="n">
-        <v>23.44</v>
+        <v>23.43</v>
       </c>
       <c r="D3020" t="inlineStr">
         <is>
@@ -81970,7 +81970,7 @@
         <v>2</v>
       </c>
       <c r="G3020" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3021">
@@ -81997,7 +81997,7 @@
         <v>2</v>
       </c>
       <c r="G3021" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3022">
@@ -82024,7 +82024,7 @@
         <v>2</v>
       </c>
       <c r="G3022" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3023">
@@ -82051,7 +82051,7 @@
         <v>2</v>
       </c>
       <c r="G3023" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3024">
@@ -82078,7 +82078,7 @@
         <v>2</v>
       </c>
       <c r="G3024" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3025">
@@ -82105,7 +82105,7 @@
         <v>2</v>
       </c>
       <c r="G3025" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3026">
@@ -82132,7 +82132,7 @@
         <v>2</v>
       </c>
       <c r="G3026" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3027">
@@ -82159,7 +82159,7 @@
         <v>2</v>
       </c>
       <c r="G3027" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3028">
@@ -82186,7 +82186,7 @@
         <v>2</v>
       </c>
       <c r="G3028" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3029">
@@ -82213,7 +82213,7 @@
         <v>2</v>
       </c>
       <c r="G3029" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3030">
@@ -82240,7 +82240,7 @@
         <v>2</v>
       </c>
       <c r="G3030" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3031">
@@ -82267,7 +82267,7 @@
         <v>2</v>
       </c>
       <c r="G3031" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3032">
@@ -82294,7 +82294,7 @@
         <v>2</v>
       </c>
       <c r="G3032" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3033">
@@ -82305,7 +82305,7 @@
         <v>8</v>
       </c>
       <c r="C3033" t="n">
-        <v>49.98</v>
+        <v>49.97</v>
       </c>
       <c r="D3033" t="inlineStr">
         <is>
@@ -82321,7 +82321,7 @@
         <v>2</v>
       </c>
       <c r="G3033" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3034">
@@ -82332,7 +82332,7 @@
         <v>9</v>
       </c>
       <c r="C3034" t="n">
-        <v>49.14</v>
+        <v>49.13</v>
       </c>
       <c r="D3034" t="inlineStr">
         <is>
@@ -82348,7 +82348,7 @@
         <v>2</v>
       </c>
       <c r="G3034" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3035">
@@ -82375,7 +82375,7 @@
         <v>2</v>
       </c>
       <c r="G3035" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3036">
@@ -82402,7 +82402,7 @@
         <v>2</v>
       </c>
       <c r="G3036" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3037">
@@ -82429,7 +82429,7 @@
         <v>2</v>
       </c>
       <c r="G3037" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3038">
@@ -82440,7 +82440,7 @@
         <v>13</v>
       </c>
       <c r="C3038" t="n">
-        <v>15.52</v>
+        <v>15.51</v>
       </c>
       <c r="D3038" t="inlineStr">
         <is>
@@ -82456,7 +82456,7 @@
         <v>2</v>
       </c>
       <c r="G3038" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3039">
@@ -82483,7 +82483,7 @@
         <v>2</v>
       </c>
       <c r="G3039" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3040">
@@ -82510,7 +82510,7 @@
         <v>2</v>
       </c>
       <c r="G3040" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3041">
@@ -82537,7 +82537,7 @@
         <v>2</v>
       </c>
       <c r="G3041" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3042">
@@ -82564,7 +82564,7 @@
         <v>2</v>
       </c>
       <c r="G3042" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3043">
@@ -82591,7 +82591,7 @@
         <v>2</v>
       </c>
       <c r="G3043" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3044">
@@ -82602,7 +82602,7 @@
         <v>19</v>
       </c>
       <c r="C3044" t="n">
-        <v>24.27</v>
+        <v>24.26</v>
       </c>
       <c r="D3044" t="inlineStr">
         <is>
@@ -82618,7 +82618,7 @@
         <v>2</v>
       </c>
       <c r="G3044" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3045">
@@ -82645,7 +82645,7 @@
         <v>2</v>
       </c>
       <c r="G3045" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3046">
@@ -82672,7 +82672,7 @@
         <v>2</v>
       </c>
       <c r="G3046" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3047">
@@ -82699,7 +82699,7 @@
         <v>2</v>
       </c>
       <c r="G3047" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3048">
@@ -82726,7 +82726,7 @@
         <v>2</v>
       </c>
       <c r="G3048" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3049">
@@ -82753,7 +82753,7 @@
         <v>2</v>
       </c>
       <c r="G3049" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3050">
@@ -82780,7 +82780,7 @@
         <v>2</v>
       </c>
       <c r="G3050" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3051">
@@ -82807,7 +82807,7 @@
         <v>2</v>
       </c>
       <c r="G3051" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3052">
@@ -82834,7 +82834,7 @@
         <v>2</v>
       </c>
       <c r="G3052" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3053">
@@ -82861,7 +82861,7 @@
         <v>2</v>
       </c>
       <c r="G3053" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3054">
@@ -82888,7 +82888,7 @@
         <v>2</v>
       </c>
       <c r="G3054" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3055">
@@ -82915,7 +82915,7 @@
         <v>2</v>
       </c>
       <c r="G3055" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3056">
@@ -82942,7 +82942,7 @@
         <v>2</v>
       </c>
       <c r="G3056" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3057">
@@ -82969,7 +82969,7 @@
         <v>2</v>
       </c>
       <c r="G3057" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3058">
@@ -82996,7 +82996,7 @@
         <v>2</v>
       </c>
       <c r="G3058" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3059">
@@ -83023,7 +83023,7 @@
         <v>2</v>
       </c>
       <c r="G3059" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3060">
@@ -83050,7 +83050,7 @@
         <v>2</v>
       </c>
       <c r="G3060" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3061">
@@ -83077,7 +83077,7 @@
         <v>2</v>
       </c>
       <c r="G3061" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3062">
@@ -83104,7 +83104,7 @@
         <v>2</v>
       </c>
       <c r="G3062" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3063">
@@ -83131,7 +83131,7 @@
         <v>2</v>
       </c>
       <c r="G3063" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3064">
@@ -83158,7 +83158,7 @@
         <v>2</v>
       </c>
       <c r="G3064" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3065">
@@ -83185,7 +83185,7 @@
         <v>2</v>
       </c>
       <c r="G3065" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3066">
@@ -83212,7 +83212,7 @@
         <v>2</v>
       </c>
       <c r="G3066" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3067">
@@ -83239,7 +83239,7 @@
         <v>2</v>
       </c>
       <c r="G3067" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3068">
@@ -83266,7 +83266,7 @@
         <v>2</v>
       </c>
       <c r="G3068" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3069">
@@ -83293,7 +83293,7 @@
         <v>2</v>
       </c>
       <c r="G3069" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3070">
@@ -83320,7 +83320,7 @@
         <v>2</v>
       </c>
       <c r="G3070" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3071">
@@ -83347,7 +83347,7 @@
         <v>2</v>
       </c>
       <c r="G3071" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3072">
@@ -83374,7 +83374,7 @@
         <v>2</v>
       </c>
       <c r="G3072" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3073">
@@ -83401,7 +83401,7 @@
         <v>2</v>
       </c>
       <c r="G3073" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3074">
@@ -83428,7 +83428,7 @@
         <v>2</v>
       </c>
       <c r="G3074" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3075">
@@ -83455,7 +83455,7 @@
         <v>2</v>
       </c>
       <c r="G3075" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3076">
@@ -83482,7 +83482,7 @@
         <v>2</v>
       </c>
       <c r="G3076" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3077">
@@ -83509,7 +83509,7 @@
         <v>2</v>
       </c>
       <c r="G3077" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3078">
@@ -83536,7 +83536,7 @@
         <v>2</v>
       </c>
       <c r="G3078" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3079">
@@ -83563,7 +83563,7 @@
         <v>2</v>
       </c>
       <c r="G3079" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3080">
@@ -83590,7 +83590,7 @@
         <v>2</v>
       </c>
       <c r="G3080" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3081">
@@ -83617,7 +83617,7 @@
         <v>2</v>
       </c>
       <c r="G3081" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3082">
@@ -83644,7 +83644,7 @@
         <v>2</v>
       </c>
       <c r="G3082" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3083">
@@ -83671,7 +83671,7 @@
         <v>2</v>
       </c>
       <c r="G3083" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3084">
@@ -83698,7 +83698,7 @@
         <v>2</v>
       </c>
       <c r="G3084" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3085">
@@ -83709,7 +83709,7 @@
         <v>12</v>
       </c>
       <c r="C3085" t="n">
-        <v>20.5</v>
+        <v>20.49</v>
       </c>
       <c r="D3085" t="inlineStr">
         <is>
@@ -83725,7 +83725,7 @@
         <v>2</v>
       </c>
       <c r="G3085" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3086">
@@ -83736,7 +83736,7 @@
         <v>13</v>
       </c>
       <c r="C3086" t="n">
-        <v>22.45</v>
+        <v>22.44</v>
       </c>
       <c r="D3086" t="inlineStr">
         <is>
@@ -83752,7 +83752,7 @@
         <v>2</v>
       </c>
       <c r="G3086" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3087">
@@ -83763,7 +83763,7 @@
         <v>14</v>
       </c>
       <c r="C3087" t="n">
-        <v>21.48</v>
+        <v>21.45</v>
       </c>
       <c r="D3087" t="inlineStr">
         <is>
@@ -83779,7 +83779,7 @@
         <v>2</v>
       </c>
       <c r="G3087" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3088">
@@ -83790,7 +83790,7 @@
         <v>15</v>
       </c>
       <c r="C3088" t="n">
-        <v>20.84</v>
+        <v>20.82</v>
       </c>
       <c r="D3088" t="inlineStr">
         <is>
@@ -83806,7 +83806,7 @@
         <v>2</v>
       </c>
       <c r="G3088" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3089">
@@ -83817,7 +83817,7 @@
         <v>16</v>
       </c>
       <c r="C3089" t="n">
-        <v>26.84</v>
+        <v>26.83</v>
       </c>
       <c r="D3089" t="inlineStr">
         <is>
@@ -83833,7 +83833,7 @@
         <v>2</v>
       </c>
       <c r="G3089" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3090">
@@ -83860,7 +83860,7 @@
         <v>2</v>
       </c>
       <c r="G3090" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3091">
@@ -83871,7 +83871,7 @@
         <v>18</v>
       </c>
       <c r="C3091" t="n">
-        <v>22.69</v>
+        <v>22.7</v>
       </c>
       <c r="D3091" t="inlineStr">
         <is>
@@ -83887,7 +83887,7 @@
         <v>2</v>
       </c>
       <c r="G3091" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3092">
@@ -83914,7 +83914,7 @@
         <v>2</v>
       </c>
       <c r="G3092" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3093">
@@ -83941,7 +83941,7 @@
         <v>2</v>
       </c>
       <c r="G3093" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3094">
@@ -83968,7 +83968,7 @@
         <v>2</v>
       </c>
       <c r="G3094" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3095">
@@ -83995,7 +83995,7 @@
         <v>2</v>
       </c>
       <c r="G3095" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3096">
@@ -84022,7 +84022,7 @@
         <v>2</v>
       </c>
       <c r="G3096" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3097">
@@ -84049,7 +84049,7 @@
         <v>2</v>
       </c>
       <c r="G3097" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3098">
@@ -84076,7 +84076,7 @@
         <v>2</v>
       </c>
       <c r="G3098" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3099">
@@ -84087,7 +84087,7 @@
         <v>2</v>
       </c>
       <c r="C3099" t="n">
-        <v>12.27</v>
+        <v>12.26</v>
       </c>
       <c r="D3099" t="inlineStr">
         <is>
@@ -84103,7 +84103,7 @@
         <v>2</v>
       </c>
       <c r="G3099" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3100">
@@ -84114,7 +84114,7 @@
         <v>3</v>
       </c>
       <c r="C3100" t="n">
-        <v>9.619999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="D3100" t="inlineStr">
         <is>
@@ -84130,7 +84130,7 @@
         <v>2</v>
       </c>
       <c r="G3100" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3101">
@@ -84141,7 +84141,7 @@
         <v>4</v>
       </c>
       <c r="C3101" t="n">
-        <v>10.3</v>
+        <v>10.28</v>
       </c>
       <c r="D3101" t="inlineStr">
         <is>
@@ -84157,7 +84157,7 @@
         <v>2</v>
       </c>
       <c r="G3101" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3102">
@@ -84168,7 +84168,7 @@
         <v>5</v>
       </c>
       <c r="C3102" t="n">
-        <v>10.78</v>
+        <v>10.77</v>
       </c>
       <c r="D3102" t="inlineStr">
         <is>
@@ -84184,7 +84184,7 @@
         <v>2</v>
       </c>
       <c r="G3102" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3103">
@@ -84195,7 +84195,7 @@
         <v>6</v>
       </c>
       <c r="C3103" t="n">
-        <v>11.59</v>
+        <v>11.58</v>
       </c>
       <c r="D3103" t="inlineStr">
         <is>
@@ -84211,7 +84211,7 @@
         <v>2</v>
       </c>
       <c r="G3103" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3104">
@@ -84222,7 +84222,7 @@
         <v>7</v>
       </c>
       <c r="C3104" t="n">
-        <v>23.23</v>
+        <v>23.22</v>
       </c>
       <c r="D3104" t="inlineStr">
         <is>
@@ -84238,7 +84238,7 @@
         <v>2</v>
       </c>
       <c r="G3104" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3105">
@@ -84249,7 +84249,7 @@
         <v>8</v>
       </c>
       <c r="C3105" t="n">
-        <v>50.33</v>
+        <v>50.32</v>
       </c>
       <c r="D3105" t="inlineStr">
         <is>
@@ -84265,7 +84265,7 @@
         <v>2</v>
       </c>
       <c r="G3105" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3106">
@@ -84276,7 +84276,7 @@
         <v>9</v>
       </c>
       <c r="C3106" t="n">
-        <v>50.17</v>
+        <v>50.16</v>
       </c>
       <c r="D3106" t="inlineStr">
         <is>
@@ -84292,7 +84292,7 @@
         <v>2</v>
       </c>
       <c r="G3106" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3107">
@@ -84319,7 +84319,7 @@
         <v>2</v>
       </c>
       <c r="G3107" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3108">
@@ -84330,7 +84330,7 @@
         <v>11</v>
       </c>
       <c r="C3108" t="n">
-        <v>18.12</v>
+        <v>18.13</v>
       </c>
       <c r="D3108" t="inlineStr">
         <is>
@@ -84346,7 +84346,7 @@
         <v>2</v>
       </c>
       <c r="G3108" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3109">
@@ -84373,7 +84373,7 @@
         <v>2</v>
       </c>
       <c r="G3109" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3110">
@@ -84400,7 +84400,7 @@
         <v>2</v>
       </c>
       <c r="G3110" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3111">
@@ -84411,7 +84411,7 @@
         <v>14</v>
       </c>
       <c r="C3111" t="n">
-        <v>21.86</v>
+        <v>21.89</v>
       </c>
       <c r="D3111" t="inlineStr">
         <is>
@@ -84427,7 +84427,7 @@
         <v>2</v>
       </c>
       <c r="G3111" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3112">
@@ -84438,7 +84438,7 @@
         <v>15</v>
       </c>
       <c r="C3112" t="n">
-        <v>22.98</v>
+        <v>22.96</v>
       </c>
       <c r="D3112" t="inlineStr">
         <is>
@@ -84454,7 +84454,7 @@
         <v>2</v>
       </c>
       <c r="G3112" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3113">
@@ -84481,7 +84481,7 @@
         <v>2</v>
       </c>
       <c r="G3113" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3114">
@@ -84508,7 +84508,7 @@
         <v>2</v>
       </c>
       <c r="G3114" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3115">
@@ -84535,7 +84535,7 @@
         <v>2</v>
       </c>
       <c r="G3115" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3116">
@@ -84562,7 +84562,7 @@
         <v>2</v>
       </c>
       <c r="G3116" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3117">
@@ -84589,7 +84589,7 @@
         <v>2</v>
       </c>
       <c r="G3117" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3118">
@@ -84616,7 +84616,7 @@
         <v>2</v>
       </c>
       <c r="G3118" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3119">
@@ -84643,7 +84643,7 @@
         <v>2</v>
       </c>
       <c r="G3119" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3120">
@@ -84670,7 +84670,7 @@
         <v>2</v>
       </c>
       <c r="G3120" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3121">
@@ -84697,7 +84697,7 @@
         <v>2</v>
       </c>
       <c r="G3121" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3122">
@@ -84724,7 +84724,7 @@
         <v>2</v>
       </c>
       <c r="G3122" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3123">
@@ -84751,7 +84751,7 @@
         <v>2</v>
       </c>
       <c r="G3123" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3124">
@@ -84778,7 +84778,7 @@
         <v>2</v>
       </c>
       <c r="G3124" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3125">
@@ -84805,7 +84805,7 @@
         <v>2</v>
       </c>
       <c r="G3125" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3126">
@@ -84832,7 +84832,7 @@
         <v>2</v>
       </c>
       <c r="G3126" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3127">
@@ -84859,7 +84859,7 @@
         <v>2</v>
       </c>
       <c r="G3127" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3128">
@@ -84886,7 +84886,7 @@
         <v>2</v>
       </c>
       <c r="G3128" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3129">
@@ -84913,7 +84913,7 @@
         <v>2</v>
       </c>
       <c r="G3129" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3130">
@@ -84940,7 +84940,7 @@
         <v>2</v>
       </c>
       <c r="G3130" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3131">
@@ -84967,7 +84967,7 @@
         <v>2</v>
       </c>
       <c r="G3131" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3132">
@@ -84994,7 +84994,7 @@
         <v>2</v>
       </c>
       <c r="G3132" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3133">
@@ -85021,7 +85021,7 @@
         <v>2</v>
       </c>
       <c r="G3133" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3134">
@@ -85048,7 +85048,7 @@
         <v>2</v>
       </c>
       <c r="G3134" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3135">
@@ -85075,7 +85075,7 @@
         <v>2</v>
       </c>
       <c r="G3135" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3136">
@@ -85086,7 +85086,7 @@
         <v>15</v>
       </c>
       <c r="C3136" t="n">
-        <v>20.91</v>
+        <v>20.93</v>
       </c>
       <c r="D3136" t="inlineStr">
         <is>
@@ -85102,7 +85102,7 @@
         <v>2</v>
       </c>
       <c r="G3136" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3137">
@@ -85129,7 +85129,7 @@
         <v>2</v>
       </c>
       <c r="G3137" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3138">
@@ -85156,7 +85156,7 @@
         <v>2</v>
       </c>
       <c r="G3138" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3139">
@@ -85183,7 +85183,7 @@
         <v>2</v>
       </c>
       <c r="G3139" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3140">
@@ -85210,7 +85210,7 @@
         <v>2</v>
       </c>
       <c r="G3140" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3141">
@@ -85237,7 +85237,7 @@
         <v>2</v>
       </c>
       <c r="G3141" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3142">
@@ -85264,7 +85264,7 @@
         <v>2</v>
       </c>
       <c r="G3142" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3143">
@@ -85291,7 +85291,7 @@
         <v>2</v>
       </c>
       <c r="G3143" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3144">
@@ -85318,7 +85318,7 @@
         <v>2</v>
       </c>
       <c r="G3144" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3145">
@@ -85345,7 +85345,7 @@
         <v>2</v>
       </c>
       <c r="G3145" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3146">
@@ -85372,7 +85372,7 @@
         <v>2</v>
       </c>
       <c r="G3146" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3147">
@@ -85399,7 +85399,7 @@
         <v>2</v>
       </c>
       <c r="G3147" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3148">
@@ -85426,7 +85426,7 @@
         <v>2</v>
       </c>
       <c r="G3148" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3149">
@@ -85453,7 +85453,7 @@
         <v>2</v>
       </c>
       <c r="G3149" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3150">
@@ -85480,7 +85480,7 @@
         <v>2</v>
       </c>
       <c r="G3150" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3151">
@@ -85507,7 +85507,7 @@
         <v>2</v>
       </c>
       <c r="G3151" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3152">
@@ -85534,7 +85534,7 @@
         <v>2</v>
       </c>
       <c r="G3152" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3153">
@@ -85561,7 +85561,7 @@
         <v>2</v>
       </c>
       <c r="G3153" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3154">
@@ -85588,7 +85588,7 @@
         <v>2</v>
       </c>
       <c r="G3154" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3155">
@@ -85615,7 +85615,7 @@
         <v>2</v>
       </c>
       <c r="G3155" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3156">
@@ -85642,7 +85642,7 @@
         <v>2</v>
       </c>
       <c r="G3156" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3157">
@@ -85669,7 +85669,7 @@
         <v>2</v>
       </c>
       <c r="G3157" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3158">
@@ -85696,7 +85696,7 @@
         <v>2</v>
       </c>
       <c r="G3158" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3159">
@@ -85707,7 +85707,7 @@
         <v>14</v>
       </c>
       <c r="C3159" t="n">
-        <v>31.73</v>
+        <v>31.71</v>
       </c>
       <c r="D3159" t="inlineStr">
         <is>
@@ -85723,7 +85723,7 @@
         <v>2</v>
       </c>
       <c r="G3159" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3160">
@@ -85734,7 +85734,7 @@
         <v>15</v>
       </c>
       <c r="C3160" t="n">
-        <v>32.12</v>
+        <v>32.09</v>
       </c>
       <c r="D3160" t="inlineStr">
         <is>
@@ -85750,7 +85750,7 @@
         <v>2</v>
       </c>
       <c r="G3160" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3161">
@@ -85761,7 +85761,7 @@
         <v>16</v>
       </c>
       <c r="C3161" t="n">
-        <v>31.2</v>
+        <v>31.19</v>
       </c>
       <c r="D3161" t="inlineStr">
         <is>
@@ -85777,7 +85777,7 @@
         <v>2</v>
       </c>
       <c r="G3161" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3162">
@@ -85804,7 +85804,7 @@
         <v>2</v>
       </c>
       <c r="G3162" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3163">
@@ -85815,7 +85815,7 @@
         <v>18</v>
       </c>
       <c r="C3163" t="n">
-        <v>34.85</v>
+        <v>34.84</v>
       </c>
       <c r="D3163" t="inlineStr">
         <is>
@@ -85831,7 +85831,7 @@
         <v>2</v>
       </c>
       <c r="G3163" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3164">
@@ -85858,7 +85858,7 @@
         <v>2</v>
       </c>
       <c r="G3164" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3165">
@@ -85885,7 +85885,7 @@
         <v>2</v>
       </c>
       <c r="G3165" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3166">
@@ -85912,7 +85912,7 @@
         <v>2</v>
       </c>
       <c r="G3166" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3167">
@@ -85939,7 +85939,7 @@
         <v>2</v>
       </c>
       <c r="G3167" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3168">
@@ -85966,7 +85966,7 @@
         <v>2</v>
       </c>
       <c r="G3168" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3169">
@@ -85993,7 +85993,7 @@
         <v>2</v>
       </c>
       <c r="G3169" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3170">
@@ -86004,7 +86004,7 @@
         <v>1</v>
       </c>
       <c r="C3170" t="n">
-        <v>20.06</v>
+        <v>20.37</v>
       </c>
       <c r="D3170" t="inlineStr">
         <is>
@@ -86020,7 +86020,7 @@
         <v>2</v>
       </c>
       <c r="G3170" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3171">
@@ -86047,7 +86047,7 @@
         <v>2</v>
       </c>
       <c r="G3171" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3172">
@@ -86058,7 +86058,7 @@
         <v>3</v>
       </c>
       <c r="C3172" t="n">
-        <v>16.58</v>
+        <v>16.63</v>
       </c>
       <c r="D3172" t="inlineStr">
         <is>
@@ -86074,7 +86074,7 @@
         <v>2</v>
       </c>
       <c r="G3172" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3173">
@@ -86085,7 +86085,7 @@
         <v>4</v>
       </c>
       <c r="C3173" t="n">
-        <v>15.83</v>
+        <v>15.84</v>
       </c>
       <c r="D3173" t="inlineStr">
         <is>
@@ -86101,7 +86101,7 @@
         <v>2</v>
       </c>
       <c r="G3173" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3174">
@@ -86112,7 +86112,7 @@
         <v>5</v>
       </c>
       <c r="C3174" t="n">
-        <v>13.64</v>
+        <v>13.69</v>
       </c>
       <c r="D3174" t="inlineStr">
         <is>
@@ -86128,7 +86128,7 @@
         <v>2</v>
       </c>
       <c r="G3174" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3175">
@@ -86139,7 +86139,7 @@
         <v>6</v>
       </c>
       <c r="C3175" t="n">
-        <v>13.12</v>
+        <v>13.2</v>
       </c>
       <c r="D3175" t="inlineStr">
         <is>
@@ -86155,7 +86155,7 @@
         <v>2</v>
       </c>
       <c r="G3175" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3176">
@@ -86182,7 +86182,7 @@
         <v>2</v>
       </c>
       <c r="G3176" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3177">
@@ -86193,7 +86193,7 @@
         <v>8</v>
       </c>
       <c r="C3177" t="n">
-        <v>40.89</v>
+        <v>40.92</v>
       </c>
       <c r="D3177" t="inlineStr">
         <is>
@@ -86209,7 +86209,7 @@
         <v>2</v>
       </c>
       <c r="G3177" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3178">
@@ -86220,7 +86220,7 @@
         <v>9</v>
       </c>
       <c r="C3178" t="n">
-        <v>42.03</v>
+        <v>41.99</v>
       </c>
       <c r="D3178" t="inlineStr">
         <is>
@@ -86236,7 +86236,7 @@
         <v>2</v>
       </c>
       <c r="G3178" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3179">
@@ -86263,7 +86263,7 @@
         <v>2</v>
       </c>
       <c r="G3179" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3180">
@@ -86274,7 +86274,7 @@
         <v>11</v>
       </c>
       <c r="C3180" t="n">
-        <v>13.82</v>
+        <v>13.75</v>
       </c>
       <c r="D3180" t="inlineStr">
         <is>
@@ -86290,7 +86290,7 @@
         <v>2</v>
       </c>
       <c r="G3180" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3181">
@@ -86301,7 +86301,7 @@
         <v>12</v>
       </c>
       <c r="C3181" t="n">
-        <v>29.13</v>
+        <v>29.04</v>
       </c>
       <c r="D3181" t="inlineStr">
         <is>
@@ -86317,7 +86317,7 @@
         <v>2</v>
       </c>
       <c r="G3181" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3182">
@@ -86328,7 +86328,7 @@
         <v>13</v>
       </c>
       <c r="C3182" t="n">
-        <v>30.51</v>
+        <v>30.36</v>
       </c>
       <c r="D3182" t="inlineStr">
         <is>
@@ -86344,7 +86344,7 @@
         <v>2</v>
       </c>
       <c r="G3182" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3183">
@@ -86355,7 +86355,7 @@
         <v>14</v>
       </c>
       <c r="C3183" t="n">
-        <v>28.89</v>
+        <v>28.76</v>
       </c>
       <c r="D3183" t="inlineStr">
         <is>
@@ -86371,7 +86371,7 @@
         <v>2</v>
       </c>
       <c r="G3183" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3184">
@@ -86382,7 +86382,7 @@
         <v>15</v>
       </c>
       <c r="C3184" t="n">
-        <v>31.91</v>
+        <v>31.82</v>
       </c>
       <c r="D3184" t="inlineStr">
         <is>
@@ -86398,7 +86398,7 @@
         <v>2</v>
       </c>
       <c r="G3184" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3185">
@@ -86425,7 +86425,7 @@
         <v>2</v>
       </c>
       <c r="G3185" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3186">
@@ -86436,7 +86436,7 @@
         <v>17</v>
       </c>
       <c r="C3186" t="n">
-        <v>31.78</v>
+        <v>31.72</v>
       </c>
       <c r="D3186" t="inlineStr">
         <is>
@@ -86452,7 +86452,7 @@
         <v>2</v>
       </c>
       <c r="G3186" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3187">
@@ -86463,7 +86463,7 @@
         <v>18</v>
       </c>
       <c r="C3187" t="n">
-        <v>27.1</v>
+        <v>27.01</v>
       </c>
       <c r="D3187" t="inlineStr">
         <is>
@@ -86479,7 +86479,7 @@
         <v>2</v>
       </c>
       <c r="G3187" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3188">
@@ -86490,7 +86490,7 @@
         <v>19</v>
       </c>
       <c r="C3188" t="n">
-        <v>22.03</v>
+        <v>22.04</v>
       </c>
       <c r="D3188" t="inlineStr">
         <is>
@@ -86506,7 +86506,7 @@
         <v>2</v>
       </c>
       <c r="G3188" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3189">
@@ -86517,7 +86517,7 @@
         <v>20</v>
       </c>
       <c r="C3189" t="n">
-        <v>17.12</v>
+        <v>17.22</v>
       </c>
       <c r="D3189" t="inlineStr">
         <is>
@@ -86533,7 +86533,7 @@
         <v>2</v>
       </c>
       <c r="G3189" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3190">
@@ -86544,7 +86544,7 @@
         <v>21</v>
       </c>
       <c r="C3190" t="n">
-        <v>26.71</v>
+        <v>26.98</v>
       </c>
       <c r="D3190" t="inlineStr">
         <is>
@@ -86560,7 +86560,7 @@
         <v>2</v>
       </c>
       <c r="G3190" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3191">
@@ -86571,7 +86571,7 @@
         <v>22</v>
       </c>
       <c r="C3191" t="n">
-        <v>28.54</v>
+        <v>28.43</v>
       </c>
       <c r="D3191" t="inlineStr">
         <is>
@@ -86587,7 +86587,7 @@
         <v>2</v>
       </c>
       <c r="G3191" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3192">
@@ -86598,7 +86598,7 @@
         <v>23</v>
       </c>
       <c r="C3192" t="n">
-        <v>27.68</v>
+        <v>27.69</v>
       </c>
       <c r="D3192" t="inlineStr">
         <is>
@@ -86614,7 +86614,7 @@
         <v>2</v>
       </c>
       <c r="G3192" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3193">
@@ -86625,7 +86625,7 @@
         <v>24</v>
       </c>
       <c r="C3193" t="n">
-        <v>28.1</v>
+        <v>28.09</v>
       </c>
       <c r="D3193" t="inlineStr">
         <is>
@@ -86641,7 +86641,7 @@
         <v>2</v>
       </c>
       <c r="G3193" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3194">
@@ -86668,7 +86668,7 @@
         <v>2</v>
       </c>
       <c r="G3194" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3195">
@@ -86695,7 +86695,7 @@
         <v>2</v>
       </c>
       <c r="G3195" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3196">
@@ -86722,7 +86722,7 @@
         <v>2</v>
       </c>
       <c r="G3196" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3197">
@@ -86749,7 +86749,7 @@
         <v>2</v>
       </c>
       <c r="G3197" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3198">
@@ -86776,7 +86776,7 @@
         <v>2</v>
       </c>
       <c r="G3198" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3199">
@@ -86803,7 +86803,7 @@
         <v>2</v>
       </c>
       <c r="G3199" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3200">
@@ -86830,7 +86830,7 @@
         <v>2</v>
       </c>
       <c r="G3200" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3201">
@@ -86841,7 +86841,7 @@
         <v>8</v>
       </c>
       <c r="C3201" t="n">
-        <v>35.69</v>
+        <v>35.7</v>
       </c>
       <c r="D3201" t="inlineStr">
         <is>
@@ -86857,7 +86857,7 @@
         <v>2</v>
       </c>
       <c r="G3201" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3202">
@@ -86884,7 +86884,7 @@
         <v>2</v>
       </c>
       <c r="G3202" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3203">
@@ -86911,7 +86911,7 @@
         <v>2</v>
       </c>
       <c r="G3203" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3204">
@@ -86938,7 +86938,7 @@
         <v>2</v>
       </c>
       <c r="G3204" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3205">
@@ -86949,7 +86949,7 @@
         <v>12</v>
       </c>
       <c r="C3205" t="n">
-        <v>42.96</v>
+        <v>42.95</v>
       </c>
       <c r="D3205" t="inlineStr">
         <is>
@@ -86965,7 +86965,7 @@
         <v>2</v>
       </c>
       <c r="G3205" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3206">
@@ -86976,7 +86976,7 @@
         <v>13</v>
       </c>
       <c r="C3206" t="n">
-        <v>46.81</v>
+        <v>46.79</v>
       </c>
       <c r="D3206" t="inlineStr">
         <is>
@@ -86992,7 +86992,7 @@
         <v>2</v>
       </c>
       <c r="G3206" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3207">
@@ -87003,7 +87003,7 @@
         <v>14</v>
       </c>
       <c r="C3207" t="n">
-        <v>50.85</v>
+        <v>50.79</v>
       </c>
       <c r="D3207" t="inlineStr">
         <is>
@@ -87019,7 +87019,7 @@
         <v>2</v>
       </c>
       <c r="G3207" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3208">
@@ -87030,7 +87030,7 @@
         <v>15</v>
       </c>
       <c r="C3208" t="n">
-        <v>49.19</v>
+        <v>49.13</v>
       </c>
       <c r="D3208" t="inlineStr">
         <is>
@@ -87046,7 +87046,7 @@
         <v>2</v>
       </c>
       <c r="G3208" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3209">
@@ -87057,7 +87057,7 @@
         <v>16</v>
       </c>
       <c r="C3209" t="n">
-        <v>50.71</v>
+        <v>50.7</v>
       </c>
       <c r="D3209" t="inlineStr">
         <is>
@@ -87073,7 +87073,7 @@
         <v>2</v>
       </c>
       <c r="G3209" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3210">
@@ -87100,7 +87100,7 @@
         <v>2</v>
       </c>
       <c r="G3210" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3211">
@@ -87111,7 +87111,7 @@
         <v>18</v>
       </c>
       <c r="C3211" t="n">
-        <v>41.16</v>
+        <v>41.15</v>
       </c>
       <c r="D3211" t="inlineStr">
         <is>
@@ -87127,7 +87127,7 @@
         <v>2</v>
       </c>
       <c r="G3211" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3212">
@@ -87154,7 +87154,7 @@
         <v>2</v>
       </c>
       <c r="G3212" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3213">
@@ -87181,7 +87181,7 @@
         <v>2</v>
       </c>
       <c r="G3213" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3214">
@@ -87208,7 +87208,7 @@
         <v>2</v>
       </c>
       <c r="G3214" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3215">
@@ -87235,7 +87235,7 @@
         <v>2</v>
       </c>
       <c r="G3215" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3216">
@@ -87262,7 +87262,7 @@
         <v>2</v>
       </c>
       <c r="G3216" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3217">
@@ -87289,7 +87289,7 @@
         <v>2</v>
       </c>
       <c r="G3217" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3218">
@@ -87316,7 +87316,7 @@
         <v>2</v>
       </c>
       <c r="G3218" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3219">
@@ -87343,7 +87343,7 @@
         <v>2</v>
       </c>
       <c r="G3219" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3220">
@@ -87370,7 +87370,7 @@
         <v>2</v>
       </c>
       <c r="G3220" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3221">
@@ -87397,7 +87397,7 @@
         <v>2</v>
       </c>
       <c r="G3221" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3222">
@@ -87424,7 +87424,7 @@
         <v>2</v>
       </c>
       <c r="G3222" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3223">
@@ -87451,7 +87451,7 @@
         <v>2</v>
       </c>
       <c r="G3223" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3224">
@@ -87478,7 +87478,7 @@
         <v>2</v>
       </c>
       <c r="G3224" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3225">
@@ -87505,7 +87505,7 @@
         <v>2</v>
       </c>
       <c r="G3225" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3226">
@@ -87532,7 +87532,7 @@
         <v>2</v>
       </c>
       <c r="G3226" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3227">
@@ -87543,7 +87543,7 @@
         <v>10</v>
       </c>
       <c r="C3227" t="n">
-        <v>23.22</v>
+        <v>23.21</v>
       </c>
       <c r="D3227" t="inlineStr">
         <is>
@@ -87559,7 +87559,7 @@
         <v>2</v>
       </c>
       <c r="G3227" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3228">
@@ -87570,7 +87570,7 @@
         <v>11</v>
       </c>
       <c r="C3228" t="n">
-        <v>27.28</v>
+        <v>27.27</v>
       </c>
       <c r="D3228" t="inlineStr">
         <is>
@@ -87586,7 +87586,7 @@
         <v>2</v>
       </c>
       <c r="G3228" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3229">
@@ -87597,7 +87597,7 @@
         <v>12</v>
       </c>
       <c r="C3229" t="n">
-        <v>29.69</v>
+        <v>29.68</v>
       </c>
       <c r="D3229" t="inlineStr">
         <is>
@@ -87613,7 +87613,7 @@
         <v>2</v>
       </c>
       <c r="G3229" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3230">
@@ -87624,7 +87624,7 @@
         <v>13</v>
       </c>
       <c r="C3230" t="n">
-        <v>35.25</v>
+        <v>35.23</v>
       </c>
       <c r="D3230" t="inlineStr">
         <is>
@@ -87640,7 +87640,7 @@
         <v>2</v>
       </c>
       <c r="G3230" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3231">
@@ -87651,7 +87651,7 @@
         <v>14</v>
       </c>
       <c r="C3231" t="n">
-        <v>35.27</v>
+        <v>35.22</v>
       </c>
       <c r="D3231" t="inlineStr">
         <is>
@@ -87667,7 +87667,7 @@
         <v>2</v>
       </c>
       <c r="G3231" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3232">
@@ -87678,7 +87678,7 @@
         <v>15</v>
       </c>
       <c r="C3232" t="n">
-        <v>34.33</v>
+        <v>34.28</v>
       </c>
       <c r="D3232" t="inlineStr">
         <is>
@@ -87694,7 +87694,7 @@
         <v>2</v>
       </c>
       <c r="G3232" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3233">
@@ -87705,7 +87705,7 @@
         <v>16</v>
       </c>
       <c r="C3233" t="n">
-        <v>35.66</v>
+        <v>35.64</v>
       </c>
       <c r="D3233" t="inlineStr">
         <is>
@@ -87721,7 +87721,7 @@
         <v>2</v>
       </c>
       <c r="G3233" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3234">
@@ -87732,7 +87732,7 @@
         <v>17</v>
       </c>
       <c r="C3234" t="n">
-        <v>36.4</v>
+        <v>36.38</v>
       </c>
       <c r="D3234" t="inlineStr">
         <is>
@@ -87748,7 +87748,7 @@
         <v>2</v>
       </c>
       <c r="G3234" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3235">
@@ -87759,7 +87759,7 @@
         <v>18</v>
       </c>
       <c r="C3235" t="n">
-        <v>33.97</v>
+        <v>33.96</v>
       </c>
       <c r="D3235" t="inlineStr">
         <is>
@@ -87775,7 +87775,7 @@
         <v>2</v>
       </c>
       <c r="G3235" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3236">
@@ -87802,7 +87802,7 @@
         <v>2</v>
       </c>
       <c r="G3236" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3237">
@@ -87829,7 +87829,7 @@
         <v>2</v>
       </c>
       <c r="G3237" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3238">
@@ -87856,7 +87856,7 @@
         <v>2</v>
       </c>
       <c r="G3238" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3239">
@@ -87883,7 +87883,7 @@
         <v>2</v>
       </c>
       <c r="G3239" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3240">
@@ -87910,7 +87910,7 @@
         <v>2</v>
       </c>
       <c r="G3240" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3241">
@@ -87937,7 +87937,7 @@
         <v>2</v>
       </c>
       <c r="G3241" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3242">
@@ -87964,7 +87964,7 @@
         <v>2</v>
       </c>
       <c r="G3242" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3243">
@@ -87991,7 +87991,7 @@
         <v>2</v>
       </c>
       <c r="G3243" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3244">
@@ -88018,7 +88018,7 @@
         <v>2</v>
       </c>
       <c r="G3244" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3245">
@@ -88045,7 +88045,7 @@
         <v>2</v>
       </c>
       <c r="G3245" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3246">
@@ -88056,7 +88056,7 @@
         <v>5</v>
       </c>
       <c r="C3246" t="n">
-        <v>11.41</v>
+        <v>11.4</v>
       </c>
       <c r="D3246" t="inlineStr">
         <is>
@@ -88072,7 +88072,7 @@
         <v>2</v>
       </c>
       <c r="G3246" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3247">
@@ -88099,7 +88099,7 @@
         <v>2</v>
       </c>
       <c r="G3247" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3248">
@@ -88126,7 +88126,7 @@
         <v>2</v>
       </c>
       <c r="G3248" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3249">
@@ -88153,7 +88153,7 @@
         <v>2</v>
       </c>
       <c r="G3249" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3250">
@@ -88180,7 +88180,7 @@
         <v>2</v>
       </c>
       <c r="G3250" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3251">
@@ -88191,7 +88191,7 @@
         <v>10</v>
       </c>
       <c r="C3251" t="n">
-        <v>25.37</v>
+        <v>25.36</v>
       </c>
       <c r="D3251" t="inlineStr">
         <is>
@@ -88207,7 +88207,7 @@
         <v>2</v>
       </c>
       <c r="G3251" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3252">
@@ -88218,7 +88218,7 @@
         <v>11</v>
       </c>
       <c r="C3252" t="n">
-        <v>22.71</v>
+        <v>22.69</v>
       </c>
       <c r="D3252" t="inlineStr">
         <is>
@@ -88234,7 +88234,7 @@
         <v>2</v>
       </c>
       <c r="G3252" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3253">
@@ -88245,7 +88245,7 @@
         <v>12</v>
       </c>
       <c r="C3253" t="n">
-        <v>22.76</v>
+        <v>22.75</v>
       </c>
       <c r="D3253" t="inlineStr">
         <is>
@@ -88261,7 +88261,7 @@
         <v>2</v>
       </c>
       <c r="G3253" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3254">
@@ -88272,7 +88272,7 @@
         <v>13</v>
       </c>
       <c r="C3254" t="n">
-        <v>40.1</v>
+        <v>40.05</v>
       </c>
       <c r="D3254" t="inlineStr">
         <is>
@@ -88288,7 +88288,7 @@
         <v>2</v>
       </c>
       <c r="G3254" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3255">
@@ -88299,7 +88299,7 @@
         <v>14</v>
       </c>
       <c r="C3255" t="n">
-        <v>38.64</v>
+        <v>38.56</v>
       </c>
       <c r="D3255" t="inlineStr">
         <is>
@@ -88315,7 +88315,7 @@
         <v>2</v>
       </c>
       <c r="G3255" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3256">
@@ -88326,7 +88326,7 @@
         <v>15</v>
       </c>
       <c r="C3256" t="n">
-        <v>34.02</v>
+        <v>33.94</v>
       </c>
       <c r="D3256" t="inlineStr">
         <is>
@@ -88342,7 +88342,7 @@
         <v>2</v>
       </c>
       <c r="G3256" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3257">
@@ -88353,7 +88353,7 @@
         <v>16</v>
       </c>
       <c r="C3257" t="n">
-        <v>34.94</v>
+        <v>34.9</v>
       </c>
       <c r="D3257" t="inlineStr">
         <is>
@@ -88369,7 +88369,7 @@
         <v>2</v>
       </c>
       <c r="G3257" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3258">
@@ -88380,7 +88380,7 @@
         <v>17</v>
       </c>
       <c r="C3258" t="n">
-        <v>31.37</v>
+        <v>31.34</v>
       </c>
       <c r="D3258" t="inlineStr">
         <is>
@@ -88396,7 +88396,7 @@
         <v>2</v>
       </c>
       <c r="G3258" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3259">
@@ -88407,7 +88407,7 @@
         <v>18</v>
       </c>
       <c r="C3259" t="n">
-        <v>29.81</v>
+        <v>29.8</v>
       </c>
       <c r="D3259" t="inlineStr">
         <is>
@@ -88423,7 +88423,7 @@
         <v>2</v>
       </c>
       <c r="G3259" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3260">
@@ -88450,7 +88450,7 @@
         <v>2</v>
       </c>
       <c r="G3260" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3261">
@@ -88461,7 +88461,7 @@
         <v>20</v>
       </c>
       <c r="C3261" t="n">
-        <v>18.72</v>
+        <v>18.73</v>
       </c>
       <c r="D3261" t="inlineStr">
         <is>
@@ -88477,7 +88477,7 @@
         <v>2</v>
       </c>
       <c r="G3261" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3262">
@@ -88504,7 +88504,7 @@
         <v>2</v>
       </c>
       <c r="G3262" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3263">
@@ -88531,7 +88531,7 @@
         <v>2</v>
       </c>
       <c r="G3263" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3264">
@@ -88558,7 +88558,7 @@
         <v>2</v>
       </c>
       <c r="G3264" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3265">
@@ -88585,7 +88585,7 @@
         <v>2</v>
       </c>
       <c r="G3265" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3266">
@@ -88596,7 +88596,7 @@
         <v>1</v>
       </c>
       <c r="C3266" t="n">
-        <v>11.94</v>
+        <v>11.8</v>
       </c>
       <c r="D3266" t="inlineStr">
         <is>
@@ -88612,7 +88612,7 @@
         <v>2</v>
       </c>
       <c r="G3266" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3267">
@@ -88623,7 +88623,7 @@
         <v>2</v>
       </c>
       <c r="C3267" t="n">
-        <v>7.6</v>
+        <v>7.83</v>
       </c>
       <c r="D3267" t="inlineStr">
         <is>
@@ -88639,7 +88639,7 @@
         <v>2</v>
       </c>
       <c r="G3267" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3268">
@@ -88650,7 +88650,7 @@
         <v>3</v>
       </c>
       <c r="C3268" t="n">
-        <v>8.25</v>
+        <v>8.42</v>
       </c>
       <c r="D3268" t="inlineStr">
         <is>
@@ -88666,7 +88666,7 @@
         <v>2</v>
       </c>
       <c r="G3268" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3269">
@@ -88677,7 +88677,7 @@
         <v>4</v>
       </c>
       <c r="C3269" t="n">
-        <v>7.46</v>
+        <v>8.01</v>
       </c>
       <c r="D3269" t="inlineStr">
         <is>
@@ -88693,7 +88693,7 @@
         <v>2</v>
       </c>
       <c r="G3269" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3270">
@@ -88704,7 +88704,7 @@
         <v>5</v>
       </c>
       <c r="C3270" t="n">
-        <v>9.24</v>
+        <v>9.74</v>
       </c>
       <c r="D3270" t="inlineStr">
         <is>
@@ -88720,7 +88720,7 @@
         <v>2</v>
       </c>
       <c r="G3270" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3271">
@@ -88731,7 +88731,7 @@
         <v>6</v>
       </c>
       <c r="C3271" t="n">
-        <v>12.03</v>
+        <v>12.34</v>
       </c>
       <c r="D3271" t="inlineStr">
         <is>
@@ -88747,7 +88747,7 @@
         <v>2</v>
       </c>
       <c r="G3271" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3272">
@@ -88758,7 +88758,7 @@
         <v>7</v>
       </c>
       <c r="C3272" t="n">
-        <v>21.71</v>
+        <v>21.69</v>
       </c>
       <c r="D3272" t="inlineStr">
         <is>
@@ -88774,7 +88774,7 @@
         <v>2</v>
       </c>
       <c r="G3272" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3273">
@@ -88785,7 +88785,7 @@
         <v>8</v>
       </c>
       <c r="C3273" t="n">
-        <v>50.2</v>
+        <v>50.02</v>
       </c>
       <c r="D3273" t="inlineStr">
         <is>
@@ -88801,7 +88801,7 @@
         <v>2</v>
       </c>
       <c r="G3273" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3274">
@@ -88812,7 +88812,7 @@
         <v>9</v>
       </c>
       <c r="C3274" t="n">
-        <v>45.02</v>
+        <v>45.25</v>
       </c>
       <c r="D3274" t="inlineStr">
         <is>
@@ -88828,7 +88828,7 @@
         <v>2</v>
       </c>
       <c r="G3274" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3275">
@@ -88839,7 +88839,7 @@
         <v>10</v>
       </c>
       <c r="C3275" t="n">
-        <v>19.73</v>
+        <v>19.69</v>
       </c>
       <c r="D3275" t="inlineStr">
         <is>
@@ -88855,7 +88855,7 @@
         <v>2</v>
       </c>
       <c r="G3275" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3276">
@@ -88866,7 +88866,7 @@
         <v>11</v>
       </c>
       <c r="C3276" t="n">
-        <v>25.19</v>
+        <v>25.05</v>
       </c>
       <c r="D3276" t="inlineStr">
         <is>
@@ -88882,7 +88882,7 @@
         <v>2</v>
       </c>
       <c r="G3276" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3277">
@@ -88909,7 +88909,7 @@
         <v>2</v>
       </c>
       <c r="G3277" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3278">
@@ -88920,7 +88920,7 @@
         <v>13</v>
       </c>
       <c r="C3278" t="n">
-        <v>34.71</v>
+        <v>34.66</v>
       </c>
       <c r="D3278" t="inlineStr">
         <is>
@@ -88936,7 +88936,7 @@
         <v>2</v>
       </c>
       <c r="G3278" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3279">
@@ -88947,7 +88947,7 @@
         <v>14</v>
       </c>
       <c r="C3279" t="n">
-        <v>38.99</v>
+        <v>38.73</v>
       </c>
       <c r="D3279" t="inlineStr">
         <is>
@@ -88963,7 +88963,7 @@
         <v>2</v>
       </c>
       <c r="G3279" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3280">
@@ -88974,7 +88974,7 @@
         <v>15</v>
       </c>
       <c r="C3280" t="n">
-        <v>38.16</v>
+        <v>37.88</v>
       </c>
       <c r="D3280" t="inlineStr">
         <is>
@@ -88990,7 +88990,7 @@
         <v>2</v>
       </c>
       <c r="G3280" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3281">
@@ -89001,7 +89001,7 @@
         <v>16</v>
       </c>
       <c r="C3281" t="n">
-        <v>39.05</v>
+        <v>38.75</v>
       </c>
       <c r="D3281" t="inlineStr">
         <is>
@@ -89017,7 +89017,7 @@
         <v>2</v>
       </c>
       <c r="G3281" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3282">
@@ -89028,7 +89028,7 @@
         <v>17</v>
       </c>
       <c r="C3282" t="n">
-        <v>36.62</v>
+        <v>36.32</v>
       </c>
       <c r="D3282" t="inlineStr">
         <is>
@@ -89044,7 +89044,7 @@
         <v>2</v>
       </c>
       <c r="G3282" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3283">
@@ -89055,7 +89055,7 @@
         <v>18</v>
       </c>
       <c r="C3283" t="n">
-        <v>31</v>
+        <v>30.86</v>
       </c>
       <c r="D3283" t="inlineStr">
         <is>
@@ -89071,7 +89071,7 @@
         <v>2</v>
       </c>
       <c r="G3283" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3284">
@@ -89082,7 +89082,7 @@
         <v>19</v>
       </c>
       <c r="C3284" t="n">
-        <v>15.79</v>
+        <v>16.06</v>
       </c>
       <c r="D3284" t="inlineStr">
         <is>
@@ -89098,7 +89098,7 @@
         <v>2</v>
       </c>
       <c r="G3284" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3285">
@@ -89109,7 +89109,7 @@
         <v>20</v>
       </c>
       <c r="C3285" t="n">
-        <v>19.55</v>
+        <v>19.82</v>
       </c>
       <c r="D3285" t="inlineStr">
         <is>
@@ -89125,7 +89125,7 @@
         <v>2</v>
       </c>
       <c r="G3285" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3286">
@@ -89136,7 +89136,7 @@
         <v>21</v>
       </c>
       <c r="C3286" t="n">
-        <v>41.78</v>
+        <v>41.76</v>
       </c>
       <c r="D3286" t="inlineStr">
         <is>
@@ -89152,7 +89152,7 @@
         <v>2</v>
       </c>
       <c r="G3286" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3287">
@@ -89163,7 +89163,7 @@
         <v>22</v>
       </c>
       <c r="C3287" t="n">
-        <v>42.32</v>
+        <v>42.26</v>
       </c>
       <c r="D3287" t="inlineStr">
         <is>
@@ -89179,7 +89179,7 @@
         <v>2</v>
       </c>
       <c r="G3287" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3288">
@@ -89190,7 +89190,7 @@
         <v>23</v>
       </c>
       <c r="C3288" t="n">
-        <v>48.36</v>
+        <v>48.28</v>
       </c>
       <c r="D3288" t="inlineStr">
         <is>
@@ -89206,7 +89206,7 @@
         <v>2</v>
       </c>
       <c r="G3288" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3289">
@@ -89217,7 +89217,7 @@
         <v>24</v>
       </c>
       <c r="C3289" t="n">
-        <v>25.59</v>
+        <v>25.58</v>
       </c>
       <c r="D3289" t="inlineStr">
         <is>
@@ -89233,7 +89233,7 @@
         <v>2</v>
       </c>
       <c r="G3289" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3290">
@@ -89244,7 +89244,7 @@
         <v>1</v>
       </c>
       <c r="C3290" t="n">
-        <v>6.18</v>
+        <v>6.23</v>
       </c>
       <c r="D3290" t="inlineStr">
         <is>
@@ -89260,7 +89260,7 @@
         <v>2</v>
       </c>
       <c r="G3290" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3291">
@@ -89271,7 +89271,7 @@
         <v>2</v>
       </c>
       <c r="C3291" t="n">
-        <v>5.34</v>
+        <v>5.49</v>
       </c>
       <c r="D3291" t="inlineStr">
         <is>
@@ -89287,7 +89287,7 @@
         <v>2</v>
       </c>
       <c r="G3291" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3292">
@@ -89298,7 +89298,7 @@
         <v>3</v>
       </c>
       <c r="C3292" t="n">
-        <v>7.07</v>
+        <v>7.29</v>
       </c>
       <c r="D3292" t="inlineStr">
         <is>
@@ -89314,7 +89314,7 @@
         <v>2</v>
       </c>
       <c r="G3292" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3293">
@@ -89325,7 +89325,7 @@
         <v>4</v>
       </c>
       <c r="C3293" t="n">
-        <v>5.69</v>
+        <v>5.88</v>
       </c>
       <c r="D3293" t="inlineStr">
         <is>
@@ -89341,7 +89341,7 @@
         <v>2</v>
       </c>
       <c r="G3293" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3294">
@@ -89352,7 +89352,7 @@
         <v>5</v>
       </c>
       <c r="C3294" t="n">
-        <v>9.06</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="D3294" t="inlineStr">
         <is>
@@ -89368,7 +89368,7 @@
         <v>2</v>
       </c>
       <c r="G3294" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3295">
@@ -89379,7 +89379,7 @@
         <v>6</v>
       </c>
       <c r="C3295" t="n">
-        <v>10.24</v>
+        <v>10.53</v>
       </c>
       <c r="D3295" t="inlineStr">
         <is>
@@ -89395,7 +89395,7 @@
         <v>2</v>
       </c>
       <c r="G3295" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3296">
@@ -89406,7 +89406,7 @@
         <v>7</v>
       </c>
       <c r="C3296" t="n">
-        <v>31.44</v>
+        <v>38.03</v>
       </c>
       <c r="D3296" t="inlineStr">
         <is>
@@ -89422,7 +89422,7 @@
         <v>2</v>
       </c>
       <c r="G3296" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3297">
@@ -89433,7 +89433,7 @@
         <v>8</v>
       </c>
       <c r="C3297" t="n">
-        <v>38.05</v>
+        <v>45.48</v>
       </c>
       <c r="D3297" t="inlineStr">
         <is>
@@ -89449,7 +89449,7 @@
         <v>2</v>
       </c>
       <c r="G3297" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3298">
@@ -89460,7 +89460,7 @@
         <v>9</v>
       </c>
       <c r="C3298" t="n">
-        <v>23.41</v>
+        <v>26.09</v>
       </c>
       <c r="D3298" t="inlineStr">
         <is>
@@ -89476,7 +89476,7 @@
         <v>2</v>
       </c>
       <c r="G3298" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3299">
@@ -89487,7 +89487,7 @@
         <v>10</v>
       </c>
       <c r="C3299" t="n">
-        <v>16.2</v>
+        <v>17.2</v>
       </c>
       <c r="D3299" t="inlineStr">
         <is>
@@ -89503,7 +89503,7 @@
         <v>2</v>
       </c>
       <c r="G3299" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3300">
@@ -89514,7 +89514,7 @@
         <v>11</v>
       </c>
       <c r="C3300" t="n">
-        <v>20.8</v>
+        <v>20.79</v>
       </c>
       <c r="D3300" t="inlineStr">
         <is>
@@ -89530,7 +89530,7 @@
         <v>2</v>
       </c>
       <c r="G3300" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3301">
@@ -89541,7 +89541,7 @@
         <v>12</v>
       </c>
       <c r="C3301" t="n">
-        <v>23.33</v>
+        <v>23.86</v>
       </c>
       <c r="D3301" t="inlineStr">
         <is>
@@ -89557,7 +89557,7 @@
         <v>2</v>
       </c>
       <c r="G3301" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3302">
@@ -89568,7 +89568,7 @@
         <v>13</v>
       </c>
       <c r="C3302" t="n">
-        <v>27.34</v>
+        <v>27.05</v>
       </c>
       <c r="D3302" t="inlineStr">
         <is>
@@ -89584,7 +89584,7 @@
         <v>2</v>
       </c>
       <c r="G3302" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3303">
@@ -89595,7 +89595,7 @@
         <v>14</v>
       </c>
       <c r="C3303" t="n">
-        <v>27.79</v>
+        <v>27.55</v>
       </c>
       <c r="D3303" t="inlineStr">
         <is>
@@ -89611,7 +89611,7 @@
         <v>2</v>
       </c>
       <c r="G3303" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3304">
@@ -89622,7 +89622,7 @@
         <v>15</v>
       </c>
       <c r="C3304" t="n">
-        <v>28.99</v>
+        <v>28.61</v>
       </c>
       <c r="D3304" t="inlineStr">
         <is>
@@ -89638,7 +89638,7 @@
         <v>2</v>
       </c>
       <c r="G3304" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3305">
@@ -89649,7 +89649,7 @@
         <v>16</v>
       </c>
       <c r="C3305" t="n">
-        <v>31.3</v>
+        <v>30.7</v>
       </c>
       <c r="D3305" t="inlineStr">
         <is>
@@ -89665,7 +89665,7 @@
         <v>2</v>
       </c>
       <c r="G3305" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3306">
@@ -89676,7 +89676,7 @@
         <v>17</v>
       </c>
       <c r="C3306" t="n">
-        <v>29.49</v>
+        <v>29.4</v>
       </c>
       <c r="D3306" t="inlineStr">
         <is>
@@ -89692,7 +89692,7 @@
         <v>2</v>
       </c>
       <c r="G3306" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3307">
@@ -89703,7 +89703,7 @@
         <v>18</v>
       </c>
       <c r="C3307" t="n">
-        <v>24.22</v>
+        <v>24.49</v>
       </c>
       <c r="D3307" t="inlineStr">
         <is>
@@ -89719,7 +89719,7 @@
         <v>2</v>
       </c>
       <c r="G3307" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3308">
@@ -89730,7 +89730,7 @@
         <v>19</v>
       </c>
       <c r="C3308" t="n">
-        <v>17.41</v>
+        <v>18.3</v>
       </c>
       <c r="D3308" t="inlineStr">
         <is>
@@ -89746,7 +89746,7 @@
         <v>2</v>
       </c>
       <c r="G3308" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3309">
@@ -89757,7 +89757,7 @@
         <v>20</v>
       </c>
       <c r="C3309" t="n">
-        <v>28.22</v>
+        <v>30.57</v>
       </c>
       <c r="D3309" t="inlineStr">
         <is>
@@ -89773,7 +89773,7 @@
         <v>2</v>
       </c>
       <c r="G3309" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3310">
@@ -89784,7 +89784,7 @@
         <v>21</v>
       </c>
       <c r="C3310" t="n">
-        <v>44.24</v>
+        <v>52.78</v>
       </c>
       <c r="D3310" t="inlineStr">
         <is>
@@ -89800,7 +89800,7 @@
         <v>2</v>
       </c>
       <c r="G3310" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3311">
@@ -89811,7 +89811,7 @@
         <v>22</v>
       </c>
       <c r="C3311" t="n">
-        <v>40.9</v>
+        <v>47.42</v>
       </c>
       <c r="D3311" t="inlineStr">
         <is>
@@ -89827,7 +89827,7 @@
         <v>2</v>
       </c>
       <c r="G3311" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3312">
@@ -89838,7 +89838,7 @@
         <v>23</v>
       </c>
       <c r="C3312" t="n">
-        <v>23.48</v>
+        <v>23.55</v>
       </c>
       <c r="D3312" t="inlineStr">
         <is>
@@ -89854,7 +89854,7 @@
         <v>2</v>
       </c>
       <c r="G3312" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
     <row r="3313">
@@ -89865,7 +89865,7 @@
         <v>24</v>
       </c>
       <c r="C3313" t="n">
-        <v>18.86</v>
+        <v>19.32</v>
       </c>
       <c r="D3313" t="inlineStr">
         <is>
@@ -89881,7 +89881,7 @@
         <v>2</v>
       </c>
       <c r="G3313" s="2" t="n">
-        <v>46281.87302596348</v>
+        <v>46282.46141540139</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3313"/>
+  <dimension ref="A1:G3361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80188,7 +80188,7 @@
         <v>2</v>
       </c>
       <c r="G2954" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2955">
@@ -80215,7 +80215,7 @@
         <v>2</v>
       </c>
       <c r="G2955" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2956">
@@ -80242,7 +80242,7 @@
         <v>2</v>
       </c>
       <c r="G2956" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2957">
@@ -80269,7 +80269,7 @@
         <v>2</v>
       </c>
       <c r="G2957" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2958">
@@ -80296,7 +80296,7 @@
         <v>2</v>
       </c>
       <c r="G2958" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2959">
@@ -80323,7 +80323,7 @@
         <v>2</v>
       </c>
       <c r="G2959" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2960">
@@ -80350,7 +80350,7 @@
         <v>2</v>
       </c>
       <c r="G2960" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2961">
@@ -80377,7 +80377,7 @@
         <v>2</v>
       </c>
       <c r="G2961" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2962">
@@ -80404,7 +80404,7 @@
         <v>2</v>
       </c>
       <c r="G2962" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2963">
@@ -80431,7 +80431,7 @@
         <v>2</v>
       </c>
       <c r="G2963" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2964">
@@ -80458,7 +80458,7 @@
         <v>2</v>
       </c>
       <c r="G2964" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2965">
@@ -80485,7 +80485,7 @@
         <v>2</v>
       </c>
       <c r="G2965" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2966">
@@ -80512,7 +80512,7 @@
         <v>2</v>
       </c>
       <c r="G2966" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2967">
@@ -80539,7 +80539,7 @@
         <v>2</v>
       </c>
       <c r="G2967" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2968">
@@ -80566,7 +80566,7 @@
         <v>2</v>
       </c>
       <c r="G2968" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2969">
@@ -80593,7 +80593,7 @@
         <v>2</v>
       </c>
       <c r="G2969" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2970">
@@ -80620,7 +80620,7 @@
         <v>2</v>
       </c>
       <c r="G2970" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2971">
@@ -80647,7 +80647,7 @@
         <v>2</v>
       </c>
       <c r="G2971" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2972">
@@ -80674,7 +80674,7 @@
         <v>2</v>
       </c>
       <c r="G2972" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2973">
@@ -80701,7 +80701,7 @@
         <v>2</v>
       </c>
       <c r="G2973" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2974">
@@ -80728,7 +80728,7 @@
         <v>2</v>
       </c>
       <c r="G2974" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2975">
@@ -80755,7 +80755,7 @@
         <v>2</v>
       </c>
       <c r="G2975" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2976">
@@ -80782,7 +80782,7 @@
         <v>2</v>
       </c>
       <c r="G2976" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2977">
@@ -80809,7 +80809,7 @@
         <v>2</v>
       </c>
       <c r="G2977" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2978">
@@ -80836,7 +80836,7 @@
         <v>2</v>
       </c>
       <c r="G2978" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2979">
@@ -80863,7 +80863,7 @@
         <v>2</v>
       </c>
       <c r="G2979" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2980">
@@ -80890,7 +80890,7 @@
         <v>2</v>
       </c>
       <c r="G2980" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2981">
@@ -80917,7 +80917,7 @@
         <v>2</v>
       </c>
       <c r="G2981" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2982">
@@ -80944,7 +80944,7 @@
         <v>2</v>
       </c>
       <c r="G2982" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2983">
@@ -80971,7 +80971,7 @@
         <v>2</v>
       </c>
       <c r="G2983" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2984">
@@ -80998,7 +80998,7 @@
         <v>2</v>
       </c>
       <c r="G2984" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2985">
@@ -81025,7 +81025,7 @@
         <v>2</v>
       </c>
       <c r="G2985" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2986">
@@ -81052,7 +81052,7 @@
         <v>2</v>
       </c>
       <c r="G2986" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2987">
@@ -81079,7 +81079,7 @@
         <v>2</v>
       </c>
       <c r="G2987" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2988">
@@ -81106,7 +81106,7 @@
         <v>2</v>
       </c>
       <c r="G2988" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2989">
@@ -81133,7 +81133,7 @@
         <v>2</v>
       </c>
       <c r="G2989" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2990">
@@ -81160,7 +81160,7 @@
         <v>2</v>
       </c>
       <c r="G2990" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2991">
@@ -81187,7 +81187,7 @@
         <v>2</v>
       </c>
       <c r="G2991" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2992">
@@ -81214,7 +81214,7 @@
         <v>2</v>
       </c>
       <c r="G2992" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2993">
@@ -81241,7 +81241,7 @@
         <v>2</v>
       </c>
       <c r="G2993" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2994">
@@ -81268,7 +81268,7 @@
         <v>2</v>
       </c>
       <c r="G2994" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2995">
@@ -81295,7 +81295,7 @@
         <v>2</v>
       </c>
       <c r="G2995" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2996">
@@ -81322,7 +81322,7 @@
         <v>2</v>
       </c>
       <c r="G2996" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2997">
@@ -81349,7 +81349,7 @@
         <v>2</v>
       </c>
       <c r="G2997" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2998">
@@ -81376,7 +81376,7 @@
         <v>2</v>
       </c>
       <c r="G2998" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="2999">
@@ -81403,7 +81403,7 @@
         <v>2</v>
       </c>
       <c r="G2999" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3000">
@@ -81430,7 +81430,7 @@
         <v>2</v>
       </c>
       <c r="G3000" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3001">
@@ -81457,7 +81457,7 @@
         <v>2</v>
       </c>
       <c r="G3001" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3002">
@@ -81484,7 +81484,7 @@
         <v>2</v>
       </c>
       <c r="G3002" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3003">
@@ -81511,7 +81511,7 @@
         <v>2</v>
       </c>
       <c r="G3003" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3004">
@@ -81538,7 +81538,7 @@
         <v>2</v>
       </c>
       <c r="G3004" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3005">
@@ -81565,7 +81565,7 @@
         <v>2</v>
       </c>
       <c r="G3005" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3006">
@@ -81592,7 +81592,7 @@
         <v>2</v>
       </c>
       <c r="G3006" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3007">
@@ -81619,7 +81619,7 @@
         <v>2</v>
       </c>
       <c r="G3007" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3008">
@@ -81646,7 +81646,7 @@
         <v>2</v>
       </c>
       <c r="G3008" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3009">
@@ -81673,7 +81673,7 @@
         <v>2</v>
       </c>
       <c r="G3009" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3010">
@@ -81700,7 +81700,7 @@
         <v>2</v>
       </c>
       <c r="G3010" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3011">
@@ -81727,7 +81727,7 @@
         <v>2</v>
       </c>
       <c r="G3011" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3012">
@@ -81754,7 +81754,7 @@
         <v>2</v>
       </c>
       <c r="G3012" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3013">
@@ -81781,7 +81781,7 @@
         <v>2</v>
       </c>
       <c r="G3013" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3014">
@@ -81808,7 +81808,7 @@
         <v>2</v>
       </c>
       <c r="G3014" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3015">
@@ -81835,7 +81835,7 @@
         <v>2</v>
       </c>
       <c r="G3015" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3016">
@@ -81862,7 +81862,7 @@
         <v>2</v>
       </c>
       <c r="G3016" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3017">
@@ -81889,7 +81889,7 @@
         <v>2</v>
       </c>
       <c r="G3017" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3018">
@@ -81916,7 +81916,7 @@
         <v>2</v>
       </c>
       <c r="G3018" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3019">
@@ -81943,7 +81943,7 @@
         <v>2</v>
       </c>
       <c r="G3019" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3020">
@@ -81970,7 +81970,7 @@
         <v>2</v>
       </c>
       <c r="G3020" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3021">
@@ -81997,7 +81997,7 @@
         <v>2</v>
       </c>
       <c r="G3021" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3022">
@@ -82024,7 +82024,7 @@
         <v>2</v>
       </c>
       <c r="G3022" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3023">
@@ -82051,7 +82051,7 @@
         <v>2</v>
       </c>
       <c r="G3023" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3024">
@@ -82078,7 +82078,7 @@
         <v>2</v>
       </c>
       <c r="G3024" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3025">
@@ -82105,7 +82105,7 @@
         <v>2</v>
       </c>
       <c r="G3025" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3026">
@@ -82132,7 +82132,7 @@
         <v>2</v>
       </c>
       <c r="G3026" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3027">
@@ -82159,7 +82159,7 @@
         <v>2</v>
       </c>
       <c r="G3027" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3028">
@@ -82186,7 +82186,7 @@
         <v>2</v>
       </c>
       <c r="G3028" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3029">
@@ -82213,7 +82213,7 @@
         <v>2</v>
       </c>
       <c r="G3029" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3030">
@@ -82240,7 +82240,7 @@
         <v>2</v>
       </c>
       <c r="G3030" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3031">
@@ -82267,7 +82267,7 @@
         <v>2</v>
       </c>
       <c r="G3031" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3032">
@@ -82294,7 +82294,7 @@
         <v>2</v>
       </c>
       <c r="G3032" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3033">
@@ -82321,7 +82321,7 @@
         <v>2</v>
       </c>
       <c r="G3033" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3034">
@@ -82348,7 +82348,7 @@
         <v>2</v>
       </c>
       <c r="G3034" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3035">
@@ -82375,7 +82375,7 @@
         <v>2</v>
       </c>
       <c r="G3035" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3036">
@@ -82402,7 +82402,7 @@
         <v>2</v>
       </c>
       <c r="G3036" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3037">
@@ -82429,7 +82429,7 @@
         <v>2</v>
       </c>
       <c r="G3037" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3038">
@@ -82456,7 +82456,7 @@
         <v>2</v>
       </c>
       <c r="G3038" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3039">
@@ -82483,7 +82483,7 @@
         <v>2</v>
       </c>
       <c r="G3039" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3040">
@@ -82510,7 +82510,7 @@
         <v>2</v>
       </c>
       <c r="G3040" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3041">
@@ -82537,7 +82537,7 @@
         <v>2</v>
       </c>
       <c r="G3041" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3042">
@@ -82564,7 +82564,7 @@
         <v>2</v>
       </c>
       <c r="G3042" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3043">
@@ -82591,7 +82591,7 @@
         <v>2</v>
       </c>
       <c r="G3043" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3044">
@@ -82618,7 +82618,7 @@
         <v>2</v>
       </c>
       <c r="G3044" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3045">
@@ -82645,7 +82645,7 @@
         <v>2</v>
       </c>
       <c r="G3045" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3046">
@@ -82672,7 +82672,7 @@
         <v>2</v>
       </c>
       <c r="G3046" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3047">
@@ -82699,7 +82699,7 @@
         <v>2</v>
       </c>
       <c r="G3047" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3048">
@@ -82726,7 +82726,7 @@
         <v>2</v>
       </c>
       <c r="G3048" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3049">
@@ -82753,7 +82753,7 @@
         <v>2</v>
       </c>
       <c r="G3049" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3050">
@@ -82780,7 +82780,7 @@
         <v>2</v>
       </c>
       <c r="G3050" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3051">
@@ -82807,7 +82807,7 @@
         <v>2</v>
       </c>
       <c r="G3051" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3052">
@@ -82834,7 +82834,7 @@
         <v>2</v>
       </c>
       <c r="G3052" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3053">
@@ -82861,7 +82861,7 @@
         <v>2</v>
       </c>
       <c r="G3053" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3054">
@@ -82888,7 +82888,7 @@
         <v>2</v>
       </c>
       <c r="G3054" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3055">
@@ -82915,7 +82915,7 @@
         <v>2</v>
       </c>
       <c r="G3055" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3056">
@@ -82942,7 +82942,7 @@
         <v>2</v>
       </c>
       <c r="G3056" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3057">
@@ -82969,7 +82969,7 @@
         <v>2</v>
       </c>
       <c r="G3057" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3058">
@@ -82996,7 +82996,7 @@
         <v>2</v>
       </c>
       <c r="G3058" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3059">
@@ -83023,7 +83023,7 @@
         <v>2</v>
       </c>
       <c r="G3059" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3060">
@@ -83050,7 +83050,7 @@
         <v>2</v>
       </c>
       <c r="G3060" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3061">
@@ -83077,7 +83077,7 @@
         <v>2</v>
       </c>
       <c r="G3061" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3062">
@@ -83104,7 +83104,7 @@
         <v>2</v>
       </c>
       <c r="G3062" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3063">
@@ -83131,7 +83131,7 @@
         <v>2</v>
       </c>
       <c r="G3063" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3064">
@@ -83158,7 +83158,7 @@
         <v>2</v>
       </c>
       <c r="G3064" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3065">
@@ -83185,7 +83185,7 @@
         <v>2</v>
       </c>
       <c r="G3065" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3066">
@@ -83212,7 +83212,7 @@
         <v>2</v>
       </c>
       <c r="G3066" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3067">
@@ -83239,7 +83239,7 @@
         <v>2</v>
       </c>
       <c r="G3067" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3068">
@@ -83266,7 +83266,7 @@
         <v>2</v>
       </c>
       <c r="G3068" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3069">
@@ -83293,7 +83293,7 @@
         <v>2</v>
       </c>
       <c r="G3069" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3070">
@@ -83320,7 +83320,7 @@
         <v>2</v>
       </c>
       <c r="G3070" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3071">
@@ -83347,7 +83347,7 @@
         <v>2</v>
       </c>
       <c r="G3071" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3072">
@@ -83374,7 +83374,7 @@
         <v>2</v>
       </c>
       <c r="G3072" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3073">
@@ -83401,7 +83401,7 @@
         <v>2</v>
       </c>
       <c r="G3073" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3074">
@@ -83428,7 +83428,7 @@
         <v>2</v>
       </c>
       <c r="G3074" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3075">
@@ -83455,7 +83455,7 @@
         <v>2</v>
       </c>
       <c r="G3075" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3076">
@@ -83482,7 +83482,7 @@
         <v>2</v>
       </c>
       <c r="G3076" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3077">
@@ -83509,7 +83509,7 @@
         <v>2</v>
       </c>
       <c r="G3077" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3078">
@@ -83536,7 +83536,7 @@
         <v>2</v>
       </c>
       <c r="G3078" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3079">
@@ -83563,7 +83563,7 @@
         <v>2</v>
       </c>
       <c r="G3079" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3080">
@@ -83590,7 +83590,7 @@
         <v>2</v>
       </c>
       <c r="G3080" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3081">
@@ -83617,7 +83617,7 @@
         <v>2</v>
       </c>
       <c r="G3081" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3082">
@@ -83644,7 +83644,7 @@
         <v>2</v>
       </c>
       <c r="G3082" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3083">
@@ -83671,7 +83671,7 @@
         <v>2</v>
       </c>
       <c r="G3083" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3084">
@@ -83698,7 +83698,7 @@
         <v>2</v>
       </c>
       <c r="G3084" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3085">
@@ -83725,7 +83725,7 @@
         <v>2</v>
       </c>
       <c r="G3085" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3086">
@@ -83752,7 +83752,7 @@
         <v>2</v>
       </c>
       <c r="G3086" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3087">
@@ -83779,7 +83779,7 @@
         <v>2</v>
       </c>
       <c r="G3087" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3088">
@@ -83806,7 +83806,7 @@
         <v>2</v>
       </c>
       <c r="G3088" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3089">
@@ -83833,7 +83833,7 @@
         <v>2</v>
       </c>
       <c r="G3089" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3090">
@@ -83860,7 +83860,7 @@
         <v>2</v>
       </c>
       <c r="G3090" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3091">
@@ -83887,7 +83887,7 @@
         <v>2</v>
       </c>
       <c r="G3091" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3092">
@@ -83914,7 +83914,7 @@
         <v>2</v>
       </c>
       <c r="G3092" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3093">
@@ -83941,7 +83941,7 @@
         <v>2</v>
       </c>
       <c r="G3093" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3094">
@@ -83968,7 +83968,7 @@
         <v>2</v>
       </c>
       <c r="G3094" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3095">
@@ -83995,7 +83995,7 @@
         <v>2</v>
       </c>
       <c r="G3095" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3096">
@@ -84022,7 +84022,7 @@
         <v>2</v>
       </c>
       <c r="G3096" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3097">
@@ -84049,7 +84049,7 @@
         <v>2</v>
       </c>
       <c r="G3097" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3098">
@@ -84076,7 +84076,7 @@
         <v>2</v>
       </c>
       <c r="G3098" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3099">
@@ -84103,7 +84103,7 @@
         <v>2</v>
       </c>
       <c r="G3099" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3100">
@@ -84130,7 +84130,7 @@
         <v>2</v>
       </c>
       <c r="G3100" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3101">
@@ -84157,7 +84157,7 @@
         <v>2</v>
       </c>
       <c r="G3101" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3102">
@@ -84184,7 +84184,7 @@
         <v>2</v>
       </c>
       <c r="G3102" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3103">
@@ -84211,7 +84211,7 @@
         <v>2</v>
       </c>
       <c r="G3103" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3104">
@@ -84238,7 +84238,7 @@
         <v>2</v>
       </c>
       <c r="G3104" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3105">
@@ -84265,7 +84265,7 @@
         <v>2</v>
       </c>
       <c r="G3105" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3106">
@@ -84292,7 +84292,7 @@
         <v>2</v>
       </c>
       <c r="G3106" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3107">
@@ -84319,7 +84319,7 @@
         <v>2</v>
       </c>
       <c r="G3107" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3108">
@@ -84346,7 +84346,7 @@
         <v>2</v>
       </c>
       <c r="G3108" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3109">
@@ -84373,7 +84373,7 @@
         <v>2</v>
       </c>
       <c r="G3109" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3110">
@@ -84400,7 +84400,7 @@
         <v>2</v>
       </c>
       <c r="G3110" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3111">
@@ -84427,7 +84427,7 @@
         <v>2</v>
       </c>
       <c r="G3111" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3112">
@@ -84454,7 +84454,7 @@
         <v>2</v>
       </c>
       <c r="G3112" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3113">
@@ -84481,7 +84481,7 @@
         <v>2</v>
       </c>
       <c r="G3113" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3114">
@@ -84508,7 +84508,7 @@
         <v>2</v>
       </c>
       <c r="G3114" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3115">
@@ -84535,7 +84535,7 @@
         <v>2</v>
       </c>
       <c r="G3115" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3116">
@@ -84562,7 +84562,7 @@
         <v>2</v>
       </c>
       <c r="G3116" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3117">
@@ -84589,7 +84589,7 @@
         <v>2</v>
       </c>
       <c r="G3117" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3118">
@@ -84616,7 +84616,7 @@
         <v>2</v>
       </c>
       <c r="G3118" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3119">
@@ -84643,7 +84643,7 @@
         <v>2</v>
       </c>
       <c r="G3119" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3120">
@@ -84670,7 +84670,7 @@
         <v>2</v>
       </c>
       <c r="G3120" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3121">
@@ -84697,7 +84697,7 @@
         <v>2</v>
       </c>
       <c r="G3121" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3122">
@@ -84724,7 +84724,7 @@
         <v>2</v>
       </c>
       <c r="G3122" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3123">
@@ -84751,7 +84751,7 @@
         <v>2</v>
       </c>
       <c r="G3123" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3124">
@@ -84778,7 +84778,7 @@
         <v>2</v>
       </c>
       <c r="G3124" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3125">
@@ -84805,7 +84805,7 @@
         <v>2</v>
       </c>
       <c r="G3125" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3126">
@@ -84832,7 +84832,7 @@
         <v>2</v>
       </c>
       <c r="G3126" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3127">
@@ -84859,7 +84859,7 @@
         <v>2</v>
       </c>
       <c r="G3127" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3128">
@@ -84886,7 +84886,7 @@
         <v>2</v>
       </c>
       <c r="G3128" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3129">
@@ -84913,7 +84913,7 @@
         <v>2</v>
       </c>
       <c r="G3129" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3130">
@@ -84940,7 +84940,7 @@
         <v>2</v>
       </c>
       <c r="G3130" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3131">
@@ -84967,7 +84967,7 @@
         <v>2</v>
       </c>
       <c r="G3131" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3132">
@@ -84994,7 +84994,7 @@
         <v>2</v>
       </c>
       <c r="G3132" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3133">
@@ -85021,7 +85021,7 @@
         <v>2</v>
       </c>
       <c r="G3133" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3134">
@@ -85048,7 +85048,7 @@
         <v>2</v>
       </c>
       <c r="G3134" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3135">
@@ -85075,7 +85075,7 @@
         <v>2</v>
       </c>
       <c r="G3135" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3136">
@@ -85102,7 +85102,7 @@
         <v>2</v>
       </c>
       <c r="G3136" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3137">
@@ -85129,7 +85129,7 @@
         <v>2</v>
       </c>
       <c r="G3137" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3138">
@@ -85156,7 +85156,7 @@
         <v>2</v>
       </c>
       <c r="G3138" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3139">
@@ -85183,7 +85183,7 @@
         <v>2</v>
       </c>
       <c r="G3139" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3140">
@@ -85210,7 +85210,7 @@
         <v>2</v>
       </c>
       <c r="G3140" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3141">
@@ -85237,7 +85237,7 @@
         <v>2</v>
       </c>
       <c r="G3141" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3142">
@@ -85264,7 +85264,7 @@
         <v>2</v>
       </c>
       <c r="G3142" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3143">
@@ -85291,7 +85291,7 @@
         <v>2</v>
       </c>
       <c r="G3143" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3144">
@@ -85318,7 +85318,7 @@
         <v>2</v>
       </c>
       <c r="G3144" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3145">
@@ -85345,7 +85345,7 @@
         <v>2</v>
       </c>
       <c r="G3145" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3146">
@@ -85372,7 +85372,7 @@
         <v>2</v>
       </c>
       <c r="G3146" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3147">
@@ -85399,7 +85399,7 @@
         <v>2</v>
       </c>
       <c r="G3147" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3148">
@@ -85426,7 +85426,7 @@
         <v>2</v>
       </c>
       <c r="G3148" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3149">
@@ -85453,7 +85453,7 @@
         <v>2</v>
       </c>
       <c r="G3149" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3150">
@@ -85480,7 +85480,7 @@
         <v>2</v>
       </c>
       <c r="G3150" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3151">
@@ -85507,7 +85507,7 @@
         <v>2</v>
       </c>
       <c r="G3151" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3152">
@@ -85534,7 +85534,7 @@
         <v>2</v>
       </c>
       <c r="G3152" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3153">
@@ -85561,7 +85561,7 @@
         <v>2</v>
       </c>
       <c r="G3153" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3154">
@@ -85588,7 +85588,7 @@
         <v>2</v>
       </c>
       <c r="G3154" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3155">
@@ -85615,7 +85615,7 @@
         <v>2</v>
       </c>
       <c r="G3155" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3156">
@@ -85642,7 +85642,7 @@
         <v>2</v>
       </c>
       <c r="G3156" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3157">
@@ -85669,7 +85669,7 @@
         <v>2</v>
       </c>
       <c r="G3157" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3158">
@@ -85696,7 +85696,7 @@
         <v>2</v>
       </c>
       <c r="G3158" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3159">
@@ -85723,7 +85723,7 @@
         <v>2</v>
       </c>
       <c r="G3159" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3160">
@@ -85750,7 +85750,7 @@
         <v>2</v>
       </c>
       <c r="G3160" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3161">
@@ -85777,7 +85777,7 @@
         <v>2</v>
       </c>
       <c r="G3161" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3162">
@@ -85804,7 +85804,7 @@
         <v>2</v>
       </c>
       <c r="G3162" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3163">
@@ -85831,7 +85831,7 @@
         <v>2</v>
       </c>
       <c r="G3163" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3164">
@@ -85858,7 +85858,7 @@
         <v>2</v>
       </c>
       <c r="G3164" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3165">
@@ -85885,7 +85885,7 @@
         <v>2</v>
       </c>
       <c r="G3165" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3166">
@@ -85912,7 +85912,7 @@
         <v>2</v>
       </c>
       <c r="G3166" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3167">
@@ -85939,7 +85939,7 @@
         <v>2</v>
       </c>
       <c r="G3167" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3168">
@@ -85966,7 +85966,7 @@
         <v>2</v>
       </c>
       <c r="G3168" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3169">
@@ -85993,7 +85993,7 @@
         <v>2</v>
       </c>
       <c r="G3169" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3170">
@@ -86020,7 +86020,7 @@
         <v>2</v>
       </c>
       <c r="G3170" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3171">
@@ -86047,7 +86047,7 @@
         <v>2</v>
       </c>
       <c r="G3171" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3172">
@@ -86074,7 +86074,7 @@
         <v>2</v>
       </c>
       <c r="G3172" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3173">
@@ -86101,7 +86101,7 @@
         <v>2</v>
       </c>
       <c r="G3173" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3174">
@@ -86128,7 +86128,7 @@
         <v>2</v>
       </c>
       <c r="G3174" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3175">
@@ -86155,7 +86155,7 @@
         <v>2</v>
       </c>
       <c r="G3175" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3176">
@@ -86182,7 +86182,7 @@
         <v>2</v>
       </c>
       <c r="G3176" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3177">
@@ -86209,7 +86209,7 @@
         <v>2</v>
       </c>
       <c r="G3177" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3178">
@@ -86236,7 +86236,7 @@
         <v>2</v>
       </c>
       <c r="G3178" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3179">
@@ -86263,7 +86263,7 @@
         <v>2</v>
       </c>
       <c r="G3179" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3180">
@@ -86290,7 +86290,7 @@
         <v>2</v>
       </c>
       <c r="G3180" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3181">
@@ -86317,7 +86317,7 @@
         <v>2</v>
       </c>
       <c r="G3181" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3182">
@@ -86344,7 +86344,7 @@
         <v>2</v>
       </c>
       <c r="G3182" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3183">
@@ -86371,7 +86371,7 @@
         <v>2</v>
       </c>
       <c r="G3183" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3184">
@@ -86398,7 +86398,7 @@
         <v>2</v>
       </c>
       <c r="G3184" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3185">
@@ -86425,7 +86425,7 @@
         <v>2</v>
       </c>
       <c r="G3185" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3186">
@@ -86452,7 +86452,7 @@
         <v>2</v>
       </c>
       <c r="G3186" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3187">
@@ -86479,7 +86479,7 @@
         <v>2</v>
       </c>
       <c r="G3187" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3188">
@@ -86506,7 +86506,7 @@
         <v>2</v>
       </c>
       <c r="G3188" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3189">
@@ -86533,7 +86533,7 @@
         <v>2</v>
       </c>
       <c r="G3189" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3190">
@@ -86560,7 +86560,7 @@
         <v>2</v>
       </c>
       <c r="G3190" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3191">
@@ -86587,7 +86587,7 @@
         <v>2</v>
       </c>
       <c r="G3191" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3192">
@@ -86614,7 +86614,7 @@
         <v>2</v>
       </c>
       <c r="G3192" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3193">
@@ -86641,7 +86641,7 @@
         <v>2</v>
       </c>
       <c r="G3193" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3194">
@@ -86668,7 +86668,7 @@
         <v>2</v>
       </c>
       <c r="G3194" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3195">
@@ -86695,7 +86695,7 @@
         <v>2</v>
       </c>
       <c r="G3195" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3196">
@@ -86722,7 +86722,7 @@
         <v>2</v>
       </c>
       <c r="G3196" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3197">
@@ -86749,7 +86749,7 @@
         <v>2</v>
       </c>
       <c r="G3197" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3198">
@@ -86776,7 +86776,7 @@
         <v>2</v>
       </c>
       <c r="G3198" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3199">
@@ -86803,7 +86803,7 @@
         <v>2</v>
       </c>
       <c r="G3199" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3200">
@@ -86830,7 +86830,7 @@
         <v>2</v>
       </c>
       <c r="G3200" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3201">
@@ -86857,7 +86857,7 @@
         <v>2</v>
       </c>
       <c r="G3201" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3202">
@@ -86884,7 +86884,7 @@
         <v>2</v>
       </c>
       <c r="G3202" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3203">
@@ -86911,7 +86911,7 @@
         <v>2</v>
       </c>
       <c r="G3203" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3204">
@@ -86938,7 +86938,7 @@
         <v>2</v>
       </c>
       <c r="G3204" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3205">
@@ -86965,7 +86965,7 @@
         <v>2</v>
       </c>
       <c r="G3205" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3206">
@@ -86992,7 +86992,7 @@
         <v>2</v>
       </c>
       <c r="G3206" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3207">
@@ -87019,7 +87019,7 @@
         <v>2</v>
       </c>
       <c r="G3207" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3208">
@@ -87046,7 +87046,7 @@
         <v>2</v>
       </c>
       <c r="G3208" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3209">
@@ -87073,7 +87073,7 @@
         <v>2</v>
       </c>
       <c r="G3209" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3210">
@@ -87100,7 +87100,7 @@
         <v>2</v>
       </c>
       <c r="G3210" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3211">
@@ -87127,7 +87127,7 @@
         <v>2</v>
       </c>
       <c r="G3211" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3212">
@@ -87154,7 +87154,7 @@
         <v>2</v>
       </c>
       <c r="G3212" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3213">
@@ -87181,7 +87181,7 @@
         <v>2</v>
       </c>
       <c r="G3213" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3214">
@@ -87208,7 +87208,7 @@
         <v>2</v>
       </c>
       <c r="G3214" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3215">
@@ -87235,7 +87235,7 @@
         <v>2</v>
       </c>
       <c r="G3215" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3216">
@@ -87262,7 +87262,7 @@
         <v>2</v>
       </c>
       <c r="G3216" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3217">
@@ -87289,7 +87289,7 @@
         <v>2</v>
       </c>
       <c r="G3217" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3218">
@@ -87316,7 +87316,7 @@
         <v>2</v>
       </c>
       <c r="G3218" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3219">
@@ -87343,7 +87343,7 @@
         <v>2</v>
       </c>
       <c r="G3219" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3220">
@@ -87370,7 +87370,7 @@
         <v>2</v>
       </c>
       <c r="G3220" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3221">
@@ -87397,7 +87397,7 @@
         <v>2</v>
       </c>
       <c r="G3221" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3222">
@@ -87424,7 +87424,7 @@
         <v>2</v>
       </c>
       <c r="G3222" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3223">
@@ -87451,7 +87451,7 @@
         <v>2</v>
       </c>
       <c r="G3223" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3224">
@@ -87478,7 +87478,7 @@
         <v>2</v>
       </c>
       <c r="G3224" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3225">
@@ -87505,7 +87505,7 @@
         <v>2</v>
       </c>
       <c r="G3225" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3226">
@@ -87532,7 +87532,7 @@
         <v>2</v>
       </c>
       <c r="G3226" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3227">
@@ -87559,7 +87559,7 @@
         <v>2</v>
       </c>
       <c r="G3227" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3228">
@@ -87586,7 +87586,7 @@
         <v>2</v>
       </c>
       <c r="G3228" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3229">
@@ -87613,7 +87613,7 @@
         <v>2</v>
       </c>
       <c r="G3229" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3230">
@@ -87640,7 +87640,7 @@
         <v>2</v>
       </c>
       <c r="G3230" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3231">
@@ -87667,7 +87667,7 @@
         <v>2</v>
       </c>
       <c r="G3231" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3232">
@@ -87694,7 +87694,7 @@
         <v>2</v>
       </c>
       <c r="G3232" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3233">
@@ -87721,7 +87721,7 @@
         <v>2</v>
       </c>
       <c r="G3233" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3234">
@@ -87748,7 +87748,7 @@
         <v>2</v>
       </c>
       <c r="G3234" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3235">
@@ -87775,7 +87775,7 @@
         <v>2</v>
       </c>
       <c r="G3235" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3236">
@@ -87802,7 +87802,7 @@
         <v>2</v>
       </c>
       <c r="G3236" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3237">
@@ -87829,7 +87829,7 @@
         <v>2</v>
       </c>
       <c r="G3237" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3238">
@@ -87856,7 +87856,7 @@
         <v>2</v>
       </c>
       <c r="G3238" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3239">
@@ -87883,7 +87883,7 @@
         <v>2</v>
       </c>
       <c r="G3239" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3240">
@@ -87910,7 +87910,7 @@
         <v>2</v>
       </c>
       <c r="G3240" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3241">
@@ -87937,7 +87937,7 @@
         <v>2</v>
       </c>
       <c r="G3241" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3242">
@@ -87964,7 +87964,7 @@
         <v>2</v>
       </c>
       <c r="G3242" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3243">
@@ -87991,7 +87991,7 @@
         <v>2</v>
       </c>
       <c r="G3243" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3244">
@@ -88018,7 +88018,7 @@
         <v>2</v>
       </c>
       <c r="G3244" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3245">
@@ -88045,7 +88045,7 @@
         <v>2</v>
       </c>
       <c r="G3245" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3246">
@@ -88072,7 +88072,7 @@
         <v>2</v>
       </c>
       <c r="G3246" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3247">
@@ -88099,7 +88099,7 @@
         <v>2</v>
       </c>
       <c r="G3247" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3248">
@@ -88126,7 +88126,7 @@
         <v>2</v>
       </c>
       <c r="G3248" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3249">
@@ -88153,7 +88153,7 @@
         <v>2</v>
       </c>
       <c r="G3249" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3250">
@@ -88180,7 +88180,7 @@
         <v>2</v>
       </c>
       <c r="G3250" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3251">
@@ -88207,7 +88207,7 @@
         <v>2</v>
       </c>
       <c r="G3251" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3252">
@@ -88234,7 +88234,7 @@
         <v>2</v>
       </c>
       <c r="G3252" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3253">
@@ -88261,7 +88261,7 @@
         <v>2</v>
       </c>
       <c r="G3253" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3254">
@@ -88288,7 +88288,7 @@
         <v>2</v>
       </c>
       <c r="G3254" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3255">
@@ -88315,7 +88315,7 @@
         <v>2</v>
       </c>
       <c r="G3255" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3256">
@@ -88342,7 +88342,7 @@
         <v>2</v>
       </c>
       <c r="G3256" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3257">
@@ -88369,7 +88369,7 @@
         <v>2</v>
       </c>
       <c r="G3257" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3258">
@@ -88396,7 +88396,7 @@
         <v>2</v>
       </c>
       <c r="G3258" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3259">
@@ -88423,7 +88423,7 @@
         <v>2</v>
       </c>
       <c r="G3259" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3260">
@@ -88450,7 +88450,7 @@
         <v>2</v>
       </c>
       <c r="G3260" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3261">
@@ -88477,7 +88477,7 @@
         <v>2</v>
       </c>
       <c r="G3261" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3262">
@@ -88504,7 +88504,7 @@
         <v>2</v>
       </c>
       <c r="G3262" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3263">
@@ -88531,7 +88531,7 @@
         <v>2</v>
       </c>
       <c r="G3263" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3264">
@@ -88558,7 +88558,7 @@
         <v>2</v>
       </c>
       <c r="G3264" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3265">
@@ -88585,7 +88585,7 @@
         <v>2</v>
       </c>
       <c r="G3265" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3266">
@@ -88612,7 +88612,7 @@
         <v>2</v>
       </c>
       <c r="G3266" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3267">
@@ -88639,7 +88639,7 @@
         <v>2</v>
       </c>
       <c r="G3267" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3268">
@@ -88666,7 +88666,7 @@
         <v>2</v>
       </c>
       <c r="G3268" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3269">
@@ -88693,7 +88693,7 @@
         <v>2</v>
       </c>
       <c r="G3269" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3270">
@@ -88720,7 +88720,7 @@
         <v>2</v>
       </c>
       <c r="G3270" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3271">
@@ -88747,7 +88747,7 @@
         <v>2</v>
       </c>
       <c r="G3271" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3272">
@@ -88774,7 +88774,7 @@
         <v>2</v>
       </c>
       <c r="G3272" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3273">
@@ -88801,7 +88801,7 @@
         <v>2</v>
       </c>
       <c r="G3273" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3274">
@@ -88828,7 +88828,7 @@
         <v>2</v>
       </c>
       <c r="G3274" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3275">
@@ -88855,7 +88855,7 @@
         <v>2</v>
       </c>
       <c r="G3275" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3276">
@@ -88882,7 +88882,7 @@
         <v>2</v>
       </c>
       <c r="G3276" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3277">
@@ -88909,7 +88909,7 @@
         <v>2</v>
       </c>
       <c r="G3277" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3278">
@@ -88936,7 +88936,7 @@
         <v>2</v>
       </c>
       <c r="G3278" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3279">
@@ -88963,7 +88963,7 @@
         <v>2</v>
       </c>
       <c r="G3279" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3280">
@@ -88990,7 +88990,7 @@
         <v>2</v>
       </c>
       <c r="G3280" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3281">
@@ -89017,7 +89017,7 @@
         <v>2</v>
       </c>
       <c r="G3281" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3282">
@@ -89044,7 +89044,7 @@
         <v>2</v>
       </c>
       <c r="G3282" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3283">
@@ -89071,7 +89071,7 @@
         <v>2</v>
       </c>
       <c r="G3283" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3284">
@@ -89098,7 +89098,7 @@
         <v>2</v>
       </c>
       <c r="G3284" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3285">
@@ -89125,7 +89125,7 @@
         <v>2</v>
       </c>
       <c r="G3285" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3286">
@@ -89152,7 +89152,7 @@
         <v>2</v>
       </c>
       <c r="G3286" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3287">
@@ -89179,7 +89179,7 @@
         <v>2</v>
       </c>
       <c r="G3287" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3288">
@@ -89206,7 +89206,7 @@
         <v>2</v>
       </c>
       <c r="G3288" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3289">
@@ -89233,7 +89233,7 @@
         <v>2</v>
       </c>
       <c r="G3289" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3290">
@@ -89260,7 +89260,7 @@
         <v>2</v>
       </c>
       <c r="G3290" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3291">
@@ -89287,7 +89287,7 @@
         <v>2</v>
       </c>
       <c r="G3291" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3292">
@@ -89314,7 +89314,7 @@
         <v>2</v>
       </c>
       <c r="G3292" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3293">
@@ -89341,7 +89341,7 @@
         <v>2</v>
       </c>
       <c r="G3293" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3294">
@@ -89368,7 +89368,7 @@
         <v>2</v>
       </c>
       <c r="G3294" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3295">
@@ -89395,7 +89395,7 @@
         <v>2</v>
       </c>
       <c r="G3295" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3296">
@@ -89422,7 +89422,7 @@
         <v>2</v>
       </c>
       <c r="G3296" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3297">
@@ -89449,7 +89449,7 @@
         <v>2</v>
       </c>
       <c r="G3297" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3298">
@@ -89476,7 +89476,7 @@
         <v>2</v>
       </c>
       <c r="G3298" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3299">
@@ -89503,7 +89503,7 @@
         <v>2</v>
       </c>
       <c r="G3299" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3300">
@@ -89530,7 +89530,7 @@
         <v>2</v>
       </c>
       <c r="G3300" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3301">
@@ -89557,7 +89557,7 @@
         <v>2</v>
       </c>
       <c r="G3301" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3302">
@@ -89584,7 +89584,7 @@
         <v>2</v>
       </c>
       <c r="G3302" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3303">
@@ -89611,7 +89611,7 @@
         <v>2</v>
       </c>
       <c r="G3303" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3304">
@@ -89638,7 +89638,7 @@
         <v>2</v>
       </c>
       <c r="G3304" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3305">
@@ -89665,7 +89665,7 @@
         <v>2</v>
       </c>
       <c r="G3305" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3306">
@@ -89692,7 +89692,7 @@
         <v>2</v>
       </c>
       <c r="G3306" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3307">
@@ -89719,7 +89719,7 @@
         <v>2</v>
       </c>
       <c r="G3307" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3308">
@@ -89746,7 +89746,7 @@
         <v>2</v>
       </c>
       <c r="G3308" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3309">
@@ -89773,7 +89773,7 @@
         <v>2</v>
       </c>
       <c r="G3309" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3310">
@@ -89800,7 +89800,7 @@
         <v>2</v>
       </c>
       <c r="G3310" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3311">
@@ -89827,7 +89827,7 @@
         <v>2</v>
       </c>
       <c r="G3311" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3312">
@@ -89854,7 +89854,7 @@
         <v>2</v>
       </c>
       <c r="G3312" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
       </c>
     </row>
     <row r="3313">
@@ -89881,7 +89881,1303 @@
         <v>2</v>
       </c>
       <c r="G3313" s="2" t="n">
-        <v>46282.46141540139</v>
+        <v>46282.46141540509</v>
+      </c>
+    </row>
+    <row r="3314">
+      <c r="A3314" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3314" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3314" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="D3314" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3314" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3314" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3314" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3315">
+      <c r="A3315" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3315" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3315" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="D3315" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3315" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3315" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3315" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3316">
+      <c r="A3316" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3316" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3316" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D3316" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3316" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3316" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3316" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3317">
+      <c r="A3317" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3317" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3317" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="D3317" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3317" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3317" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3317" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3318">
+      <c r="A3318" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3318" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3318" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="D3318" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3318" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3318" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3318" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3319">
+      <c r="A3319" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3319" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3319" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D3319" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3319" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3319" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3319" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3320">
+      <c r="A3320" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3320" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3320" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="D3320" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3320" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3320" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3320" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3321">
+      <c r="A3321" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3321" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3321" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="D3321" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3321" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3321" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3321" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3322">
+      <c r="A3322" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3322" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3322" t="n">
+        <v>27.61</v>
+      </c>
+      <c r="D3322" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3322" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3322" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3322" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3323">
+      <c r="A3323" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3323" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3323" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="D3323" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3323" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3323" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3323" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3324">
+      <c r="A3324" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3324" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3324" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="D3324" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3324" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3324" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3324" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3325">
+      <c r="A3325" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3325" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3325" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="D3325" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3325" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3325" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3325" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3326">
+      <c r="A3326" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3326" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3326" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="D3326" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3326" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3326" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3326" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3327">
+      <c r="A3327" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3327" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3327" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="D3327" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3327" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3327" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3327" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3328">
+      <c r="A3328" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3328" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3328" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="D3328" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3328" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3328" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3328" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3329">
+      <c r="A3329" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3329" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3329" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="D3329" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3329" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3329" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3329" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3330">
+      <c r="A3330" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3330" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3330" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D3330" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3330" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3330" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3330" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3331">
+      <c r="A3331" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3331" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3331" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="D3331" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3331" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3331" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3331" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3332">
+      <c r="A3332" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3332" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3332" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="D3332" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3332" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3332" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3332" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3333">
+      <c r="A3333" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3333" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3333" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="D3333" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3333" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3333" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3333" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3334">
+      <c r="A3334" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3334" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3334" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="D3334" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3334" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3334" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3334" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3335">
+      <c r="A3335" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3335" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3335" t="n">
+        <v>22.72</v>
+      </c>
+      <c r="D3335" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3335" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3335" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3335" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3336">
+      <c r="A3336" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3336" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3336" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="D3336" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3336" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3336" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3336" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3337">
+      <c r="A3337" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3337" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3337" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="D3337" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3337" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3337" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3337" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3338">
+      <c r="A3338" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3338" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3338" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="D3338" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3338" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3338" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3338" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3339">
+      <c r="A3339" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3339" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3339" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="D3339" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3339" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3339" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3339" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3340">
+      <c r="A3340" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3340" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3340" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="D3340" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3340" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3340" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3340" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3341">
+      <c r="A3341" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3341" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3341" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="D3341" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3341" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3341" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3341" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3342">
+      <c r="A3342" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3342" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3342" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="D3342" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3342" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3342" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3342" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3343">
+      <c r="A3343" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3343" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3343" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="D3343" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3343" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3343" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3343" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3344">
+      <c r="A3344" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3344" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3344" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="D3344" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3344" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3344" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3344" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3345">
+      <c r="A3345" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3345" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3345" t="n">
+        <v>40.79</v>
+      </c>
+      <c r="D3345" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3345" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3345" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3345" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3346">
+      <c r="A3346" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3346" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3346" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="D3346" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3346" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3346" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3346" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3347">
+      <c r="A3347" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3347" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3347" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="D3347" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3347" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3347" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3347" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3348">
+      <c r="A3348" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3348" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3348" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="D3348" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3348" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3348" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3348" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3349">
+      <c r="A3349" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3349" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3349" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="D3349" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3349" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3349" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3349" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3350">
+      <c r="A3350" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3350" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3350" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="D3350" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3350" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3350" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3350" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3351">
+      <c r="A3351" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3351" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3351" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="D3351" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3351" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3351" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3351" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3352">
+      <c r="A3352" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3352" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3352" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="D3352" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3352" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3352" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3352" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3353">
+      <c r="A3353" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3353" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3353" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="D3353" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3353" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3353" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3353" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3354">
+      <c r="A3354" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3354" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3354" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="D3354" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3354" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3354" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3354" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3355">
+      <c r="A3355" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3355" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3355" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D3355" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3355" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3355" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3355" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3356">
+      <c r="A3356" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3356" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3356" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="D3356" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3356" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3356" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3356" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3357">
+      <c r="A3357" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3357" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3357" t="n">
+        <v>23.22</v>
+      </c>
+      <c r="D3357" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3357" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3357" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3357" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3358">
+      <c r="A3358" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3358" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3358" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="D3358" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3358" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3358" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3358" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3359">
+      <c r="A3359" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3359" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3359" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="D3359" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3359" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3359" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3359" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3360">
+      <c r="A3360" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3360" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3360" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="D3360" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3360" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3360" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3360" s="2" t="n">
+        <v>46282.87519636663</v>
+      </c>
+    </row>
+    <row r="3361">
+      <c r="A3361" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3361" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3361" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="D3361" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3361" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3361" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3361" s="2" t="n">
+        <v>46282.87519636663</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3324">
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3333">
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3335">
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3337">
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3341">
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3343">
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3344">
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3345">
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3346">
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3347">
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3355">
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3356">
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3357">
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3360">
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46282.87519636663</v>
+        <v>46283.44437546001</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3361"/>
+  <dimension ref="A1:G3385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89892,7 +89892,7 @@
         <v>1</v>
       </c>
       <c r="C3314" t="n">
-        <v>9.73</v>
+        <v>8.74</v>
       </c>
       <c r="D3314" t="inlineStr">
         <is>
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3315">
@@ -89919,7 +89919,7 @@
         <v>2</v>
       </c>
       <c r="C3315" t="n">
-        <v>9.74</v>
+        <v>8.59</v>
       </c>
       <c r="D3315" t="inlineStr">
         <is>
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3316">
@@ -89946,7 +89946,7 @@
         <v>3</v>
       </c>
       <c r="C3316" t="n">
-        <v>4.6</v>
+        <v>5.33</v>
       </c>
       <c r="D3316" t="inlineStr">
         <is>
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3317">
@@ -89973,7 +89973,7 @@
         <v>4</v>
       </c>
       <c r="C3317" t="n">
-        <v>8.56</v>
+        <v>9.9</v>
       </c>
       <c r="D3317" t="inlineStr">
         <is>
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3318">
@@ -90000,7 +90000,7 @@
         <v>5</v>
       </c>
       <c r="C3318" t="n">
-        <v>9.130000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="D3318" t="inlineStr">
         <is>
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3319">
@@ -90027,7 +90027,7 @@
         <v>6</v>
       </c>
       <c r="C3319" t="n">
-        <v>5.25</v>
+        <v>6.28</v>
       </c>
       <c r="D3319" t="inlineStr">
         <is>
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3320">
@@ -90054,7 +90054,7 @@
         <v>7</v>
       </c>
       <c r="C3320" t="n">
-        <v>8.65</v>
+        <v>9.49</v>
       </c>
       <c r="D3320" t="inlineStr">
         <is>
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3321">
@@ -90081,7 +90081,7 @@
         <v>8</v>
       </c>
       <c r="C3321" t="n">
-        <v>29.31</v>
+        <v>29.07</v>
       </c>
       <c r="D3321" t="inlineStr">
         <is>
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3322">
@@ -90108,7 +90108,7 @@
         <v>9</v>
       </c>
       <c r="C3322" t="n">
-        <v>27.61</v>
+        <v>28.5</v>
       </c>
       <c r="D3322" t="inlineStr">
         <is>
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3323">
@@ -90135,7 +90135,7 @@
         <v>10</v>
       </c>
       <c r="C3323" t="n">
-        <v>16.32</v>
+        <v>18.22</v>
       </c>
       <c r="D3323" t="inlineStr">
         <is>
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3324">
@@ -90162,7 +90162,7 @@
         <v>11</v>
       </c>
       <c r="C3324" t="n">
-        <v>14.34</v>
+        <v>19.03</v>
       </c>
       <c r="D3324" t="inlineStr">
         <is>
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3325">
@@ -90189,7 +90189,7 @@
         <v>12</v>
       </c>
       <c r="C3325" t="n">
-        <v>26.22</v>
+        <v>28.34</v>
       </c>
       <c r="D3325" t="inlineStr">
         <is>
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3326">
@@ -90216,7 +90216,7 @@
         <v>13</v>
       </c>
       <c r="C3326" t="n">
-        <v>26.05</v>
+        <v>28.08</v>
       </c>
       <c r="D3326" t="inlineStr">
         <is>
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3327">
@@ -90243,7 +90243,7 @@
         <v>14</v>
       </c>
       <c r="C3327" t="n">
-        <v>27.51</v>
+        <v>29.23</v>
       </c>
       <c r="D3327" t="inlineStr">
         <is>
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3328">
@@ -90270,7 +90270,7 @@
         <v>15</v>
       </c>
       <c r="C3328" t="n">
-        <v>26.33</v>
+        <v>28.53</v>
       </c>
       <c r="D3328" t="inlineStr">
         <is>
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3329">
@@ -90297,7 +90297,7 @@
         <v>16</v>
       </c>
       <c r="C3329" t="n">
-        <v>26.91</v>
+        <v>29</v>
       </c>
       <c r="D3329" t="inlineStr">
         <is>
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3330">
@@ -90324,7 +90324,7 @@
         <v>17</v>
       </c>
       <c r="C3330" t="n">
-        <v>20.9</v>
+        <v>24.51</v>
       </c>
       <c r="D3330" t="inlineStr">
         <is>
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3331">
@@ -90351,7 +90351,7 @@
         <v>18</v>
       </c>
       <c r="C3331" t="n">
-        <v>22.13</v>
+        <v>26.03</v>
       </c>
       <c r="D3331" t="inlineStr">
         <is>
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3332">
@@ -90378,7 +90378,7 @@
         <v>19</v>
       </c>
       <c r="C3332" t="n">
-        <v>16.91</v>
+        <v>21.47</v>
       </c>
       <c r="D3332" t="inlineStr">
         <is>
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3333">
@@ -90405,7 +90405,7 @@
         <v>20</v>
       </c>
       <c r="C3333" t="n">
-        <v>13.54</v>
+        <v>17.03</v>
       </c>
       <c r="D3333" t="inlineStr">
         <is>
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3334">
@@ -90432,7 +90432,7 @@
         <v>21</v>
       </c>
       <c r="C3334" t="n">
-        <v>27.13</v>
+        <v>31.2</v>
       </c>
       <c r="D3334" t="inlineStr">
         <is>
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3335">
@@ -90459,7 +90459,7 @@
         <v>22</v>
       </c>
       <c r="C3335" t="n">
-        <v>22.72</v>
+        <v>26.96</v>
       </c>
       <c r="D3335" t="inlineStr">
         <is>
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3336">
@@ -90486,7 +90486,7 @@
         <v>23</v>
       </c>
       <c r="C3336" t="n">
-        <v>23.15</v>
+        <v>24.62</v>
       </c>
       <c r="D3336" t="inlineStr">
         <is>
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3337">
@@ -90513,7 +90513,7 @@
         <v>24</v>
       </c>
       <c r="C3337" t="n">
-        <v>14.35</v>
+        <v>17.39</v>
       </c>
       <c r="D3337" t="inlineStr">
         <is>
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3338">
@@ -90540,7 +90540,7 @@
         <v>1</v>
       </c>
       <c r="C3338" t="n">
-        <v>11.92</v>
+        <v>-1.26</v>
       </c>
       <c r="D3338" t="inlineStr">
         <is>
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3339">
@@ -90567,7 +90567,7 @@
         <v>2</v>
       </c>
       <c r="C3339" t="n">
-        <v>14.88</v>
+        <v>-2.99</v>
       </c>
       <c r="D3339" t="inlineStr">
         <is>
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3340">
@@ -90594,7 +90594,7 @@
         <v>3</v>
       </c>
       <c r="C3340" t="n">
-        <v>17.57</v>
+        <v>-1.12</v>
       </c>
       <c r="D3340" t="inlineStr">
         <is>
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3341">
@@ -90621,7 +90621,7 @@
         <v>4</v>
       </c>
       <c r="C3341" t="n">
-        <v>18.77</v>
+        <v>1.91</v>
       </c>
       <c r="D3341" t="inlineStr">
         <is>
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3342">
@@ -90648,7 +90648,7 @@
         <v>5</v>
       </c>
       <c r="C3342" t="n">
-        <v>19.05</v>
+        <v>-2.47</v>
       </c>
       <c r="D3342" t="inlineStr">
         <is>
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3343">
@@ -90675,7 +90675,7 @@
         <v>6</v>
       </c>
       <c r="C3343" t="n">
-        <v>17.31</v>
+        <v>-3.5</v>
       </c>
       <c r="D3343" t="inlineStr">
         <is>
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3344">
@@ -90702,7 +90702,7 @@
         <v>7</v>
       </c>
       <c r="C3344" t="n">
-        <v>18.91</v>
+        <v>2.3</v>
       </c>
       <c r="D3344" t="inlineStr">
         <is>
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3345">
@@ -90729,7 +90729,7 @@
         <v>8</v>
       </c>
       <c r="C3345" t="n">
-        <v>40.79</v>
+        <v>37.56</v>
       </c>
       <c r="D3345" t="inlineStr">
         <is>
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3346">
@@ -90756,7 +90756,7 @@
         <v>9</v>
       </c>
       <c r="C3346" t="n">
-        <v>39.16</v>
+        <v>31.21</v>
       </c>
       <c r="D3346" t="inlineStr">
         <is>
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3347">
@@ -90783,7 +90783,7 @@
         <v>10</v>
       </c>
       <c r="C3347" t="n">
-        <v>20.04</v>
+        <v>-4.68</v>
       </c>
       <c r="D3347" t="inlineStr">
         <is>
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3348">
@@ -90810,7 +90810,7 @@
         <v>11</v>
       </c>
       <c r="C3348" t="n">
-        <v>19.94</v>
+        <v>19.35</v>
       </c>
       <c r="D3348" t="inlineStr">
         <is>
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3349">
@@ -90837,7 +90837,7 @@
         <v>12</v>
       </c>
       <c r="C3349" t="n">
-        <v>22.04</v>
+        <v>23.72</v>
       </c>
       <c r="D3349" t="inlineStr">
         <is>
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3350">
@@ -90864,7 +90864,7 @@
         <v>13</v>
       </c>
       <c r="C3350" t="n">
-        <v>18.14</v>
+        <v>22.9</v>
       </c>
       <c r="D3350" t="inlineStr">
         <is>
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3351">
@@ -90891,7 +90891,7 @@
         <v>14</v>
       </c>
       <c r="C3351" t="n">
-        <v>17.96</v>
+        <v>24.01</v>
       </c>
       <c r="D3351" t="inlineStr">
         <is>
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3352">
@@ -90918,7 +90918,7 @@
         <v>15</v>
       </c>
       <c r="C3352" t="n">
-        <v>17.98</v>
+        <v>22.69</v>
       </c>
       <c r="D3352" t="inlineStr">
         <is>
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3353">
@@ -90945,7 +90945,7 @@
         <v>16</v>
       </c>
       <c r="C3353" t="n">
-        <v>18.24</v>
+        <v>24.83</v>
       </c>
       <c r="D3353" t="inlineStr">
         <is>
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3354">
@@ -90972,7 +90972,7 @@
         <v>17</v>
       </c>
       <c r="C3354" t="n">
-        <v>18.17</v>
+        <v>11.01</v>
       </c>
       <c r="D3354" t="inlineStr">
         <is>
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3355">
@@ -90999,7 +90999,7 @@
         <v>18</v>
       </c>
       <c r="C3355" t="n">
-        <v>20.1</v>
+        <v>-29.17</v>
       </c>
       <c r="D3355" t="inlineStr">
         <is>
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3356">
@@ -91026,7 +91026,7 @@
         <v>19</v>
       </c>
       <c r="C3356" t="n">
-        <v>17.41</v>
+        <v>-26.67</v>
       </c>
       <c r="D3356" t="inlineStr">
         <is>
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3357">
@@ -91053,7 +91053,7 @@
         <v>20</v>
       </c>
       <c r="C3357" t="n">
-        <v>23.22</v>
+        <v>14.32</v>
       </c>
       <c r="D3357" t="inlineStr">
         <is>
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3358">
@@ -91080,7 +91080,7 @@
         <v>21</v>
       </c>
       <c r="C3358" t="n">
-        <v>28.82</v>
+        <v>26.06</v>
       </c>
       <c r="D3358" t="inlineStr">
         <is>
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3359">
@@ -91107,7 +91107,7 @@
         <v>22</v>
       </c>
       <c r="C3359" t="n">
-        <v>26.15</v>
+        <v>27.09</v>
       </c>
       <c r="D3359" t="inlineStr">
         <is>
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3360">
@@ -91134,7 +91134,7 @@
         <v>23</v>
       </c>
       <c r="C3360" t="n">
-        <v>26.41</v>
+        <v>25.3</v>
       </c>
       <c r="D3360" t="inlineStr">
         <is>
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
       </c>
     </row>
     <row r="3361">
@@ -91161,7 +91161,7 @@
         <v>24</v>
       </c>
       <c r="C3361" t="n">
-        <v>22.24</v>
+        <v>23.48</v>
       </c>
       <c r="D3361" t="inlineStr">
         <is>
@@ -91177,7 +91177,655 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46283.44437546001</v>
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3362">
+      <c r="A3362" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3362" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3362" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="D3362" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3362" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3362" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3362" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3363">
+      <c r="A3363" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3363" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3363" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="D3363" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3363" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3363" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3363" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3364">
+      <c r="A3364" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3364" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3364" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="D3364" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3364" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3364" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3364" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3365">
+      <c r="A3365" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3365" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3365" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="D3365" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3365" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3365" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3365" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3366">
+      <c r="A3366" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3366" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3366" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="D3366" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3366" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3366" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3366" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3367">
+      <c r="A3367" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3367" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3367" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="D3367" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3367" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3367" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3367" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3368">
+      <c r="A3368" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3368" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3368" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="D3368" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3368" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3368" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3368" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3369">
+      <c r="A3369" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3369" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3369" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="D3369" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3369" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3369" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3369" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3370">
+      <c r="A3370" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3370" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3370" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="D3370" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3370" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3370" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3370" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3371">
+      <c r="A3371" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3371" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3371" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="D3371" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3371" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3371" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3371" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3372">
+      <c r="A3372" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3372" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3372" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="D3372" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3372" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3372" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3372" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3373">
+      <c r="A3373" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3373" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3373" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="D3373" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3373" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3373" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3373" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3374">
+      <c r="A3374" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3374" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3374" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="D3374" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3374" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3374" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3374" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3375">
+      <c r="A3375" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3375" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3375" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="D3375" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3375" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3375" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3375" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3376">
+      <c r="A3376" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3376" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3376" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D3376" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3376" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3376" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3376" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3377">
+      <c r="A3377" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3377" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3377" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="D3377" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3377" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3377" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3377" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3378">
+      <c r="A3378" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3378" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3378" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="D3378" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3378" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3378" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3378" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3379">
+      <c r="A3379" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3379" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3379" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="D3379" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3379" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3379" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3379" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3380">
+      <c r="A3380" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3380" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3380" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="D3380" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3380" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3380" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3380" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3381">
+      <c r="A3381" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3381" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3381" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="D3381" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3381" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3381" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3381" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3382">
+      <c r="A3382" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3382" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3382" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="D3382" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3382" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3382" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3382" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3383">
+      <c r="A3383" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3383" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3383" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="D3383" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3383" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3383" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3383" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3384">
+      <c r="A3384" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3384" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3384" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="D3384" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3384" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3384" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3384" s="2" t="n">
+        <v>46283.85478670016</v>
+      </c>
+    </row>
+    <row r="3385">
+      <c r="A3385" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3385" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3385" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D3385" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3385" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3385" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3385" s="2" t="n">
+        <v>46283.85478670016</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3324">
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3333">
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3335">
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3337">
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3341">
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3343">
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3344">
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3345">
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3346">
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3347">
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3355">
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3356">
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3357">
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3360">
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3362">
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3364">
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3365">
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3366">
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3367">
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3368">
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3369">
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3370">
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3371">
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3372">
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3373">
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3374">
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3375">
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3376">
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3377">
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3378">
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3379">
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3380">
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3381">
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3382">
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3383">
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3384">
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
     <row r="3385">
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46283.85478670016</v>
+        <v>46284.433508858</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3385"/>
+  <dimension ref="A1:G3409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3324">
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3329">
@@ -90297,7 +90297,7 @@
         <v>16</v>
       </c>
       <c r="C3329" t="n">
-        <v>29</v>
+        <v>29.01</v>
       </c>
       <c r="D3329" t="inlineStr">
         <is>
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3333">
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3335">
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3337">
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3341">
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3343">
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3344">
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3345">
@@ -90729,7 +90729,7 @@
         <v>8</v>
       </c>
       <c r="C3345" t="n">
-        <v>37.56</v>
+        <v>40.11</v>
       </c>
       <c r="D3345" t="inlineStr">
         <is>
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3346">
@@ -90756,7 +90756,7 @@
         <v>9</v>
       </c>
       <c r="C3346" t="n">
-        <v>31.21</v>
+        <v>33.89</v>
       </c>
       <c r="D3346" t="inlineStr">
         <is>
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3347">
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3355">
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3356">
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3357">
@@ -91053,7 +91053,7 @@
         <v>20</v>
       </c>
       <c r="C3357" t="n">
-        <v>14.32</v>
+        <v>15.04</v>
       </c>
       <c r="D3357" t="inlineStr">
         <is>
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3358">
@@ -91080,7 +91080,7 @@
         <v>21</v>
       </c>
       <c r="C3358" t="n">
-        <v>26.06</v>
+        <v>31.44</v>
       </c>
       <c r="D3358" t="inlineStr">
         <is>
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3359">
@@ -91107,7 +91107,7 @@
         <v>22</v>
       </c>
       <c r="C3359" t="n">
-        <v>27.09</v>
+        <v>32.6</v>
       </c>
       <c r="D3359" t="inlineStr">
         <is>
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3360">
@@ -91134,7 +91134,7 @@
         <v>23</v>
       </c>
       <c r="C3360" t="n">
-        <v>25.3</v>
+        <v>26.39</v>
       </c>
       <c r="D3360" t="inlineStr">
         <is>
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3362">
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3363">
@@ -91215,7 +91215,7 @@
         <v>2</v>
       </c>
       <c r="C3363" t="n">
-        <v>13.52</v>
+        <v>13.53</v>
       </c>
       <c r="D3363" t="inlineStr">
         <is>
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3364">
@@ -91242,7 +91242,7 @@
         <v>3</v>
       </c>
       <c r="C3364" t="n">
-        <v>14.23</v>
+        <v>14.24</v>
       </c>
       <c r="D3364" t="inlineStr">
         <is>
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3365">
@@ -91269,7 +91269,7 @@
         <v>4</v>
       </c>
       <c r="C3365" t="n">
-        <v>15.46</v>
+        <v>15.45</v>
       </c>
       <c r="D3365" t="inlineStr">
         <is>
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3366">
@@ -91296,7 +91296,7 @@
         <v>5</v>
       </c>
       <c r="C3366" t="n">
-        <v>17.19</v>
+        <v>17.12</v>
       </c>
       <c r="D3366" t="inlineStr">
         <is>
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3367">
@@ -91323,7 +91323,7 @@
         <v>6</v>
       </c>
       <c r="C3367" t="n">
-        <v>18.72</v>
+        <v>18.34</v>
       </c>
       <c r="D3367" t="inlineStr">
         <is>
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3368">
@@ -91350,7 +91350,7 @@
         <v>7</v>
       </c>
       <c r="C3368" t="n">
-        <v>22.67</v>
+        <v>18.8</v>
       </c>
       <c r="D3368" t="inlineStr">
         <is>
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3369">
@@ -91377,7 +91377,7 @@
         <v>8</v>
       </c>
       <c r="C3369" t="n">
-        <v>43.71</v>
+        <v>20.91</v>
       </c>
       <c r="D3369" t="inlineStr">
         <is>
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3370">
@@ -91404,7 +91404,7 @@
         <v>9</v>
       </c>
       <c r="C3370" t="n">
-        <v>41.06</v>
+        <v>19.14</v>
       </c>
       <c r="D3370" t="inlineStr">
         <is>
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3371">
@@ -91431,7 +91431,7 @@
         <v>10</v>
       </c>
       <c r="C3371" t="n">
-        <v>23.04</v>
+        <v>16.99</v>
       </c>
       <c r="D3371" t="inlineStr">
         <is>
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3372">
@@ -91458,7 +91458,7 @@
         <v>11</v>
       </c>
       <c r="C3372" t="n">
-        <v>22.13</v>
+        <v>18.79</v>
       </c>
       <c r="D3372" t="inlineStr">
         <is>
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3373">
@@ -91485,7 +91485,7 @@
         <v>12</v>
       </c>
       <c r="C3373" t="n">
-        <v>24.57</v>
+        <v>21.17</v>
       </c>
       <c r="D3373" t="inlineStr">
         <is>
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3374">
@@ -91512,7 +91512,7 @@
         <v>13</v>
       </c>
       <c r="C3374" t="n">
-        <v>24.35</v>
+        <v>21.02</v>
       </c>
       <c r="D3374" t="inlineStr">
         <is>
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3375">
@@ -91539,7 +91539,7 @@
         <v>14</v>
       </c>
       <c r="C3375" t="n">
-        <v>21.11</v>
+        <v>18.36</v>
       </c>
       <c r="D3375" t="inlineStr">
         <is>
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3376">
@@ -91566,7 +91566,7 @@
         <v>15</v>
       </c>
       <c r="C3376" t="n">
-        <v>21.3</v>
+        <v>18.56</v>
       </c>
       <c r="D3376" t="inlineStr">
         <is>
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3377">
@@ -91593,7 +91593,7 @@
         <v>16</v>
       </c>
       <c r="C3377" t="n">
-        <v>21.75</v>
+        <v>18.99</v>
       </c>
       <c r="D3377" t="inlineStr">
         <is>
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3378">
@@ -91620,7 +91620,7 @@
         <v>17</v>
       </c>
       <c r="C3378" t="n">
-        <v>21.91</v>
+        <v>19.08</v>
       </c>
       <c r="D3378" t="inlineStr">
         <is>
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3379">
@@ -91647,7 +91647,7 @@
         <v>18</v>
       </c>
       <c r="C3379" t="n">
-        <v>22.73</v>
+        <v>19.47</v>
       </c>
       <c r="D3379" t="inlineStr">
         <is>
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3380">
@@ -91674,7 +91674,7 @@
         <v>19</v>
       </c>
       <c r="C3380" t="n">
-        <v>20.13</v>
+        <v>16.72</v>
       </c>
       <c r="D3380" t="inlineStr">
         <is>
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3381">
@@ -91701,7 +91701,7 @@
         <v>20</v>
       </c>
       <c r="C3381" t="n">
-        <v>25.92</v>
+        <v>15.45</v>
       </c>
       <c r="D3381" t="inlineStr">
         <is>
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3382">
@@ -91728,7 +91728,7 @@
         <v>21</v>
       </c>
       <c r="C3382" t="n">
-        <v>35.21</v>
+        <v>15.19</v>
       </c>
       <c r="D3382" t="inlineStr">
         <is>
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3383">
@@ -91755,7 +91755,7 @@
         <v>22</v>
       </c>
       <c r="C3383" t="n">
-        <v>37.27</v>
+        <v>17.35</v>
       </c>
       <c r="D3383" t="inlineStr">
         <is>
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3384">
@@ -91782,7 +91782,7 @@
         <v>23</v>
       </c>
       <c r="C3384" t="n">
-        <v>27.86</v>
+        <v>15.98</v>
       </c>
       <c r="D3384" t="inlineStr">
         <is>
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
       </c>
     </row>
     <row r="3385">
@@ -91809,7 +91809,7 @@
         <v>24</v>
       </c>
       <c r="C3385" t="n">
-        <v>20.6</v>
+        <v>13.01</v>
       </c>
       <c r="D3385" t="inlineStr">
         <is>
@@ -91825,7 +91825,655 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46284.433508858</v>
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3386">
+      <c r="A3386" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3386" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3386" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="D3386" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3386" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3386" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3386" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3387">
+      <c r="A3387" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3387" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3387" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="D3387" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3387" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3387" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3387" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3388">
+      <c r="A3388" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3388" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3388" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="D3388" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3388" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3388" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3388" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3389">
+      <c r="A3389" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3389" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3389" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="D3389" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3389" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3389" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3389" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3390">
+      <c r="A3390" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3390" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3390" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="D3390" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3390" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3390" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3390" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3391">
+      <c r="A3391" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3391" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3391" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="D3391" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3391" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3391" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3391" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3392">
+      <c r="A3392" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3392" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3392" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="D3392" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3392" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3392" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3392" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3393">
+      <c r="A3393" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3393" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3393" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="D3393" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3393" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3393" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3393" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3394">
+      <c r="A3394" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3394" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3394" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="D3394" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3394" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3394" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3394" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3395">
+      <c r="A3395" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3395" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3395" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="D3395" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3395" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3395" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3395" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3396">
+      <c r="A3396" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3396" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3396" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="D3396" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3396" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3396" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3396" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3397">
+      <c r="A3397" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3397" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3397" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3397" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3397" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3397" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3397" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3398">
+      <c r="A3398" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3398" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3398" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="D3398" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3398" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3398" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3398" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3399">
+      <c r="A3399" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3399" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3399" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D3399" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3399" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3399" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3399" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3400">
+      <c r="A3400" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3400" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3400" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="D3400" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3400" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3400" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3400" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3401">
+      <c r="A3401" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3401" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3401" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D3401" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3401" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3401" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3401" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3402">
+      <c r="A3402" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3402" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3402" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="D3402" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3402" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3402" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3402" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3403">
+      <c r="A3403" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3403" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3403" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="D3403" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3403" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3403" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3403" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3404">
+      <c r="A3404" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3404" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3404" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="D3404" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3404" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3404" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3404" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3405">
+      <c r="A3405" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3405" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3405" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="D3405" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3405" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3405" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3405" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3406">
+      <c r="A3406" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3406" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3406" t="n">
+        <v>40.73</v>
+      </c>
+      <c r="D3406" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3406" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3406" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3406" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3407">
+      <c r="A3407" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3407" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3407" t="n">
+        <v>39.54</v>
+      </c>
+      <c r="D3407" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3407" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3407" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3407" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3408">
+      <c r="A3408" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3408" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3408" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="D3408" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3408" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3408" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3408" s="2" t="n">
+        <v>46284.83947000239</v>
+      </c>
+    </row>
+    <row r="3409">
+      <c r="A3409" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3409" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3409" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="D3409" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3409" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3409" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3409" s="2" t="n">
+        <v>46284.83947000239</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3324">
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3333">
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3335">
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3337">
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3341">
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3343">
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3344">
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3345">
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3346">
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3347">
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3355">
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3356">
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3357">
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3360">
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3362">
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3364">
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3365">
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3366">
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3367">
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3368">
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3369">
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3370">
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3371">
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3372">
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3373">
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3374">
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3375">
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3376">
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3377">
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3378">
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3379">
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3380">
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3381">
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3382">
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3383">
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3384">
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3385">
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3386">
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3387">
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3388">
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3389">
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3390">
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3391">
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3392">
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3393">
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3394">
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3395">
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3396">
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3397">
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3398">
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3399">
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3400">
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3401">
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3402">
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3403">
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3404">
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3405">
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3406">
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3407">
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3408">
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
     <row r="3409">
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46284.83947000239</v>
+        <v>46285.44740370638</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3409"/>
+  <dimension ref="A1:G3433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89892,7 +89892,7 @@
         <v>1</v>
       </c>
       <c r="C3314" t="n">
-        <v>8.74</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="D3314" t="inlineStr">
         <is>
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3315">
@@ -89919,7 +89919,7 @@
         <v>2</v>
       </c>
       <c r="C3315" t="n">
-        <v>8.59</v>
+        <v>10.55</v>
       </c>
       <c r="D3315" t="inlineStr">
         <is>
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3316">
@@ -89946,7 +89946,7 @@
         <v>3</v>
       </c>
       <c r="C3316" t="n">
-        <v>5.33</v>
+        <v>12.1</v>
       </c>
       <c r="D3316" t="inlineStr">
         <is>
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3317">
@@ -89973,7 +89973,7 @@
         <v>4</v>
       </c>
       <c r="C3317" t="n">
-        <v>9.9</v>
+        <v>13.5</v>
       </c>
       <c r="D3317" t="inlineStr">
         <is>
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3318">
@@ -90000,7 +90000,7 @@
         <v>5</v>
       </c>
       <c r="C3318" t="n">
-        <v>10.07</v>
+        <v>13.4</v>
       </c>
       <c r="D3318" t="inlineStr">
         <is>
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3319">
@@ -90027,7 +90027,7 @@
         <v>6</v>
       </c>
       <c r="C3319" t="n">
-        <v>6.28</v>
+        <v>11.61</v>
       </c>
       <c r="D3319" t="inlineStr">
         <is>
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3320">
@@ -90054,7 +90054,7 @@
         <v>7</v>
       </c>
       <c r="C3320" t="n">
-        <v>9.49</v>
+        <v>12.69</v>
       </c>
       <c r="D3320" t="inlineStr">
         <is>
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3321">
@@ -90081,7 +90081,7 @@
         <v>8</v>
       </c>
       <c r="C3321" t="n">
-        <v>29.07</v>
+        <v>32</v>
       </c>
       <c r="D3321" t="inlineStr">
         <is>
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3322">
@@ -90108,7 +90108,7 @@
         <v>9</v>
       </c>
       <c r="C3322" t="n">
-        <v>28.5</v>
+        <v>33.09</v>
       </c>
       <c r="D3322" t="inlineStr">
         <is>
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3323">
@@ -90135,7 +90135,7 @@
         <v>10</v>
       </c>
       <c r="C3323" t="n">
-        <v>18.22</v>
+        <v>22.91</v>
       </c>
       <c r="D3323" t="inlineStr">
         <is>
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3324">
@@ -90162,7 +90162,7 @@
         <v>11</v>
       </c>
       <c r="C3324" t="n">
-        <v>19.03</v>
+        <v>26.67</v>
       </c>
       <c r="D3324" t="inlineStr">
         <is>
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3325">
@@ -90189,7 +90189,7 @@
         <v>12</v>
       </c>
       <c r="C3325" t="n">
-        <v>28.34</v>
+        <v>32.36</v>
       </c>
       <c r="D3325" t="inlineStr">
         <is>
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3326">
@@ -90216,7 +90216,7 @@
         <v>13</v>
       </c>
       <c r="C3326" t="n">
-        <v>28.08</v>
+        <v>32.04</v>
       </c>
       <c r="D3326" t="inlineStr">
         <is>
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3327">
@@ -90243,7 +90243,7 @@
         <v>14</v>
       </c>
       <c r="C3327" t="n">
-        <v>29.23</v>
+        <v>32.73</v>
       </c>
       <c r="D3327" t="inlineStr">
         <is>
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3328">
@@ -90270,7 +90270,7 @@
         <v>15</v>
       </c>
       <c r="C3328" t="n">
-        <v>28.53</v>
+        <v>33.27</v>
       </c>
       <c r="D3328" t="inlineStr">
         <is>
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3329">
@@ -90297,7 +90297,7 @@
         <v>16</v>
       </c>
       <c r="C3329" t="n">
-        <v>29.01</v>
+        <v>33.19</v>
       </c>
       <c r="D3329" t="inlineStr">
         <is>
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3330">
@@ -90324,7 +90324,7 @@
         <v>17</v>
       </c>
       <c r="C3330" t="n">
-        <v>24.51</v>
+        <v>31.59</v>
       </c>
       <c r="D3330" t="inlineStr">
         <is>
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3331">
@@ -90351,7 +90351,7 @@
         <v>18</v>
       </c>
       <c r="C3331" t="n">
-        <v>26.03</v>
+        <v>34.24</v>
       </c>
       <c r="D3331" t="inlineStr">
         <is>
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3332">
@@ -90378,7 +90378,7 @@
         <v>19</v>
       </c>
       <c r="C3332" t="n">
-        <v>21.47</v>
+        <v>30.8</v>
       </c>
       <c r="D3332" t="inlineStr">
         <is>
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3333">
@@ -90405,7 +90405,7 @@
         <v>20</v>
       </c>
       <c r="C3333" t="n">
-        <v>17.03</v>
+        <v>24.06</v>
       </c>
       <c r="D3333" t="inlineStr">
         <is>
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3334">
@@ -90432,7 +90432,7 @@
         <v>21</v>
       </c>
       <c r="C3334" t="n">
-        <v>31.2</v>
+        <v>34.32</v>
       </c>
       <c r="D3334" t="inlineStr">
         <is>
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3335">
@@ -90459,7 +90459,7 @@
         <v>22</v>
       </c>
       <c r="C3335" t="n">
-        <v>26.96</v>
+        <v>33.48</v>
       </c>
       <c r="D3335" t="inlineStr">
         <is>
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3336">
@@ -90486,7 +90486,7 @@
         <v>23</v>
       </c>
       <c r="C3336" t="n">
-        <v>24.62</v>
+        <v>28.29</v>
       </c>
       <c r="D3336" t="inlineStr">
         <is>
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3337">
@@ -90513,7 +90513,7 @@
         <v>24</v>
       </c>
       <c r="C3337" t="n">
-        <v>17.39</v>
+        <v>22.79</v>
       </c>
       <c r="D3337" t="inlineStr">
         <is>
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3338">
@@ -90540,7 +90540,7 @@
         <v>1</v>
       </c>
       <c r="C3338" t="n">
-        <v>-1.26</v>
+        <v>10.17</v>
       </c>
       <c r="D3338" t="inlineStr">
         <is>
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3339">
@@ -90567,7 +90567,7 @@
         <v>2</v>
       </c>
       <c r="C3339" t="n">
-        <v>-2.99</v>
+        <v>13.19</v>
       </c>
       <c r="D3339" t="inlineStr">
         <is>
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3340">
@@ -90594,7 +90594,7 @@
         <v>3</v>
       </c>
       <c r="C3340" t="n">
-        <v>-1.12</v>
+        <v>15.44</v>
       </c>
       <c r="D3340" t="inlineStr">
         <is>
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3341">
@@ -90621,7 +90621,7 @@
         <v>4</v>
       </c>
       <c r="C3341" t="n">
-        <v>1.91</v>
+        <v>17.67</v>
       </c>
       <c r="D3341" t="inlineStr">
         <is>
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3342">
@@ -90648,7 +90648,7 @@
         <v>5</v>
       </c>
       <c r="C3342" t="n">
-        <v>-2.47</v>
+        <v>16.86</v>
       </c>
       <c r="D3342" t="inlineStr">
         <is>
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3343">
@@ -90675,7 +90675,7 @@
         <v>6</v>
       </c>
       <c r="C3343" t="n">
-        <v>-3.5</v>
+        <v>15.43</v>
       </c>
       <c r="D3343" t="inlineStr">
         <is>
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3344">
@@ -90702,7 +90702,7 @@
         <v>7</v>
       </c>
       <c r="C3344" t="n">
-        <v>2.3</v>
+        <v>20.02</v>
       </c>
       <c r="D3344" t="inlineStr">
         <is>
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3345">
@@ -90729,7 +90729,7 @@
         <v>8</v>
       </c>
       <c r="C3345" t="n">
-        <v>40.11</v>
+        <v>43.69</v>
       </c>
       <c r="D3345" t="inlineStr">
         <is>
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3346">
@@ -90756,7 +90756,7 @@
         <v>9</v>
       </c>
       <c r="C3346" t="n">
-        <v>33.89</v>
+        <v>44.24</v>
       </c>
       <c r="D3346" t="inlineStr">
         <is>
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3347">
@@ -90783,7 +90783,7 @@
         <v>10</v>
       </c>
       <c r="C3347" t="n">
-        <v>-4.68</v>
+        <v>26.21</v>
       </c>
       <c r="D3347" t="inlineStr">
         <is>
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3348">
@@ -90810,7 +90810,7 @@
         <v>11</v>
       </c>
       <c r="C3348" t="n">
-        <v>19.35</v>
+        <v>22.15</v>
       </c>
       <c r="D3348" t="inlineStr">
         <is>
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3349">
@@ -90837,7 +90837,7 @@
         <v>12</v>
       </c>
       <c r="C3349" t="n">
-        <v>23.72</v>
+        <v>26.25</v>
       </c>
       <c r="D3349" t="inlineStr">
         <is>
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3350">
@@ -90864,7 +90864,7 @@
         <v>13</v>
       </c>
       <c r="C3350" t="n">
-        <v>22.9</v>
+        <v>24.25</v>
       </c>
       <c r="D3350" t="inlineStr">
         <is>
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3351">
@@ -90891,7 +90891,7 @@
         <v>14</v>
       </c>
       <c r="C3351" t="n">
-        <v>24.01</v>
+        <v>24.42</v>
       </c>
       <c r="D3351" t="inlineStr">
         <is>
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3352">
@@ -90918,7 +90918,7 @@
         <v>15</v>
       </c>
       <c r="C3352" t="n">
-        <v>22.69</v>
+        <v>24.53</v>
       </c>
       <c r="D3352" t="inlineStr">
         <is>
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3353">
@@ -90945,7 +90945,7 @@
         <v>16</v>
       </c>
       <c r="C3353" t="n">
-        <v>24.83</v>
+        <v>24.72</v>
       </c>
       <c r="D3353" t="inlineStr">
         <is>
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3354">
@@ -90972,7 +90972,7 @@
         <v>17</v>
       </c>
       <c r="C3354" t="n">
-        <v>11.01</v>
+        <v>23.64</v>
       </c>
       <c r="D3354" t="inlineStr">
         <is>
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3355">
@@ -90999,7 +90999,7 @@
         <v>18</v>
       </c>
       <c r="C3355" t="n">
-        <v>-29.17</v>
+        <v>20.54</v>
       </c>
       <c r="D3355" t="inlineStr">
         <is>
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3356">
@@ -91026,7 +91026,7 @@
         <v>19</v>
       </c>
       <c r="C3356" t="n">
-        <v>-26.67</v>
+        <v>17.15</v>
       </c>
       <c r="D3356" t="inlineStr">
         <is>
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3357">
@@ -91053,7 +91053,7 @@
         <v>20</v>
       </c>
       <c r="C3357" t="n">
-        <v>15.04</v>
+        <v>25.95</v>
       </c>
       <c r="D3357" t="inlineStr">
         <is>
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3358">
@@ -91080,7 +91080,7 @@
         <v>21</v>
       </c>
       <c r="C3358" t="n">
-        <v>31.44</v>
+        <v>36.48</v>
       </c>
       <c r="D3358" t="inlineStr">
         <is>
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3359">
@@ -91107,7 +91107,7 @@
         <v>22</v>
       </c>
       <c r="C3359" t="n">
-        <v>32.6</v>
+        <v>33.76</v>
       </c>
       <c r="D3359" t="inlineStr">
         <is>
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3360">
@@ -91134,7 +91134,7 @@
         <v>23</v>
       </c>
       <c r="C3360" t="n">
-        <v>26.39</v>
+        <v>28.94</v>
       </c>
       <c r="D3360" t="inlineStr">
         <is>
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3361">
@@ -91161,7 +91161,7 @@
         <v>24</v>
       </c>
       <c r="C3361" t="n">
-        <v>23.48</v>
+        <v>24.13</v>
       </c>
       <c r="D3361" t="inlineStr">
         <is>
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3362">
@@ -91188,7 +91188,7 @@
         <v>1</v>
       </c>
       <c r="C3362" t="n">
-        <v>12.17</v>
+        <v>10.46</v>
       </c>
       <c r="D3362" t="inlineStr">
         <is>
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3363">
@@ -91215,7 +91215,7 @@
         <v>2</v>
       </c>
       <c r="C3363" t="n">
-        <v>13.53</v>
+        <v>13.32</v>
       </c>
       <c r="D3363" t="inlineStr">
         <is>
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3364">
@@ -91242,7 +91242,7 @@
         <v>3</v>
       </c>
       <c r="C3364" t="n">
-        <v>14.24</v>
+        <v>13.95</v>
       </c>
       <c r="D3364" t="inlineStr">
         <is>
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3365">
@@ -91269,7 +91269,7 @@
         <v>4</v>
       </c>
       <c r="C3365" t="n">
-        <v>15.45</v>
+        <v>14.01</v>
       </c>
       <c r="D3365" t="inlineStr">
         <is>
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3366">
@@ -91296,7 +91296,7 @@
         <v>5</v>
       </c>
       <c r="C3366" t="n">
-        <v>17.12</v>
+        <v>16.89</v>
       </c>
       <c r="D3366" t="inlineStr">
         <is>
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3367">
@@ -91323,7 +91323,7 @@
         <v>6</v>
       </c>
       <c r="C3367" t="n">
-        <v>18.34</v>
+        <v>18.78</v>
       </c>
       <c r="D3367" t="inlineStr">
         <is>
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3368">
@@ -91350,7 +91350,7 @@
         <v>7</v>
       </c>
       <c r="C3368" t="n">
-        <v>18.8</v>
+        <v>17.17</v>
       </c>
       <c r="D3368" t="inlineStr">
         <is>
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3369">
@@ -91377,7 +91377,7 @@
         <v>8</v>
       </c>
       <c r="C3369" t="n">
-        <v>20.91</v>
+        <v>44.73</v>
       </c>
       <c r="D3369" t="inlineStr">
         <is>
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3370">
@@ -91404,7 +91404,7 @@
         <v>9</v>
       </c>
       <c r="C3370" t="n">
-        <v>19.14</v>
+        <v>43.44</v>
       </c>
       <c r="D3370" t="inlineStr">
         <is>
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3371">
@@ -91431,7 +91431,7 @@
         <v>10</v>
       </c>
       <c r="C3371" t="n">
-        <v>16.99</v>
+        <v>32.74</v>
       </c>
       <c r="D3371" t="inlineStr">
         <is>
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3372">
@@ -91458,7 +91458,7 @@
         <v>11</v>
       </c>
       <c r="C3372" t="n">
-        <v>18.79</v>
+        <v>22.73</v>
       </c>
       <c r="D3372" t="inlineStr">
         <is>
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3373">
@@ -91485,7 +91485,7 @@
         <v>12</v>
       </c>
       <c r="C3373" t="n">
-        <v>21.17</v>
+        <v>28.54</v>
       </c>
       <c r="D3373" t="inlineStr">
         <is>
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3374">
@@ -91512,7 +91512,7 @@
         <v>13</v>
       </c>
       <c r="C3374" t="n">
-        <v>21.02</v>
+        <v>29.22</v>
       </c>
       <c r="D3374" t="inlineStr">
         <is>
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3375">
@@ -91539,7 +91539,7 @@
         <v>14</v>
       </c>
       <c r="C3375" t="n">
-        <v>18.36</v>
+        <v>26.29</v>
       </c>
       <c r="D3375" t="inlineStr">
         <is>
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3376">
@@ -91566,7 +91566,7 @@
         <v>15</v>
       </c>
       <c r="C3376" t="n">
-        <v>18.56</v>
+        <v>28.37</v>
       </c>
       <c r="D3376" t="inlineStr">
         <is>
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3377">
@@ -91593,7 +91593,7 @@
         <v>16</v>
       </c>
       <c r="C3377" t="n">
-        <v>18.99</v>
+        <v>27.39</v>
       </c>
       <c r="D3377" t="inlineStr">
         <is>
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3378">
@@ -91620,7 +91620,7 @@
         <v>17</v>
       </c>
       <c r="C3378" t="n">
-        <v>19.08</v>
+        <v>27.72</v>
       </c>
       <c r="D3378" t="inlineStr">
         <is>
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3379">
@@ -91647,7 +91647,7 @@
         <v>18</v>
       </c>
       <c r="C3379" t="n">
-        <v>19.47</v>
+        <v>25.05</v>
       </c>
       <c r="D3379" t="inlineStr">
         <is>
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3380">
@@ -91674,7 +91674,7 @@
         <v>19</v>
       </c>
       <c r="C3380" t="n">
-        <v>16.72</v>
+        <v>19.15</v>
       </c>
       <c r="D3380" t="inlineStr">
         <is>
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3381">
@@ -91701,7 +91701,7 @@
         <v>20</v>
       </c>
       <c r="C3381" t="n">
-        <v>15.45</v>
+        <v>31.38</v>
       </c>
       <c r="D3381" t="inlineStr">
         <is>
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3382">
@@ -91728,7 +91728,7 @@
         <v>21</v>
       </c>
       <c r="C3382" t="n">
-        <v>15.19</v>
+        <v>46.85</v>
       </c>
       <c r="D3382" t="inlineStr">
         <is>
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3383">
@@ -91755,7 +91755,7 @@
         <v>22</v>
       </c>
       <c r="C3383" t="n">
-        <v>17.35</v>
+        <v>48.85</v>
       </c>
       <c r="D3383" t="inlineStr">
         <is>
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3384">
@@ -91782,7 +91782,7 @@
         <v>23</v>
       </c>
       <c r="C3384" t="n">
-        <v>15.98</v>
+        <v>35.28</v>
       </c>
       <c r="D3384" t="inlineStr">
         <is>
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3385">
@@ -91809,7 +91809,7 @@
         <v>24</v>
       </c>
       <c r="C3385" t="n">
-        <v>13.01</v>
+        <v>25.4</v>
       </c>
       <c r="D3385" t="inlineStr">
         <is>
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3386">
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3387">
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3388">
@@ -91890,7 +91890,7 @@
         <v>3</v>
       </c>
       <c r="C3388" t="n">
-        <v>13.92</v>
+        <v>13.89</v>
       </c>
       <c r="D3388" t="inlineStr">
         <is>
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3389">
@@ -91917,7 +91917,7 @@
         <v>4</v>
       </c>
       <c r="C3389" t="n">
-        <v>13.79</v>
+        <v>13.77</v>
       </c>
       <c r="D3389" t="inlineStr">
         <is>
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3390">
@@ -91944,7 +91944,7 @@
         <v>5</v>
       </c>
       <c r="C3390" t="n">
-        <v>13.84</v>
+        <v>13.8</v>
       </c>
       <c r="D3390" t="inlineStr">
         <is>
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3391">
@@ -91971,7 +91971,7 @@
         <v>6</v>
       </c>
       <c r="C3391" t="n">
-        <v>14.84</v>
+        <v>14.78</v>
       </c>
       <c r="D3391" t="inlineStr">
         <is>
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3392">
@@ -91998,7 +91998,7 @@
         <v>7</v>
       </c>
       <c r="C3392" t="n">
-        <v>18.59</v>
+        <v>15.68</v>
       </c>
       <c r="D3392" t="inlineStr">
         <is>
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3393">
@@ -92025,7 +92025,7 @@
         <v>8</v>
       </c>
       <c r="C3393" t="n">
-        <v>32.93</v>
+        <v>27.33</v>
       </c>
       <c r="D3393" t="inlineStr">
         <is>
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3394">
@@ -92052,7 +92052,7 @@
         <v>9</v>
       </c>
       <c r="C3394" t="n">
-        <v>35.79</v>
+        <v>33.01</v>
       </c>
       <c r="D3394" t="inlineStr">
         <is>
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3395">
@@ -92079,7 +92079,7 @@
         <v>10</v>
       </c>
       <c r="C3395" t="n">
-        <v>21.77</v>
+        <v>21.78</v>
       </c>
       <c r="D3395" t="inlineStr">
         <is>
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3396">
@@ -92106,7 +92106,7 @@
         <v>11</v>
       </c>
       <c r="C3396" t="n">
-        <v>22.13</v>
+        <v>22.17</v>
       </c>
       <c r="D3396" t="inlineStr">
         <is>
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3397">
@@ -92133,7 +92133,7 @@
         <v>12</v>
       </c>
       <c r="C3397" t="n">
-        <v>22</v>
+        <v>22.03</v>
       </c>
       <c r="D3397" t="inlineStr">
         <is>
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3398">
@@ -92160,7 +92160,7 @@
         <v>13</v>
       </c>
       <c r="C3398" t="n">
-        <v>21.85</v>
+        <v>21.84</v>
       </c>
       <c r="D3398" t="inlineStr">
         <is>
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3399">
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3400">
@@ -92214,7 +92214,7 @@
         <v>15</v>
       </c>
       <c r="C3400" t="n">
-        <v>21.56</v>
+        <v>21.54</v>
       </c>
       <c r="D3400" t="inlineStr">
         <is>
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3401">
@@ -92241,7 +92241,7 @@
         <v>16</v>
       </c>
       <c r="C3401" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="D3401" t="inlineStr">
         <is>
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3402">
@@ -92268,7 +92268,7 @@
         <v>17</v>
       </c>
       <c r="C3402" t="n">
-        <v>22.29</v>
+        <v>22.17</v>
       </c>
       <c r="D3402" t="inlineStr">
         <is>
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3403">
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3404">
@@ -92322,7 +92322,7 @@
         <v>19</v>
       </c>
       <c r="C3404" t="n">
-        <v>21.64</v>
+        <v>21.47</v>
       </c>
       <c r="D3404" t="inlineStr">
         <is>
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3405">
@@ -92349,7 +92349,7 @@
         <v>20</v>
       </c>
       <c r="C3405" t="n">
-        <v>26.85</v>
+        <v>20.83</v>
       </c>
       <c r="D3405" t="inlineStr">
         <is>
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3406">
@@ -92376,7 +92376,7 @@
         <v>21</v>
       </c>
       <c r="C3406" t="n">
-        <v>40.73</v>
+        <v>19.15</v>
       </c>
       <c r="D3406" t="inlineStr">
         <is>
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3407">
@@ -92403,7 +92403,7 @@
         <v>22</v>
       </c>
       <c r="C3407" t="n">
-        <v>39.54</v>
+        <v>15.22</v>
       </c>
       <c r="D3407" t="inlineStr">
         <is>
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3408">
@@ -92430,7 +92430,7 @@
         <v>23</v>
       </c>
       <c r="C3408" t="n">
-        <v>21.53</v>
+        <v>10.96</v>
       </c>
       <c r="D3408" t="inlineStr">
         <is>
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
       </c>
     </row>
     <row r="3409">
@@ -92457,7 +92457,7 @@
         <v>24</v>
       </c>
       <c r="C3409" t="n">
-        <v>22.84</v>
+        <v>11.57</v>
       </c>
       <c r="D3409" t="inlineStr">
         <is>
@@ -92473,7 +92473,655 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46285.44740370638</v>
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3410">
+      <c r="A3410" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3410" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3410" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="D3410" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3410" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3410" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3410" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3411">
+      <c r="A3411" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3411" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3411" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="D3411" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3411" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3411" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3411" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3412">
+      <c r="A3412" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3412" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3412" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="D3412" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3412" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3412" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3412" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3413">
+      <c r="A3413" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3413" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3413" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="D3413" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3413" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3413" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3413" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3414">
+      <c r="A3414" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3414" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3414" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D3414" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3414" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3414" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3414" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3415">
+      <c r="A3415" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3415" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3415" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="D3415" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3415" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3415" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3415" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3416">
+      <c r="A3416" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3416" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3416" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="D3416" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3416" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3416" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3416" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3417">
+      <c r="A3417" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3417" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3417" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="D3417" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3417" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3417" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3417" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3418">
+      <c r="A3418" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3418" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3418" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="D3418" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3418" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3418" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3418" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3419">
+      <c r="A3419" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3419" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3419" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="D3419" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3419" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3419" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3419" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3420">
+      <c r="A3420" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3420" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3420" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="D3420" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3420" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3420" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3420" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3421">
+      <c r="A3421" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3421" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3421" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D3421" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3421" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3421" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3421" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3422">
+      <c r="A3422" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3422" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3422" t="n">
+        <v>28.64</v>
+      </c>
+      <c r="D3422" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3422" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3422" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3422" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3423">
+      <c r="A3423" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3423" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3423" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D3423" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3423" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3423" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3423" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3424">
+      <c r="A3424" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3424" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3424" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="D3424" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3424" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3424" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3424" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3425">
+      <c r="A3425" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3425" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3425" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="D3425" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3425" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3425" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3425" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3426">
+      <c r="A3426" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3426" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3426" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="D3426" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3426" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3426" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3426" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3427">
+      <c r="A3427" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3427" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3427" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="D3427" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3427" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3427" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3427" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3428">
+      <c r="A3428" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3428" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3428" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="D3428" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3428" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3428" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3428" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3429">
+      <c r="A3429" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3429" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3429" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="D3429" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3429" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3429" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3429" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3430">
+      <c r="A3430" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3430" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3430" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="D3430" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3430" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3430" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3430" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3431">
+      <c r="A3431" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3431" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3431" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="D3431" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3431" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3431" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3431" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3432">
+      <c r="A3432" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3432" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3432" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="D3432" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3432" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3432" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3432" s="2" t="n">
+        <v>46285.851082999</v>
+      </c>
+    </row>
+    <row r="3433">
+      <c r="A3433" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3433" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3433" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="D3433" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3433" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3433" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3433" s="2" t="n">
+        <v>46285.851082999</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3324">
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3333">
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3335">
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3337">
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3341">
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3343">
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3344">
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3345">
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3346">
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3347">
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3355">
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3356">
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3357">
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3360">
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3362">
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3364">
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3365">
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3366">
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3367">
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3368">
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3369">
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3370">
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3371">
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3372">
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3373">
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3374">
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3375">
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3376">
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3377">
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3378">
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3379">
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3380">
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3381">
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3382">
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3383">
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3384">
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3385">
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3386">
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3387">
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3388">
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3389">
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3390">
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3391">
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3392">
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3393">
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3394">
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3395">
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3396">
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3397">
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3398">
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3399">
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3400">
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3401">
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3402">
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3403">
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3404">
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3405">
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3406">
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3407">
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3408">
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3409">
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3410">
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3411">
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3412">
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3413">
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3415">
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3416">
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3417">
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3418">
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3419">
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3420">
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3421">
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3422">
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3423">
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3424">
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3425">
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3426">
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3427">
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3428">
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3429">
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3430">
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3431">
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3432">
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
     <row r="3433">
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46285.851082999</v>
+        <v>46286.50551372054</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3433"/>
+  <dimension ref="A1:G3457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89892,7 +89892,7 @@
         <v>1</v>
       </c>
       <c r="C3314" t="n">
-        <v>9.869999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="D3314" t="inlineStr">
         <is>
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3315">
@@ -89919,7 +89919,7 @@
         <v>2</v>
       </c>
       <c r="C3315" t="n">
-        <v>10.55</v>
+        <v>10.52</v>
       </c>
       <c r="D3315" t="inlineStr">
         <is>
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3316">
@@ -89946,7 +89946,7 @@
         <v>3</v>
       </c>
       <c r="C3316" t="n">
-        <v>12.1</v>
+        <v>12.03</v>
       </c>
       <c r="D3316" t="inlineStr">
         <is>
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3317">
@@ -89973,7 +89973,7 @@
         <v>4</v>
       </c>
       <c r="C3317" t="n">
-        <v>13.5</v>
+        <v>13.45</v>
       </c>
       <c r="D3317" t="inlineStr">
         <is>
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3318">
@@ -90000,7 +90000,7 @@
         <v>5</v>
       </c>
       <c r="C3318" t="n">
-        <v>13.4</v>
+        <v>13.37</v>
       </c>
       <c r="D3318" t="inlineStr">
         <is>
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3319">
@@ -90027,7 +90027,7 @@
         <v>6</v>
       </c>
       <c r="C3319" t="n">
-        <v>11.61</v>
+        <v>11.57</v>
       </c>
       <c r="D3319" t="inlineStr">
         <is>
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3320">
@@ -90054,7 +90054,7 @@
         <v>7</v>
       </c>
       <c r="C3320" t="n">
-        <v>12.69</v>
+        <v>12.65</v>
       </c>
       <c r="D3320" t="inlineStr">
         <is>
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3321">
@@ -90081,7 +90081,7 @@
         <v>8</v>
       </c>
       <c r="C3321" t="n">
-        <v>32</v>
+        <v>31.93</v>
       </c>
       <c r="D3321" t="inlineStr">
         <is>
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3322">
@@ -90108,7 +90108,7 @@
         <v>9</v>
       </c>
       <c r="C3322" t="n">
-        <v>33.09</v>
+        <v>33.07</v>
       </c>
       <c r="D3322" t="inlineStr">
         <is>
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3324">
@@ -90162,7 +90162,7 @@
         <v>11</v>
       </c>
       <c r="C3324" t="n">
-        <v>26.67</v>
+        <v>26.79</v>
       </c>
       <c r="D3324" t="inlineStr">
         <is>
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3325">
@@ -90189,7 +90189,7 @@
         <v>12</v>
       </c>
       <c r="C3325" t="n">
-        <v>32.36</v>
+        <v>32.28</v>
       </c>
       <c r="D3325" t="inlineStr">
         <is>
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3326">
@@ -90216,7 +90216,7 @@
         <v>13</v>
       </c>
       <c r="C3326" t="n">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="D3326" t="inlineStr">
         <is>
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3327">
@@ -90243,7 +90243,7 @@
         <v>14</v>
       </c>
       <c r="C3327" t="n">
-        <v>32.73</v>
+        <v>32.59</v>
       </c>
       <c r="D3327" t="inlineStr">
         <is>
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3328">
@@ -90270,7 +90270,7 @@
         <v>15</v>
       </c>
       <c r="C3328" t="n">
-        <v>33.27</v>
+        <v>33.15</v>
       </c>
       <c r="D3328" t="inlineStr">
         <is>
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3329">
@@ -90297,7 +90297,7 @@
         <v>16</v>
       </c>
       <c r="C3329" t="n">
-        <v>33.19</v>
+        <v>33.05</v>
       </c>
       <c r="D3329" t="inlineStr">
         <is>
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3330">
@@ -90324,7 +90324,7 @@
         <v>17</v>
       </c>
       <c r="C3330" t="n">
-        <v>31.59</v>
+        <v>31.57</v>
       </c>
       <c r="D3330" t="inlineStr">
         <is>
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3331">
@@ -90351,7 +90351,7 @@
         <v>18</v>
       </c>
       <c r="C3331" t="n">
-        <v>34.24</v>
+        <v>34.2</v>
       </c>
       <c r="D3331" t="inlineStr">
         <is>
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3333">
@@ -90405,7 +90405,7 @@
         <v>20</v>
       </c>
       <c r="C3333" t="n">
-        <v>24.06</v>
+        <v>24.03</v>
       </c>
       <c r="D3333" t="inlineStr">
         <is>
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3334">
@@ -90432,7 +90432,7 @@
         <v>21</v>
       </c>
       <c r="C3334" t="n">
-        <v>34.32</v>
+        <v>34.24</v>
       </c>
       <c r="D3334" t="inlineStr">
         <is>
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3335">
@@ -90459,7 +90459,7 @@
         <v>22</v>
       </c>
       <c r="C3335" t="n">
-        <v>33.48</v>
+        <v>33.39</v>
       </c>
       <c r="D3335" t="inlineStr">
         <is>
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3336">
@@ -90486,7 +90486,7 @@
         <v>23</v>
       </c>
       <c r="C3336" t="n">
-        <v>28.29</v>
+        <v>28.25</v>
       </c>
       <c r="D3336" t="inlineStr">
         <is>
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3337">
@@ -90513,7 +90513,7 @@
         <v>24</v>
       </c>
       <c r="C3337" t="n">
-        <v>22.79</v>
+        <v>22.78</v>
       </c>
       <c r="D3337" t="inlineStr">
         <is>
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3338">
@@ -90540,7 +90540,7 @@
         <v>1</v>
       </c>
       <c r="C3338" t="n">
-        <v>10.17</v>
+        <v>10.21</v>
       </c>
       <c r="D3338" t="inlineStr">
         <is>
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3339">
@@ -90567,7 +90567,7 @@
         <v>2</v>
       </c>
       <c r="C3339" t="n">
-        <v>13.19</v>
+        <v>13.11</v>
       </c>
       <c r="D3339" t="inlineStr">
         <is>
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3340">
@@ -90594,7 +90594,7 @@
         <v>3</v>
       </c>
       <c r="C3340" t="n">
-        <v>15.44</v>
+        <v>15.42</v>
       </c>
       <c r="D3340" t="inlineStr">
         <is>
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3341">
@@ -90621,7 +90621,7 @@
         <v>4</v>
       </c>
       <c r="C3341" t="n">
-        <v>17.67</v>
+        <v>17.64</v>
       </c>
       <c r="D3341" t="inlineStr">
         <is>
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3342">
@@ -90648,7 +90648,7 @@
         <v>5</v>
       </c>
       <c r="C3342" t="n">
-        <v>16.86</v>
+        <v>16.79</v>
       </c>
       <c r="D3342" t="inlineStr">
         <is>
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3343">
@@ -90675,7 +90675,7 @@
         <v>6</v>
       </c>
       <c r="C3343" t="n">
-        <v>15.43</v>
+        <v>15.41</v>
       </c>
       <c r="D3343" t="inlineStr">
         <is>
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3344">
@@ -90702,7 +90702,7 @@
         <v>7</v>
       </c>
       <c r="C3344" t="n">
-        <v>20.02</v>
+        <v>19.88</v>
       </c>
       <c r="D3344" t="inlineStr">
         <is>
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3345">
@@ -90729,7 +90729,7 @@
         <v>8</v>
       </c>
       <c r="C3345" t="n">
-        <v>43.69</v>
+        <v>43.51</v>
       </c>
       <c r="D3345" t="inlineStr">
         <is>
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3346">
@@ -90756,7 +90756,7 @@
         <v>9</v>
       </c>
       <c r="C3346" t="n">
-        <v>44.24</v>
+        <v>44.08</v>
       </c>
       <c r="D3346" t="inlineStr">
         <is>
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3347">
@@ -90783,7 +90783,7 @@
         <v>10</v>
       </c>
       <c r="C3347" t="n">
-        <v>26.21</v>
+        <v>26.02</v>
       </c>
       <c r="D3347" t="inlineStr">
         <is>
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3348">
@@ -90810,7 +90810,7 @@
         <v>11</v>
       </c>
       <c r="C3348" t="n">
-        <v>22.15</v>
+        <v>21.89</v>
       </c>
       <c r="D3348" t="inlineStr">
         <is>
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3349">
@@ -90837,7 +90837,7 @@
         <v>12</v>
       </c>
       <c r="C3349" t="n">
-        <v>26.25</v>
+        <v>25.93</v>
       </c>
       <c r="D3349" t="inlineStr">
         <is>
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3350">
@@ -90864,7 +90864,7 @@
         <v>13</v>
       </c>
       <c r="C3350" t="n">
-        <v>24.25</v>
+        <v>23.97</v>
       </c>
       <c r="D3350" t="inlineStr">
         <is>
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3351">
@@ -90891,7 +90891,7 @@
         <v>14</v>
       </c>
       <c r="C3351" t="n">
-        <v>24.42</v>
+        <v>24.17</v>
       </c>
       <c r="D3351" t="inlineStr">
         <is>
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3352">
@@ -90918,7 +90918,7 @@
         <v>15</v>
       </c>
       <c r="C3352" t="n">
-        <v>24.53</v>
+        <v>24.3</v>
       </c>
       <c r="D3352" t="inlineStr">
         <is>
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3353">
@@ -90945,7 +90945,7 @@
         <v>16</v>
       </c>
       <c r="C3353" t="n">
-        <v>24.72</v>
+        <v>24.44</v>
       </c>
       <c r="D3353" t="inlineStr">
         <is>
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3354">
@@ -90972,7 +90972,7 @@
         <v>17</v>
       </c>
       <c r="C3354" t="n">
-        <v>23.64</v>
+        <v>23.41</v>
       </c>
       <c r="D3354" t="inlineStr">
         <is>
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3355">
@@ -90999,7 +90999,7 @@
         <v>18</v>
       </c>
       <c r="C3355" t="n">
-        <v>20.54</v>
+        <v>21.1</v>
       </c>
       <c r="D3355" t="inlineStr">
         <is>
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3356">
@@ -91026,7 +91026,7 @@
         <v>19</v>
       </c>
       <c r="C3356" t="n">
-        <v>17.15</v>
+        <v>17.41</v>
       </c>
       <c r="D3356" t="inlineStr">
         <is>
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3357">
@@ -91053,7 +91053,7 @@
         <v>20</v>
       </c>
       <c r="C3357" t="n">
-        <v>25.95</v>
+        <v>25.87</v>
       </c>
       <c r="D3357" t="inlineStr">
         <is>
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3358">
@@ -91080,7 +91080,7 @@
         <v>21</v>
       </c>
       <c r="C3358" t="n">
-        <v>36.48</v>
+        <v>36.36</v>
       </c>
       <c r="D3358" t="inlineStr">
         <is>
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3359">
@@ -91107,7 +91107,7 @@
         <v>22</v>
       </c>
       <c r="C3359" t="n">
-        <v>33.76</v>
+        <v>33.65</v>
       </c>
       <c r="D3359" t="inlineStr">
         <is>
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3360">
@@ -91134,7 +91134,7 @@
         <v>23</v>
       </c>
       <c r="C3360" t="n">
-        <v>28.94</v>
+        <v>28.84</v>
       </c>
       <c r="D3360" t="inlineStr">
         <is>
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3361">
@@ -91161,7 +91161,7 @@
         <v>24</v>
       </c>
       <c r="C3361" t="n">
-        <v>24.13</v>
+        <v>24.02</v>
       </c>
       <c r="D3361" t="inlineStr">
         <is>
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3362">
@@ -91188,7 +91188,7 @@
         <v>1</v>
       </c>
       <c r="C3362" t="n">
-        <v>10.46</v>
+        <v>11.43</v>
       </c>
       <c r="D3362" t="inlineStr">
         <is>
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3363">
@@ -91215,7 +91215,7 @@
         <v>2</v>
       </c>
       <c r="C3363" t="n">
-        <v>13.32</v>
+        <v>13.6</v>
       </c>
       <c r="D3363" t="inlineStr">
         <is>
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3364">
@@ -91242,7 +91242,7 @@
         <v>3</v>
       </c>
       <c r="C3364" t="n">
-        <v>13.95</v>
+        <v>13.8</v>
       </c>
       <c r="D3364" t="inlineStr">
         <is>
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3365">
@@ -91269,7 +91269,7 @@
         <v>4</v>
       </c>
       <c r="C3365" t="n">
-        <v>14.01</v>
+        <v>14.17</v>
       </c>
       <c r="D3365" t="inlineStr">
         <is>
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3366">
@@ -91296,7 +91296,7 @@
         <v>5</v>
       </c>
       <c r="C3366" t="n">
-        <v>16.89</v>
+        <v>16.45</v>
       </c>
       <c r="D3366" t="inlineStr">
         <is>
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3367">
@@ -91323,7 +91323,7 @@
         <v>6</v>
       </c>
       <c r="C3367" t="n">
-        <v>18.78</v>
+        <v>18.38</v>
       </c>
       <c r="D3367" t="inlineStr">
         <is>
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3368">
@@ -91350,7 +91350,7 @@
         <v>7</v>
       </c>
       <c r="C3368" t="n">
-        <v>17.17</v>
+        <v>17.12</v>
       </c>
       <c r="D3368" t="inlineStr">
         <is>
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3369">
@@ -91377,7 +91377,7 @@
         <v>8</v>
       </c>
       <c r="C3369" t="n">
-        <v>44.73</v>
+        <v>43.73</v>
       </c>
       <c r="D3369" t="inlineStr">
         <is>
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3370">
@@ -91404,7 +91404,7 @@
         <v>9</v>
       </c>
       <c r="C3370" t="n">
-        <v>43.44</v>
+        <v>42.63</v>
       </c>
       <c r="D3370" t="inlineStr">
         <is>
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3371">
@@ -91431,7 +91431,7 @@
         <v>10</v>
       </c>
       <c r="C3371" t="n">
-        <v>32.74</v>
+        <v>32.6</v>
       </c>
       <c r="D3371" t="inlineStr">
         <is>
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3372">
@@ -91458,7 +91458,7 @@
         <v>11</v>
       </c>
       <c r="C3372" t="n">
-        <v>22.73</v>
+        <v>24.05</v>
       </c>
       <c r="D3372" t="inlineStr">
         <is>
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3373">
@@ -91485,7 +91485,7 @@
         <v>12</v>
       </c>
       <c r="C3373" t="n">
-        <v>28.54</v>
+        <v>27.63</v>
       </c>
       <c r="D3373" t="inlineStr">
         <is>
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3374">
@@ -91512,7 +91512,7 @@
         <v>13</v>
       </c>
       <c r="C3374" t="n">
-        <v>29.22</v>
+        <v>27.48</v>
       </c>
       <c r="D3374" t="inlineStr">
         <is>
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3375">
@@ -91539,7 +91539,7 @@
         <v>14</v>
       </c>
       <c r="C3375" t="n">
-        <v>26.29</v>
+        <v>25.4</v>
       </c>
       <c r="D3375" t="inlineStr">
         <is>
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3376">
@@ -91566,7 +91566,7 @@
         <v>15</v>
       </c>
       <c r="C3376" t="n">
-        <v>28.37</v>
+        <v>26.62</v>
       </c>
       <c r="D3376" t="inlineStr">
         <is>
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3377">
@@ -91593,7 +91593,7 @@
         <v>16</v>
       </c>
       <c r="C3377" t="n">
-        <v>27.39</v>
+        <v>26.41</v>
       </c>
       <c r="D3377" t="inlineStr">
         <is>
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3378">
@@ -91620,7 +91620,7 @@
         <v>17</v>
       </c>
       <c r="C3378" t="n">
-        <v>27.72</v>
+        <v>25.89</v>
       </c>
       <c r="D3378" t="inlineStr">
         <is>
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3379">
@@ -91647,7 +91647,7 @@
         <v>18</v>
       </c>
       <c r="C3379" t="n">
-        <v>25.05</v>
+        <v>24.62</v>
       </c>
       <c r="D3379" t="inlineStr">
         <is>
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3380">
@@ -91674,7 +91674,7 @@
         <v>19</v>
       </c>
       <c r="C3380" t="n">
-        <v>19.15</v>
+        <v>20.39</v>
       </c>
       <c r="D3380" t="inlineStr">
         <is>
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3381">
@@ -91701,7 +91701,7 @@
         <v>20</v>
       </c>
       <c r="C3381" t="n">
-        <v>31.38</v>
+        <v>31.7</v>
       </c>
       <c r="D3381" t="inlineStr">
         <is>
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3382">
@@ -91728,7 +91728,7 @@
         <v>21</v>
       </c>
       <c r="C3382" t="n">
-        <v>46.85</v>
+        <v>46.35</v>
       </c>
       <c r="D3382" t="inlineStr">
         <is>
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3383">
@@ -91755,7 +91755,7 @@
         <v>22</v>
       </c>
       <c r="C3383" t="n">
-        <v>48.85</v>
+        <v>47.88</v>
       </c>
       <c r="D3383" t="inlineStr">
         <is>
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3384">
@@ -91782,7 +91782,7 @@
         <v>23</v>
       </c>
       <c r="C3384" t="n">
-        <v>35.28</v>
+        <v>34.94</v>
       </c>
       <c r="D3384" t="inlineStr">
         <is>
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3385">
@@ -91809,7 +91809,7 @@
         <v>24</v>
       </c>
       <c r="C3385" t="n">
-        <v>25.4</v>
+        <v>25.15</v>
       </c>
       <c r="D3385" t="inlineStr">
         <is>
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3386">
@@ -91836,7 +91836,7 @@
         <v>1</v>
       </c>
       <c r="C3386" t="n">
-        <v>11.53</v>
+        <v>11.45</v>
       </c>
       <c r="D3386" t="inlineStr">
         <is>
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3387">
@@ -91863,7 +91863,7 @@
         <v>2</v>
       </c>
       <c r="C3387" t="n">
-        <v>13.33</v>
+        <v>12.73</v>
       </c>
       <c r="D3387" t="inlineStr">
         <is>
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3388">
@@ -91890,7 +91890,7 @@
         <v>3</v>
       </c>
       <c r="C3388" t="n">
-        <v>13.89</v>
+        <v>13.56</v>
       </c>
       <c r="D3388" t="inlineStr">
         <is>
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3389">
@@ -91917,7 +91917,7 @@
         <v>4</v>
       </c>
       <c r="C3389" t="n">
-        <v>13.77</v>
+        <v>15.25</v>
       </c>
       <c r="D3389" t="inlineStr">
         <is>
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3390">
@@ -91944,7 +91944,7 @@
         <v>5</v>
       </c>
       <c r="C3390" t="n">
-        <v>13.8</v>
+        <v>14.58</v>
       </c>
       <c r="D3390" t="inlineStr">
         <is>
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3391">
@@ -91971,7 +91971,7 @@
         <v>6</v>
       </c>
       <c r="C3391" t="n">
-        <v>14.78</v>
+        <v>15.26</v>
       </c>
       <c r="D3391" t="inlineStr">
         <is>
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3392">
@@ -91998,7 +91998,7 @@
         <v>7</v>
       </c>
       <c r="C3392" t="n">
-        <v>15.68</v>
+        <v>21.04</v>
       </c>
       <c r="D3392" t="inlineStr">
         <is>
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3393">
@@ -92025,7 +92025,7 @@
         <v>8</v>
       </c>
       <c r="C3393" t="n">
-        <v>27.33</v>
+        <v>37.47</v>
       </c>
       <c r="D3393" t="inlineStr">
         <is>
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3394">
@@ -92052,7 +92052,7 @@
         <v>9</v>
       </c>
       <c r="C3394" t="n">
-        <v>33.01</v>
+        <v>36.89</v>
       </c>
       <c r="D3394" t="inlineStr">
         <is>
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3395">
@@ -92079,7 +92079,7 @@
         <v>10</v>
       </c>
       <c r="C3395" t="n">
-        <v>21.78</v>
+        <v>18.57</v>
       </c>
       <c r="D3395" t="inlineStr">
         <is>
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3396">
@@ -92106,7 +92106,7 @@
         <v>11</v>
       </c>
       <c r="C3396" t="n">
-        <v>22.17</v>
+        <v>22.53</v>
       </c>
       <c r="D3396" t="inlineStr">
         <is>
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3397">
@@ -92133,7 +92133,7 @@
         <v>12</v>
       </c>
       <c r="C3397" t="n">
-        <v>22.03</v>
+        <v>23.44</v>
       </c>
       <c r="D3397" t="inlineStr">
         <is>
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3398">
@@ -92160,7 +92160,7 @@
         <v>13</v>
       </c>
       <c r="C3398" t="n">
-        <v>21.84</v>
+        <v>23.81</v>
       </c>
       <c r="D3398" t="inlineStr">
         <is>
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3399">
@@ -92187,7 +92187,7 @@
         <v>14</v>
       </c>
       <c r="C3399" t="n">
-        <v>21.5</v>
+        <v>23.16</v>
       </c>
       <c r="D3399" t="inlineStr">
         <is>
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3400">
@@ -92214,7 +92214,7 @@
         <v>15</v>
       </c>
       <c r="C3400" t="n">
-        <v>21.54</v>
+        <v>23.46</v>
       </c>
       <c r="D3400" t="inlineStr">
         <is>
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3401">
@@ -92241,7 +92241,7 @@
         <v>16</v>
       </c>
       <c r="C3401" t="n">
-        <v>22</v>
+        <v>24.23</v>
       </c>
       <c r="D3401" t="inlineStr">
         <is>
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3402">
@@ -92268,7 +92268,7 @@
         <v>17</v>
       </c>
       <c r="C3402" t="n">
-        <v>22.17</v>
+        <v>24.59</v>
       </c>
       <c r="D3402" t="inlineStr">
         <is>
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3403">
@@ -92295,7 +92295,7 @@
         <v>18</v>
       </c>
       <c r="C3403" t="n">
-        <v>21.77</v>
+        <v>22.37</v>
       </c>
       <c r="D3403" t="inlineStr">
         <is>
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3404">
@@ -92322,7 +92322,7 @@
         <v>19</v>
       </c>
       <c r="C3404" t="n">
-        <v>21.47</v>
+        <v>20.49</v>
       </c>
       <c r="D3404" t="inlineStr">
         <is>
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3405">
@@ -92349,7 +92349,7 @@
         <v>20</v>
       </c>
       <c r="C3405" t="n">
-        <v>20.83</v>
+        <v>25.24</v>
       </c>
       <c r="D3405" t="inlineStr">
         <is>
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3406">
@@ -92376,7 +92376,7 @@
         <v>21</v>
       </c>
       <c r="C3406" t="n">
-        <v>19.15</v>
+        <v>36.55</v>
       </c>
       <c r="D3406" t="inlineStr">
         <is>
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3407">
@@ -92403,7 +92403,7 @@
         <v>22</v>
       </c>
       <c r="C3407" t="n">
-        <v>15.22</v>
+        <v>38.44</v>
       </c>
       <c r="D3407" t="inlineStr">
         <is>
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3408">
@@ -92430,7 +92430,7 @@
         <v>23</v>
       </c>
       <c r="C3408" t="n">
-        <v>10.96</v>
+        <v>24.08</v>
       </c>
       <c r="D3408" t="inlineStr">
         <is>
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3409">
@@ -92457,7 +92457,7 @@
         <v>24</v>
       </c>
       <c r="C3409" t="n">
-        <v>11.57</v>
+        <v>24.32</v>
       </c>
       <c r="D3409" t="inlineStr">
         <is>
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3410">
@@ -92484,7 +92484,7 @@
         <v>1</v>
       </c>
       <c r="C3410" t="n">
-        <v>13.82</v>
+        <v>14.94</v>
       </c>
       <c r="D3410" t="inlineStr">
         <is>
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3411">
@@ -92511,7 +92511,7 @@
         <v>2</v>
       </c>
       <c r="C3411" t="n">
-        <v>14.12</v>
+        <v>17.12</v>
       </c>
       <c r="D3411" t="inlineStr">
         <is>
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3412">
@@ -92538,7 +92538,7 @@
         <v>3</v>
       </c>
       <c r="C3412" t="n">
-        <v>11.69</v>
+        <v>12.25</v>
       </c>
       <c r="D3412" t="inlineStr">
         <is>
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3413">
@@ -92565,7 +92565,7 @@
         <v>4</v>
       </c>
       <c r="C3413" t="n">
-        <v>11.54</v>
+        <v>11.7</v>
       </c>
       <c r="D3413" t="inlineStr">
         <is>
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3414">
@@ -92592,7 +92592,7 @@
         <v>5</v>
       </c>
       <c r="C3414" t="n">
-        <v>11.6</v>
+        <v>13.97</v>
       </c>
       <c r="D3414" t="inlineStr">
         <is>
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3415">
@@ -92619,7 +92619,7 @@
         <v>6</v>
       </c>
       <c r="C3415" t="n">
-        <v>11.92</v>
+        <v>17.5</v>
       </c>
       <c r="D3415" t="inlineStr">
         <is>
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3416">
@@ -92646,7 +92646,7 @@
         <v>7</v>
       </c>
       <c r="C3416" t="n">
-        <v>12.55</v>
+        <v>16.49</v>
       </c>
       <c r="D3416" t="inlineStr">
         <is>
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3417">
@@ -92673,7 +92673,7 @@
         <v>8</v>
       </c>
       <c r="C3417" t="n">
-        <v>28.45</v>
+        <v>28.91</v>
       </c>
       <c r="D3417" t="inlineStr">
         <is>
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3418">
@@ -92700,7 +92700,7 @@
         <v>9</v>
       </c>
       <c r="C3418" t="n">
-        <v>44.42</v>
+        <v>42.55</v>
       </c>
       <c r="D3418" t="inlineStr">
         <is>
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3419">
@@ -92727,7 +92727,7 @@
         <v>10</v>
       </c>
       <c r="C3419" t="n">
-        <v>28.44</v>
+        <v>33.44</v>
       </c>
       <c r="D3419" t="inlineStr">
         <is>
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3420">
@@ -92754,7 +92754,7 @@
         <v>11</v>
       </c>
       <c r="C3420" t="n">
-        <v>23.62</v>
+        <v>27.77</v>
       </c>
       <c r="D3420" t="inlineStr">
         <is>
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3421">
@@ -92781,7 +92781,7 @@
         <v>12</v>
       </c>
       <c r="C3421" t="n">
-        <v>26.2</v>
+        <v>30.59</v>
       </c>
       <c r="D3421" t="inlineStr">
         <is>
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3422">
@@ -92808,7 +92808,7 @@
         <v>13</v>
       </c>
       <c r="C3422" t="n">
-        <v>28.64</v>
+        <v>33.59</v>
       </c>
       <c r="D3422" t="inlineStr">
         <is>
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3423">
@@ -92835,7 +92835,7 @@
         <v>14</v>
       </c>
       <c r="C3423" t="n">
-        <v>27.7</v>
+        <v>32.5</v>
       </c>
       <c r="D3423" t="inlineStr">
         <is>
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3424">
@@ -92862,7 +92862,7 @@
         <v>15</v>
       </c>
       <c r="C3424" t="n">
-        <v>27.38</v>
+        <v>32.81</v>
       </c>
       <c r="D3424" t="inlineStr">
         <is>
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3425">
@@ -92889,7 +92889,7 @@
         <v>16</v>
       </c>
       <c r="C3425" t="n">
-        <v>28.14</v>
+        <v>33.51</v>
       </c>
       <c r="D3425" t="inlineStr">
         <is>
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3426">
@@ -92916,7 +92916,7 @@
         <v>17</v>
       </c>
       <c r="C3426" t="n">
-        <v>28.19</v>
+        <v>32.57</v>
       </c>
       <c r="D3426" t="inlineStr">
         <is>
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3427">
@@ -92943,7 +92943,7 @@
         <v>18</v>
       </c>
       <c r="C3427" t="n">
-        <v>27.47</v>
+        <v>29.68</v>
       </c>
       <c r="D3427" t="inlineStr">
         <is>
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3428">
@@ -92970,7 +92970,7 @@
         <v>19</v>
       </c>
       <c r="C3428" t="n">
-        <v>26.08</v>
+        <v>24.82</v>
       </c>
       <c r="D3428" t="inlineStr">
         <is>
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3429">
@@ -92997,7 +92997,7 @@
         <v>20</v>
       </c>
       <c r="C3429" t="n">
-        <v>31.61</v>
+        <v>23.54</v>
       </c>
       <c r="D3429" t="inlineStr">
         <is>
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3430">
@@ -93024,7 +93024,7 @@
         <v>21</v>
       </c>
       <c r="C3430" t="n">
-        <v>41.14</v>
+        <v>33.13</v>
       </c>
       <c r="D3430" t="inlineStr">
         <is>
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3431">
@@ -93051,7 +93051,7 @@
         <v>22</v>
       </c>
       <c r="C3431" t="n">
-        <v>38.14</v>
+        <v>34.2</v>
       </c>
       <c r="D3431" t="inlineStr">
         <is>
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3432">
@@ -93078,7 +93078,7 @@
         <v>23</v>
       </c>
       <c r="C3432" t="n">
-        <v>20.06</v>
+        <v>22.36</v>
       </c>
       <c r="D3432" t="inlineStr">
         <is>
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46286.50551372054</v>
+        <v>46286.90642067112</v>
       </c>
     </row>
     <row r="3433">
@@ -93105,23 +93105,671 @@
         <v>24</v>
       </c>
       <c r="C3433" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="D3433" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3433" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3433" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3433" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3434">
+      <c r="A3434" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3434" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3434" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="D3434" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3434" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3434" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3434" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3435">
+      <c r="A3435" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3435" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3435" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="D3435" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3435" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3435" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3435" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3436">
+      <c r="A3436" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3436" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3436" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="D3436" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3436" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3436" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3436" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3437">
+      <c r="A3437" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3437" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3437" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="D3437" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3437" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3437" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3437" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3438">
+      <c r="A3438" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3438" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3438" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="D3438" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3438" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3438" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3438" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3439">
+      <c r="A3439" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3439" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3439" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="D3439" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3439" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3439" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3439" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3440">
+      <c r="A3440" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3440" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3440" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="D3440" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3440" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3440" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3440" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3441">
+      <c r="A3441" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3441" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3441" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="D3441" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3441" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3441" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3441" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3442">
+      <c r="A3442" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3442" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3442" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="D3442" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3442" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3442" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3442" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3443">
+      <c r="A3443" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3443" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3443" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="D3443" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3443" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3443" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3443" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3444">
+      <c r="A3444" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3444" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3444" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="D3444" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3444" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3444" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3444" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3445">
+      <c r="A3445" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3445" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3445" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="D3445" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3445" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3445" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3445" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3446">
+      <c r="A3446" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3446" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3446" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="D3446" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3446" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3446" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3446" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3447">
+      <c r="A3447" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3447" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3447" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="D3447" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3447" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3447" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3447" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3448">
+      <c r="A3448" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3448" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3448" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="D3448" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3448" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3448" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3448" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3449">
+      <c r="A3449" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3449" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3449" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="D3449" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3449" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3449" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3449" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3450">
+      <c r="A3450" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3450" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3450" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="D3450" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3450" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3450" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3450" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3451">
+      <c r="A3451" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3451" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3451" t="n">
         <v>22.24</v>
       </c>
-      <c r="D3433" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="E3433" t="inlineStr">
+      <c r="D3451" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3451" t="inlineStr">
         <is>
           <t>A2_prdemcad_20260901_20260930</t>
         </is>
       </c>
-      <c r="F3433" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3433" s="2" t="n">
-        <v>46286.50551372054</v>
+      <c r="F3451" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3451" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3452">
+      <c r="A3452" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3452" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3452" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="D3452" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3452" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3452" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3452" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3453">
+      <c r="A3453" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3453" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3453" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="D3453" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3453" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3453" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3453" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3454">
+      <c r="A3454" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3454" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3454" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="D3454" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3454" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3454" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3454" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3455">
+      <c r="A3455" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3455" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3455" t="n">
+        <v>46.11</v>
+      </c>
+      <c r="D3455" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3455" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3455" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3455" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3456">
+      <c r="A3456" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3456" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3456" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="D3456" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3456" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3456" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3456" s="2" t="n">
+        <v>46286.90642067112</v>
+      </c>
+    </row>
+    <row r="3457">
+      <c r="A3457" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3457" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3457" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="D3457" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3457" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3457" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3457" s="2" t="n">
+        <v>46286.90642067112</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3324">
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3333">
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3335">
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3337">
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3341">
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3343">
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3344">
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3345">
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3346">
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3347">
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3355">
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3356">
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3357">
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3360">
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3362">
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3364">
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3365">
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3366">
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3367">
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3368">
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3369">
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3370">
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3371">
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3372">
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3373">
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3374">
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3375">
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3376">
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3377">
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3378">
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3379">
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3380">
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3381">
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3382">
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3383">
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3384">
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3385">
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3386">
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3387">
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3388">
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3389">
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3390">
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3391">
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3392">
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3393">
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3394">
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3395">
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3396">
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3397">
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3398">
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3399">
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3400">
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3401">
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3402">
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3403">
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3404">
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3405">
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3406">
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3407">
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3408">
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3409">
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3410">
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3411">
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3412">
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3413">
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3415">
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3416">
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3417">
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3418">
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3419">
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3420">
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3421">
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3422">
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3423">
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3424">
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3425">
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3426">
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3427">
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3428">
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3429">
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3430">
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3431">
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3432">
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3433">
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3434">
@@ -93148,7 +93148,7 @@
         <v>3</v>
       </c>
       <c r="G3434" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3435">
@@ -93175,7 +93175,7 @@
         <v>3</v>
       </c>
       <c r="G3435" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3436">
@@ -93202,7 +93202,7 @@
         <v>3</v>
       </c>
       <c r="G3436" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3437">
@@ -93229,7 +93229,7 @@
         <v>3</v>
       </c>
       <c r="G3437" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3438">
@@ -93256,7 +93256,7 @@
         <v>3</v>
       </c>
       <c r="G3438" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3439">
@@ -93283,7 +93283,7 @@
         <v>3</v>
       </c>
       <c r="G3439" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3440">
@@ -93310,7 +93310,7 @@
         <v>3</v>
       </c>
       <c r="G3440" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3441">
@@ -93337,7 +93337,7 @@
         <v>3</v>
       </c>
       <c r="G3441" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3442">
@@ -93364,7 +93364,7 @@
         <v>3</v>
       </c>
       <c r="G3442" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3443">
@@ -93391,7 +93391,7 @@
         <v>3</v>
       </c>
       <c r="G3443" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3444">
@@ -93418,7 +93418,7 @@
         <v>3</v>
       </c>
       <c r="G3444" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3445">
@@ -93445,7 +93445,7 @@
         <v>3</v>
       </c>
       <c r="G3445" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3446">
@@ -93472,7 +93472,7 @@
         <v>3</v>
       </c>
       <c r="G3446" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3447">
@@ -93499,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="G3447" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3448">
@@ -93526,7 +93526,7 @@
         <v>3</v>
       </c>
       <c r="G3448" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3449">
@@ -93553,7 +93553,7 @@
         <v>3</v>
       </c>
       <c r="G3449" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3450">
@@ -93580,7 +93580,7 @@
         <v>3</v>
       </c>
       <c r="G3450" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3451">
@@ -93607,7 +93607,7 @@
         <v>3</v>
       </c>
       <c r="G3451" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3452">
@@ -93634,7 +93634,7 @@
         <v>3</v>
       </c>
       <c r="G3452" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3453">
@@ -93661,7 +93661,7 @@
         <v>3</v>
       </c>
       <c r="G3453" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3454">
@@ -93688,7 +93688,7 @@
         <v>3</v>
       </c>
       <c r="G3454" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3455">
@@ -93715,7 +93715,7 @@
         <v>3</v>
       </c>
       <c r="G3455" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3456">
@@ -93742,7 +93742,7 @@
         <v>3</v>
       </c>
       <c r="G3456" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
     <row r="3457">
@@ -93769,7 +93769,7 @@
         <v>3</v>
       </c>
       <c r="G3457" s="2" t="n">
-        <v>46286.90642067112</v>
+        <v>46287.46056840286</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3457"/>
+  <dimension ref="A1:G3481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3316">
@@ -89946,7 +89946,7 @@
         <v>3</v>
       </c>
       <c r="C3316" t="n">
-        <v>12.03</v>
+        <v>12.05</v>
       </c>
       <c r="D3316" t="inlineStr">
         <is>
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3320">
@@ -90054,7 +90054,7 @@
         <v>7</v>
       </c>
       <c r="C3320" t="n">
-        <v>12.65</v>
+        <v>12.64</v>
       </c>
       <c r="D3320" t="inlineStr">
         <is>
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3321">
@@ -90081,7 +90081,7 @@
         <v>8</v>
       </c>
       <c r="C3321" t="n">
-        <v>31.93</v>
+        <v>31.92</v>
       </c>
       <c r="D3321" t="inlineStr">
         <is>
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3322">
@@ -90108,7 +90108,7 @@
         <v>9</v>
       </c>
       <c r="C3322" t="n">
-        <v>33.07</v>
+        <v>33.01</v>
       </c>
       <c r="D3322" t="inlineStr">
         <is>
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3324">
@@ -90162,7 +90162,7 @@
         <v>11</v>
       </c>
       <c r="C3324" t="n">
-        <v>26.79</v>
+        <v>26.75</v>
       </c>
       <c r="D3324" t="inlineStr">
         <is>
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3325">
@@ -90189,7 +90189,7 @@
         <v>12</v>
       </c>
       <c r="C3325" t="n">
-        <v>32.28</v>
+        <v>32.27</v>
       </c>
       <c r="D3325" t="inlineStr">
         <is>
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3326">
@@ -90216,7 +90216,7 @@
         <v>13</v>
       </c>
       <c r="C3326" t="n">
-        <v>31.93</v>
+        <v>31.92</v>
       </c>
       <c r="D3326" t="inlineStr">
         <is>
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3328">
@@ -90270,7 +90270,7 @@
         <v>15</v>
       </c>
       <c r="C3328" t="n">
-        <v>33.15</v>
+        <v>33.1</v>
       </c>
       <c r="D3328" t="inlineStr">
         <is>
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3329">
@@ -90297,7 +90297,7 @@
         <v>16</v>
       </c>
       <c r="C3329" t="n">
-        <v>33.05</v>
+        <v>33.03</v>
       </c>
       <c r="D3329" t="inlineStr">
         <is>
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3330">
@@ -90324,7 +90324,7 @@
         <v>17</v>
       </c>
       <c r="C3330" t="n">
-        <v>31.57</v>
+        <v>31.58</v>
       </c>
       <c r="D3330" t="inlineStr">
         <is>
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3331">
@@ -90351,7 +90351,7 @@
         <v>18</v>
       </c>
       <c r="C3331" t="n">
-        <v>34.2</v>
+        <v>34.17</v>
       </c>
       <c r="D3331" t="inlineStr">
         <is>
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3332">
@@ -90378,7 +90378,7 @@
         <v>19</v>
       </c>
       <c r="C3332" t="n">
-        <v>30.8</v>
+        <v>30.72</v>
       </c>
       <c r="D3332" t="inlineStr">
         <is>
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3333">
@@ -90405,7 +90405,7 @@
         <v>20</v>
       </c>
       <c r="C3333" t="n">
-        <v>24.03</v>
+        <v>24.01</v>
       </c>
       <c r="D3333" t="inlineStr">
         <is>
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3334">
@@ -90432,7 +90432,7 @@
         <v>21</v>
       </c>
       <c r="C3334" t="n">
-        <v>34.24</v>
+        <v>34.25</v>
       </c>
       <c r="D3334" t="inlineStr">
         <is>
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3335">
@@ -90459,7 +90459,7 @@
         <v>22</v>
       </c>
       <c r="C3335" t="n">
-        <v>33.39</v>
+        <v>33.35</v>
       </c>
       <c r="D3335" t="inlineStr">
         <is>
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3337">
@@ -90513,7 +90513,7 @@
         <v>24</v>
       </c>
       <c r="C3337" t="n">
-        <v>22.78</v>
+        <v>22.69</v>
       </c>
       <c r="D3337" t="inlineStr">
         <is>
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3338">
@@ -90540,7 +90540,7 @@
         <v>1</v>
       </c>
       <c r="C3338" t="n">
-        <v>10.21</v>
+        <v>10.14</v>
       </c>
       <c r="D3338" t="inlineStr">
         <is>
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3339">
@@ -90567,7 +90567,7 @@
         <v>2</v>
       </c>
       <c r="C3339" t="n">
-        <v>13.11</v>
+        <v>13.05</v>
       </c>
       <c r="D3339" t="inlineStr">
         <is>
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3340">
@@ -90594,7 +90594,7 @@
         <v>3</v>
       </c>
       <c r="C3340" t="n">
-        <v>15.42</v>
+        <v>15.32</v>
       </c>
       <c r="D3340" t="inlineStr">
         <is>
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3341">
@@ -90621,7 +90621,7 @@
         <v>4</v>
       </c>
       <c r="C3341" t="n">
-        <v>17.64</v>
+        <v>17.53</v>
       </c>
       <c r="D3341" t="inlineStr">
         <is>
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3342">
@@ -90648,7 +90648,7 @@
         <v>5</v>
       </c>
       <c r="C3342" t="n">
-        <v>16.79</v>
+        <v>16.72</v>
       </c>
       <c r="D3342" t="inlineStr">
         <is>
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3343">
@@ -90675,7 +90675,7 @@
         <v>6</v>
       </c>
       <c r="C3343" t="n">
-        <v>15.41</v>
+        <v>15.31</v>
       </c>
       <c r="D3343" t="inlineStr">
         <is>
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3344">
@@ -90702,7 +90702,7 @@
         <v>7</v>
       </c>
       <c r="C3344" t="n">
-        <v>19.88</v>
+        <v>19.86</v>
       </c>
       <c r="D3344" t="inlineStr">
         <is>
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3345">
@@ -90729,7 +90729,7 @@
         <v>8</v>
       </c>
       <c r="C3345" t="n">
-        <v>43.51</v>
+        <v>43.52</v>
       </c>
       <c r="D3345" t="inlineStr">
         <is>
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3346">
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3347">
@@ -90783,7 +90783,7 @@
         <v>10</v>
       </c>
       <c r="C3347" t="n">
-        <v>26.02</v>
+        <v>26</v>
       </c>
       <c r="D3347" t="inlineStr">
         <is>
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3348">
@@ -90810,7 +90810,7 @@
         <v>11</v>
       </c>
       <c r="C3348" t="n">
-        <v>21.89</v>
+        <v>21.88</v>
       </c>
       <c r="D3348" t="inlineStr">
         <is>
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3349">
@@ -90837,7 +90837,7 @@
         <v>12</v>
       </c>
       <c r="C3349" t="n">
-        <v>25.93</v>
+        <v>25.92</v>
       </c>
       <c r="D3349" t="inlineStr">
         <is>
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3351">
@@ -90891,7 +90891,7 @@
         <v>14</v>
       </c>
       <c r="C3351" t="n">
-        <v>24.17</v>
+        <v>24.16</v>
       </c>
       <c r="D3351" t="inlineStr">
         <is>
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3352">
@@ -90918,7 +90918,7 @@
         <v>15</v>
       </c>
       <c r="C3352" t="n">
-        <v>24.3</v>
+        <v>24.28</v>
       </c>
       <c r="D3352" t="inlineStr">
         <is>
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3353">
@@ -90945,7 +90945,7 @@
         <v>16</v>
       </c>
       <c r="C3353" t="n">
-        <v>24.44</v>
+        <v>24.43</v>
       </c>
       <c r="D3353" t="inlineStr">
         <is>
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3354">
@@ -90972,7 +90972,7 @@
         <v>17</v>
       </c>
       <c r="C3354" t="n">
-        <v>23.41</v>
+        <v>23.36</v>
       </c>
       <c r="D3354" t="inlineStr">
         <is>
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3355">
@@ -90999,7 +90999,7 @@
         <v>18</v>
       </c>
       <c r="C3355" t="n">
-        <v>21.1</v>
+        <v>20.97</v>
       </c>
       <c r="D3355" t="inlineStr">
         <is>
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3356">
@@ -91026,7 +91026,7 @@
         <v>19</v>
       </c>
       <c r="C3356" t="n">
-        <v>17.41</v>
+        <v>17.34</v>
       </c>
       <c r="D3356" t="inlineStr">
         <is>
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3357">
@@ -91053,7 +91053,7 @@
         <v>20</v>
       </c>
       <c r="C3357" t="n">
-        <v>25.87</v>
+        <v>25.82</v>
       </c>
       <c r="D3357" t="inlineStr">
         <is>
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3360">
@@ -91134,7 +91134,7 @@
         <v>23</v>
       </c>
       <c r="C3360" t="n">
-        <v>28.84</v>
+        <v>28.83</v>
       </c>
       <c r="D3360" t="inlineStr">
         <is>
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3362">
@@ -91188,7 +91188,7 @@
         <v>1</v>
       </c>
       <c r="C3362" t="n">
-        <v>11.43</v>
+        <v>11.6</v>
       </c>
       <c r="D3362" t="inlineStr">
         <is>
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3363">
@@ -91215,7 +91215,7 @@
         <v>2</v>
       </c>
       <c r="C3363" t="n">
-        <v>13.6</v>
+        <v>14.25</v>
       </c>
       <c r="D3363" t="inlineStr">
         <is>
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3364">
@@ -91242,7 +91242,7 @@
         <v>3</v>
       </c>
       <c r="C3364" t="n">
-        <v>13.8</v>
+        <v>13.62</v>
       </c>
       <c r="D3364" t="inlineStr">
         <is>
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3365">
@@ -91269,7 +91269,7 @@
         <v>4</v>
       </c>
       <c r="C3365" t="n">
-        <v>14.17</v>
+        <v>12.65</v>
       </c>
       <c r="D3365" t="inlineStr">
         <is>
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3366">
@@ -91296,7 +91296,7 @@
         <v>5</v>
       </c>
       <c r="C3366" t="n">
-        <v>16.45</v>
+        <v>16.79</v>
       </c>
       <c r="D3366" t="inlineStr">
         <is>
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3367">
@@ -91323,7 +91323,7 @@
         <v>6</v>
       </c>
       <c r="C3367" t="n">
-        <v>18.38</v>
+        <v>18.67</v>
       </c>
       <c r="D3367" t="inlineStr">
         <is>
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3368">
@@ -91350,7 +91350,7 @@
         <v>7</v>
       </c>
       <c r="C3368" t="n">
-        <v>17.12</v>
+        <v>16.38</v>
       </c>
       <c r="D3368" t="inlineStr">
         <is>
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3369">
@@ -91377,7 +91377,7 @@
         <v>8</v>
       </c>
       <c r="C3369" t="n">
-        <v>43.73</v>
+        <v>44.03</v>
       </c>
       <c r="D3369" t="inlineStr">
         <is>
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3370">
@@ -91404,7 +91404,7 @@
         <v>9</v>
       </c>
       <c r="C3370" t="n">
-        <v>42.63</v>
+        <v>42.81</v>
       </c>
       <c r="D3370" t="inlineStr">
         <is>
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3371">
@@ -91431,7 +91431,7 @@
         <v>10</v>
       </c>
       <c r="C3371" t="n">
-        <v>32.6</v>
+        <v>31.47</v>
       </c>
       <c r="D3371" t="inlineStr">
         <is>
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3372">
@@ -91458,7 +91458,7 @@
         <v>11</v>
       </c>
       <c r="C3372" t="n">
-        <v>24.05</v>
+        <v>24.45</v>
       </c>
       <c r="D3372" t="inlineStr">
         <is>
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3373">
@@ -91485,7 +91485,7 @@
         <v>12</v>
       </c>
       <c r="C3373" t="n">
-        <v>27.63</v>
+        <v>27.54</v>
       </c>
       <c r="D3373" t="inlineStr">
         <is>
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3374">
@@ -91512,7 +91512,7 @@
         <v>13</v>
       </c>
       <c r="C3374" t="n">
-        <v>27.48</v>
+        <v>27.69</v>
       </c>
       <c r="D3374" t="inlineStr">
         <is>
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3375">
@@ -91539,7 +91539,7 @@
         <v>14</v>
       </c>
       <c r="C3375" t="n">
-        <v>25.4</v>
+        <v>25.42</v>
       </c>
       <c r="D3375" t="inlineStr">
         <is>
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3376">
@@ -91566,7 +91566,7 @@
         <v>15</v>
       </c>
       <c r="C3376" t="n">
-        <v>26.62</v>
+        <v>26.3</v>
       </c>
       <c r="D3376" t="inlineStr">
         <is>
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3377">
@@ -91593,7 +91593,7 @@
         <v>16</v>
       </c>
       <c r="C3377" t="n">
-        <v>26.41</v>
+        <v>25.27</v>
       </c>
       <c r="D3377" t="inlineStr">
         <is>
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3378">
@@ -91620,7 +91620,7 @@
         <v>17</v>
       </c>
       <c r="C3378" t="n">
-        <v>25.89</v>
+        <v>26.09</v>
       </c>
       <c r="D3378" t="inlineStr">
         <is>
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3379">
@@ -91647,7 +91647,7 @@
         <v>18</v>
       </c>
       <c r="C3379" t="n">
-        <v>24.62</v>
+        <v>24.84</v>
       </c>
       <c r="D3379" t="inlineStr">
         <is>
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3380">
@@ -91674,7 +91674,7 @@
         <v>19</v>
       </c>
       <c r="C3380" t="n">
-        <v>20.39</v>
+        <v>20.48</v>
       </c>
       <c r="D3380" t="inlineStr">
         <is>
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3381">
@@ -91701,7 +91701,7 @@
         <v>20</v>
       </c>
       <c r="C3381" t="n">
-        <v>31.7</v>
+        <v>31.26</v>
       </c>
       <c r="D3381" t="inlineStr">
         <is>
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3382">
@@ -91728,7 +91728,7 @@
         <v>21</v>
       </c>
       <c r="C3382" t="n">
-        <v>46.35</v>
+        <v>45.53</v>
       </c>
       <c r="D3382" t="inlineStr">
         <is>
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3383">
@@ -91755,7 +91755,7 @@
         <v>22</v>
       </c>
       <c r="C3383" t="n">
-        <v>47.88</v>
+        <v>48.1</v>
       </c>
       <c r="D3383" t="inlineStr">
         <is>
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3384">
@@ -91782,7 +91782,7 @@
         <v>23</v>
       </c>
       <c r="C3384" t="n">
-        <v>34.94</v>
+        <v>34.85</v>
       </c>
       <c r="D3384" t="inlineStr">
         <is>
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3385">
@@ -91809,7 +91809,7 @@
         <v>24</v>
       </c>
       <c r="C3385" t="n">
-        <v>25.15</v>
+        <v>25.16</v>
       </c>
       <c r="D3385" t="inlineStr">
         <is>
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3386">
@@ -91836,7 +91836,7 @@
         <v>1</v>
       </c>
       <c r="C3386" t="n">
-        <v>11.45</v>
+        <v>11.43</v>
       </c>
       <c r="D3386" t="inlineStr">
         <is>
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3387">
@@ -91863,7 +91863,7 @@
         <v>2</v>
       </c>
       <c r="C3387" t="n">
-        <v>12.73</v>
+        <v>12.68</v>
       </c>
       <c r="D3387" t="inlineStr">
         <is>
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3388">
@@ -91890,7 +91890,7 @@
         <v>3</v>
       </c>
       <c r="C3388" t="n">
-        <v>13.56</v>
+        <v>13.5</v>
       </c>
       <c r="D3388" t="inlineStr">
         <is>
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3389">
@@ -91917,7 +91917,7 @@
         <v>4</v>
       </c>
       <c r="C3389" t="n">
-        <v>15.25</v>
+        <v>15.23</v>
       </c>
       <c r="D3389" t="inlineStr">
         <is>
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3390">
@@ -91944,7 +91944,7 @@
         <v>5</v>
       </c>
       <c r="C3390" t="n">
-        <v>14.58</v>
+        <v>14.56</v>
       </c>
       <c r="D3390" t="inlineStr">
         <is>
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3391">
@@ -91971,7 +91971,7 @@
         <v>6</v>
       </c>
       <c r="C3391" t="n">
-        <v>15.26</v>
+        <v>15.25</v>
       </c>
       <c r="D3391" t="inlineStr">
         <is>
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3392">
@@ -91998,7 +91998,7 @@
         <v>7</v>
       </c>
       <c r="C3392" t="n">
-        <v>21.04</v>
+        <v>21.03</v>
       </c>
       <c r="D3392" t="inlineStr">
         <is>
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3393">
@@ -92025,7 +92025,7 @@
         <v>8</v>
       </c>
       <c r="C3393" t="n">
-        <v>37.47</v>
+        <v>37.44</v>
       </c>
       <c r="D3393" t="inlineStr">
         <is>
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3394">
@@ -92052,7 +92052,7 @@
         <v>9</v>
       </c>
       <c r="C3394" t="n">
-        <v>36.89</v>
+        <v>36.84</v>
       </c>
       <c r="D3394" t="inlineStr">
         <is>
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3395">
@@ -92079,7 +92079,7 @@
         <v>10</v>
       </c>
       <c r="C3395" t="n">
-        <v>18.57</v>
+        <v>18.41</v>
       </c>
       <c r="D3395" t="inlineStr">
         <is>
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3396">
@@ -92106,7 +92106,7 @@
         <v>11</v>
       </c>
       <c r="C3396" t="n">
-        <v>22.53</v>
+        <v>22.5</v>
       </c>
       <c r="D3396" t="inlineStr">
         <is>
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3397">
@@ -92133,7 +92133,7 @@
         <v>12</v>
       </c>
       <c r="C3397" t="n">
-        <v>23.44</v>
+        <v>23.43</v>
       </c>
       <c r="D3397" t="inlineStr">
         <is>
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3398">
@@ -92160,7 +92160,7 @@
         <v>13</v>
       </c>
       <c r="C3398" t="n">
-        <v>23.81</v>
+        <v>23.8</v>
       </c>
       <c r="D3398" t="inlineStr">
         <is>
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3399">
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3400">
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3401">
@@ -92241,7 +92241,7 @@
         <v>16</v>
       </c>
       <c r="C3401" t="n">
-        <v>24.23</v>
+        <v>24.22</v>
       </c>
       <c r="D3401" t="inlineStr">
         <is>
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3402">
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3403">
@@ -92295,7 +92295,7 @@
         <v>18</v>
       </c>
       <c r="C3403" t="n">
-        <v>22.37</v>
+        <v>22.33</v>
       </c>
       <c r="D3403" t="inlineStr">
         <is>
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3404">
@@ -92322,7 +92322,7 @@
         <v>19</v>
       </c>
       <c r="C3404" t="n">
-        <v>20.49</v>
+        <v>20.43</v>
       </c>
       <c r="D3404" t="inlineStr">
         <is>
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3405">
@@ -92349,7 +92349,7 @@
         <v>20</v>
       </c>
       <c r="C3405" t="n">
-        <v>25.24</v>
+        <v>25.2</v>
       </c>
       <c r="D3405" t="inlineStr">
         <is>
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3406">
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3407">
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3408">
@@ -92430,7 +92430,7 @@
         <v>23</v>
       </c>
       <c r="C3408" t="n">
-        <v>24.08</v>
+        <v>24.06</v>
       </c>
       <c r="D3408" t="inlineStr">
         <is>
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3409">
@@ -92457,7 +92457,7 @@
         <v>24</v>
       </c>
       <c r="C3409" t="n">
-        <v>24.32</v>
+        <v>24.29</v>
       </c>
       <c r="D3409" t="inlineStr">
         <is>
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3410">
@@ -92484,7 +92484,7 @@
         <v>1</v>
       </c>
       <c r="C3410" t="n">
-        <v>14.94</v>
+        <v>14.95</v>
       </c>
       <c r="D3410" t="inlineStr">
         <is>
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3411">
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3412">
@@ -92538,7 +92538,7 @@
         <v>3</v>
       </c>
       <c r="C3412" t="n">
-        <v>12.25</v>
+        <v>12.26</v>
       </c>
       <c r="D3412" t="inlineStr">
         <is>
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3413">
@@ -92565,7 +92565,7 @@
         <v>4</v>
       </c>
       <c r="C3413" t="n">
-        <v>11.7</v>
+        <v>11.75</v>
       </c>
       <c r="D3413" t="inlineStr">
         <is>
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3415">
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3416">
@@ -92646,7 +92646,7 @@
         <v>7</v>
       </c>
       <c r="C3416" t="n">
-        <v>16.49</v>
+        <v>16.5</v>
       </c>
       <c r="D3416" t="inlineStr">
         <is>
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3417">
@@ -92673,7 +92673,7 @@
         <v>8</v>
       </c>
       <c r="C3417" t="n">
-        <v>28.91</v>
+        <v>30.1</v>
       </c>
       <c r="D3417" t="inlineStr">
         <is>
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3418">
@@ -92700,7 +92700,7 @@
         <v>9</v>
       </c>
       <c r="C3418" t="n">
-        <v>42.55</v>
+        <v>43.69</v>
       </c>
       <c r="D3418" t="inlineStr">
         <is>
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3419">
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3420">
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3421">
@@ -92781,7 +92781,7 @@
         <v>12</v>
       </c>
       <c r="C3421" t="n">
-        <v>30.59</v>
+        <v>31.4</v>
       </c>
       <c r="D3421" t="inlineStr">
         <is>
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3422">
@@ -92808,7 +92808,7 @@
         <v>13</v>
       </c>
       <c r="C3422" t="n">
-        <v>33.59</v>
+        <v>34.41</v>
       </c>
       <c r="D3422" t="inlineStr">
         <is>
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3423">
@@ -92835,7 +92835,7 @@
         <v>14</v>
       </c>
       <c r="C3423" t="n">
-        <v>32.5</v>
+        <v>33.28</v>
       </c>
       <c r="D3423" t="inlineStr">
         <is>
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3424">
@@ -92862,7 +92862,7 @@
         <v>15</v>
       </c>
       <c r="C3424" t="n">
-        <v>32.81</v>
+        <v>33.6</v>
       </c>
       <c r="D3424" t="inlineStr">
         <is>
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3425">
@@ -92889,7 +92889,7 @@
         <v>16</v>
       </c>
       <c r="C3425" t="n">
-        <v>33.51</v>
+        <v>34.34</v>
       </c>
       <c r="D3425" t="inlineStr">
         <is>
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3426">
@@ -92916,7 +92916,7 @@
         <v>17</v>
       </c>
       <c r="C3426" t="n">
-        <v>32.57</v>
+        <v>33.37</v>
       </c>
       <c r="D3426" t="inlineStr">
         <is>
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3427">
@@ -92943,7 +92943,7 @@
         <v>18</v>
       </c>
       <c r="C3427" t="n">
-        <v>29.68</v>
+        <v>30.42</v>
       </c>
       <c r="D3427" t="inlineStr">
         <is>
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3428">
@@ -92970,7 +92970,7 @@
         <v>19</v>
       </c>
       <c r="C3428" t="n">
-        <v>24.82</v>
+        <v>24.86</v>
       </c>
       <c r="D3428" t="inlineStr">
         <is>
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3429">
@@ -92997,7 +92997,7 @@
         <v>20</v>
       </c>
       <c r="C3429" t="n">
-        <v>23.54</v>
+        <v>24.34</v>
       </c>
       <c r="D3429" t="inlineStr">
         <is>
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3430">
@@ -93024,7 +93024,7 @@
         <v>21</v>
       </c>
       <c r="C3430" t="n">
-        <v>33.13</v>
+        <v>35.28</v>
       </c>
       <c r="D3430" t="inlineStr">
         <is>
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3431">
@@ -93051,7 +93051,7 @@
         <v>22</v>
       </c>
       <c r="C3431" t="n">
-        <v>34.2</v>
+        <v>36.35</v>
       </c>
       <c r="D3431" t="inlineStr">
         <is>
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3432">
@@ -93078,7 +93078,7 @@
         <v>23</v>
       </c>
       <c r="C3432" t="n">
-        <v>22.36</v>
+        <v>23.63</v>
       </c>
       <c r="D3432" t="inlineStr">
         <is>
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3433">
@@ -93105,7 +93105,7 @@
         <v>24</v>
       </c>
       <c r="C3433" t="n">
-        <v>23.89</v>
+        <v>25.29</v>
       </c>
       <c r="D3433" t="inlineStr">
         <is>
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3434">
@@ -93132,7 +93132,7 @@
         <v>1</v>
       </c>
       <c r="C3434" t="n">
-        <v>13.95</v>
+        <v>13.14</v>
       </c>
       <c r="D3434" t="inlineStr">
         <is>
@@ -93148,7 +93148,7 @@
         <v>3</v>
       </c>
       <c r="G3434" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3435">
@@ -93159,7 +93159,7 @@
         <v>2</v>
       </c>
       <c r="C3435" t="n">
-        <v>12.69</v>
+        <v>12.9</v>
       </c>
       <c r="D3435" t="inlineStr">
         <is>
@@ -93175,7 +93175,7 @@
         <v>3</v>
       </c>
       <c r="G3435" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3436">
@@ -93186,7 +93186,7 @@
         <v>3</v>
       </c>
       <c r="C3436" t="n">
-        <v>13.93</v>
+        <v>15.48</v>
       </c>
       <c r="D3436" t="inlineStr">
         <is>
@@ -93202,7 +93202,7 @@
         <v>3</v>
       </c>
       <c r="G3436" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3437">
@@ -93213,7 +93213,7 @@
         <v>4</v>
       </c>
       <c r="C3437" t="n">
-        <v>15.13</v>
+        <v>16.8</v>
       </c>
       <c r="D3437" t="inlineStr">
         <is>
@@ -93229,7 +93229,7 @@
         <v>3</v>
       </c>
       <c r="G3437" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3438">
@@ -93240,7 +93240,7 @@
         <v>5</v>
       </c>
       <c r="C3438" t="n">
-        <v>14.75</v>
+        <v>15.33</v>
       </c>
       <c r="D3438" t="inlineStr">
         <is>
@@ -93256,7 +93256,7 @@
         <v>3</v>
       </c>
       <c r="G3438" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3439">
@@ -93267,7 +93267,7 @@
         <v>6</v>
       </c>
       <c r="C3439" t="n">
-        <v>19.88</v>
+        <v>22.41</v>
       </c>
       <c r="D3439" t="inlineStr">
         <is>
@@ -93283,7 +93283,7 @@
         <v>3</v>
       </c>
       <c r="G3439" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3440">
@@ -93294,7 +93294,7 @@
         <v>7</v>
       </c>
       <c r="C3440" t="n">
-        <v>27.69</v>
+        <v>27.55</v>
       </c>
       <c r="D3440" t="inlineStr">
         <is>
@@ -93310,7 +93310,7 @@
         <v>3</v>
       </c>
       <c r="G3440" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3441">
@@ -93321,7 +93321,7 @@
         <v>8</v>
       </c>
       <c r="C3441" t="n">
-        <v>56.09</v>
+        <v>49.14</v>
       </c>
       <c r="D3441" t="inlineStr">
         <is>
@@ -93337,7 +93337,7 @@
         <v>3</v>
       </c>
       <c r="G3441" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3442">
@@ -93348,7 +93348,7 @@
         <v>9</v>
       </c>
       <c r="C3442" t="n">
-        <v>50.42</v>
+        <v>42.92</v>
       </c>
       <c r="D3442" t="inlineStr">
         <is>
@@ -93364,7 +93364,7 @@
         <v>3</v>
       </c>
       <c r="G3442" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3443">
@@ -93375,7 +93375,7 @@
         <v>10</v>
       </c>
       <c r="C3443" t="n">
-        <v>27.65</v>
+        <v>29.76</v>
       </c>
       <c r="D3443" t="inlineStr">
         <is>
@@ -93391,7 +93391,7 @@
         <v>3</v>
       </c>
       <c r="G3443" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3444">
@@ -93402,7 +93402,7 @@
         <v>11</v>
       </c>
       <c r="C3444" t="n">
-        <v>24.47</v>
+        <v>26.26</v>
       </c>
       <c r="D3444" t="inlineStr">
         <is>
@@ -93418,7 +93418,7 @@
         <v>3</v>
       </c>
       <c r="G3444" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3445">
@@ -93429,7 +93429,7 @@
         <v>12</v>
       </c>
       <c r="C3445" t="n">
-        <v>27.69</v>
+        <v>30.95</v>
       </c>
       <c r="D3445" t="inlineStr">
         <is>
@@ -93445,7 +93445,7 @@
         <v>3</v>
       </c>
       <c r="G3445" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3446">
@@ -93456,7 +93456,7 @@
         <v>13</v>
       </c>
       <c r="C3446" t="n">
-        <v>27.09</v>
+        <v>30.47</v>
       </c>
       <c r="D3446" t="inlineStr">
         <is>
@@ -93472,7 +93472,7 @@
         <v>3</v>
       </c>
       <c r="G3446" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3447">
@@ -93483,7 +93483,7 @@
         <v>14</v>
       </c>
       <c r="C3447" t="n">
-        <v>26.77</v>
+        <v>27.02</v>
       </c>
       <c r="D3447" t="inlineStr">
         <is>
@@ -93499,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="G3447" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3448">
@@ -93510,7 +93510,7 @@
         <v>15</v>
       </c>
       <c r="C3448" t="n">
-        <v>26.48</v>
+        <v>30.5</v>
       </c>
       <c r="D3448" t="inlineStr">
         <is>
@@ -93526,7 +93526,7 @@
         <v>3</v>
       </c>
       <c r="G3448" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3449">
@@ -93537,7 +93537,7 @@
         <v>16</v>
       </c>
       <c r="C3449" t="n">
-        <v>28.3</v>
+        <v>27.55</v>
       </c>
       <c r="D3449" t="inlineStr">
         <is>
@@ -93553,7 +93553,7 @@
         <v>3</v>
       </c>
       <c r="G3449" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3450">
@@ -93564,7 +93564,7 @@
         <v>17</v>
       </c>
       <c r="C3450" t="n">
-        <v>26.09</v>
+        <v>30.79</v>
       </c>
       <c r="D3450" t="inlineStr">
         <is>
@@ -93580,7 +93580,7 @@
         <v>3</v>
       </c>
       <c r="G3450" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3451">
@@ -93591,7 +93591,7 @@
         <v>18</v>
       </c>
       <c r="C3451" t="n">
-        <v>22.24</v>
+        <v>19.95</v>
       </c>
       <c r="D3451" t="inlineStr">
         <is>
@@ -93607,7 +93607,7 @@
         <v>3</v>
       </c>
       <c r="G3451" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3452">
@@ -93618,7 +93618,7 @@
         <v>19</v>
       </c>
       <c r="C3452" t="n">
-        <v>23.27</v>
+        <v>24.72</v>
       </c>
       <c r="D3452" t="inlineStr">
         <is>
@@ -93634,7 +93634,7 @@
         <v>3</v>
       </c>
       <c r="G3452" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3453">
@@ -93645,7 +93645,7 @@
         <v>20</v>
       </c>
       <c r="C3453" t="n">
-        <v>29.14</v>
+        <v>20.01</v>
       </c>
       <c r="D3453" t="inlineStr">
         <is>
@@ -93661,7 +93661,7 @@
         <v>3</v>
       </c>
       <c r="G3453" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3454">
@@ -93672,7 +93672,7 @@
         <v>21</v>
       </c>
       <c r="C3454" t="n">
-        <v>51.51</v>
+        <v>33.39</v>
       </c>
       <c r="D3454" t="inlineStr">
         <is>
@@ -93688,7 +93688,7 @@
         <v>3</v>
       </c>
       <c r="G3454" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3455">
@@ -93699,7 +93699,7 @@
         <v>22</v>
       </c>
       <c r="C3455" t="n">
-        <v>46.11</v>
+        <v>35.9</v>
       </c>
       <c r="D3455" t="inlineStr">
         <is>
@@ -93715,7 +93715,7 @@
         <v>3</v>
       </c>
       <c r="G3455" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3456">
@@ -93726,7 +93726,7 @@
         <v>23</v>
       </c>
       <c r="C3456" t="n">
-        <v>33.1</v>
+        <v>32.08</v>
       </c>
       <c r="D3456" t="inlineStr">
         <is>
@@ -93742,7 +93742,7 @@
         <v>3</v>
       </c>
       <c r="G3456" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
       </c>
     </row>
     <row r="3457">
@@ -93753,7 +93753,7 @@
         <v>24</v>
       </c>
       <c r="C3457" t="n">
-        <v>26.37</v>
+        <v>25.46</v>
       </c>
       <c r="D3457" t="inlineStr">
         <is>
@@ -93769,7 +93769,655 @@
         <v>3</v>
       </c>
       <c r="G3457" s="2" t="n">
-        <v>46287.46056840286</v>
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3458">
+      <c r="A3458" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3458" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3458" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="D3458" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3458" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3458" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3458" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3459">
+      <c r="A3459" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3459" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3459" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="D3459" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3459" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3459" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3459" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3460">
+      <c r="A3460" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3460" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3460" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="D3460" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3460" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3460" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3460" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3461">
+      <c r="A3461" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3461" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3461" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="D3461" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3461" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3461" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3461" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3462">
+      <c r="A3462" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3462" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3462" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="D3462" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3462" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3462" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3462" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3463">
+      <c r="A3463" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3463" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3463" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="D3463" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3463" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3463" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3463" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3464">
+      <c r="A3464" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3464" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3464" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="D3464" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3464" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3464" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3464" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3465">
+      <c r="A3465" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3465" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3465" t="n">
+        <v>68.41</v>
+      </c>
+      <c r="D3465" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3465" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3465" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3465" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3466">
+      <c r="A3466" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3466" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3466" t="n">
+        <v>61.78</v>
+      </c>
+      <c r="D3466" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3466" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3466" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3466" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3467">
+      <c r="A3467" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3467" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3467" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="D3467" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3467" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3467" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3467" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3468">
+      <c r="A3468" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3468" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3468" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="D3468" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3468" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3468" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3468" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3469">
+      <c r="A3469" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3469" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3469" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="D3469" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3469" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3469" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3469" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3470">
+      <c r="A3470" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3470" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3470" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D3470" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3470" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3470" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3470" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3471">
+      <c r="A3471" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3471" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3471" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="D3471" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3471" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3471" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3471" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3472">
+      <c r="A3472" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3472" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3472" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="D3472" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3472" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3472" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3472" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3473">
+      <c r="A3473" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3473" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3473" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="D3473" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3473" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3473" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3473" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3474">
+      <c r="A3474" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3474" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3474" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="D3474" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3474" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3474" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3474" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3475">
+      <c r="A3475" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3475" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3475" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="D3475" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3475" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3475" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3475" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3476">
+      <c r="A3476" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3476" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3476" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="D3476" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3476" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3476" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3476" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3477">
+      <c r="A3477" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3477" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3477" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="D3477" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3477" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3477" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3477" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3478">
+      <c r="A3478" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3478" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3478" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="D3478" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3478" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3478" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3478" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3479">
+      <c r="A3479" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3479" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3479" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="D3479" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3479" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3479" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3479" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3480">
+      <c r="A3480" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3480" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3480" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="D3480" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3480" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3480" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3480" s="2" t="n">
+        <v>46287.87342691478</v>
+      </c>
+    </row>
+    <row r="3481">
+      <c r="A3481" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3481" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3481" t="n">
+        <v>29.49</v>
+      </c>
+      <c r="D3481" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3481" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3481" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3481" s="2" t="n">
+        <v>46287.87342691478</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3324">
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3333">
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3335">
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3337">
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3341">
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3343">
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3344">
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3345">
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3346">
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3347">
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3355">
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3356">
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3357">
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3360">
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3362">
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3364">
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3365">
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3366">
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3367">
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3368">
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3369">
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3370">
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3371">
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3372">
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3373">
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3374">
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3375">
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3376">
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3377">
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3378">
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3379">
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3380">
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3381">
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3382">
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3383">
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3384">
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3385">
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3386">
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3387">
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3388">
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3389">
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3390">
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3391">
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3392">
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3393">
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3394">
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3395">
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3396">
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3397">
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3398">
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3399">
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3400">
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3401">
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3402">
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3403">
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3404">
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3405">
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3406">
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3407">
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3408">
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3409">
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3410">
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3411">
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3412">
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3413">
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3415">
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3416">
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3417">
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3418">
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3419">
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3420">
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3421">
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3422">
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3423">
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3424">
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3425">
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3426">
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3427">
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3428">
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3429">
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3430">
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3431">
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3432">
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3433">
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3434">
@@ -93148,7 +93148,7 @@
         <v>3</v>
       </c>
       <c r="G3434" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3435">
@@ -93175,7 +93175,7 @@
         <v>3</v>
       </c>
       <c r="G3435" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3436">
@@ -93202,7 +93202,7 @@
         <v>3</v>
       </c>
       <c r="G3436" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3437">
@@ -93229,7 +93229,7 @@
         <v>3</v>
       </c>
       <c r="G3437" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3438">
@@ -93256,7 +93256,7 @@
         <v>3</v>
       </c>
       <c r="G3438" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3439">
@@ -93283,7 +93283,7 @@
         <v>3</v>
       </c>
       <c r="G3439" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3440">
@@ -93310,7 +93310,7 @@
         <v>3</v>
       </c>
       <c r="G3440" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3441">
@@ -93337,7 +93337,7 @@
         <v>3</v>
       </c>
       <c r="G3441" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3442">
@@ -93364,7 +93364,7 @@
         <v>3</v>
       </c>
       <c r="G3442" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3443">
@@ -93391,7 +93391,7 @@
         <v>3</v>
       </c>
       <c r="G3443" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3444">
@@ -93418,7 +93418,7 @@
         <v>3</v>
       </c>
       <c r="G3444" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3445">
@@ -93445,7 +93445,7 @@
         <v>3</v>
       </c>
       <c r="G3445" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3446">
@@ -93472,7 +93472,7 @@
         <v>3</v>
       </c>
       <c r="G3446" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3447">
@@ -93499,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="G3447" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3448">
@@ -93526,7 +93526,7 @@
         <v>3</v>
       </c>
       <c r="G3448" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3449">
@@ -93553,7 +93553,7 @@
         <v>3</v>
       </c>
       <c r="G3449" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3450">
@@ -93580,7 +93580,7 @@
         <v>3</v>
       </c>
       <c r="G3450" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3451">
@@ -93607,7 +93607,7 @@
         <v>3</v>
       </c>
       <c r="G3451" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3452">
@@ -93634,7 +93634,7 @@
         <v>3</v>
       </c>
       <c r="G3452" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3453">
@@ -93661,7 +93661,7 @@
         <v>3</v>
       </c>
       <c r="G3453" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3454">
@@ -93688,7 +93688,7 @@
         <v>3</v>
       </c>
       <c r="G3454" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3455">
@@ -93715,7 +93715,7 @@
         <v>3</v>
       </c>
       <c r="G3455" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3456">
@@ -93742,7 +93742,7 @@
         <v>3</v>
       </c>
       <c r="G3456" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3457">
@@ -93769,7 +93769,7 @@
         <v>3</v>
       </c>
       <c r="G3457" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3458">
@@ -93796,7 +93796,7 @@
         <v>3</v>
       </c>
       <c r="G3458" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3459">
@@ -93823,7 +93823,7 @@
         <v>3</v>
       </c>
       <c r="G3459" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3460">
@@ -93850,7 +93850,7 @@
         <v>3</v>
       </c>
       <c r="G3460" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3461">
@@ -93877,7 +93877,7 @@
         <v>3</v>
       </c>
       <c r="G3461" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3462">
@@ -93904,7 +93904,7 @@
         <v>3</v>
       </c>
       <c r="G3462" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3463">
@@ -93931,7 +93931,7 @@
         <v>3</v>
       </c>
       <c r="G3463" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3464">
@@ -93958,7 +93958,7 @@
         <v>3</v>
       </c>
       <c r="G3464" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3465">
@@ -93985,7 +93985,7 @@
         <v>3</v>
       </c>
       <c r="G3465" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3466">
@@ -94012,7 +94012,7 @@
         <v>3</v>
       </c>
       <c r="G3466" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3467">
@@ -94039,7 +94039,7 @@
         <v>3</v>
       </c>
       <c r="G3467" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3468">
@@ -94066,7 +94066,7 @@
         <v>3</v>
       </c>
       <c r="G3468" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3469">
@@ -94093,7 +94093,7 @@
         <v>3</v>
       </c>
       <c r="G3469" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3470">
@@ -94120,7 +94120,7 @@
         <v>3</v>
       </c>
       <c r="G3470" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3471">
@@ -94147,7 +94147,7 @@
         <v>3</v>
       </c>
       <c r="G3471" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3472">
@@ -94174,7 +94174,7 @@
         <v>3</v>
       </c>
       <c r="G3472" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3473">
@@ -94201,7 +94201,7 @@
         <v>3</v>
       </c>
       <c r="G3473" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3474">
@@ -94228,7 +94228,7 @@
         <v>3</v>
       </c>
       <c r="G3474" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3475">
@@ -94255,7 +94255,7 @@
         <v>3</v>
       </c>
       <c r="G3475" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3476">
@@ -94282,7 +94282,7 @@
         <v>3</v>
       </c>
       <c r="G3476" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3477">
@@ -94309,7 +94309,7 @@
         <v>3</v>
       </c>
       <c r="G3477" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3478">
@@ -94336,7 +94336,7 @@
         <v>3</v>
       </c>
       <c r="G3478" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3479">
@@ -94363,7 +94363,7 @@
         <v>3</v>
       </c>
       <c r="G3479" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3480">
@@ -94390,7 +94390,7 @@
         <v>3</v>
       </c>
       <c r="G3480" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
     <row r="3481">
@@ -94417,7 +94417,7 @@
         <v>3</v>
       </c>
       <c r="G3481" s="2" t="n">
-        <v>46287.87342691478</v>
+        <v>46288.4532080768</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3481"/>
+  <dimension ref="A1:G3505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3316">
@@ -89946,7 +89946,7 @@
         <v>3</v>
       </c>
       <c r="C3316" t="n">
-        <v>12.05</v>
+        <v>12.1</v>
       </c>
       <c r="D3316" t="inlineStr">
         <is>
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3317">
@@ -89973,7 +89973,7 @@
         <v>4</v>
       </c>
       <c r="C3317" t="n">
-        <v>13.45</v>
+        <v>13.48</v>
       </c>
       <c r="D3317" t="inlineStr">
         <is>
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3322">
@@ -90108,7 +90108,7 @@
         <v>9</v>
       </c>
       <c r="C3322" t="n">
-        <v>33.01</v>
+        <v>33</v>
       </c>
       <c r="D3322" t="inlineStr">
         <is>
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3323">
@@ -90135,7 +90135,7 @@
         <v>10</v>
       </c>
       <c r="C3323" t="n">
-        <v>22.91</v>
+        <v>22.9</v>
       </c>
       <c r="D3323" t="inlineStr">
         <is>
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3324">
@@ -90162,7 +90162,7 @@
         <v>11</v>
       </c>
       <c r="C3324" t="n">
-        <v>26.75</v>
+        <v>26.78</v>
       </c>
       <c r="D3324" t="inlineStr">
         <is>
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3325">
@@ -90189,7 +90189,7 @@
         <v>12</v>
       </c>
       <c r="C3325" t="n">
-        <v>32.27</v>
+        <v>32.23</v>
       </c>
       <c r="D3325" t="inlineStr">
         <is>
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3326">
@@ -90216,7 +90216,7 @@
         <v>13</v>
       </c>
       <c r="C3326" t="n">
-        <v>31.92</v>
+        <v>31.88</v>
       </c>
       <c r="D3326" t="inlineStr">
         <is>
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3327">
@@ -90243,7 +90243,7 @@
         <v>14</v>
       </c>
       <c r="C3327" t="n">
-        <v>32.59</v>
+        <v>32.53</v>
       </c>
       <c r="D3327" t="inlineStr">
         <is>
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3328">
@@ -90270,7 +90270,7 @@
         <v>15</v>
       </c>
       <c r="C3328" t="n">
-        <v>33.1</v>
+        <v>33.11</v>
       </c>
       <c r="D3328" t="inlineStr">
         <is>
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3329">
@@ -90297,7 +90297,7 @@
         <v>16</v>
       </c>
       <c r="C3329" t="n">
-        <v>33.03</v>
+        <v>33</v>
       </c>
       <c r="D3329" t="inlineStr">
         <is>
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3330">
@@ -90324,7 +90324,7 @@
         <v>17</v>
       </c>
       <c r="C3330" t="n">
-        <v>31.58</v>
+        <v>31.79</v>
       </c>
       <c r="D3330" t="inlineStr">
         <is>
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3331">
@@ -90351,7 +90351,7 @@
         <v>18</v>
       </c>
       <c r="C3331" t="n">
-        <v>34.17</v>
+        <v>34.44</v>
       </c>
       <c r="D3331" t="inlineStr">
         <is>
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3332">
@@ -90378,7 +90378,7 @@
         <v>19</v>
       </c>
       <c r="C3332" t="n">
-        <v>30.72</v>
+        <v>31.34</v>
       </c>
       <c r="D3332" t="inlineStr">
         <is>
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3333">
@@ -90405,7 +90405,7 @@
         <v>20</v>
       </c>
       <c r="C3333" t="n">
-        <v>24.01</v>
+        <v>24.39</v>
       </c>
       <c r="D3333" t="inlineStr">
         <is>
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3334">
@@ -90432,7 +90432,7 @@
         <v>21</v>
       </c>
       <c r="C3334" t="n">
-        <v>34.25</v>
+        <v>34.04</v>
       </c>
       <c r="D3334" t="inlineStr">
         <is>
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3335">
@@ -90459,7 +90459,7 @@
         <v>22</v>
       </c>
       <c r="C3335" t="n">
-        <v>33.35</v>
+        <v>33.45</v>
       </c>
       <c r="D3335" t="inlineStr">
         <is>
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3336">
@@ -90486,7 +90486,7 @@
         <v>23</v>
       </c>
       <c r="C3336" t="n">
-        <v>28.25</v>
+        <v>28.28</v>
       </c>
       <c r="D3336" t="inlineStr">
         <is>
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3337">
@@ -90513,7 +90513,7 @@
         <v>24</v>
       </c>
       <c r="C3337" t="n">
-        <v>22.69</v>
+        <v>23.28</v>
       </c>
       <c r="D3337" t="inlineStr">
         <is>
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3338">
@@ -90540,7 +90540,7 @@
         <v>1</v>
       </c>
       <c r="C3338" t="n">
-        <v>10.14</v>
+        <v>10.59</v>
       </c>
       <c r="D3338" t="inlineStr">
         <is>
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3339">
@@ -90567,7 +90567,7 @@
         <v>2</v>
       </c>
       <c r="C3339" t="n">
-        <v>13.05</v>
+        <v>13.64</v>
       </c>
       <c r="D3339" t="inlineStr">
         <is>
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3340">
@@ -90594,7 +90594,7 @@
         <v>3</v>
       </c>
       <c r="C3340" t="n">
-        <v>15.32</v>
+        <v>15.9</v>
       </c>
       <c r="D3340" t="inlineStr">
         <is>
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3341">
@@ -90621,7 +90621,7 @@
         <v>4</v>
       </c>
       <c r="C3341" t="n">
-        <v>17.53</v>
+        <v>17.95</v>
       </c>
       <c r="D3341" t="inlineStr">
         <is>
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3342">
@@ -90648,7 +90648,7 @@
         <v>5</v>
       </c>
       <c r="C3342" t="n">
-        <v>16.72</v>
+        <v>17.06</v>
       </c>
       <c r="D3342" t="inlineStr">
         <is>
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3343">
@@ -90675,7 +90675,7 @@
         <v>6</v>
       </c>
       <c r="C3343" t="n">
-        <v>15.31</v>
+        <v>15.96</v>
       </c>
       <c r="D3343" t="inlineStr">
         <is>
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3344">
@@ -90702,7 +90702,7 @@
         <v>7</v>
       </c>
       <c r="C3344" t="n">
-        <v>19.86</v>
+        <v>20.01</v>
       </c>
       <c r="D3344" t="inlineStr">
         <is>
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3345">
@@ -90729,7 +90729,7 @@
         <v>8</v>
       </c>
       <c r="C3345" t="n">
-        <v>43.52</v>
+        <v>43.4</v>
       </c>
       <c r="D3345" t="inlineStr">
         <is>
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3346">
@@ -90756,7 +90756,7 @@
         <v>9</v>
       </c>
       <c r="C3346" t="n">
-        <v>44.08</v>
+        <v>44.01</v>
       </c>
       <c r="D3346" t="inlineStr">
         <is>
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3347">
@@ -90783,7 +90783,7 @@
         <v>10</v>
       </c>
       <c r="C3347" t="n">
-        <v>26</v>
+        <v>26.06</v>
       </c>
       <c r="D3347" t="inlineStr">
         <is>
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3348">
@@ -90810,7 +90810,7 @@
         <v>11</v>
       </c>
       <c r="C3348" t="n">
-        <v>21.88</v>
+        <v>21.8</v>
       </c>
       <c r="D3348" t="inlineStr">
         <is>
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3349">
@@ -90837,7 +90837,7 @@
         <v>12</v>
       </c>
       <c r="C3349" t="n">
-        <v>25.92</v>
+        <v>25.75</v>
       </c>
       <c r="D3349" t="inlineStr">
         <is>
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3350">
@@ -90864,7 +90864,7 @@
         <v>13</v>
       </c>
       <c r="C3350" t="n">
-        <v>23.97</v>
+        <v>23.78</v>
       </c>
       <c r="D3350" t="inlineStr">
         <is>
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3351">
@@ -90891,7 +90891,7 @@
         <v>14</v>
       </c>
       <c r="C3351" t="n">
-        <v>24.16</v>
+        <v>24.02</v>
       </c>
       <c r="D3351" t="inlineStr">
         <is>
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3352">
@@ -90918,7 +90918,7 @@
         <v>15</v>
       </c>
       <c r="C3352" t="n">
-        <v>24.28</v>
+        <v>24.21</v>
       </c>
       <c r="D3352" t="inlineStr">
         <is>
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3353">
@@ -90945,7 +90945,7 @@
         <v>16</v>
       </c>
       <c r="C3353" t="n">
-        <v>24.43</v>
+        <v>24.36</v>
       </c>
       <c r="D3353" t="inlineStr">
         <is>
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3354">
@@ -90972,7 +90972,7 @@
         <v>17</v>
       </c>
       <c r="C3354" t="n">
-        <v>23.36</v>
+        <v>23.31</v>
       </c>
       <c r="D3354" t="inlineStr">
         <is>
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3355">
@@ -90999,7 +90999,7 @@
         <v>18</v>
       </c>
       <c r="C3355" t="n">
-        <v>20.97</v>
+        <v>20.93</v>
       </c>
       <c r="D3355" t="inlineStr">
         <is>
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3356">
@@ -91026,7 +91026,7 @@
         <v>19</v>
       </c>
       <c r="C3356" t="n">
-        <v>17.34</v>
+        <v>17.37</v>
       </c>
       <c r="D3356" t="inlineStr">
         <is>
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3357">
@@ -91053,7 +91053,7 @@
         <v>20</v>
       </c>
       <c r="C3357" t="n">
-        <v>25.82</v>
+        <v>25.86</v>
       </c>
       <c r="D3357" t="inlineStr">
         <is>
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3358">
@@ -91080,7 +91080,7 @@
         <v>21</v>
       </c>
       <c r="C3358" t="n">
-        <v>36.36</v>
+        <v>36.33</v>
       </c>
       <c r="D3358" t="inlineStr">
         <is>
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3359">
@@ -91107,7 +91107,7 @@
         <v>22</v>
       </c>
       <c r="C3359" t="n">
-        <v>33.65</v>
+        <v>33.61</v>
       </c>
       <c r="D3359" t="inlineStr">
         <is>
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3360">
@@ -91134,7 +91134,7 @@
         <v>23</v>
       </c>
       <c r="C3360" t="n">
-        <v>28.83</v>
+        <v>28.77</v>
       </c>
       <c r="D3360" t="inlineStr">
         <is>
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3361">
@@ -91161,7 +91161,7 @@
         <v>24</v>
       </c>
       <c r="C3361" t="n">
-        <v>24.02</v>
+        <v>23.94</v>
       </c>
       <c r="D3361" t="inlineStr">
         <is>
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3362">
@@ -91188,7 +91188,7 @@
         <v>1</v>
       </c>
       <c r="C3362" t="n">
-        <v>11.6</v>
+        <v>11.74</v>
       </c>
       <c r="D3362" t="inlineStr">
         <is>
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3363">
@@ -91215,7 +91215,7 @@
         <v>2</v>
       </c>
       <c r="C3363" t="n">
-        <v>14.25</v>
+        <v>14.24</v>
       </c>
       <c r="D3363" t="inlineStr">
         <is>
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3364">
@@ -91242,7 +91242,7 @@
         <v>3</v>
       </c>
       <c r="C3364" t="n">
-        <v>13.62</v>
+        <v>13.61</v>
       </c>
       <c r="D3364" t="inlineStr">
         <is>
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3365">
@@ -91269,7 +91269,7 @@
         <v>4</v>
       </c>
       <c r="C3365" t="n">
-        <v>12.65</v>
+        <v>12.96</v>
       </c>
       <c r="D3365" t="inlineStr">
         <is>
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3366">
@@ -91296,7 +91296,7 @@
         <v>5</v>
       </c>
       <c r="C3366" t="n">
-        <v>16.79</v>
+        <v>16.83</v>
       </c>
       <c r="D3366" t="inlineStr">
         <is>
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3367">
@@ -91323,7 +91323,7 @@
         <v>6</v>
       </c>
       <c r="C3367" t="n">
-        <v>18.67</v>
+        <v>18.66</v>
       </c>
       <c r="D3367" t="inlineStr">
         <is>
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3368">
@@ -91350,7 +91350,7 @@
         <v>7</v>
       </c>
       <c r="C3368" t="n">
-        <v>16.38</v>
+        <v>16.32</v>
       </c>
       <c r="D3368" t="inlineStr">
         <is>
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3369">
@@ -91377,7 +91377,7 @@
         <v>8</v>
       </c>
       <c r="C3369" t="n">
-        <v>44.03</v>
+        <v>43.85</v>
       </c>
       <c r="D3369" t="inlineStr">
         <is>
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3370">
@@ -91404,7 +91404,7 @@
         <v>9</v>
       </c>
       <c r="C3370" t="n">
-        <v>42.81</v>
+        <v>42.67</v>
       </c>
       <c r="D3370" t="inlineStr">
         <is>
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3371">
@@ -91431,7 +91431,7 @@
         <v>10</v>
       </c>
       <c r="C3371" t="n">
-        <v>31.47</v>
+        <v>31.36</v>
       </c>
       <c r="D3371" t="inlineStr">
         <is>
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3372">
@@ -91458,7 +91458,7 @@
         <v>11</v>
       </c>
       <c r="C3372" t="n">
-        <v>24.45</v>
+        <v>24.49</v>
       </c>
       <c r="D3372" t="inlineStr">
         <is>
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3373">
@@ -91485,7 +91485,7 @@
         <v>12</v>
       </c>
       <c r="C3373" t="n">
-        <v>27.54</v>
+        <v>27.48</v>
       </c>
       <c r="D3373" t="inlineStr">
         <is>
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3374">
@@ -91512,7 +91512,7 @@
         <v>13</v>
       </c>
       <c r="C3374" t="n">
-        <v>27.69</v>
+        <v>27.56</v>
       </c>
       <c r="D3374" t="inlineStr">
         <is>
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3375">
@@ -91539,7 +91539,7 @@
         <v>14</v>
       </c>
       <c r="C3375" t="n">
-        <v>25.42</v>
+        <v>25.35</v>
       </c>
       <c r="D3375" t="inlineStr">
         <is>
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3376">
@@ -91566,7 +91566,7 @@
         <v>15</v>
       </c>
       <c r="C3376" t="n">
-        <v>26.3</v>
+        <v>26.19</v>
       </c>
       <c r="D3376" t="inlineStr">
         <is>
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3377">
@@ -91593,7 +91593,7 @@
         <v>16</v>
       </c>
       <c r="C3377" t="n">
-        <v>25.27</v>
+        <v>25.47</v>
       </c>
       <c r="D3377" t="inlineStr">
         <is>
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3378">
@@ -91620,7 +91620,7 @@
         <v>17</v>
       </c>
       <c r="C3378" t="n">
-        <v>26.09</v>
+        <v>25.95</v>
       </c>
       <c r="D3378" t="inlineStr">
         <is>
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3379">
@@ -91647,7 +91647,7 @@
         <v>18</v>
       </c>
       <c r="C3379" t="n">
-        <v>24.84</v>
+        <v>24.76</v>
       </c>
       <c r="D3379" t="inlineStr">
         <is>
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3380">
@@ -91674,7 +91674,7 @@
         <v>19</v>
       </c>
       <c r="C3380" t="n">
-        <v>20.48</v>
+        <v>20.61</v>
       </c>
       <c r="D3380" t="inlineStr">
         <is>
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3381">
@@ -91701,7 +91701,7 @@
         <v>20</v>
       </c>
       <c r="C3381" t="n">
-        <v>31.26</v>
+        <v>31.24</v>
       </c>
       <c r="D3381" t="inlineStr">
         <is>
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3382">
@@ -91728,7 +91728,7 @@
         <v>21</v>
       </c>
       <c r="C3382" t="n">
-        <v>45.53</v>
+        <v>45.37</v>
       </c>
       <c r="D3382" t="inlineStr">
         <is>
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3383">
@@ -91755,7 +91755,7 @@
         <v>22</v>
       </c>
       <c r="C3383" t="n">
-        <v>48.1</v>
+        <v>47.86</v>
       </c>
       <c r="D3383" t="inlineStr">
         <is>
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3384">
@@ -91782,7 +91782,7 @@
         <v>23</v>
       </c>
       <c r="C3384" t="n">
-        <v>34.85</v>
+        <v>34.63</v>
       </c>
       <c r="D3384" t="inlineStr">
         <is>
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3385">
@@ -91809,7 +91809,7 @@
         <v>24</v>
       </c>
       <c r="C3385" t="n">
-        <v>25.16</v>
+        <v>24.97</v>
       </c>
       <c r="D3385" t="inlineStr">
         <is>
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3386">
@@ -91836,7 +91836,7 @@
         <v>1</v>
       </c>
       <c r="C3386" t="n">
-        <v>11.43</v>
+        <v>11.47</v>
       </c>
       <c r="D3386" t="inlineStr">
         <is>
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3387">
@@ -91863,7 +91863,7 @@
         <v>2</v>
       </c>
       <c r="C3387" t="n">
-        <v>12.68</v>
+        <v>12.88</v>
       </c>
       <c r="D3387" t="inlineStr">
         <is>
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3388">
@@ -91890,7 +91890,7 @@
         <v>3</v>
       </c>
       <c r="C3388" t="n">
-        <v>13.5</v>
+        <v>13.71</v>
       </c>
       <c r="D3388" t="inlineStr">
         <is>
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3389">
@@ -91917,7 +91917,7 @@
         <v>4</v>
       </c>
       <c r="C3389" t="n">
-        <v>15.23</v>
+        <v>15.24</v>
       </c>
       <c r="D3389" t="inlineStr">
         <is>
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3390">
@@ -91944,7 +91944,7 @@
         <v>5</v>
       </c>
       <c r="C3390" t="n">
-        <v>14.56</v>
+        <v>14.58</v>
       </c>
       <c r="D3390" t="inlineStr">
         <is>
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3391">
@@ -91971,7 +91971,7 @@
         <v>6</v>
       </c>
       <c r="C3391" t="n">
-        <v>15.25</v>
+        <v>15.26</v>
       </c>
       <c r="D3391" t="inlineStr">
         <is>
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3392">
@@ -91998,7 +91998,7 @@
         <v>7</v>
       </c>
       <c r="C3392" t="n">
-        <v>21.03</v>
+        <v>21.12</v>
       </c>
       <c r="D3392" t="inlineStr">
         <is>
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3393">
@@ -92025,7 +92025,7 @@
         <v>8</v>
       </c>
       <c r="C3393" t="n">
-        <v>37.44</v>
+        <v>37.22</v>
       </c>
       <c r="D3393" t="inlineStr">
         <is>
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3394">
@@ -92052,7 +92052,7 @@
         <v>9</v>
       </c>
       <c r="C3394" t="n">
-        <v>36.84</v>
+        <v>36.89</v>
       </c>
       <c r="D3394" t="inlineStr">
         <is>
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3395">
@@ -92079,7 +92079,7 @@
         <v>10</v>
       </c>
       <c r="C3395" t="n">
-        <v>18.41</v>
+        <v>19.39</v>
       </c>
       <c r="D3395" t="inlineStr">
         <is>
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3396">
@@ -92106,7 +92106,7 @@
         <v>11</v>
       </c>
       <c r="C3396" t="n">
-        <v>22.5</v>
+        <v>22.25</v>
       </c>
       <c r="D3396" t="inlineStr">
         <is>
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3397">
@@ -92133,7 +92133,7 @@
         <v>12</v>
       </c>
       <c r="C3397" t="n">
-        <v>23.43</v>
+        <v>22.93</v>
       </c>
       <c r="D3397" t="inlineStr">
         <is>
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3398">
@@ -92160,7 +92160,7 @@
         <v>13</v>
       </c>
       <c r="C3398" t="n">
-        <v>23.8</v>
+        <v>23.25</v>
       </c>
       <c r="D3398" t="inlineStr">
         <is>
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3399">
@@ -92187,7 +92187,7 @@
         <v>14</v>
       </c>
       <c r="C3399" t="n">
-        <v>23.16</v>
+        <v>22.77</v>
       </c>
       <c r="D3399" t="inlineStr">
         <is>
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3400">
@@ -92214,7 +92214,7 @@
         <v>15</v>
       </c>
       <c r="C3400" t="n">
-        <v>23.46</v>
+        <v>23.02</v>
       </c>
       <c r="D3400" t="inlineStr">
         <is>
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3401">
@@ -92241,7 +92241,7 @@
         <v>16</v>
       </c>
       <c r="C3401" t="n">
-        <v>24.22</v>
+        <v>23.76</v>
       </c>
       <c r="D3401" t="inlineStr">
         <is>
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3402">
@@ -92268,7 +92268,7 @@
         <v>17</v>
       </c>
       <c r="C3402" t="n">
-        <v>24.59</v>
+        <v>24.1</v>
       </c>
       <c r="D3402" t="inlineStr">
         <is>
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3403">
@@ -92295,7 +92295,7 @@
         <v>18</v>
       </c>
       <c r="C3403" t="n">
-        <v>22.33</v>
+        <v>22.35</v>
       </c>
       <c r="D3403" t="inlineStr">
         <is>
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3404">
@@ -92322,7 +92322,7 @@
         <v>19</v>
       </c>
       <c r="C3404" t="n">
-        <v>20.43</v>
+        <v>20.5</v>
       </c>
       <c r="D3404" t="inlineStr">
         <is>
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3405">
@@ -92349,7 +92349,7 @@
         <v>20</v>
       </c>
       <c r="C3405" t="n">
-        <v>25.2</v>
+        <v>25.22</v>
       </c>
       <c r="D3405" t="inlineStr">
         <is>
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3406">
@@ -92376,7 +92376,7 @@
         <v>21</v>
       </c>
       <c r="C3406" t="n">
-        <v>36.55</v>
+        <v>36.37</v>
       </c>
       <c r="D3406" t="inlineStr">
         <is>
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3407">
@@ -92403,7 +92403,7 @@
         <v>22</v>
       </c>
       <c r="C3407" t="n">
-        <v>38.44</v>
+        <v>38.21</v>
       </c>
       <c r="D3407" t="inlineStr">
         <is>
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3408">
@@ -92430,7 +92430,7 @@
         <v>23</v>
       </c>
       <c r="C3408" t="n">
-        <v>24.06</v>
+        <v>24.19</v>
       </c>
       <c r="D3408" t="inlineStr">
         <is>
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3409">
@@ -92457,7 +92457,7 @@
         <v>24</v>
       </c>
       <c r="C3409" t="n">
-        <v>24.29</v>
+        <v>24.69</v>
       </c>
       <c r="D3409" t="inlineStr">
         <is>
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3410">
@@ -92484,7 +92484,7 @@
         <v>1</v>
       </c>
       <c r="C3410" t="n">
-        <v>14.95</v>
+        <v>14.94</v>
       </c>
       <c r="D3410" t="inlineStr">
         <is>
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3411">
@@ -92511,7 +92511,7 @@
         <v>2</v>
       </c>
       <c r="C3411" t="n">
-        <v>17.12</v>
+        <v>16.88</v>
       </c>
       <c r="D3411" t="inlineStr">
         <is>
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3412">
@@ -92538,7 +92538,7 @@
         <v>3</v>
       </c>
       <c r="C3412" t="n">
-        <v>12.26</v>
+        <v>12.4</v>
       </c>
       <c r="D3412" t="inlineStr">
         <is>
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3413">
@@ -92565,7 +92565,7 @@
         <v>4</v>
       </c>
       <c r="C3413" t="n">
-        <v>11.75</v>
+        <v>13.19</v>
       </c>
       <c r="D3413" t="inlineStr">
         <is>
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3415">
@@ -92619,7 +92619,7 @@
         <v>6</v>
       </c>
       <c r="C3415" t="n">
-        <v>17.5</v>
+        <v>17.25</v>
       </c>
       <c r="D3415" t="inlineStr">
         <is>
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3416">
@@ -92646,7 +92646,7 @@
         <v>7</v>
       </c>
       <c r="C3416" t="n">
-        <v>16.5</v>
+        <v>17.32</v>
       </c>
       <c r="D3416" t="inlineStr">
         <is>
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3417">
@@ -92673,7 +92673,7 @@
         <v>8</v>
       </c>
       <c r="C3417" t="n">
-        <v>30.1</v>
+        <v>32.19</v>
       </c>
       <c r="D3417" t="inlineStr">
         <is>
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3418">
@@ -92700,7 +92700,7 @@
         <v>9</v>
       </c>
       <c r="C3418" t="n">
-        <v>43.69</v>
+        <v>45.46</v>
       </c>
       <c r="D3418" t="inlineStr">
         <is>
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3419">
@@ -92727,7 +92727,7 @@
         <v>10</v>
       </c>
       <c r="C3419" t="n">
-        <v>33.44</v>
+        <v>32.07</v>
       </c>
       <c r="D3419" t="inlineStr">
         <is>
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3420">
@@ -92754,7 +92754,7 @@
         <v>11</v>
       </c>
       <c r="C3420" t="n">
-        <v>27.77</v>
+        <v>25.97</v>
       </c>
       <c r="D3420" t="inlineStr">
         <is>
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3421">
@@ -92781,7 +92781,7 @@
         <v>12</v>
       </c>
       <c r="C3421" t="n">
-        <v>31.4</v>
+        <v>28.74</v>
       </c>
       <c r="D3421" t="inlineStr">
         <is>
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3422">
@@ -92808,7 +92808,7 @@
         <v>13</v>
       </c>
       <c r="C3422" t="n">
-        <v>34.41</v>
+        <v>31.87</v>
       </c>
       <c r="D3422" t="inlineStr">
         <is>
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3423">
@@ -92835,7 +92835,7 @@
         <v>14</v>
       </c>
       <c r="C3423" t="n">
-        <v>33.28</v>
+        <v>31.33</v>
       </c>
       <c r="D3423" t="inlineStr">
         <is>
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3424">
@@ -92862,7 +92862,7 @@
         <v>15</v>
       </c>
       <c r="C3424" t="n">
-        <v>33.6</v>
+        <v>31.33</v>
       </c>
       <c r="D3424" t="inlineStr">
         <is>
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3425">
@@ -92889,7 +92889,7 @@
         <v>16</v>
       </c>
       <c r="C3425" t="n">
-        <v>34.34</v>
+        <v>32.07</v>
       </c>
       <c r="D3425" t="inlineStr">
         <is>
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3426">
@@ -92916,7 +92916,7 @@
         <v>17</v>
       </c>
       <c r="C3426" t="n">
-        <v>33.37</v>
+        <v>31.46</v>
       </c>
       <c r="D3426" t="inlineStr">
         <is>
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3427">
@@ -92943,7 +92943,7 @@
         <v>18</v>
       </c>
       <c r="C3427" t="n">
-        <v>30.42</v>
+        <v>29.31</v>
       </c>
       <c r="D3427" t="inlineStr">
         <is>
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3428">
@@ -92970,7 +92970,7 @@
         <v>19</v>
       </c>
       <c r="C3428" t="n">
-        <v>24.86</v>
+        <v>26.37</v>
       </c>
       <c r="D3428" t="inlineStr">
         <is>
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3429">
@@ -92997,7 +92997,7 @@
         <v>20</v>
       </c>
       <c r="C3429" t="n">
-        <v>24.34</v>
+        <v>25.19</v>
       </c>
       <c r="D3429" t="inlineStr">
         <is>
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3430">
@@ -93024,7 +93024,7 @@
         <v>21</v>
       </c>
       <c r="C3430" t="n">
-        <v>35.28</v>
+        <v>36.42</v>
       </c>
       <c r="D3430" t="inlineStr">
         <is>
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3431">
@@ -93051,7 +93051,7 @@
         <v>22</v>
       </c>
       <c r="C3431" t="n">
-        <v>36.35</v>
+        <v>37.23</v>
       </c>
       <c r="D3431" t="inlineStr">
         <is>
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3432">
@@ -93078,7 +93078,7 @@
         <v>23</v>
       </c>
       <c r="C3432" t="n">
-        <v>23.63</v>
+        <v>23.44</v>
       </c>
       <c r="D3432" t="inlineStr">
         <is>
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3433">
@@ -93105,7 +93105,7 @@
         <v>24</v>
       </c>
       <c r="C3433" t="n">
-        <v>25.29</v>
+        <v>24.84</v>
       </c>
       <c r="D3433" t="inlineStr">
         <is>
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3434">
@@ -93132,7 +93132,7 @@
         <v>1</v>
       </c>
       <c r="C3434" t="n">
-        <v>13.14</v>
+        <v>13.24</v>
       </c>
       <c r="D3434" t="inlineStr">
         <is>
@@ -93148,7 +93148,7 @@
         <v>3</v>
       </c>
       <c r="G3434" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3435">
@@ -93159,7 +93159,7 @@
         <v>2</v>
       </c>
       <c r="C3435" t="n">
-        <v>12.9</v>
+        <v>12.78</v>
       </c>
       <c r="D3435" t="inlineStr">
         <is>
@@ -93175,7 +93175,7 @@
         <v>3</v>
       </c>
       <c r="G3435" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3436">
@@ -93186,7 +93186,7 @@
         <v>3</v>
       </c>
       <c r="C3436" t="n">
-        <v>15.48</v>
+        <v>15.36</v>
       </c>
       <c r="D3436" t="inlineStr">
         <is>
@@ -93202,7 +93202,7 @@
         <v>3</v>
       </c>
       <c r="G3436" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3437">
@@ -93213,7 +93213,7 @@
         <v>4</v>
       </c>
       <c r="C3437" t="n">
-        <v>16.8</v>
+        <v>16.83</v>
       </c>
       <c r="D3437" t="inlineStr">
         <is>
@@ -93229,7 +93229,7 @@
         <v>3</v>
       </c>
       <c r="G3437" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3438">
@@ -93240,7 +93240,7 @@
         <v>5</v>
       </c>
       <c r="C3438" t="n">
-        <v>15.33</v>
+        <v>15.23</v>
       </c>
       <c r="D3438" t="inlineStr">
         <is>
@@ -93256,7 +93256,7 @@
         <v>3</v>
       </c>
       <c r="G3438" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3439">
@@ -93267,7 +93267,7 @@
         <v>6</v>
       </c>
       <c r="C3439" t="n">
-        <v>22.41</v>
+        <v>23.25</v>
       </c>
       <c r="D3439" t="inlineStr">
         <is>
@@ -93283,7 +93283,7 @@
         <v>3</v>
       </c>
       <c r="G3439" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3440">
@@ -93294,7 +93294,7 @@
         <v>7</v>
       </c>
       <c r="C3440" t="n">
-        <v>27.55</v>
+        <v>28.86</v>
       </c>
       <c r="D3440" t="inlineStr">
         <is>
@@ -93310,7 +93310,7 @@
         <v>3</v>
       </c>
       <c r="G3440" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3441">
@@ -93321,7 +93321,7 @@
         <v>8</v>
       </c>
       <c r="C3441" t="n">
-        <v>49.14</v>
+        <v>57.92</v>
       </c>
       <c r="D3441" t="inlineStr">
         <is>
@@ -93337,7 +93337,7 @@
         <v>3</v>
       </c>
       <c r="G3441" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3442">
@@ -93348,7 +93348,7 @@
         <v>9</v>
       </c>
       <c r="C3442" t="n">
-        <v>42.92</v>
+        <v>53.48</v>
       </c>
       <c r="D3442" t="inlineStr">
         <is>
@@ -93364,7 +93364,7 @@
         <v>3</v>
       </c>
       <c r="G3442" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3443">
@@ -93375,7 +93375,7 @@
         <v>10</v>
       </c>
       <c r="C3443" t="n">
-        <v>29.76</v>
+        <v>30.28</v>
       </c>
       <c r="D3443" t="inlineStr">
         <is>
@@ -93391,7 +93391,7 @@
         <v>3</v>
       </c>
       <c r="G3443" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3444">
@@ -93402,7 +93402,7 @@
         <v>11</v>
       </c>
       <c r="C3444" t="n">
-        <v>26.26</v>
+        <v>27.16</v>
       </c>
       <c r="D3444" t="inlineStr">
         <is>
@@ -93418,7 +93418,7 @@
         <v>3</v>
       </c>
       <c r="G3444" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3445">
@@ -93429,7 +93429,7 @@
         <v>12</v>
       </c>
       <c r="C3445" t="n">
-        <v>30.95</v>
+        <v>31.6</v>
       </c>
       <c r="D3445" t="inlineStr">
         <is>
@@ -93445,7 +93445,7 @@
         <v>3</v>
       </c>
       <c r="G3445" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3446">
@@ -93456,7 +93456,7 @@
         <v>13</v>
       </c>
       <c r="C3446" t="n">
-        <v>30.47</v>
+        <v>31.28</v>
       </c>
       <c r="D3446" t="inlineStr">
         <is>
@@ -93472,7 +93472,7 @@
         <v>3</v>
       </c>
       <c r="G3446" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3447">
@@ -93483,7 +93483,7 @@
         <v>14</v>
       </c>
       <c r="C3447" t="n">
-        <v>27.02</v>
+        <v>30.91</v>
       </c>
       <c r="D3447" t="inlineStr">
         <is>
@@ -93499,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="G3447" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3448">
@@ -93510,7 +93510,7 @@
         <v>15</v>
       </c>
       <c r="C3448" t="n">
-        <v>30.5</v>
+        <v>31.39</v>
       </c>
       <c r="D3448" t="inlineStr">
         <is>
@@ -93526,7 +93526,7 @@
         <v>3</v>
       </c>
       <c r="G3448" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3449">
@@ -93537,7 +93537,7 @@
         <v>16</v>
       </c>
       <c r="C3449" t="n">
-        <v>27.55</v>
+        <v>31.67</v>
       </c>
       <c r="D3449" t="inlineStr">
         <is>
@@ -93553,7 +93553,7 @@
         <v>3</v>
       </c>
       <c r="G3449" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3450">
@@ -93564,7 +93564,7 @@
         <v>17</v>
       </c>
       <c r="C3450" t="n">
-        <v>30.79</v>
+        <v>29.58</v>
       </c>
       <c r="D3450" t="inlineStr">
         <is>
@@ -93580,7 +93580,7 @@
         <v>3</v>
       </c>
       <c r="G3450" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3451">
@@ -93591,7 +93591,7 @@
         <v>18</v>
       </c>
       <c r="C3451" t="n">
-        <v>19.95</v>
+        <v>23.45</v>
       </c>
       <c r="D3451" t="inlineStr">
         <is>
@@ -93607,7 +93607,7 @@
         <v>3</v>
       </c>
       <c r="G3451" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3452">
@@ -93618,7 +93618,7 @@
         <v>19</v>
       </c>
       <c r="C3452" t="n">
-        <v>24.72</v>
+        <v>23.39</v>
       </c>
       <c r="D3452" t="inlineStr">
         <is>
@@ -93634,7 +93634,7 @@
         <v>3</v>
       </c>
       <c r="G3452" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3453">
@@ -93645,7 +93645,7 @@
         <v>20</v>
       </c>
       <c r="C3453" t="n">
-        <v>20.01</v>
+        <v>25.92</v>
       </c>
       <c r="D3453" t="inlineStr">
         <is>
@@ -93661,7 +93661,7 @@
         <v>3</v>
       </c>
       <c r="G3453" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3454">
@@ -93672,7 +93672,7 @@
         <v>21</v>
       </c>
       <c r="C3454" t="n">
-        <v>33.39</v>
+        <v>47.36</v>
       </c>
       <c r="D3454" t="inlineStr">
         <is>
@@ -93688,7 +93688,7 @@
         <v>3</v>
       </c>
       <c r="G3454" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3455">
@@ -93699,7 +93699,7 @@
         <v>22</v>
       </c>
       <c r="C3455" t="n">
-        <v>35.9</v>
+        <v>48.13</v>
       </c>
       <c r="D3455" t="inlineStr">
         <is>
@@ -93715,7 +93715,7 @@
         <v>3</v>
       </c>
       <c r="G3455" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3456">
@@ -93726,7 +93726,7 @@
         <v>23</v>
       </c>
       <c r="C3456" t="n">
-        <v>32.08</v>
+        <v>34.41</v>
       </c>
       <c r="D3456" t="inlineStr">
         <is>
@@ -93742,7 +93742,7 @@
         <v>3</v>
       </c>
       <c r="G3456" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3457">
@@ -93753,7 +93753,7 @@
         <v>24</v>
       </c>
       <c r="C3457" t="n">
-        <v>25.46</v>
+        <v>27.41</v>
       </c>
       <c r="D3457" t="inlineStr">
         <is>
@@ -93769,7 +93769,7 @@
         <v>3</v>
       </c>
       <c r="G3457" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3458">
@@ -93780,7 +93780,7 @@
         <v>1</v>
       </c>
       <c r="C3458" t="n">
-        <v>9.69</v>
+        <v>10.75</v>
       </c>
       <c r="D3458" t="inlineStr">
         <is>
@@ -93796,7 +93796,7 @@
         <v>3</v>
       </c>
       <c r="G3458" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3459">
@@ -93807,7 +93807,7 @@
         <v>2</v>
       </c>
       <c r="C3459" t="n">
-        <v>10.69</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D3459" t="inlineStr">
         <is>
@@ -93823,7 +93823,7 @@
         <v>3</v>
       </c>
       <c r="G3459" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3460">
@@ -93834,7 +93834,7 @@
         <v>3</v>
       </c>
       <c r="C3460" t="n">
-        <v>9.890000000000001</v>
+        <v>4.17</v>
       </c>
       <c r="D3460" t="inlineStr">
         <is>
@@ -93850,7 +93850,7 @@
         <v>3</v>
       </c>
       <c r="G3460" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3461">
@@ -93861,7 +93861,7 @@
         <v>4</v>
       </c>
       <c r="C3461" t="n">
-        <v>9.83</v>
+        <v>7.77</v>
       </c>
       <c r="D3461" t="inlineStr">
         <is>
@@ -93877,7 +93877,7 @@
         <v>3</v>
       </c>
       <c r="G3461" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3462">
@@ -93888,7 +93888,7 @@
         <v>5</v>
       </c>
       <c r="C3462" t="n">
-        <v>10.24</v>
+        <v>6.51</v>
       </c>
       <c r="D3462" t="inlineStr">
         <is>
@@ -93904,7 +93904,7 @@
         <v>3</v>
       </c>
       <c r="G3462" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3463">
@@ -93915,7 +93915,7 @@
         <v>6</v>
       </c>
       <c r="C3463" t="n">
-        <v>16.46</v>
+        <v>11.26</v>
       </c>
       <c r="D3463" t="inlineStr">
         <is>
@@ -93931,7 +93931,7 @@
         <v>3</v>
       </c>
       <c r="G3463" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3464">
@@ -93942,7 +93942,7 @@
         <v>7</v>
       </c>
       <c r="C3464" t="n">
-        <v>24.86</v>
+        <v>21.01</v>
       </c>
       <c r="D3464" t="inlineStr">
         <is>
@@ -93958,7 +93958,7 @@
         <v>3</v>
       </c>
       <c r="G3464" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3465">
@@ -93969,7 +93969,7 @@
         <v>8</v>
       </c>
       <c r="C3465" t="n">
-        <v>68.41</v>
+        <v>49.54</v>
       </c>
       <c r="D3465" t="inlineStr">
         <is>
@@ -93985,7 +93985,7 @@
         <v>3</v>
       </c>
       <c r="G3465" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3466">
@@ -93996,7 +93996,7 @@
         <v>9</v>
       </c>
       <c r="C3466" t="n">
-        <v>61.78</v>
+        <v>47.62</v>
       </c>
       <c r="D3466" t="inlineStr">
         <is>
@@ -94012,7 +94012,7 @@
         <v>3</v>
       </c>
       <c r="G3466" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3467">
@@ -94023,7 +94023,7 @@
         <v>10</v>
       </c>
       <c r="C3467" t="n">
-        <v>21.54</v>
+        <v>20.33</v>
       </c>
       <c r="D3467" t="inlineStr">
         <is>
@@ -94039,7 +94039,7 @@
         <v>3</v>
       </c>
       <c r="G3467" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3468">
@@ -94050,7 +94050,7 @@
         <v>11</v>
       </c>
       <c r="C3468" t="n">
-        <v>21.11</v>
+        <v>24.6</v>
       </c>
       <c r="D3468" t="inlineStr">
         <is>
@@ -94066,7 +94066,7 @@
         <v>3</v>
       </c>
       <c r="G3468" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3469">
@@ -94077,7 +94077,7 @@
         <v>12</v>
       </c>
       <c r="C3469" t="n">
-        <v>27.99</v>
+        <v>29.54</v>
       </c>
       <c r="D3469" t="inlineStr">
         <is>
@@ -94093,7 +94093,7 @@
         <v>3</v>
       </c>
       <c r="G3469" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3470">
@@ -94104,7 +94104,7 @@
         <v>13</v>
       </c>
       <c r="C3470" t="n">
-        <v>27.2</v>
+        <v>34.33</v>
       </c>
       <c r="D3470" t="inlineStr">
         <is>
@@ -94120,7 +94120,7 @@
         <v>3</v>
       </c>
       <c r="G3470" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3471">
@@ -94131,7 +94131,7 @@
         <v>14</v>
       </c>
       <c r="C3471" t="n">
-        <v>24.24</v>
+        <v>27.94</v>
       </c>
       <c r="D3471" t="inlineStr">
         <is>
@@ -94147,7 +94147,7 @@
         <v>3</v>
       </c>
       <c r="G3471" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3472">
@@ -94158,7 +94158,7 @@
         <v>15</v>
       </c>
       <c r="C3472" t="n">
-        <v>23.78</v>
+        <v>30.26</v>
       </c>
       <c r="D3472" t="inlineStr">
         <is>
@@ -94174,7 +94174,7 @@
         <v>3</v>
       </c>
       <c r="G3472" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3473">
@@ -94185,7 +94185,7 @@
         <v>16</v>
       </c>
       <c r="C3473" t="n">
-        <v>24.43</v>
+        <v>30.91</v>
       </c>
       <c r="D3473" t="inlineStr">
         <is>
@@ -94201,7 +94201,7 @@
         <v>3</v>
       </c>
       <c r="G3473" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3474">
@@ -94212,7 +94212,7 @@
         <v>17</v>
       </c>
       <c r="C3474" t="n">
-        <v>21.35</v>
+        <v>19.19</v>
       </c>
       <c r="D3474" t="inlineStr">
         <is>
@@ -94228,7 +94228,7 @@
         <v>3</v>
       </c>
       <c r="G3474" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3475">
@@ -94239,7 +94239,7 @@
         <v>18</v>
       </c>
       <c r="C3475" t="n">
-        <v>19.2</v>
+        <v>30.89</v>
       </c>
       <c r="D3475" t="inlineStr">
         <is>
@@ -94255,7 +94255,7 @@
         <v>3</v>
       </c>
       <c r="G3475" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3476">
@@ -94266,7 +94266,7 @@
         <v>19</v>
       </c>
       <c r="C3476" t="n">
-        <v>20.24</v>
+        <v>23.42</v>
       </c>
       <c r="D3476" t="inlineStr">
         <is>
@@ -94282,7 +94282,7 @@
         <v>3</v>
       </c>
       <c r="G3476" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3477">
@@ -94293,7 +94293,7 @@
         <v>20</v>
       </c>
       <c r="C3477" t="n">
-        <v>30.77</v>
+        <v>14.01</v>
       </c>
       <c r="D3477" t="inlineStr">
         <is>
@@ -94309,7 +94309,7 @@
         <v>3</v>
       </c>
       <c r="G3477" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3478">
@@ -94320,7 +94320,7 @@
         <v>21</v>
       </c>
       <c r="C3478" t="n">
-        <v>32.67</v>
+        <v>26.19</v>
       </c>
       <c r="D3478" t="inlineStr">
         <is>
@@ -94336,7 +94336,7 @@
         <v>3</v>
       </c>
       <c r="G3478" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3479">
@@ -94347,7 +94347,7 @@
         <v>22</v>
       </c>
       <c r="C3479" t="n">
-        <v>34.7</v>
+        <v>29.63</v>
       </c>
       <c r="D3479" t="inlineStr">
         <is>
@@ -94363,7 +94363,7 @@
         <v>3</v>
       </c>
       <c r="G3479" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3480">
@@ -94374,7 +94374,7 @@
         <v>23</v>
       </c>
       <c r="C3480" t="n">
-        <v>34.98</v>
+        <v>32.11</v>
       </c>
       <c r="D3480" t="inlineStr">
         <is>
@@ -94390,7 +94390,7 @@
         <v>3</v>
       </c>
       <c r="G3480" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
       </c>
     </row>
     <row r="3481">
@@ -94401,7 +94401,7 @@
         <v>24</v>
       </c>
       <c r="C3481" t="n">
-        <v>29.49</v>
+        <v>34.03</v>
       </c>
       <c r="D3481" t="inlineStr">
         <is>
@@ -94417,7 +94417,655 @@
         <v>3</v>
       </c>
       <c r="G3481" s="2" t="n">
-        <v>46288.4532080768</v>
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3482">
+      <c r="A3482" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3482" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3482" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="D3482" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3482" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3482" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3482" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3483">
+      <c r="A3483" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3483" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3483" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="D3483" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3483" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3483" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3483" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3484">
+      <c r="A3484" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3484" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3484" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="D3484" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3484" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3484" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3484" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3485">
+      <c r="A3485" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3485" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3485" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="D3485" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3485" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3485" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3485" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3486">
+      <c r="A3486" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3486" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3486" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="D3486" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3486" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3486" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3486" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3487">
+      <c r="A3487" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3487" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3487" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="D3487" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3487" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3487" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3487" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3488">
+      <c r="A3488" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3488" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3488" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="D3488" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3488" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3488" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3488" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3489">
+      <c r="A3489" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3489" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3489" t="n">
+        <v>48.04</v>
+      </c>
+      <c r="D3489" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3489" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3489" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3489" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3490">
+      <c r="A3490" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3490" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3490" t="n">
+        <v>43.81</v>
+      </c>
+      <c r="D3490" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3490" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3490" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3490" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3491">
+      <c r="A3491" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3491" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3491" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="D3491" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3491" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3491" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3491" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3492">
+      <c r="A3492" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3492" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3492" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="D3492" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3492" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3492" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3492" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3493">
+      <c r="A3493" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3493" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3493" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="D3493" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3493" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3493" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3493" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3494">
+      <c r="A3494" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3494" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3494" t="n">
+        <v>31.28</v>
+      </c>
+      <c r="D3494" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3494" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3494" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3494" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3495">
+      <c r="A3495" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3495" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3495" t="n">
+        <v>30.31</v>
+      </c>
+      <c r="D3495" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3495" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3495" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3495" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3496">
+      <c r="A3496" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3496" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3496" t="n">
+        <v>33.11</v>
+      </c>
+      <c r="D3496" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3496" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3496" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3496" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3497">
+      <c r="A3497" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3497" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3497" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="D3497" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3497" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3497" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3497" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3498">
+      <c r="A3498" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3498" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3498" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="D3498" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3498" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3498" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3498" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3499">
+      <c r="A3499" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3499" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3499" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="D3499" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3499" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3499" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3499" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3500">
+      <c r="A3500" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3500" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3500" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="D3500" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3500" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3500" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3500" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3501">
+      <c r="A3501" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3501" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3501" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="D3501" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3501" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3501" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3501" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3502">
+      <c r="A3502" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3502" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3502" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="D3502" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3502" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3502" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3502" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3503">
+      <c r="A3503" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3503" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3503" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="D3503" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3503" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3503" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3503" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3504">
+      <c r="A3504" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3504" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3504" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="D3504" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3504" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3504" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3504" s="2" t="n">
+        <v>46288.88258519529</v>
+      </c>
+    </row>
+    <row r="3505">
+      <c r="A3505" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3505" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3505" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="D3505" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3505" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3505" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3505" s="2" t="n">
+        <v>46288.88258519529</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3324">
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3333">
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3335">
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3337">
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3341">
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3343">
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3344">
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3345">
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3346">
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3347">
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3355">
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3356">
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3357">
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3360">
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3362">
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3364">
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3365">
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3366">
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3367">
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3368">
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3369">
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3370">
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3371">
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3372">
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3373">
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3374">
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3375">
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3376">
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3377">
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3378">
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3379">
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3380">
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3381">
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3382">
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3383">
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3384">
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3385">
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3386">
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3387">
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3388">
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3389">
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3390">
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3391">
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3392">
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3393">
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3394">
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3395">
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3396">
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3397">
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3398">
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3399">
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3400">
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3401">
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3402">
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3403">
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3404">
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3405">
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3406">
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3407">
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3408">
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3409">
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3410">
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3411">
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3412">
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3413">
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3415">
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3416">
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3417">
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3418">
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3419">
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3420">
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3421">
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3422">
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3423">
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3424">
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3425">
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3426">
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3427">
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3428">
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3429">
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3430">
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3431">
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3432">
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3433">
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3434">
@@ -93148,7 +93148,7 @@
         <v>3</v>
       </c>
       <c r="G3434" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3435">
@@ -93175,7 +93175,7 @@
         <v>3</v>
       </c>
       <c r="G3435" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3436">
@@ -93202,7 +93202,7 @@
         <v>3</v>
       </c>
       <c r="G3436" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3437">
@@ -93229,7 +93229,7 @@
         <v>3</v>
       </c>
       <c r="G3437" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3438">
@@ -93256,7 +93256,7 @@
         <v>3</v>
       </c>
       <c r="G3438" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3439">
@@ -93283,7 +93283,7 @@
         <v>3</v>
       </c>
       <c r="G3439" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3440">
@@ -93310,7 +93310,7 @@
         <v>3</v>
       </c>
       <c r="G3440" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3441">
@@ -93337,7 +93337,7 @@
         <v>3</v>
       </c>
       <c r="G3441" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3442">
@@ -93364,7 +93364,7 @@
         <v>3</v>
       </c>
       <c r="G3442" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3443">
@@ -93391,7 +93391,7 @@
         <v>3</v>
       </c>
       <c r="G3443" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3444">
@@ -93418,7 +93418,7 @@
         <v>3</v>
       </c>
       <c r="G3444" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3445">
@@ -93445,7 +93445,7 @@
         <v>3</v>
       </c>
       <c r="G3445" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3446">
@@ -93472,7 +93472,7 @@
         <v>3</v>
       </c>
       <c r="G3446" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3447">
@@ -93499,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="G3447" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3448">
@@ -93526,7 +93526,7 @@
         <v>3</v>
       </c>
       <c r="G3448" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3449">
@@ -93553,7 +93553,7 @@
         <v>3</v>
       </c>
       <c r="G3449" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3450">
@@ -93580,7 +93580,7 @@
         <v>3</v>
       </c>
       <c r="G3450" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3451">
@@ -93607,7 +93607,7 @@
         <v>3</v>
       </c>
       <c r="G3451" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3452">
@@ -93634,7 +93634,7 @@
         <v>3</v>
       </c>
       <c r="G3452" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3453">
@@ -93661,7 +93661,7 @@
         <v>3</v>
       </c>
       <c r="G3453" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3454">
@@ -93688,7 +93688,7 @@
         <v>3</v>
       </c>
       <c r="G3454" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3455">
@@ -93715,7 +93715,7 @@
         <v>3</v>
       </c>
       <c r="G3455" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3456">
@@ -93742,7 +93742,7 @@
         <v>3</v>
       </c>
       <c r="G3456" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3457">
@@ -93769,7 +93769,7 @@
         <v>3</v>
       </c>
       <c r="G3457" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3458">
@@ -93796,7 +93796,7 @@
         <v>3</v>
       </c>
       <c r="G3458" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3459">
@@ -93823,7 +93823,7 @@
         <v>3</v>
       </c>
       <c r="G3459" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3460">
@@ -93850,7 +93850,7 @@
         <v>3</v>
       </c>
       <c r="G3460" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3461">
@@ -93877,7 +93877,7 @@
         <v>3</v>
       </c>
       <c r="G3461" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3462">
@@ -93904,7 +93904,7 @@
         <v>3</v>
       </c>
       <c r="G3462" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3463">
@@ -93931,7 +93931,7 @@
         <v>3</v>
       </c>
       <c r="G3463" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3464">
@@ -93958,7 +93958,7 @@
         <v>3</v>
       </c>
       <c r="G3464" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3465">
@@ -93985,7 +93985,7 @@
         <v>3</v>
       </c>
       <c r="G3465" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3466">
@@ -94012,7 +94012,7 @@
         <v>3</v>
       </c>
       <c r="G3466" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3467">
@@ -94039,7 +94039,7 @@
         <v>3</v>
       </c>
       <c r="G3467" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3468">
@@ -94066,7 +94066,7 @@
         <v>3</v>
       </c>
       <c r="G3468" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3469">
@@ -94093,7 +94093,7 @@
         <v>3</v>
       </c>
       <c r="G3469" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3470">
@@ -94120,7 +94120,7 @@
         <v>3</v>
       </c>
       <c r="G3470" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3471">
@@ -94147,7 +94147,7 @@
         <v>3</v>
       </c>
       <c r="G3471" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3472">
@@ -94174,7 +94174,7 @@
         <v>3</v>
       </c>
       <c r="G3472" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3473">
@@ -94201,7 +94201,7 @@
         <v>3</v>
       </c>
       <c r="G3473" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3474">
@@ -94228,7 +94228,7 @@
         <v>3</v>
       </c>
       <c r="G3474" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3475">
@@ -94255,7 +94255,7 @@
         <v>3</v>
       </c>
       <c r="G3475" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3476">
@@ -94282,7 +94282,7 @@
         <v>3</v>
       </c>
       <c r="G3476" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3477">
@@ -94309,7 +94309,7 @@
         <v>3</v>
       </c>
       <c r="G3477" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3478">
@@ -94336,7 +94336,7 @@
         <v>3</v>
       </c>
       <c r="G3478" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3479">
@@ -94363,7 +94363,7 @@
         <v>3</v>
       </c>
       <c r="G3479" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3480">
@@ -94390,7 +94390,7 @@
         <v>3</v>
       </c>
       <c r="G3480" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3481">
@@ -94417,7 +94417,7 @@
         <v>3</v>
       </c>
       <c r="G3481" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3482">
@@ -94444,7 +94444,7 @@
         <v>3</v>
       </c>
       <c r="G3482" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3483">
@@ -94471,7 +94471,7 @@
         <v>3</v>
       </c>
       <c r="G3483" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3484">
@@ -94498,7 +94498,7 @@
         <v>3</v>
       </c>
       <c r="G3484" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3485">
@@ -94525,7 +94525,7 @@
         <v>3</v>
       </c>
       <c r="G3485" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3486">
@@ -94552,7 +94552,7 @@
         <v>3</v>
       </c>
       <c r="G3486" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3487">
@@ -94579,7 +94579,7 @@
         <v>3</v>
       </c>
       <c r="G3487" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3488">
@@ -94606,7 +94606,7 @@
         <v>3</v>
       </c>
       <c r="G3488" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3489">
@@ -94633,7 +94633,7 @@
         <v>3</v>
       </c>
       <c r="G3489" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3490">
@@ -94660,7 +94660,7 @@
         <v>3</v>
       </c>
       <c r="G3490" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3491">
@@ -94687,7 +94687,7 @@
         <v>3</v>
       </c>
       <c r="G3491" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3492">
@@ -94714,7 +94714,7 @@
         <v>3</v>
       </c>
       <c r="G3492" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3493">
@@ -94741,7 +94741,7 @@
         <v>3</v>
       </c>
       <c r="G3493" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3494">
@@ -94768,7 +94768,7 @@
         <v>3</v>
       </c>
       <c r="G3494" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3495">
@@ -94795,7 +94795,7 @@
         <v>3</v>
       </c>
       <c r="G3495" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3496">
@@ -94822,7 +94822,7 @@
         <v>3</v>
       </c>
       <c r="G3496" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3497">
@@ -94849,7 +94849,7 @@
         <v>3</v>
       </c>
       <c r="G3497" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3498">
@@ -94876,7 +94876,7 @@
         <v>3</v>
       </c>
       <c r="G3498" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3499">
@@ -94903,7 +94903,7 @@
         <v>3</v>
       </c>
       <c r="G3499" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3500">
@@ -94930,7 +94930,7 @@
         <v>3</v>
       </c>
       <c r="G3500" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3501">
@@ -94957,7 +94957,7 @@
         <v>3</v>
       </c>
       <c r="G3501" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3502">
@@ -94984,7 +94984,7 @@
         <v>3</v>
       </c>
       <c r="G3502" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3503">
@@ -95011,7 +95011,7 @@
         <v>3</v>
       </c>
       <c r="G3503" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3504">
@@ -95038,7 +95038,7 @@
         <v>3</v>
       </c>
       <c r="G3504" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
     <row r="3505">
@@ -95065,7 +95065,7 @@
         <v>3</v>
       </c>
       <c r="G3505" s="2" t="n">
-        <v>46288.88258519529</v>
+        <v>46289.46728715212</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3505"/>
+  <dimension ref="A1:G3529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3324">
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3333">
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3335">
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3337">
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3341">
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3343">
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3344">
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3345">
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3346">
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3347">
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3355">
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3356">
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3357">
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3360">
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3362">
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3364">
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3365">
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3366">
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3367">
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3368">
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3369">
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3370">
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3371">
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3372">
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3373">
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3374">
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3375">
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3376">
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3377">
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3378">
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3379">
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3380">
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3381">
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3382">
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3383">
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3384">
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3385">
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3386">
@@ -91836,7 +91836,7 @@
         <v>1</v>
       </c>
       <c r="C3386" t="n">
-        <v>11.47</v>
+        <v>12.11</v>
       </c>
       <c r="D3386" t="inlineStr">
         <is>
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3387">
@@ -91863,7 +91863,7 @@
         <v>2</v>
       </c>
       <c r="C3387" t="n">
-        <v>12.88</v>
+        <v>13.17</v>
       </c>
       <c r="D3387" t="inlineStr">
         <is>
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3388">
@@ -91890,7 +91890,7 @@
         <v>3</v>
       </c>
       <c r="C3388" t="n">
-        <v>13.71</v>
+        <v>13.75</v>
       </c>
       <c r="D3388" t="inlineStr">
         <is>
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3389">
@@ -91917,7 +91917,7 @@
         <v>4</v>
       </c>
       <c r="C3389" t="n">
-        <v>15.24</v>
+        <v>15.23</v>
       </c>
       <c r="D3389" t="inlineStr">
         <is>
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3390">
@@ -91944,7 +91944,7 @@
         <v>5</v>
       </c>
       <c r="C3390" t="n">
-        <v>14.58</v>
+        <v>14.66</v>
       </c>
       <c r="D3390" t="inlineStr">
         <is>
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3391">
@@ -91971,7 +91971,7 @@
         <v>6</v>
       </c>
       <c r="C3391" t="n">
-        <v>15.26</v>
+        <v>15.48</v>
       </c>
       <c r="D3391" t="inlineStr">
         <is>
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3392">
@@ -91998,7 +91998,7 @@
         <v>7</v>
       </c>
       <c r="C3392" t="n">
-        <v>21.12</v>
+        <v>21.34</v>
       </c>
       <c r="D3392" t="inlineStr">
         <is>
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3393">
@@ -92025,7 +92025,7 @@
         <v>8</v>
       </c>
       <c r="C3393" t="n">
-        <v>37.22</v>
+        <v>37.58</v>
       </c>
       <c r="D3393" t="inlineStr">
         <is>
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3394">
@@ -92052,7 +92052,7 @@
         <v>9</v>
       </c>
       <c r="C3394" t="n">
-        <v>36.89</v>
+        <v>36.54</v>
       </c>
       <c r="D3394" t="inlineStr">
         <is>
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3395">
@@ -92079,7 +92079,7 @@
         <v>10</v>
       </c>
       <c r="C3395" t="n">
-        <v>19.39</v>
+        <v>19.69</v>
       </c>
       <c r="D3395" t="inlineStr">
         <is>
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3396">
@@ -92106,7 +92106,7 @@
         <v>11</v>
       </c>
       <c r="C3396" t="n">
-        <v>22.25</v>
+        <v>22.31</v>
       </c>
       <c r="D3396" t="inlineStr">
         <is>
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3397">
@@ -92133,7 +92133,7 @@
         <v>12</v>
       </c>
       <c r="C3397" t="n">
-        <v>22.93</v>
+        <v>22.92</v>
       </c>
       <c r="D3397" t="inlineStr">
         <is>
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3398">
@@ -92160,7 +92160,7 @@
         <v>13</v>
       </c>
       <c r="C3398" t="n">
-        <v>23.25</v>
+        <v>23.24</v>
       </c>
       <c r="D3398" t="inlineStr">
         <is>
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3399">
@@ -92187,7 +92187,7 @@
         <v>14</v>
       </c>
       <c r="C3399" t="n">
-        <v>22.77</v>
+        <v>22.79</v>
       </c>
       <c r="D3399" t="inlineStr">
         <is>
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3400">
@@ -92214,7 +92214,7 @@
         <v>15</v>
       </c>
       <c r="C3400" t="n">
-        <v>23.02</v>
+        <v>23.08</v>
       </c>
       <c r="D3400" t="inlineStr">
         <is>
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3401">
@@ -92241,7 +92241,7 @@
         <v>16</v>
       </c>
       <c r="C3401" t="n">
-        <v>23.76</v>
+        <v>23.78</v>
       </c>
       <c r="D3401" t="inlineStr">
         <is>
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3402">
@@ -92268,7 +92268,7 @@
         <v>17</v>
       </c>
       <c r="C3402" t="n">
-        <v>24.1</v>
+        <v>23.58</v>
       </c>
       <c r="D3402" t="inlineStr">
         <is>
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3403">
@@ -92295,7 +92295,7 @@
         <v>18</v>
       </c>
       <c r="C3403" t="n">
-        <v>22.35</v>
+        <v>22.28</v>
       </c>
       <c r="D3403" t="inlineStr">
         <is>
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3404">
@@ -92322,7 +92322,7 @@
         <v>19</v>
       </c>
       <c r="C3404" t="n">
-        <v>20.5</v>
+        <v>20.83</v>
       </c>
       <c r="D3404" t="inlineStr">
         <is>
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3405">
@@ -92349,7 +92349,7 @@
         <v>20</v>
       </c>
       <c r="C3405" t="n">
-        <v>25.22</v>
+        <v>24.84</v>
       </c>
       <c r="D3405" t="inlineStr">
         <is>
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3406">
@@ -92376,7 +92376,7 @@
         <v>21</v>
       </c>
       <c r="C3406" t="n">
-        <v>36.37</v>
+        <v>36.04</v>
       </c>
       <c r="D3406" t="inlineStr">
         <is>
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3407">
@@ -92403,7 +92403,7 @@
         <v>22</v>
       </c>
       <c r="C3407" t="n">
-        <v>38.21</v>
+        <v>38.62</v>
       </c>
       <c r="D3407" t="inlineStr">
         <is>
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3408">
@@ -92430,7 +92430,7 @@
         <v>23</v>
       </c>
       <c r="C3408" t="n">
-        <v>24.19</v>
+        <v>25.29</v>
       </c>
       <c r="D3408" t="inlineStr">
         <is>
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3409">
@@ -92457,7 +92457,7 @@
         <v>24</v>
       </c>
       <c r="C3409" t="n">
-        <v>24.69</v>
+        <v>25.12</v>
       </c>
       <c r="D3409" t="inlineStr">
         <is>
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3410">
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3411">
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3412">
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3413">
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3415">
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3416">
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3417">
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3418">
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3419">
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3420">
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3421">
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3422">
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3423">
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3424">
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3425">
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3426">
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3427">
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3428">
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3429">
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3430">
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3431">
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3432">
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3433">
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3434">
@@ -93148,7 +93148,7 @@
         <v>3</v>
       </c>
       <c r="G3434" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3435">
@@ -93175,7 +93175,7 @@
         <v>3</v>
       </c>
       <c r="G3435" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3436">
@@ -93202,7 +93202,7 @@
         <v>3</v>
       </c>
       <c r="G3436" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3437">
@@ -93229,7 +93229,7 @@
         <v>3</v>
       </c>
       <c r="G3437" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3438">
@@ -93256,7 +93256,7 @@
         <v>3</v>
       </c>
       <c r="G3438" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3439">
@@ -93283,7 +93283,7 @@
         <v>3</v>
       </c>
       <c r="G3439" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3440">
@@ -93310,7 +93310,7 @@
         <v>3</v>
       </c>
       <c r="G3440" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3441">
@@ -93337,7 +93337,7 @@
         <v>3</v>
       </c>
       <c r="G3441" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3442">
@@ -93364,7 +93364,7 @@
         <v>3</v>
       </c>
       <c r="G3442" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3443">
@@ -93391,7 +93391,7 @@
         <v>3</v>
       </c>
       <c r="G3443" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3444">
@@ -93418,7 +93418,7 @@
         <v>3</v>
       </c>
       <c r="G3444" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3445">
@@ -93445,7 +93445,7 @@
         <v>3</v>
       </c>
       <c r="G3445" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3446">
@@ -93472,7 +93472,7 @@
         <v>3</v>
       </c>
       <c r="G3446" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3447">
@@ -93499,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="G3447" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3448">
@@ -93526,7 +93526,7 @@
         <v>3</v>
       </c>
       <c r="G3448" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3449">
@@ -93553,7 +93553,7 @@
         <v>3</v>
       </c>
       <c r="G3449" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3450">
@@ -93580,7 +93580,7 @@
         <v>3</v>
       </c>
       <c r="G3450" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3451">
@@ -93607,7 +93607,7 @@
         <v>3</v>
       </c>
       <c r="G3451" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3452">
@@ -93634,7 +93634,7 @@
         <v>3</v>
       </c>
       <c r="G3452" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3453">
@@ -93661,7 +93661,7 @@
         <v>3</v>
       </c>
       <c r="G3453" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3454">
@@ -93688,7 +93688,7 @@
         <v>3</v>
       </c>
       <c r="G3454" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3455">
@@ -93715,7 +93715,7 @@
         <v>3</v>
       </c>
       <c r="G3455" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3456">
@@ -93742,7 +93742,7 @@
         <v>3</v>
       </c>
       <c r="G3456" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3457">
@@ -93769,7 +93769,7 @@
         <v>3</v>
       </c>
       <c r="G3457" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3458">
@@ -93780,7 +93780,7 @@
         <v>1</v>
       </c>
       <c r="C3458" t="n">
-        <v>10.75</v>
+        <v>10.39</v>
       </c>
       <c r="D3458" t="inlineStr">
         <is>
@@ -93796,7 +93796,7 @@
         <v>3</v>
       </c>
       <c r="G3458" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3459">
@@ -93807,7 +93807,7 @@
         <v>2</v>
       </c>
       <c r="C3459" t="n">
-        <v>9.369999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="D3459" t="inlineStr">
         <is>
@@ -93823,7 +93823,7 @@
         <v>3</v>
       </c>
       <c r="G3459" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3460">
@@ -93834,7 +93834,7 @@
         <v>3</v>
       </c>
       <c r="C3460" t="n">
-        <v>4.17</v>
+        <v>2.3</v>
       </c>
       <c r="D3460" t="inlineStr">
         <is>
@@ -93850,7 +93850,7 @@
         <v>3</v>
       </c>
       <c r="G3460" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3461">
@@ -93861,7 +93861,7 @@
         <v>4</v>
       </c>
       <c r="C3461" t="n">
-        <v>7.77</v>
+        <v>7.95</v>
       </c>
       <c r="D3461" t="inlineStr">
         <is>
@@ -93877,7 +93877,7 @@
         <v>3</v>
       </c>
       <c r="G3461" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3462">
@@ -93888,7 +93888,7 @@
         <v>5</v>
       </c>
       <c r="C3462" t="n">
-        <v>6.51</v>
+        <v>5.83</v>
       </c>
       <c r="D3462" t="inlineStr">
         <is>
@@ -93904,7 +93904,7 @@
         <v>3</v>
       </c>
       <c r="G3462" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3463">
@@ -93915,7 +93915,7 @@
         <v>6</v>
       </c>
       <c r="C3463" t="n">
-        <v>11.26</v>
+        <v>12.04</v>
       </c>
       <c r="D3463" t="inlineStr">
         <is>
@@ -93931,7 +93931,7 @@
         <v>3</v>
       </c>
       <c r="G3463" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3464">
@@ -93942,7 +93942,7 @@
         <v>7</v>
       </c>
       <c r="C3464" t="n">
-        <v>21.01</v>
+        <v>21.89</v>
       </c>
       <c r="D3464" t="inlineStr">
         <is>
@@ -93958,7 +93958,7 @@
         <v>3</v>
       </c>
       <c r="G3464" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3465">
@@ -93969,7 +93969,7 @@
         <v>8</v>
       </c>
       <c r="C3465" t="n">
-        <v>49.54</v>
+        <v>62.29</v>
       </c>
       <c r="D3465" t="inlineStr">
         <is>
@@ -93985,7 +93985,7 @@
         <v>3</v>
       </c>
       <c r="G3465" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3466">
@@ -93996,7 +93996,7 @@
         <v>9</v>
       </c>
       <c r="C3466" t="n">
-        <v>47.62</v>
+        <v>59.15</v>
       </c>
       <c r="D3466" t="inlineStr">
         <is>
@@ -94012,7 +94012,7 @@
         <v>3</v>
       </c>
       <c r="G3466" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3467">
@@ -94023,7 +94023,7 @@
         <v>10</v>
       </c>
       <c r="C3467" t="n">
-        <v>20.33</v>
+        <v>18.68</v>
       </c>
       <c r="D3467" t="inlineStr">
         <is>
@@ -94039,7 +94039,7 @@
         <v>3</v>
       </c>
       <c r="G3467" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3468">
@@ -94050,7 +94050,7 @@
         <v>11</v>
       </c>
       <c r="C3468" t="n">
-        <v>24.6</v>
+        <v>23.99</v>
       </c>
       <c r="D3468" t="inlineStr">
         <is>
@@ -94066,7 +94066,7 @@
         <v>3</v>
       </c>
       <c r="G3468" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3469">
@@ -94077,7 +94077,7 @@
         <v>12</v>
       </c>
       <c r="C3469" t="n">
-        <v>29.54</v>
+        <v>31.12</v>
       </c>
       <c r="D3469" t="inlineStr">
         <is>
@@ -94093,7 +94093,7 @@
         <v>3</v>
       </c>
       <c r="G3469" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3470">
@@ -94104,7 +94104,7 @@
         <v>13</v>
       </c>
       <c r="C3470" t="n">
-        <v>34.33</v>
+        <v>33.94</v>
       </c>
       <c r="D3470" t="inlineStr">
         <is>
@@ -94120,7 +94120,7 @@
         <v>3</v>
       </c>
       <c r="G3470" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3471">
@@ -94131,7 +94131,7 @@
         <v>14</v>
       </c>
       <c r="C3471" t="n">
-        <v>27.94</v>
+        <v>28.25</v>
       </c>
       <c r="D3471" t="inlineStr">
         <is>
@@ -94147,7 +94147,7 @@
         <v>3</v>
       </c>
       <c r="G3471" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3472">
@@ -94158,7 +94158,7 @@
         <v>15</v>
       </c>
       <c r="C3472" t="n">
-        <v>30.26</v>
+        <v>29.81</v>
       </c>
       <c r="D3472" t="inlineStr">
         <is>
@@ -94174,7 +94174,7 @@
         <v>3</v>
       </c>
       <c r="G3472" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3473">
@@ -94185,7 +94185,7 @@
         <v>16</v>
       </c>
       <c r="C3473" t="n">
-        <v>30.91</v>
+        <v>33.16</v>
       </c>
       <c r="D3473" t="inlineStr">
         <is>
@@ -94201,7 +94201,7 @@
         <v>3</v>
       </c>
       <c r="G3473" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3474">
@@ -94212,7 +94212,7 @@
         <v>17</v>
       </c>
       <c r="C3474" t="n">
-        <v>19.19</v>
+        <v>19.75</v>
       </c>
       <c r="D3474" t="inlineStr">
         <is>
@@ -94228,7 +94228,7 @@
         <v>3</v>
       </c>
       <c r="G3474" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3475">
@@ -94239,7 +94239,7 @@
         <v>18</v>
       </c>
       <c r="C3475" t="n">
-        <v>30.89</v>
+        <v>31.1</v>
       </c>
       <c r="D3475" t="inlineStr">
         <is>
@@ -94255,7 +94255,7 @@
         <v>3</v>
       </c>
       <c r="G3475" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3476">
@@ -94266,7 +94266,7 @@
         <v>19</v>
       </c>
       <c r="C3476" t="n">
-        <v>23.42</v>
+        <v>23.54</v>
       </c>
       <c r="D3476" t="inlineStr">
         <is>
@@ -94282,7 +94282,7 @@
         <v>3</v>
       </c>
       <c r="G3476" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3477">
@@ -94293,7 +94293,7 @@
         <v>20</v>
       </c>
       <c r="C3477" t="n">
-        <v>14.01</v>
+        <v>17.81</v>
       </c>
       <c r="D3477" t="inlineStr">
         <is>
@@ -94309,7 +94309,7 @@
         <v>3</v>
       </c>
       <c r="G3477" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3478">
@@ -94320,7 +94320,7 @@
         <v>21</v>
       </c>
       <c r="C3478" t="n">
-        <v>26.19</v>
+        <v>32.19</v>
       </c>
       <c r="D3478" t="inlineStr">
         <is>
@@ -94336,7 +94336,7 @@
         <v>3</v>
       </c>
       <c r="G3478" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3479">
@@ -94347,7 +94347,7 @@
         <v>22</v>
       </c>
       <c r="C3479" t="n">
-        <v>29.63</v>
+        <v>35.95</v>
       </c>
       <c r="D3479" t="inlineStr">
         <is>
@@ -94363,7 +94363,7 @@
         <v>3</v>
       </c>
       <c r="G3479" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3480">
@@ -94374,7 +94374,7 @@
         <v>23</v>
       </c>
       <c r="C3480" t="n">
-        <v>32.11</v>
+        <v>37.79</v>
       </c>
       <c r="D3480" t="inlineStr">
         <is>
@@ -94390,7 +94390,7 @@
         <v>3</v>
       </c>
       <c r="G3480" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3481">
@@ -94401,7 +94401,7 @@
         <v>24</v>
       </c>
       <c r="C3481" t="n">
-        <v>34.03</v>
+        <v>35.62</v>
       </c>
       <c r="D3481" t="inlineStr">
         <is>
@@ -94417,7 +94417,7 @@
         <v>3</v>
       </c>
       <c r="G3481" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3482">
@@ -94428,7 +94428,7 @@
         <v>1</v>
       </c>
       <c r="C3482" t="n">
-        <v>13.37</v>
+        <v>12.55</v>
       </c>
       <c r="D3482" t="inlineStr">
         <is>
@@ -94444,7 +94444,7 @@
         <v>3</v>
       </c>
       <c r="G3482" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3483">
@@ -94455,7 +94455,7 @@
         <v>2</v>
       </c>
       <c r="C3483" t="n">
-        <v>9.49</v>
+        <v>8</v>
       </c>
       <c r="D3483" t="inlineStr">
         <is>
@@ -94471,7 +94471,7 @@
         <v>3</v>
       </c>
       <c r="G3483" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3484">
@@ -94482,7 +94482,7 @@
         <v>3</v>
       </c>
       <c r="C3484" t="n">
-        <v>10.13</v>
+        <v>9.4</v>
       </c>
       <c r="D3484" t="inlineStr">
         <is>
@@ -94498,7 +94498,7 @@
         <v>3</v>
       </c>
       <c r="G3484" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3485">
@@ -94509,7 +94509,7 @@
         <v>4</v>
       </c>
       <c r="C3485" t="n">
-        <v>10.22</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="D3485" t="inlineStr">
         <is>
@@ -94525,7 +94525,7 @@
         <v>3</v>
       </c>
       <c r="G3485" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3486">
@@ -94536,7 +94536,7 @@
         <v>5</v>
       </c>
       <c r="C3486" t="n">
-        <v>10.63</v>
+        <v>8.06</v>
       </c>
       <c r="D3486" t="inlineStr">
         <is>
@@ -94552,7 +94552,7 @@
         <v>3</v>
       </c>
       <c r="G3486" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3487">
@@ -94563,7 +94563,7 @@
         <v>6</v>
       </c>
       <c r="C3487" t="n">
-        <v>10.75</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="D3487" t="inlineStr">
         <is>
@@ -94579,7 +94579,7 @@
         <v>3</v>
       </c>
       <c r="G3487" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3488">
@@ -94590,7 +94590,7 @@
         <v>7</v>
       </c>
       <c r="C3488" t="n">
-        <v>20.71</v>
+        <v>20.59</v>
       </c>
       <c r="D3488" t="inlineStr">
         <is>
@@ -94606,7 +94606,7 @@
         <v>3</v>
       </c>
       <c r="G3488" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3489">
@@ -94617,7 +94617,7 @@
         <v>8</v>
       </c>
       <c r="C3489" t="n">
-        <v>48.04</v>
+        <v>37.23</v>
       </c>
       <c r="D3489" t="inlineStr">
         <is>
@@ -94633,7 +94633,7 @@
         <v>3</v>
       </c>
       <c r="G3489" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3490">
@@ -94644,7 +94644,7 @@
         <v>9</v>
       </c>
       <c r="C3490" t="n">
-        <v>43.81</v>
+        <v>35.55</v>
       </c>
       <c r="D3490" t="inlineStr">
         <is>
@@ -94660,7 +94660,7 @@
         <v>3</v>
       </c>
       <c r="G3490" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3491">
@@ -94671,7 +94671,7 @@
         <v>10</v>
       </c>
       <c r="C3491" t="n">
-        <v>27.52</v>
+        <v>27.57</v>
       </c>
       <c r="D3491" t="inlineStr">
         <is>
@@ -94687,7 +94687,7 @@
         <v>3</v>
       </c>
       <c r="G3491" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3492">
@@ -94698,7 +94698,7 @@
         <v>11</v>
       </c>
       <c r="C3492" t="n">
-        <v>21.37</v>
+        <v>24.04</v>
       </c>
       <c r="D3492" t="inlineStr">
         <is>
@@ -94714,7 +94714,7 @@
         <v>3</v>
       </c>
       <c r="G3492" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3493">
@@ -94725,7 +94725,7 @@
         <v>12</v>
       </c>
       <c r="C3493" t="n">
-        <v>29.92</v>
+        <v>33.81</v>
       </c>
       <c r="D3493" t="inlineStr">
         <is>
@@ -94741,7 +94741,7 @@
         <v>3</v>
       </c>
       <c r="G3493" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3494">
@@ -94752,7 +94752,7 @@
         <v>13</v>
       </c>
       <c r="C3494" t="n">
-        <v>31.28</v>
+        <v>36.63</v>
       </c>
       <c r="D3494" t="inlineStr">
         <is>
@@ -94768,7 +94768,7 @@
         <v>3</v>
       </c>
       <c r="G3494" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3495">
@@ -94779,7 +94779,7 @@
         <v>14</v>
       </c>
       <c r="C3495" t="n">
-        <v>30.31</v>
+        <v>36.54</v>
       </c>
       <c r="D3495" t="inlineStr">
         <is>
@@ -94795,7 +94795,7 @@
         <v>3</v>
       </c>
       <c r="G3495" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3496">
@@ -94806,7 +94806,7 @@
         <v>15</v>
       </c>
       <c r="C3496" t="n">
-        <v>33.11</v>
+        <v>36.09</v>
       </c>
       <c r="D3496" t="inlineStr">
         <is>
@@ -94822,7 +94822,7 @@
         <v>3</v>
       </c>
       <c r="G3496" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3497">
@@ -94833,7 +94833,7 @@
         <v>16</v>
       </c>
       <c r="C3497" t="n">
-        <v>32.28</v>
+        <v>30.38</v>
       </c>
       <c r="D3497" t="inlineStr">
         <is>
@@ -94849,7 +94849,7 @@
         <v>3</v>
       </c>
       <c r="G3497" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3498">
@@ -94860,7 +94860,7 @@
         <v>17</v>
       </c>
       <c r="C3498" t="n">
-        <v>29.98</v>
+        <v>32.25</v>
       </c>
       <c r="D3498" t="inlineStr">
         <is>
@@ -94876,7 +94876,7 @@
         <v>3</v>
       </c>
       <c r="G3498" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3499">
@@ -94887,7 +94887,7 @@
         <v>18</v>
       </c>
       <c r="C3499" t="n">
-        <v>25.91</v>
+        <v>25.99</v>
       </c>
       <c r="D3499" t="inlineStr">
         <is>
@@ -94903,7 +94903,7 @@
         <v>3</v>
       </c>
       <c r="G3499" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3500">
@@ -94914,7 +94914,7 @@
         <v>19</v>
       </c>
       <c r="C3500" t="n">
-        <v>32.08</v>
+        <v>33.47</v>
       </c>
       <c r="D3500" t="inlineStr">
         <is>
@@ -94930,7 +94930,7 @@
         <v>3</v>
       </c>
       <c r="G3500" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3501">
@@ -94941,7 +94941,7 @@
         <v>20</v>
       </c>
       <c r="C3501" t="n">
-        <v>34.7</v>
+        <v>34.15</v>
       </c>
       <c r="D3501" t="inlineStr">
         <is>
@@ -94957,7 +94957,7 @@
         <v>3</v>
       </c>
       <c r="G3501" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3502">
@@ -94968,7 +94968,7 @@
         <v>21</v>
       </c>
       <c r="C3502" t="n">
-        <v>38.26</v>
+        <v>31.86</v>
       </c>
       <c r="D3502" t="inlineStr">
         <is>
@@ -94984,7 +94984,7 @@
         <v>3</v>
       </c>
       <c r="G3502" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3503">
@@ -94995,7 +94995,7 @@
         <v>22</v>
       </c>
       <c r="C3503" t="n">
-        <v>41.07</v>
+        <v>34.68</v>
       </c>
       <c r="D3503" t="inlineStr">
         <is>
@@ -95011,7 +95011,7 @@
         <v>3</v>
       </c>
       <c r="G3503" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3504">
@@ -95022,7 +95022,7 @@
         <v>23</v>
       </c>
       <c r="C3504" t="n">
-        <v>46.33</v>
+        <v>37.93</v>
       </c>
       <c r="D3504" t="inlineStr">
         <is>
@@ -95038,7 +95038,7 @@
         <v>3</v>
       </c>
       <c r="G3504" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
       </c>
     </row>
     <row r="3505">
@@ -95049,7 +95049,7 @@
         <v>24</v>
       </c>
       <c r="C3505" t="n">
-        <v>26.51</v>
+        <v>26.61</v>
       </c>
       <c r="D3505" t="inlineStr">
         <is>
@@ -95065,7 +95065,655 @@
         <v>3</v>
       </c>
       <c r="G3505" s="2" t="n">
-        <v>46289.46728715212</v>
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3506">
+      <c r="A3506" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3506" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3506" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="D3506" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3506" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3506" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3506" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3507">
+      <c r="A3507" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3507" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3507" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="D3507" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3507" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3507" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3507" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3508">
+      <c r="A3508" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3508" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3508" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="D3508" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3508" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3508" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3508" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3509">
+      <c r="A3509" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3509" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3509" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="D3509" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3509" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3509" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3509" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3510">
+      <c r="A3510" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3510" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3510" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="D3510" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3510" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3510" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3510" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3511">
+      <c r="A3511" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3511" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3511" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="D3511" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3511" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3511" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3511" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3512">
+      <c r="A3512" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3512" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3512" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="D3512" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3512" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3512" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3512" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3513">
+      <c r="A3513" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3513" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3513" t="n">
+        <v>40.86</v>
+      </c>
+      <c r="D3513" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3513" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3513" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3513" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3514">
+      <c r="A3514" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3514" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3514" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="D3514" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3514" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3514" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3514" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3515">
+      <c r="A3515" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3515" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3515" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="D3515" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3515" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3515" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3515" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3516">
+      <c r="A3516" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3516" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3516" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="D3516" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3516" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3516" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3516" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3517">
+      <c r="A3517" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3517" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3517" t="n">
+        <v>31.67</v>
+      </c>
+      <c r="D3517" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3517" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3517" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3517" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3518">
+      <c r="A3518" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3518" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3518" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="D3518" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3518" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3518" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3518" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3519">
+      <c r="A3519" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3519" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3519" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="D3519" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3519" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3519" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3519" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3520">
+      <c r="A3520" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3520" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3520" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="D3520" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3520" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3520" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3520" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3521">
+      <c r="A3521" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3521" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3521" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="D3521" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3521" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3521" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3521" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3522">
+      <c r="A3522" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3522" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3522" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="D3522" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3522" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3522" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3522" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3523">
+      <c r="A3523" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3523" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3523" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="D3523" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3523" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3523" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3523" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3524">
+      <c r="A3524" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3524" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3524" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="D3524" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3524" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3524" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3524" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3525">
+      <c r="A3525" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3525" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3525" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="D3525" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3525" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3525" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3525" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3526">
+      <c r="A3526" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3526" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3526" t="n">
+        <v>44.59</v>
+      </c>
+      <c r="D3526" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3526" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3526" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3526" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3527">
+      <c r="A3527" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3527" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3527" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="D3527" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3527" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3527" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3527" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3528">
+      <c r="A3528" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3528" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3528" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="D3528" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3528" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3528" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3528" s="2" t="n">
+        <v>46289.88433801506</v>
+      </c>
+    </row>
+    <row r="3529">
+      <c r="A3529" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3529" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3529" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="D3529" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3529" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3529" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3529" s="2" t="n">
+        <v>46289.88433801506</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3324">
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3333">
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3335">
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3337">
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3341">
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3343">
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3344">
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3345">
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3346">
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3347">
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3355">
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3356">
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3357">
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3360">
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3362">
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3364">
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3365">
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3366">
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3367">
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3368">
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3369">
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3370">
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3371">
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3372">
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3373">
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3374">
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3375">
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3376">
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3377">
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3378">
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3379">
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3380">
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3381">
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3382">
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3383">
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3384">
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3385">
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3386">
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3387">
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3388">
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3389">
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3390">
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3391">
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3392">
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3393">
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3394">
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3395">
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3396">
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3397">
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3398">
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3399">
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3400">
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3401">
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3402">
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3403">
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3404">
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3405">
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3406">
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3407">
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3408">
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3409">
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3410">
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3411">
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3412">
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3413">
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3415">
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3416">
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3417">
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3418">
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3419">
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3420">
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3421">
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3422">
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3423">
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3424">
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3425">
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3426">
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3427">
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3428">
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3429">
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3430">
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3431">
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3432">
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3433">
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3434">
@@ -93148,7 +93148,7 @@
         <v>3</v>
       </c>
       <c r="G3434" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3435">
@@ -93175,7 +93175,7 @@
         <v>3</v>
       </c>
       <c r="G3435" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3436">
@@ -93202,7 +93202,7 @@
         <v>3</v>
       </c>
       <c r="G3436" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3437">
@@ -93229,7 +93229,7 @@
         <v>3</v>
       </c>
       <c r="G3437" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3438">
@@ -93256,7 +93256,7 @@
         <v>3</v>
       </c>
       <c r="G3438" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3439">
@@ -93283,7 +93283,7 @@
         <v>3</v>
       </c>
       <c r="G3439" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3440">
@@ -93310,7 +93310,7 @@
         <v>3</v>
       </c>
       <c r="G3440" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3441">
@@ -93337,7 +93337,7 @@
         <v>3</v>
       </c>
       <c r="G3441" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3442">
@@ -93364,7 +93364,7 @@
         <v>3</v>
       </c>
       <c r="G3442" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3443">
@@ -93391,7 +93391,7 @@
         <v>3</v>
       </c>
       <c r="G3443" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3444">
@@ -93418,7 +93418,7 @@
         <v>3</v>
       </c>
       <c r="G3444" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3445">
@@ -93445,7 +93445,7 @@
         <v>3</v>
       </c>
       <c r="G3445" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3446">
@@ -93472,7 +93472,7 @@
         <v>3</v>
       </c>
       <c r="G3446" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3447">
@@ -93499,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="G3447" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3448">
@@ -93526,7 +93526,7 @@
         <v>3</v>
       </c>
       <c r="G3448" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3449">
@@ -93553,7 +93553,7 @@
         <v>3</v>
       </c>
       <c r="G3449" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3450">
@@ -93580,7 +93580,7 @@
         <v>3</v>
       </c>
       <c r="G3450" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3451">
@@ -93607,7 +93607,7 @@
         <v>3</v>
       </c>
       <c r="G3451" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3452">
@@ -93634,7 +93634,7 @@
         <v>3</v>
       </c>
       <c r="G3452" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3453">
@@ -93661,7 +93661,7 @@
         <v>3</v>
       </c>
       <c r="G3453" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3454">
@@ -93688,7 +93688,7 @@
         <v>3</v>
       </c>
       <c r="G3454" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3455">
@@ -93715,7 +93715,7 @@
         <v>3</v>
       </c>
       <c r="G3455" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3456">
@@ -93742,7 +93742,7 @@
         <v>3</v>
       </c>
       <c r="G3456" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3457">
@@ -93769,7 +93769,7 @@
         <v>3</v>
       </c>
       <c r="G3457" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3458">
@@ -93796,7 +93796,7 @@
         <v>3</v>
       </c>
       <c r="G3458" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3459">
@@ -93823,7 +93823,7 @@
         <v>3</v>
       </c>
       <c r="G3459" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3460">
@@ -93850,7 +93850,7 @@
         <v>3</v>
       </c>
       <c r="G3460" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3461">
@@ -93877,7 +93877,7 @@
         <v>3</v>
       </c>
       <c r="G3461" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3462">
@@ -93904,7 +93904,7 @@
         <v>3</v>
       </c>
       <c r="G3462" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3463">
@@ -93931,7 +93931,7 @@
         <v>3</v>
       </c>
       <c r="G3463" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3464">
@@ -93958,7 +93958,7 @@
         <v>3</v>
       </c>
       <c r="G3464" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3465">
@@ -93985,7 +93985,7 @@
         <v>3</v>
       </c>
       <c r="G3465" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3466">
@@ -94012,7 +94012,7 @@
         <v>3</v>
       </c>
       <c r="G3466" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3467">
@@ -94039,7 +94039,7 @@
         <v>3</v>
       </c>
       <c r="G3467" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3468">
@@ -94066,7 +94066,7 @@
         <v>3</v>
       </c>
       <c r="G3468" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3469">
@@ -94093,7 +94093,7 @@
         <v>3</v>
       </c>
       <c r="G3469" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3470">
@@ -94120,7 +94120,7 @@
         <v>3</v>
       </c>
       <c r="G3470" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3471">
@@ -94147,7 +94147,7 @@
         <v>3</v>
       </c>
       <c r="G3471" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3472">
@@ -94174,7 +94174,7 @@
         <v>3</v>
       </c>
       <c r="G3472" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3473">
@@ -94201,7 +94201,7 @@
         <v>3</v>
       </c>
       <c r="G3473" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3474">
@@ -94228,7 +94228,7 @@
         <v>3</v>
       </c>
       <c r="G3474" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3475">
@@ -94255,7 +94255,7 @@
         <v>3</v>
       </c>
       <c r="G3475" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3476">
@@ -94282,7 +94282,7 @@
         <v>3</v>
       </c>
       <c r="G3476" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3477">
@@ -94309,7 +94309,7 @@
         <v>3</v>
       </c>
       <c r="G3477" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3478">
@@ -94336,7 +94336,7 @@
         <v>3</v>
       </c>
       <c r="G3478" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3479">
@@ -94363,7 +94363,7 @@
         <v>3</v>
       </c>
       <c r="G3479" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3480">
@@ -94390,7 +94390,7 @@
         <v>3</v>
       </c>
       <c r="G3480" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3481">
@@ -94417,7 +94417,7 @@
         <v>3</v>
       </c>
       <c r="G3481" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3482">
@@ -94444,7 +94444,7 @@
         <v>3</v>
       </c>
       <c r="G3482" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3483">
@@ -94471,7 +94471,7 @@
         <v>3</v>
       </c>
       <c r="G3483" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3484">
@@ -94498,7 +94498,7 @@
         <v>3</v>
       </c>
       <c r="G3484" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3485">
@@ -94525,7 +94525,7 @@
         <v>3</v>
       </c>
       <c r="G3485" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3486">
@@ -94552,7 +94552,7 @@
         <v>3</v>
       </c>
       <c r="G3486" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3487">
@@ -94579,7 +94579,7 @@
         <v>3</v>
       </c>
       <c r="G3487" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3488">
@@ -94606,7 +94606,7 @@
         <v>3</v>
       </c>
       <c r="G3488" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3489">
@@ -94633,7 +94633,7 @@
         <v>3</v>
       </c>
       <c r="G3489" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3490">
@@ -94660,7 +94660,7 @@
         <v>3</v>
       </c>
       <c r="G3490" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3491">
@@ -94687,7 +94687,7 @@
         <v>3</v>
       </c>
       <c r="G3491" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3492">
@@ -94714,7 +94714,7 @@
         <v>3</v>
       </c>
       <c r="G3492" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3493">
@@ -94741,7 +94741,7 @@
         <v>3</v>
       </c>
       <c r="G3493" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3494">
@@ -94768,7 +94768,7 @@
         <v>3</v>
       </c>
       <c r="G3494" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3495">
@@ -94795,7 +94795,7 @@
         <v>3</v>
       </c>
       <c r="G3495" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3496">
@@ -94822,7 +94822,7 @@
         <v>3</v>
       </c>
       <c r="G3496" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3497">
@@ -94849,7 +94849,7 @@
         <v>3</v>
       </c>
       <c r="G3497" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3498">
@@ -94876,7 +94876,7 @@
         <v>3</v>
       </c>
       <c r="G3498" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3499">
@@ -94903,7 +94903,7 @@
         <v>3</v>
       </c>
       <c r="G3499" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3500">
@@ -94930,7 +94930,7 @@
         <v>3</v>
       </c>
       <c r="G3500" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3501">
@@ -94957,7 +94957,7 @@
         <v>3</v>
       </c>
       <c r="G3501" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3502">
@@ -94984,7 +94984,7 @@
         <v>3</v>
       </c>
       <c r="G3502" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3503">
@@ -95011,7 +95011,7 @@
         <v>3</v>
       </c>
       <c r="G3503" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3504">
@@ -95038,7 +95038,7 @@
         <v>3</v>
       </c>
       <c r="G3504" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3505">
@@ -95065,7 +95065,7 @@
         <v>3</v>
       </c>
       <c r="G3505" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3506">
@@ -95092,7 +95092,7 @@
         <v>3</v>
       </c>
       <c r="G3506" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3507">
@@ -95119,7 +95119,7 @@
         <v>3</v>
       </c>
       <c r="G3507" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3508">
@@ -95146,7 +95146,7 @@
         <v>3</v>
       </c>
       <c r="G3508" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3509">
@@ -95173,7 +95173,7 @@
         <v>3</v>
       </c>
       <c r="G3509" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3510">
@@ -95200,7 +95200,7 @@
         <v>3</v>
       </c>
       <c r="G3510" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3511">
@@ -95227,7 +95227,7 @@
         <v>3</v>
       </c>
       <c r="G3511" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3512">
@@ -95254,7 +95254,7 @@
         <v>3</v>
       </c>
       <c r="G3512" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3513">
@@ -95281,7 +95281,7 @@
         <v>3</v>
       </c>
       <c r="G3513" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3514">
@@ -95308,7 +95308,7 @@
         <v>3</v>
       </c>
       <c r="G3514" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3515">
@@ -95335,7 +95335,7 @@
         <v>3</v>
       </c>
       <c r="G3515" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3516">
@@ -95362,7 +95362,7 @@
         <v>3</v>
       </c>
       <c r="G3516" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3517">
@@ -95389,7 +95389,7 @@
         <v>3</v>
       </c>
       <c r="G3517" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3518">
@@ -95416,7 +95416,7 @@
         <v>3</v>
       </c>
       <c r="G3518" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3519">
@@ -95443,7 +95443,7 @@
         <v>3</v>
       </c>
       <c r="G3519" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3520">
@@ -95470,7 +95470,7 @@
         <v>3</v>
       </c>
       <c r="G3520" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3521">
@@ -95497,7 +95497,7 @@
         <v>3</v>
       </c>
       <c r="G3521" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3522">
@@ -95524,7 +95524,7 @@
         <v>3</v>
       </c>
       <c r="G3522" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3523">
@@ -95551,7 +95551,7 @@
         <v>3</v>
       </c>
       <c r="G3523" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3524">
@@ -95578,7 +95578,7 @@
         <v>3</v>
       </c>
       <c r="G3524" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3525">
@@ -95605,7 +95605,7 @@
         <v>3</v>
       </c>
       <c r="G3525" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3526">
@@ -95632,7 +95632,7 @@
         <v>3</v>
       </c>
       <c r="G3526" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3527">
@@ -95659,7 +95659,7 @@
         <v>3</v>
       </c>
       <c r="G3527" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3528">
@@ -95686,7 +95686,7 @@
         <v>3</v>
       </c>
       <c r="G3528" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
     <row r="3529">
@@ -95713,7 +95713,7 @@
         <v>3</v>
       </c>
       <c r="G3529" s="2" t="n">
-        <v>46289.88433801506</v>
+        <v>46290.47009576231</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3529"/>
+  <dimension ref="A1:G3553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3316">
@@ -89946,7 +89946,7 @@
         <v>3</v>
       </c>
       <c r="C3316" t="n">
-        <v>12.1</v>
+        <v>12.09</v>
       </c>
       <c r="D3316" t="inlineStr">
         <is>
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3317">
@@ -89973,7 +89973,7 @@
         <v>4</v>
       </c>
       <c r="C3317" t="n">
-        <v>13.48</v>
+        <v>13.47</v>
       </c>
       <c r="D3317" t="inlineStr">
         <is>
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3319">
@@ -90027,7 +90027,7 @@
         <v>6</v>
       </c>
       <c r="C3319" t="n">
-        <v>11.57</v>
+        <v>11.56</v>
       </c>
       <c r="D3319" t="inlineStr">
         <is>
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3324">
@@ -90162,7 +90162,7 @@
         <v>11</v>
       </c>
       <c r="C3324" t="n">
-        <v>26.78</v>
+        <v>26.77</v>
       </c>
       <c r="D3324" t="inlineStr">
         <is>
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3325">
@@ -90189,7 +90189,7 @@
         <v>12</v>
       </c>
       <c r="C3325" t="n">
-        <v>32.23</v>
+        <v>32.22</v>
       </c>
       <c r="D3325" t="inlineStr">
         <is>
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3326">
@@ -90216,7 +90216,7 @@
         <v>13</v>
       </c>
       <c r="C3326" t="n">
-        <v>31.88</v>
+        <v>31.87</v>
       </c>
       <c r="D3326" t="inlineStr">
         <is>
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3327">
@@ -90243,7 +90243,7 @@
         <v>14</v>
       </c>
       <c r="C3327" t="n">
-        <v>32.53</v>
+        <v>32.52</v>
       </c>
       <c r="D3327" t="inlineStr">
         <is>
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3328">
@@ -90270,7 +90270,7 @@
         <v>15</v>
       </c>
       <c r="C3328" t="n">
-        <v>33.11</v>
+        <v>33.1</v>
       </c>
       <c r="D3328" t="inlineStr">
         <is>
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3329">
@@ -90297,7 +90297,7 @@
         <v>16</v>
       </c>
       <c r="C3329" t="n">
-        <v>33</v>
+        <v>32.99</v>
       </c>
       <c r="D3329" t="inlineStr">
         <is>
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3330">
@@ -90324,7 +90324,7 @@
         <v>17</v>
       </c>
       <c r="C3330" t="n">
-        <v>31.79</v>
+        <v>31.78</v>
       </c>
       <c r="D3330" t="inlineStr">
         <is>
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3332">
@@ -90378,7 +90378,7 @@
         <v>19</v>
       </c>
       <c r="C3332" t="n">
-        <v>31.34</v>
+        <v>31.32</v>
       </c>
       <c r="D3332" t="inlineStr">
         <is>
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3333">
@@ -90405,7 +90405,7 @@
         <v>20</v>
       </c>
       <c r="C3333" t="n">
-        <v>24.39</v>
+        <v>24.38</v>
       </c>
       <c r="D3333" t="inlineStr">
         <is>
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3334">
@@ -90432,7 +90432,7 @@
         <v>21</v>
       </c>
       <c r="C3334" t="n">
-        <v>34.04</v>
+        <v>34.03</v>
       </c>
       <c r="D3334" t="inlineStr">
         <is>
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3335">
@@ -90459,7 +90459,7 @@
         <v>22</v>
       </c>
       <c r="C3335" t="n">
-        <v>33.45</v>
+        <v>33.44</v>
       </c>
       <c r="D3335" t="inlineStr">
         <is>
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3337">
@@ -90513,7 +90513,7 @@
         <v>24</v>
       </c>
       <c r="C3337" t="n">
-        <v>23.28</v>
+        <v>23.29</v>
       </c>
       <c r="D3337" t="inlineStr">
         <is>
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3338">
@@ -90540,7 +90540,7 @@
         <v>1</v>
       </c>
       <c r="C3338" t="n">
-        <v>10.59</v>
+        <v>10.64</v>
       </c>
       <c r="D3338" t="inlineStr">
         <is>
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3339">
@@ -90567,7 +90567,7 @@
         <v>2</v>
       </c>
       <c r="C3339" t="n">
-        <v>13.64</v>
+        <v>13.67</v>
       </c>
       <c r="D3339" t="inlineStr">
         <is>
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3340">
@@ -90594,7 +90594,7 @@
         <v>3</v>
       </c>
       <c r="C3340" t="n">
-        <v>15.9</v>
+        <v>15.95</v>
       </c>
       <c r="D3340" t="inlineStr">
         <is>
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3341">
@@ -90621,7 +90621,7 @@
         <v>4</v>
       </c>
       <c r="C3341" t="n">
-        <v>17.95</v>
+        <v>17.99</v>
       </c>
       <c r="D3341" t="inlineStr">
         <is>
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3342">
@@ -90648,7 +90648,7 @@
         <v>5</v>
       </c>
       <c r="C3342" t="n">
-        <v>17.06</v>
+        <v>17.11</v>
       </c>
       <c r="D3342" t="inlineStr">
         <is>
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3343">
@@ -90675,7 +90675,7 @@
         <v>6</v>
       </c>
       <c r="C3343" t="n">
-        <v>15.96</v>
+        <v>16.01</v>
       </c>
       <c r="D3343" t="inlineStr">
         <is>
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3344">
@@ -90702,7 +90702,7 @@
         <v>7</v>
       </c>
       <c r="C3344" t="n">
-        <v>20.01</v>
+        <v>20.02</v>
       </c>
       <c r="D3344" t="inlineStr">
         <is>
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3345">
@@ -90729,7 +90729,7 @@
         <v>8</v>
       </c>
       <c r="C3345" t="n">
-        <v>43.4</v>
+        <v>43.38</v>
       </c>
       <c r="D3345" t="inlineStr">
         <is>
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3346">
@@ -90756,7 +90756,7 @@
         <v>9</v>
       </c>
       <c r="C3346" t="n">
-        <v>44.01</v>
+        <v>44</v>
       </c>
       <c r="D3346" t="inlineStr">
         <is>
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3347">
@@ -90783,7 +90783,7 @@
         <v>10</v>
       </c>
       <c r="C3347" t="n">
-        <v>26.06</v>
+        <v>26.05</v>
       </c>
       <c r="D3347" t="inlineStr">
         <is>
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3348">
@@ -90810,7 +90810,7 @@
         <v>11</v>
       </c>
       <c r="C3348" t="n">
-        <v>21.8</v>
+        <v>21.79</v>
       </c>
       <c r="D3348" t="inlineStr">
         <is>
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3349">
@@ -90837,7 +90837,7 @@
         <v>12</v>
       </c>
       <c r="C3349" t="n">
-        <v>25.75</v>
+        <v>25.74</v>
       </c>
       <c r="D3349" t="inlineStr">
         <is>
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3350">
@@ -90864,7 +90864,7 @@
         <v>13</v>
       </c>
       <c r="C3350" t="n">
-        <v>23.78</v>
+        <v>23.77</v>
       </c>
       <c r="D3350" t="inlineStr">
         <is>
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3351">
@@ -90891,7 +90891,7 @@
         <v>14</v>
       </c>
       <c r="C3351" t="n">
-        <v>24.02</v>
+        <v>24.01</v>
       </c>
       <c r="D3351" t="inlineStr">
         <is>
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3352">
@@ -90918,7 +90918,7 @@
         <v>15</v>
       </c>
       <c r="C3352" t="n">
-        <v>24.21</v>
+        <v>24.2</v>
       </c>
       <c r="D3352" t="inlineStr">
         <is>
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3353">
@@ -90945,7 +90945,7 @@
         <v>16</v>
       </c>
       <c r="C3353" t="n">
-        <v>24.36</v>
+        <v>24.35</v>
       </c>
       <c r="D3353" t="inlineStr">
         <is>
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3355">
@@ -90999,7 +90999,7 @@
         <v>18</v>
       </c>
       <c r="C3355" t="n">
-        <v>20.93</v>
+        <v>20.92</v>
       </c>
       <c r="D3355" t="inlineStr">
         <is>
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3356">
@@ -91026,7 +91026,7 @@
         <v>19</v>
       </c>
       <c r="C3356" t="n">
-        <v>17.37</v>
+        <v>17.39</v>
       </c>
       <c r="D3356" t="inlineStr">
         <is>
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3357">
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3358">
@@ -91080,7 +91080,7 @@
         <v>21</v>
       </c>
       <c r="C3358" t="n">
-        <v>36.33</v>
+        <v>36.32</v>
       </c>
       <c r="D3358" t="inlineStr">
         <is>
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3360">
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3361">
@@ -91161,7 +91161,7 @@
         <v>24</v>
       </c>
       <c r="C3361" t="n">
-        <v>23.94</v>
+        <v>23.93</v>
       </c>
       <c r="D3361" t="inlineStr">
         <is>
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3362">
@@ -91188,7 +91188,7 @@
         <v>1</v>
       </c>
       <c r="C3362" t="n">
-        <v>11.74</v>
+        <v>11.73</v>
       </c>
       <c r="D3362" t="inlineStr">
         <is>
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3364">
@@ -91242,7 +91242,7 @@
         <v>3</v>
       </c>
       <c r="C3364" t="n">
-        <v>13.61</v>
+        <v>13.6</v>
       </c>
       <c r="D3364" t="inlineStr">
         <is>
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3365">
@@ -91269,7 +91269,7 @@
         <v>4</v>
       </c>
       <c r="C3365" t="n">
-        <v>12.96</v>
+        <v>12.97</v>
       </c>
       <c r="D3365" t="inlineStr">
         <is>
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3366">
@@ -91296,7 +91296,7 @@
         <v>5</v>
       </c>
       <c r="C3366" t="n">
-        <v>16.83</v>
+        <v>16.82</v>
       </c>
       <c r="D3366" t="inlineStr">
         <is>
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3367">
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3368">
@@ -91350,7 +91350,7 @@
         <v>7</v>
       </c>
       <c r="C3368" t="n">
-        <v>16.32</v>
+        <v>16.31</v>
       </c>
       <c r="D3368" t="inlineStr">
         <is>
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3369">
@@ -91377,7 +91377,7 @@
         <v>8</v>
       </c>
       <c r="C3369" t="n">
-        <v>43.85</v>
+        <v>43.84</v>
       </c>
       <c r="D3369" t="inlineStr">
         <is>
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3370">
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3371">
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3372">
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3373">
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3374">
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3375">
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3376">
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3377">
@@ -91593,7 +91593,7 @@
         <v>16</v>
       </c>
       <c r="C3377" t="n">
-        <v>25.47</v>
+        <v>25.48</v>
       </c>
       <c r="D3377" t="inlineStr">
         <is>
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3378">
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3379">
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3380">
@@ -91674,7 +91674,7 @@
         <v>19</v>
       </c>
       <c r="C3380" t="n">
-        <v>20.61</v>
+        <v>20.62</v>
       </c>
       <c r="D3380" t="inlineStr">
         <is>
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3381">
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3382">
@@ -91728,7 +91728,7 @@
         <v>21</v>
       </c>
       <c r="C3382" t="n">
-        <v>45.37</v>
+        <v>45.36</v>
       </c>
       <c r="D3382" t="inlineStr">
         <is>
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3383">
@@ -91755,7 +91755,7 @@
         <v>22</v>
       </c>
       <c r="C3383" t="n">
-        <v>47.86</v>
+        <v>47.85</v>
       </c>
       <c r="D3383" t="inlineStr">
         <is>
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3384">
@@ -91782,7 +91782,7 @@
         <v>23</v>
       </c>
       <c r="C3384" t="n">
-        <v>34.63</v>
+        <v>34.62</v>
       </c>
       <c r="D3384" t="inlineStr">
         <is>
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3385">
@@ -91809,7 +91809,7 @@
         <v>24</v>
       </c>
       <c r="C3385" t="n">
-        <v>24.97</v>
+        <v>24.96</v>
       </c>
       <c r="D3385" t="inlineStr">
         <is>
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3386">
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3387">
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3388">
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3389">
@@ -91917,7 +91917,7 @@
         <v>4</v>
       </c>
       <c r="C3389" t="n">
-        <v>15.23</v>
+        <v>15.24</v>
       </c>
       <c r="D3389" t="inlineStr">
         <is>
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3390">
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3391">
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3392">
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3393">
@@ -92025,7 +92025,7 @@
         <v>8</v>
       </c>
       <c r="C3393" t="n">
-        <v>37.58</v>
+        <v>37.57</v>
       </c>
       <c r="D3393" t="inlineStr">
         <is>
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3394">
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3395">
@@ -92079,7 +92079,7 @@
         <v>10</v>
       </c>
       <c r="C3395" t="n">
-        <v>19.69</v>
+        <v>19.7</v>
       </c>
       <c r="D3395" t="inlineStr">
         <is>
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3396">
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3397">
@@ -92133,7 +92133,7 @@
         <v>12</v>
       </c>
       <c r="C3397" t="n">
-        <v>22.92</v>
+        <v>22.91</v>
       </c>
       <c r="D3397" t="inlineStr">
         <is>
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3398">
@@ -92160,7 +92160,7 @@
         <v>13</v>
       </c>
       <c r="C3398" t="n">
-        <v>23.24</v>
+        <v>23.23</v>
       </c>
       <c r="D3398" t="inlineStr">
         <is>
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3399">
@@ -92187,7 +92187,7 @@
         <v>14</v>
       </c>
       <c r="C3399" t="n">
-        <v>22.79</v>
+        <v>22.78</v>
       </c>
       <c r="D3399" t="inlineStr">
         <is>
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3400">
@@ -92214,7 +92214,7 @@
         <v>15</v>
       </c>
       <c r="C3400" t="n">
-        <v>23.08</v>
+        <v>23.07</v>
       </c>
       <c r="D3400" t="inlineStr">
         <is>
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3401">
@@ -92241,7 +92241,7 @@
         <v>16</v>
       </c>
       <c r="C3401" t="n">
-        <v>23.78</v>
+        <v>23.77</v>
       </c>
       <c r="D3401" t="inlineStr">
         <is>
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3402">
@@ -92268,7 +92268,7 @@
         <v>17</v>
       </c>
       <c r="C3402" t="n">
-        <v>23.58</v>
+        <v>23.57</v>
       </c>
       <c r="D3402" t="inlineStr">
         <is>
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3403">
@@ -92295,7 +92295,7 @@
         <v>18</v>
       </c>
       <c r="C3403" t="n">
-        <v>22.28</v>
+        <v>22.36</v>
       </c>
       <c r="D3403" t="inlineStr">
         <is>
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3404">
@@ -92322,7 +92322,7 @@
         <v>19</v>
       </c>
       <c r="C3404" t="n">
-        <v>20.83</v>
+        <v>20.84</v>
       </c>
       <c r="D3404" t="inlineStr">
         <is>
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3405">
@@ -92349,7 +92349,7 @@
         <v>20</v>
       </c>
       <c r="C3405" t="n">
-        <v>24.84</v>
+        <v>24.85</v>
       </c>
       <c r="D3405" t="inlineStr">
         <is>
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3406">
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3407">
@@ -92403,7 +92403,7 @@
         <v>22</v>
       </c>
       <c r="C3407" t="n">
-        <v>38.62</v>
+        <v>38.61</v>
       </c>
       <c r="D3407" t="inlineStr">
         <is>
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3408">
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3409">
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3410">
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3411">
@@ -92511,7 +92511,7 @@
         <v>2</v>
       </c>
       <c r="C3411" t="n">
-        <v>16.88</v>
+        <v>16.87</v>
       </c>
       <c r="D3411" t="inlineStr">
         <is>
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3412">
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3413">
@@ -92565,7 +92565,7 @@
         <v>4</v>
       </c>
       <c r="C3413" t="n">
-        <v>13.19</v>
+        <v>13.21</v>
       </c>
       <c r="D3413" t="inlineStr">
         <is>
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3415">
@@ -92619,7 +92619,7 @@
         <v>6</v>
       </c>
       <c r="C3415" t="n">
-        <v>17.25</v>
+        <v>17.24</v>
       </c>
       <c r="D3415" t="inlineStr">
         <is>
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3416">
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3417">
@@ -92673,7 +92673,7 @@
         <v>8</v>
       </c>
       <c r="C3417" t="n">
-        <v>32.19</v>
+        <v>32.18</v>
       </c>
       <c r="D3417" t="inlineStr">
         <is>
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3418">
@@ -92700,7 +92700,7 @@
         <v>9</v>
       </c>
       <c r="C3418" t="n">
-        <v>45.46</v>
+        <v>45.49</v>
       </c>
       <c r="D3418" t="inlineStr">
         <is>
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3419">
@@ -92727,7 +92727,7 @@
         <v>10</v>
       </c>
       <c r="C3419" t="n">
-        <v>32.07</v>
+        <v>32.02</v>
       </c>
       <c r="D3419" t="inlineStr">
         <is>
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3420">
@@ -92754,7 +92754,7 @@
         <v>11</v>
       </c>
       <c r="C3420" t="n">
-        <v>25.97</v>
+        <v>25.93</v>
       </c>
       <c r="D3420" t="inlineStr">
         <is>
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3421">
@@ -92781,7 +92781,7 @@
         <v>12</v>
       </c>
       <c r="C3421" t="n">
-        <v>28.74</v>
+        <v>28.66</v>
       </c>
       <c r="D3421" t="inlineStr">
         <is>
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3422">
@@ -92808,7 +92808,7 @@
         <v>13</v>
       </c>
       <c r="C3422" t="n">
-        <v>31.87</v>
+        <v>31.76</v>
       </c>
       <c r="D3422" t="inlineStr">
         <is>
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3423">
@@ -92835,7 +92835,7 @@
         <v>14</v>
       </c>
       <c r="C3423" t="n">
-        <v>31.33</v>
+        <v>31.25</v>
       </c>
       <c r="D3423" t="inlineStr">
         <is>
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3424">
@@ -92862,7 +92862,7 @@
         <v>15</v>
       </c>
       <c r="C3424" t="n">
-        <v>31.33</v>
+        <v>31.21</v>
       </c>
       <c r="D3424" t="inlineStr">
         <is>
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3425">
@@ -92889,7 +92889,7 @@
         <v>16</v>
       </c>
       <c r="C3425" t="n">
-        <v>32.07</v>
+        <v>31.98</v>
       </c>
       <c r="D3425" t="inlineStr">
         <is>
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3426">
@@ -92916,7 +92916,7 @@
         <v>17</v>
       </c>
       <c r="C3426" t="n">
-        <v>31.46</v>
+        <v>31.41</v>
       </c>
       <c r="D3426" t="inlineStr">
         <is>
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3427">
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3428">
@@ -92970,7 +92970,7 @@
         <v>19</v>
       </c>
       <c r="C3428" t="n">
-        <v>26.37</v>
+        <v>26.38</v>
       </c>
       <c r="D3428" t="inlineStr">
         <is>
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3429">
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3430">
@@ -93024,7 +93024,7 @@
         <v>21</v>
       </c>
       <c r="C3430" t="n">
-        <v>36.42</v>
+        <v>36.4</v>
       </c>
       <c r="D3430" t="inlineStr">
         <is>
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3431">
@@ -93051,7 +93051,7 @@
         <v>22</v>
       </c>
       <c r="C3431" t="n">
-        <v>37.23</v>
+        <v>37.21</v>
       </c>
       <c r="D3431" t="inlineStr">
         <is>
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3432">
@@ -93078,7 +93078,7 @@
         <v>23</v>
       </c>
       <c r="C3432" t="n">
-        <v>23.44</v>
+        <v>23.42</v>
       </c>
       <c r="D3432" t="inlineStr">
         <is>
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3433">
@@ -93105,7 +93105,7 @@
         <v>24</v>
       </c>
       <c r="C3433" t="n">
-        <v>24.84</v>
+        <v>24.83</v>
       </c>
       <c r="D3433" t="inlineStr">
         <is>
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3434">
@@ -93132,7 +93132,7 @@
         <v>1</v>
       </c>
       <c r="C3434" t="n">
-        <v>13.24</v>
+        <v>13.23</v>
       </c>
       <c r="D3434" t="inlineStr">
         <is>
@@ -93148,7 +93148,7 @@
         <v>3</v>
       </c>
       <c r="G3434" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3435">
@@ -93159,7 +93159,7 @@
         <v>2</v>
       </c>
       <c r="C3435" t="n">
-        <v>12.78</v>
+        <v>12.92</v>
       </c>
       <c r="D3435" t="inlineStr">
         <is>
@@ -93175,7 +93175,7 @@
         <v>3</v>
       </c>
       <c r="G3435" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3436">
@@ -93186,7 +93186,7 @@
         <v>3</v>
       </c>
       <c r="C3436" t="n">
-        <v>15.36</v>
+        <v>15.49</v>
       </c>
       <c r="D3436" t="inlineStr">
         <is>
@@ -93202,7 +93202,7 @@
         <v>3</v>
       </c>
       <c r="G3436" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3437">
@@ -93229,7 +93229,7 @@
         <v>3</v>
       </c>
       <c r="G3437" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3438">
@@ -93240,7 +93240,7 @@
         <v>5</v>
       </c>
       <c r="C3438" t="n">
-        <v>15.23</v>
+        <v>15.28</v>
       </c>
       <c r="D3438" t="inlineStr">
         <is>
@@ -93256,7 +93256,7 @@
         <v>3</v>
       </c>
       <c r="G3438" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3439">
@@ -93267,7 +93267,7 @@
         <v>6</v>
       </c>
       <c r="C3439" t="n">
-        <v>23.25</v>
+        <v>23.2</v>
       </c>
       <c r="D3439" t="inlineStr">
         <is>
@@ -93283,7 +93283,7 @@
         <v>3</v>
       </c>
       <c r="G3439" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3440">
@@ -93294,7 +93294,7 @@
         <v>7</v>
       </c>
       <c r="C3440" t="n">
-        <v>28.86</v>
+        <v>28.69</v>
       </c>
       <c r="D3440" t="inlineStr">
         <is>
@@ -93310,7 +93310,7 @@
         <v>3</v>
       </c>
       <c r="G3440" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3441">
@@ -93321,7 +93321,7 @@
         <v>8</v>
       </c>
       <c r="C3441" t="n">
-        <v>57.92</v>
+        <v>57.52</v>
       </c>
       <c r="D3441" t="inlineStr">
         <is>
@@ -93337,7 +93337,7 @@
         <v>3</v>
       </c>
       <c r="G3441" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3442">
@@ -93348,7 +93348,7 @@
         <v>9</v>
       </c>
       <c r="C3442" t="n">
-        <v>53.48</v>
+        <v>53.26</v>
       </c>
       <c r="D3442" t="inlineStr">
         <is>
@@ -93364,7 +93364,7 @@
         <v>3</v>
       </c>
       <c r="G3442" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3443">
@@ -93375,7 +93375,7 @@
         <v>10</v>
       </c>
       <c r="C3443" t="n">
-        <v>30.28</v>
+        <v>30.01</v>
       </c>
       <c r="D3443" t="inlineStr">
         <is>
@@ -93391,7 +93391,7 @@
         <v>3</v>
       </c>
       <c r="G3443" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3444">
@@ -93402,7 +93402,7 @@
         <v>11</v>
       </c>
       <c r="C3444" t="n">
-        <v>27.16</v>
+        <v>26.8</v>
       </c>
       <c r="D3444" t="inlineStr">
         <is>
@@ -93418,7 +93418,7 @@
         <v>3</v>
       </c>
       <c r="G3444" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3445">
@@ -93429,7 +93429,7 @@
         <v>12</v>
       </c>
       <c r="C3445" t="n">
-        <v>31.6</v>
+        <v>31.3</v>
       </c>
       <c r="D3445" t="inlineStr">
         <is>
@@ -93445,7 +93445,7 @@
         <v>3</v>
       </c>
       <c r="G3445" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3446">
@@ -93456,7 +93456,7 @@
         <v>13</v>
       </c>
       <c r="C3446" t="n">
-        <v>31.28</v>
+        <v>30.95</v>
       </c>
       <c r="D3446" t="inlineStr">
         <is>
@@ -93472,7 +93472,7 @@
         <v>3</v>
       </c>
       <c r="G3446" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3447">
@@ -93483,7 +93483,7 @@
         <v>14</v>
       </c>
       <c r="C3447" t="n">
-        <v>30.91</v>
+        <v>30.95</v>
       </c>
       <c r="D3447" t="inlineStr">
         <is>
@@ -93499,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="G3447" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3448">
@@ -93510,7 +93510,7 @@
         <v>15</v>
       </c>
       <c r="C3448" t="n">
-        <v>31.39</v>
+        <v>30.97</v>
       </c>
       <c r="D3448" t="inlineStr">
         <is>
@@ -93526,7 +93526,7 @@
         <v>3</v>
       </c>
       <c r="G3448" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3449">
@@ -93537,7 +93537,7 @@
         <v>16</v>
       </c>
       <c r="C3449" t="n">
-        <v>31.67</v>
+        <v>31.79</v>
       </c>
       <c r="D3449" t="inlineStr">
         <is>
@@ -93553,7 +93553,7 @@
         <v>3</v>
       </c>
       <c r="G3449" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3450">
@@ -93564,7 +93564,7 @@
         <v>17</v>
       </c>
       <c r="C3450" t="n">
-        <v>29.58</v>
+        <v>29.75</v>
       </c>
       <c r="D3450" t="inlineStr">
         <is>
@@ -93580,7 +93580,7 @@
         <v>3</v>
       </c>
       <c r="G3450" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3451">
@@ -93591,7 +93591,7 @@
         <v>18</v>
       </c>
       <c r="C3451" t="n">
-        <v>23.45</v>
+        <v>23.92</v>
       </c>
       <c r="D3451" t="inlineStr">
         <is>
@@ -93607,7 +93607,7 @@
         <v>3</v>
       </c>
       <c r="G3451" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3452">
@@ -93618,7 +93618,7 @@
         <v>19</v>
       </c>
       <c r="C3452" t="n">
-        <v>23.39</v>
+        <v>24.2</v>
       </c>
       <c r="D3452" t="inlineStr">
         <is>
@@ -93634,7 +93634,7 @@
         <v>3</v>
       </c>
       <c r="G3452" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3453">
@@ -93645,7 +93645,7 @@
         <v>20</v>
       </c>
       <c r="C3453" t="n">
-        <v>25.92</v>
+        <v>25.99</v>
       </c>
       <c r="D3453" t="inlineStr">
         <is>
@@ -93661,7 +93661,7 @@
         <v>3</v>
       </c>
       <c r="G3453" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3454">
@@ -93672,7 +93672,7 @@
         <v>21</v>
       </c>
       <c r="C3454" t="n">
-        <v>47.36</v>
+        <v>47.27</v>
       </c>
       <c r="D3454" t="inlineStr">
         <is>
@@ -93688,7 +93688,7 @@
         <v>3</v>
       </c>
       <c r="G3454" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3455">
@@ -93699,7 +93699,7 @@
         <v>22</v>
       </c>
       <c r="C3455" t="n">
-        <v>48.13</v>
+        <v>47.97</v>
       </c>
       <c r="D3455" t="inlineStr">
         <is>
@@ -93715,7 +93715,7 @@
         <v>3</v>
       </c>
       <c r="G3455" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3456">
@@ -93726,7 +93726,7 @@
         <v>23</v>
       </c>
       <c r="C3456" t="n">
-        <v>34.41</v>
+        <v>34.27</v>
       </c>
       <c r="D3456" t="inlineStr">
         <is>
@@ -93742,7 +93742,7 @@
         <v>3</v>
       </c>
       <c r="G3456" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3457">
@@ -93753,7 +93753,7 @@
         <v>24</v>
       </c>
       <c r="C3457" t="n">
-        <v>27.41</v>
+        <v>27.51</v>
       </c>
       <c r="D3457" t="inlineStr">
         <is>
@@ -93769,7 +93769,7 @@
         <v>3</v>
       </c>
       <c r="G3457" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3458">
@@ -93780,7 +93780,7 @@
         <v>1</v>
       </c>
       <c r="C3458" t="n">
-        <v>10.39</v>
+        <v>12.16</v>
       </c>
       <c r="D3458" t="inlineStr">
         <is>
@@ -93796,7 +93796,7 @@
         <v>3</v>
       </c>
       <c r="G3458" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3459">
@@ -93807,7 +93807,7 @@
         <v>2</v>
       </c>
       <c r="C3459" t="n">
-        <v>7.4</v>
+        <v>10.24</v>
       </c>
       <c r="D3459" t="inlineStr">
         <is>
@@ -93823,7 +93823,7 @@
         <v>3</v>
       </c>
       <c r="G3459" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3460">
@@ -93834,7 +93834,7 @@
         <v>3</v>
       </c>
       <c r="C3460" t="n">
-        <v>2.3</v>
+        <v>8.27</v>
       </c>
       <c r="D3460" t="inlineStr">
         <is>
@@ -93850,7 +93850,7 @@
         <v>3</v>
       </c>
       <c r="G3460" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3461">
@@ -93861,7 +93861,7 @@
         <v>4</v>
       </c>
       <c r="C3461" t="n">
-        <v>7.95</v>
+        <v>9.08</v>
       </c>
       <c r="D3461" t="inlineStr">
         <is>
@@ -93877,7 +93877,7 @@
         <v>3</v>
       </c>
       <c r="G3461" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3462">
@@ -93888,7 +93888,7 @@
         <v>5</v>
       </c>
       <c r="C3462" t="n">
-        <v>5.83</v>
+        <v>7.98</v>
       </c>
       <c r="D3462" t="inlineStr">
         <is>
@@ -93904,7 +93904,7 @@
         <v>3</v>
       </c>
       <c r="G3462" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3463">
@@ -93915,7 +93915,7 @@
         <v>6</v>
       </c>
       <c r="C3463" t="n">
-        <v>12.04</v>
+        <v>13.54</v>
       </c>
       <c r="D3463" t="inlineStr">
         <is>
@@ -93931,7 +93931,7 @@
         <v>3</v>
       </c>
       <c r="G3463" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3464">
@@ -93942,7 +93942,7 @@
         <v>7</v>
       </c>
       <c r="C3464" t="n">
-        <v>21.89</v>
+        <v>21.84</v>
       </c>
       <c r="D3464" t="inlineStr">
         <is>
@@ -93958,7 +93958,7 @@
         <v>3</v>
       </c>
       <c r="G3464" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3465">
@@ -93969,7 +93969,7 @@
         <v>8</v>
       </c>
       <c r="C3465" t="n">
-        <v>62.29</v>
+        <v>61.39</v>
       </c>
       <c r="D3465" t="inlineStr">
         <is>
@@ -93985,7 +93985,7 @@
         <v>3</v>
       </c>
       <c r="G3465" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3466">
@@ -93996,7 +93996,7 @@
         <v>9</v>
       </c>
       <c r="C3466" t="n">
-        <v>59.15</v>
+        <v>58.86</v>
       </c>
       <c r="D3466" t="inlineStr">
         <is>
@@ -94012,7 +94012,7 @@
         <v>3</v>
       </c>
       <c r="G3466" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3467">
@@ -94023,7 +94023,7 @@
         <v>10</v>
       </c>
       <c r="C3467" t="n">
-        <v>18.68</v>
+        <v>22.29</v>
       </c>
       <c r="D3467" t="inlineStr">
         <is>
@@ -94039,7 +94039,7 @@
         <v>3</v>
       </c>
       <c r="G3467" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3468">
@@ -94050,7 +94050,7 @@
         <v>11</v>
       </c>
       <c r="C3468" t="n">
-        <v>23.99</v>
+        <v>23.18</v>
       </c>
       <c r="D3468" t="inlineStr">
         <is>
@@ -94066,7 +94066,7 @@
         <v>3</v>
       </c>
       <c r="G3468" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3469">
@@ -94077,7 +94077,7 @@
         <v>12</v>
       </c>
       <c r="C3469" t="n">
-        <v>31.12</v>
+        <v>32.79</v>
       </c>
       <c r="D3469" t="inlineStr">
         <is>
@@ -94093,7 +94093,7 @@
         <v>3</v>
       </c>
       <c r="G3469" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3470">
@@ -94104,7 +94104,7 @@
         <v>13</v>
       </c>
       <c r="C3470" t="n">
-        <v>33.94</v>
+        <v>31.93</v>
       </c>
       <c r="D3470" t="inlineStr">
         <is>
@@ -94120,7 +94120,7 @@
         <v>3</v>
       </c>
       <c r="G3470" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3471">
@@ -94131,7 +94131,7 @@
         <v>14</v>
       </c>
       <c r="C3471" t="n">
-        <v>28.25</v>
+        <v>28.59</v>
       </c>
       <c r="D3471" t="inlineStr">
         <is>
@@ -94147,7 +94147,7 @@
         <v>3</v>
       </c>
       <c r="G3471" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3472">
@@ -94158,7 +94158,7 @@
         <v>15</v>
       </c>
       <c r="C3472" t="n">
-        <v>29.81</v>
+        <v>28.58</v>
       </c>
       <c r="D3472" t="inlineStr">
         <is>
@@ -94174,7 +94174,7 @@
         <v>3</v>
       </c>
       <c r="G3472" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3473">
@@ -94185,7 +94185,7 @@
         <v>16</v>
       </c>
       <c r="C3473" t="n">
-        <v>33.16</v>
+        <v>31.36</v>
       </c>
       <c r="D3473" t="inlineStr">
         <is>
@@ -94201,7 +94201,7 @@
         <v>3</v>
       </c>
       <c r="G3473" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3474">
@@ -94212,7 +94212,7 @@
         <v>17</v>
       </c>
       <c r="C3474" t="n">
-        <v>19.75</v>
+        <v>28.22</v>
       </c>
       <c r="D3474" t="inlineStr">
         <is>
@@ -94228,7 +94228,7 @@
         <v>3</v>
       </c>
       <c r="G3474" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3475">
@@ -94239,7 +94239,7 @@
         <v>18</v>
       </c>
       <c r="C3475" t="n">
-        <v>31.1</v>
+        <v>29.29</v>
       </c>
       <c r="D3475" t="inlineStr">
         <is>
@@ -94255,7 +94255,7 @@
         <v>3</v>
       </c>
       <c r="G3475" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3476">
@@ -94266,7 +94266,7 @@
         <v>19</v>
       </c>
       <c r="C3476" t="n">
-        <v>23.54</v>
+        <v>26.91</v>
       </c>
       <c r="D3476" t="inlineStr">
         <is>
@@ -94282,7 +94282,7 @@
         <v>3</v>
       </c>
       <c r="G3476" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3477">
@@ -94293,7 +94293,7 @@
         <v>20</v>
       </c>
       <c r="C3477" t="n">
-        <v>17.81</v>
+        <v>21.54</v>
       </c>
       <c r="D3477" t="inlineStr">
         <is>
@@ -94309,7 +94309,7 @@
         <v>3</v>
       </c>
       <c r="G3477" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3478">
@@ -94320,7 +94320,7 @@
         <v>21</v>
       </c>
       <c r="C3478" t="n">
-        <v>32.19</v>
+        <v>32.1</v>
       </c>
       <c r="D3478" t="inlineStr">
         <is>
@@ -94336,7 +94336,7 @@
         <v>3</v>
       </c>
       <c r="G3478" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3479">
@@ -94347,7 +94347,7 @@
         <v>22</v>
       </c>
       <c r="C3479" t="n">
-        <v>35.95</v>
+        <v>35.93</v>
       </c>
       <c r="D3479" t="inlineStr">
         <is>
@@ -94363,7 +94363,7 @@
         <v>3</v>
       </c>
       <c r="G3479" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3480">
@@ -94374,7 +94374,7 @@
         <v>23</v>
       </c>
       <c r="C3480" t="n">
-        <v>37.79</v>
+        <v>37.62</v>
       </c>
       <c r="D3480" t="inlineStr">
         <is>
@@ -94390,7 +94390,7 @@
         <v>3</v>
       </c>
       <c r="G3480" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3481">
@@ -94401,7 +94401,7 @@
         <v>24</v>
       </c>
       <c r="C3481" t="n">
-        <v>35.62</v>
+        <v>34.85</v>
       </c>
       <c r="D3481" t="inlineStr">
         <is>
@@ -94417,7 +94417,7 @@
         <v>3</v>
       </c>
       <c r="G3481" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3482">
@@ -94428,7 +94428,7 @@
         <v>1</v>
       </c>
       <c r="C3482" t="n">
-        <v>12.55</v>
+        <v>12.45</v>
       </c>
       <c r="D3482" t="inlineStr">
         <is>
@@ -94444,7 +94444,7 @@
         <v>3</v>
       </c>
       <c r="G3482" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3483">
@@ -94455,7 +94455,7 @@
         <v>2</v>
       </c>
       <c r="C3483" t="n">
-        <v>8</v>
+        <v>7.98</v>
       </c>
       <c r="D3483" t="inlineStr">
         <is>
@@ -94471,7 +94471,7 @@
         <v>3</v>
       </c>
       <c r="G3483" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3484">
@@ -94482,7 +94482,7 @@
         <v>3</v>
       </c>
       <c r="C3484" t="n">
-        <v>9.4</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D3484" t="inlineStr">
         <is>
@@ -94498,7 +94498,7 @@
         <v>3</v>
       </c>
       <c r="G3484" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3485">
@@ -94509,7 +94509,7 @@
         <v>4</v>
       </c>
       <c r="C3485" t="n">
-        <v>9.640000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D3485" t="inlineStr">
         <is>
@@ -94525,7 +94525,7 @@
         <v>3</v>
       </c>
       <c r="G3485" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3486">
@@ -94536,7 +94536,7 @@
         <v>5</v>
       </c>
       <c r="C3486" t="n">
-        <v>8.06</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="D3486" t="inlineStr">
         <is>
@@ -94552,7 +94552,7 @@
         <v>3</v>
       </c>
       <c r="G3486" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3487">
@@ -94563,7 +94563,7 @@
         <v>6</v>
       </c>
       <c r="C3487" t="n">
-        <v>8.550000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="D3487" t="inlineStr">
         <is>
@@ -94579,7 +94579,7 @@
         <v>3</v>
       </c>
       <c r="G3487" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3488">
@@ -94590,7 +94590,7 @@
         <v>7</v>
       </c>
       <c r="C3488" t="n">
-        <v>20.59</v>
+        <v>20.41</v>
       </c>
       <c r="D3488" t="inlineStr">
         <is>
@@ -94606,7 +94606,7 @@
         <v>3</v>
       </c>
       <c r="G3488" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3489">
@@ -94617,7 +94617,7 @@
         <v>8</v>
       </c>
       <c r="C3489" t="n">
-        <v>37.23</v>
+        <v>44.04</v>
       </c>
       <c r="D3489" t="inlineStr">
         <is>
@@ -94633,7 +94633,7 @@
         <v>3</v>
       </c>
       <c r="G3489" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3490">
@@ -94644,7 +94644,7 @@
         <v>9</v>
       </c>
       <c r="C3490" t="n">
-        <v>35.55</v>
+        <v>42.14</v>
       </c>
       <c r="D3490" t="inlineStr">
         <is>
@@ -94660,7 +94660,7 @@
         <v>3</v>
       </c>
       <c r="G3490" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3491">
@@ -94671,7 +94671,7 @@
         <v>10</v>
       </c>
       <c r="C3491" t="n">
-        <v>27.57</v>
+        <v>28.21</v>
       </c>
       <c r="D3491" t="inlineStr">
         <is>
@@ -94687,7 +94687,7 @@
         <v>3</v>
       </c>
       <c r="G3491" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3492">
@@ -94698,7 +94698,7 @@
         <v>11</v>
       </c>
       <c r="C3492" t="n">
-        <v>24.04</v>
+        <v>23.23</v>
       </c>
       <c r="D3492" t="inlineStr">
         <is>
@@ -94714,7 +94714,7 @@
         <v>3</v>
       </c>
       <c r="G3492" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3493">
@@ -94725,7 +94725,7 @@
         <v>12</v>
       </c>
       <c r="C3493" t="n">
-        <v>33.81</v>
+        <v>32.88</v>
       </c>
       <c r="D3493" t="inlineStr">
         <is>
@@ -94741,7 +94741,7 @@
         <v>3</v>
       </c>
       <c r="G3493" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3494">
@@ -94752,7 +94752,7 @@
         <v>13</v>
       </c>
       <c r="C3494" t="n">
-        <v>36.63</v>
+        <v>35.52</v>
       </c>
       <c r="D3494" t="inlineStr">
         <is>
@@ -94768,7 +94768,7 @@
         <v>3</v>
       </c>
       <c r="G3494" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3495">
@@ -94779,7 +94779,7 @@
         <v>14</v>
       </c>
       <c r="C3495" t="n">
-        <v>36.54</v>
+        <v>35.29</v>
       </c>
       <c r="D3495" t="inlineStr">
         <is>
@@ -94795,7 +94795,7 @@
         <v>3</v>
       </c>
       <c r="G3495" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3496">
@@ -94806,7 +94806,7 @@
         <v>15</v>
       </c>
       <c r="C3496" t="n">
-        <v>36.09</v>
+        <v>36.27</v>
       </c>
       <c r="D3496" t="inlineStr">
         <is>
@@ -94822,7 +94822,7 @@
         <v>3</v>
       </c>
       <c r="G3496" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3497">
@@ -94833,7 +94833,7 @@
         <v>16</v>
       </c>
       <c r="C3497" t="n">
-        <v>30.38</v>
+        <v>32.72</v>
       </c>
       <c r="D3497" t="inlineStr">
         <is>
@@ -94849,7 +94849,7 @@
         <v>3</v>
       </c>
       <c r="G3497" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3498">
@@ -94860,7 +94860,7 @@
         <v>17</v>
       </c>
       <c r="C3498" t="n">
-        <v>32.25</v>
+        <v>33.35</v>
       </c>
       <c r="D3498" t="inlineStr">
         <is>
@@ -94876,7 +94876,7 @@
         <v>3</v>
       </c>
       <c r="G3498" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3499">
@@ -94887,7 +94887,7 @@
         <v>18</v>
       </c>
       <c r="C3499" t="n">
-        <v>25.99</v>
+        <v>26.7</v>
       </c>
       <c r="D3499" t="inlineStr">
         <is>
@@ -94903,7 +94903,7 @@
         <v>3</v>
       </c>
       <c r="G3499" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3500">
@@ -94914,7 +94914,7 @@
         <v>19</v>
       </c>
       <c r="C3500" t="n">
-        <v>33.47</v>
+        <v>34.58</v>
       </c>
       <c r="D3500" t="inlineStr">
         <is>
@@ -94930,7 +94930,7 @@
         <v>3</v>
       </c>
       <c r="G3500" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3501">
@@ -94941,7 +94941,7 @@
         <v>20</v>
       </c>
       <c r="C3501" t="n">
-        <v>34.15</v>
+        <v>37.72</v>
       </c>
       <c r="D3501" t="inlineStr">
         <is>
@@ -94957,7 +94957,7 @@
         <v>3</v>
       </c>
       <c r="G3501" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3502">
@@ -94968,7 +94968,7 @@
         <v>21</v>
       </c>
       <c r="C3502" t="n">
-        <v>31.86</v>
+        <v>38.45</v>
       </c>
       <c r="D3502" t="inlineStr">
         <is>
@@ -94984,7 +94984,7 @@
         <v>3</v>
       </c>
       <c r="G3502" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3503">
@@ -94995,7 +94995,7 @@
         <v>22</v>
       </c>
       <c r="C3503" t="n">
-        <v>34.68</v>
+        <v>41.44</v>
       </c>
       <c r="D3503" t="inlineStr">
         <is>
@@ -95011,7 +95011,7 @@
         <v>3</v>
       </c>
       <c r="G3503" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3504">
@@ -95022,7 +95022,7 @@
         <v>23</v>
       </c>
       <c r="C3504" t="n">
-        <v>37.93</v>
+        <v>45.36</v>
       </c>
       <c r="D3504" t="inlineStr">
         <is>
@@ -95038,7 +95038,7 @@
         <v>3</v>
       </c>
       <c r="G3504" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3505">
@@ -95049,7 +95049,7 @@
         <v>24</v>
       </c>
       <c r="C3505" t="n">
-        <v>26.61</v>
+        <v>26.62</v>
       </c>
       <c r="D3505" t="inlineStr">
         <is>
@@ -95065,7 +95065,7 @@
         <v>3</v>
       </c>
       <c r="G3505" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3506">
@@ -95076,7 +95076,7 @@
         <v>1</v>
       </c>
       <c r="C3506" t="n">
-        <v>10.84</v>
+        <v>7.5</v>
       </c>
       <c r="D3506" t="inlineStr">
         <is>
@@ -95092,7 +95092,7 @@
         <v>3</v>
       </c>
       <c r="G3506" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3507">
@@ -95103,7 +95103,7 @@
         <v>2</v>
       </c>
       <c r="C3507" t="n">
-        <v>10.74</v>
+        <v>8.69</v>
       </c>
       <c r="D3507" t="inlineStr">
         <is>
@@ -95119,7 +95119,7 @@
         <v>3</v>
       </c>
       <c r="G3507" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3508">
@@ -95130,7 +95130,7 @@
         <v>3</v>
       </c>
       <c r="C3508" t="n">
-        <v>11.26</v>
+        <v>14.44</v>
       </c>
       <c r="D3508" t="inlineStr">
         <is>
@@ -95146,7 +95146,7 @@
         <v>3</v>
       </c>
       <c r="G3508" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3509">
@@ -95157,7 +95157,7 @@
         <v>4</v>
       </c>
       <c r="C3509" t="n">
-        <v>11.56</v>
+        <v>11.51</v>
       </c>
       <c r="D3509" t="inlineStr">
         <is>
@@ -95173,7 +95173,7 @@
         <v>3</v>
       </c>
       <c r="G3509" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3510">
@@ -95184,7 +95184,7 @@
         <v>5</v>
       </c>
       <c r="C3510" t="n">
-        <v>11.37</v>
+        <v>12.71</v>
       </c>
       <c r="D3510" t="inlineStr">
         <is>
@@ -95200,7 +95200,7 @@
         <v>3</v>
       </c>
       <c r="G3510" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3511">
@@ -95211,7 +95211,7 @@
         <v>6</v>
       </c>
       <c r="C3511" t="n">
-        <v>11.87</v>
+        <v>12.96</v>
       </c>
       <c r="D3511" t="inlineStr">
         <is>
@@ -95227,7 +95227,7 @@
         <v>3</v>
       </c>
       <c r="G3511" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3512">
@@ -95238,7 +95238,7 @@
         <v>7</v>
       </c>
       <c r="C3512" t="n">
-        <v>20.03</v>
+        <v>23.13</v>
       </c>
       <c r="D3512" t="inlineStr">
         <is>
@@ -95254,7 +95254,7 @@
         <v>3</v>
       </c>
       <c r="G3512" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3513">
@@ -95265,7 +95265,7 @@
         <v>8</v>
       </c>
       <c r="C3513" t="n">
-        <v>40.86</v>
+        <v>36.87</v>
       </c>
       <c r="D3513" t="inlineStr">
         <is>
@@ -95281,7 +95281,7 @@
         <v>3</v>
       </c>
       <c r="G3513" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3514">
@@ -95292,7 +95292,7 @@
         <v>9</v>
       </c>
       <c r="C3514" t="n">
-        <v>36.68</v>
+        <v>34.48</v>
       </c>
       <c r="D3514" t="inlineStr">
         <is>
@@ -95308,7 +95308,7 @@
         <v>3</v>
       </c>
       <c r="G3514" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3515">
@@ -95319,7 +95319,7 @@
         <v>10</v>
       </c>
       <c r="C3515" t="n">
-        <v>24.77</v>
+        <v>25.3</v>
       </c>
       <c r="D3515" t="inlineStr">
         <is>
@@ -95335,7 +95335,7 @@
         <v>3</v>
       </c>
       <c r="G3515" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3516">
@@ -95346,7 +95346,7 @@
         <v>11</v>
       </c>
       <c r="C3516" t="n">
-        <v>25.12</v>
+        <v>24.66</v>
       </c>
       <c r="D3516" t="inlineStr">
         <is>
@@ -95362,7 +95362,7 @@
         <v>3</v>
       </c>
       <c r="G3516" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3517">
@@ -95373,7 +95373,7 @@
         <v>12</v>
       </c>
       <c r="C3517" t="n">
-        <v>31.67</v>
+        <v>29.13</v>
       </c>
       <c r="D3517" t="inlineStr">
         <is>
@@ -95389,7 +95389,7 @@
         <v>3</v>
       </c>
       <c r="G3517" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3518">
@@ -95400,7 +95400,7 @@
         <v>13</v>
       </c>
       <c r="C3518" t="n">
-        <v>33.74</v>
+        <v>24.38</v>
       </c>
       <c r="D3518" t="inlineStr">
         <is>
@@ -95416,7 +95416,7 @@
         <v>3</v>
       </c>
       <c r="G3518" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3519">
@@ -95427,7 +95427,7 @@
         <v>14</v>
       </c>
       <c r="C3519" t="n">
-        <v>32.95</v>
+        <v>31.74</v>
       </c>
       <c r="D3519" t="inlineStr">
         <is>
@@ -95443,7 +95443,7 @@
         <v>3</v>
       </c>
       <c r="G3519" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3520">
@@ -95454,7 +95454,7 @@
         <v>15</v>
       </c>
       <c r="C3520" t="n">
-        <v>32.62</v>
+        <v>32.53</v>
       </c>
       <c r="D3520" t="inlineStr">
         <is>
@@ -95470,7 +95470,7 @@
         <v>3</v>
       </c>
       <c r="G3520" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3521">
@@ -95481,7 +95481,7 @@
         <v>16</v>
       </c>
       <c r="C3521" t="n">
-        <v>32.49</v>
+        <v>33.49</v>
       </c>
       <c r="D3521" t="inlineStr">
         <is>
@@ -95497,7 +95497,7 @@
         <v>3</v>
       </c>
       <c r="G3521" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3522">
@@ -95508,7 +95508,7 @@
         <v>17</v>
       </c>
       <c r="C3522" t="n">
-        <v>29.06</v>
+        <v>29.89</v>
       </c>
       <c r="D3522" t="inlineStr">
         <is>
@@ -95524,7 +95524,7 @@
         <v>3</v>
       </c>
       <c r="G3522" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3523">
@@ -95535,7 +95535,7 @@
         <v>18</v>
       </c>
       <c r="C3523" t="n">
-        <v>25.88</v>
+        <v>27.09</v>
       </c>
       <c r="D3523" t="inlineStr">
         <is>
@@ -95551,7 +95551,7 @@
         <v>3</v>
       </c>
       <c r="G3523" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3524">
@@ -95562,7 +95562,7 @@
         <v>19</v>
       </c>
       <c r="C3524" t="n">
-        <v>24.92</v>
+        <v>27.53</v>
       </c>
       <c r="D3524" t="inlineStr">
         <is>
@@ -95578,7 +95578,7 @@
         <v>3</v>
       </c>
       <c r="G3524" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3525">
@@ -95589,7 +95589,7 @@
         <v>20</v>
       </c>
       <c r="C3525" t="n">
-        <v>32.88</v>
+        <v>23.05</v>
       </c>
       <c r="D3525" t="inlineStr">
         <is>
@@ -95605,7 +95605,7 @@
         <v>3</v>
       </c>
       <c r="G3525" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3526">
@@ -95616,7 +95616,7 @@
         <v>21</v>
       </c>
       <c r="C3526" t="n">
-        <v>44.59</v>
+        <v>23.7</v>
       </c>
       <c r="D3526" t="inlineStr">
         <is>
@@ -95632,7 +95632,7 @@
         <v>3</v>
       </c>
       <c r="G3526" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3527">
@@ -95643,7 +95643,7 @@
         <v>22</v>
       </c>
       <c r="C3527" t="n">
-        <v>39.9</v>
+        <v>25.53</v>
       </c>
       <c r="D3527" t="inlineStr">
         <is>
@@ -95659,7 +95659,7 @@
         <v>3</v>
       </c>
       <c r="G3527" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3528">
@@ -95670,7 +95670,7 @@
         <v>23</v>
       </c>
       <c r="C3528" t="n">
-        <v>29.84</v>
+        <v>27.01</v>
       </c>
       <c r="D3528" t="inlineStr">
         <is>
@@ -95686,7 +95686,7 @@
         <v>3</v>
       </c>
       <c r="G3528" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
       </c>
     </row>
     <row r="3529">
@@ -95697,7 +95697,7 @@
         <v>24</v>
       </c>
       <c r="C3529" t="n">
-        <v>23.83</v>
+        <v>22.37</v>
       </c>
       <c r="D3529" t="inlineStr">
         <is>
@@ -95713,7 +95713,655 @@
         <v>3</v>
       </c>
       <c r="G3529" s="2" t="n">
-        <v>46290.47009576231</v>
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3530">
+      <c r="A3530" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3530" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3530" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="D3530" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3530" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3530" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3530" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3531">
+      <c r="A3531" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3531" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3531" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="D3531" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3531" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3531" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3531" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3532">
+      <c r="A3532" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3532" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3532" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="D3532" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3532" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3532" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3532" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3533">
+      <c r="A3533" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3533" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3533" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="D3533" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3533" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3533" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3533" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3534">
+      <c r="A3534" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3534" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3534" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="D3534" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3534" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3534" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3534" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3535">
+      <c r="A3535" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3535" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3535" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="D3535" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3535" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3535" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3535" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3536">
+      <c r="A3536" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3536" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3536" t="n">
+        <v>27.18</v>
+      </c>
+      <c r="D3536" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3536" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3536" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3536" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3537">
+      <c r="A3537" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3537" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3537" t="n">
+        <v>43.77</v>
+      </c>
+      <c r="D3537" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3537" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3537" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3537" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3538">
+      <c r="A3538" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3538" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3538" t="n">
+        <v>39.64</v>
+      </c>
+      <c r="D3538" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3538" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3538" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3538" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3539">
+      <c r="A3539" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3539" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3539" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="D3539" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3539" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3539" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3539" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3540">
+      <c r="A3540" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3540" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3540" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="D3540" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3540" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3540" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3540" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3541">
+      <c r="A3541" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3541" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3541" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D3541" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3541" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3541" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3541" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3542">
+      <c r="A3542" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3542" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3542" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="D3542" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3542" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3542" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3542" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3543">
+      <c r="A3543" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3543" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3543" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="D3543" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3543" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3543" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3543" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3544">
+      <c r="A3544" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3544" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3544" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D3544" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3544" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3544" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3544" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3545">
+      <c r="A3545" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3545" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3545" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="D3545" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3545" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3545" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3545" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3546">
+      <c r="A3546" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3546" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3546" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="D3546" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3546" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3546" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3546" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3547">
+      <c r="A3547" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3547" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3547" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="D3547" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3547" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3547" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3547" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3548">
+      <c r="A3548" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3548" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3548" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="D3548" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3548" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3548" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3548" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3549">
+      <c r="A3549" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3549" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3549" t="n">
+        <v>43.21</v>
+      </c>
+      <c r="D3549" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3549" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3549" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3549" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3550">
+      <c r="A3550" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3550" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3550" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="D3550" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3550" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3550" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3550" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3551">
+      <c r="A3551" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3551" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3551" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="D3551" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3551" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3551" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3551" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3552">
+      <c r="A3552" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3552" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3552" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="D3552" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3552" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3552" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3552" s="2" t="n">
+        <v>46290.88247446862</v>
+      </c>
+    </row>
+    <row r="3553">
+      <c r="A3553" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3553" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3553" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="D3553" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3553" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3553" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3553" s="2" t="n">
+        <v>46290.88247446862</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3324">
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3333">
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3335">
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3337">
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3341">
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3343">
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3344">
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3345">
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3346">
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3347">
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3355">
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3356">
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3357">
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3360">
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3362">
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3364">
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3365">
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3366">
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3367">
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3368">
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3369">
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3370">
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3371">
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3372">
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3373">
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3374">
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3375">
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3376">
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3377">
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3378">
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3379">
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3380">
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3381">
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3382">
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3383">
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3384">
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3385">
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3386">
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3387">
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3388">
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3389">
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3390">
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3391">
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3392">
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3393">
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3394">
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3395">
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3396">
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3397">
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3398">
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3399">
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3400">
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3401">
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3402">
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3403">
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3404">
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3405">
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3406">
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3407">
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3408">
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3409">
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3410">
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3411">
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3412">
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3413">
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3415">
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3416">
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3417">
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3418">
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3419">
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3420">
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3421">
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3422">
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3423">
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3424">
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3425">
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3426">
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3427">
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3428">
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3429">
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3430">
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3431">
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3432">
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3433">
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3434">
@@ -93148,7 +93148,7 @@
         <v>3</v>
       </c>
       <c r="G3434" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3435">
@@ -93175,7 +93175,7 @@
         <v>3</v>
       </c>
       <c r="G3435" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3436">
@@ -93202,7 +93202,7 @@
         <v>3</v>
       </c>
       <c r="G3436" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3437">
@@ -93229,7 +93229,7 @@
         <v>3</v>
       </c>
       <c r="G3437" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3438">
@@ -93256,7 +93256,7 @@
         <v>3</v>
       </c>
       <c r="G3438" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3439">
@@ -93283,7 +93283,7 @@
         <v>3</v>
       </c>
       <c r="G3439" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3440">
@@ -93310,7 +93310,7 @@
         <v>3</v>
       </c>
       <c r="G3440" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3441">
@@ -93337,7 +93337,7 @@
         <v>3</v>
       </c>
       <c r="G3441" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3442">
@@ -93364,7 +93364,7 @@
         <v>3</v>
       </c>
       <c r="G3442" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3443">
@@ -93391,7 +93391,7 @@
         <v>3</v>
       </c>
       <c r="G3443" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3444">
@@ -93418,7 +93418,7 @@
         <v>3</v>
       </c>
       <c r="G3444" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3445">
@@ -93445,7 +93445,7 @@
         <v>3</v>
       </c>
       <c r="G3445" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3446">
@@ -93472,7 +93472,7 @@
         <v>3</v>
       </c>
       <c r="G3446" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3447">
@@ -93499,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="G3447" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3448">
@@ -93526,7 +93526,7 @@
         <v>3</v>
       </c>
       <c r="G3448" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3449">
@@ -93553,7 +93553,7 @@
         <v>3</v>
       </c>
       <c r="G3449" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3450">
@@ -93580,7 +93580,7 @@
         <v>3</v>
       </c>
       <c r="G3450" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3451">
@@ -93607,7 +93607,7 @@
         <v>3</v>
       </c>
       <c r="G3451" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3452">
@@ -93634,7 +93634,7 @@
         <v>3</v>
       </c>
       <c r="G3452" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3453">
@@ -93661,7 +93661,7 @@
         <v>3</v>
       </c>
       <c r="G3453" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3454">
@@ -93688,7 +93688,7 @@
         <v>3</v>
       </c>
       <c r="G3454" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3455">
@@ -93715,7 +93715,7 @@
         <v>3</v>
       </c>
       <c r="G3455" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3456">
@@ -93742,7 +93742,7 @@
         <v>3</v>
       </c>
       <c r="G3456" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3457">
@@ -93769,7 +93769,7 @@
         <v>3</v>
       </c>
       <c r="G3457" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3458">
@@ -93796,7 +93796,7 @@
         <v>3</v>
       </c>
       <c r="G3458" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3459">
@@ -93823,7 +93823,7 @@
         <v>3</v>
       </c>
       <c r="G3459" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3460">
@@ -93850,7 +93850,7 @@
         <v>3</v>
       </c>
       <c r="G3460" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3461">
@@ -93877,7 +93877,7 @@
         <v>3</v>
       </c>
       <c r="G3461" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3462">
@@ -93904,7 +93904,7 @@
         <v>3</v>
       </c>
       <c r="G3462" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3463">
@@ -93931,7 +93931,7 @@
         <v>3</v>
       </c>
       <c r="G3463" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3464">
@@ -93958,7 +93958,7 @@
         <v>3</v>
       </c>
       <c r="G3464" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3465">
@@ -93985,7 +93985,7 @@
         <v>3</v>
       </c>
       <c r="G3465" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3466">
@@ -94012,7 +94012,7 @@
         <v>3</v>
       </c>
       <c r="G3466" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3467">
@@ -94039,7 +94039,7 @@
         <v>3</v>
       </c>
       <c r="G3467" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3468">
@@ -94066,7 +94066,7 @@
         <v>3</v>
       </c>
       <c r="G3468" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3469">
@@ -94093,7 +94093,7 @@
         <v>3</v>
       </c>
       <c r="G3469" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3470">
@@ -94120,7 +94120,7 @@
         <v>3</v>
       </c>
       <c r="G3470" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3471">
@@ -94147,7 +94147,7 @@
         <v>3</v>
       </c>
       <c r="G3471" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3472">
@@ -94174,7 +94174,7 @@
         <v>3</v>
       </c>
       <c r="G3472" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3473">
@@ -94201,7 +94201,7 @@
         <v>3</v>
       </c>
       <c r="G3473" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3474">
@@ -94228,7 +94228,7 @@
         <v>3</v>
       </c>
       <c r="G3474" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3475">
@@ -94255,7 +94255,7 @@
         <v>3</v>
       </c>
       <c r="G3475" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3476">
@@ -94282,7 +94282,7 @@
         <v>3</v>
       </c>
       <c r="G3476" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3477">
@@ -94309,7 +94309,7 @@
         <v>3</v>
       </c>
       <c r="G3477" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3478">
@@ -94336,7 +94336,7 @@
         <v>3</v>
       </c>
       <c r="G3478" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3479">
@@ -94363,7 +94363,7 @@
         <v>3</v>
       </c>
       <c r="G3479" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3480">
@@ -94390,7 +94390,7 @@
         <v>3</v>
       </c>
       <c r="G3480" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3481">
@@ -94417,7 +94417,7 @@
         <v>3</v>
       </c>
       <c r="G3481" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3482">
@@ -94444,7 +94444,7 @@
         <v>3</v>
       </c>
       <c r="G3482" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3483">
@@ -94471,7 +94471,7 @@
         <v>3</v>
       </c>
       <c r="G3483" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3484">
@@ -94498,7 +94498,7 @@
         <v>3</v>
       </c>
       <c r="G3484" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3485">
@@ -94525,7 +94525,7 @@
         <v>3</v>
       </c>
       <c r="G3485" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3486">
@@ -94552,7 +94552,7 @@
         <v>3</v>
       </c>
       <c r="G3486" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3487">
@@ -94579,7 +94579,7 @@
         <v>3</v>
       </c>
       <c r="G3487" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3488">
@@ -94606,7 +94606,7 @@
         <v>3</v>
       </c>
       <c r="G3488" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3489">
@@ -94633,7 +94633,7 @@
         <v>3</v>
       </c>
       <c r="G3489" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3490">
@@ -94660,7 +94660,7 @@
         <v>3</v>
       </c>
       <c r="G3490" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3491">
@@ -94687,7 +94687,7 @@
         <v>3</v>
       </c>
       <c r="G3491" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3492">
@@ -94714,7 +94714,7 @@
         <v>3</v>
       </c>
       <c r="G3492" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3493">
@@ -94741,7 +94741,7 @@
         <v>3</v>
       </c>
       <c r="G3493" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3494">
@@ -94768,7 +94768,7 @@
         <v>3</v>
       </c>
       <c r="G3494" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3495">
@@ -94795,7 +94795,7 @@
         <v>3</v>
       </c>
       <c r="G3495" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3496">
@@ -94822,7 +94822,7 @@
         <v>3</v>
       </c>
       <c r="G3496" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3497">
@@ -94849,7 +94849,7 @@
         <v>3</v>
       </c>
       <c r="G3497" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3498">
@@ -94876,7 +94876,7 @@
         <v>3</v>
       </c>
       <c r="G3498" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3499">
@@ -94903,7 +94903,7 @@
         <v>3</v>
       </c>
       <c r="G3499" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3500">
@@ -94930,7 +94930,7 @@
         <v>3</v>
       </c>
       <c r="G3500" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3501">
@@ -94957,7 +94957,7 @@
         <v>3</v>
       </c>
       <c r="G3501" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3502">
@@ -94984,7 +94984,7 @@
         <v>3</v>
       </c>
       <c r="G3502" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3503">
@@ -95011,7 +95011,7 @@
         <v>3</v>
       </c>
       <c r="G3503" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3504">
@@ -95038,7 +95038,7 @@
         <v>3</v>
       </c>
       <c r="G3504" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3505">
@@ -95065,7 +95065,7 @@
         <v>3</v>
       </c>
       <c r="G3505" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3506">
@@ -95092,7 +95092,7 @@
         <v>3</v>
       </c>
       <c r="G3506" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3507">
@@ -95119,7 +95119,7 @@
         <v>3</v>
       </c>
       <c r="G3507" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3508">
@@ -95146,7 +95146,7 @@
         <v>3</v>
       </c>
       <c r="G3508" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3509">
@@ -95173,7 +95173,7 @@
         <v>3</v>
       </c>
       <c r="G3509" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3510">
@@ -95200,7 +95200,7 @@
         <v>3</v>
       </c>
       <c r="G3510" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3511">
@@ -95227,7 +95227,7 @@
         <v>3</v>
       </c>
       <c r="G3511" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3512">
@@ -95254,7 +95254,7 @@
         <v>3</v>
       </c>
       <c r="G3512" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3513">
@@ -95281,7 +95281,7 @@
         <v>3</v>
       </c>
       <c r="G3513" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3514">
@@ -95308,7 +95308,7 @@
         <v>3</v>
       </c>
       <c r="G3514" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3515">
@@ -95335,7 +95335,7 @@
         <v>3</v>
       </c>
       <c r="G3515" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3516">
@@ -95362,7 +95362,7 @@
         <v>3</v>
       </c>
       <c r="G3516" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3517">
@@ -95389,7 +95389,7 @@
         <v>3</v>
       </c>
       <c r="G3517" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3518">
@@ -95416,7 +95416,7 @@
         <v>3</v>
       </c>
       <c r="G3518" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3519">
@@ -95443,7 +95443,7 @@
         <v>3</v>
       </c>
       <c r="G3519" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3520">
@@ -95470,7 +95470,7 @@
         <v>3</v>
       </c>
       <c r="G3520" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3521">
@@ -95497,7 +95497,7 @@
         <v>3</v>
       </c>
       <c r="G3521" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3522">
@@ -95524,7 +95524,7 @@
         <v>3</v>
       </c>
       <c r="G3522" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3523">
@@ -95551,7 +95551,7 @@
         <v>3</v>
       </c>
       <c r="G3523" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3524">
@@ -95578,7 +95578,7 @@
         <v>3</v>
       </c>
       <c r="G3524" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3525">
@@ -95605,7 +95605,7 @@
         <v>3</v>
       </c>
       <c r="G3525" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3526">
@@ -95632,7 +95632,7 @@
         <v>3</v>
       </c>
       <c r="G3526" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3527">
@@ -95659,7 +95659,7 @@
         <v>3</v>
       </c>
       <c r="G3527" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3528">
@@ -95686,7 +95686,7 @@
         <v>3</v>
       </c>
       <c r="G3528" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3529">
@@ -95713,7 +95713,7 @@
         <v>3</v>
       </c>
       <c r="G3529" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3530">
@@ -95740,7 +95740,7 @@
         <v>3</v>
       </c>
       <c r="G3530" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3531">
@@ -95767,7 +95767,7 @@
         <v>3</v>
       </c>
       <c r="G3531" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3532">
@@ -95794,7 +95794,7 @@
         <v>3</v>
       </c>
       <c r="G3532" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3533">
@@ -95821,7 +95821,7 @@
         <v>3</v>
       </c>
       <c r="G3533" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3534">
@@ -95848,7 +95848,7 @@
         <v>3</v>
       </c>
       <c r="G3534" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3535">
@@ -95875,7 +95875,7 @@
         <v>3</v>
       </c>
       <c r="G3535" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3536">
@@ -95902,7 +95902,7 @@
         <v>3</v>
       </c>
       <c r="G3536" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3537">
@@ -95929,7 +95929,7 @@
         <v>3</v>
       </c>
       <c r="G3537" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3538">
@@ -95956,7 +95956,7 @@
         <v>3</v>
       </c>
       <c r="G3538" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3539">
@@ -95983,7 +95983,7 @@
         <v>3</v>
       </c>
       <c r="G3539" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3540">
@@ -96010,7 +96010,7 @@
         <v>3</v>
       </c>
       <c r="G3540" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3541">
@@ -96037,7 +96037,7 @@
         <v>3</v>
       </c>
       <c r="G3541" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3542">
@@ -96064,7 +96064,7 @@
         <v>3</v>
       </c>
       <c r="G3542" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3543">
@@ -96091,7 +96091,7 @@
         <v>3</v>
       </c>
       <c r="G3543" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3544">
@@ -96118,7 +96118,7 @@
         <v>3</v>
       </c>
       <c r="G3544" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3545">
@@ -96145,7 +96145,7 @@
         <v>3</v>
       </c>
       <c r="G3545" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3546">
@@ -96172,7 +96172,7 @@
         <v>3</v>
       </c>
       <c r="G3546" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3547">
@@ -96199,7 +96199,7 @@
         <v>3</v>
       </c>
       <c r="G3547" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3548">
@@ -96226,7 +96226,7 @@
         <v>3</v>
       </c>
       <c r="G3548" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3549">
@@ -96253,7 +96253,7 @@
         <v>3</v>
       </c>
       <c r="G3549" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3550">
@@ -96280,7 +96280,7 @@
         <v>3</v>
       </c>
       <c r="G3550" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3551">
@@ -96307,7 +96307,7 @@
         <v>3</v>
       </c>
       <c r="G3551" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3552">
@@ -96334,7 +96334,7 @@
         <v>3</v>
       </c>
       <c r="G3552" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
     <row r="3553">
@@ -96361,7 +96361,7 @@
         <v>3</v>
       </c>
       <c r="G3553" s="2" t="n">
-        <v>46290.88247446862</v>
+        <v>46291.45404645446</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3553"/>
+  <dimension ref="A1:G3577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89892,7 +89892,7 @@
         <v>1</v>
       </c>
       <c r="C3314" t="n">
-        <v>9.85</v>
+        <v>9.84</v>
       </c>
       <c r="D3314" t="inlineStr">
         <is>
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3316">
@@ -89946,7 +89946,7 @@
         <v>3</v>
       </c>
       <c r="C3316" t="n">
-        <v>12.09</v>
+        <v>12.11</v>
       </c>
       <c r="D3316" t="inlineStr">
         <is>
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3317">
@@ -89973,7 +89973,7 @@
         <v>4</v>
       </c>
       <c r="C3317" t="n">
-        <v>13.47</v>
+        <v>13.48</v>
       </c>
       <c r="D3317" t="inlineStr">
         <is>
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3319">
@@ -90027,7 +90027,7 @@
         <v>6</v>
       </c>
       <c r="C3319" t="n">
-        <v>11.56</v>
+        <v>11.57</v>
       </c>
       <c r="D3319" t="inlineStr">
         <is>
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3320">
@@ -90054,7 +90054,7 @@
         <v>7</v>
       </c>
       <c r="C3320" t="n">
-        <v>12.64</v>
+        <v>12.63</v>
       </c>
       <c r="D3320" t="inlineStr">
         <is>
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3321">
@@ -90081,7 +90081,7 @@
         <v>8</v>
       </c>
       <c r="C3321" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="D3321" t="inlineStr">
         <is>
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3322">
@@ -90108,7 +90108,7 @@
         <v>9</v>
       </c>
       <c r="C3322" t="n">
-        <v>33</v>
+        <v>32.99</v>
       </c>
       <c r="D3322" t="inlineStr">
         <is>
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3324">
@@ -90162,7 +90162,7 @@
         <v>11</v>
       </c>
       <c r="C3324" t="n">
-        <v>26.77</v>
+        <v>26.75</v>
       </c>
       <c r="D3324" t="inlineStr">
         <is>
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3330">
@@ -90324,7 +90324,7 @@
         <v>17</v>
       </c>
       <c r="C3330" t="n">
-        <v>31.78</v>
+        <v>31.77</v>
       </c>
       <c r="D3330" t="inlineStr">
         <is>
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3331">
@@ -90351,7 +90351,7 @@
         <v>18</v>
       </c>
       <c r="C3331" t="n">
-        <v>34.44</v>
+        <v>34.43</v>
       </c>
       <c r="D3331" t="inlineStr">
         <is>
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3332">
@@ -90378,7 +90378,7 @@
         <v>19</v>
       </c>
       <c r="C3332" t="n">
-        <v>31.32</v>
+        <v>31.3</v>
       </c>
       <c r="D3332" t="inlineStr">
         <is>
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3333">
@@ -90405,7 +90405,7 @@
         <v>20</v>
       </c>
       <c r="C3333" t="n">
-        <v>24.38</v>
+        <v>24.37</v>
       </c>
       <c r="D3333" t="inlineStr">
         <is>
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3335">
@@ -90459,7 +90459,7 @@
         <v>22</v>
       </c>
       <c r="C3335" t="n">
-        <v>33.44</v>
+        <v>33.43</v>
       </c>
       <c r="D3335" t="inlineStr">
         <is>
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3337">
@@ -90513,7 +90513,7 @@
         <v>24</v>
       </c>
       <c r="C3337" t="n">
-        <v>23.29</v>
+        <v>23.32</v>
       </c>
       <c r="D3337" t="inlineStr">
         <is>
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3338">
@@ -90540,7 +90540,7 @@
         <v>1</v>
       </c>
       <c r="C3338" t="n">
-        <v>10.64</v>
+        <v>10.66</v>
       </c>
       <c r="D3338" t="inlineStr">
         <is>
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3339">
@@ -90567,7 +90567,7 @@
         <v>2</v>
       </c>
       <c r="C3339" t="n">
-        <v>13.67</v>
+        <v>13.7</v>
       </c>
       <c r="D3339" t="inlineStr">
         <is>
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3340">
@@ -90594,7 +90594,7 @@
         <v>3</v>
       </c>
       <c r="C3340" t="n">
-        <v>15.95</v>
+        <v>15.99</v>
       </c>
       <c r="D3340" t="inlineStr">
         <is>
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3341">
@@ -90621,7 +90621,7 @@
         <v>4</v>
       </c>
       <c r="C3341" t="n">
-        <v>17.99</v>
+        <v>18.02</v>
       </c>
       <c r="D3341" t="inlineStr">
         <is>
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3342">
@@ -90648,7 +90648,7 @@
         <v>5</v>
       </c>
       <c r="C3342" t="n">
-        <v>17.11</v>
+        <v>17.15</v>
       </c>
       <c r="D3342" t="inlineStr">
         <is>
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3343">
@@ -90675,7 +90675,7 @@
         <v>6</v>
       </c>
       <c r="C3343" t="n">
-        <v>16.01</v>
+        <v>16.05</v>
       </c>
       <c r="D3343" t="inlineStr">
         <is>
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3344">
@@ -90702,7 +90702,7 @@
         <v>7</v>
       </c>
       <c r="C3344" t="n">
-        <v>20.02</v>
+        <v>20.03</v>
       </c>
       <c r="D3344" t="inlineStr">
         <is>
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3345">
@@ -90729,7 +90729,7 @@
         <v>8</v>
       </c>
       <c r="C3345" t="n">
-        <v>43.38</v>
+        <v>43.35</v>
       </c>
       <c r="D3345" t="inlineStr">
         <is>
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3346">
@@ -90756,7 +90756,7 @@
         <v>9</v>
       </c>
       <c r="C3346" t="n">
-        <v>44</v>
+        <v>43.98</v>
       </c>
       <c r="D3346" t="inlineStr">
         <is>
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3347">
@@ -90783,7 +90783,7 @@
         <v>10</v>
       </c>
       <c r="C3347" t="n">
-        <v>26.05</v>
+        <v>26.04</v>
       </c>
       <c r="D3347" t="inlineStr">
         <is>
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3354">
@@ -90972,7 +90972,7 @@
         <v>17</v>
       </c>
       <c r="C3354" t="n">
-        <v>23.31</v>
+        <v>23.3</v>
       </c>
       <c r="D3354" t="inlineStr">
         <is>
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3355">
@@ -90999,7 +90999,7 @@
         <v>18</v>
       </c>
       <c r="C3355" t="n">
-        <v>20.92</v>
+        <v>20.91</v>
       </c>
       <c r="D3355" t="inlineStr">
         <is>
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3356">
@@ -91026,7 +91026,7 @@
         <v>19</v>
       </c>
       <c r="C3356" t="n">
-        <v>17.39</v>
+        <v>17.37</v>
       </c>
       <c r="D3356" t="inlineStr">
         <is>
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3357">
@@ -91053,7 +91053,7 @@
         <v>20</v>
       </c>
       <c r="C3357" t="n">
-        <v>25.86</v>
+        <v>25.85</v>
       </c>
       <c r="D3357" t="inlineStr">
         <is>
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3359">
@@ -91107,7 +91107,7 @@
         <v>22</v>
       </c>
       <c r="C3359" t="n">
-        <v>33.61</v>
+        <v>33.6</v>
       </c>
       <c r="D3359" t="inlineStr">
         <is>
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3360">
@@ -91134,7 +91134,7 @@
         <v>23</v>
       </c>
       <c r="C3360" t="n">
-        <v>28.77</v>
+        <v>28.76</v>
       </c>
       <c r="D3360" t="inlineStr">
         <is>
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3361">
@@ -91161,7 +91161,7 @@
         <v>24</v>
       </c>
       <c r="C3361" t="n">
-        <v>23.93</v>
+        <v>23.97</v>
       </c>
       <c r="D3361" t="inlineStr">
         <is>
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3362">
@@ -91188,7 +91188,7 @@
         <v>1</v>
       </c>
       <c r="C3362" t="n">
-        <v>11.73</v>
+        <v>11.72</v>
       </c>
       <c r="D3362" t="inlineStr">
         <is>
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3364">
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3365">
@@ -91269,7 +91269,7 @@
         <v>4</v>
       </c>
       <c r="C3365" t="n">
-        <v>12.97</v>
+        <v>12.98</v>
       </c>
       <c r="D3365" t="inlineStr">
         <is>
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3366">
@@ -91296,7 +91296,7 @@
         <v>5</v>
       </c>
       <c r="C3366" t="n">
-        <v>16.82</v>
+        <v>16.8</v>
       </c>
       <c r="D3366" t="inlineStr">
         <is>
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3367">
@@ -91323,7 +91323,7 @@
         <v>6</v>
       </c>
       <c r="C3367" t="n">
-        <v>18.66</v>
+        <v>18.64</v>
       </c>
       <c r="D3367" t="inlineStr">
         <is>
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3368">
@@ -91350,7 +91350,7 @@
         <v>7</v>
       </c>
       <c r="C3368" t="n">
-        <v>16.31</v>
+        <v>16.3</v>
       </c>
       <c r="D3368" t="inlineStr">
         <is>
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3369">
@@ -91377,7 +91377,7 @@
         <v>8</v>
       </c>
       <c r="C3369" t="n">
-        <v>43.84</v>
+        <v>43.81</v>
       </c>
       <c r="D3369" t="inlineStr">
         <is>
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3370">
@@ -91404,7 +91404,7 @@
         <v>9</v>
       </c>
       <c r="C3370" t="n">
-        <v>42.67</v>
+        <v>42.64</v>
       </c>
       <c r="D3370" t="inlineStr">
         <is>
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3371">
@@ -91431,7 +91431,7 @@
         <v>10</v>
       </c>
       <c r="C3371" t="n">
-        <v>31.36</v>
+        <v>31.34</v>
       </c>
       <c r="D3371" t="inlineStr">
         <is>
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3372">
@@ -91458,7 +91458,7 @@
         <v>11</v>
       </c>
       <c r="C3372" t="n">
-        <v>24.49</v>
+        <v>24.46</v>
       </c>
       <c r="D3372" t="inlineStr">
         <is>
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3373">
@@ -91485,7 +91485,7 @@
         <v>12</v>
       </c>
       <c r="C3373" t="n">
-        <v>27.48</v>
+        <v>27.44</v>
       </c>
       <c r="D3373" t="inlineStr">
         <is>
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3374">
@@ -91512,7 +91512,7 @@
         <v>13</v>
       </c>
       <c r="C3374" t="n">
-        <v>27.56</v>
+        <v>27.54</v>
       </c>
       <c r="D3374" t="inlineStr">
         <is>
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3375">
@@ -91539,7 +91539,7 @@
         <v>14</v>
       </c>
       <c r="C3375" t="n">
-        <v>25.35</v>
+        <v>25.32</v>
       </c>
       <c r="D3375" t="inlineStr">
         <is>
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3376">
@@ -91566,7 +91566,7 @@
         <v>15</v>
       </c>
       <c r="C3376" t="n">
-        <v>26.19</v>
+        <v>26.18</v>
       </c>
       <c r="D3376" t="inlineStr">
         <is>
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3377">
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3378">
@@ -91620,7 +91620,7 @@
         <v>17</v>
       </c>
       <c r="C3378" t="n">
-        <v>25.95</v>
+        <v>25.93</v>
       </c>
       <c r="D3378" t="inlineStr">
         <is>
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3379">
@@ -91647,7 +91647,7 @@
         <v>18</v>
       </c>
       <c r="C3379" t="n">
-        <v>24.76</v>
+        <v>24.75</v>
       </c>
       <c r="D3379" t="inlineStr">
         <is>
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3380">
@@ -91674,7 +91674,7 @@
         <v>19</v>
       </c>
       <c r="C3380" t="n">
-        <v>20.62</v>
+        <v>20.6</v>
       </c>
       <c r="D3380" t="inlineStr">
         <is>
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3381">
@@ -91701,7 +91701,7 @@
         <v>20</v>
       </c>
       <c r="C3381" t="n">
-        <v>31.24</v>
+        <v>31.23</v>
       </c>
       <c r="D3381" t="inlineStr">
         <is>
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3382">
@@ -91728,7 +91728,7 @@
         <v>21</v>
       </c>
       <c r="C3382" t="n">
-        <v>45.36</v>
+        <v>45.35</v>
       </c>
       <c r="D3382" t="inlineStr">
         <is>
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3383">
@@ -91755,7 +91755,7 @@
         <v>22</v>
       </c>
       <c r="C3383" t="n">
-        <v>47.85</v>
+        <v>47.83</v>
       </c>
       <c r="D3383" t="inlineStr">
         <is>
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3384">
@@ -91782,7 +91782,7 @@
         <v>23</v>
       </c>
       <c r="C3384" t="n">
-        <v>34.62</v>
+        <v>34.6</v>
       </c>
       <c r="D3384" t="inlineStr">
         <is>
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3385">
@@ -91809,7 +91809,7 @@
         <v>24</v>
       </c>
       <c r="C3385" t="n">
-        <v>24.96</v>
+        <v>24.95</v>
       </c>
       <c r="D3385" t="inlineStr">
         <is>
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3386">
@@ -91836,7 +91836,7 @@
         <v>1</v>
       </c>
       <c r="C3386" t="n">
-        <v>12.11</v>
+        <v>12.14</v>
       </c>
       <c r="D3386" t="inlineStr">
         <is>
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3387">
@@ -91863,7 +91863,7 @@
         <v>2</v>
       </c>
       <c r="C3387" t="n">
-        <v>13.17</v>
+        <v>13.22</v>
       </c>
       <c r="D3387" t="inlineStr">
         <is>
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3388">
@@ -91890,7 +91890,7 @@
         <v>3</v>
       </c>
       <c r="C3388" t="n">
-        <v>13.75</v>
+        <v>13.8</v>
       </c>
       <c r="D3388" t="inlineStr">
         <is>
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3389">
@@ -91917,7 +91917,7 @@
         <v>4</v>
       </c>
       <c r="C3389" t="n">
-        <v>15.24</v>
+        <v>15.25</v>
       </c>
       <c r="D3389" t="inlineStr">
         <is>
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3390">
@@ -91944,7 +91944,7 @@
         <v>5</v>
       </c>
       <c r="C3390" t="n">
-        <v>14.66</v>
+        <v>14.67</v>
       </c>
       <c r="D3390" t="inlineStr">
         <is>
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3391">
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3392">
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3393">
@@ -92025,7 +92025,7 @@
         <v>8</v>
       </c>
       <c r="C3393" t="n">
-        <v>37.57</v>
+        <v>37.55</v>
       </c>
       <c r="D3393" t="inlineStr">
         <is>
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3394">
@@ -92052,7 +92052,7 @@
         <v>9</v>
       </c>
       <c r="C3394" t="n">
-        <v>36.54</v>
+        <v>36.56</v>
       </c>
       <c r="D3394" t="inlineStr">
         <is>
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3395">
@@ -92079,7 +92079,7 @@
         <v>10</v>
       </c>
       <c r="C3395" t="n">
-        <v>19.7</v>
+        <v>19.78</v>
       </c>
       <c r="D3395" t="inlineStr">
         <is>
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3396">
@@ -92106,7 +92106,7 @@
         <v>11</v>
       </c>
       <c r="C3396" t="n">
-        <v>22.31</v>
+        <v>22.29</v>
       </c>
       <c r="D3396" t="inlineStr">
         <is>
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3397">
@@ -92133,7 +92133,7 @@
         <v>12</v>
       </c>
       <c r="C3397" t="n">
-        <v>22.91</v>
+        <v>22.88</v>
       </c>
       <c r="D3397" t="inlineStr">
         <is>
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3398">
@@ -92160,7 +92160,7 @@
         <v>13</v>
       </c>
       <c r="C3398" t="n">
-        <v>23.23</v>
+        <v>23.2</v>
       </c>
       <c r="D3398" t="inlineStr">
         <is>
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3399">
@@ -92187,7 +92187,7 @@
         <v>14</v>
       </c>
       <c r="C3399" t="n">
-        <v>22.78</v>
+        <v>22.77</v>
       </c>
       <c r="D3399" t="inlineStr">
         <is>
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3400">
@@ -92214,7 +92214,7 @@
         <v>15</v>
       </c>
       <c r="C3400" t="n">
-        <v>23.07</v>
+        <v>23.05</v>
       </c>
       <c r="D3400" t="inlineStr">
         <is>
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3401">
@@ -92241,7 +92241,7 @@
         <v>16</v>
       </c>
       <c r="C3401" t="n">
-        <v>23.77</v>
+        <v>23.76</v>
       </c>
       <c r="D3401" t="inlineStr">
         <is>
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3402">
@@ -92268,7 +92268,7 @@
         <v>17</v>
       </c>
       <c r="C3402" t="n">
-        <v>23.57</v>
+        <v>23.56</v>
       </c>
       <c r="D3402" t="inlineStr">
         <is>
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3403">
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3404">
@@ -92322,7 +92322,7 @@
         <v>19</v>
       </c>
       <c r="C3404" t="n">
-        <v>20.84</v>
+        <v>20.86</v>
       </c>
       <c r="D3404" t="inlineStr">
         <is>
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3405">
@@ -92349,7 +92349,7 @@
         <v>20</v>
       </c>
       <c r="C3405" t="n">
-        <v>24.85</v>
+        <v>24.9</v>
       </c>
       <c r="D3405" t="inlineStr">
         <is>
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3406">
@@ -92376,7 +92376,7 @@
         <v>21</v>
       </c>
       <c r="C3406" t="n">
-        <v>36.04</v>
+        <v>36.03</v>
       </c>
       <c r="D3406" t="inlineStr">
         <is>
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3407">
@@ -92403,7 +92403,7 @@
         <v>22</v>
       </c>
       <c r="C3407" t="n">
-        <v>38.61</v>
+        <v>38.58</v>
       </c>
       <c r="D3407" t="inlineStr">
         <is>
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3408">
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3409">
@@ -92457,7 +92457,7 @@
         <v>24</v>
       </c>
       <c r="C3409" t="n">
-        <v>25.12</v>
+        <v>25.16</v>
       </c>
       <c r="D3409" t="inlineStr">
         <is>
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3410">
@@ -92484,7 +92484,7 @@
         <v>1</v>
       </c>
       <c r="C3410" t="n">
-        <v>14.94</v>
+        <v>14.95</v>
       </c>
       <c r="D3410" t="inlineStr">
         <is>
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3411">
@@ -92511,7 +92511,7 @@
         <v>2</v>
       </c>
       <c r="C3411" t="n">
-        <v>16.87</v>
+        <v>16.86</v>
       </c>
       <c r="D3411" t="inlineStr">
         <is>
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3412">
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3413">
@@ -92565,7 +92565,7 @@
         <v>4</v>
       </c>
       <c r="C3413" t="n">
-        <v>13.21</v>
+        <v>13.3</v>
       </c>
       <c r="D3413" t="inlineStr">
         <is>
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3415">
@@ -92619,7 +92619,7 @@
         <v>6</v>
       </c>
       <c r="C3415" t="n">
-        <v>17.24</v>
+        <v>17.22</v>
       </c>
       <c r="D3415" t="inlineStr">
         <is>
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3416">
@@ -92646,7 +92646,7 @@
         <v>7</v>
       </c>
       <c r="C3416" t="n">
-        <v>17.32</v>
+        <v>17.34</v>
       </c>
       <c r="D3416" t="inlineStr">
         <is>
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3417">
@@ -92673,7 +92673,7 @@
         <v>8</v>
       </c>
       <c r="C3417" t="n">
-        <v>32.18</v>
+        <v>32.16</v>
       </c>
       <c r="D3417" t="inlineStr">
         <is>
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3418">
@@ -92700,7 +92700,7 @@
         <v>9</v>
       </c>
       <c r="C3418" t="n">
-        <v>45.49</v>
+        <v>45.5</v>
       </c>
       <c r="D3418" t="inlineStr">
         <is>
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3419">
@@ -92727,7 +92727,7 @@
         <v>10</v>
       </c>
       <c r="C3419" t="n">
-        <v>32.02</v>
+        <v>31.98</v>
       </c>
       <c r="D3419" t="inlineStr">
         <is>
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3420">
@@ -92754,7 +92754,7 @@
         <v>11</v>
       </c>
       <c r="C3420" t="n">
-        <v>25.93</v>
+        <v>25.88</v>
       </c>
       <c r="D3420" t="inlineStr">
         <is>
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3421">
@@ -92781,7 +92781,7 @@
         <v>12</v>
       </c>
       <c r="C3421" t="n">
-        <v>28.66</v>
+        <v>28.62</v>
       </c>
       <c r="D3421" t="inlineStr">
         <is>
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3422">
@@ -92808,7 +92808,7 @@
         <v>13</v>
       </c>
       <c r="C3422" t="n">
-        <v>31.76</v>
+        <v>31.73</v>
       </c>
       <c r="D3422" t="inlineStr">
         <is>
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3423">
@@ -92835,7 +92835,7 @@
         <v>14</v>
       </c>
       <c r="C3423" t="n">
-        <v>31.25</v>
+        <v>31.23</v>
       </c>
       <c r="D3423" t="inlineStr">
         <is>
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3424">
@@ -92862,7 +92862,7 @@
         <v>15</v>
       </c>
       <c r="C3424" t="n">
-        <v>31.21</v>
+        <v>31.18</v>
       </c>
       <c r="D3424" t="inlineStr">
         <is>
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3425">
@@ -92889,7 +92889,7 @@
         <v>16</v>
       </c>
       <c r="C3425" t="n">
-        <v>31.98</v>
+        <v>31.95</v>
       </c>
       <c r="D3425" t="inlineStr">
         <is>
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3426">
@@ -92916,7 +92916,7 @@
         <v>17</v>
       </c>
       <c r="C3426" t="n">
-        <v>31.41</v>
+        <v>31.38</v>
       </c>
       <c r="D3426" t="inlineStr">
         <is>
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3427">
@@ -92943,7 +92943,7 @@
         <v>18</v>
       </c>
       <c r="C3427" t="n">
-        <v>29.31</v>
+        <v>29.3</v>
       </c>
       <c r="D3427" t="inlineStr">
         <is>
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3428">
@@ -92970,7 +92970,7 @@
         <v>19</v>
       </c>
       <c r="C3428" t="n">
-        <v>26.38</v>
+        <v>26.36</v>
       </c>
       <c r="D3428" t="inlineStr">
         <is>
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3429">
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3430">
@@ -93024,7 +93024,7 @@
         <v>21</v>
       </c>
       <c r="C3430" t="n">
-        <v>36.4</v>
+        <v>36.39</v>
       </c>
       <c r="D3430" t="inlineStr">
         <is>
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3431">
@@ -93051,7 +93051,7 @@
         <v>22</v>
       </c>
       <c r="C3431" t="n">
-        <v>37.21</v>
+        <v>37.19</v>
       </c>
       <c r="D3431" t="inlineStr">
         <is>
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3432">
@@ -93078,7 +93078,7 @@
         <v>23</v>
       </c>
       <c r="C3432" t="n">
-        <v>23.42</v>
+        <v>23.41</v>
       </c>
       <c r="D3432" t="inlineStr">
         <is>
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3433">
@@ -93105,7 +93105,7 @@
         <v>24</v>
       </c>
       <c r="C3433" t="n">
-        <v>24.83</v>
+        <v>24.82</v>
       </c>
       <c r="D3433" t="inlineStr">
         <is>
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3434">
@@ -93132,7 +93132,7 @@
         <v>1</v>
       </c>
       <c r="C3434" t="n">
-        <v>13.23</v>
+        <v>13.19</v>
       </c>
       <c r="D3434" t="inlineStr">
         <is>
@@ -93148,7 +93148,7 @@
         <v>3</v>
       </c>
       <c r="G3434" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3435">
@@ -93159,7 +93159,7 @@
         <v>2</v>
       </c>
       <c r="C3435" t="n">
-        <v>12.92</v>
+        <v>12.96</v>
       </c>
       <c r="D3435" t="inlineStr">
         <is>
@@ -93175,7 +93175,7 @@
         <v>3</v>
       </c>
       <c r="G3435" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3436">
@@ -93186,7 +93186,7 @@
         <v>3</v>
       </c>
       <c r="C3436" t="n">
-        <v>15.49</v>
+        <v>15.53</v>
       </c>
       <c r="D3436" t="inlineStr">
         <is>
@@ -93202,7 +93202,7 @@
         <v>3</v>
       </c>
       <c r="G3436" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3437">
@@ -93213,7 +93213,7 @@
         <v>4</v>
       </c>
       <c r="C3437" t="n">
-        <v>16.83</v>
+        <v>16.79</v>
       </c>
       <c r="D3437" t="inlineStr">
         <is>
@@ -93229,7 +93229,7 @@
         <v>3</v>
       </c>
       <c r="G3437" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3438">
@@ -93240,7 +93240,7 @@
         <v>5</v>
       </c>
       <c r="C3438" t="n">
-        <v>15.28</v>
+        <v>15.29</v>
       </c>
       <c r="D3438" t="inlineStr">
         <is>
@@ -93256,7 +93256,7 @@
         <v>3</v>
       </c>
       <c r="G3438" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3439">
@@ -93267,7 +93267,7 @@
         <v>6</v>
       </c>
       <c r="C3439" t="n">
-        <v>23.2</v>
+        <v>23.17</v>
       </c>
       <c r="D3439" t="inlineStr">
         <is>
@@ -93283,7 +93283,7 @@
         <v>3</v>
       </c>
       <c r="G3439" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3440">
@@ -93294,7 +93294,7 @@
         <v>7</v>
       </c>
       <c r="C3440" t="n">
-        <v>28.69</v>
+        <v>28.58</v>
       </c>
       <c r="D3440" t="inlineStr">
         <is>
@@ -93310,7 +93310,7 @@
         <v>3</v>
       </c>
       <c r="G3440" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3441">
@@ -93321,7 +93321,7 @@
         <v>8</v>
       </c>
       <c r="C3441" t="n">
-        <v>57.52</v>
+        <v>57.28</v>
       </c>
       <c r="D3441" t="inlineStr">
         <is>
@@ -93337,7 +93337,7 @@
         <v>3</v>
       </c>
       <c r="G3441" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3442">
@@ -93348,7 +93348,7 @@
         <v>9</v>
       </c>
       <c r="C3442" t="n">
-        <v>53.26</v>
+        <v>53.24</v>
       </c>
       <c r="D3442" t="inlineStr">
         <is>
@@ -93364,7 +93364,7 @@
         <v>3</v>
       </c>
       <c r="G3442" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3443">
@@ -93375,7 +93375,7 @@
         <v>10</v>
       </c>
       <c r="C3443" t="n">
-        <v>30.01</v>
+        <v>29.97</v>
       </c>
       <c r="D3443" t="inlineStr">
         <is>
@@ -93391,7 +93391,7 @@
         <v>3</v>
       </c>
       <c r="G3443" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3444">
@@ -93402,7 +93402,7 @@
         <v>11</v>
       </c>
       <c r="C3444" t="n">
-        <v>26.8</v>
+        <v>26.76</v>
       </c>
       <c r="D3444" t="inlineStr">
         <is>
@@ -93418,7 +93418,7 @@
         <v>3</v>
       </c>
       <c r="G3444" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3445">
@@ -93429,7 +93429,7 @@
         <v>12</v>
       </c>
       <c r="C3445" t="n">
-        <v>31.3</v>
+        <v>31.26</v>
       </c>
       <c r="D3445" t="inlineStr">
         <is>
@@ -93445,7 +93445,7 @@
         <v>3</v>
       </c>
       <c r="G3445" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3446">
@@ -93456,7 +93456,7 @@
         <v>13</v>
       </c>
       <c r="C3446" t="n">
-        <v>30.95</v>
+        <v>30.88</v>
       </c>
       <c r="D3446" t="inlineStr">
         <is>
@@ -93472,7 +93472,7 @@
         <v>3</v>
       </c>
       <c r="G3446" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3447">
@@ -93483,7 +93483,7 @@
         <v>14</v>
       </c>
       <c r="C3447" t="n">
-        <v>30.95</v>
+        <v>30.89</v>
       </c>
       <c r="D3447" t="inlineStr">
         <is>
@@ -93499,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="G3447" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3448">
@@ -93510,7 +93510,7 @@
         <v>15</v>
       </c>
       <c r="C3448" t="n">
-        <v>30.97</v>
+        <v>30.85</v>
       </c>
       <c r="D3448" t="inlineStr">
         <is>
@@ -93526,7 +93526,7 @@
         <v>3</v>
       </c>
       <c r="G3448" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3449">
@@ -93537,7 +93537,7 @@
         <v>16</v>
       </c>
       <c r="C3449" t="n">
-        <v>31.79</v>
+        <v>31.78</v>
       </c>
       <c r="D3449" t="inlineStr">
         <is>
@@ -93553,7 +93553,7 @@
         <v>3</v>
       </c>
       <c r="G3449" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3450">
@@ -93564,7 +93564,7 @@
         <v>17</v>
       </c>
       <c r="C3450" t="n">
-        <v>29.75</v>
+        <v>29.73</v>
       </c>
       <c r="D3450" t="inlineStr">
         <is>
@@ -93580,7 +93580,7 @@
         <v>3</v>
       </c>
       <c r="G3450" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3451">
@@ -93607,7 +93607,7 @@
         <v>3</v>
       </c>
       <c r="G3451" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3452">
@@ -93634,7 +93634,7 @@
         <v>3</v>
       </c>
       <c r="G3452" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3453">
@@ -93661,7 +93661,7 @@
         <v>3</v>
       </c>
       <c r="G3453" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3454">
@@ -93672,7 +93672,7 @@
         <v>21</v>
       </c>
       <c r="C3454" t="n">
-        <v>47.27</v>
+        <v>47.17</v>
       </c>
       <c r="D3454" t="inlineStr">
         <is>
@@ -93688,7 +93688,7 @@
         <v>3</v>
       </c>
       <c r="G3454" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3455">
@@ -93699,7 +93699,7 @@
         <v>22</v>
       </c>
       <c r="C3455" t="n">
-        <v>47.97</v>
+        <v>47.87</v>
       </c>
       <c r="D3455" t="inlineStr">
         <is>
@@ -93715,7 +93715,7 @@
         <v>3</v>
       </c>
       <c r="G3455" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3456">
@@ -93726,7 +93726,7 @@
         <v>23</v>
       </c>
       <c r="C3456" t="n">
-        <v>34.27</v>
+        <v>34.21</v>
       </c>
       <c r="D3456" t="inlineStr">
         <is>
@@ -93742,7 +93742,7 @@
         <v>3</v>
       </c>
       <c r="G3456" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3457">
@@ -93753,7 +93753,7 @@
         <v>24</v>
       </c>
       <c r="C3457" t="n">
-        <v>27.51</v>
+        <v>27.38</v>
       </c>
       <c r="D3457" t="inlineStr">
         <is>
@@ -93769,7 +93769,7 @@
         <v>3</v>
       </c>
       <c r="G3457" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3458">
@@ -93796,7 +93796,7 @@
         <v>3</v>
       </c>
       <c r="G3458" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3459">
@@ -93823,7 +93823,7 @@
         <v>3</v>
       </c>
       <c r="G3459" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3460">
@@ -93850,7 +93850,7 @@
         <v>3</v>
       </c>
       <c r="G3460" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3461">
@@ -93877,7 +93877,7 @@
         <v>3</v>
       </c>
       <c r="G3461" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3462">
@@ -93904,7 +93904,7 @@
         <v>3</v>
       </c>
       <c r="G3462" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3463">
@@ -93931,7 +93931,7 @@
         <v>3</v>
       </c>
       <c r="G3463" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3464">
@@ -93958,7 +93958,7 @@
         <v>3</v>
       </c>
       <c r="G3464" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3465">
@@ -93985,7 +93985,7 @@
         <v>3</v>
       </c>
       <c r="G3465" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3466">
@@ -94012,7 +94012,7 @@
         <v>3</v>
       </c>
       <c r="G3466" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3467">
@@ -94039,7 +94039,7 @@
         <v>3</v>
       </c>
       <c r="G3467" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3468">
@@ -94066,7 +94066,7 @@
         <v>3</v>
       </c>
       <c r="G3468" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3469">
@@ -94077,7 +94077,7 @@
         <v>12</v>
       </c>
       <c r="C3469" t="n">
-        <v>32.79</v>
+        <v>32.78</v>
       </c>
       <c r="D3469" t="inlineStr">
         <is>
@@ -94093,7 +94093,7 @@
         <v>3</v>
       </c>
       <c r="G3469" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3470">
@@ -94120,7 +94120,7 @@
         <v>3</v>
       </c>
       <c r="G3470" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3471">
@@ -94147,7 +94147,7 @@
         <v>3</v>
       </c>
       <c r="G3471" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3472">
@@ -94174,7 +94174,7 @@
         <v>3</v>
       </c>
       <c r="G3472" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3473">
@@ -94201,7 +94201,7 @@
         <v>3</v>
       </c>
       <c r="G3473" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3474">
@@ -94212,7 +94212,7 @@
         <v>17</v>
       </c>
       <c r="C3474" t="n">
-        <v>28.22</v>
+        <v>28.21</v>
       </c>
       <c r="D3474" t="inlineStr">
         <is>
@@ -94228,7 +94228,7 @@
         <v>3</v>
       </c>
       <c r="G3474" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3475">
@@ -94255,7 +94255,7 @@
         <v>3</v>
       </c>
       <c r="G3475" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3476">
@@ -94282,7 +94282,7 @@
         <v>3</v>
       </c>
       <c r="G3476" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3477">
@@ -94309,7 +94309,7 @@
         <v>3</v>
       </c>
       <c r="G3477" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3478">
@@ -94336,7 +94336,7 @@
         <v>3</v>
       </c>
       <c r="G3478" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3479">
@@ -94363,7 +94363,7 @@
         <v>3</v>
       </c>
       <c r="G3479" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3480">
@@ -94390,7 +94390,7 @@
         <v>3</v>
       </c>
       <c r="G3480" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3481">
@@ -94417,7 +94417,7 @@
         <v>3</v>
       </c>
       <c r="G3481" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3482">
@@ -94444,7 +94444,7 @@
         <v>3</v>
       </c>
       <c r="G3482" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3483">
@@ -94471,7 +94471,7 @@
         <v>3</v>
       </c>
       <c r="G3483" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3484">
@@ -94498,7 +94498,7 @@
         <v>3</v>
       </c>
       <c r="G3484" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3485">
@@ -94525,7 +94525,7 @@
         <v>3</v>
       </c>
       <c r="G3485" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3486">
@@ -94552,7 +94552,7 @@
         <v>3</v>
       </c>
       <c r="G3486" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3487">
@@ -94579,7 +94579,7 @@
         <v>3</v>
       </c>
       <c r="G3487" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3488">
@@ -94606,7 +94606,7 @@
         <v>3</v>
       </c>
       <c r="G3488" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3489">
@@ -94633,7 +94633,7 @@
         <v>3</v>
       </c>
       <c r="G3489" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3490">
@@ -94660,7 +94660,7 @@
         <v>3</v>
       </c>
       <c r="G3490" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3491">
@@ -94687,7 +94687,7 @@
         <v>3</v>
       </c>
       <c r="G3491" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3492">
@@ -94714,7 +94714,7 @@
         <v>3</v>
       </c>
       <c r="G3492" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3493">
@@ -94741,7 +94741,7 @@
         <v>3</v>
       </c>
       <c r="G3493" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3494">
@@ -94768,7 +94768,7 @@
         <v>3</v>
       </c>
       <c r="G3494" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3495">
@@ -94795,7 +94795,7 @@
         <v>3</v>
       </c>
       <c r="G3495" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3496">
@@ -94822,7 +94822,7 @@
         <v>3</v>
       </c>
       <c r="G3496" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3497">
@@ -94849,7 +94849,7 @@
         <v>3</v>
       </c>
       <c r="G3497" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3498">
@@ -94876,7 +94876,7 @@
         <v>3</v>
       </c>
       <c r="G3498" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3499">
@@ -94903,7 +94903,7 @@
         <v>3</v>
       </c>
       <c r="G3499" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3500">
@@ -94930,7 +94930,7 @@
         <v>3</v>
       </c>
       <c r="G3500" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3501">
@@ -94957,7 +94957,7 @@
         <v>3</v>
       </c>
       <c r="G3501" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3502">
@@ -94984,7 +94984,7 @@
         <v>3</v>
       </c>
       <c r="G3502" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3503">
@@ -95011,7 +95011,7 @@
         <v>3</v>
       </c>
       <c r="G3503" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3504">
@@ -95038,7 +95038,7 @@
         <v>3</v>
       </c>
       <c r="G3504" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3505">
@@ -95065,7 +95065,7 @@
         <v>3</v>
       </c>
       <c r="G3505" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3506">
@@ -95076,7 +95076,7 @@
         <v>1</v>
       </c>
       <c r="C3506" t="n">
-        <v>7.5</v>
+        <v>7.62</v>
       </c>
       <c r="D3506" t="inlineStr">
         <is>
@@ -95092,7 +95092,7 @@
         <v>3</v>
       </c>
       <c r="G3506" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3507">
@@ -95103,7 +95103,7 @@
         <v>2</v>
       </c>
       <c r="C3507" t="n">
-        <v>8.69</v>
+        <v>8.5</v>
       </c>
       <c r="D3507" t="inlineStr">
         <is>
@@ -95119,7 +95119,7 @@
         <v>3</v>
       </c>
       <c r="G3507" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3508">
@@ -95146,7 +95146,7 @@
         <v>3</v>
       </c>
       <c r="G3508" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3509">
@@ -95157,7 +95157,7 @@
         <v>4</v>
       </c>
       <c r="C3509" t="n">
-        <v>11.51</v>
+        <v>12.08</v>
       </c>
       <c r="D3509" t="inlineStr">
         <is>
@@ -95173,7 +95173,7 @@
         <v>3</v>
       </c>
       <c r="G3509" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3510">
@@ -95184,7 +95184,7 @@
         <v>5</v>
       </c>
       <c r="C3510" t="n">
-        <v>12.71</v>
+        <v>12.32</v>
       </c>
       <c r="D3510" t="inlineStr">
         <is>
@@ -95200,7 +95200,7 @@
         <v>3</v>
       </c>
       <c r="G3510" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3511">
@@ -95211,7 +95211,7 @@
         <v>6</v>
       </c>
       <c r="C3511" t="n">
-        <v>12.96</v>
+        <v>12.7</v>
       </c>
       <c r="D3511" t="inlineStr">
         <is>
@@ -95227,7 +95227,7 @@
         <v>3</v>
       </c>
       <c r="G3511" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3512">
@@ -95238,7 +95238,7 @@
         <v>7</v>
       </c>
       <c r="C3512" t="n">
-        <v>23.13</v>
+        <v>25.44</v>
       </c>
       <c r="D3512" t="inlineStr">
         <is>
@@ -95254,7 +95254,7 @@
         <v>3</v>
       </c>
       <c r="G3512" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3513">
@@ -95265,7 +95265,7 @@
         <v>8</v>
       </c>
       <c r="C3513" t="n">
-        <v>36.87</v>
+        <v>40.29</v>
       </c>
       <c r="D3513" t="inlineStr">
         <is>
@@ -95281,7 +95281,7 @@
         <v>3</v>
       </c>
       <c r="G3513" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3514">
@@ -95292,7 +95292,7 @@
         <v>9</v>
       </c>
       <c r="C3514" t="n">
-        <v>34.48</v>
+        <v>36.96</v>
       </c>
       <c r="D3514" t="inlineStr">
         <is>
@@ -95308,7 +95308,7 @@
         <v>3</v>
       </c>
       <c r="G3514" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3515">
@@ -95319,7 +95319,7 @@
         <v>10</v>
       </c>
       <c r="C3515" t="n">
-        <v>25.3</v>
+        <v>27.02</v>
       </c>
       <c r="D3515" t="inlineStr">
         <is>
@@ -95335,7 +95335,7 @@
         <v>3</v>
       </c>
       <c r="G3515" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3516">
@@ -95346,7 +95346,7 @@
         <v>11</v>
       </c>
       <c r="C3516" t="n">
-        <v>24.66</v>
+        <v>25.15</v>
       </c>
       <c r="D3516" t="inlineStr">
         <is>
@@ -95362,7 +95362,7 @@
         <v>3</v>
       </c>
       <c r="G3516" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3517">
@@ -95373,7 +95373,7 @@
         <v>12</v>
       </c>
       <c r="C3517" t="n">
-        <v>29.13</v>
+        <v>29.46</v>
       </c>
       <c r="D3517" t="inlineStr">
         <is>
@@ -95389,7 +95389,7 @@
         <v>3</v>
       </c>
       <c r="G3517" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3518">
@@ -95400,7 +95400,7 @@
         <v>13</v>
       </c>
       <c r="C3518" t="n">
-        <v>24.38</v>
+        <v>25.92</v>
       </c>
       <c r="D3518" t="inlineStr">
         <is>
@@ -95416,7 +95416,7 @@
         <v>3</v>
       </c>
       <c r="G3518" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3519">
@@ -95427,7 +95427,7 @@
         <v>14</v>
       </c>
       <c r="C3519" t="n">
-        <v>31.74</v>
+        <v>31.22</v>
       </c>
       <c r="D3519" t="inlineStr">
         <is>
@@ -95443,7 +95443,7 @@
         <v>3</v>
       </c>
       <c r="G3519" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3520">
@@ -95454,7 +95454,7 @@
         <v>15</v>
       </c>
       <c r="C3520" t="n">
-        <v>32.53</v>
+        <v>26.46</v>
       </c>
       <c r="D3520" t="inlineStr">
         <is>
@@ -95470,7 +95470,7 @@
         <v>3</v>
       </c>
       <c r="G3520" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3521">
@@ -95481,7 +95481,7 @@
         <v>16</v>
       </c>
       <c r="C3521" t="n">
-        <v>33.49</v>
+        <v>30.83</v>
       </c>
       <c r="D3521" t="inlineStr">
         <is>
@@ -95497,7 +95497,7 @@
         <v>3</v>
       </c>
       <c r="G3521" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3522">
@@ -95508,7 +95508,7 @@
         <v>17</v>
       </c>
       <c r="C3522" t="n">
-        <v>29.89</v>
+        <v>30.34</v>
       </c>
       <c r="D3522" t="inlineStr">
         <is>
@@ -95524,7 +95524,7 @@
         <v>3</v>
       </c>
       <c r="G3522" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3523">
@@ -95535,7 +95535,7 @@
         <v>18</v>
       </c>
       <c r="C3523" t="n">
-        <v>27.09</v>
+        <v>25.4</v>
       </c>
       <c r="D3523" t="inlineStr">
         <is>
@@ -95551,7 +95551,7 @@
         <v>3</v>
       </c>
       <c r="G3523" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3524">
@@ -95562,7 +95562,7 @@
         <v>19</v>
       </c>
       <c r="C3524" t="n">
-        <v>27.53</v>
+        <v>27.75</v>
       </c>
       <c r="D3524" t="inlineStr">
         <is>
@@ -95578,7 +95578,7 @@
         <v>3</v>
       </c>
       <c r="G3524" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3525">
@@ -95589,7 +95589,7 @@
         <v>20</v>
       </c>
       <c r="C3525" t="n">
-        <v>23.05</v>
+        <v>26.58</v>
       </c>
       <c r="D3525" t="inlineStr">
         <is>
@@ -95605,7 +95605,7 @@
         <v>3</v>
       </c>
       <c r="G3525" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3526">
@@ -95616,7 +95616,7 @@
         <v>21</v>
       </c>
       <c r="C3526" t="n">
-        <v>23.7</v>
+        <v>35.43</v>
       </c>
       <c r="D3526" t="inlineStr">
         <is>
@@ -95632,7 +95632,7 @@
         <v>3</v>
       </c>
       <c r="G3526" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3527">
@@ -95643,7 +95643,7 @@
         <v>22</v>
       </c>
       <c r="C3527" t="n">
-        <v>25.53</v>
+        <v>34.35</v>
       </c>
       <c r="D3527" t="inlineStr">
         <is>
@@ -95659,7 +95659,7 @@
         <v>3</v>
       </c>
       <c r="G3527" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3528">
@@ -95670,7 +95670,7 @@
         <v>23</v>
       </c>
       <c r="C3528" t="n">
-        <v>27.01</v>
+        <v>27.99</v>
       </c>
       <c r="D3528" t="inlineStr">
         <is>
@@ -95686,7 +95686,7 @@
         <v>3</v>
       </c>
       <c r="G3528" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3529">
@@ -95697,7 +95697,7 @@
         <v>24</v>
       </c>
       <c r="C3529" t="n">
-        <v>22.37</v>
+        <v>23.07</v>
       </c>
       <c r="D3529" t="inlineStr">
         <is>
@@ -95713,7 +95713,7 @@
         <v>3</v>
       </c>
       <c r="G3529" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3530">
@@ -95724,7 +95724,7 @@
         <v>1</v>
       </c>
       <c r="C3530" t="n">
-        <v>19.15</v>
+        <v>15.1</v>
       </c>
       <c r="D3530" t="inlineStr">
         <is>
@@ -95740,7 +95740,7 @@
         <v>3</v>
       </c>
       <c r="G3530" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3531">
@@ -95751,7 +95751,7 @@
         <v>2</v>
       </c>
       <c r="C3531" t="n">
-        <v>21.29</v>
+        <v>17.08</v>
       </c>
       <c r="D3531" t="inlineStr">
         <is>
@@ -95767,7 +95767,7 @@
         <v>3</v>
       </c>
       <c r="G3531" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3532">
@@ -95794,7 +95794,7 @@
         <v>3</v>
       </c>
       <c r="G3532" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3533">
@@ -95821,7 +95821,7 @@
         <v>3</v>
       </c>
       <c r="G3533" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3534">
@@ -95848,7 +95848,7 @@
         <v>3</v>
       </c>
       <c r="G3534" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3535">
@@ -95859,7 +95859,7 @@
         <v>6</v>
       </c>
       <c r="C3535" t="n">
-        <v>13.74</v>
+        <v>12.65</v>
       </c>
       <c r="D3535" t="inlineStr">
         <is>
@@ -95875,7 +95875,7 @@
         <v>3</v>
       </c>
       <c r="G3535" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3536">
@@ -95886,7 +95886,7 @@
         <v>7</v>
       </c>
       <c r="C3536" t="n">
-        <v>27.18</v>
+        <v>18.41</v>
       </c>
       <c r="D3536" t="inlineStr">
         <is>
@@ -95902,7 +95902,7 @@
         <v>3</v>
       </c>
       <c r="G3536" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3537">
@@ -95913,7 +95913,7 @@
         <v>8</v>
       </c>
       <c r="C3537" t="n">
-        <v>43.77</v>
+        <v>19.68</v>
       </c>
       <c r="D3537" t="inlineStr">
         <is>
@@ -95929,7 +95929,7 @@
         <v>3</v>
       </c>
       <c r="G3537" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3538">
@@ -95940,7 +95940,7 @@
         <v>9</v>
       </c>
       <c r="C3538" t="n">
-        <v>39.64</v>
+        <v>16.72</v>
       </c>
       <c r="D3538" t="inlineStr">
         <is>
@@ -95956,7 +95956,7 @@
         <v>3</v>
       </c>
       <c r="G3538" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3539">
@@ -95967,7 +95967,7 @@
         <v>10</v>
       </c>
       <c r="C3539" t="n">
-        <v>21.63</v>
+        <v>17.9</v>
       </c>
       <c r="D3539" t="inlineStr">
         <is>
@@ -95983,7 +95983,7 @@
         <v>3</v>
       </c>
       <c r="G3539" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3540">
@@ -95994,7 +95994,7 @@
         <v>11</v>
       </c>
       <c r="C3540" t="n">
-        <v>22.18</v>
+        <v>19.27</v>
       </c>
       <c r="D3540" t="inlineStr">
         <is>
@@ -96010,7 +96010,7 @@
         <v>3</v>
       </c>
       <c r="G3540" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3541">
@@ -96021,7 +96021,7 @@
         <v>12</v>
       </c>
       <c r="C3541" t="n">
-        <v>25.9</v>
+        <v>22.99</v>
       </c>
       <c r="D3541" t="inlineStr">
         <is>
@@ -96037,7 +96037,7 @@
         <v>3</v>
       </c>
       <c r="G3541" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3542">
@@ -96048,7 +96048,7 @@
         <v>13</v>
       </c>
       <c r="C3542" t="n">
-        <v>27.78</v>
+        <v>25.12</v>
       </c>
       <c r="D3542" t="inlineStr">
         <is>
@@ -96064,7 +96064,7 @@
         <v>3</v>
       </c>
       <c r="G3542" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3543">
@@ -96075,7 +96075,7 @@
         <v>14</v>
       </c>
       <c r="C3543" t="n">
-        <v>28.21</v>
+        <v>25.43</v>
       </c>
       <c r="D3543" t="inlineStr">
         <is>
@@ -96091,7 +96091,7 @@
         <v>3</v>
       </c>
       <c r="G3543" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3544">
@@ -96102,7 +96102,7 @@
         <v>15</v>
       </c>
       <c r="C3544" t="n">
-        <v>28.1</v>
+        <v>25.32</v>
       </c>
       <c r="D3544" t="inlineStr">
         <is>
@@ -96118,7 +96118,7 @@
         <v>3</v>
       </c>
       <c r="G3544" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3545">
@@ -96129,7 +96129,7 @@
         <v>16</v>
       </c>
       <c r="C3545" t="n">
-        <v>27.33</v>
+        <v>24.39</v>
       </c>
       <c r="D3545" t="inlineStr">
         <is>
@@ -96145,7 +96145,7 @@
         <v>3</v>
       </c>
       <c r="G3545" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3546">
@@ -96156,7 +96156,7 @@
         <v>17</v>
       </c>
       <c r="C3546" t="n">
-        <v>24.21</v>
+        <v>21.08</v>
       </c>
       <c r="D3546" t="inlineStr">
         <is>
@@ -96172,7 +96172,7 @@
         <v>3</v>
       </c>
       <c r="G3546" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3547">
@@ -96183,7 +96183,7 @@
         <v>18</v>
       </c>
       <c r="C3547" t="n">
-        <v>21.13</v>
+        <v>18.01</v>
       </c>
       <c r="D3547" t="inlineStr">
         <is>
@@ -96199,7 +96199,7 @@
         <v>3</v>
       </c>
       <c r="G3547" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3548">
@@ -96210,7 +96210,7 @@
         <v>19</v>
       </c>
       <c r="C3548" t="n">
-        <v>27.32</v>
+        <v>22.9</v>
       </c>
       <c r="D3548" t="inlineStr">
         <is>
@@ -96226,7 +96226,7 @@
         <v>3</v>
       </c>
       <c r="G3548" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3549">
@@ -96237,7 +96237,7 @@
         <v>20</v>
       </c>
       <c r="C3549" t="n">
-        <v>43.21</v>
+        <v>24.24</v>
       </c>
       <c r="D3549" t="inlineStr">
         <is>
@@ -96253,7 +96253,7 @@
         <v>3</v>
       </c>
       <c r="G3549" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3550">
@@ -96264,7 +96264,7 @@
         <v>21</v>
       </c>
       <c r="C3550" t="n">
-        <v>42.92</v>
+        <v>14.79</v>
       </c>
       <c r="D3550" t="inlineStr">
         <is>
@@ -96280,7 +96280,7 @@
         <v>3</v>
       </c>
       <c r="G3550" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3551">
@@ -96291,7 +96291,7 @@
         <v>22</v>
       </c>
       <c r="C3551" t="n">
-        <v>36.04</v>
+        <v>14.68</v>
       </c>
       <c r="D3551" t="inlineStr">
         <is>
@@ -96307,7 +96307,7 @@
         <v>3</v>
       </c>
       <c r="G3551" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3552">
@@ -96318,7 +96318,7 @@
         <v>23</v>
       </c>
       <c r="C3552" t="n">
-        <v>27.14</v>
+        <v>12.74</v>
       </c>
       <c r="D3552" t="inlineStr">
         <is>
@@ -96334,7 +96334,7 @@
         <v>3</v>
       </c>
       <c r="G3552" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
       </c>
     </row>
     <row r="3553">
@@ -96345,7 +96345,7 @@
         <v>24</v>
       </c>
       <c r="C3553" t="n">
-        <v>23.39</v>
+        <v>13.09</v>
       </c>
       <c r="D3553" t="inlineStr">
         <is>
@@ -96361,7 +96361,655 @@
         <v>3</v>
       </c>
       <c r="G3553" s="2" t="n">
-        <v>46291.45404645446</v>
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3554">
+      <c r="A3554" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3554" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3554" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="D3554" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3554" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3554" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3554" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3555">
+      <c r="A3555" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3555" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3555" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="D3555" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3555" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3555" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3555" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3556">
+      <c r="A3556" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3556" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3556" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="D3556" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3556" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3556" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3556" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3557">
+      <c r="A3557" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3557" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3557" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="D3557" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3557" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3557" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3557" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3558">
+      <c r="A3558" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3558" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3558" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="D3558" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3558" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3558" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3558" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3559">
+      <c r="A3559" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3559" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3559" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="D3559" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3559" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3559" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3559" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3560">
+      <c r="A3560" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3560" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3560" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="D3560" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3560" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3560" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3560" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3561">
+      <c r="A3561" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3561" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3561" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="D3561" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3561" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3561" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3561" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3562">
+      <c r="A3562" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3562" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3562" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="D3562" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3562" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3562" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3562" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3563">
+      <c r="A3563" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3563" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3563" t="n">
+        <v>28.51</v>
+      </c>
+      <c r="D3563" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3563" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3563" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3563" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3564">
+      <c r="A3564" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3564" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3564" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="D3564" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3564" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3564" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3564" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3565">
+      <c r="A3565" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3565" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3565" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="D3565" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3565" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3565" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3565" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3566">
+      <c r="A3566" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3566" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3566" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D3566" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3566" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3566" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3566" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3567">
+      <c r="A3567" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3567" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3567" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="D3567" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3567" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3567" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3567" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3568">
+      <c r="A3568" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3568" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3568" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="D3568" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3568" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3568" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3568" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3569">
+      <c r="A3569" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3569" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3569" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="D3569" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3569" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3569" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3569" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3570">
+      <c r="A3570" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3570" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3570" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="D3570" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3570" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3570" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3570" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3571">
+      <c r="A3571" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3571" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3571" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="D3571" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3571" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3571" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3571" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3572">
+      <c r="A3572" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3572" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3572" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="D3572" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3572" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3572" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3572" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3573">
+      <c r="A3573" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3573" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3573" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="D3573" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3573" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3573" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3573" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3574">
+      <c r="A3574" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3574" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3574" t="n">
+        <v>60.53</v>
+      </c>
+      <c r="D3574" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3574" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3574" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3574" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3575">
+      <c r="A3575" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3575" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3575" t="n">
+        <v>53.21</v>
+      </c>
+      <c r="D3575" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3575" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3575" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3575" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3576">
+      <c r="A3576" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3576" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3576" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="D3576" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3576" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3576" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3576" s="2" t="n">
+        <v>46291.863521075</v>
+      </c>
+    </row>
+    <row r="3577">
+      <c r="A3577" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3577" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3577" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="D3577" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3577" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3577" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3577" s="2" t="n">
+        <v>46291.863521075</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3324">
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3333">
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3335">
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3337">
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3341">
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3343">
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3344">
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3345">
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3346">
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3347">
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3355">
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3356">
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3357">
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3360">
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3362">
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3364">
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3365">
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3366">
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3367">
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3368">
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3369">
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3370">
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3371">
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3372">
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3373">
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3374">
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3375">
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3376">
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3377">
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3378">
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3379">
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3380">
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3381">
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3382">
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3383">
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3384">
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3385">
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3386">
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3387">
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3388">
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3389">
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3390">
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3391">
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3392">
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3393">
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3394">
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3395">
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3396">
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3397">
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3398">
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3399">
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3400">
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3401">
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3402">
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3403">
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3404">
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3405">
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3406">
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3407">
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3408">
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3409">
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3410">
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3411">
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3412">
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3413">
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3415">
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3416">
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3417">
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3418">
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3419">
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3420">
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3421">
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3422">
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3423">
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3424">
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3425">
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3426">
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3427">
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3428">
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3429">
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3430">
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3431">
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3432">
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3433">
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3434">
@@ -93148,7 +93148,7 @@
         <v>3</v>
       </c>
       <c r="G3434" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3435">
@@ -93175,7 +93175,7 @@
         <v>3</v>
       </c>
       <c r="G3435" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3436">
@@ -93202,7 +93202,7 @@
         <v>3</v>
       </c>
       <c r="G3436" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3437">
@@ -93229,7 +93229,7 @@
         <v>3</v>
       </c>
       <c r="G3437" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3438">
@@ -93256,7 +93256,7 @@
         <v>3</v>
       </c>
       <c r="G3438" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3439">
@@ -93283,7 +93283,7 @@
         <v>3</v>
       </c>
       <c r="G3439" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3440">
@@ -93310,7 +93310,7 @@
         <v>3</v>
       </c>
       <c r="G3440" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3441">
@@ -93337,7 +93337,7 @@
         <v>3</v>
       </c>
       <c r="G3441" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3442">
@@ -93364,7 +93364,7 @@
         <v>3</v>
       </c>
       <c r="G3442" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3443">
@@ -93391,7 +93391,7 @@
         <v>3</v>
       </c>
       <c r="G3443" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3444">
@@ -93418,7 +93418,7 @@
         <v>3</v>
       </c>
       <c r="G3444" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3445">
@@ -93445,7 +93445,7 @@
         <v>3</v>
       </c>
       <c r="G3445" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3446">
@@ -93472,7 +93472,7 @@
         <v>3</v>
       </c>
       <c r="G3446" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3447">
@@ -93499,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="G3447" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3448">
@@ -93526,7 +93526,7 @@
         <v>3</v>
       </c>
       <c r="G3448" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3449">
@@ -93553,7 +93553,7 @@
         <v>3</v>
       </c>
       <c r="G3449" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3450">
@@ -93580,7 +93580,7 @@
         <v>3</v>
       </c>
       <c r="G3450" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3451">
@@ -93607,7 +93607,7 @@
         <v>3</v>
       </c>
       <c r="G3451" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3452">
@@ -93634,7 +93634,7 @@
         <v>3</v>
       </c>
       <c r="G3452" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3453">
@@ -93661,7 +93661,7 @@
         <v>3</v>
       </c>
       <c r="G3453" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3454">
@@ -93688,7 +93688,7 @@
         <v>3</v>
       </c>
       <c r="G3454" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3455">
@@ -93715,7 +93715,7 @@
         <v>3</v>
       </c>
       <c r="G3455" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3456">
@@ -93742,7 +93742,7 @@
         <v>3</v>
       </c>
       <c r="G3456" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3457">
@@ -93769,7 +93769,7 @@
         <v>3</v>
       </c>
       <c r="G3457" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3458">
@@ -93796,7 +93796,7 @@
         <v>3</v>
       </c>
       <c r="G3458" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3459">
@@ -93823,7 +93823,7 @@
         <v>3</v>
       </c>
       <c r="G3459" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3460">
@@ -93850,7 +93850,7 @@
         <v>3</v>
       </c>
       <c r="G3460" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3461">
@@ -93877,7 +93877,7 @@
         <v>3</v>
       </c>
       <c r="G3461" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3462">
@@ -93904,7 +93904,7 @@
         <v>3</v>
       </c>
       <c r="G3462" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3463">
@@ -93931,7 +93931,7 @@
         <v>3</v>
       </c>
       <c r="G3463" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3464">
@@ -93958,7 +93958,7 @@
         <v>3</v>
       </c>
       <c r="G3464" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3465">
@@ -93985,7 +93985,7 @@
         <v>3</v>
       </c>
       <c r="G3465" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3466">
@@ -94012,7 +94012,7 @@
         <v>3</v>
       </c>
       <c r="G3466" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3467">
@@ -94039,7 +94039,7 @@
         <v>3</v>
       </c>
       <c r="G3467" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3468">
@@ -94066,7 +94066,7 @@
         <v>3</v>
       </c>
       <c r="G3468" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3469">
@@ -94093,7 +94093,7 @@
         <v>3</v>
       </c>
       <c r="G3469" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3470">
@@ -94120,7 +94120,7 @@
         <v>3</v>
       </c>
       <c r="G3470" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3471">
@@ -94147,7 +94147,7 @@
         <v>3</v>
       </c>
       <c r="G3471" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3472">
@@ -94174,7 +94174,7 @@
         <v>3</v>
       </c>
       <c r="G3472" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3473">
@@ -94201,7 +94201,7 @@
         <v>3</v>
       </c>
       <c r="G3473" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3474">
@@ -94228,7 +94228,7 @@
         <v>3</v>
       </c>
       <c r="G3474" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3475">
@@ -94255,7 +94255,7 @@
         <v>3</v>
       </c>
       <c r="G3475" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3476">
@@ -94282,7 +94282,7 @@
         <v>3</v>
       </c>
       <c r="G3476" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3477">
@@ -94309,7 +94309,7 @@
         <v>3</v>
       </c>
       <c r="G3477" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3478">
@@ -94336,7 +94336,7 @@
         <v>3</v>
       </c>
       <c r="G3478" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3479">
@@ -94363,7 +94363,7 @@
         <v>3</v>
       </c>
       <c r="G3479" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3480">
@@ -94390,7 +94390,7 @@
         <v>3</v>
       </c>
       <c r="G3480" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3481">
@@ -94417,7 +94417,7 @@
         <v>3</v>
       </c>
       <c r="G3481" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3482">
@@ -94444,7 +94444,7 @@
         <v>3</v>
       </c>
       <c r="G3482" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3483">
@@ -94471,7 +94471,7 @@
         <v>3</v>
       </c>
       <c r="G3483" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3484">
@@ -94498,7 +94498,7 @@
         <v>3</v>
       </c>
       <c r="G3484" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3485">
@@ -94525,7 +94525,7 @@
         <v>3</v>
       </c>
       <c r="G3485" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3486">
@@ -94552,7 +94552,7 @@
         <v>3</v>
       </c>
       <c r="G3486" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3487">
@@ -94579,7 +94579,7 @@
         <v>3</v>
       </c>
       <c r="G3487" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3488">
@@ -94606,7 +94606,7 @@
         <v>3</v>
       </c>
       <c r="G3488" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3489">
@@ -94633,7 +94633,7 @@
         <v>3</v>
       </c>
       <c r="G3489" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3490">
@@ -94660,7 +94660,7 @@
         <v>3</v>
       </c>
       <c r="G3490" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3491">
@@ -94687,7 +94687,7 @@
         <v>3</v>
       </c>
       <c r="G3491" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3492">
@@ -94714,7 +94714,7 @@
         <v>3</v>
       </c>
       <c r="G3492" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3493">
@@ -94741,7 +94741,7 @@
         <v>3</v>
       </c>
       <c r="G3493" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3494">
@@ -94768,7 +94768,7 @@
         <v>3</v>
       </c>
       <c r="G3494" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3495">
@@ -94795,7 +94795,7 @@
         <v>3</v>
       </c>
       <c r="G3495" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3496">
@@ -94822,7 +94822,7 @@
         <v>3</v>
       </c>
       <c r="G3496" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3497">
@@ -94849,7 +94849,7 @@
         <v>3</v>
       </c>
       <c r="G3497" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3498">
@@ -94876,7 +94876,7 @@
         <v>3</v>
       </c>
       <c r="G3498" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3499">
@@ -94903,7 +94903,7 @@
         <v>3</v>
       </c>
       <c r="G3499" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3500">
@@ -94930,7 +94930,7 @@
         <v>3</v>
       </c>
       <c r="G3500" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3501">
@@ -94957,7 +94957,7 @@
         <v>3</v>
       </c>
       <c r="G3501" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3502">
@@ -94984,7 +94984,7 @@
         <v>3</v>
       </c>
       <c r="G3502" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3503">
@@ -95011,7 +95011,7 @@
         <v>3</v>
       </c>
       <c r="G3503" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3504">
@@ -95038,7 +95038,7 @@
         <v>3</v>
       </c>
       <c r="G3504" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3505">
@@ -95065,7 +95065,7 @@
         <v>3</v>
       </c>
       <c r="G3505" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3506">
@@ -95092,7 +95092,7 @@
         <v>3</v>
       </c>
       <c r="G3506" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3507">
@@ -95119,7 +95119,7 @@
         <v>3</v>
       </c>
       <c r="G3507" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3508">
@@ -95146,7 +95146,7 @@
         <v>3</v>
       </c>
       <c r="G3508" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3509">
@@ -95173,7 +95173,7 @@
         <v>3</v>
       </c>
       <c r="G3509" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3510">
@@ -95200,7 +95200,7 @@
         <v>3</v>
       </c>
       <c r="G3510" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3511">
@@ -95227,7 +95227,7 @@
         <v>3</v>
       </c>
       <c r="G3511" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3512">
@@ -95254,7 +95254,7 @@
         <v>3</v>
       </c>
       <c r="G3512" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3513">
@@ -95281,7 +95281,7 @@
         <v>3</v>
       </c>
       <c r="G3513" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3514">
@@ -95308,7 +95308,7 @@
         <v>3</v>
       </c>
       <c r="G3514" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3515">
@@ -95335,7 +95335,7 @@
         <v>3</v>
       </c>
       <c r="G3515" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3516">
@@ -95362,7 +95362,7 @@
         <v>3</v>
       </c>
       <c r="G3516" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3517">
@@ -95389,7 +95389,7 @@
         <v>3</v>
       </c>
       <c r="G3517" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3518">
@@ -95416,7 +95416,7 @@
         <v>3</v>
       </c>
       <c r="G3518" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3519">
@@ -95443,7 +95443,7 @@
         <v>3</v>
       </c>
       <c r="G3519" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3520">
@@ -95470,7 +95470,7 @@
         <v>3</v>
       </c>
       <c r="G3520" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3521">
@@ -95497,7 +95497,7 @@
         <v>3</v>
       </c>
       <c r="G3521" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3522">
@@ -95524,7 +95524,7 @@
         <v>3</v>
       </c>
       <c r="G3522" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3523">
@@ -95551,7 +95551,7 @@
         <v>3</v>
       </c>
       <c r="G3523" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3524">
@@ -95578,7 +95578,7 @@
         <v>3</v>
       </c>
       <c r="G3524" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3525">
@@ -95605,7 +95605,7 @@
         <v>3</v>
       </c>
       <c r="G3525" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3526">
@@ -95632,7 +95632,7 @@
         <v>3</v>
       </c>
       <c r="G3526" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3527">
@@ -95659,7 +95659,7 @@
         <v>3</v>
       </c>
       <c r="G3527" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3528">
@@ -95686,7 +95686,7 @@
         <v>3</v>
       </c>
       <c r="G3528" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3529">
@@ -95713,7 +95713,7 @@
         <v>3</v>
       </c>
       <c r="G3529" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3530">
@@ -95740,7 +95740,7 @@
         <v>3</v>
       </c>
       <c r="G3530" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3531">
@@ -95767,7 +95767,7 @@
         <v>3</v>
       </c>
       <c r="G3531" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3532">
@@ -95794,7 +95794,7 @@
         <v>3</v>
       </c>
       <c r="G3532" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3533">
@@ -95821,7 +95821,7 @@
         <v>3</v>
       </c>
       <c r="G3533" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3534">
@@ -95848,7 +95848,7 @@
         <v>3</v>
       </c>
       <c r="G3534" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3535">
@@ -95875,7 +95875,7 @@
         <v>3</v>
       </c>
       <c r="G3535" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3536">
@@ -95902,7 +95902,7 @@
         <v>3</v>
       </c>
       <c r="G3536" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3537">
@@ -95929,7 +95929,7 @@
         <v>3</v>
       </c>
       <c r="G3537" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3538">
@@ -95956,7 +95956,7 @@
         <v>3</v>
       </c>
       <c r="G3538" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3539">
@@ -95983,7 +95983,7 @@
         <v>3</v>
       </c>
       <c r="G3539" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3540">
@@ -96010,7 +96010,7 @@
         <v>3</v>
       </c>
       <c r="G3540" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3541">
@@ -96037,7 +96037,7 @@
         <v>3</v>
       </c>
       <c r="G3541" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3542">
@@ -96064,7 +96064,7 @@
         <v>3</v>
       </c>
       <c r="G3542" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3543">
@@ -96091,7 +96091,7 @@
         <v>3</v>
       </c>
       <c r="G3543" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3544">
@@ -96118,7 +96118,7 @@
         <v>3</v>
       </c>
       <c r="G3544" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3545">
@@ -96145,7 +96145,7 @@
         <v>3</v>
       </c>
       <c r="G3545" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3546">
@@ -96172,7 +96172,7 @@
         <v>3</v>
       </c>
       <c r="G3546" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3547">
@@ -96199,7 +96199,7 @@
         <v>3</v>
       </c>
       <c r="G3547" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3548">
@@ -96226,7 +96226,7 @@
         <v>3</v>
       </c>
       <c r="G3548" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3549">
@@ -96253,7 +96253,7 @@
         <v>3</v>
       </c>
       <c r="G3549" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3550">
@@ -96280,7 +96280,7 @@
         <v>3</v>
       </c>
       <c r="G3550" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3551">
@@ -96307,7 +96307,7 @@
         <v>3</v>
       </c>
       <c r="G3551" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3552">
@@ -96334,7 +96334,7 @@
         <v>3</v>
       </c>
       <c r="G3552" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3553">
@@ -96361,7 +96361,7 @@
         <v>3</v>
       </c>
       <c r="G3553" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3554">
@@ -96388,7 +96388,7 @@
         <v>3</v>
       </c>
       <c r="G3554" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3555">
@@ -96415,7 +96415,7 @@
         <v>3</v>
       </c>
       <c r="G3555" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3556">
@@ -96442,7 +96442,7 @@
         <v>3</v>
       </c>
       <c r="G3556" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3557">
@@ -96469,7 +96469,7 @@
         <v>3</v>
       </c>
       <c r="G3557" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3558">
@@ -96496,7 +96496,7 @@
         <v>3</v>
       </c>
       <c r="G3558" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3559">
@@ -96523,7 +96523,7 @@
         <v>3</v>
       </c>
       <c r="G3559" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3560">
@@ -96550,7 +96550,7 @@
         <v>3</v>
       </c>
       <c r="G3560" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3561">
@@ -96577,7 +96577,7 @@
         <v>3</v>
       </c>
       <c r="G3561" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3562">
@@ -96604,7 +96604,7 @@
         <v>3</v>
       </c>
       <c r="G3562" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3563">
@@ -96631,7 +96631,7 @@
         <v>3</v>
       </c>
       <c r="G3563" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3564">
@@ -96658,7 +96658,7 @@
         <v>3</v>
       </c>
       <c r="G3564" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3565">
@@ -96685,7 +96685,7 @@
         <v>3</v>
       </c>
       <c r="G3565" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3566">
@@ -96712,7 +96712,7 @@
         <v>3</v>
       </c>
       <c r="G3566" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3567">
@@ -96739,7 +96739,7 @@
         <v>3</v>
       </c>
       <c r="G3567" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3568">
@@ -96766,7 +96766,7 @@
         <v>3</v>
       </c>
       <c r="G3568" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3569">
@@ -96793,7 +96793,7 @@
         <v>3</v>
       </c>
       <c r="G3569" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3570">
@@ -96820,7 +96820,7 @@
         <v>3</v>
       </c>
       <c r="G3570" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3571">
@@ -96847,7 +96847,7 @@
         <v>3</v>
       </c>
       <c r="G3571" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3572">
@@ -96874,7 +96874,7 @@
         <v>3</v>
       </c>
       <c r="G3572" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3573">
@@ -96901,7 +96901,7 @@
         <v>3</v>
       </c>
       <c r="G3573" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3574">
@@ -96928,7 +96928,7 @@
         <v>3</v>
       </c>
       <c r="G3574" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3575">
@@ -96955,7 +96955,7 @@
         <v>3</v>
       </c>
       <c r="G3575" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3576">
@@ -96982,7 +96982,7 @@
         <v>3</v>
       </c>
       <c r="G3576" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
     <row r="3577">
@@ -97009,7 +97009,7 @@
         <v>3</v>
       </c>
       <c r="G3577" s="2" t="n">
-        <v>46291.863521075</v>
+        <v>46292.47933705992</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3577"/>
+  <dimension ref="A1:G3601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3321">
@@ -90081,7 +90081,7 @@
         <v>8</v>
       </c>
       <c r="C3321" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="D3321" t="inlineStr">
         <is>
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3323">
@@ -90135,7 +90135,7 @@
         <v>10</v>
       </c>
       <c r="C3323" t="n">
-        <v>22.9</v>
+        <v>22.89</v>
       </c>
       <c r="D3323" t="inlineStr">
         <is>
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3324">
@@ -90162,7 +90162,7 @@
         <v>11</v>
       </c>
       <c r="C3324" t="n">
-        <v>26.75</v>
+        <v>26.7</v>
       </c>
       <c r="D3324" t="inlineStr">
         <is>
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3325">
@@ -90189,7 +90189,7 @@
         <v>12</v>
       </c>
       <c r="C3325" t="n">
-        <v>32.22</v>
+        <v>32.2</v>
       </c>
       <c r="D3325" t="inlineStr">
         <is>
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3326">
@@ -90216,7 +90216,7 @@
         <v>13</v>
       </c>
       <c r="C3326" t="n">
-        <v>31.87</v>
+        <v>31.85</v>
       </c>
       <c r="D3326" t="inlineStr">
         <is>
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3327">
@@ -90243,7 +90243,7 @@
         <v>14</v>
       </c>
       <c r="C3327" t="n">
-        <v>32.52</v>
+        <v>32.51</v>
       </c>
       <c r="D3327" t="inlineStr">
         <is>
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3328">
@@ -90270,7 +90270,7 @@
         <v>15</v>
       </c>
       <c r="C3328" t="n">
-        <v>33.1</v>
+        <v>33.09</v>
       </c>
       <c r="D3328" t="inlineStr">
         <is>
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3332">
@@ -90378,7 +90378,7 @@
         <v>19</v>
       </c>
       <c r="C3332" t="n">
-        <v>31.3</v>
+        <v>31.29</v>
       </c>
       <c r="D3332" t="inlineStr">
         <is>
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3333">
@@ -90405,7 +90405,7 @@
         <v>20</v>
       </c>
       <c r="C3333" t="n">
-        <v>24.37</v>
+        <v>24.38</v>
       </c>
       <c r="D3333" t="inlineStr">
         <is>
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3334">
@@ -90432,7 +90432,7 @@
         <v>21</v>
       </c>
       <c r="C3334" t="n">
-        <v>34.03</v>
+        <v>34.02</v>
       </c>
       <c r="D3334" t="inlineStr">
         <is>
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3335">
@@ -90459,7 +90459,7 @@
         <v>22</v>
       </c>
       <c r="C3335" t="n">
-        <v>33.43</v>
+        <v>33.42</v>
       </c>
       <c r="D3335" t="inlineStr">
         <is>
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3337">
@@ -90513,7 +90513,7 @@
         <v>24</v>
       </c>
       <c r="C3337" t="n">
-        <v>23.32</v>
+        <v>23.33</v>
       </c>
       <c r="D3337" t="inlineStr">
         <is>
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3341">
@@ -90621,7 +90621,7 @@
         <v>4</v>
       </c>
       <c r="C3341" t="n">
-        <v>18.02</v>
+        <v>18.01</v>
       </c>
       <c r="D3341" t="inlineStr">
         <is>
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3343">
@@ -90675,7 +90675,7 @@
         <v>6</v>
       </c>
       <c r="C3343" t="n">
-        <v>16.05</v>
+        <v>16.06</v>
       </c>
       <c r="D3343" t="inlineStr">
         <is>
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3344">
@@ -90702,7 +90702,7 @@
         <v>7</v>
       </c>
       <c r="C3344" t="n">
-        <v>20.03</v>
+        <v>20.02</v>
       </c>
       <c r="D3344" t="inlineStr">
         <is>
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3345">
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3346">
@@ -90756,7 +90756,7 @@
         <v>9</v>
       </c>
       <c r="C3346" t="n">
-        <v>43.98</v>
+        <v>43.97</v>
       </c>
       <c r="D3346" t="inlineStr">
         <is>
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3347">
@@ -90783,7 +90783,7 @@
         <v>10</v>
       </c>
       <c r="C3347" t="n">
-        <v>26.04</v>
+        <v>26.05</v>
       </c>
       <c r="D3347" t="inlineStr">
         <is>
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3349">
@@ -90837,7 +90837,7 @@
         <v>12</v>
       </c>
       <c r="C3349" t="n">
-        <v>25.74</v>
+        <v>25.72</v>
       </c>
       <c r="D3349" t="inlineStr">
         <is>
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3350">
@@ -90864,7 +90864,7 @@
         <v>13</v>
       </c>
       <c r="C3350" t="n">
-        <v>23.77</v>
+        <v>23.74</v>
       </c>
       <c r="D3350" t="inlineStr">
         <is>
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3351">
@@ -90891,7 +90891,7 @@
         <v>14</v>
       </c>
       <c r="C3351" t="n">
-        <v>24.01</v>
+        <v>23.97</v>
       </c>
       <c r="D3351" t="inlineStr">
         <is>
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3352">
@@ -90918,7 +90918,7 @@
         <v>15</v>
       </c>
       <c r="C3352" t="n">
-        <v>24.2</v>
+        <v>24.17</v>
       </c>
       <c r="D3352" t="inlineStr">
         <is>
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3353">
@@ -90945,7 +90945,7 @@
         <v>16</v>
       </c>
       <c r="C3353" t="n">
-        <v>24.35</v>
+        <v>24.32</v>
       </c>
       <c r="D3353" t="inlineStr">
         <is>
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3354">
@@ -90972,7 +90972,7 @@
         <v>17</v>
       </c>
       <c r="C3354" t="n">
-        <v>23.3</v>
+        <v>23.31</v>
       </c>
       <c r="D3354" t="inlineStr">
         <is>
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3355">
@@ -90999,7 +90999,7 @@
         <v>18</v>
       </c>
       <c r="C3355" t="n">
-        <v>20.91</v>
+        <v>21</v>
       </c>
       <c r="D3355" t="inlineStr">
         <is>
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3356">
@@ -91026,7 +91026,7 @@
         <v>19</v>
       </c>
       <c r="C3356" t="n">
-        <v>17.37</v>
+        <v>17.45</v>
       </c>
       <c r="D3356" t="inlineStr">
         <is>
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3357">
@@ -91053,7 +91053,7 @@
         <v>20</v>
       </c>
       <c r="C3357" t="n">
-        <v>25.85</v>
+        <v>25.87</v>
       </c>
       <c r="D3357" t="inlineStr">
         <is>
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3360">
@@ -91134,7 +91134,7 @@
         <v>23</v>
       </c>
       <c r="C3360" t="n">
-        <v>28.76</v>
+        <v>28.75</v>
       </c>
       <c r="D3360" t="inlineStr">
         <is>
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3361">
@@ -91161,7 +91161,7 @@
         <v>24</v>
       </c>
       <c r="C3361" t="n">
-        <v>23.97</v>
+        <v>23.96</v>
       </c>
       <c r="D3361" t="inlineStr">
         <is>
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3362">
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3364">
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3365">
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3366">
@@ -91296,7 +91296,7 @@
         <v>5</v>
       </c>
       <c r="C3366" t="n">
-        <v>16.8</v>
+        <v>16.79</v>
       </c>
       <c r="D3366" t="inlineStr">
         <is>
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3367">
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3368">
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3369">
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3370">
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3371">
@@ -91431,7 +91431,7 @@
         <v>10</v>
       </c>
       <c r="C3371" t="n">
-        <v>31.34</v>
+        <v>31.32</v>
       </c>
       <c r="D3371" t="inlineStr">
         <is>
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3372">
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3373">
@@ -91485,7 +91485,7 @@
         <v>12</v>
       </c>
       <c r="C3373" t="n">
-        <v>27.44</v>
+        <v>27.43</v>
       </c>
       <c r="D3373" t="inlineStr">
         <is>
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3374">
@@ -91512,7 +91512,7 @@
         <v>13</v>
       </c>
       <c r="C3374" t="n">
-        <v>27.54</v>
+        <v>27.52</v>
       </c>
       <c r="D3374" t="inlineStr">
         <is>
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3375">
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3376">
@@ -91566,7 +91566,7 @@
         <v>15</v>
       </c>
       <c r="C3376" t="n">
-        <v>26.18</v>
+        <v>26.17</v>
       </c>
       <c r="D3376" t="inlineStr">
         <is>
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3377">
@@ -91593,7 +91593,7 @@
         <v>16</v>
       </c>
       <c r="C3377" t="n">
-        <v>25.48</v>
+        <v>25.5</v>
       </c>
       <c r="D3377" t="inlineStr">
         <is>
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3378">
@@ -91620,7 +91620,7 @@
         <v>17</v>
       </c>
       <c r="C3378" t="n">
-        <v>25.93</v>
+        <v>25.91</v>
       </c>
       <c r="D3378" t="inlineStr">
         <is>
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3379">
@@ -91647,7 +91647,7 @@
         <v>18</v>
       </c>
       <c r="C3379" t="n">
-        <v>24.75</v>
+        <v>24.74</v>
       </c>
       <c r="D3379" t="inlineStr">
         <is>
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3380">
@@ -91674,7 +91674,7 @@
         <v>19</v>
       </c>
       <c r="C3380" t="n">
-        <v>20.6</v>
+        <v>20.63</v>
       </c>
       <c r="D3380" t="inlineStr">
         <is>
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3381">
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3382">
@@ -91728,7 +91728,7 @@
         <v>21</v>
       </c>
       <c r="C3382" t="n">
-        <v>45.35</v>
+        <v>45.34</v>
       </c>
       <c r="D3382" t="inlineStr">
         <is>
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3383">
@@ -91755,7 +91755,7 @@
         <v>22</v>
       </c>
       <c r="C3383" t="n">
-        <v>47.83</v>
+        <v>47.82</v>
       </c>
       <c r="D3383" t="inlineStr">
         <is>
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3384">
@@ -91782,7 +91782,7 @@
         <v>23</v>
       </c>
       <c r="C3384" t="n">
-        <v>34.6</v>
+        <v>34.59</v>
       </c>
       <c r="D3384" t="inlineStr">
         <is>
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3385">
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3386">
@@ -91836,7 +91836,7 @@
         <v>1</v>
       </c>
       <c r="C3386" t="n">
-        <v>12.14</v>
+        <v>12.15</v>
       </c>
       <c r="D3386" t="inlineStr">
         <is>
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3387">
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3388">
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3389">
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3390">
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3391">
@@ -91971,7 +91971,7 @@
         <v>6</v>
       </c>
       <c r="C3391" t="n">
-        <v>15.48</v>
+        <v>15.47</v>
       </c>
       <c r="D3391" t="inlineStr">
         <is>
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3392">
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3393">
@@ -92025,7 +92025,7 @@
         <v>8</v>
       </c>
       <c r="C3393" t="n">
-        <v>37.55</v>
+        <v>37.54</v>
       </c>
       <c r="D3393" t="inlineStr">
         <is>
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3394">
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3395">
@@ -92079,7 +92079,7 @@
         <v>10</v>
       </c>
       <c r="C3395" t="n">
-        <v>19.78</v>
+        <v>19.82</v>
       </c>
       <c r="D3395" t="inlineStr">
         <is>
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3396">
@@ -92106,7 +92106,7 @@
         <v>11</v>
       </c>
       <c r="C3396" t="n">
-        <v>22.29</v>
+        <v>22.28</v>
       </c>
       <c r="D3396" t="inlineStr">
         <is>
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3397">
@@ -92133,7 +92133,7 @@
         <v>12</v>
       </c>
       <c r="C3397" t="n">
-        <v>22.88</v>
+        <v>22.85</v>
       </c>
       <c r="D3397" t="inlineStr">
         <is>
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3398">
@@ -92160,7 +92160,7 @@
         <v>13</v>
       </c>
       <c r="C3398" t="n">
-        <v>23.2</v>
+        <v>23.16</v>
       </c>
       <c r="D3398" t="inlineStr">
         <is>
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3399">
@@ -92187,7 +92187,7 @@
         <v>14</v>
       </c>
       <c r="C3399" t="n">
-        <v>22.77</v>
+        <v>22.74</v>
       </c>
       <c r="D3399" t="inlineStr">
         <is>
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3400">
@@ -92214,7 +92214,7 @@
         <v>15</v>
       </c>
       <c r="C3400" t="n">
-        <v>23.05</v>
+        <v>23.02</v>
       </c>
       <c r="D3400" t="inlineStr">
         <is>
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3401">
@@ -92241,7 +92241,7 @@
         <v>16</v>
       </c>
       <c r="C3401" t="n">
-        <v>23.76</v>
+        <v>23.72</v>
       </c>
       <c r="D3401" t="inlineStr">
         <is>
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3402">
@@ -92268,7 +92268,7 @@
         <v>17</v>
       </c>
       <c r="C3402" t="n">
-        <v>23.56</v>
+        <v>23.54</v>
       </c>
       <c r="D3402" t="inlineStr">
         <is>
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3403">
@@ -92295,7 +92295,7 @@
         <v>18</v>
       </c>
       <c r="C3403" t="n">
-        <v>22.36</v>
+        <v>22.37</v>
       </c>
       <c r="D3403" t="inlineStr">
         <is>
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3404">
@@ -92322,7 +92322,7 @@
         <v>19</v>
       </c>
       <c r="C3404" t="n">
-        <v>20.86</v>
+        <v>20.88</v>
       </c>
       <c r="D3404" t="inlineStr">
         <is>
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3405">
@@ -92349,7 +92349,7 @@
         <v>20</v>
       </c>
       <c r="C3405" t="n">
-        <v>24.9</v>
+        <v>24.92</v>
       </c>
       <c r="D3405" t="inlineStr">
         <is>
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3406">
@@ -92376,7 +92376,7 @@
         <v>21</v>
       </c>
       <c r="C3406" t="n">
-        <v>36.03</v>
+        <v>36.02</v>
       </c>
       <c r="D3406" t="inlineStr">
         <is>
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3407">
@@ -92403,7 +92403,7 @@
         <v>22</v>
       </c>
       <c r="C3407" t="n">
-        <v>38.58</v>
+        <v>38.57</v>
       </c>
       <c r="D3407" t="inlineStr">
         <is>
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3408">
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3409">
@@ -92457,7 +92457,7 @@
         <v>24</v>
       </c>
       <c r="C3409" t="n">
-        <v>25.16</v>
+        <v>25.15</v>
       </c>
       <c r="D3409" t="inlineStr">
         <is>
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3410">
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3411">
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3412">
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3413">
@@ -92565,7 +92565,7 @@
         <v>4</v>
       </c>
       <c r="C3413" t="n">
-        <v>13.3</v>
+        <v>13.29</v>
       </c>
       <c r="D3413" t="inlineStr">
         <is>
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3415">
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3416">
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3417">
@@ -92673,7 +92673,7 @@
         <v>8</v>
       </c>
       <c r="C3417" t="n">
-        <v>32.16</v>
+        <v>32.15</v>
       </c>
       <c r="D3417" t="inlineStr">
         <is>
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3418">
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3419">
@@ -92727,7 +92727,7 @@
         <v>10</v>
       </c>
       <c r="C3419" t="n">
-        <v>31.98</v>
+        <v>31.96</v>
       </c>
       <c r="D3419" t="inlineStr">
         <is>
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3420">
@@ -92754,7 +92754,7 @@
         <v>11</v>
       </c>
       <c r="C3420" t="n">
-        <v>25.88</v>
+        <v>25.84</v>
       </c>
       <c r="D3420" t="inlineStr">
         <is>
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3421">
@@ -92781,7 +92781,7 @@
         <v>12</v>
       </c>
       <c r="C3421" t="n">
-        <v>28.62</v>
+        <v>28.56</v>
       </c>
       <c r="D3421" t="inlineStr">
         <is>
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3422">
@@ -92808,7 +92808,7 @@
         <v>13</v>
       </c>
       <c r="C3422" t="n">
-        <v>31.73</v>
+        <v>31.66</v>
       </c>
       <c r="D3422" t="inlineStr">
         <is>
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3423">
@@ -92835,7 +92835,7 @@
         <v>14</v>
       </c>
       <c r="C3423" t="n">
-        <v>31.23</v>
+        <v>31.19</v>
       </c>
       <c r="D3423" t="inlineStr">
         <is>
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3424">
@@ -92862,7 +92862,7 @@
         <v>15</v>
       </c>
       <c r="C3424" t="n">
-        <v>31.18</v>
+        <v>31.12</v>
       </c>
       <c r="D3424" t="inlineStr">
         <is>
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3425">
@@ -92889,7 +92889,7 @@
         <v>16</v>
       </c>
       <c r="C3425" t="n">
-        <v>31.95</v>
+        <v>31.89</v>
       </c>
       <c r="D3425" t="inlineStr">
         <is>
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3426">
@@ -92916,7 +92916,7 @@
         <v>17</v>
       </c>
       <c r="C3426" t="n">
-        <v>31.38</v>
+        <v>31.34</v>
       </c>
       <c r="D3426" t="inlineStr">
         <is>
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3427">
@@ -92943,7 +92943,7 @@
         <v>18</v>
       </c>
       <c r="C3427" t="n">
-        <v>29.3</v>
+        <v>29.28</v>
       </c>
       <c r="D3427" t="inlineStr">
         <is>
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3428">
@@ -92970,7 +92970,7 @@
         <v>19</v>
       </c>
       <c r="C3428" t="n">
-        <v>26.36</v>
+        <v>26.4</v>
       </c>
       <c r="D3428" t="inlineStr">
         <is>
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3429">
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3430">
@@ -93024,7 +93024,7 @@
         <v>21</v>
       </c>
       <c r="C3430" t="n">
-        <v>36.39</v>
+        <v>36.38</v>
       </c>
       <c r="D3430" t="inlineStr">
         <is>
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3431">
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3432">
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3433">
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3434">
@@ -93132,7 +93132,7 @@
         <v>1</v>
       </c>
       <c r="C3434" t="n">
-        <v>13.19</v>
+        <v>13.12</v>
       </c>
       <c r="D3434" t="inlineStr">
         <is>
@@ -93148,7 +93148,7 @@
         <v>3</v>
       </c>
       <c r="G3434" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3435">
@@ -93159,7 +93159,7 @@
         <v>2</v>
       </c>
       <c r="C3435" t="n">
-        <v>12.96</v>
+        <v>12.94</v>
       </c>
       <c r="D3435" t="inlineStr">
         <is>
@@ -93175,7 +93175,7 @@
         <v>3</v>
       </c>
       <c r="G3435" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3436">
@@ -93186,7 +93186,7 @@
         <v>3</v>
       </c>
       <c r="C3436" t="n">
-        <v>15.53</v>
+        <v>15.52</v>
       </c>
       <c r="D3436" t="inlineStr">
         <is>
@@ -93202,7 +93202,7 @@
         <v>3</v>
       </c>
       <c r="G3436" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3437">
@@ -93213,7 +93213,7 @@
         <v>4</v>
       </c>
       <c r="C3437" t="n">
-        <v>16.79</v>
+        <v>16.74</v>
       </c>
       <c r="D3437" t="inlineStr">
         <is>
@@ -93229,7 +93229,7 @@
         <v>3</v>
       </c>
       <c r="G3437" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3438">
@@ -93240,7 +93240,7 @@
         <v>5</v>
       </c>
       <c r="C3438" t="n">
-        <v>15.29</v>
+        <v>15.26</v>
       </c>
       <c r="D3438" t="inlineStr">
         <is>
@@ -93256,7 +93256,7 @@
         <v>3</v>
       </c>
       <c r="G3438" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3439">
@@ -93267,7 +93267,7 @@
         <v>6</v>
       </c>
       <c r="C3439" t="n">
-        <v>23.17</v>
+        <v>23.12</v>
       </c>
       <c r="D3439" t="inlineStr">
         <is>
@@ -93283,7 +93283,7 @@
         <v>3</v>
       </c>
       <c r="G3439" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3440">
@@ -93294,7 +93294,7 @@
         <v>7</v>
       </c>
       <c r="C3440" t="n">
-        <v>28.58</v>
+        <v>28.5</v>
       </c>
       <c r="D3440" t="inlineStr">
         <is>
@@ -93310,7 +93310,7 @@
         <v>3</v>
       </c>
       <c r="G3440" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3441">
@@ -93321,7 +93321,7 @@
         <v>8</v>
       </c>
       <c r="C3441" t="n">
-        <v>57.28</v>
+        <v>57.1</v>
       </c>
       <c r="D3441" t="inlineStr">
         <is>
@@ -93337,7 +93337,7 @@
         <v>3</v>
       </c>
       <c r="G3441" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3442">
@@ -93348,7 +93348,7 @@
         <v>9</v>
       </c>
       <c r="C3442" t="n">
-        <v>53.24</v>
+        <v>53.08</v>
       </c>
       <c r="D3442" t="inlineStr">
         <is>
@@ -93364,7 +93364,7 @@
         <v>3</v>
       </c>
       <c r="G3442" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3443">
@@ -93375,7 +93375,7 @@
         <v>10</v>
       </c>
       <c r="C3443" t="n">
-        <v>29.97</v>
+        <v>29.92</v>
       </c>
       <c r="D3443" t="inlineStr">
         <is>
@@ -93391,7 +93391,7 @@
         <v>3</v>
       </c>
       <c r="G3443" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3444">
@@ -93402,7 +93402,7 @@
         <v>11</v>
       </c>
       <c r="C3444" t="n">
-        <v>26.76</v>
+        <v>26.69</v>
       </c>
       <c r="D3444" t="inlineStr">
         <is>
@@ -93418,7 +93418,7 @@
         <v>3</v>
       </c>
       <c r="G3444" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3445">
@@ -93429,7 +93429,7 @@
         <v>12</v>
       </c>
       <c r="C3445" t="n">
-        <v>31.26</v>
+        <v>31.2</v>
       </c>
       <c r="D3445" t="inlineStr">
         <is>
@@ -93445,7 +93445,7 @@
         <v>3</v>
       </c>
       <c r="G3445" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3446">
@@ -93456,7 +93456,7 @@
         <v>13</v>
       </c>
       <c r="C3446" t="n">
-        <v>30.88</v>
+        <v>30.83</v>
       </c>
       <c r="D3446" t="inlineStr">
         <is>
@@ -93472,7 +93472,7 @@
         <v>3</v>
       </c>
       <c r="G3446" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3447">
@@ -93483,7 +93483,7 @@
         <v>14</v>
       </c>
       <c r="C3447" t="n">
-        <v>30.89</v>
+        <v>30.92</v>
       </c>
       <c r="D3447" t="inlineStr">
         <is>
@@ -93499,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="G3447" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3448">
@@ -93510,7 +93510,7 @@
         <v>15</v>
       </c>
       <c r="C3448" t="n">
-        <v>30.85</v>
+        <v>30.76</v>
       </c>
       <c r="D3448" t="inlineStr">
         <is>
@@ -93526,7 +93526,7 @@
         <v>3</v>
       </c>
       <c r="G3448" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3449">
@@ -93537,7 +93537,7 @@
         <v>16</v>
       </c>
       <c r="C3449" t="n">
-        <v>31.78</v>
+        <v>31.9</v>
       </c>
       <c r="D3449" t="inlineStr">
         <is>
@@ -93553,7 +93553,7 @@
         <v>3</v>
       </c>
       <c r="G3449" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3450">
@@ -93564,7 +93564,7 @@
         <v>17</v>
       </c>
       <c r="C3450" t="n">
-        <v>29.73</v>
+        <v>29.88</v>
       </c>
       <c r="D3450" t="inlineStr">
         <is>
@@ -93580,7 +93580,7 @@
         <v>3</v>
       </c>
       <c r="G3450" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3451">
@@ -93591,7 +93591,7 @@
         <v>18</v>
       </c>
       <c r="C3451" t="n">
-        <v>23.92</v>
+        <v>24.13</v>
       </c>
       <c r="D3451" t="inlineStr">
         <is>
@@ -93607,7 +93607,7 @@
         <v>3</v>
       </c>
       <c r="G3451" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3452">
@@ -93618,7 +93618,7 @@
         <v>19</v>
       </c>
       <c r="C3452" t="n">
-        <v>24.2</v>
+        <v>24.44</v>
       </c>
       <c r="D3452" t="inlineStr">
         <is>
@@ -93634,7 +93634,7 @@
         <v>3</v>
       </c>
       <c r="G3452" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3453">
@@ -93645,7 +93645,7 @@
         <v>20</v>
       </c>
       <c r="C3453" t="n">
-        <v>25.99</v>
+        <v>25.98</v>
       </c>
       <c r="D3453" t="inlineStr">
         <is>
@@ -93661,7 +93661,7 @@
         <v>3</v>
       </c>
       <c r="G3453" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3454">
@@ -93672,7 +93672,7 @@
         <v>21</v>
       </c>
       <c r="C3454" t="n">
-        <v>47.17</v>
+        <v>47.11</v>
       </c>
       <c r="D3454" t="inlineStr">
         <is>
@@ -93688,7 +93688,7 @@
         <v>3</v>
       </c>
       <c r="G3454" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3455">
@@ -93699,7 +93699,7 @@
         <v>22</v>
       </c>
       <c r="C3455" t="n">
-        <v>47.87</v>
+        <v>47.78</v>
       </c>
       <c r="D3455" t="inlineStr">
         <is>
@@ -93715,7 +93715,7 @@
         <v>3</v>
       </c>
       <c r="G3455" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3456">
@@ -93726,7 +93726,7 @@
         <v>23</v>
       </c>
       <c r="C3456" t="n">
-        <v>34.21</v>
+        <v>34.1</v>
       </c>
       <c r="D3456" t="inlineStr">
         <is>
@@ -93742,7 +93742,7 @@
         <v>3</v>
       </c>
       <c r="G3456" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3457">
@@ -93753,7 +93753,7 @@
         <v>24</v>
       </c>
       <c r="C3457" t="n">
-        <v>27.38</v>
+        <v>27.22</v>
       </c>
       <c r="D3457" t="inlineStr">
         <is>
@@ -93769,7 +93769,7 @@
         <v>3</v>
       </c>
       <c r="G3457" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3458">
@@ -93780,7 +93780,7 @@
         <v>1</v>
       </c>
       <c r="C3458" t="n">
-        <v>12.16</v>
+        <v>12.15</v>
       </c>
       <c r="D3458" t="inlineStr">
         <is>
@@ -93796,7 +93796,7 @@
         <v>3</v>
       </c>
       <c r="G3458" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3459">
@@ -93823,7 +93823,7 @@
         <v>3</v>
       </c>
       <c r="G3459" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3460">
@@ -93834,7 +93834,7 @@
         <v>3</v>
       </c>
       <c r="C3460" t="n">
-        <v>8.27</v>
+        <v>8.25</v>
       </c>
       <c r="D3460" t="inlineStr">
         <is>
@@ -93850,7 +93850,7 @@
         <v>3</v>
       </c>
       <c r="G3460" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3461">
@@ -93861,7 +93861,7 @@
         <v>4</v>
       </c>
       <c r="C3461" t="n">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
       <c r="D3461" t="inlineStr">
         <is>
@@ -93877,7 +93877,7 @@
         <v>3</v>
       </c>
       <c r="G3461" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3462">
@@ -93888,7 +93888,7 @@
         <v>5</v>
       </c>
       <c r="C3462" t="n">
-        <v>7.98</v>
+        <v>7.96</v>
       </c>
       <c r="D3462" t="inlineStr">
         <is>
@@ -93904,7 +93904,7 @@
         <v>3</v>
       </c>
       <c r="G3462" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3463">
@@ -93915,7 +93915,7 @@
         <v>6</v>
       </c>
       <c r="C3463" t="n">
-        <v>13.54</v>
+        <v>13.52</v>
       </c>
       <c r="D3463" t="inlineStr">
         <is>
@@ -93931,7 +93931,7 @@
         <v>3</v>
       </c>
       <c r="G3463" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3464">
@@ -93942,7 +93942,7 @@
         <v>7</v>
       </c>
       <c r="C3464" t="n">
-        <v>21.84</v>
+        <v>21.82</v>
       </c>
       <c r="D3464" t="inlineStr">
         <is>
@@ -93958,7 +93958,7 @@
         <v>3</v>
       </c>
       <c r="G3464" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3465">
@@ -93969,7 +93969,7 @@
         <v>8</v>
       </c>
       <c r="C3465" t="n">
-        <v>61.39</v>
+        <v>61.34</v>
       </c>
       <c r="D3465" t="inlineStr">
         <is>
@@ -93985,7 +93985,7 @@
         <v>3</v>
       </c>
       <c r="G3465" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3466">
@@ -93996,7 +93996,7 @@
         <v>9</v>
       </c>
       <c r="C3466" t="n">
-        <v>58.86</v>
+        <v>58.81</v>
       </c>
       <c r="D3466" t="inlineStr">
         <is>
@@ -94012,7 +94012,7 @@
         <v>3</v>
       </c>
       <c r="G3466" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3467">
@@ -94023,7 +94023,7 @@
         <v>10</v>
       </c>
       <c r="C3467" t="n">
-        <v>22.29</v>
+        <v>22.31</v>
       </c>
       <c r="D3467" t="inlineStr">
         <is>
@@ -94039,7 +94039,7 @@
         <v>3</v>
       </c>
       <c r="G3467" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3468">
@@ -94050,7 +94050,7 @@
         <v>11</v>
       </c>
       <c r="C3468" t="n">
-        <v>23.18</v>
+        <v>23.15</v>
       </c>
       <c r="D3468" t="inlineStr">
         <is>
@@ -94066,7 +94066,7 @@
         <v>3</v>
       </c>
       <c r="G3468" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3469">
@@ -94077,7 +94077,7 @@
         <v>12</v>
       </c>
       <c r="C3469" t="n">
-        <v>32.78</v>
+        <v>32.79</v>
       </c>
       <c r="D3469" t="inlineStr">
         <is>
@@ -94093,7 +94093,7 @@
         <v>3</v>
       </c>
       <c r="G3469" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3470">
@@ -94104,7 +94104,7 @@
         <v>13</v>
       </c>
       <c r="C3470" t="n">
-        <v>31.93</v>
+        <v>31.85</v>
       </c>
       <c r="D3470" t="inlineStr">
         <is>
@@ -94120,7 +94120,7 @@
         <v>3</v>
       </c>
       <c r="G3470" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3471">
@@ -94131,7 +94131,7 @@
         <v>14</v>
       </c>
       <c r="C3471" t="n">
-        <v>28.59</v>
+        <v>28.58</v>
       </c>
       <c r="D3471" t="inlineStr">
         <is>
@@ -94147,7 +94147,7 @@
         <v>3</v>
       </c>
       <c r="G3471" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3472">
@@ -94158,7 +94158,7 @@
         <v>15</v>
       </c>
       <c r="C3472" t="n">
-        <v>28.58</v>
+        <v>28.52</v>
       </c>
       <c r="D3472" t="inlineStr">
         <is>
@@ -94174,7 +94174,7 @@
         <v>3</v>
       </c>
       <c r="G3472" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3473">
@@ -94185,7 +94185,7 @@
         <v>16</v>
       </c>
       <c r="C3473" t="n">
-        <v>31.36</v>
+        <v>31.29</v>
       </c>
       <c r="D3473" t="inlineStr">
         <is>
@@ -94201,7 +94201,7 @@
         <v>3</v>
       </c>
       <c r="G3473" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3474">
@@ -94212,7 +94212,7 @@
         <v>17</v>
       </c>
       <c r="C3474" t="n">
-        <v>28.21</v>
+        <v>28.54</v>
       </c>
       <c r="D3474" t="inlineStr">
         <is>
@@ -94228,7 +94228,7 @@
         <v>3</v>
       </c>
       <c r="G3474" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3475">
@@ -94239,7 +94239,7 @@
         <v>18</v>
       </c>
       <c r="C3475" t="n">
-        <v>29.29</v>
+        <v>29.22</v>
       </c>
       <c r="D3475" t="inlineStr">
         <is>
@@ -94255,7 +94255,7 @@
         <v>3</v>
       </c>
       <c r="G3475" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3476">
@@ -94266,7 +94266,7 @@
         <v>19</v>
       </c>
       <c r="C3476" t="n">
-        <v>26.91</v>
+        <v>27</v>
       </c>
       <c r="D3476" t="inlineStr">
         <is>
@@ -94282,7 +94282,7 @@
         <v>3</v>
       </c>
       <c r="G3476" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3477">
@@ -94293,7 +94293,7 @@
         <v>20</v>
       </c>
       <c r="C3477" t="n">
-        <v>21.54</v>
+        <v>21.58</v>
       </c>
       <c r="D3477" t="inlineStr">
         <is>
@@ -94309,7 +94309,7 @@
         <v>3</v>
       </c>
       <c r="G3477" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3478">
@@ -94320,7 +94320,7 @@
         <v>21</v>
       </c>
       <c r="C3478" t="n">
-        <v>32.1</v>
+        <v>32.09</v>
       </c>
       <c r="D3478" t="inlineStr">
         <is>
@@ -94336,7 +94336,7 @@
         <v>3</v>
       </c>
       <c r="G3478" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3479">
@@ -94347,7 +94347,7 @@
         <v>22</v>
       </c>
       <c r="C3479" t="n">
-        <v>35.93</v>
+        <v>35.92</v>
       </c>
       <c r="D3479" t="inlineStr">
         <is>
@@ -94363,7 +94363,7 @@
         <v>3</v>
       </c>
       <c r="G3479" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3480">
@@ -94374,7 +94374,7 @@
         <v>23</v>
       </c>
       <c r="C3480" t="n">
-        <v>37.62</v>
+        <v>37.61</v>
       </c>
       <c r="D3480" t="inlineStr">
         <is>
@@ -94390,7 +94390,7 @@
         <v>3</v>
       </c>
       <c r="G3480" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3481">
@@ -94401,7 +94401,7 @@
         <v>24</v>
       </c>
       <c r="C3481" t="n">
-        <v>34.85</v>
+        <v>34.84</v>
       </c>
       <c r="D3481" t="inlineStr">
         <is>
@@ -94417,7 +94417,7 @@
         <v>3</v>
       </c>
       <c r="G3481" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3482">
@@ -94428,7 +94428,7 @@
         <v>1</v>
       </c>
       <c r="C3482" t="n">
-        <v>12.45</v>
+        <v>12.4</v>
       </c>
       <c r="D3482" t="inlineStr">
         <is>
@@ -94444,7 +94444,7 @@
         <v>3</v>
       </c>
       <c r="G3482" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3483">
@@ -94471,7 +94471,7 @@
         <v>3</v>
       </c>
       <c r="G3483" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3484">
@@ -94482,7 +94482,7 @@
         <v>3</v>
       </c>
       <c r="C3484" t="n">
-        <v>9.369999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="D3484" t="inlineStr">
         <is>
@@ -94498,7 +94498,7 @@
         <v>3</v>
       </c>
       <c r="G3484" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3485">
@@ -94509,7 +94509,7 @@
         <v>4</v>
       </c>
       <c r="C3485" t="n">
-        <v>9.779999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="D3485" t="inlineStr">
         <is>
@@ -94525,7 +94525,7 @@
         <v>3</v>
       </c>
       <c r="G3485" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3486">
@@ -94536,7 +94536,7 @@
         <v>5</v>
       </c>
       <c r="C3486" t="n">
-        <v>8.050000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="D3486" t="inlineStr">
         <is>
@@ -94552,7 +94552,7 @@
         <v>3</v>
       </c>
       <c r="G3486" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3487">
@@ -94563,7 +94563,7 @@
         <v>6</v>
       </c>
       <c r="C3487" t="n">
-        <v>8.69</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D3487" t="inlineStr">
         <is>
@@ -94579,7 +94579,7 @@
         <v>3</v>
       </c>
       <c r="G3487" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3488">
@@ -94590,7 +94590,7 @@
         <v>7</v>
       </c>
       <c r="C3488" t="n">
-        <v>20.41</v>
+        <v>20.33</v>
       </c>
       <c r="D3488" t="inlineStr">
         <is>
@@ -94606,7 +94606,7 @@
         <v>3</v>
       </c>
       <c r="G3488" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3489">
@@ -94617,7 +94617,7 @@
         <v>8</v>
       </c>
       <c r="C3489" t="n">
-        <v>44.04</v>
+        <v>43.91</v>
       </c>
       <c r="D3489" t="inlineStr">
         <is>
@@ -94633,7 +94633,7 @@
         <v>3</v>
       </c>
       <c r="G3489" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3490">
@@ -94644,7 +94644,7 @@
         <v>9</v>
       </c>
       <c r="C3490" t="n">
-        <v>42.14</v>
+        <v>41.96</v>
       </c>
       <c r="D3490" t="inlineStr">
         <is>
@@ -94660,7 +94660,7 @@
         <v>3</v>
       </c>
       <c r="G3490" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3491">
@@ -94671,7 +94671,7 @@
         <v>10</v>
       </c>
       <c r="C3491" t="n">
-        <v>28.21</v>
+        <v>28.07</v>
       </c>
       <c r="D3491" t="inlineStr">
         <is>
@@ -94687,7 +94687,7 @@
         <v>3</v>
       </c>
       <c r="G3491" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3492">
@@ -94698,7 +94698,7 @@
         <v>11</v>
       </c>
       <c r="C3492" t="n">
-        <v>23.23</v>
+        <v>23.02</v>
       </c>
       <c r="D3492" t="inlineStr">
         <is>
@@ -94714,7 +94714,7 @@
         <v>3</v>
       </c>
       <c r="G3492" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3493">
@@ -94725,7 +94725,7 @@
         <v>12</v>
       </c>
       <c r="C3493" t="n">
-        <v>32.88</v>
+        <v>32.44</v>
       </c>
       <c r="D3493" t="inlineStr">
         <is>
@@ -94741,7 +94741,7 @@
         <v>3</v>
       </c>
       <c r="G3493" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3494">
@@ -94752,7 +94752,7 @@
         <v>13</v>
       </c>
       <c r="C3494" t="n">
-        <v>35.52</v>
+        <v>35</v>
       </c>
       <c r="D3494" t="inlineStr">
         <is>
@@ -94768,7 +94768,7 @@
         <v>3</v>
       </c>
       <c r="G3494" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3495">
@@ -94779,7 +94779,7 @@
         <v>14</v>
       </c>
       <c r="C3495" t="n">
-        <v>35.29</v>
+        <v>34.78</v>
       </c>
       <c r="D3495" t="inlineStr">
         <is>
@@ -94795,7 +94795,7 @@
         <v>3</v>
       </c>
       <c r="G3495" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3496">
@@ -94806,7 +94806,7 @@
         <v>15</v>
       </c>
       <c r="C3496" t="n">
-        <v>36.27</v>
+        <v>36.48</v>
       </c>
       <c r="D3496" t="inlineStr">
         <is>
@@ -94822,7 +94822,7 @@
         <v>3</v>
       </c>
       <c r="G3496" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3497">
@@ -94833,7 +94833,7 @@
         <v>16</v>
       </c>
       <c r="C3497" t="n">
-        <v>32.72</v>
+        <v>33.89</v>
       </c>
       <c r="D3497" t="inlineStr">
         <is>
@@ -94849,7 +94849,7 @@
         <v>3</v>
       </c>
       <c r="G3497" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3498">
@@ -94860,7 +94860,7 @@
         <v>17</v>
       </c>
       <c r="C3498" t="n">
-        <v>33.35</v>
+        <v>34.14</v>
       </c>
       <c r="D3498" t="inlineStr">
         <is>
@@ -94876,7 +94876,7 @@
         <v>3</v>
       </c>
       <c r="G3498" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3499">
@@ -94887,7 +94887,7 @@
         <v>18</v>
       </c>
       <c r="C3499" t="n">
-        <v>26.7</v>
+        <v>27.34</v>
       </c>
       <c r="D3499" t="inlineStr">
         <is>
@@ -94903,7 +94903,7 @@
         <v>3</v>
       </c>
       <c r="G3499" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3500">
@@ -94914,7 +94914,7 @@
         <v>19</v>
       </c>
       <c r="C3500" t="n">
-        <v>34.58</v>
+        <v>34.75</v>
       </c>
       <c r="D3500" t="inlineStr">
         <is>
@@ -94930,7 +94930,7 @@
         <v>3</v>
       </c>
       <c r="G3500" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3501">
@@ -94941,7 +94941,7 @@
         <v>20</v>
       </c>
       <c r="C3501" t="n">
-        <v>37.72</v>
+        <v>37.55</v>
       </c>
       <c r="D3501" t="inlineStr">
         <is>
@@ -94957,7 +94957,7 @@
         <v>3</v>
       </c>
       <c r="G3501" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3502">
@@ -94968,7 +94968,7 @@
         <v>21</v>
       </c>
       <c r="C3502" t="n">
-        <v>38.45</v>
+        <v>38.33</v>
       </c>
       <c r="D3502" t="inlineStr">
         <is>
@@ -94984,7 +94984,7 @@
         <v>3</v>
       </c>
       <c r="G3502" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3503">
@@ -94995,7 +94995,7 @@
         <v>22</v>
       </c>
       <c r="C3503" t="n">
-        <v>41.44</v>
+        <v>41.27</v>
       </c>
       <c r="D3503" t="inlineStr">
         <is>
@@ -95011,7 +95011,7 @@
         <v>3</v>
       </c>
       <c r="G3503" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3504">
@@ -95022,7 +95022,7 @@
         <v>23</v>
       </c>
       <c r="C3504" t="n">
-        <v>45.36</v>
+        <v>45.14</v>
       </c>
       <c r="D3504" t="inlineStr">
         <is>
@@ -95038,7 +95038,7 @@
         <v>3</v>
       </c>
       <c r="G3504" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3505">
@@ -95049,7 +95049,7 @@
         <v>24</v>
       </c>
       <c r="C3505" t="n">
-        <v>26.62</v>
+        <v>26.52</v>
       </c>
       <c r="D3505" t="inlineStr">
         <is>
@@ -95065,7 +95065,7 @@
         <v>3</v>
       </c>
       <c r="G3505" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3506">
@@ -95076,7 +95076,7 @@
         <v>1</v>
       </c>
       <c r="C3506" t="n">
-        <v>7.62</v>
+        <v>8.09</v>
       </c>
       <c r="D3506" t="inlineStr">
         <is>
@@ -95092,7 +95092,7 @@
         <v>3</v>
       </c>
       <c r="G3506" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3507">
@@ -95103,7 +95103,7 @@
         <v>2</v>
       </c>
       <c r="C3507" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="D3507" t="inlineStr">
         <is>
@@ -95119,7 +95119,7 @@
         <v>3</v>
       </c>
       <c r="G3507" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3508">
@@ -95130,7 +95130,7 @@
         <v>3</v>
       </c>
       <c r="C3508" t="n">
-        <v>14.44</v>
+        <v>14.68</v>
       </c>
       <c r="D3508" t="inlineStr">
         <is>
@@ -95146,7 +95146,7 @@
         <v>3</v>
       </c>
       <c r="G3508" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3509">
@@ -95157,7 +95157,7 @@
         <v>4</v>
       </c>
       <c r="C3509" t="n">
-        <v>12.08</v>
+        <v>12.83</v>
       </c>
       <c r="D3509" t="inlineStr">
         <is>
@@ -95173,7 +95173,7 @@
         <v>3</v>
       </c>
       <c r="G3509" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3510">
@@ -95184,7 +95184,7 @@
         <v>5</v>
       </c>
       <c r="C3510" t="n">
-        <v>12.32</v>
+        <v>12.94</v>
       </c>
       <c r="D3510" t="inlineStr">
         <is>
@@ -95200,7 +95200,7 @@
         <v>3</v>
       </c>
       <c r="G3510" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3511">
@@ -95211,7 +95211,7 @@
         <v>6</v>
       </c>
       <c r="C3511" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="D3511" t="inlineStr">
         <is>
@@ -95227,7 +95227,7 @@
         <v>3</v>
       </c>
       <c r="G3511" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3512">
@@ -95238,7 +95238,7 @@
         <v>7</v>
       </c>
       <c r="C3512" t="n">
-        <v>25.44</v>
+        <v>25.29</v>
       </c>
       <c r="D3512" t="inlineStr">
         <is>
@@ -95254,7 +95254,7 @@
         <v>3</v>
       </c>
       <c r="G3512" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3513">
@@ -95265,7 +95265,7 @@
         <v>8</v>
       </c>
       <c r="C3513" t="n">
-        <v>40.29</v>
+        <v>42.18</v>
       </c>
       <c r="D3513" t="inlineStr">
         <is>
@@ -95281,7 +95281,7 @@
         <v>3</v>
       </c>
       <c r="G3513" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3514">
@@ -95292,7 +95292,7 @@
         <v>9</v>
       </c>
       <c r="C3514" t="n">
-        <v>36.96</v>
+        <v>38.82</v>
       </c>
       <c r="D3514" t="inlineStr">
         <is>
@@ -95308,7 +95308,7 @@
         <v>3</v>
       </c>
       <c r="G3514" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3515">
@@ -95319,7 +95319,7 @@
         <v>10</v>
       </c>
       <c r="C3515" t="n">
-        <v>27.02</v>
+        <v>26.38</v>
       </c>
       <c r="D3515" t="inlineStr">
         <is>
@@ -95335,7 +95335,7 @@
         <v>3</v>
       </c>
       <c r="G3515" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3516">
@@ -95346,7 +95346,7 @@
         <v>11</v>
       </c>
       <c r="C3516" t="n">
-        <v>25.15</v>
+        <v>24.68</v>
       </c>
       <c r="D3516" t="inlineStr">
         <is>
@@ -95362,7 +95362,7 @@
         <v>3</v>
       </c>
       <c r="G3516" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3517">
@@ -95373,7 +95373,7 @@
         <v>12</v>
       </c>
       <c r="C3517" t="n">
-        <v>29.46</v>
+        <v>29.83</v>
       </c>
       <c r="D3517" t="inlineStr">
         <is>
@@ -95389,7 +95389,7 @@
         <v>3</v>
       </c>
       <c r="G3517" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3518">
@@ -95400,7 +95400,7 @@
         <v>13</v>
       </c>
       <c r="C3518" t="n">
-        <v>25.92</v>
+        <v>28.21</v>
       </c>
       <c r="D3518" t="inlineStr">
         <is>
@@ -95416,7 +95416,7 @@
         <v>3</v>
       </c>
       <c r="G3518" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3519">
@@ -95427,7 +95427,7 @@
         <v>14</v>
       </c>
       <c r="C3519" t="n">
-        <v>31.22</v>
+        <v>33.69</v>
       </c>
       <c r="D3519" t="inlineStr">
         <is>
@@ -95443,7 +95443,7 @@
         <v>3</v>
       </c>
       <c r="G3519" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3520">
@@ -95454,7 +95454,7 @@
         <v>15</v>
       </c>
       <c r="C3520" t="n">
-        <v>26.46</v>
+        <v>28.45</v>
       </c>
       <c r="D3520" t="inlineStr">
         <is>
@@ -95470,7 +95470,7 @@
         <v>3</v>
       </c>
       <c r="G3520" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3521">
@@ -95481,7 +95481,7 @@
         <v>16</v>
       </c>
       <c r="C3521" t="n">
-        <v>30.83</v>
+        <v>31.78</v>
       </c>
       <c r="D3521" t="inlineStr">
         <is>
@@ -95497,7 +95497,7 @@
         <v>3</v>
       </c>
       <c r="G3521" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3522">
@@ -95508,7 +95508,7 @@
         <v>17</v>
       </c>
       <c r="C3522" t="n">
-        <v>30.34</v>
+        <v>30.54</v>
       </c>
       <c r="D3522" t="inlineStr">
         <is>
@@ -95524,7 +95524,7 @@
         <v>3</v>
       </c>
       <c r="G3522" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3523">
@@ -95535,7 +95535,7 @@
         <v>18</v>
       </c>
       <c r="C3523" t="n">
-        <v>25.4</v>
+        <v>25.96</v>
       </c>
       <c r="D3523" t="inlineStr">
         <is>
@@ -95551,7 +95551,7 @@
         <v>3</v>
       </c>
       <c r="G3523" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3524">
@@ -95562,7 +95562,7 @@
         <v>19</v>
       </c>
       <c r="C3524" t="n">
-        <v>27.75</v>
+        <v>27.53</v>
       </c>
       <c r="D3524" t="inlineStr">
         <is>
@@ -95578,7 +95578,7 @@
         <v>3</v>
       </c>
       <c r="G3524" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3525">
@@ -95589,7 +95589,7 @@
         <v>20</v>
       </c>
       <c r="C3525" t="n">
-        <v>26.58</v>
+        <v>27.13</v>
       </c>
       <c r="D3525" t="inlineStr">
         <is>
@@ -95605,7 +95605,7 @@
         <v>3</v>
       </c>
       <c r="G3525" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3526">
@@ -95616,7 +95616,7 @@
         <v>21</v>
       </c>
       <c r="C3526" t="n">
-        <v>35.43</v>
+        <v>36.28</v>
       </c>
       <c r="D3526" t="inlineStr">
         <is>
@@ -95632,7 +95632,7 @@
         <v>3</v>
       </c>
       <c r="G3526" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3527">
@@ -95643,7 +95643,7 @@
         <v>22</v>
       </c>
       <c r="C3527" t="n">
-        <v>34.35</v>
+        <v>35.25</v>
       </c>
       <c r="D3527" t="inlineStr">
         <is>
@@ -95659,7 +95659,7 @@
         <v>3</v>
       </c>
       <c r="G3527" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3528">
@@ -95670,7 +95670,7 @@
         <v>23</v>
       </c>
       <c r="C3528" t="n">
-        <v>27.99</v>
+        <v>28.81</v>
       </c>
       <c r="D3528" t="inlineStr">
         <is>
@@ -95686,7 +95686,7 @@
         <v>3</v>
       </c>
       <c r="G3528" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3529">
@@ -95697,7 +95697,7 @@
         <v>24</v>
       </c>
       <c r="C3529" t="n">
-        <v>23.07</v>
+        <v>22.96</v>
       </c>
       <c r="D3529" t="inlineStr">
         <is>
@@ -95713,7 +95713,7 @@
         <v>3</v>
       </c>
       <c r="G3529" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3530">
@@ -95724,7 +95724,7 @@
         <v>1</v>
       </c>
       <c r="C3530" t="n">
-        <v>15.1</v>
+        <v>14.03</v>
       </c>
       <c r="D3530" t="inlineStr">
         <is>
@@ -95740,7 +95740,7 @@
         <v>3</v>
       </c>
       <c r="G3530" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3531">
@@ -95751,7 +95751,7 @@
         <v>2</v>
       </c>
       <c r="C3531" t="n">
-        <v>17.08</v>
+        <v>16.84</v>
       </c>
       <c r="D3531" t="inlineStr">
         <is>
@@ -95767,7 +95767,7 @@
         <v>3</v>
       </c>
       <c r="G3531" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3532">
@@ -95778,7 +95778,7 @@
         <v>3</v>
       </c>
       <c r="C3532" t="n">
-        <v>10.26</v>
+        <v>11.4</v>
       </c>
       <c r="D3532" t="inlineStr">
         <is>
@@ -95794,7 +95794,7 @@
         <v>3</v>
       </c>
       <c r="G3532" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3533">
@@ -95805,7 +95805,7 @@
         <v>4</v>
       </c>
       <c r="C3533" t="n">
-        <v>11.32</v>
+        <v>10.79</v>
       </c>
       <c r="D3533" t="inlineStr">
         <is>
@@ -95821,7 +95821,7 @@
         <v>3</v>
       </c>
       <c r="G3533" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3534">
@@ -95832,7 +95832,7 @@
         <v>5</v>
       </c>
       <c r="C3534" t="n">
-        <v>11.77</v>
+        <v>12.71</v>
       </c>
       <c r="D3534" t="inlineStr">
         <is>
@@ -95848,7 +95848,7 @@
         <v>3</v>
       </c>
       <c r="G3534" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3535">
@@ -95859,7 +95859,7 @@
         <v>6</v>
       </c>
       <c r="C3535" t="n">
-        <v>12.65</v>
+        <v>14.15</v>
       </c>
       <c r="D3535" t="inlineStr">
         <is>
@@ -95875,7 +95875,7 @@
         <v>3</v>
       </c>
       <c r="G3535" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3536">
@@ -95886,7 +95886,7 @@
         <v>7</v>
       </c>
       <c r="C3536" t="n">
-        <v>18.41</v>
+        <v>24.98</v>
       </c>
       <c r="D3536" t="inlineStr">
         <is>
@@ -95902,7 +95902,7 @@
         <v>3</v>
       </c>
       <c r="G3536" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3537">
@@ -95913,7 +95913,7 @@
         <v>8</v>
       </c>
       <c r="C3537" t="n">
-        <v>19.68</v>
+        <v>38.43</v>
       </c>
       <c r="D3537" t="inlineStr">
         <is>
@@ -95929,7 +95929,7 @@
         <v>3</v>
       </c>
       <c r="G3537" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3538">
@@ -95940,7 +95940,7 @@
         <v>9</v>
       </c>
       <c r="C3538" t="n">
-        <v>16.72</v>
+        <v>36.03</v>
       </c>
       <c r="D3538" t="inlineStr">
         <is>
@@ -95956,7 +95956,7 @@
         <v>3</v>
       </c>
       <c r="G3538" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3539">
@@ -95967,7 +95967,7 @@
         <v>10</v>
       </c>
       <c r="C3539" t="n">
-        <v>17.9</v>
+        <v>21.56</v>
       </c>
       <c r="D3539" t="inlineStr">
         <is>
@@ -95983,7 +95983,7 @@
         <v>3</v>
       </c>
       <c r="G3539" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3540">
@@ -95994,7 +95994,7 @@
         <v>11</v>
       </c>
       <c r="C3540" t="n">
-        <v>19.27</v>
+        <v>27.23</v>
       </c>
       <c r="D3540" t="inlineStr">
         <is>
@@ -96010,7 +96010,7 @@
         <v>3</v>
       </c>
       <c r="G3540" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3541">
@@ -96021,7 +96021,7 @@
         <v>12</v>
       </c>
       <c r="C3541" t="n">
-        <v>22.99</v>
+        <v>30.29</v>
       </c>
       <c r="D3541" t="inlineStr">
         <is>
@@ -96037,7 +96037,7 @@
         <v>3</v>
       </c>
       <c r="G3541" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3542">
@@ -96048,7 +96048,7 @@
         <v>13</v>
       </c>
       <c r="C3542" t="n">
-        <v>25.12</v>
+        <v>34.58</v>
       </c>
       <c r="D3542" t="inlineStr">
         <is>
@@ -96064,7 +96064,7 @@
         <v>3</v>
       </c>
       <c r="G3542" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3543">
@@ -96075,7 +96075,7 @@
         <v>14</v>
       </c>
       <c r="C3543" t="n">
-        <v>25.43</v>
+        <v>37.11</v>
       </c>
       <c r="D3543" t="inlineStr">
         <is>
@@ -96091,7 +96091,7 @@
         <v>3</v>
       </c>
       <c r="G3543" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3544">
@@ -96102,7 +96102,7 @@
         <v>15</v>
       </c>
       <c r="C3544" t="n">
-        <v>25.32</v>
+        <v>28.4</v>
       </c>
       <c r="D3544" t="inlineStr">
         <is>
@@ -96118,7 +96118,7 @@
         <v>3</v>
       </c>
       <c r="G3544" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3545">
@@ -96129,7 +96129,7 @@
         <v>16</v>
       </c>
       <c r="C3545" t="n">
-        <v>24.39</v>
+        <v>29.86</v>
       </c>
       <c r="D3545" t="inlineStr">
         <is>
@@ -96145,7 +96145,7 @@
         <v>3</v>
       </c>
       <c r="G3545" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3546">
@@ -96156,7 +96156,7 @@
         <v>17</v>
       </c>
       <c r="C3546" t="n">
-        <v>21.08</v>
+        <v>27.72</v>
       </c>
       <c r="D3546" t="inlineStr">
         <is>
@@ -96172,7 +96172,7 @@
         <v>3</v>
       </c>
       <c r="G3546" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3547">
@@ -96183,7 +96183,7 @@
         <v>18</v>
       </c>
       <c r="C3547" t="n">
-        <v>18.01</v>
+        <v>19.84</v>
       </c>
       <c r="D3547" t="inlineStr">
         <is>
@@ -96199,7 +96199,7 @@
         <v>3</v>
       </c>
       <c r="G3547" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3548">
@@ -96210,7 +96210,7 @@
         <v>19</v>
       </c>
       <c r="C3548" t="n">
-        <v>22.9</v>
+        <v>26.88</v>
       </c>
       <c r="D3548" t="inlineStr">
         <is>
@@ -96226,7 +96226,7 @@
         <v>3</v>
       </c>
       <c r="G3548" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3549">
@@ -96237,7 +96237,7 @@
         <v>20</v>
       </c>
       <c r="C3549" t="n">
-        <v>24.24</v>
+        <v>44.64</v>
       </c>
       <c r="D3549" t="inlineStr">
         <is>
@@ -96253,7 +96253,7 @@
         <v>3</v>
       </c>
       <c r="G3549" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3550">
@@ -96264,7 +96264,7 @@
         <v>21</v>
       </c>
       <c r="C3550" t="n">
-        <v>14.79</v>
+        <v>48.64</v>
       </c>
       <c r="D3550" t="inlineStr">
         <is>
@@ -96280,7 +96280,7 @@
         <v>3</v>
       </c>
       <c r="G3550" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3551">
@@ -96291,7 +96291,7 @@
         <v>22</v>
       </c>
       <c r="C3551" t="n">
-        <v>14.68</v>
+        <v>43.67</v>
       </c>
       <c r="D3551" t="inlineStr">
         <is>
@@ -96307,7 +96307,7 @@
         <v>3</v>
       </c>
       <c r="G3551" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3552">
@@ -96318,7 +96318,7 @@
         <v>23</v>
       </c>
       <c r="C3552" t="n">
-        <v>12.74</v>
+        <v>35.79</v>
       </c>
       <c r="D3552" t="inlineStr">
         <is>
@@ -96334,7 +96334,7 @@
         <v>3</v>
       </c>
       <c r="G3552" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3553">
@@ -96345,7 +96345,7 @@
         <v>24</v>
       </c>
       <c r="C3553" t="n">
-        <v>13.09</v>
+        <v>42.21</v>
       </c>
       <c r="D3553" t="inlineStr">
         <is>
@@ -96361,7 +96361,7 @@
         <v>3</v>
       </c>
       <c r="G3553" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3554">
@@ -96388,7 +96388,7 @@
         <v>3</v>
       </c>
       <c r="G3554" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3555">
@@ -96415,7 +96415,7 @@
         <v>3</v>
       </c>
       <c r="G3555" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3556">
@@ -96442,7 +96442,7 @@
         <v>3</v>
       </c>
       <c r="G3556" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3557">
@@ -96469,7 +96469,7 @@
         <v>3</v>
       </c>
       <c r="G3557" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3558">
@@ -96496,7 +96496,7 @@
         <v>3</v>
       </c>
       <c r="G3558" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3559">
@@ -96523,7 +96523,7 @@
         <v>3</v>
       </c>
       <c r="G3559" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3560">
@@ -96534,7 +96534,7 @@
         <v>7</v>
       </c>
       <c r="C3560" t="n">
-        <v>13.98</v>
+        <v>13.5</v>
       </c>
       <c r="D3560" t="inlineStr">
         <is>
@@ -96550,7 +96550,7 @@
         <v>3</v>
       </c>
       <c r="G3560" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3561">
@@ -96561,7 +96561,7 @@
         <v>8</v>
       </c>
       <c r="C3561" t="n">
-        <v>32.65</v>
+        <v>24.03</v>
       </c>
       <c r="D3561" t="inlineStr">
         <is>
@@ -96577,7 +96577,7 @@
         <v>3</v>
       </c>
       <c r="G3561" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3562">
@@ -96588,7 +96588,7 @@
         <v>9</v>
       </c>
       <c r="C3562" t="n">
-        <v>40.42</v>
+        <v>32.17</v>
       </c>
       <c r="D3562" t="inlineStr">
         <is>
@@ -96604,7 +96604,7 @@
         <v>3</v>
       </c>
       <c r="G3562" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3563">
@@ -96615,7 +96615,7 @@
         <v>10</v>
       </c>
       <c r="C3563" t="n">
-        <v>28.51</v>
+        <v>27.96</v>
       </c>
       <c r="D3563" t="inlineStr">
         <is>
@@ -96631,7 +96631,7 @@
         <v>3</v>
       </c>
       <c r="G3563" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3564">
@@ -96642,7 +96642,7 @@
         <v>11</v>
       </c>
       <c r="C3564" t="n">
-        <v>20.96</v>
+        <v>20.52</v>
       </c>
       <c r="D3564" t="inlineStr">
         <is>
@@ -96658,7 +96658,7 @@
         <v>3</v>
       </c>
       <c r="G3564" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3565">
@@ -96669,7 +96669,7 @@
         <v>12</v>
       </c>
       <c r="C3565" t="n">
-        <v>21.44</v>
+        <v>21.01</v>
       </c>
       <c r="D3565" t="inlineStr">
         <is>
@@ -96685,7 +96685,7 @@
         <v>3</v>
       </c>
       <c r="G3565" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3566">
@@ -96696,7 +96696,7 @@
         <v>13</v>
       </c>
       <c r="C3566" t="n">
-        <v>21.1</v>
+        <v>20.81</v>
       </c>
       <c r="D3566" t="inlineStr">
         <is>
@@ -96712,7 +96712,7 @@
         <v>3</v>
       </c>
       <c r="G3566" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3567">
@@ -96723,7 +96723,7 @@
         <v>14</v>
       </c>
       <c r="C3567" t="n">
-        <v>20.69</v>
+        <v>20.39</v>
       </c>
       <c r="D3567" t="inlineStr">
         <is>
@@ -96739,7 +96739,7 @@
         <v>3</v>
       </c>
       <c r="G3567" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3568">
@@ -96750,7 +96750,7 @@
         <v>15</v>
       </c>
       <c r="C3568" t="n">
-        <v>20.62</v>
+        <v>20.3</v>
       </c>
       <c r="D3568" t="inlineStr">
         <is>
@@ -96766,7 +96766,7 @@
         <v>3</v>
       </c>
       <c r="G3568" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3569">
@@ -96777,7 +96777,7 @@
         <v>16</v>
       </c>
       <c r="C3569" t="n">
-        <v>21.14</v>
+        <v>20.84</v>
       </c>
       <c r="D3569" t="inlineStr">
         <is>
@@ -96793,7 +96793,7 @@
         <v>3</v>
       </c>
       <c r="G3569" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3570">
@@ -96804,7 +96804,7 @@
         <v>17</v>
       </c>
       <c r="C3570" t="n">
-        <v>21.48</v>
+        <v>21.16</v>
       </c>
       <c r="D3570" t="inlineStr">
         <is>
@@ -96820,7 +96820,7 @@
         <v>3</v>
       </c>
       <c r="G3570" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3571">
@@ -96831,7 +96831,7 @@
         <v>18</v>
       </c>
       <c r="C3571" t="n">
-        <v>19.68</v>
+        <v>19.36</v>
       </c>
       <c r="D3571" t="inlineStr">
         <is>
@@ -96847,7 +96847,7 @@
         <v>3</v>
       </c>
       <c r="G3571" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3572">
@@ -96858,7 +96858,7 @@
         <v>19</v>
       </c>
       <c r="C3572" t="n">
-        <v>29.29</v>
+        <v>25.11</v>
       </c>
       <c r="D3572" t="inlineStr">
         <is>
@@ -96874,7 +96874,7 @@
         <v>3</v>
       </c>
       <c r="G3572" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3573">
@@ -96885,7 +96885,7 @@
         <v>20</v>
       </c>
       <c r="C3573" t="n">
-        <v>34.51</v>
+        <v>17.6</v>
       </c>
       <c r="D3573" t="inlineStr">
         <is>
@@ -96901,7 +96901,7 @@
         <v>3</v>
       </c>
       <c r="G3573" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3574">
@@ -96912,7 +96912,7 @@
         <v>21</v>
       </c>
       <c r="C3574" t="n">
-        <v>60.53</v>
+        <v>24.09</v>
       </c>
       <c r="D3574" t="inlineStr">
         <is>
@@ -96928,7 +96928,7 @@
         <v>3</v>
       </c>
       <c r="G3574" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3575">
@@ -96939,7 +96939,7 @@
         <v>22</v>
       </c>
       <c r="C3575" t="n">
-        <v>53.21</v>
+        <v>19.93</v>
       </c>
       <c r="D3575" t="inlineStr">
         <is>
@@ -96955,7 +96955,7 @@
         <v>3</v>
       </c>
       <c r="G3575" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3576">
@@ -96966,7 +96966,7 @@
         <v>23</v>
       </c>
       <c r="C3576" t="n">
-        <v>24.03</v>
+        <v>11.59</v>
       </c>
       <c r="D3576" t="inlineStr">
         <is>
@@ -96982,7 +96982,7 @@
         <v>3</v>
       </c>
       <c r="G3576" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
       </c>
     </row>
     <row r="3577">
@@ -96993,7 +96993,7 @@
         <v>24</v>
       </c>
       <c r="C3577" t="n">
-        <v>26.48</v>
+        <v>13.95</v>
       </c>
       <c r="D3577" t="inlineStr">
         <is>
@@ -97009,7 +97009,655 @@
         <v>3</v>
       </c>
       <c r="G3577" s="2" t="n">
-        <v>46292.47933705992</v>
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3578">
+      <c r="A3578" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3578" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3578" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D3578" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3578" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3578" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3578" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3579">
+      <c r="A3579" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3579" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3579" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="D3579" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3579" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3579" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3579" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3580">
+      <c r="A3580" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3580" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3580" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="D3580" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3580" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3580" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3580" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3581">
+      <c r="A3581" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3581" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3581" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="D3581" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3581" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3581" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3581" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3582">
+      <c r="A3582" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3582" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3582" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="D3582" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3582" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3582" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3582" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3583">
+      <c r="A3583" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3583" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3583" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="D3583" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3583" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3583" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3583" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3584">
+      <c r="A3584" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3584" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3584" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="D3584" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3584" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3584" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3584" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3585">
+      <c r="A3585" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3585" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3585" t="n">
+        <v>22.87</v>
+      </c>
+      <c r="D3585" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3585" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3585" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3585" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3586">
+      <c r="A3586" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3586" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3586" t="n">
+        <v>30.84</v>
+      </c>
+      <c r="D3586" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3586" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3586" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3586" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3587">
+      <c r="A3587" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3587" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3587" t="n">
+        <v>30.76</v>
+      </c>
+      <c r="D3587" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3587" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3587" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3587" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3588">
+      <c r="A3588" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3588" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3588" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="D3588" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3588" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3588" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3588" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3589">
+      <c r="A3589" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3589" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3589" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="D3589" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3589" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3589" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3589" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3590">
+      <c r="A3590" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3590" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3590" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="D3590" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3590" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3590" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3590" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3591">
+      <c r="A3591" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3591" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3591" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="D3591" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3591" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3591" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3591" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3592">
+      <c r="A3592" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3592" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3592" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="D3592" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3592" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3592" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3592" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3593">
+      <c r="A3593" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3593" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3593" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="D3593" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3593" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3593" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3593" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3594">
+      <c r="A3594" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3594" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3594" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="D3594" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3594" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3594" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3594" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3595">
+      <c r="A3595" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3595" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3595" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="D3595" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3595" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3595" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3595" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3596">
+      <c r="A3596" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3596" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3596" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="D3596" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3596" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3596" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3596" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3597">
+      <c r="A3597" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3597" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3597" t="n">
+        <v>34.94</v>
+      </c>
+      <c r="D3597" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3597" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3597" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3597" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3598">
+      <c r="A3598" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3598" t="n">
+        <v>21</v>
+      </c>
+      <c r="C3598" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="D3598" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3598" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3598" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3598" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3599">
+      <c r="A3599" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3599" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3599" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="D3599" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3599" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3599" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3599" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3600">
+      <c r="A3600" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3600" t="n">
+        <v>23</v>
+      </c>
+      <c r="C3600" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="D3600" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3600" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3600" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3600" s="2" t="n">
+        <v>46292.87449335245</v>
+      </c>
+    </row>
+    <row r="3601">
+      <c r="A3601" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3601" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3601" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="D3601" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E3601" t="inlineStr">
+        <is>
+          <t>A2_prdemcad_20260901_20260930</t>
+        </is>
+      </c>
+      <c r="F3601" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3601" s="2" t="n">
+        <v>46292.87449335245</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3324">
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3333">
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3335">
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3337">
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3341">
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3343">
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3344">
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3345">
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3346">
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3347">
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3355">
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3356">
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3357">
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3360">
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3362">
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3364">
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3365">
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3366">
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3367">
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3368">
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3369">
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3370">
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3371">
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3372">
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3373">
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3374">
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3375">
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3376">
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3377">
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3378">
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3379">
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3380">
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3381">
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3382">
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3383">
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3384">
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3385">
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3386">
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3387">
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3388">
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3389">
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3390">
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3391">
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3392">
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3393">
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3394">
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3395">
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3396">
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3397">
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3398">
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3399">
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3400">
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3401">
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3402">
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3403">
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3404">
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3405">
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3406">
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3407">
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3408">
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3409">
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3410">
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3411">
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3412">
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3413">
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3415">
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3416">
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3417">
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3418">
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3419">
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3420">
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3421">
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3422">
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3423">
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3424">
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3425">
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3426">
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3427">
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3428">
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3429">
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3430">
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3431">
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3432">
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3433">
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3434">
@@ -93148,7 +93148,7 @@
         <v>3</v>
       </c>
       <c r="G3434" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3435">
@@ -93175,7 +93175,7 @@
         <v>3</v>
       </c>
       <c r="G3435" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3436">
@@ -93202,7 +93202,7 @@
         <v>3</v>
       </c>
       <c r="G3436" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3437">
@@ -93229,7 +93229,7 @@
         <v>3</v>
       </c>
       <c r="G3437" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3438">
@@ -93256,7 +93256,7 @@
         <v>3</v>
       </c>
       <c r="G3438" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3439">
@@ -93283,7 +93283,7 @@
         <v>3</v>
       </c>
       <c r="G3439" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3440">
@@ -93310,7 +93310,7 @@
         <v>3</v>
       </c>
       <c r="G3440" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3441">
@@ -93337,7 +93337,7 @@
         <v>3</v>
       </c>
       <c r="G3441" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3442">
@@ -93364,7 +93364,7 @@
         <v>3</v>
       </c>
       <c r="G3442" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3443">
@@ -93391,7 +93391,7 @@
         <v>3</v>
       </c>
       <c r="G3443" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3444">
@@ -93418,7 +93418,7 @@
         <v>3</v>
       </c>
       <c r="G3444" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3445">
@@ -93445,7 +93445,7 @@
         <v>3</v>
       </c>
       <c r="G3445" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3446">
@@ -93472,7 +93472,7 @@
         <v>3</v>
       </c>
       <c r="G3446" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3447">
@@ -93499,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="G3447" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3448">
@@ -93526,7 +93526,7 @@
         <v>3</v>
       </c>
       <c r="G3448" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3449">
@@ -93553,7 +93553,7 @@
         <v>3</v>
       </c>
       <c r="G3449" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3450">
@@ -93580,7 +93580,7 @@
         <v>3</v>
       </c>
       <c r="G3450" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3451">
@@ -93607,7 +93607,7 @@
         <v>3</v>
       </c>
       <c r="G3451" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3452">
@@ -93634,7 +93634,7 @@
         <v>3</v>
       </c>
       <c r="G3452" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3453">
@@ -93661,7 +93661,7 @@
         <v>3</v>
       </c>
       <c r="G3453" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3454">
@@ -93688,7 +93688,7 @@
         <v>3</v>
       </c>
       <c r="G3454" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3455">
@@ -93715,7 +93715,7 @@
         <v>3</v>
       </c>
       <c r="G3455" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3456">
@@ -93742,7 +93742,7 @@
         <v>3</v>
       </c>
       <c r="G3456" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3457">
@@ -93769,7 +93769,7 @@
         <v>3</v>
       </c>
       <c r="G3457" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3458">
@@ -93796,7 +93796,7 @@
         <v>3</v>
       </c>
       <c r="G3458" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3459">
@@ -93823,7 +93823,7 @@
         <v>3</v>
       </c>
       <c r="G3459" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3460">
@@ -93850,7 +93850,7 @@
         <v>3</v>
       </c>
       <c r="G3460" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3461">
@@ -93877,7 +93877,7 @@
         <v>3</v>
       </c>
       <c r="G3461" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3462">
@@ -93904,7 +93904,7 @@
         <v>3</v>
       </c>
       <c r="G3462" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3463">
@@ -93931,7 +93931,7 @@
         <v>3</v>
       </c>
       <c r="G3463" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3464">
@@ -93958,7 +93958,7 @@
         <v>3</v>
       </c>
       <c r="G3464" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3465">
@@ -93985,7 +93985,7 @@
         <v>3</v>
       </c>
       <c r="G3465" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3466">
@@ -94012,7 +94012,7 @@
         <v>3</v>
       </c>
       <c r="G3466" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3467">
@@ -94039,7 +94039,7 @@
         <v>3</v>
       </c>
       <c r="G3467" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3468">
@@ -94066,7 +94066,7 @@
         <v>3</v>
       </c>
       <c r="G3468" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3469">
@@ -94093,7 +94093,7 @@
         <v>3</v>
       </c>
       <c r="G3469" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3470">
@@ -94120,7 +94120,7 @@
         <v>3</v>
       </c>
       <c r="G3470" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3471">
@@ -94147,7 +94147,7 @@
         <v>3</v>
       </c>
       <c r="G3471" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3472">
@@ -94174,7 +94174,7 @@
         <v>3</v>
       </c>
       <c r="G3472" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3473">
@@ -94201,7 +94201,7 @@
         <v>3</v>
       </c>
       <c r="G3473" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3474">
@@ -94228,7 +94228,7 @@
         <v>3</v>
       </c>
       <c r="G3474" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3475">
@@ -94255,7 +94255,7 @@
         <v>3</v>
       </c>
       <c r="G3475" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3476">
@@ -94282,7 +94282,7 @@
         <v>3</v>
       </c>
       <c r="G3476" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3477">
@@ -94309,7 +94309,7 @@
         <v>3</v>
       </c>
       <c r="G3477" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3478">
@@ -94336,7 +94336,7 @@
         <v>3</v>
       </c>
       <c r="G3478" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3479">
@@ -94363,7 +94363,7 @@
         <v>3</v>
       </c>
       <c r="G3479" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3480">
@@ -94390,7 +94390,7 @@
         <v>3</v>
       </c>
       <c r="G3480" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3481">
@@ -94417,7 +94417,7 @@
         <v>3</v>
       </c>
       <c r="G3481" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3482">
@@ -94444,7 +94444,7 @@
         <v>3</v>
       </c>
       <c r="G3482" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3483">
@@ -94471,7 +94471,7 @@
         <v>3</v>
       </c>
       <c r="G3483" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3484">
@@ -94498,7 +94498,7 @@
         <v>3</v>
       </c>
       <c r="G3484" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3485">
@@ -94525,7 +94525,7 @@
         <v>3</v>
       </c>
       <c r="G3485" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3486">
@@ -94552,7 +94552,7 @@
         <v>3</v>
       </c>
       <c r="G3486" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3487">
@@ -94579,7 +94579,7 @@
         <v>3</v>
       </c>
       <c r="G3487" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3488">
@@ -94606,7 +94606,7 @@
         <v>3</v>
       </c>
       <c r="G3488" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3489">
@@ -94633,7 +94633,7 @@
         <v>3</v>
       </c>
       <c r="G3489" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3490">
@@ -94660,7 +94660,7 @@
         <v>3</v>
       </c>
       <c r="G3490" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3491">
@@ -94687,7 +94687,7 @@
         <v>3</v>
       </c>
       <c r="G3491" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3492">
@@ -94714,7 +94714,7 @@
         <v>3</v>
       </c>
       <c r="G3492" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3493">
@@ -94741,7 +94741,7 @@
         <v>3</v>
       </c>
       <c r="G3493" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3494">
@@ -94768,7 +94768,7 @@
         <v>3</v>
       </c>
       <c r="G3494" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3495">
@@ -94795,7 +94795,7 @@
         <v>3</v>
       </c>
       <c r="G3495" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3496">
@@ -94822,7 +94822,7 @@
         <v>3</v>
       </c>
       <c r="G3496" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3497">
@@ -94849,7 +94849,7 @@
         <v>3</v>
       </c>
       <c r="G3497" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3498">
@@ -94876,7 +94876,7 @@
         <v>3</v>
       </c>
       <c r="G3498" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3499">
@@ -94903,7 +94903,7 @@
         <v>3</v>
       </c>
       <c r="G3499" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3500">
@@ -94930,7 +94930,7 @@
         <v>3</v>
       </c>
       <c r="G3500" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3501">
@@ -94957,7 +94957,7 @@
         <v>3</v>
       </c>
       <c r="G3501" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3502">
@@ -94984,7 +94984,7 @@
         <v>3</v>
       </c>
       <c r="G3502" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3503">
@@ -95011,7 +95011,7 @@
         <v>3</v>
       </c>
       <c r="G3503" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3504">
@@ -95038,7 +95038,7 @@
         <v>3</v>
       </c>
       <c r="G3504" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3505">
@@ -95065,7 +95065,7 @@
         <v>3</v>
       </c>
       <c r="G3505" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3506">
@@ -95092,7 +95092,7 @@
         <v>3</v>
       </c>
       <c r="G3506" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3507">
@@ -95119,7 +95119,7 @@
         <v>3</v>
       </c>
       <c r="G3507" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3508">
@@ -95146,7 +95146,7 @@
         <v>3</v>
       </c>
       <c r="G3508" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3509">
@@ -95173,7 +95173,7 @@
         <v>3</v>
       </c>
       <c r="G3509" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3510">
@@ -95200,7 +95200,7 @@
         <v>3</v>
       </c>
       <c r="G3510" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3511">
@@ -95227,7 +95227,7 @@
         <v>3</v>
       </c>
       <c r="G3511" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3512">
@@ -95254,7 +95254,7 @@
         <v>3</v>
       </c>
       <c r="G3512" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3513">
@@ -95281,7 +95281,7 @@
         <v>3</v>
       </c>
       <c r="G3513" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3514">
@@ -95308,7 +95308,7 @@
         <v>3</v>
       </c>
       <c r="G3514" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3515">
@@ -95335,7 +95335,7 @@
         <v>3</v>
       </c>
       <c r="G3515" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3516">
@@ -95362,7 +95362,7 @@
         <v>3</v>
       </c>
       <c r="G3516" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3517">
@@ -95389,7 +95389,7 @@
         <v>3</v>
       </c>
       <c r="G3517" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3518">
@@ -95416,7 +95416,7 @@
         <v>3</v>
       </c>
       <c r="G3518" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3519">
@@ -95443,7 +95443,7 @@
         <v>3</v>
       </c>
       <c r="G3519" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3520">
@@ -95470,7 +95470,7 @@
         <v>3</v>
       </c>
       <c r="G3520" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3521">
@@ -95497,7 +95497,7 @@
         <v>3</v>
       </c>
       <c r="G3521" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3522">
@@ -95524,7 +95524,7 @@
         <v>3</v>
       </c>
       <c r="G3522" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3523">
@@ -95551,7 +95551,7 @@
         <v>3</v>
       </c>
       <c r="G3523" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3524">
@@ -95578,7 +95578,7 @@
         <v>3</v>
       </c>
       <c r="G3524" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3525">
@@ -95605,7 +95605,7 @@
         <v>3</v>
       </c>
       <c r="G3525" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3526">
@@ -95632,7 +95632,7 @@
         <v>3</v>
       </c>
       <c r="G3526" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3527">
@@ -95659,7 +95659,7 @@
         <v>3</v>
       </c>
       <c r="G3527" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3528">
@@ -95686,7 +95686,7 @@
         <v>3</v>
       </c>
       <c r="G3528" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3529">
@@ -95713,7 +95713,7 @@
         <v>3</v>
       </c>
       <c r="G3529" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3530">
@@ -95740,7 +95740,7 @@
         <v>3</v>
       </c>
       <c r="G3530" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3531">
@@ -95767,7 +95767,7 @@
         <v>3</v>
       </c>
       <c r="G3531" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3532">
@@ -95794,7 +95794,7 @@
         <v>3</v>
       </c>
       <c r="G3532" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3533">
@@ -95821,7 +95821,7 @@
         <v>3</v>
       </c>
       <c r="G3533" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3534">
@@ -95848,7 +95848,7 @@
         <v>3</v>
       </c>
       <c r="G3534" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3535">
@@ -95875,7 +95875,7 @@
         <v>3</v>
       </c>
       <c r="G3535" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3536">
@@ -95902,7 +95902,7 @@
         <v>3</v>
       </c>
       <c r="G3536" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3537">
@@ -95929,7 +95929,7 @@
         <v>3</v>
       </c>
       <c r="G3537" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3538">
@@ -95956,7 +95956,7 @@
         <v>3</v>
       </c>
       <c r="G3538" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3539">
@@ -95983,7 +95983,7 @@
         <v>3</v>
       </c>
       <c r="G3539" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3540">
@@ -96010,7 +96010,7 @@
         <v>3</v>
       </c>
       <c r="G3540" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3541">
@@ -96037,7 +96037,7 @@
         <v>3</v>
       </c>
       <c r="G3541" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3542">
@@ -96064,7 +96064,7 @@
         <v>3</v>
       </c>
       <c r="G3542" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3543">
@@ -96091,7 +96091,7 @@
         <v>3</v>
       </c>
       <c r="G3543" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3544">
@@ -96118,7 +96118,7 @@
         <v>3</v>
       </c>
       <c r="G3544" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3545">
@@ -96145,7 +96145,7 @@
         <v>3</v>
       </c>
       <c r="G3545" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3546">
@@ -96172,7 +96172,7 @@
         <v>3</v>
       </c>
       <c r="G3546" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3547">
@@ -96199,7 +96199,7 @@
         <v>3</v>
       </c>
       <c r="G3547" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3548">
@@ -96226,7 +96226,7 @@
         <v>3</v>
       </c>
       <c r="G3548" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3549">
@@ -96253,7 +96253,7 @@
         <v>3</v>
       </c>
       <c r="G3549" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3550">
@@ -96280,7 +96280,7 @@
         <v>3</v>
       </c>
       <c r="G3550" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3551">
@@ -96307,7 +96307,7 @@
         <v>3</v>
       </c>
       <c r="G3551" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3552">
@@ -96334,7 +96334,7 @@
         <v>3</v>
       </c>
       <c r="G3552" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3553">
@@ -96361,7 +96361,7 @@
         <v>3</v>
       </c>
       <c r="G3553" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3554">
@@ -96388,7 +96388,7 @@
         <v>3</v>
       </c>
       <c r="G3554" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3555">
@@ -96415,7 +96415,7 @@
         <v>3</v>
       </c>
       <c r="G3555" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3556">
@@ -96442,7 +96442,7 @@
         <v>3</v>
       </c>
       <c r="G3556" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3557">
@@ -96469,7 +96469,7 @@
         <v>3</v>
       </c>
       <c r="G3557" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3558">
@@ -96496,7 +96496,7 @@
         <v>3</v>
       </c>
       <c r="G3558" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3559">
@@ -96523,7 +96523,7 @@
         <v>3</v>
       </c>
       <c r="G3559" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3560">
@@ -96550,7 +96550,7 @@
         <v>3</v>
       </c>
       <c r="G3560" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3561">
@@ -96577,7 +96577,7 @@
         <v>3</v>
       </c>
       <c r="G3561" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3562">
@@ -96604,7 +96604,7 @@
         <v>3</v>
       </c>
       <c r="G3562" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3563">
@@ -96631,7 +96631,7 @@
         <v>3</v>
       </c>
       <c r="G3563" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3564">
@@ -96658,7 +96658,7 @@
         <v>3</v>
       </c>
       <c r="G3564" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3565">
@@ -96685,7 +96685,7 @@
         <v>3</v>
       </c>
       <c r="G3565" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3566">
@@ -96712,7 +96712,7 @@
         <v>3</v>
       </c>
       <c r="G3566" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3567">
@@ -96739,7 +96739,7 @@
         <v>3</v>
       </c>
       <c r="G3567" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3568">
@@ -96766,7 +96766,7 @@
         <v>3</v>
       </c>
       <c r="G3568" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3569">
@@ -96793,7 +96793,7 @@
         <v>3</v>
       </c>
       <c r="G3569" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3570">
@@ -96820,7 +96820,7 @@
         <v>3</v>
       </c>
       <c r="G3570" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3571">
@@ -96847,7 +96847,7 @@
         <v>3</v>
       </c>
       <c r="G3571" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3572">
@@ -96874,7 +96874,7 @@
         <v>3</v>
       </c>
       <c r="G3572" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3573">
@@ -96901,7 +96901,7 @@
         <v>3</v>
       </c>
       <c r="G3573" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3574">
@@ -96928,7 +96928,7 @@
         <v>3</v>
       </c>
       <c r="G3574" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3575">
@@ -96955,7 +96955,7 @@
         <v>3</v>
       </c>
       <c r="G3575" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3576">
@@ -96982,7 +96982,7 @@
         <v>3</v>
       </c>
       <c r="G3576" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3577">
@@ -97009,7 +97009,7 @@
         <v>3</v>
       </c>
       <c r="G3577" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3578">
@@ -97036,7 +97036,7 @@
         <v>3</v>
       </c>
       <c r="G3578" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3579">
@@ -97063,7 +97063,7 @@
         <v>3</v>
       </c>
       <c r="G3579" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3580">
@@ -97090,7 +97090,7 @@
         <v>3</v>
       </c>
       <c r="G3580" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3581">
@@ -97117,7 +97117,7 @@
         <v>3</v>
       </c>
       <c r="G3581" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3582">
@@ -97144,7 +97144,7 @@
         <v>3</v>
       </c>
       <c r="G3582" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3583">
@@ -97171,7 +97171,7 @@
         <v>3</v>
       </c>
       <c r="G3583" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3584">
@@ -97198,7 +97198,7 @@
         <v>3</v>
       </c>
       <c r="G3584" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3585">
@@ -97225,7 +97225,7 @@
         <v>3</v>
       </c>
       <c r="G3585" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3586">
@@ -97252,7 +97252,7 @@
         <v>3</v>
       </c>
       <c r="G3586" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3587">
@@ -97279,7 +97279,7 @@
         <v>3</v>
       </c>
       <c r="G3587" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3588">
@@ -97306,7 +97306,7 @@
         <v>3</v>
       </c>
       <c r="G3588" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3589">
@@ -97333,7 +97333,7 @@
         <v>3</v>
       </c>
       <c r="G3589" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3590">
@@ -97360,7 +97360,7 @@
         <v>3</v>
       </c>
       <c r="G3590" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3591">
@@ -97387,7 +97387,7 @@
         <v>3</v>
       </c>
       <c r="G3591" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3592">
@@ -97414,7 +97414,7 @@
         <v>3</v>
       </c>
       <c r="G3592" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3593">
@@ -97441,7 +97441,7 @@
         <v>3</v>
       </c>
       <c r="G3593" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3594">
@@ -97468,7 +97468,7 @@
         <v>3</v>
       </c>
       <c r="G3594" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3595">
@@ -97495,7 +97495,7 @@
         <v>3</v>
       </c>
       <c r="G3595" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3596">
@@ -97522,7 +97522,7 @@
         <v>3</v>
       </c>
       <c r="G3596" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3597">
@@ -97549,7 +97549,7 @@
         <v>3</v>
       </c>
       <c r="G3597" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3598">
@@ -97576,7 +97576,7 @@
         <v>3</v>
       </c>
       <c r="G3598" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3599">
@@ -97603,7 +97603,7 @@
         <v>3</v>
       </c>
       <c r="G3599" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3600">
@@ -97630,7 +97630,7 @@
         <v>3</v>
       </c>
       <c r="G3600" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
     <row r="3601">
@@ -97657,7 +97657,7 @@
         <v>3</v>
       </c>
       <c r="G3601" s="2" t="n">
-        <v>46292.87449335245</v>
+        <v>46293.54374556483</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_prdemcad.xlsx
+++ b/Historico_prdemcad.xlsx
@@ -89908,7 +89908,7 @@
         <v>3</v>
       </c>
       <c r="G3314" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3315">
@@ -89935,7 +89935,7 @@
         <v>3</v>
       </c>
       <c r="G3315" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3316">
@@ -89962,7 +89962,7 @@
         <v>3</v>
       </c>
       <c r="G3316" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3317">
@@ -89989,7 +89989,7 @@
         <v>3</v>
       </c>
       <c r="G3317" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3318">
@@ -90016,7 +90016,7 @@
         <v>3</v>
       </c>
       <c r="G3318" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3319">
@@ -90043,7 +90043,7 @@
         <v>3</v>
       </c>
       <c r="G3319" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3320">
@@ -90070,7 +90070,7 @@
         <v>3</v>
       </c>
       <c r="G3320" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3321">
@@ -90097,7 +90097,7 @@
         <v>3</v>
       </c>
       <c r="G3321" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3322">
@@ -90124,7 +90124,7 @@
         <v>3</v>
       </c>
       <c r="G3322" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3323">
@@ -90151,7 +90151,7 @@
         <v>3</v>
       </c>
       <c r="G3323" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3324">
@@ -90178,7 +90178,7 @@
         <v>3</v>
       </c>
       <c r="G3324" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3325">
@@ -90205,7 +90205,7 @@
         <v>3</v>
       </c>
       <c r="G3325" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3326">
@@ -90232,7 +90232,7 @@
         <v>3</v>
       </c>
       <c r="G3326" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3327">
@@ -90259,7 +90259,7 @@
         <v>3</v>
       </c>
       <c r="G3327" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3328">
@@ -90286,7 +90286,7 @@
         <v>3</v>
       </c>
       <c r="G3328" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3329">
@@ -90313,7 +90313,7 @@
         <v>3</v>
       </c>
       <c r="G3329" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3330">
@@ -90340,7 +90340,7 @@
         <v>3</v>
       </c>
       <c r="G3330" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3331">
@@ -90367,7 +90367,7 @@
         <v>3</v>
       </c>
       <c r="G3331" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3332">
@@ -90394,7 +90394,7 @@
         <v>3</v>
       </c>
       <c r="G3332" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3333">
@@ -90421,7 +90421,7 @@
         <v>3</v>
       </c>
       <c r="G3333" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3334">
@@ -90448,7 +90448,7 @@
         <v>3</v>
       </c>
       <c r="G3334" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3335">
@@ -90475,7 +90475,7 @@
         <v>3</v>
       </c>
       <c r="G3335" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3336">
@@ -90502,7 +90502,7 @@
         <v>3</v>
       </c>
       <c r="G3336" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3337">
@@ -90529,7 +90529,7 @@
         <v>3</v>
       </c>
       <c r="G3337" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3338">
@@ -90556,7 +90556,7 @@
         <v>3</v>
       </c>
       <c r="G3338" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3339">
@@ -90583,7 +90583,7 @@
         <v>3</v>
       </c>
       <c r="G3339" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3340">
@@ -90610,7 +90610,7 @@
         <v>3</v>
       </c>
       <c r="G3340" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3341">
@@ -90637,7 +90637,7 @@
         <v>3</v>
       </c>
       <c r="G3341" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3342">
@@ -90664,7 +90664,7 @@
         <v>3</v>
       </c>
       <c r="G3342" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3343">
@@ -90691,7 +90691,7 @@
         <v>3</v>
       </c>
       <c r="G3343" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3344">
@@ -90718,7 +90718,7 @@
         <v>3</v>
       </c>
       <c r="G3344" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3345">
@@ -90745,7 +90745,7 @@
         <v>3</v>
       </c>
       <c r="G3345" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3346">
@@ -90772,7 +90772,7 @@
         <v>3</v>
       </c>
       <c r="G3346" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3347">
@@ -90799,7 +90799,7 @@
         <v>3</v>
       </c>
       <c r="G3347" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3348">
@@ -90826,7 +90826,7 @@
         <v>3</v>
       </c>
       <c r="G3348" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3349">
@@ -90853,7 +90853,7 @@
         <v>3</v>
       </c>
       <c r="G3349" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3350">
@@ -90880,7 +90880,7 @@
         <v>3</v>
       </c>
       <c r="G3350" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3351">
@@ -90907,7 +90907,7 @@
         <v>3</v>
       </c>
       <c r="G3351" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3352">
@@ -90934,7 +90934,7 @@
         <v>3</v>
       </c>
       <c r="G3352" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3353">
@@ -90961,7 +90961,7 @@
         <v>3</v>
       </c>
       <c r="G3353" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3354">
@@ -90988,7 +90988,7 @@
         <v>3</v>
       </c>
       <c r="G3354" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3355">
@@ -91015,7 +91015,7 @@
         <v>3</v>
       </c>
       <c r="G3355" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3356">
@@ -91042,7 +91042,7 @@
         <v>3</v>
       </c>
       <c r="G3356" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3357">
@@ -91069,7 +91069,7 @@
         <v>3</v>
       </c>
       <c r="G3357" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3358">
@@ -91096,7 +91096,7 @@
         <v>3</v>
       </c>
       <c r="G3358" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3359">
@@ -91123,7 +91123,7 @@
         <v>3</v>
       </c>
       <c r="G3359" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3360">
@@ -91150,7 +91150,7 @@
         <v>3</v>
       </c>
       <c r="G3360" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3361">
@@ -91177,7 +91177,7 @@
         <v>3</v>
       </c>
       <c r="G3361" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3362">
@@ -91204,7 +91204,7 @@
         <v>3</v>
       </c>
       <c r="G3362" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3363">
@@ -91231,7 +91231,7 @@
         <v>3</v>
       </c>
       <c r="G3363" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3364">
@@ -91258,7 +91258,7 @@
         <v>3</v>
       </c>
       <c r="G3364" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3365">
@@ -91285,7 +91285,7 @@
         <v>3</v>
       </c>
       <c r="G3365" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3366">
@@ -91312,7 +91312,7 @@
         <v>3</v>
       </c>
       <c r="G3366" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3367">
@@ -91339,7 +91339,7 @@
         <v>3</v>
       </c>
       <c r="G3367" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3368">
@@ -91366,7 +91366,7 @@
         <v>3</v>
       </c>
       <c r="G3368" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3369">
@@ -91393,7 +91393,7 @@
         <v>3</v>
       </c>
       <c r="G3369" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3370">
@@ -91420,7 +91420,7 @@
         <v>3</v>
       </c>
       <c r="G3370" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3371">
@@ -91447,7 +91447,7 @@
         <v>3</v>
       </c>
       <c r="G3371" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3372">
@@ -91474,7 +91474,7 @@
         <v>3</v>
       </c>
       <c r="G3372" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3373">
@@ -91501,7 +91501,7 @@
         <v>3</v>
       </c>
       <c r="G3373" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3374">
@@ -91528,7 +91528,7 @@
         <v>3</v>
       </c>
       <c r="G3374" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3375">
@@ -91555,7 +91555,7 @@
         <v>3</v>
       </c>
       <c r="G3375" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3376">
@@ -91582,7 +91582,7 @@
         <v>3</v>
       </c>
       <c r="G3376" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3377">
@@ -91609,7 +91609,7 @@
         <v>3</v>
       </c>
       <c r="G3377" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3378">
@@ -91636,7 +91636,7 @@
         <v>3</v>
       </c>
       <c r="G3378" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3379">
@@ -91663,7 +91663,7 @@
         <v>3</v>
       </c>
       <c r="G3379" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3380">
@@ -91690,7 +91690,7 @@
         <v>3</v>
       </c>
       <c r="G3380" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3381">
@@ -91717,7 +91717,7 @@
         <v>3</v>
       </c>
       <c r="G3381" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3382">
@@ -91744,7 +91744,7 @@
         <v>3</v>
       </c>
       <c r="G3382" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3383">
@@ -91771,7 +91771,7 @@
         <v>3</v>
       </c>
       <c r="G3383" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3384">
@@ -91798,7 +91798,7 @@
         <v>3</v>
       </c>
       <c r="G3384" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3385">
@@ -91825,7 +91825,7 @@
         <v>3</v>
       </c>
       <c r="G3385" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3386">
@@ -91852,7 +91852,7 @@
         <v>3</v>
       </c>
       <c r="G3386" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3387">
@@ -91879,7 +91879,7 @@
         <v>3</v>
       </c>
       <c r="G3387" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3388">
@@ -91906,7 +91906,7 @@
         <v>3</v>
       </c>
       <c r="G3388" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3389">
@@ -91933,7 +91933,7 @@
         <v>3</v>
       </c>
       <c r="G3389" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3390">
@@ -91960,7 +91960,7 @@
         <v>3</v>
       </c>
       <c r="G3390" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3391">
@@ -91987,7 +91987,7 @@
         <v>3</v>
       </c>
       <c r="G3391" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3392">
@@ -92014,7 +92014,7 @@
         <v>3</v>
       </c>
       <c r="G3392" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3393">
@@ -92041,7 +92041,7 @@
         <v>3</v>
       </c>
       <c r="G3393" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3394">
@@ -92068,7 +92068,7 @@
         <v>3</v>
       </c>
       <c r="G3394" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3395">
@@ -92095,7 +92095,7 @@
         <v>3</v>
       </c>
       <c r="G3395" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3396">
@@ -92122,7 +92122,7 @@
         <v>3</v>
       </c>
       <c r="G3396" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3397">
@@ -92149,7 +92149,7 @@
         <v>3</v>
       </c>
       <c r="G3397" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3398">
@@ -92176,7 +92176,7 @@
         <v>3</v>
       </c>
       <c r="G3398" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3399">
@@ -92203,7 +92203,7 @@
         <v>3</v>
       </c>
       <c r="G3399" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3400">
@@ -92230,7 +92230,7 @@
         <v>3</v>
       </c>
       <c r="G3400" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3401">
@@ -92257,7 +92257,7 @@
         <v>3</v>
       </c>
       <c r="G3401" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3402">
@@ -92284,7 +92284,7 @@
         <v>3</v>
       </c>
       <c r="G3402" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3403">
@@ -92311,7 +92311,7 @@
         <v>3</v>
       </c>
       <c r="G3403" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3404">
@@ -92338,7 +92338,7 @@
         <v>3</v>
       </c>
       <c r="G3404" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3405">
@@ -92365,7 +92365,7 @@
         <v>3</v>
       </c>
       <c r="G3405" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3406">
@@ -92392,7 +92392,7 @@
         <v>3</v>
       </c>
       <c r="G3406" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3407">
@@ -92419,7 +92419,7 @@
         <v>3</v>
       </c>
       <c r="G3407" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3408">
@@ -92446,7 +92446,7 @@
         <v>3</v>
       </c>
       <c r="G3408" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3409">
@@ -92473,7 +92473,7 @@
         <v>3</v>
       </c>
       <c r="G3409" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3410">
@@ -92500,7 +92500,7 @@
         <v>3</v>
       </c>
       <c r="G3410" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3411">
@@ -92527,7 +92527,7 @@
         <v>3</v>
       </c>
       <c r="G3411" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3412">
@@ -92554,7 +92554,7 @@
         <v>3</v>
       </c>
       <c r="G3412" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3413">
@@ -92581,7 +92581,7 @@
         <v>3</v>
       </c>
       <c r="G3413" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3414">
@@ -92608,7 +92608,7 @@
         <v>3</v>
       </c>
       <c r="G3414" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3415">
@@ -92635,7 +92635,7 @@
         <v>3</v>
       </c>
       <c r="G3415" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3416">
@@ -92662,7 +92662,7 @@
         <v>3</v>
       </c>
       <c r="G3416" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3417">
@@ -92689,7 +92689,7 @@
         <v>3</v>
       </c>
       <c r="G3417" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3418">
@@ -92716,7 +92716,7 @@
         <v>3</v>
       </c>
       <c r="G3418" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3419">
@@ -92743,7 +92743,7 @@
         <v>3</v>
       </c>
       <c r="G3419" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3420">
@@ -92770,7 +92770,7 @@
         <v>3</v>
       </c>
       <c r="G3420" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3421">
@@ -92797,7 +92797,7 @@
         <v>3</v>
       </c>
       <c r="G3421" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3422">
@@ -92824,7 +92824,7 @@
         <v>3</v>
       </c>
       <c r="G3422" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3423">
@@ -92851,7 +92851,7 @@
         <v>3</v>
       </c>
       <c r="G3423" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3424">
@@ -92878,7 +92878,7 @@
         <v>3</v>
       </c>
       <c r="G3424" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3425">
@@ -92905,7 +92905,7 @@
         <v>3</v>
       </c>
       <c r="G3425" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3426">
@@ -92932,7 +92932,7 @@
         <v>3</v>
       </c>
       <c r="G3426" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3427">
@@ -92959,7 +92959,7 @@
         <v>3</v>
       </c>
       <c r="G3427" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3428">
@@ -92986,7 +92986,7 @@
         <v>3</v>
       </c>
       <c r="G3428" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3429">
@@ -93013,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="G3429" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3430">
@@ -93040,7 +93040,7 @@
         <v>3</v>
       </c>
       <c r="G3430" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3431">
@@ -93067,7 +93067,7 @@
         <v>3</v>
       </c>
       <c r="G3431" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3432">
@@ -93094,7 +93094,7 @@
         <v>3</v>
       </c>
       <c r="G3432" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3433">
@@ -93121,7 +93121,7 @@
         <v>3</v>
       </c>
       <c r="G3433" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3434">
@@ -93148,7 +93148,7 @@
         <v>3</v>
       </c>
       <c r="G3434" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3435">
@@ -93175,7 +93175,7 @@
         <v>3</v>
       </c>
       <c r="G3435" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3436">
@@ -93202,7 +93202,7 @@
         <v>3</v>
       </c>
       <c r="G3436" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3437">
@@ -93229,7 +93229,7 @@
         <v>3</v>
       </c>
       <c r="G3437" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3438">
@@ -93256,7 +93256,7 @@
         <v>3</v>
       </c>
       <c r="G3438" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3439">
@@ -93283,7 +93283,7 @@
         <v>3</v>
       </c>
       <c r="G3439" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3440">
@@ -93310,7 +93310,7 @@
         <v>3</v>
       </c>
       <c r="G3440" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3441">
@@ -93337,7 +93337,7 @@
         <v>3</v>
       </c>
       <c r="G3441" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3442">
@@ -93364,7 +93364,7 @@
         <v>3</v>
       </c>
       <c r="G3442" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3443">
@@ -93391,7 +93391,7 @@
         <v>3</v>
       </c>
       <c r="G3443" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3444">
@@ -93418,7 +93418,7 @@
         <v>3</v>
       </c>
       <c r="G3444" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3445">
@@ -93445,7 +93445,7 @@
         <v>3</v>
       </c>
       <c r="G3445" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3446">
@@ -93472,7 +93472,7 @@
         <v>3</v>
       </c>
       <c r="G3446" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3447">
@@ -93499,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="G3447" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3448">
@@ -93526,7 +93526,7 @@
         <v>3</v>
       </c>
       <c r="G3448" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3449">
@@ -93553,7 +93553,7 @@
         <v>3</v>
       </c>
       <c r="G3449" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3450">
@@ -93580,7 +93580,7 @@
         <v>3</v>
       </c>
       <c r="G3450" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3451">
@@ -93607,7 +93607,7 @@
         <v>3</v>
       </c>
       <c r="G3451" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3452">
@@ -93634,7 +93634,7 @@
         <v>3</v>
       </c>
       <c r="G3452" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3453">
@@ -93661,7 +93661,7 @@
         <v>3</v>
       </c>
       <c r="G3453" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3454">
@@ -93688,7 +93688,7 @@
         <v>3</v>
       </c>
       <c r="G3454" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3455">
@@ -93715,7 +93715,7 @@
         <v>3</v>
       </c>
       <c r="G3455" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3456">
@@ -93742,7 +93742,7 @@
         <v>3</v>
       </c>
       <c r="G3456" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3457">
@@ -93769,7 +93769,7 @@
         <v>3</v>
       </c>
       <c r="G3457" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3458">
@@ -93796,7 +93796,7 @@
         <v>3</v>
       </c>
       <c r="G3458" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3459">
@@ -93823,7 +93823,7 @@
         <v>3</v>
       </c>
       <c r="G3459" s="2" t="n">
-        <v>46293.54374556483</v>
+        <v>46293.95777583749</v>
       </c>
     </row>
     <row r="3460">
@@ -93850,7 +93850,7 @@
         <v>3</v>
       </